--- a/data-source/护甲数据.xlsx
+++ b/data-source/护甲数据.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jasonX\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{398C576B-27A9-43BA-91ED-682F98BCC890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -5090,15 +5090,15 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5425,7 +5425,7 @@
       <c r="D2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="108">
+      <c r="E2" s="112">
         <v>91</v>
       </c>
       <c r="F2" s="11" t="s">
@@ -5517,7 +5517,7 @@
       <c r="D7" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="110"/>
+      <c r="E7" s="111"/>
       <c r="F7" s="19" t="s">
         <v>16</v>
       </c>
@@ -5535,7 +5535,7 @@
       <c r="D8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="111">
+      <c r="E8" s="108">
         <v>91</v>
       </c>
       <c r="F8" s="11" t="s">
@@ -5627,7 +5627,7 @@
       <c r="D13" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="112"/>
+      <c r="E13" s="110"/>
       <c r="F13" s="26" t="s">
         <v>16</v>
       </c>
@@ -5747,7 +5747,7 @@
       <c r="D19" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="110"/>
+      <c r="E19" s="111"/>
       <c r="F19" s="19" t="s">
         <v>34</v>
       </c>
@@ -5770,7 +5770,7 @@
       <c r="D20" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="111">
+      <c r="E20" s="108">
         <v>100</v>
       </c>
       <c r="F20" s="11" t="s">
@@ -5862,7 +5862,7 @@
       <c r="D25" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="110"/>
+      <c r="E25" s="111"/>
       <c r="F25" s="19" t="s">
         <v>34</v>
       </c>
@@ -5880,7 +5880,7 @@
       <c r="D26" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="111">
+      <c r="E26" s="108">
         <v>100</v>
       </c>
       <c r="F26" s="31" t="s">
@@ -5972,7 +5972,7 @@
       <c r="D31" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="112"/>
+      <c r="E31" s="110"/>
       <c r="F31" s="34" t="s">
         <v>34</v>
       </c>
@@ -5990,7 +5990,7 @@
       <c r="D32" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="111">
+      <c r="E32" s="108">
         <v>112</v>
       </c>
       <c r="F32" s="31" t="s">
@@ -6107,7 +6107,7 @@
       <c r="D37" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E37" s="112"/>
+      <c r="E37" s="110"/>
       <c r="F37" s="26" t="s">
         <v>60</v>
       </c>
@@ -6130,7 +6130,7 @@
       <c r="D38" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="111">
+      <c r="E38" s="108">
         <v>100</v>
       </c>
       <c r="F38" s="11" t="s">
@@ -6247,7 +6247,7 @@
       <c r="D43" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E43" s="112"/>
+      <c r="E43" s="110"/>
       <c r="F43" s="26" t="s">
         <v>34</v>
       </c>
@@ -6270,7 +6270,7 @@
       <c r="D44" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E44" s="108">
+      <c r="E44" s="112">
         <v>112</v>
       </c>
       <c r="F44" s="11" t="s">
@@ -6387,7 +6387,7 @@
       <c r="D49" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E49" s="110"/>
+      <c r="E49" s="111"/>
       <c r="F49" s="19" t="s">
         <v>82</v>
       </c>
@@ -6410,7 +6410,7 @@
       <c r="D50" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E50" s="111">
+      <c r="E50" s="108">
         <v>112</v>
       </c>
       <c r="F50" s="15" t="s">
@@ -6502,7 +6502,7 @@
       <c r="D55" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E55" s="110"/>
+      <c r="E55" s="111"/>
       <c r="F55" s="19" t="s">
         <v>82</v>
       </c>
@@ -6520,7 +6520,7 @@
       <c r="D56" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E56" s="111">
+      <c r="E56" s="108">
         <v>112</v>
       </c>
       <c r="F56" s="47" t="s">
@@ -6612,7 +6612,7 @@
       <c r="D61" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E61" s="110"/>
+      <c r="E61" s="111"/>
       <c r="F61" s="53" t="s">
         <v>7</v>
       </c>
@@ -6630,7 +6630,7 @@
       <c r="D62" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E62" s="111">
+      <c r="E62" s="108">
         <v>143</v>
       </c>
       <c r="F62" s="31" t="s">
@@ -6745,7 +6745,7 @@
         <v>12</v>
       </c>
       <c r="D67" s="18"/>
-      <c r="E67" s="110"/>
+      <c r="E67" s="111"/>
       <c r="F67" s="19" t="s">
         <v>111</v>
       </c>
@@ -6768,7 +6768,7 @@
       <c r="D68" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E68" s="111">
+      <c r="E68" s="108">
         <v>143</v>
       </c>
       <c r="F68" s="31" t="s">
@@ -6860,7 +6860,7 @@
       <c r="D73" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E73" s="110"/>
+      <c r="E73" s="111"/>
       <c r="F73" s="57" t="s">
         <v>126</v>
       </c>
@@ -6878,7 +6878,7 @@
       <c r="D74" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E74" s="111">
+      <c r="E74" s="108">
         <v>143</v>
       </c>
       <c r="F74" s="58" t="s">
@@ -6970,7 +6970,7 @@
       <c r="D79" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E79" s="110"/>
+      <c r="E79" s="111"/>
       <c r="F79" s="57" t="s">
         <v>131</v>
       </c>
@@ -6988,7 +6988,7 @@
       <c r="D80" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E80" s="111">
+      <c r="E80" s="108">
         <v>112</v>
       </c>
       <c r="F80" s="11" t="s">
@@ -7105,7 +7105,7 @@
       <c r="D85" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E85" s="112"/>
+      <c r="E85" s="110"/>
       <c r="F85" s="26" t="s">
         <v>147</v>
       </c>
@@ -7128,7 +7128,7 @@
       <c r="D86" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E86" s="108">
+      <c r="E86" s="112">
         <v>125</v>
       </c>
       <c r="F86" s="11" t="s">
@@ -7245,7 +7245,7 @@
       <c r="D91" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E91" s="110"/>
+      <c r="E91" s="111"/>
       <c r="F91" s="19" t="s">
         <v>159</v>
       </c>
@@ -7268,7 +7268,7 @@
       <c r="D92" s="62" t="s">
         <v>161</v>
       </c>
-      <c r="E92" s="111">
+      <c r="E92" s="108">
         <v>125</v>
       </c>
       <c r="F92" s="47" t="s">
@@ -7360,7 +7360,7 @@
       <c r="D97" s="65" t="s">
         <v>165</v>
       </c>
-      <c r="E97" s="110"/>
+      <c r="E97" s="111"/>
       <c r="F97" s="53" t="s">
         <v>162</v>
       </c>
@@ -7378,7 +7378,7 @@
       <c r="D98" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E98" s="111">
+      <c r="E98" s="108">
         <v>125</v>
       </c>
       <c r="F98" s="58" t="s">
@@ -7470,7 +7470,7 @@
       <c r="D103" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E103" s="110"/>
+      <c r="E103" s="111"/>
       <c r="F103" s="57" t="s">
         <v>184</v>
       </c>
@@ -7488,7 +7488,7 @@
       <c r="D104" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E104" s="111">
+      <c r="E104" s="108">
         <v>125</v>
       </c>
       <c r="F104" s="31" t="s">
@@ -7580,7 +7580,7 @@
       <c r="D109" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E109" s="112"/>
+      <c r="E109" s="110"/>
       <c r="F109" s="34" t="s">
         <v>159</v>
       </c>
@@ -7598,7 +7598,7 @@
       <c r="D110" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E110" s="111">
+      <c r="E110" s="108">
         <v>143</v>
       </c>
       <c r="F110" s="31" t="s">
@@ -7690,7 +7690,7 @@
       <c r="D115" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E115" s="112"/>
+      <c r="E115" s="110"/>
       <c r="F115" s="26" t="s">
         <v>205</v>
       </c>
@@ -7708,7 +7708,7 @@
       <c r="D116" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E116" s="111">
+      <c r="E116" s="108">
         <v>125</v>
       </c>
       <c r="F116" s="72" t="s">
@@ -7825,7 +7825,7 @@
       <c r="D121" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E121" s="112"/>
+      <c r="E121" s="110"/>
       <c r="F121" s="73" t="s">
         <v>218</v>
       </c>
@@ -7849,7 +7849,7 @@
       <c r="D122" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E122" s="111">
+      <c r="E122" s="108">
         <v>143</v>
       </c>
       <c r="F122" s="72" t="s">
@@ -7966,7 +7966,7 @@
       <c r="D127" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E127" s="112"/>
+      <c r="E127" s="110"/>
       <c r="F127" s="73" t="s">
         <v>232</v>
       </c>
@@ -8081,7 +8081,7 @@
       <c r="D133" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E133" s="110"/>
+      <c r="E133" s="111"/>
       <c r="F133" s="19" t="s">
         <v>245</v>
       </c>
@@ -8099,7 +8099,7 @@
       <c r="D134" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E134" s="111">
+      <c r="E134" s="108">
         <v>143</v>
       </c>
       <c r="F134" s="31" t="s">
@@ -8216,7 +8216,7 @@
       <c r="D139" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E139" s="110"/>
+      <c r="E139" s="111"/>
       <c r="F139" s="19" t="s">
         <v>245</v>
       </c>
@@ -8239,7 +8239,7 @@
       <c r="D140" s="79" t="s">
         <v>258</v>
       </c>
-      <c r="E140" s="111">
+      <c r="E140" s="108">
         <v>143</v>
       </c>
       <c r="F140" s="47" t="s">
@@ -8331,7 +8331,7 @@
       <c r="D145" s="81" t="s">
         <v>261</v>
       </c>
-      <c r="E145" s="110"/>
+      <c r="E145" s="111"/>
       <c r="F145" s="53" t="s">
         <v>162</v>
       </c>
@@ -8349,7 +8349,7 @@
       <c r="D146" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E146" s="111">
+      <c r="E146" s="108">
         <v>167</v>
       </c>
       <c r="F146" s="31" t="s">
@@ -8441,7 +8441,7 @@
       <c r="D151" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E151" s="110"/>
+      <c r="E151" s="111"/>
       <c r="F151" s="19" t="s">
         <v>276</v>
       </c>
@@ -8459,7 +8459,7 @@
       <c r="D152" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E152" s="111">
+      <c r="E152" s="108">
         <v>125</v>
       </c>
       <c r="F152" s="58" t="s">
@@ -8551,7 +8551,7 @@
       <c r="D157" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E157" s="110"/>
+      <c r="E157" s="111"/>
       <c r="F157" s="57" t="s">
         <v>289</v>
       </c>
@@ -8569,7 +8569,7 @@
       <c r="D158" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E158" s="108">
+      <c r="E158" s="112">
         <v>200</v>
       </c>
       <c r="F158" s="50" t="s">
@@ -8686,7 +8686,7 @@
       <c r="D163" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E163" s="112"/>
+      <c r="E163" s="110"/>
       <c r="F163" s="50" t="s">
         <v>7</v>
       </c>
@@ -8709,7 +8709,7 @@
       <c r="D164" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E164" s="111">
+      <c r="E164" s="108">
         <v>125</v>
       </c>
       <c r="F164" s="58" t="s">
@@ -8801,7 +8801,7 @@
       <c r="D169" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E169" s="110"/>
+      <c r="E169" s="111"/>
       <c r="F169" s="88" t="s">
         <v>313</v>
       </c>
@@ -8936,7 +8936,7 @@
       <c r="D175" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E175" s="110"/>
+      <c r="E175" s="111"/>
       <c r="F175" s="19" t="s">
         <v>322</v>
       </c>
@@ -8959,7 +8959,7 @@
       <c r="D176" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E176" s="111">
+      <c r="E176" s="108">
         <v>167</v>
       </c>
       <c r="F176" s="50" t="s">
@@ -9076,7 +9076,7 @@
       <c r="D181" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E181" s="112"/>
+      <c r="E181" s="110"/>
       <c r="F181" s="89" t="s">
         <v>7</v>
       </c>
@@ -9099,7 +9099,7 @@
       <c r="D182" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E182" s="111">
+      <c r="E182" s="108">
         <v>143</v>
       </c>
       <c r="F182" s="72" t="s">
@@ -9206,7 +9206,7 @@
       <c r="D187" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E187" s="112"/>
+      <c r="E187" s="110"/>
       <c r="F187" s="89" t="s">
         <v>7</v>
       </c>
@@ -9230,7 +9230,7 @@
       <c r="D188" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E188" s="111">
+      <c r="E188" s="108">
         <v>233</v>
       </c>
       <c r="F188" s="72"/>
@@ -9335,7 +9335,7 @@
       <c r="D193" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E193" s="112"/>
+      <c r="E193" s="110"/>
       <c r="F193" s="89"/>
       <c r="G193" s="90" t="s">
         <v>326</v>
@@ -14471,6 +14471,31 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="32">
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="E8:E13"/>
+    <mergeCell ref="E14:E19"/>
+    <mergeCell ref="E20:E25"/>
+    <mergeCell ref="E26:E31"/>
+    <mergeCell ref="E32:E37"/>
+    <mergeCell ref="E38:E43"/>
+    <mergeCell ref="E44:E49"/>
+    <mergeCell ref="E50:E55"/>
+    <mergeCell ref="E56:E61"/>
+    <mergeCell ref="E62:E67"/>
+    <mergeCell ref="E68:E73"/>
+    <mergeCell ref="E74:E79"/>
+    <mergeCell ref="E80:E85"/>
+    <mergeCell ref="E86:E91"/>
+    <mergeCell ref="E92:E97"/>
+    <mergeCell ref="E98:E103"/>
+    <mergeCell ref="E104:E109"/>
+    <mergeCell ref="E110:E115"/>
+    <mergeCell ref="E116:E121"/>
+    <mergeCell ref="E122:E127"/>
+    <mergeCell ref="E128:E133"/>
+    <mergeCell ref="E134:E139"/>
+    <mergeCell ref="E140:E145"/>
+    <mergeCell ref="E146:E151"/>
     <mergeCell ref="E182:E187"/>
     <mergeCell ref="E188:E193"/>
     <mergeCell ref="E152:E157"/>
@@ -14478,31 +14503,6 @@
     <mergeCell ref="E164:E169"/>
     <mergeCell ref="E170:E175"/>
     <mergeCell ref="E176:E181"/>
-    <mergeCell ref="E122:E127"/>
-    <mergeCell ref="E128:E133"/>
-    <mergeCell ref="E134:E139"/>
-    <mergeCell ref="E140:E145"/>
-    <mergeCell ref="E146:E151"/>
-    <mergeCell ref="E92:E97"/>
-    <mergeCell ref="E98:E103"/>
-    <mergeCell ref="E104:E109"/>
-    <mergeCell ref="E110:E115"/>
-    <mergeCell ref="E116:E121"/>
-    <mergeCell ref="E62:E67"/>
-    <mergeCell ref="E68:E73"/>
-    <mergeCell ref="E74:E79"/>
-    <mergeCell ref="E80:E85"/>
-    <mergeCell ref="E86:E91"/>
-    <mergeCell ref="E32:E37"/>
-    <mergeCell ref="E38:E43"/>
-    <mergeCell ref="E44:E49"/>
-    <mergeCell ref="E50:E55"/>
-    <mergeCell ref="E56:E61"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="E8:E13"/>
-    <mergeCell ref="E14:E19"/>
-    <mergeCell ref="E20:E25"/>
-    <mergeCell ref="E26:E31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data-source/护甲数据.xlsx
+++ b/data-source/护甲数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F0F9EA0-009A-470C-8B73-68E5889A4FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7022E2C6-D5C7-42B2-BA3D-BC2D64BEEFF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -876,9 +876,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">玄鳞套装（T5+级）  </t>
-  </si>
-  <si>
     <t>提升耐久度</t>
   </si>
   <si>
@@ -1844,9 +1841,6 @@
     <t>冰霜靴子</t>
   </si>
   <si>
-    <t xml:space="preserve">决斗者套装（T5+级）  </t>
-  </si>
-  <si>
     <t xml:space="preserve">决斗者战盔  </t>
   </si>
   <si>
@@ -2350,6 +2344,12 @@
   </si>
   <si>
     <t>哈利德，古墓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">决斗者套装（T5级）  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">玄鳞套装（T5级）  </t>
   </si>
 </sst>
 </file>
@@ -3709,12 +3709,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3727,21 +3727,21 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4057,7 +4057,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
@@ -4070,22 +4070,22 @@
       <c r="D2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="148">
+      <c r="E2" s="149">
         <v>91</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="133" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="15.75" customHeight="1">
       <c r="B3" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C3" s="14">
         <v>10</v>
@@ -4093,7 +4093,7 @@
       <c r="D3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="142"/>
+      <c r="E3" s="145"/>
       <c r="F3" s="15" t="s">
         <v>8</v>
       </c>
@@ -4104,7 +4104,7 @@
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1">
       <c r="B4" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C4" s="14">
         <v>25</v>
@@ -4112,9 +4112,9 @@
       <c r="D4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="142"/>
+      <c r="E4" s="145"/>
       <c r="F4" s="15" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>7</v>
@@ -4123,7 +4123,7 @@
     </row>
     <row r="5" spans="2:8" ht="15.75" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C5" s="14">
         <v>10</v>
@@ -4131,7 +4131,7 @@
       <c r="D5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="142"/>
+      <c r="E5" s="145"/>
       <c r="F5" s="15" t="s">
         <v>8</v>
       </c>
@@ -4142,7 +4142,7 @@
     </row>
     <row r="6" spans="2:8" ht="15.75" customHeight="1">
       <c r="B6" s="13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C6" s="14">
         <v>25</v>
@@ -4150,9 +4150,9 @@
       <c r="D6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="142"/>
+      <c r="E6" s="145"/>
       <c r="F6" s="15" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>7</v>
@@ -4161,7 +4161,7 @@
     </row>
     <row r="7" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B7" s="16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C7" s="17">
         <v>0</v>
@@ -4169,14 +4169,14 @@
       <c r="D7" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="143"/>
+      <c r="E7" s="148"/>
       <c r="F7" s="19" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="135"/>
+      <c r="H7" s="136"/>
     </row>
     <row r="8" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B8" s="21" t="s">
@@ -4188,17 +4188,17 @@
       <c r="D8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="141">
+      <c r="E8" s="144">
         <v>91</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H8" s="133" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15.75" customHeight="1">
@@ -4211,7 +4211,7 @@
       <c r="D9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="142"/>
+      <c r="E9" s="145"/>
       <c r="F9" s="15" t="s">
         <v>8</v>
       </c>
@@ -4230,9 +4230,9 @@
       <c r="D10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="142"/>
+      <c r="E10" s="145"/>
       <c r="F10" s="15" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>7</v>
@@ -4249,7 +4249,7 @@
       <c r="D11" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="142"/>
+      <c r="E11" s="145"/>
       <c r="F11" s="15" t="s">
         <v>8</v>
       </c>
@@ -4260,7 +4260,7 @@
     </row>
     <row r="12" spans="2:8" ht="15.75" customHeight="1">
       <c r="B12" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C12" s="14">
         <v>25</v>
@@ -4268,9 +4268,9 @@
       <c r="D12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="142"/>
+      <c r="E12" s="145"/>
       <c r="F12" s="15" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>7</v>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="13" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B13" s="23" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C13" s="24">
         <v>0</v>
@@ -4287,14 +4287,14 @@
       <c r="D13" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="147"/>
+      <c r="E13" s="146"/>
       <c r="F13" s="26" t="s">
         <v>9</v>
       </c>
       <c r="G13" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="135"/>
+      <c r="H13" s="136"/>
     </row>
     <row r="14" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B14" s="8" t="s">
@@ -4306,22 +4306,22 @@
       <c r="D14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="149">
+      <c r="E14" s="147">
         <v>100</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H14" s="133" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15.75" customHeight="1">
       <c r="B15" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C15" s="14">
         <v>30</v>
@@ -4329,9 +4329,9 @@
       <c r="D15" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="142"/>
+      <c r="E15" s="145"/>
       <c r="F15" s="15" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>7</v>
@@ -4340,7 +4340,7 @@
     </row>
     <row r="16" spans="2:8" ht="15.75" customHeight="1">
       <c r="B16" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C16" s="14">
         <v>50</v>
@@ -4348,9 +4348,9 @@
       <c r="D16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="142"/>
+      <c r="E16" s="145"/>
       <c r="F16" s="15" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>7</v>
@@ -4367,9 +4367,9 @@
       <c r="D17" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="142"/>
+      <c r="E17" s="145"/>
       <c r="F17" s="15" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>7</v>
@@ -4382,7 +4382,7 @@
     </row>
     <row r="18" spans="2:12" ht="15.75" customHeight="1">
       <c r="B18" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C18" s="14">
         <v>50</v>
@@ -4390,9 +4390,9 @@
       <c r="D18" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="142"/>
+      <c r="E18" s="145"/>
       <c r="F18" s="15" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>7</v>
@@ -4405,7 +4405,7 @@
     </row>
     <row r="19" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B19" s="16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C19" s="17">
         <v>0</v>
@@ -4413,14 +4413,14 @@
       <c r="D19" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="143"/>
+      <c r="E19" s="148"/>
       <c r="F19" s="19" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="135"/>
+      <c r="H19" s="136"/>
       <c r="I19" s="29"/>
       <c r="J19" s="29"/>
       <c r="K19" s="29"/>
@@ -4436,22 +4436,22 @@
       <c r="D20" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="141">
+      <c r="E20" s="144">
         <v>100</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G20" s="30" t="s">
         <v>7</v>
       </c>
       <c r="H20" s="133" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="15.75" customHeight="1">
       <c r="B21" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C21" s="14">
         <v>30</v>
@@ -4459,9 +4459,9 @@
       <c r="D21" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="142"/>
+      <c r="E21" s="145"/>
       <c r="F21" s="15" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>7</v>
@@ -4470,7 +4470,7 @@
     </row>
     <row r="22" spans="2:12" ht="15.75" customHeight="1">
       <c r="B22" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C22" s="14">
         <v>50</v>
@@ -4478,9 +4478,9 @@
       <c r="D22" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="142"/>
+      <c r="E22" s="145"/>
       <c r="F22" s="15" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>7</v>
@@ -4497,9 +4497,9 @@
       <c r="D23" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="142"/>
+      <c r="E23" s="145"/>
       <c r="F23" s="15" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>7</v>
@@ -4508,7 +4508,7 @@
     </row>
     <row r="24" spans="2:12" ht="15.75" customHeight="1">
       <c r="B24" s="13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C24" s="14">
         <v>50</v>
@@ -4516,9 +4516,9 @@
       <c r="D24" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="142"/>
+      <c r="E24" s="145"/>
       <c r="F24" s="15" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>7</v>
@@ -4527,7 +4527,7 @@
     </row>
     <row r="25" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B25" s="107" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C25" s="17">
         <v>0</v>
@@ -4535,14 +4535,14 @@
       <c r="D25" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="143"/>
+      <c r="E25" s="148"/>
       <c r="F25" s="19" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H25" s="135"/>
+      <c r="H25" s="136"/>
     </row>
     <row r="26" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B26" s="21" t="s">
@@ -4554,22 +4554,22 @@
       <c r="D26" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="141">
+      <c r="E26" s="144">
         <v>100</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G26" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H26" s="133" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="27" spans="2:12" ht="15.75" customHeight="1">
       <c r="B27" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C27" s="14">
         <v>30</v>
@@ -4577,9 +4577,9 @@
       <c r="D27" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="142"/>
+      <c r="E27" s="145"/>
       <c r="F27" s="15" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G27" s="12" t="s">
         <v>7</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="28" spans="2:12" ht="15.75" customHeight="1">
       <c r="B28" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C28" s="14">
         <v>50</v>
@@ -4596,9 +4596,9 @@
       <c r="D28" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="142"/>
+      <c r="E28" s="145"/>
       <c r="F28" s="15" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>7</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="29" spans="2:12" ht="15.75" customHeight="1">
       <c r="B29" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C29" s="14">
         <v>20</v>
@@ -4615,9 +4615,9 @@
       <c r="D29" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="142"/>
+      <c r="E29" s="145"/>
       <c r="F29" s="15" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G29" s="12" t="s">
         <v>7</v>
@@ -4626,7 +4626,7 @@
     </row>
     <row r="30" spans="2:12" ht="15.75" customHeight="1">
       <c r="B30" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C30" s="14">
         <v>50</v>
@@ -4634,9 +4634,9 @@
       <c r="D30" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="142"/>
+      <c r="E30" s="145"/>
       <c r="F30" s="15" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>7</v>
@@ -4645,7 +4645,7 @@
     </row>
     <row r="31" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B31" s="32" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C31" s="33">
         <v>0</v>
@@ -4653,14 +4653,14 @@
       <c r="D31" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="147"/>
+      <c r="E31" s="146"/>
       <c r="F31" s="34" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H31" s="135"/>
+      <c r="H31" s="136"/>
     </row>
     <row r="32" spans="2:12" ht="25.9" thickTop="1">
       <c r="B32" s="36" t="s">
@@ -4672,17 +4672,17 @@
       <c r="D32" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="141">
+      <c r="E32" s="144">
         <v>112</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G32" s="37" t="s">
         <v>22</v>
       </c>
       <c r="H32" s="133" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -4691,7 +4691,7 @@
     </row>
     <row r="33" spans="2:12" ht="15.75" customHeight="1">
       <c r="B33" s="87" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C33" s="14">
         <v>40</v>
@@ -4699,9 +4699,9 @@
       <c r="D33" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="142"/>
+      <c r="E33" s="145"/>
       <c r="F33" s="15" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>7</v>
@@ -4722,9 +4722,9 @@
       <c r="D34" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="142"/>
+      <c r="E34" s="145"/>
       <c r="F34" s="15" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>7</v>
@@ -4737,7 +4737,7 @@
     </row>
     <row r="35" spans="2:12" ht="15.75" customHeight="1">
       <c r="B35" s="38" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C35" s="14">
         <v>30</v>
@@ -4745,9 +4745,9 @@
       <c r="D35" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="142"/>
+      <c r="E35" s="145"/>
       <c r="F35" s="15" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>7</v>
@@ -4760,7 +4760,7 @@
     </row>
     <row r="36" spans="2:12" ht="15.75" customHeight="1">
       <c r="B36" s="87" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C36" s="14">
         <v>60</v>
@@ -4768,9 +4768,9 @@
       <c r="D36" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="142"/>
+      <c r="E36" s="145"/>
       <c r="F36" s="15" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>7</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="37" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B37" s="108" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C37" s="24">
         <v>10</v>
@@ -4791,14 +4791,14 @@
       <c r="D37" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E37" s="147"/>
+      <c r="E37" s="146"/>
       <c r="F37" s="26" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G37" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="H37" s="135"/>
+      <c r="H37" s="136"/>
       <c r="I37" s="29"/>
       <c r="J37" s="29"/>
       <c r="K37" s="29"/>
@@ -4814,17 +4814,17 @@
       <c r="D38" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="141">
+      <c r="E38" s="144">
         <v>100</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G38" s="41" t="s">
         <v>26</v>
       </c>
       <c r="H38" s="133" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="I38" s="29"/>
       <c r="J38" s="29"/>
@@ -4841,9 +4841,9 @@
       <c r="D39" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E39" s="142"/>
+      <c r="E39" s="145"/>
       <c r="F39" s="15" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>28</v>
@@ -4864,9 +4864,9 @@
       <c r="D40" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E40" s="142"/>
+      <c r="E40" s="145"/>
       <c r="F40" s="15" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G40" s="12" t="s">
         <v>28</v>
@@ -4887,9 +4887,9 @@
       <c r="D41" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E41" s="142"/>
+      <c r="E41" s="145"/>
       <c r="F41" s="15" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G41" s="12" t="s">
         <v>28</v>
@@ -4902,7 +4902,7 @@
     </row>
     <row r="42" spans="2:12" ht="15.75" customHeight="1">
       <c r="B42" s="44" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C42" s="14">
         <v>50</v>
@@ -4910,9 +4910,9 @@
       <c r="D42" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E42" s="142"/>
+      <c r="E42" s="145"/>
       <c r="F42" s="15" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G42" s="12" t="s">
         <v>28</v>
@@ -4925,7 +4925,7 @@
     </row>
     <row r="43" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B43" s="45" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C43" s="24">
         <v>0</v>
@@ -4933,14 +4933,14 @@
       <c r="D43" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E43" s="147"/>
+      <c r="E43" s="146"/>
       <c r="F43" s="26" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G43" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="H43" s="135"/>
+      <c r="H43" s="136"/>
       <c r="I43" s="29"/>
       <c r="J43" s="29"/>
       <c r="K43" s="29"/>
@@ -4956,17 +4956,17 @@
       <c r="D44" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E44" s="148">
+      <c r="E44" s="149">
         <v>112</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G44" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H44" s="133" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I44" s="29"/>
       <c r="J44" s="29"/>
@@ -4975,7 +4975,7 @@
     </row>
     <row r="45" spans="2:12" ht="15.75" customHeight="1">
       <c r="B45" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C45" s="14">
         <v>50</v>
@@ -4983,7 +4983,7 @@
       <c r="D45" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E45" s="142"/>
+      <c r="E45" s="145"/>
       <c r="F45" s="15" t="s">
         <v>33</v>
       </c>
@@ -4998,7 +4998,7 @@
     </row>
     <row r="46" spans="2:12" ht="15.75" customHeight="1">
       <c r="B46" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C46" s="14">
         <v>90</v>
@@ -5006,7 +5006,7 @@
       <c r="D46" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E46" s="142"/>
+      <c r="E46" s="145"/>
       <c r="F46" s="15" t="s">
         <v>34</v>
       </c>
@@ -5021,7 +5021,7 @@
     </row>
     <row r="47" spans="2:12" ht="15.75" customHeight="1">
       <c r="B47" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C47" s="14">
         <v>30</v>
@@ -5029,7 +5029,7 @@
       <c r="D47" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E47" s="142"/>
+      <c r="E47" s="145"/>
       <c r="F47" s="15" t="s">
         <v>35</v>
       </c>
@@ -5044,7 +5044,7 @@
     </row>
     <row r="48" spans="2:12" ht="15.75" customHeight="1">
       <c r="B48" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C48" s="14">
         <v>80</v>
@@ -5052,7 +5052,7 @@
       <c r="D48" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E48" s="142"/>
+      <c r="E48" s="145"/>
       <c r="F48" s="15" t="s">
         <v>36</v>
       </c>
@@ -5067,7 +5067,7 @@
     </row>
     <row r="49" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B49" s="16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C49" s="17">
         <v>10</v>
@@ -5075,14 +5075,14 @@
       <c r="D49" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E49" s="143"/>
+      <c r="E49" s="148"/>
       <c r="F49" s="19" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G49" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H49" s="135"/>
+      <c r="H49" s="136"/>
       <c r="I49" s="29"/>
       <c r="J49" s="29"/>
       <c r="K49" s="29"/>
@@ -5098,17 +5098,17 @@
       <c r="D50" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E50" s="141">
+      <c r="E50" s="144">
         <v>112</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G50" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H50" s="133" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="51" spans="2:12" ht="15.75" customHeight="1">
@@ -5121,7 +5121,7 @@
       <c r="D51" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E51" s="142"/>
+      <c r="E51" s="145"/>
       <c r="F51" s="15" t="s">
         <v>33</v>
       </c>
@@ -5132,7 +5132,7 @@
     </row>
     <row r="52" spans="2:12" ht="15.75" customHeight="1">
       <c r="B52" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C52" s="14">
         <v>90</v>
@@ -5140,7 +5140,7 @@
       <c r="D52" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E52" s="142"/>
+      <c r="E52" s="145"/>
       <c r="F52" s="15" t="s">
         <v>34</v>
       </c>
@@ -5151,7 +5151,7 @@
     </row>
     <row r="53" spans="2:12" ht="15.75" customHeight="1">
       <c r="B53" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C53" s="14">
         <v>30</v>
@@ -5159,7 +5159,7 @@
       <c r="D53" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E53" s="142"/>
+      <c r="E53" s="145"/>
       <c r="F53" s="15" t="s">
         <v>35</v>
       </c>
@@ -5170,7 +5170,7 @@
     </row>
     <row r="54" spans="2:12" ht="15.75" customHeight="1">
       <c r="B54" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C54" s="14">
         <v>80</v>
@@ -5178,7 +5178,7 @@
       <c r="D54" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E54" s="142"/>
+      <c r="E54" s="145"/>
       <c r="F54" s="15" t="s">
         <v>36</v>
       </c>
@@ -5189,7 +5189,7 @@
     </row>
     <row r="55" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B55" s="16" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C55" s="17">
         <v>10</v>
@@ -5197,14 +5197,14 @@
       <c r="D55" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E55" s="143"/>
+      <c r="E55" s="148"/>
       <c r="F55" s="19" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G55" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H55" s="135"/>
+      <c r="H55" s="136"/>
     </row>
     <row r="56" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B56" s="36" t="s">
@@ -5214,9 +5214,9 @@
         <v>260</v>
       </c>
       <c r="D56" s="63" t="s">
-        <v>183</v>
-      </c>
-      <c r="E56" s="141">
+        <v>182</v>
+      </c>
+      <c r="E56" s="144">
         <v>112</v>
       </c>
       <c r="F56" s="47" t="s">
@@ -5226,20 +5226,20 @@
         <v>41</v>
       </c>
       <c r="H56" s="133" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="57" spans="2:12" ht="15.75" customHeight="1">
       <c r="B57" s="38" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C57" s="49">
         <v>50</v>
       </c>
       <c r="D57" s="63" t="s">
-        <v>181</v>
-      </c>
-      <c r="E57" s="142"/>
+        <v>180</v>
+      </c>
+      <c r="E57" s="145"/>
       <c r="F57" s="50" t="s">
         <v>7</v>
       </c>
@@ -5250,15 +5250,15 @@
     </row>
     <row r="58" spans="2:12" ht="15.75" customHeight="1">
       <c r="B58" s="38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C58" s="49">
         <v>90</v>
       </c>
       <c r="D58" s="63" t="s">
-        <v>182</v>
-      </c>
-      <c r="E58" s="142"/>
+        <v>181</v>
+      </c>
+      <c r="E58" s="145"/>
       <c r="F58" s="50" t="s">
         <v>7</v>
       </c>
@@ -5269,15 +5269,15 @@
     </row>
     <row r="59" spans="2:12" ht="15.75" customHeight="1">
       <c r="B59" s="38" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C59" s="49">
         <v>30</v>
       </c>
       <c r="D59" s="63" t="s">
-        <v>181</v>
-      </c>
-      <c r="E59" s="142"/>
+        <v>180</v>
+      </c>
+      <c r="E59" s="145"/>
       <c r="F59" s="50" t="s">
         <v>7</v>
       </c>
@@ -5288,15 +5288,15 @@
     </row>
     <row r="60" spans="2:12" ht="15.75" customHeight="1">
       <c r="B60" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C60" s="49">
         <v>80</v>
       </c>
       <c r="D60" s="63" t="s">
-        <v>182</v>
-      </c>
-      <c r="E60" s="142"/>
+        <v>181</v>
+      </c>
+      <c r="E60" s="145"/>
       <c r="F60" s="50" t="s">
         <v>7</v>
       </c>
@@ -5307,22 +5307,22 @@
     </row>
     <row r="61" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B61" s="51" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C61" s="52">
         <v>10</v>
       </c>
       <c r="D61" s="63" t="s">
-        <v>181</v>
-      </c>
-      <c r="E61" s="143"/>
+        <v>180</v>
+      </c>
+      <c r="E61" s="148"/>
       <c r="F61" s="53" t="s">
         <v>7</v>
       </c>
       <c r="G61" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H61" s="135"/>
+      <c r="H61" s="136"/>
     </row>
     <row r="62" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B62" s="36" t="s">
@@ -5334,17 +5334,17 @@
       <c r="D62" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E62" s="141">
+      <c r="E62" s="144">
         <v>143</v>
       </c>
       <c r="F62" s="31" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G62" s="48" t="s">
         <v>43</v>
       </c>
       <c r="H62" s="133" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="I62" s="29"/>
       <c r="J62" s="29"/>
@@ -5353,7 +5353,7 @@
     </row>
     <row r="63" spans="2:12" ht="15.75" customHeight="1">
       <c r="B63" s="38" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C63" s="14">
         <v>60</v>
@@ -5361,9 +5361,9 @@
       <c r="D63" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E63" s="142"/>
+      <c r="E63" s="145"/>
       <c r="F63" s="15" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G63" s="54" t="s">
         <v>44</v>
@@ -5376,7 +5376,7 @@
     </row>
     <row r="64" spans="2:12" ht="15.75" customHeight="1">
       <c r="B64" s="38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C64" s="14">
         <v>110</v>
@@ -5384,9 +5384,9 @@
       <c r="D64" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E64" s="142"/>
+      <c r="E64" s="145"/>
       <c r="F64" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G64" s="55" t="s">
         <v>45</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="65" spans="2:12" ht="15.75" customHeight="1">
       <c r="B65" s="38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C65" s="14">
         <v>35</v>
@@ -5407,9 +5407,9 @@
       <c r="D65" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E65" s="142"/>
+      <c r="E65" s="145"/>
       <c r="F65" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G65" s="12" t="s">
         <v>7</v>
@@ -5422,7 +5422,7 @@
     </row>
     <row r="66" spans="2:12" ht="15.75" customHeight="1">
       <c r="B66" s="38" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C66" s="14">
         <v>95</v>
@@ -5430,9 +5430,9 @@
       <c r="D66" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E66" s="142"/>
+      <c r="E66" s="145"/>
       <c r="F66" s="15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G66" s="12" t="s">
         <v>7</v>
@@ -5445,20 +5445,20 @@
     </row>
     <row r="67" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B67" s="51" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C67" s="17">
         <v>12</v>
       </c>
       <c r="D67" s="18"/>
-      <c r="E67" s="143"/>
+      <c r="E67" s="148"/>
       <c r="F67" s="19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G67" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H67" s="135"/>
+      <c r="H67" s="136"/>
       <c r="I67" s="29"/>
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
@@ -5474,17 +5474,17 @@
       <c r="D68" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E68" s="141">
+      <c r="E68" s="144">
         <v>143</v>
       </c>
       <c r="F68" s="31" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G68" s="37" t="s">
         <v>48</v>
       </c>
       <c r="H68" s="133" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="69" spans="2:12" ht="15.75" customHeight="1">
@@ -5497,9 +5497,9 @@
       <c r="D69" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E69" s="142"/>
+      <c r="E69" s="145"/>
       <c r="F69" s="56" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G69" s="55" t="s">
         <v>50</v>
@@ -5508,7 +5508,7 @@
     </row>
     <row r="70" spans="2:12" ht="15.75" customHeight="1">
       <c r="B70" s="38" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C70" s="14">
         <v>110</v>
@@ -5516,9 +5516,9 @@
       <c r="D70" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E70" s="142"/>
+      <c r="E70" s="145"/>
       <c r="F70" s="15" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G70" s="54" t="s">
         <v>45</v>
@@ -5527,7 +5527,7 @@
     </row>
     <row r="71" spans="2:12" ht="15.75" customHeight="1">
       <c r="B71" s="38" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C71" s="14">
         <v>35</v>
@@ -5535,9 +5535,9 @@
       <c r="D71" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E71" s="142"/>
+      <c r="E71" s="145"/>
       <c r="F71" s="56" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G71" s="12" t="s">
         <v>7</v>
@@ -5546,7 +5546,7 @@
     </row>
     <row r="72" spans="2:12" ht="15.75" customHeight="1">
       <c r="B72" s="38" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C72" s="14">
         <v>95</v>
@@ -5554,9 +5554,9 @@
       <c r="D72" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E72" s="142"/>
+      <c r="E72" s="145"/>
       <c r="F72" s="15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G72" s="12" t="s">
         <v>7</v>
@@ -5565,7 +5565,7 @@
     </row>
     <row r="73" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B73" s="51" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C73" s="17">
         <v>12</v>
@@ -5573,14 +5573,14 @@
       <c r="D73" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E73" s="143"/>
+      <c r="E73" s="148"/>
       <c r="F73" s="57" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G73" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H73" s="135"/>
+      <c r="H73" s="136"/>
     </row>
     <row r="74" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B74" s="36" t="s">
@@ -5592,22 +5592,22 @@
       <c r="D74" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E74" s="141">
+      <c r="E74" s="144">
         <v>143</v>
       </c>
       <c r="F74" s="58" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G74" s="37" t="s">
         <v>52</v>
       </c>
       <c r="H74" s="133" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="75" spans="2:12" ht="15.75" customHeight="1">
       <c r="B75" s="38" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C75" s="49">
         <v>70</v>
@@ -5615,9 +5615,9 @@
       <c r="D75" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E75" s="142"/>
+      <c r="E75" s="145"/>
       <c r="F75" s="56" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G75" s="54" t="s">
         <v>53</v>
@@ -5626,7 +5626,7 @@
     </row>
     <row r="76" spans="2:12" ht="15.75" customHeight="1">
       <c r="B76" s="38" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C76" s="49">
         <v>110</v>
@@ -5634,9 +5634,9 @@
       <c r="D76" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E76" s="142"/>
+      <c r="E76" s="145"/>
       <c r="F76" s="56" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G76" s="55" t="s">
         <v>45</v>
@@ -5645,7 +5645,7 @@
     </row>
     <row r="77" spans="2:12" ht="15.75" customHeight="1">
       <c r="B77" s="38" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C77" s="49">
         <v>35</v>
@@ -5653,9 +5653,9 @@
       <c r="D77" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E77" s="142"/>
+      <c r="E77" s="145"/>
       <c r="F77" s="56" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G77" s="12" t="s">
         <v>7</v>
@@ -5664,7 +5664,7 @@
     </row>
     <row r="78" spans="2:12" ht="15.75" customHeight="1">
       <c r="B78" s="38" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C78" s="49">
         <v>95</v>
@@ -5672,9 +5672,9 @@
       <c r="D78" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E78" s="142"/>
+      <c r="E78" s="145"/>
       <c r="F78" s="56" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G78" s="12" t="s">
         <v>7</v>
@@ -5683,7 +5683,7 @@
     </row>
     <row r="79" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B79" s="51" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C79" s="52">
         <v>12</v>
@@ -5691,14 +5691,14 @@
       <c r="D79" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E79" s="143"/>
+      <c r="E79" s="148"/>
       <c r="F79" s="57" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G79" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H79" s="135"/>
+      <c r="H79" s="136"/>
     </row>
     <row r="80" spans="2:12" ht="38.65" thickTop="1">
       <c r="B80" s="40" t="s">
@@ -5710,17 +5710,17 @@
       <c r="D80" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E80" s="141">
+      <c r="E80" s="144">
         <v>112</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G80" s="59" t="s">
         <v>55</v>
       </c>
       <c r="H80" s="133" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="I80" s="29"/>
       <c r="J80" s="29"/>
@@ -5729,7 +5729,7 @@
     </row>
     <row r="81" spans="2:12" ht="15.75" customHeight="1">
       <c r="B81" s="44" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C81" s="14">
         <v>60</v>
@@ -5737,7 +5737,7 @@
       <c r="D81" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E81" s="142"/>
+      <c r="E81" s="145"/>
       <c r="F81" s="15" t="s">
         <v>33</v>
       </c>
@@ -5752,7 +5752,7 @@
     </row>
     <row r="82" spans="2:12" ht="15.75" customHeight="1">
       <c r="B82" s="44" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C82" s="14">
         <v>100</v>
@@ -5760,7 +5760,7 @@
       <c r="D82" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E82" s="142"/>
+      <c r="E82" s="145"/>
       <c r="F82" s="15" t="s">
         <v>34</v>
       </c>
@@ -5783,7 +5783,7 @@
       <c r="D83" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E83" s="142"/>
+      <c r="E83" s="145"/>
       <c r="F83" s="15" t="s">
         <v>35</v>
       </c>
@@ -5798,7 +5798,7 @@
     </row>
     <row r="84" spans="2:12" ht="15.75" customHeight="1">
       <c r="B84" s="44" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C84" s="14">
         <v>90</v>
@@ -5806,7 +5806,7 @@
       <c r="D84" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E84" s="142"/>
+      <c r="E84" s="145"/>
       <c r="F84" s="15" t="s">
         <v>36</v>
       </c>
@@ -5821,7 +5821,7 @@
     </row>
     <row r="85" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B85" s="60" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C85" s="24">
         <v>20</v>
@@ -5829,14 +5829,14 @@
       <c r="D85" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E85" s="147"/>
+      <c r="E85" s="146"/>
       <c r="F85" s="26" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G85" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H85" s="135"/>
+      <c r="H85" s="136"/>
       <c r="I85" s="29"/>
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
@@ -5852,7 +5852,7 @@
       <c r="D86" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E86" s="148">
+      <c r="E86" s="149">
         <v>125</v>
       </c>
       <c r="F86" s="11" t="s">
@@ -5862,7 +5862,7 @@
         <v>7</v>
       </c>
       <c r="H86" s="133" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I86" s="29"/>
       <c r="J86" s="29"/>
@@ -5879,7 +5879,7 @@
       <c r="D87" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E87" s="142"/>
+      <c r="E87" s="145"/>
       <c r="F87" s="15" t="s">
         <v>60</v>
       </c>
@@ -5902,7 +5902,7 @@
       <c r="D88" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E88" s="142"/>
+      <c r="E88" s="145"/>
       <c r="F88" s="15" t="s">
         <v>62</v>
       </c>
@@ -5917,7 +5917,7 @@
     </row>
     <row r="89" spans="2:12" ht="15.75" customHeight="1">
       <c r="B89" s="13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C89" s="14">
         <v>50</v>
@@ -5925,7 +5925,7 @@
       <c r="D89" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E89" s="142"/>
+      <c r="E89" s="145"/>
       <c r="F89" s="15" t="s">
         <v>63</v>
       </c>
@@ -5940,7 +5940,7 @@
     </row>
     <row r="90" spans="2:12" ht="15.75" customHeight="1">
       <c r="B90" s="13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C90" s="14">
         <v>120</v>
@@ -5948,7 +5948,7 @@
       <c r="D90" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E90" s="142"/>
+      <c r="E90" s="145"/>
       <c r="F90" s="15" t="s">
         <v>64</v>
       </c>
@@ -5963,7 +5963,7 @@
     </row>
     <row r="91" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B91" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C91" s="17">
         <v>30</v>
@@ -5971,14 +5971,14 @@
       <c r="D91" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E91" s="143"/>
+      <c r="E91" s="148"/>
       <c r="F91" s="19" t="s">
         <v>65</v>
       </c>
       <c r="G91" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H91" s="135"/>
+      <c r="H91" s="136"/>
       <c r="I91" s="29"/>
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
@@ -5986,30 +5986,30 @@
     </row>
     <row r="92" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B92" s="61" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C92" s="22">
         <v>440</v>
       </c>
       <c r="D92" s="62" t="s">
-        <v>334</v>
-      </c>
-      <c r="E92" s="141">
+        <v>332</v>
+      </c>
+      <c r="E92" s="144">
         <v>125</v>
       </c>
       <c r="F92" s="47" t="s">
         <v>66</v>
       </c>
       <c r="G92" s="48" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H92" s="140" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="93" spans="2:12" ht="15.75" customHeight="1">
       <c r="B93" s="44" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C93" s="14">
         <v>80</v>
@@ -6017,7 +6017,7 @@
       <c r="D93" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="E93" s="142"/>
+      <c r="E93" s="145"/>
       <c r="F93" s="50" t="s">
         <v>66</v>
       </c>
@@ -6028,7 +6028,7 @@
     </row>
     <row r="94" spans="2:12" ht="15.75" customHeight="1">
       <c r="B94" s="44" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C94" s="14">
         <v>140</v>
@@ -6036,7 +6036,7 @@
       <c r="D94" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="E94" s="142"/>
+      <c r="E94" s="145"/>
       <c r="F94" s="50" t="s">
         <v>66</v>
       </c>
@@ -6047,7 +6047,7 @@
     </row>
     <row r="95" spans="2:12" ht="15.75" customHeight="1">
       <c r="B95" s="44" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C95" s="14">
         <v>55</v>
@@ -6055,7 +6055,7 @@
       <c r="D95" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="E95" s="142"/>
+      <c r="E95" s="145"/>
       <c r="F95" s="50" t="s">
         <v>66</v>
       </c>
@@ -6066,7 +6066,7 @@
     </row>
     <row r="96" spans="2:12" ht="15.75" customHeight="1">
       <c r="B96" s="44" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C96" s="14">
         <v>130</v>
@@ -6074,7 +6074,7 @@
       <c r="D96" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="E96" s="142"/>
+      <c r="E96" s="145"/>
       <c r="F96" s="50" t="s">
         <v>66</v>
       </c>
@@ -6085,7 +6085,7 @@
     </row>
     <row r="97" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B97" s="64" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C97" s="17">
         <v>35</v>
@@ -6093,7 +6093,7 @@
       <c r="D97" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="E97" s="143"/>
+      <c r="E97" s="148"/>
       <c r="F97" s="53" t="s">
         <v>66</v>
       </c>
@@ -6112,17 +6112,17 @@
       <c r="D98" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E98" s="141">
+      <c r="E98" s="144">
         <v>125</v>
       </c>
       <c r="F98" s="58" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G98" s="37" t="s">
         <v>70</v>
       </c>
       <c r="H98" s="133" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="99" spans="2:8" ht="15.75" customHeight="1">
@@ -6135,18 +6135,18 @@
       <c r="D99" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E99" s="142"/>
+      <c r="E99" s="145"/>
       <c r="F99" s="56" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G99" s="54" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H99" s="134"/>
     </row>
     <row r="100" spans="2:8" ht="15.75" customHeight="1">
       <c r="B100" s="38" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C100" s="14">
         <v>140</v>
@@ -6154,9 +6154,9 @@
       <c r="D100" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E100" s="142"/>
+      <c r="E100" s="145"/>
       <c r="F100" s="56" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G100" s="54" t="s">
         <v>45</v>
@@ -6165,7 +6165,7 @@
     </row>
     <row r="101" spans="2:8" ht="15.75" customHeight="1">
       <c r="B101" s="38" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C101" s="14">
         <v>55</v>
@@ -6173,9 +6173,9 @@
       <c r="D101" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E101" s="142"/>
+      <c r="E101" s="145"/>
       <c r="F101" s="56" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G101" s="12" t="s">
         <v>7</v>
@@ -6184,7 +6184,7 @@
     </row>
     <row r="102" spans="2:8" ht="15.75" customHeight="1">
       <c r="B102" s="38" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C102" s="14">
         <v>130</v>
@@ -6192,9 +6192,9 @@
       <c r="D102" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E102" s="142"/>
+      <c r="E102" s="145"/>
       <c r="F102" s="56" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G102" s="12" t="s">
         <v>7</v>
@@ -6203,7 +6203,7 @@
     </row>
     <row r="103" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B103" s="51" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C103" s="17">
         <v>40</v>
@@ -6211,18 +6211,18 @@
       <c r="D103" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E103" s="143"/>
+      <c r="E103" s="148"/>
       <c r="F103" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G103" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="H103" s="135"/>
+      <c r="H103" s="136"/>
     </row>
     <row r="104" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B104" s="61" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C104" s="22">
         <v>450</v>
@@ -6230,7 +6230,7 @@
       <c r="D104" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E104" s="141">
+      <c r="E104" s="144">
         <v>125</v>
       </c>
       <c r="F104" s="31" t="s">
@@ -6240,7 +6240,7 @@
         <v>17</v>
       </c>
       <c r="H104" s="133" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="105" spans="2:8" ht="15.75" customHeight="1">
@@ -6253,7 +6253,7 @@
       <c r="D105" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E105" s="142"/>
+      <c r="E105" s="145"/>
       <c r="F105" s="15" t="s">
         <v>60</v>
       </c>
@@ -6264,7 +6264,7 @@
     </row>
     <row r="106" spans="2:8" ht="15.75" customHeight="1">
       <c r="B106" s="44" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C106" s="14">
         <v>140</v>
@@ -6272,7 +6272,7 @@
       <c r="D106" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E106" s="142"/>
+      <c r="E106" s="145"/>
       <c r="F106" s="15" t="s">
         <v>62</v>
       </c>
@@ -6291,7 +6291,7 @@
       <c r="D107" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E107" s="142"/>
+      <c r="E107" s="145"/>
       <c r="F107" s="15" t="s">
         <v>75</v>
       </c>
@@ -6302,7 +6302,7 @@
     </row>
     <row r="108" spans="2:8" ht="15.75" customHeight="1">
       <c r="B108" s="44" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C108" s="14">
         <v>130</v>
@@ -6310,7 +6310,7 @@
       <c r="D108" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E108" s="142"/>
+      <c r="E108" s="145"/>
       <c r="F108" s="15" t="s">
         <v>64</v>
       </c>
@@ -6321,7 +6321,7 @@
     </row>
     <row r="109" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B109" s="66" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C109" s="33">
         <v>40</v>
@@ -6329,18 +6329,18 @@
       <c r="D109" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E109" s="147"/>
+      <c r="E109" s="146"/>
       <c r="F109" s="34" t="s">
         <v>65</v>
       </c>
       <c r="G109" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="H109" s="135"/>
+      <c r="H109" s="136"/>
     </row>
     <row r="110" spans="2:8" ht="25.5" customHeight="1" thickTop="1">
       <c r="B110" s="36" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C110" s="22">
         <v>450</v>
@@ -6348,22 +6348,22 @@
       <c r="D110" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E110" s="141">
+      <c r="E110" s="144">
         <v>125</v>
       </c>
       <c r="F110" s="72" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="G110" s="37" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="H110" s="133" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="111" spans="2:8" ht="15.75" customHeight="1">
       <c r="B111" s="38" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C111" s="14">
         <v>80</v>
@@ -6371,18 +6371,18 @@
       <c r="D111" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E111" s="142"/>
+      <c r="E111" s="145"/>
       <c r="F111" s="56" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G111" s="54" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H111" s="134"/>
     </row>
     <row r="112" spans="2:8" ht="15.75" customHeight="1">
       <c r="B112" s="38" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C112" s="14">
         <v>140</v>
@@ -6390,18 +6390,18 @@
       <c r="D112" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E112" s="142"/>
+      <c r="E112" s="145"/>
       <c r="F112" s="56" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G112" s="54" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="H112" s="134"/>
     </row>
     <row r="113" spans="2:12" ht="15.75" customHeight="1">
       <c r="B113" s="38" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C113" s="14">
         <v>60</v>
@@ -6409,18 +6409,18 @@
       <c r="D113" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E113" s="142"/>
+      <c r="E113" s="145"/>
       <c r="F113" s="56" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G113" s="54" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H113" s="134"/>
     </row>
     <row r="114" spans="2:12" ht="15.75" customHeight="1">
       <c r="B114" s="38" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C114" s="14">
         <v>130</v>
@@ -6428,18 +6428,18 @@
       <c r="D114" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E114" s="142"/>
+      <c r="E114" s="145"/>
       <c r="F114" s="56" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G114" s="54" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H114" s="134"/>
     </row>
     <row r="115" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B115" s="51" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C115" s="17">
         <v>40</v>
@@ -6447,18 +6447,18 @@
       <c r="D115" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E115" s="143"/>
+      <c r="E115" s="148"/>
       <c r="F115" s="57" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G115" s="54" t="s">
-        <v>381</v>
-      </c>
-      <c r="H115" s="135"/>
+        <v>379</v>
+      </c>
+      <c r="H115" s="136"/>
     </row>
     <row r="116" spans="2:12" ht="25.9" thickTop="1">
       <c r="B116" s="68" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C116" s="22">
         <v>630</v>
@@ -6466,17 +6466,17 @@
       <c r="D116" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E116" s="141">
+      <c r="E116" s="144">
         <v>143</v>
       </c>
       <c r="F116" s="31" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G116" s="48" t="s">
         <v>76</v>
       </c>
       <c r="H116" s="133" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I116" s="29"/>
       <c r="J116" s="29"/>
@@ -6485,7 +6485,7 @@
     </row>
     <row r="117" spans="2:12" ht="15.75" customHeight="1">
       <c r="B117" s="70" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C117" s="14">
         <v>110</v>
@@ -6493,9 +6493,9 @@
       <c r="D117" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E117" s="142"/>
+      <c r="E117" s="145"/>
       <c r="F117" s="15" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G117" s="12" t="s">
         <v>7</v>
@@ -6508,7 +6508,7 @@
     </row>
     <row r="118" spans="2:12" ht="15.75" customHeight="1">
       <c r="B118" s="70" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C118" s="14">
         <v>190</v>
@@ -6516,9 +6516,9 @@
       <c r="D118" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E118" s="142"/>
+      <c r="E118" s="145"/>
       <c r="F118" s="15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G118" s="55" t="s">
         <v>45</v>
@@ -6531,7 +6531,7 @@
     </row>
     <row r="119" spans="2:12" ht="15.75" customHeight="1">
       <c r="B119" s="70" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C119" s="14">
         <v>90</v>
@@ -6539,9 +6539,9 @@
       <c r="D119" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E119" s="142"/>
+      <c r="E119" s="145"/>
       <c r="F119" s="15" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G119" s="12" t="s">
         <v>7</v>
@@ -6554,7 +6554,7 @@
     </row>
     <row r="120" spans="2:12" ht="15.75" customHeight="1">
       <c r="B120" s="70" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C120" s="14">
         <v>180</v>
@@ -6562,9 +6562,9 @@
       <c r="D120" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E120" s="142"/>
+      <c r="E120" s="145"/>
       <c r="F120" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G120" s="12" t="s">
         <v>7</v>
@@ -6577,7 +6577,7 @@
     </row>
     <row r="121" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B121" s="71" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C121" s="24">
         <v>60</v>
@@ -6585,14 +6585,14 @@
       <c r="D121" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E121" s="147"/>
+      <c r="E121" s="146"/>
       <c r="F121" s="26" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G121" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="H121" s="135"/>
+      <c r="H121" s="136"/>
       <c r="I121" s="29"/>
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
@@ -6608,17 +6608,17 @@
       <c r="D122" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E122" s="141">
+      <c r="E122" s="144">
         <v>125</v>
       </c>
       <c r="F122" s="72" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G122" s="37" t="s">
         <v>78</v>
       </c>
       <c r="H122" s="133" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="I122" s="29"/>
       <c r="J122" s="29"/>
@@ -6635,9 +6635,9 @@
       <c r="D123" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E123" s="142"/>
+      <c r="E123" s="145"/>
       <c r="F123" s="56" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G123" s="12" t="s">
         <v>7</v>
@@ -6658,9 +6658,9 @@
       <c r="D124" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E124" s="142"/>
+      <c r="E124" s="145"/>
       <c r="F124" s="56" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G124" s="54" t="s">
         <v>45</v>
@@ -6681,9 +6681,9 @@
       <c r="D125" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E125" s="142"/>
+      <c r="E125" s="145"/>
       <c r="F125" s="56" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G125" s="12" t="s">
         <v>7</v>
@@ -6704,9 +6704,9 @@
       <c r="D126" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E126" s="142"/>
+      <c r="E126" s="145"/>
       <c r="F126" s="56" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G126" s="12" t="s">
         <v>7</v>
@@ -6719,7 +6719,7 @@
     </row>
     <row r="127" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B127" s="39" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C127" s="24">
         <v>60</v>
@@ -6727,14 +6727,14 @@
       <c r="D127" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E127" s="147"/>
+      <c r="E127" s="146"/>
       <c r="F127" s="73" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G127" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="H127" s="135"/>
+      <c r="H127" s="136"/>
       <c r="I127" s="29"/>
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
@@ -6745,23 +6745,22 @@
         <v>83</v>
       </c>
       <c r="C128" s="22">
-        <f>SUM(C129:C133)</f>
         <v>630</v>
       </c>
       <c r="D128" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E128" s="141">
+      <c r="E128" s="144">
         <v>143</v>
       </c>
       <c r="F128" s="72" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G128" s="48" t="s">
         <v>84</v>
       </c>
       <c r="H128" s="133" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="129" spans="2:12" ht="15.75" customHeight="1">
@@ -6774,9 +6773,9 @@
       <c r="D129" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E129" s="142"/>
+      <c r="E129" s="145"/>
       <c r="F129" s="56" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G129" s="12" t="s">
         <v>86</v>
@@ -6785,7 +6784,7 @@
     </row>
     <row r="130" spans="2:12" ht="15.75" customHeight="1">
       <c r="B130" s="70" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C130" s="14">
         <v>190</v>
@@ -6793,9 +6792,9 @@
       <c r="D130" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E130" s="142"/>
+      <c r="E130" s="145"/>
       <c r="F130" s="56" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G130" s="55" t="s">
         <v>45</v>
@@ -6804,7 +6803,7 @@
     </row>
     <row r="131" spans="2:12" ht="15.75" customHeight="1">
       <c r="B131" s="74" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C131" s="14">
         <v>90</v>
@@ -6812,9 +6811,9 @@
       <c r="D131" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E131" s="142"/>
+      <c r="E131" s="145"/>
       <c r="F131" s="56" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G131" s="12" t="s">
         <v>7</v>
@@ -6823,7 +6822,7 @@
     </row>
     <row r="132" spans="2:12" ht="15.75" customHeight="1">
       <c r="B132" s="74" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C132" s="14">
         <v>180</v>
@@ -6831,9 +6830,9 @@
       <c r="D132" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E132" s="142"/>
+      <c r="E132" s="145"/>
       <c r="F132" s="56" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G132" s="12" t="s">
         <v>7</v>
@@ -6842,7 +6841,7 @@
     </row>
     <row r="133" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B133" s="71" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C133" s="24">
         <v>60</v>
@@ -6850,14 +6849,14 @@
       <c r="D133" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E133" s="147"/>
+      <c r="E133" s="146"/>
       <c r="F133" s="73" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G133" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="H133" s="135"/>
+      <c r="H133" s="136"/>
     </row>
     <row r="134" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B134" s="75" t="s">
@@ -6869,17 +6868,17 @@
       <c r="D134" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E134" s="149">
+      <c r="E134" s="147">
         <v>143</v>
       </c>
       <c r="F134" s="28" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G134" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H134" s="133" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I134" s="29"/>
       <c r="J134" s="29"/>
@@ -6896,9 +6895,9 @@
       <c r="D135" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E135" s="142"/>
+      <c r="E135" s="145"/>
       <c r="F135" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G135" s="12" t="s">
         <v>7</v>
@@ -6919,9 +6918,9 @@
       <c r="D136" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E136" s="142"/>
+      <c r="E136" s="145"/>
       <c r="F136" s="15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G136" s="54" t="s">
         <v>45</v>
@@ -6934,7 +6933,7 @@
     </row>
     <row r="137" spans="2:12" ht="15.75" customHeight="1">
       <c r="B137" s="44" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C137" s="14">
         <v>80</v>
@@ -6942,9 +6941,9 @@
       <c r="D137" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E137" s="142"/>
+      <c r="E137" s="145"/>
       <c r="F137" s="15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G137" s="12" t="s">
         <v>7</v>
@@ -6957,7 +6956,7 @@
     </row>
     <row r="138" spans="2:12" ht="15.75" customHeight="1">
       <c r="B138" s="44" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C138" s="14">
         <v>170</v>
@@ -6965,9 +6964,9 @@
       <c r="D138" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E138" s="142"/>
+      <c r="E138" s="145"/>
       <c r="F138" s="15" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G138" s="12" t="s">
         <v>7</v>
@@ -6988,14 +6987,14 @@
       <c r="D139" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E139" s="143"/>
+      <c r="E139" s="148"/>
       <c r="F139" s="19" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G139" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H139" s="135"/>
+      <c r="H139" s="136"/>
       <c r="I139" s="29"/>
       <c r="J139" s="29"/>
       <c r="K139" s="29"/>
@@ -7011,17 +7010,17 @@
       <c r="D140" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E140" s="141">
+      <c r="E140" s="144">
         <v>143</v>
       </c>
       <c r="F140" s="31" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G140" s="77" t="s">
         <v>93</v>
       </c>
       <c r="H140" s="133" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="141" spans="2:12" ht="15.75" customHeight="1">
@@ -7034,9 +7033,9 @@
       <c r="D141" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E141" s="142"/>
+      <c r="E141" s="145"/>
       <c r="F141" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G141" s="77" t="s">
         <v>95</v>
@@ -7045,7 +7044,7 @@
     </row>
     <row r="142" spans="2:12" ht="15.75" customHeight="1">
       <c r="B142" s="44" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C142" s="14">
         <v>180</v>
@@ -7053,9 +7052,9 @@
       <c r="D142" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E142" s="142"/>
+      <c r="E142" s="145"/>
       <c r="F142" s="15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G142" s="78" t="s">
         <v>96</v>
@@ -7072,9 +7071,9 @@
       <c r="D143" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E143" s="142"/>
+      <c r="E143" s="145"/>
       <c r="F143" s="15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G143" s="77" t="s">
         <v>95</v>
@@ -7083,7 +7082,7 @@
     </row>
     <row r="144" spans="2:12" ht="15.75" customHeight="1">
       <c r="B144" s="44" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C144" s="14">
         <v>170</v>
@@ -7091,9 +7090,9 @@
       <c r="D144" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E144" s="142"/>
+      <c r="E144" s="145"/>
       <c r="F144" s="15" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G144" s="77" t="s">
         <v>95</v>
@@ -7102,7 +7101,7 @@
     </row>
     <row r="145" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B145" s="64" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C145" s="17">
         <v>50</v>
@@ -7110,41 +7109,41 @@
       <c r="D145" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E145" s="143"/>
+      <c r="E145" s="148"/>
       <c r="F145" s="19" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G145" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="H145" s="135"/>
+      <c r="H145" s="136"/>
     </row>
     <row r="146" spans="1:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B146" s="112" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C146" s="22">
         <v>615</v>
       </c>
       <c r="D146" s="79" t="s">
-        <v>335</v>
-      </c>
-      <c r="E146" s="141">
+        <v>333</v>
+      </c>
+      <c r="E146" s="144">
         <v>143</v>
       </c>
       <c r="F146" s="47" t="s">
         <v>66</v>
       </c>
       <c r="G146" s="48" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H146" s="140" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="147" spans="1:12" ht="15.75" customHeight="1">
       <c r="B147" s="44" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C147" s="14">
         <v>105</v>
@@ -7152,7 +7151,7 @@
       <c r="D147" s="80" t="s">
         <v>99</v>
       </c>
-      <c r="E147" s="142"/>
+      <c r="E147" s="145"/>
       <c r="F147" s="50" t="s">
         <v>66</v>
       </c>
@@ -7163,7 +7162,7 @@
     </row>
     <row r="148" spans="1:12" ht="15.75" customHeight="1">
       <c r="B148" s="44" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C148" s="14">
         <v>190</v>
@@ -7171,7 +7170,7 @@
       <c r="D148" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="E148" s="142"/>
+      <c r="E148" s="145"/>
       <c r="F148" s="50" t="s">
         <v>66</v>
       </c>
@@ -7182,7 +7181,7 @@
     </row>
     <row r="149" spans="1:12" ht="15.75" customHeight="1">
       <c r="B149" s="44" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C149" s="14">
         <v>85</v>
@@ -7190,7 +7189,7 @@
       <c r="D149" s="80" t="s">
         <v>99</v>
       </c>
-      <c r="E149" s="142"/>
+      <c r="E149" s="145"/>
       <c r="F149" s="50" t="s">
         <v>66</v>
       </c>
@@ -7201,7 +7200,7 @@
     </row>
     <row r="150" spans="1:12" ht="15.75" customHeight="1">
       <c r="B150" s="44" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C150" s="14">
         <v>180</v>
@@ -7209,7 +7208,7 @@
       <c r="D150" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="E150" s="142"/>
+      <c r="E150" s="145"/>
       <c r="F150" s="50" t="s">
         <v>66</v>
       </c>
@@ -7220,7 +7219,7 @@
     </row>
     <row r="151" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B151" s="64" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C151" s="17">
         <v>55</v>
@@ -7228,7 +7227,7 @@
       <c r="D151" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="E151" s="143"/>
+      <c r="E151" s="148"/>
       <c r="F151" s="53" t="s">
         <v>66</v>
       </c>
@@ -7240,38 +7239,38 @@
     <row r="152" spans="1:12" ht="13.5" thickTop="1">
       <c r="A152" s="111"/>
       <c r="B152" s="110" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C152" s="22">
         <v>615</v>
       </c>
       <c r="D152" s="109" t="s">
-        <v>394</v>
-      </c>
-      <c r="E152" s="141">
+        <v>392</v>
+      </c>
+      <c r="E152" s="144">
         <v>143</v>
       </c>
       <c r="F152" s="47" t="s">
         <v>66</v>
       </c>
       <c r="G152" s="114" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H152" s="140" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="153" spans="1:12" ht="15.75" customHeight="1">
       <c r="B153" s="113" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C153" s="14">
         <v>105</v>
       </c>
       <c r="D153" s="109" t="s">
-        <v>387</v>
-      </c>
-      <c r="E153" s="142"/>
+        <v>385</v>
+      </c>
+      <c r="E153" s="145"/>
       <c r="F153" s="50" t="s">
         <v>66</v>
       </c>
@@ -7280,15 +7279,15 @@
     </row>
     <row r="154" spans="1:12" ht="15.75" customHeight="1">
       <c r="B154" s="113" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C154" s="14">
         <v>190</v>
       </c>
       <c r="D154" s="109" t="s">
-        <v>389</v>
-      </c>
-      <c r="E154" s="142"/>
+        <v>387</v>
+      </c>
+      <c r="E154" s="145"/>
       <c r="F154" s="50" t="s">
         <v>66</v>
       </c>
@@ -7299,15 +7298,15 @@
     </row>
     <row r="155" spans="1:12" ht="15.75" customHeight="1">
       <c r="B155" s="113" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C155" s="14">
         <v>85</v>
       </c>
       <c r="D155" s="109" t="s">
-        <v>387</v>
-      </c>
-      <c r="E155" s="142"/>
+        <v>385</v>
+      </c>
+      <c r="E155" s="145"/>
       <c r="F155" s="50" t="s">
         <v>66</v>
       </c>
@@ -7316,15 +7315,15 @@
     </row>
     <row r="156" spans="1:12" ht="15.75" customHeight="1">
       <c r="B156" s="113" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C156" s="14">
         <v>180</v>
       </c>
       <c r="D156" s="109" t="s">
-        <v>389</v>
-      </c>
-      <c r="E156" s="142"/>
+        <v>387</v>
+      </c>
+      <c r="E156" s="145"/>
       <c r="F156" s="50" t="s">
         <v>66</v>
       </c>
@@ -7333,15 +7332,15 @@
     </row>
     <row r="157" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B157" s="116" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C157" s="17">
         <v>55</v>
       </c>
       <c r="D157" s="109" t="s">
-        <v>387</v>
-      </c>
-      <c r="E157" s="143"/>
+        <v>385</v>
+      </c>
+      <c r="E157" s="148"/>
       <c r="F157" s="53" t="s">
         <v>66</v>
       </c>
@@ -7352,7 +7351,7 @@
     </row>
     <row r="158" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B158" s="82" t="s">
-        <v>307</v>
+        <v>430</v>
       </c>
       <c r="C158" s="22">
         <v>580</v>
@@ -7360,17 +7359,17 @@
       <c r="D158" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E158" s="141">
+      <c r="E158" s="144">
         <v>167</v>
       </c>
       <c r="F158" s="31" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G158" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H158" s="133" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="I158" s="29"/>
       <c r="J158" s="29"/>
@@ -7379,7 +7378,7 @@
     </row>
     <row r="159" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B159" s="84" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C159" s="14">
         <v>100</v>
@@ -7387,9 +7386,9 @@
       <c r="D159" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E159" s="142"/>
+      <c r="E159" s="145"/>
       <c r="F159" s="15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G159" s="12" t="s">
         <v>7</v>
@@ -7402,7 +7401,7 @@
     </row>
     <row r="160" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B160" s="84" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C160" s="14">
         <v>180</v>
@@ -7410,9 +7409,9 @@
       <c r="D160" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E160" s="142"/>
+      <c r="E160" s="145"/>
       <c r="F160" s="15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G160" s="54" t="s">
         <v>45</v>
@@ -7425,7 +7424,7 @@
     </row>
     <row r="161" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B161" s="84" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C161" s="14">
         <v>80</v>
@@ -7433,9 +7432,9 @@
       <c r="D161" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E161" s="142"/>
+      <c r="E161" s="145"/>
       <c r="F161" s="15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G161" s="12" t="s">
         <v>7</v>
@@ -7448,7 +7447,7 @@
     </row>
     <row r="162" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B162" s="84" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C162" s="14">
         <v>170</v>
@@ -7456,9 +7455,9 @@
       <c r="D162" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E162" s="142"/>
+      <c r="E162" s="145"/>
       <c r="F162" s="15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G162" s="12" t="s">
         <v>7</v>
@@ -7471,7 +7470,7 @@
     </row>
     <row r="163" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B163" s="85" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C163" s="17">
         <v>50</v>
@@ -7479,14 +7478,14 @@
       <c r="D163" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E163" s="143"/>
+      <c r="E163" s="148"/>
       <c r="F163" s="19" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G163" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="H163" s="135"/>
+      <c r="H163" s="136"/>
       <c r="I163" s="29"/>
       <c r="J163" s="29"/>
       <c r="K163" s="29"/>
@@ -7502,17 +7501,17 @@
       <c r="D164" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E164" s="141">
+      <c r="E164" s="144">
         <v>125</v>
       </c>
       <c r="F164" s="58" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G164" s="37" t="s">
         <v>102</v>
       </c>
       <c r="H164" s="133" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="165" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
@@ -7525,9 +7524,9 @@
       <c r="D165" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E165" s="142"/>
+      <c r="E165" s="145"/>
       <c r="F165" s="56" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G165" s="12" t="s">
         <v>7</v>
@@ -7536,7 +7535,7 @@
     </row>
     <row r="166" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B166" s="38" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C166" s="14">
         <v>180</v>
@@ -7544,9 +7543,9 @@
       <c r="D166" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E166" s="142"/>
+      <c r="E166" s="145"/>
       <c r="F166" s="56" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G166" s="54" t="s">
         <v>45</v>
@@ -7563,9 +7562,9 @@
       <c r="D167" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E167" s="142"/>
+      <c r="E167" s="145"/>
       <c r="F167" s="56" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G167" s="12" t="s">
         <v>7</v>
@@ -7574,7 +7573,7 @@
     </row>
     <row r="168" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B168" s="87" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C168" s="14">
         <v>170</v>
@@ -7582,9 +7581,9 @@
       <c r="D168" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E168" s="142"/>
+      <c r="E168" s="145"/>
       <c r="F168" s="56" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G168" s="12" t="s">
         <v>7</v>
@@ -7593,7 +7592,7 @@
     </row>
     <row r="169" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B169" s="51" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C169" s="17">
         <v>50</v>
@@ -7601,18 +7600,18 @@
       <c r="D169" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E169" s="143"/>
+      <c r="E169" s="148"/>
       <c r="F169" s="57" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G169" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H169" s="135"/>
+      <c r="H169" s="136"/>
     </row>
     <row r="170" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B170" s="40" t="s">
-        <v>105</v>
+        <v>431</v>
       </c>
       <c r="C170" s="9">
         <v>580</v>
@@ -7620,7 +7619,7 @@
       <c r="D170" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E170" s="148">
+      <c r="E170" s="149">
         <v>200</v>
       </c>
       <c r="F170" s="50" t="s">
@@ -7630,7 +7629,7 @@
         <v>7</v>
       </c>
       <c r="H170" s="133" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="I170" s="29"/>
       <c r="J170" s="29"/>
@@ -7639,7 +7638,7 @@
     </row>
     <row r="171" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B171" s="44" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C171" s="14">
         <v>100</v>
@@ -7647,12 +7646,12 @@
       <c r="D171" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E171" s="142"/>
+      <c r="E171" s="145"/>
       <c r="F171" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G171" s="55" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H171" s="134"/>
       <c r="I171" s="29"/>
@@ -7662,7 +7661,7 @@
     </row>
     <row r="172" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B172" s="44" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C172" s="14">
         <v>180</v>
@@ -7670,12 +7669,12 @@
       <c r="D172" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E172" s="142"/>
+      <c r="E172" s="145"/>
       <c r="F172" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G172" s="55" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H172" s="134"/>
       <c r="I172" s="29"/>
@@ -7685,7 +7684,7 @@
     </row>
     <row r="173" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B173" s="44" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C173" s="14">
         <v>80</v>
@@ -7693,12 +7692,12 @@
       <c r="D173" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E173" s="142"/>
+      <c r="E173" s="145"/>
       <c r="F173" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G173" s="55" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H173" s="134"/>
       <c r="I173" s="29"/>
@@ -7708,7 +7707,7 @@
     </row>
     <row r="174" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B174" s="44" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C174" s="14">
         <v>170</v>
@@ -7716,12 +7715,12 @@
       <c r="D174" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E174" s="142"/>
+      <c r="E174" s="145"/>
       <c r="F174" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G174" s="55" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H174" s="134"/>
       <c r="I174" s="29"/>
@@ -7731,7 +7730,7 @@
     </row>
     <row r="175" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B175" s="60" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C175" s="24">
         <v>50</v>
@@ -7739,14 +7738,14 @@
       <c r="D175" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E175" s="147"/>
+      <c r="E175" s="146"/>
       <c r="F175" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G175" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="H175" s="135"/>
+        <v>107</v>
+      </c>
+      <c r="H175" s="136"/>
       <c r="I175" s="29"/>
       <c r="J175" s="29"/>
       <c r="K175" s="29"/>
@@ -7754,7 +7753,7 @@
     </row>
     <row r="176" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B176" s="36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C176" s="22">
         <v>580</v>
@@ -7762,17 +7761,17 @@
       <c r="D176" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E176" s="141">
+      <c r="E176" s="144">
         <v>125</v>
       </c>
       <c r="F176" s="58" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G176" s="37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H176" s="133" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="I176" s="29"/>
       <c r="J176" s="29"/>
@@ -7781,7 +7780,7 @@
     </row>
     <row r="177" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B177" s="38" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C177" s="14">
         <v>100</v>
@@ -7789,12 +7788,12 @@
       <c r="D177" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E177" s="142"/>
+      <c r="E177" s="145"/>
       <c r="F177" s="56" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G177" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H177" s="134"/>
       <c r="I177" s="29"/>
@@ -7804,7 +7803,7 @@
     </row>
     <row r="178" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B178" s="87" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C178" s="14">
         <v>180</v>
@@ -7812,12 +7811,12 @@
       <c r="D178" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E178" s="142"/>
+      <c r="E178" s="145"/>
       <c r="F178" s="56" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G178" s="78" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H178" s="134"/>
       <c r="I178" s="29"/>
@@ -7827,7 +7826,7 @@
     </row>
     <row r="179" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B179" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C179" s="14">
         <v>80</v>
@@ -7835,12 +7834,12 @@
       <c r="D179" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E179" s="142"/>
+      <c r="E179" s="145"/>
       <c r="F179" s="56" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G179" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H179" s="134"/>
       <c r="I179" s="29"/>
@@ -7850,7 +7849,7 @@
     </row>
     <row r="180" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B180" s="38" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C180" s="14">
         <v>170</v>
@@ -7858,12 +7857,12 @@
       <c r="D180" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E180" s="142"/>
+      <c r="E180" s="145"/>
       <c r="F180" s="56" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G180" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H180" s="134"/>
       <c r="I180" s="29"/>
@@ -7873,7 +7872,7 @@
     </row>
     <row r="181" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B181" s="51" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C181" s="17">
         <v>50</v>
@@ -7881,14 +7880,14 @@
       <c r="D181" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E181" s="143"/>
+      <c r="E181" s="148"/>
       <c r="F181" s="88" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G181" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="H181" s="135"/>
+        <v>115</v>
+      </c>
+      <c r="H181" s="136"/>
       <c r="I181" s="29"/>
       <c r="J181" s="29"/>
       <c r="K181" s="29"/>
@@ -7896,7 +7895,7 @@
     </row>
     <row r="182" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B182" s="75" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C182" s="76">
         <v>1010</v>
@@ -7904,17 +7903,17 @@
       <c r="D182" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E182" s="149">
+      <c r="E182" s="147">
         <v>167</v>
       </c>
       <c r="F182" s="28" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G182" s="54" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H182" s="133" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I182" s="29"/>
       <c r="J182" s="29"/>
@@ -7923,7 +7922,7 @@
     </row>
     <row r="183" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B183" s="44" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C183" s="14">
         <v>140</v>
@@ -7931,9 +7930,9 @@
       <c r="D183" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E183" s="142"/>
+      <c r="E183" s="145"/>
       <c r="F183" s="15" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G183" s="12" t="s">
         <v>7</v>
@@ -7946,7 +7945,7 @@
     </row>
     <row r="184" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B184" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C184" s="14">
         <v>240</v>
@@ -7954,9 +7953,9 @@
       <c r="D184" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E184" s="142"/>
+      <c r="E184" s="145"/>
       <c r="F184" s="15" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G184" s="54" t="s">
         <v>45</v>
@@ -7965,7 +7964,7 @@
     </row>
     <row r="185" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B185" s="42" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C185" s="14">
         <v>120</v>
@@ -7973,9 +7972,9 @@
       <c r="D185" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E185" s="142"/>
+      <c r="E185" s="145"/>
       <c r="F185" s="15" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G185" s="12" t="s">
         <v>7</v>
@@ -7984,7 +7983,7 @@
     </row>
     <row r="186" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B186" s="44" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C186" s="14">
         <v>230</v>
@@ -7992,9 +7991,9 @@
       <c r="D186" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E186" s="142"/>
+      <c r="E186" s="145"/>
       <c r="F186" s="15" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G186" s="12" t="s">
         <v>7</v>
@@ -8007,7 +8006,7 @@
     </row>
     <row r="187" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B187" s="64" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C187" s="17">
         <v>80</v>
@@ -8015,14 +8014,14 @@
       <c r="D187" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E187" s="143"/>
+      <c r="E187" s="148"/>
       <c r="F187" s="19" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G187" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="H187" s="136"/>
+        <v>120</v>
+      </c>
+      <c r="H187" s="135"/>
       <c r="I187" s="29"/>
       <c r="J187" s="29"/>
       <c r="K187" s="29"/>
@@ -8030,7 +8029,7 @@
     </row>
     <row r="188" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B188" s="61" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C188" s="22">
         <v>1325</v>
@@ -8038,17 +8037,17 @@
       <c r="D188" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E188" s="141">
+      <c r="E188" s="144">
         <v>167</v>
       </c>
       <c r="F188" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G188" s="54" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H188" s="133" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="I188" s="29"/>
       <c r="J188" s="29"/>
@@ -8057,7 +8056,7 @@
     </row>
     <row r="189" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B189" s="44" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C189" s="14">
         <v>160</v>
@@ -8065,7 +8064,7 @@
       <c r="D189" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E189" s="142"/>
+      <c r="E189" s="145"/>
       <c r="F189" s="50" t="s">
         <v>7</v>
       </c>
@@ -8080,7 +8079,7 @@
     </row>
     <row r="190" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B190" s="44" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C190" s="14">
         <v>270</v>
@@ -8088,7 +8087,7 @@
       <c r="D190" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E190" s="142"/>
+      <c r="E190" s="145"/>
       <c r="F190" s="50" t="s">
         <v>7</v>
       </c>
@@ -8103,7 +8102,7 @@
     </row>
     <row r="191" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B191" s="44" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C191" s="14">
         <v>140</v>
@@ -8111,7 +8110,7 @@
       <c r="D191" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E191" s="142"/>
+      <c r="E191" s="145"/>
       <c r="F191" s="50" t="s">
         <v>7</v>
       </c>
@@ -8126,7 +8125,7 @@
     </row>
     <row r="192" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B192" s="44" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C192" s="14">
         <v>260</v>
@@ -8134,7 +8133,7 @@
       <c r="D192" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E192" s="142"/>
+      <c r="E192" s="145"/>
       <c r="F192" s="50" t="s">
         <v>7</v>
       </c>
@@ -8149,7 +8148,7 @@
     </row>
     <row r="193" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B193" s="60" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C193" s="24">
         <v>95</v>
@@ -8157,14 +8156,14 @@
       <c r="D193" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E193" s="147"/>
+      <c r="E193" s="146"/>
       <c r="F193" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G193" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="H193" s="136"/>
+        <v>120</v>
+      </c>
+      <c r="H193" s="135"/>
       <c r="I193" s="29"/>
       <c r="J193" s="29"/>
       <c r="K193" s="29"/>
@@ -8172,7 +8171,7 @@
     </row>
     <row r="194" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B194" s="36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C194" s="22">
         <v>810</v>
@@ -8180,22 +8179,22 @@
       <c r="D194" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E194" s="141">
+      <c r="E194" s="144">
         <v>143</v>
       </c>
       <c r="F194" s="72" t="s">
         <v>7</v>
       </c>
       <c r="G194" s="37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H194" s="133" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="195" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B195" s="38" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C195" s="14">
         <v>140</v>
@@ -8203,18 +8202,18 @@
       <c r="D195" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E195" s="142"/>
+      <c r="E195" s="145"/>
       <c r="F195" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G195" s="54" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H195" s="134"/>
     </row>
     <row r="196" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B196" s="38" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C196" s="14">
         <v>240</v>
@@ -8222,7 +8221,7 @@
       <c r="D196" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E196" s="142"/>
+      <c r="E196" s="145"/>
       <c r="F196" s="50" t="s">
         <v>7</v>
       </c>
@@ -8233,7 +8232,7 @@
     </row>
     <row r="197" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B197" s="38" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C197" s="14">
         <v>120</v>
@@ -8241,7 +8240,7 @@
       <c r="D197" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E197" s="142"/>
+      <c r="E197" s="145"/>
       <c r="F197" s="50" t="s">
         <v>7</v>
       </c>
@@ -8252,7 +8251,7 @@
     </row>
     <row r="198" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B198" s="38" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C198" s="14">
         <v>230</v>
@@ -8260,7 +8259,7 @@
       <c r="D198" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E198" s="142"/>
+      <c r="E198" s="145"/>
       <c r="F198" s="50" t="s">
         <v>7</v>
       </c>
@@ -8271,7 +8270,7 @@
     </row>
     <row r="199" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B199" s="39" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C199" s="24">
         <v>80</v>
@@ -8279,18 +8278,18 @@
       <c r="D199" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E199" s="147"/>
+      <c r="E199" s="146"/>
       <c r="F199" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G199" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="H199" s="135"/>
+        <v>120</v>
+      </c>
+      <c r="H199" s="136"/>
     </row>
     <row r="200" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B200" s="68" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C200" s="22">
         <f>925+600</f>
@@ -8299,20 +8298,20 @@
       <c r="D200" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E200" s="141">
+      <c r="E200" s="144">
         <v>233</v>
       </c>
       <c r="F200" s="72"/>
       <c r="G200" s="48" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H200" s="137" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="201" spans="2:12" ht="15.75" customHeight="1">
       <c r="B201" s="74" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C201" s="14">
         <v>160</v>
@@ -8320,14 +8319,14 @@
       <c r="D201" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E201" s="142"/>
+      <c r="E201" s="145"/>
       <c r="F201" s="50"/>
       <c r="G201" s="12"/>
       <c r="H201" s="138"/>
     </row>
     <row r="202" spans="2:12" ht="15.75" customHeight="1">
       <c r="B202" s="70" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C202" s="14">
         <v>270</v>
@@ -8335,7 +8334,7 @@
       <c r="D202" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E202" s="142"/>
+      <c r="E202" s="145"/>
       <c r="F202" s="50"/>
       <c r="G202" s="55" t="s">
         <v>45</v>
@@ -8344,7 +8343,7 @@
     </row>
     <row r="203" spans="2:12" ht="15.75" customHeight="1">
       <c r="B203" s="70" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C203" s="14">
         <v>140</v>
@@ -8352,7 +8351,7 @@
       <c r="D203" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E203" s="142"/>
+      <c r="E203" s="145"/>
       <c r="F203" s="50"/>
       <c r="G203" s="12" t="s">
         <v>7</v>
@@ -8361,7 +8360,7 @@
     </row>
     <row r="204" spans="2:12" ht="15.75" customHeight="1">
       <c r="B204" s="70" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C204" s="14">
         <v>260</v>
@@ -8369,7 +8368,7 @@
       <c r="D204" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E204" s="142"/>
+      <c r="E204" s="145"/>
       <c r="F204" s="50"/>
       <c r="G204" s="12" t="s">
         <v>7</v>
@@ -8378,7 +8377,7 @@
     </row>
     <row r="205" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B205" s="71" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C205" s="24">
         <v>95</v>
@@ -8386,16 +8385,16 @@
       <c r="D205" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E205" s="147"/>
+      <c r="E205" s="146"/>
       <c r="F205" s="89"/>
       <c r="G205" s="90" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H205" s="139"/>
     </row>
     <row r="206" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B206" s="117" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C206" s="22">
         <v>1110</v>
@@ -8403,22 +8402,22 @@
       <c r="D206" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E206" s="141">
+      <c r="E206" s="144">
         <v>167</v>
       </c>
       <c r="F206" s="127" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G206" s="114" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H206" s="133" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="207" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B207" s="74" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C207" s="14">
         <v>200</v>
@@ -8426,18 +8425,18 @@
       <c r="D207" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E207" s="142"/>
+      <c r="E207" s="145"/>
       <c r="F207" s="127" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G207" s="119" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="H207" s="134"/>
     </row>
     <row r="208" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B208" s="125" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C208" s="14">
         <v>300</v>
@@ -8445,18 +8444,18 @@
       <c r="D208" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E208" s="142"/>
+      <c r="E208" s="145"/>
       <c r="F208" s="127" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G208" s="120" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="H208" s="134"/>
     </row>
     <row r="209" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B209" s="125" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C209" s="14">
         <v>180</v>
@@ -8464,18 +8463,18 @@
       <c r="D209" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E209" s="142"/>
+      <c r="E209" s="145"/>
       <c r="F209" s="127" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G209" s="119" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="H209" s="134"/>
     </row>
     <row r="210" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B210" s="125" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C210" s="14">
         <v>290</v>
@@ -8483,18 +8482,18 @@
       <c r="D210" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E210" s="142"/>
+      <c r="E210" s="145"/>
       <c r="F210" s="127" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G210" s="122" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="H210" s="134"/>
     </row>
     <row r="211" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B211" s="126" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C211" s="24">
         <v>140</v>
@@ -8502,18 +8501,18 @@
       <c r="D211" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E211" s="147"/>
+      <c r="E211" s="146"/>
       <c r="F211" s="127" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G211" s="121" t="s">
-        <v>399</v>
-      </c>
-      <c r="H211" s="135"/>
+        <v>397</v>
+      </c>
+      <c r="H211" s="136"/>
     </row>
     <row r="212" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B212" s="117" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C212" s="22">
         <f>C213+C214+C215+C216+C217</f>
@@ -8522,22 +8521,22 @@
       <c r="D212" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E212" s="144">
+      <c r="E212" s="141">
         <v>167</v>
       </c>
       <c r="F212" s="127" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="G212" s="114" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H212" s="133" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="213" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B213" s="74" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C213" s="14">
         <v>200</v>
@@ -8545,18 +8544,18 @@
       <c r="D213" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E213" s="145"/>
+      <c r="E213" s="142"/>
       <c r="F213" s="127" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="G213" s="118" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H213" s="134"/>
     </row>
     <row r="214" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B214" s="125" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C214" s="14">
         <v>300</v>
@@ -8564,18 +8563,18 @@
       <c r="D214" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E214" s="145"/>
+      <c r="E214" s="142"/>
       <c r="F214" s="127" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G214" s="118" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H214" s="134"/>
     </row>
     <row r="215" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B215" s="125" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C215" s="14">
         <v>180</v>
@@ -8583,18 +8582,18 @@
       <c r="D215" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E215" s="145"/>
+      <c r="E215" s="142"/>
       <c r="F215" s="127" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G215" s="118" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H215" s="134"/>
     </row>
     <row r="216" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B216" s="125" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C216" s="14">
         <v>290</v>
@@ -8602,18 +8601,18 @@
       <c r="D216" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E216" s="145"/>
+      <c r="E216" s="142"/>
       <c r="F216" s="127" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G216" s="118" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H216" s="134"/>
     </row>
     <row r="217" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B217" s="126" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C217" s="123">
         <v>140</v>
@@ -8621,18 +8620,18 @@
       <c r="D217" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="E217" s="146"/>
+      <c r="E217" s="143"/>
       <c r="F217" s="127" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G217" s="119" t="s">
-        <v>411</v>
-      </c>
-      <c r="H217" s="135"/>
+        <v>409</v>
+      </c>
+      <c r="H217" s="136"/>
     </row>
     <row r="218" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B218" s="91" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C218" s="92">
         <v>5</v>
@@ -8644,18 +8643,18 @@
         <v>100</v>
       </c>
       <c r="F218" s="94" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G218" s="59" t="s">
         <v>17</v>
       </c>
       <c r="H218" s="128" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="219" spans="2:8" ht="15.75" customHeight="1">
       <c r="B219" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C219" s="14">
         <v>12</v>
@@ -8673,12 +8672,12 @@
         <v>7</v>
       </c>
       <c r="H219" s="128" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="220" spans="2:8" ht="15.75" customHeight="1">
       <c r="B220" s="44" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C220" s="14">
         <v>30</v>
@@ -8696,12 +8695,12 @@
         <v>7</v>
       </c>
       <c r="H220" s="129" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="221" spans="2:8" ht="15.75" customHeight="1">
       <c r="B221" s="44" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C221" s="14">
         <v>35</v>
@@ -8713,18 +8712,18 @@
         <v>100</v>
       </c>
       <c r="F221" s="15" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G221" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H221" s="128" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="222" spans="2:8" ht="15.75" customHeight="1">
       <c r="B222" s="13" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C222" s="14">
         <v>58</v>
@@ -8736,18 +8735,18 @@
         <v>100</v>
       </c>
       <c r="F222" s="96" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G222" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H222" s="128" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="223" spans="2:8" ht="15.75" customHeight="1">
       <c r="B223" s="38" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C223" s="14">
         <v>60</v>
@@ -8762,15 +8761,15 @@
         <v>7</v>
       </c>
       <c r="G223" s="54" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H223" s="130" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="224" spans="2:8" ht="15.75" customHeight="1">
       <c r="B224" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C224" s="14">
         <v>70</v>
@@ -8788,12 +8787,12 @@
         <v>7</v>
       </c>
       <c r="H224" s="128" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="225" spans="2:8" ht="15.75" customHeight="1">
       <c r="B225" s="44" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C225" s="14">
         <v>70</v>
@@ -8811,12 +8810,12 @@
         <v>7</v>
       </c>
       <c r="H225" s="128" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="226" spans="2:8" ht="15.75" customHeight="1">
       <c r="B226" s="97" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C226" s="14">
         <v>100</v>
@@ -8834,12 +8833,12 @@
         <v>7</v>
       </c>
       <c r="H226" s="128" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="227" spans="2:8" ht="15.75" customHeight="1">
       <c r="B227" s="44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C227" s="14">
         <v>115</v>
@@ -8851,18 +8850,18 @@
         <v>143</v>
       </c>
       <c r="F227" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G227" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H227" s="128" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="228" spans="2:8" ht="15.75" customHeight="1">
       <c r="B228" s="87" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C228" s="14">
         <v>150</v>
@@ -8874,18 +8873,18 @@
         <v>125</v>
       </c>
       <c r="F228" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G228" s="54" t="s">
         <v>45</v>
       </c>
       <c r="H228" s="128" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="229" spans="2:8" ht="15.75" customHeight="1">
       <c r="B229" s="44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C229" s="14">
         <v>160</v>
@@ -8897,18 +8896,18 @@
         <v>167</v>
       </c>
       <c r="F229" s="56" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G229" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H229" s="129" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="230" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B230" s="131" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C230" s="24">
         <v>200</v>
@@ -8923,10 +8922,10 @@
         <v>7</v>
       </c>
       <c r="G230" s="27" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H230" s="132" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="231" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
@@ -13803,11 +13802,13 @@
     <mergeCell ref="E176:E181"/>
     <mergeCell ref="E182:E187"/>
     <mergeCell ref="E188:E193"/>
+    <mergeCell ref="E152:E157"/>
     <mergeCell ref="E92:E97"/>
     <mergeCell ref="E98:E103"/>
     <mergeCell ref="E104:E109"/>
     <mergeCell ref="E116:E121"/>
     <mergeCell ref="E122:E127"/>
+    <mergeCell ref="E110:E115"/>
     <mergeCell ref="E62:E67"/>
     <mergeCell ref="E68:E73"/>
     <mergeCell ref="E74:E79"/>
@@ -13823,8 +13824,6 @@
     <mergeCell ref="E14:E19"/>
     <mergeCell ref="E20:E25"/>
     <mergeCell ref="E26:E31"/>
-    <mergeCell ref="E110:E115"/>
-    <mergeCell ref="E152:E157"/>
     <mergeCell ref="E212:E217"/>
     <mergeCell ref="E206:E211"/>
     <mergeCell ref="H122:H127"/>
@@ -13839,6 +13838,8 @@
     <mergeCell ref="H176:H181"/>
     <mergeCell ref="E128:E133"/>
     <mergeCell ref="E134:E139"/>
+    <mergeCell ref="H212:H217"/>
+    <mergeCell ref="H182:H187"/>
     <mergeCell ref="H2:H7"/>
     <mergeCell ref="H8:H13"/>
     <mergeCell ref="H14:H19"/>
@@ -13854,17 +13855,15 @@
     <mergeCell ref="H74:H79"/>
     <mergeCell ref="H80:H85"/>
     <mergeCell ref="H86:H91"/>
+    <mergeCell ref="H188:H193"/>
+    <mergeCell ref="H194:H199"/>
+    <mergeCell ref="H200:H205"/>
+    <mergeCell ref="H206:H211"/>
     <mergeCell ref="H92:H97"/>
     <mergeCell ref="H98:H103"/>
     <mergeCell ref="H104:H109"/>
     <mergeCell ref="H110:H115"/>
     <mergeCell ref="H116:H121"/>
-    <mergeCell ref="H212:H217"/>
-    <mergeCell ref="H182:H187"/>
-    <mergeCell ref="H188:H193"/>
-    <mergeCell ref="H194:H199"/>
-    <mergeCell ref="H200:H205"/>
-    <mergeCell ref="H206:H211"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-source/护甲数据.xlsx
+++ b/data-source/护甲数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7022E2C6-D5C7-42B2-BA3D-BC2D64BEEFF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FED9E47-7AEC-4546-97D3-2026395D4826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -114,7 +114,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>T2+</t>
     </r>
@@ -134,7 +134,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -158,7 +158,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -183,7 +183,7 @@
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>T2+</t>
     </r>
@@ -203,7 +203,7 @@
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -220,7 +220,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>2%</t>
     </r>
@@ -252,7 +252,7 @@
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -272,7 +272,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>6</t>
     </r>
@@ -290,7 +290,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>2%</t>
     </r>
@@ -400,7 +400,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -465,7 +465,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>2</t>
     </r>
@@ -483,7 +483,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>4</t>
     </r>
@@ -501,7 +501,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>4</t>
     </r>
@@ -519,7 +519,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">6  </t>
     </r>
@@ -563,7 +563,7 @@
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>T4+</t>
     </r>
@@ -583,7 +583,7 @@
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -594,7 +594,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>25%</t>
     </r>
@@ -626,7 +626,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>6</t>
     </r>
@@ -646,7 +646,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>12</t>
     </r>
@@ -669,7 +669,7 @@
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -692,7 +692,7 @@
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -714,7 +714,7 @@
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>T5+</t>
     </r>
@@ -734,7 +734,7 @@
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -769,7 +769,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>12</t>
     </r>
@@ -806,7 +806,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>T5+</t>
     </r>
@@ -826,7 +826,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -850,7 +850,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -870,7 +870,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -901,7 +901,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>T5+</t>
     </r>
@@ -921,7 +921,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -941,7 +941,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>30%</t>
     </r>
@@ -970,7 +970,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -990,7 +990,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>1%</t>
     </r>
@@ -1025,7 +1025,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -1045,7 +1045,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>12</t>
     </r>
@@ -1063,7 +1063,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>1%</t>
     </r>
@@ -1095,7 +1095,7 @@
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -1118,7 +1118,7 @@
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1158,7 +1158,7 @@
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>T6+</t>
     </r>
@@ -1178,7 +1178,7 @@
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -1201,7 +1201,7 @@
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -1221,7 +1221,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -1241,7 +1241,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -1261,7 +1261,7 @@
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1299,7 +1299,7 @@
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -1385,7 +1385,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -1411,7 +1411,7 @@
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1498,36 +1498,12 @@
     <t>术士靴子</t>
   </si>
   <si>
-    <t>魔法皮革：28；铜碎片：76；厚布：34</t>
-  </si>
-  <si>
-    <t>魔法皮革：5；铜碎片：12；厚布：5</t>
-  </si>
-  <si>
-    <t>魔法皮革：8；铜碎片：20；厚布：10</t>
-  </si>
-  <si>
-    <t>魔法皮革：3；铜碎片：4；厚布：4</t>
-  </si>
-  <si>
-    <t>魔法皮革：7；铜碎片：16；厚布：10</t>
-  </si>
-  <si>
-    <t>魔法皮革：5；铜碎片：24；厚布：5</t>
-  </si>
-  <si>
-    <t>硬化铆钉：17；魔法皮革：28；铜碎片：4；厚布：34</t>
-  </si>
-  <si>
     <t>硬化铆钉：3；魔法皮革：5；厚布：5</t>
   </si>
   <si>
     <t>硬化铆钉：5；魔法皮革：8；厚布：10</t>
   </si>
   <si>
-    <t>硬化铆钉：2；魔法皮革：3；铜碎片：4；厚布：4</t>
-  </si>
-  <si>
     <t>硬化铆钉：4；魔法皮革：7；厚布：10</t>
   </si>
   <si>
@@ -1549,16 +1525,10 @@
     <t>魔法皮革：5；铁碎片：15；铁锭：8；厚布：16</t>
   </si>
   <si>
-    <t>修博尔的灰烬：17；魔法皮革：28；铜碎片：4；头骨：1；厚布：34</t>
-  </si>
-  <si>
     <t>修博尔的灰烬：3；魔法皮革：5；头骨：1；厚布：5</t>
   </si>
   <si>
     <t>修博尔的灰烬：5；魔法皮革：8；厚布：10</t>
-  </si>
-  <si>
-    <t>修博尔的灰烬：2；魔法皮革：3；铜碎片：4；厚布：4</t>
   </si>
   <si>
     <t>修博尔的灰烬：4；魔法皮革：7；厚布：10</t>
@@ -1870,7 +1840,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1908,7 +1878,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1997,7 +1967,7 @@
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -2017,7 +1987,7 @@
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -2037,7 +2007,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>00</t>
     </r>
@@ -2351,6 +2321,36 @@
   <si>
     <t xml:space="preserve">玄鳞套装（T5级）  </t>
   </si>
+  <si>
+    <t>魔法皮革：28；碎铜片：76；厚布：34</t>
+  </si>
+  <si>
+    <t>魔法皮革：5；碎铜片：12；厚布：5</t>
+  </si>
+  <si>
+    <t>魔法皮革：8；碎铜片：20；厚布：10</t>
+  </si>
+  <si>
+    <t>魔法皮革：3；碎铜片：4；厚布：4</t>
+  </si>
+  <si>
+    <t>魔法皮革：7；碎铜片：16；厚布：10</t>
+  </si>
+  <si>
+    <t>魔法皮革：5；碎铜片：24；厚布：5</t>
+  </si>
+  <si>
+    <t>修博尔的灰烬：17；魔法皮革：28；碎铜片：4；头骨：1；厚布：34</t>
+  </si>
+  <si>
+    <t>修博尔的灰烬：2；魔法皮革：3；碎铜片：4；厚布：4</t>
+  </si>
+  <si>
+    <t>硬化铆钉：17；魔法皮革：28；碎铜片：4；厚布：34</t>
+  </si>
+  <si>
+    <t>硬化铆钉：2；魔法皮革：3；碎铜片：4；厚布：4</t>
+  </si>
 </sst>
 </file>
 
@@ -2368,7 +2368,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2383,24 +2383,24 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2408,7 +2408,7 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2426,20 +2426,19 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Roboto"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2447,7 +2446,7 @@
       <sz val="10"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2460,7 +2459,7 @@
     <font>
       <sz val="8"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3703,46 +3702,46 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4057,7 +4056,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
@@ -4070,17 +4069,17 @@
       <c r="D2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="149">
+      <c r="E2" s="137">
         <v>91</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="133" t="s">
-        <v>416</v>
+      <c r="H2" s="142" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="15.75" customHeight="1">
@@ -4093,14 +4092,14 @@
       <c r="D3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="145"/>
+      <c r="E3" s="134"/>
       <c r="F3" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="134"/>
+      <c r="H3" s="143"/>
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1">
       <c r="B4" s="13" t="s">
@@ -4112,14 +4111,14 @@
       <c r="D4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="145"/>
+      <c r="E4" s="134"/>
       <c r="F4" s="15" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="134"/>
+      <c r="H4" s="143"/>
     </row>
     <row r="5" spans="2:8" ht="15.75" customHeight="1">
       <c r="B5" s="13" t="s">
@@ -4131,14 +4130,14 @@
       <c r="D5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="145"/>
+      <c r="E5" s="134"/>
       <c r="F5" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="134"/>
+      <c r="H5" s="143"/>
     </row>
     <row r="6" spans="2:8" ht="15.75" customHeight="1">
       <c r="B6" s="13" t="s">
@@ -4150,14 +4149,14 @@
       <c r="D6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="145"/>
+      <c r="E6" s="134"/>
       <c r="F6" s="15" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="134"/>
+      <c r="H6" s="143"/>
     </row>
     <row r="7" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B7" s="16" t="s">
@@ -4169,14 +4168,14 @@
       <c r="D7" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="148"/>
+      <c r="E7" s="135"/>
       <c r="F7" s="19" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="136"/>
+      <c r="H7" s="144"/>
     </row>
     <row r="8" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B8" s="21" t="s">
@@ -4188,17 +4187,17 @@
       <c r="D8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="144">
+      <c r="E8" s="133">
         <v>91</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="133" t="s">
-        <v>417</v>
+      <c r="H8" s="142" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15.75" customHeight="1">
@@ -4211,14 +4210,14 @@
       <c r="D9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="145"/>
+      <c r="E9" s="134"/>
       <c r="F9" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="134"/>
+      <c r="H9" s="143"/>
     </row>
     <row r="10" spans="2:8" ht="15.75" customHeight="1">
       <c r="B10" s="13" t="s">
@@ -4230,14 +4229,14 @@
       <c r="D10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="145"/>
+      <c r="E10" s="134"/>
       <c r="F10" s="15" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="134"/>
+      <c r="H10" s="143"/>
     </row>
     <row r="11" spans="2:8" ht="15.75" customHeight="1">
       <c r="B11" s="13" t="s">
@@ -4249,14 +4248,14 @@
       <c r="D11" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="145"/>
+      <c r="E11" s="134"/>
       <c r="F11" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="134"/>
+      <c r="H11" s="143"/>
     </row>
     <row r="12" spans="2:8" ht="15.75" customHeight="1">
       <c r="B12" s="13" t="s">
@@ -4268,14 +4267,14 @@
       <c r="D12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="145"/>
+      <c r="E12" s="134"/>
       <c r="F12" s="15" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="134"/>
+      <c r="H12" s="143"/>
     </row>
     <row r="13" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B13" s="23" t="s">
@@ -4287,14 +4286,14 @@
       <c r="D13" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="146"/>
+      <c r="E13" s="136"/>
       <c r="F13" s="26" t="s">
         <v>9</v>
       </c>
       <c r="G13" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="136"/>
+      <c r="H13" s="144"/>
     </row>
     <row r="14" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B14" s="8" t="s">
@@ -4306,17 +4305,17 @@
       <c r="D14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="147">
+      <c r="E14" s="138">
         <v>100</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="133" t="s">
-        <v>416</v>
+      <c r="H14" s="142" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15.75" customHeight="1">
@@ -4329,18 +4328,18 @@
       <c r="D15" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="145"/>
+      <c r="E15" s="134"/>
       <c r="F15" s="15" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H15" s="134"/>
+      <c r="H15" s="143"/>
     </row>
     <row r="16" spans="2:8" ht="15.75" customHeight="1">
       <c r="B16" s="13" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="C16" s="14">
         <v>50</v>
@@ -4348,14 +4347,14 @@
       <c r="D16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="145"/>
+      <c r="E16" s="134"/>
       <c r="F16" s="15" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="134"/>
+      <c r="H16" s="143"/>
     </row>
     <row r="17" spans="2:12" ht="15.75" customHeight="1">
       <c r="B17" s="13" t="s">
@@ -4367,14 +4366,14 @@
       <c r="D17" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="145"/>
+      <c r="E17" s="134"/>
       <c r="F17" s="15" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H17" s="134"/>
+      <c r="H17" s="143"/>
       <c r="I17" s="29"/>
       <c r="J17" s="29"/>
       <c r="K17" s="29"/>
@@ -4390,14 +4389,14 @@
       <c r="D18" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="145"/>
+      <c r="E18" s="134"/>
       <c r="F18" s="15" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="134"/>
+      <c r="H18" s="143"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
       <c r="K18" s="29"/>
@@ -4413,14 +4412,14 @@
       <c r="D19" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="148"/>
+      <c r="E19" s="135"/>
       <c r="F19" s="19" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="136"/>
+      <c r="H19" s="144"/>
       <c r="I19" s="29"/>
       <c r="J19" s="29"/>
       <c r="K19" s="29"/>
@@ -4436,17 +4435,17 @@
       <c r="D20" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="144">
+      <c r="E20" s="133">
         <v>100</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="G20" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="H20" s="133" t="s">
-        <v>418</v>
+      <c r="H20" s="142" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="15.75" customHeight="1">
@@ -4459,14 +4458,14 @@
       <c r="D21" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="145"/>
+      <c r="E21" s="134"/>
       <c r="F21" s="15" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H21" s="134"/>
+      <c r="H21" s="143"/>
     </row>
     <row r="22" spans="2:12" ht="15.75" customHeight="1">
       <c r="B22" s="13" t="s">
@@ -4478,14 +4477,14 @@
       <c r="D22" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="145"/>
+      <c r="E22" s="134"/>
       <c r="F22" s="15" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H22" s="134"/>
+      <c r="H22" s="143"/>
     </row>
     <row r="23" spans="2:12" ht="15.75" customHeight="1">
       <c r="B23" s="13" t="s">
@@ -4497,14 +4496,14 @@
       <c r="D23" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="145"/>
+      <c r="E23" s="134"/>
       <c r="F23" s="15" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H23" s="134"/>
+      <c r="H23" s="143"/>
     </row>
     <row r="24" spans="2:12" ht="15.75" customHeight="1">
       <c r="B24" s="13" t="s">
@@ -4516,14 +4515,14 @@
       <c r="D24" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="145"/>
+      <c r="E24" s="134"/>
       <c r="F24" s="15" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H24" s="134"/>
+      <c r="H24" s="143"/>
     </row>
     <row r="25" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B25" s="107" t="s">
@@ -4535,14 +4534,14 @@
       <c r="D25" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="148"/>
+      <c r="E25" s="135"/>
       <c r="F25" s="19" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H25" s="136"/>
+      <c r="H25" s="144"/>
     </row>
     <row r="26" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B26" s="21" t="s">
@@ -4554,17 +4553,17 @@
       <c r="D26" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="144">
+      <c r="E26" s="133">
         <v>100</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="G26" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H26" s="133" t="s">
-        <v>417</v>
+      <c r="H26" s="142" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="27" spans="2:12" ht="15.75" customHeight="1">
@@ -4577,14 +4576,14 @@
       <c r="D27" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="145"/>
+      <c r="E27" s="134"/>
       <c r="F27" s="15" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="G27" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H27" s="134"/>
+      <c r="H27" s="143"/>
     </row>
     <row r="28" spans="2:12" ht="15.75" customHeight="1">
       <c r="B28" s="13" t="s">
@@ -4596,14 +4595,14 @@
       <c r="D28" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="145"/>
+      <c r="E28" s="134"/>
       <c r="F28" s="15" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H28" s="134"/>
+      <c r="H28" s="143"/>
     </row>
     <row r="29" spans="2:12" ht="15.75" customHeight="1">
       <c r="B29" s="13" t="s">
@@ -4615,14 +4614,14 @@
       <c r="D29" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="145"/>
+      <c r="E29" s="134"/>
       <c r="F29" s="15" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="G29" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H29" s="134"/>
+      <c r="H29" s="143"/>
     </row>
     <row r="30" spans="2:12" ht="15.75" customHeight="1">
       <c r="B30" s="13" t="s">
@@ -4634,14 +4633,14 @@
       <c r="D30" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="145"/>
+      <c r="E30" s="134"/>
       <c r="F30" s="15" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H30" s="134"/>
+      <c r="H30" s="143"/>
     </row>
     <row r="31" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B31" s="32" t="s">
@@ -4653,14 +4652,14 @@
       <c r="D31" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="146"/>
+      <c r="E31" s="136"/>
       <c r="F31" s="34" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H31" s="136"/>
+      <c r="H31" s="144"/>
     </row>
     <row r="32" spans="2:12" ht="25.9" thickTop="1">
       <c r="B32" s="36" t="s">
@@ -4672,17 +4671,17 @@
       <c r="D32" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="144">
+      <c r="E32" s="133">
         <v>112</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="G32" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="H32" s="133" t="s">
-        <v>417</v>
+      <c r="H32" s="142" t="s">
+        <v>407</v>
       </c>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -4699,14 +4698,14 @@
       <c r="D33" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="145"/>
+      <c r="E33" s="134"/>
       <c r="F33" s="15" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H33" s="134"/>
+      <c r="H33" s="143"/>
       <c r="I33" s="29"/>
       <c r="J33" s="29"/>
       <c r="K33" s="29"/>
@@ -4722,14 +4721,14 @@
       <c r="D34" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="145"/>
+      <c r="E34" s="134"/>
       <c r="F34" s="15" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="134"/>
+      <c r="H34" s="143"/>
       <c r="I34" s="29"/>
       <c r="J34" s="29"/>
       <c r="K34" s="29"/>
@@ -4745,14 +4744,14 @@
       <c r="D35" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="145"/>
+      <c r="E35" s="134"/>
       <c r="F35" s="15" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H35" s="134"/>
+      <c r="H35" s="143"/>
       <c r="I35" s="29"/>
       <c r="J35" s="29"/>
       <c r="K35" s="29"/>
@@ -4768,14 +4767,14 @@
       <c r="D36" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="145"/>
+      <c r="E36" s="134"/>
       <c r="F36" s="15" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H36" s="134"/>
+      <c r="H36" s="143"/>
       <c r="I36" s="29"/>
       <c r="J36" s="29"/>
       <c r="K36" s="29"/>
@@ -4791,14 +4790,14 @@
       <c r="D37" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E37" s="146"/>
+      <c r="E37" s="136"/>
       <c r="F37" s="26" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="G37" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="H37" s="136"/>
+      <c r="H37" s="144"/>
       <c r="I37" s="29"/>
       <c r="J37" s="29"/>
       <c r="K37" s="29"/>
@@ -4814,17 +4813,17 @@
       <c r="D38" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="144">
+      <c r="E38" s="133">
         <v>100</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="G38" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="H38" s="133" t="s">
-        <v>417</v>
+      <c r="H38" s="142" t="s">
+        <v>407</v>
       </c>
       <c r="I38" s="29"/>
       <c r="J38" s="29"/>
@@ -4841,14 +4840,14 @@
       <c r="D39" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E39" s="145"/>
+      <c r="E39" s="134"/>
       <c r="F39" s="15" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H39" s="134"/>
+      <c r="H39" s="143"/>
       <c r="I39" s="29"/>
       <c r="J39" s="29"/>
       <c r="K39" s="29"/>
@@ -4864,14 +4863,14 @@
       <c r="D40" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E40" s="145"/>
+      <c r="E40" s="134"/>
       <c r="F40" s="15" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="G40" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H40" s="134"/>
+      <c r="H40" s="143"/>
       <c r="I40" s="29"/>
       <c r="J40" s="29"/>
       <c r="K40" s="29"/>
@@ -4887,14 +4886,14 @@
       <c r="D41" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E41" s="145"/>
+      <c r="E41" s="134"/>
       <c r="F41" s="15" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="G41" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H41" s="134"/>
+      <c r="H41" s="143"/>
       <c r="I41" s="29"/>
       <c r="J41" s="29"/>
       <c r="K41" s="29"/>
@@ -4910,14 +4909,14 @@
       <c r="D42" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E42" s="145"/>
+      <c r="E42" s="134"/>
       <c r="F42" s="15" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="G42" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="134"/>
+      <c r="H42" s="143"/>
       <c r="I42" s="29"/>
       <c r="J42" s="29"/>
       <c r="K42" s="29"/>
@@ -4933,14 +4932,14 @@
       <c r="D43" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E43" s="146"/>
+      <c r="E43" s="136"/>
       <c r="F43" s="26" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="G43" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="H43" s="136"/>
+      <c r="H43" s="144"/>
       <c r="I43" s="29"/>
       <c r="J43" s="29"/>
       <c r="K43" s="29"/>
@@ -4956,17 +4955,17 @@
       <c r="D44" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E44" s="149">
+      <c r="E44" s="137">
         <v>112</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="G44" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H44" s="133" t="s">
-        <v>416</v>
+      <c r="H44" s="142" t="s">
+        <v>406</v>
       </c>
       <c r="I44" s="29"/>
       <c r="J44" s="29"/>
@@ -4983,14 +4982,14 @@
       <c r="D45" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E45" s="145"/>
+      <c r="E45" s="134"/>
       <c r="F45" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G45" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H45" s="134"/>
+      <c r="H45" s="143"/>
       <c r="I45" s="29"/>
       <c r="J45" s="29"/>
       <c r="K45" s="29"/>
@@ -5006,14 +5005,14 @@
       <c r="D46" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E46" s="145"/>
+      <c r="E46" s="134"/>
       <c r="F46" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G46" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H46" s="134"/>
+      <c r="H46" s="143"/>
       <c r="I46" s="29"/>
       <c r="J46" s="29"/>
       <c r="K46" s="29"/>
@@ -5029,14 +5028,14 @@
       <c r="D47" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E47" s="145"/>
+      <c r="E47" s="134"/>
       <c r="F47" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G47" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H47" s="134"/>
+      <c r="H47" s="143"/>
       <c r="I47" s="29"/>
       <c r="J47" s="29"/>
       <c r="K47" s="29"/>
@@ -5052,14 +5051,14 @@
       <c r="D48" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E48" s="145"/>
+      <c r="E48" s="134"/>
       <c r="F48" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G48" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H48" s="134"/>
+      <c r="H48" s="143"/>
       <c r="I48" s="29"/>
       <c r="J48" s="29"/>
       <c r="K48" s="29"/>
@@ -5075,14 +5074,14 @@
       <c r="D49" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E49" s="148"/>
+      <c r="E49" s="135"/>
       <c r="F49" s="19" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="G49" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H49" s="136"/>
+      <c r="H49" s="144"/>
       <c r="I49" s="29"/>
       <c r="J49" s="29"/>
       <c r="K49" s="29"/>
@@ -5098,17 +5097,17 @@
       <c r="D50" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E50" s="144">
+      <c r="E50" s="133">
         <v>112</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="G50" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H50" s="133" t="s">
-        <v>419</v>
+      <c r="H50" s="142" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="51" spans="2:12" ht="15.75" customHeight="1">
@@ -5121,14 +5120,14 @@
       <c r="D51" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E51" s="145"/>
+      <c r="E51" s="134"/>
       <c r="F51" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G51" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H51" s="134"/>
+      <c r="H51" s="143"/>
     </row>
     <row r="52" spans="2:12" ht="15.75" customHeight="1">
       <c r="B52" s="13" t="s">
@@ -5140,14 +5139,14 @@
       <c r="D52" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E52" s="145"/>
+      <c r="E52" s="134"/>
       <c r="F52" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G52" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H52" s="134"/>
+      <c r="H52" s="143"/>
     </row>
     <row r="53" spans="2:12" ht="15.75" customHeight="1">
       <c r="B53" s="13" t="s">
@@ -5159,14 +5158,14 @@
       <c r="D53" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E53" s="145"/>
+      <c r="E53" s="134"/>
       <c r="F53" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G53" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H53" s="134"/>
+      <c r="H53" s="143"/>
     </row>
     <row r="54" spans="2:12" ht="15.75" customHeight="1">
       <c r="B54" s="13" t="s">
@@ -5178,14 +5177,14 @@
       <c r="D54" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E54" s="145"/>
+      <c r="E54" s="134"/>
       <c r="F54" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H54" s="134"/>
+      <c r="H54" s="143"/>
     </row>
     <row r="55" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B55" s="16" t="s">
@@ -5197,14 +5196,14 @@
       <c r="D55" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E55" s="148"/>
+      <c r="E55" s="135"/>
       <c r="F55" s="19" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="G55" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H55" s="136"/>
+      <c r="H55" s="144"/>
     </row>
     <row r="56" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B56" s="36" t="s">
@@ -5216,7 +5215,7 @@
       <c r="D56" s="63" t="s">
         <v>182</v>
       </c>
-      <c r="E56" s="144">
+      <c r="E56" s="133">
         <v>112</v>
       </c>
       <c r="F56" s="47" t="s">
@@ -5225,8 +5224,8 @@
       <c r="G56" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="H56" s="133" t="s">
-        <v>420</v>
+      <c r="H56" s="142" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="57" spans="2:12" ht="15.75" customHeight="1">
@@ -5239,14 +5238,14 @@
       <c r="D57" s="63" t="s">
         <v>180</v>
       </c>
-      <c r="E57" s="145"/>
+      <c r="E57" s="134"/>
       <c r="F57" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G57" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H57" s="134"/>
+      <c r="H57" s="143"/>
     </row>
     <row r="58" spans="2:12" ht="15.75" customHeight="1">
       <c r="B58" s="38" t="s">
@@ -5258,14 +5257,14 @@
       <c r="D58" s="63" t="s">
         <v>181</v>
       </c>
-      <c r="E58" s="145"/>
+      <c r="E58" s="134"/>
       <c r="F58" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G58" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H58" s="134"/>
+      <c r="H58" s="143"/>
     </row>
     <row r="59" spans="2:12" ht="15.75" customHeight="1">
       <c r="B59" s="38" t="s">
@@ -5277,14 +5276,14 @@
       <c r="D59" s="63" t="s">
         <v>180</v>
       </c>
-      <c r="E59" s="145"/>
+      <c r="E59" s="134"/>
       <c r="F59" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G59" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H59" s="134"/>
+      <c r="H59" s="143"/>
     </row>
     <row r="60" spans="2:12" ht="15.75" customHeight="1">
       <c r="B60" s="38" t="s">
@@ -5296,14 +5295,14 @@
       <c r="D60" s="63" t="s">
         <v>181</v>
       </c>
-      <c r="E60" s="145"/>
+      <c r="E60" s="134"/>
       <c r="F60" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G60" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H60" s="134"/>
+      <c r="H60" s="143"/>
     </row>
     <row r="61" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B61" s="51" t="s">
@@ -5315,14 +5314,14 @@
       <c r="D61" s="63" t="s">
         <v>180</v>
       </c>
-      <c r="E61" s="148"/>
+      <c r="E61" s="135"/>
       <c r="F61" s="53" t="s">
         <v>7</v>
       </c>
       <c r="G61" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H61" s="136"/>
+      <c r="H61" s="144"/>
     </row>
     <row r="62" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B62" s="36" t="s">
@@ -5334,17 +5333,17 @@
       <c r="D62" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E62" s="144">
+      <c r="E62" s="133">
         <v>143</v>
       </c>
       <c r="F62" s="31" t="s">
-        <v>192</v>
+        <v>422</v>
       </c>
       <c r="G62" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="H62" s="133" t="s">
-        <v>417</v>
+      <c r="H62" s="142" t="s">
+        <v>407</v>
       </c>
       <c r="I62" s="29"/>
       <c r="J62" s="29"/>
@@ -5361,14 +5360,14 @@
       <c r="D63" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E63" s="145"/>
+      <c r="E63" s="134"/>
       <c r="F63" s="15" t="s">
-        <v>193</v>
+        <v>423</v>
       </c>
       <c r="G63" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H63" s="134"/>
+      <c r="H63" s="143"/>
       <c r="I63" s="29"/>
       <c r="J63" s="29"/>
       <c r="K63" s="29"/>
@@ -5384,14 +5383,14 @@
       <c r="D64" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E64" s="145"/>
+      <c r="E64" s="134"/>
       <c r="F64" s="15" t="s">
-        <v>194</v>
+        <v>424</v>
       </c>
       <c r="G64" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H64" s="134"/>
+      <c r="H64" s="143"/>
       <c r="I64" s="29"/>
       <c r="J64" s="29"/>
       <c r="K64" s="29"/>
@@ -5407,14 +5406,14 @@
       <c r="D65" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E65" s="145"/>
+      <c r="E65" s="134"/>
       <c r="F65" s="15" t="s">
-        <v>195</v>
+        <v>425</v>
       </c>
       <c r="G65" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H65" s="134"/>
+      <c r="H65" s="143"/>
       <c r="I65" s="29"/>
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
@@ -5430,14 +5429,14 @@
       <c r="D66" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E66" s="145"/>
+      <c r="E66" s="134"/>
       <c r="F66" s="15" t="s">
-        <v>196</v>
+        <v>426</v>
       </c>
       <c r="G66" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H66" s="134"/>
+      <c r="H66" s="143"/>
       <c r="I66" s="29"/>
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
@@ -5451,14 +5450,14 @@
         <v>12</v>
       </c>
       <c r="D67" s="18"/>
-      <c r="E67" s="148"/>
+      <c r="E67" s="135"/>
       <c r="F67" s="19" t="s">
-        <v>197</v>
+        <v>427</v>
       </c>
       <c r="G67" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H67" s="136"/>
+      <c r="H67" s="144"/>
       <c r="I67" s="29"/>
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
@@ -5474,17 +5473,17 @@
       <c r="D68" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E68" s="144">
+      <c r="E68" s="133">
         <v>143</v>
       </c>
       <c r="F68" s="31" t="s">
-        <v>209</v>
+        <v>428</v>
       </c>
       <c r="G68" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="H68" s="133" t="s">
-        <v>417</v>
+      <c r="H68" s="142" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="69" spans="2:12" ht="15.75" customHeight="1">
@@ -5497,14 +5496,14 @@
       <c r="D69" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E69" s="145"/>
+      <c r="E69" s="134"/>
       <c r="F69" s="56" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="G69" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="H69" s="134"/>
+      <c r="H69" s="143"/>
     </row>
     <row r="70" spans="2:12" ht="15.75" customHeight="1">
       <c r="B70" s="38" t="s">
@@ -5516,14 +5515,14 @@
       <c r="D70" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E70" s="145"/>
+      <c r="E70" s="134"/>
       <c r="F70" s="15" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="G70" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H70" s="134"/>
+      <c r="H70" s="143"/>
     </row>
     <row r="71" spans="2:12" ht="15.75" customHeight="1">
       <c r="B71" s="38" t="s">
@@ -5535,14 +5534,14 @@
       <c r="D71" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E71" s="145"/>
+      <c r="E71" s="134"/>
       <c r="F71" s="56" t="s">
-        <v>212</v>
+        <v>429</v>
       </c>
       <c r="G71" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H71" s="134"/>
+      <c r="H71" s="143"/>
     </row>
     <row r="72" spans="2:12" ht="15.75" customHeight="1">
       <c r="B72" s="38" t="s">
@@ -5554,14 +5553,14 @@
       <c r="D72" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E72" s="145"/>
+      <c r="E72" s="134"/>
       <c r="F72" s="15" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G72" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H72" s="134"/>
+      <c r="H72" s="143"/>
     </row>
     <row r="73" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B73" s="51" t="s">
@@ -5573,14 +5572,14 @@
       <c r="D73" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E73" s="148"/>
+      <c r="E73" s="135"/>
       <c r="F73" s="57" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="G73" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H73" s="136"/>
+      <c r="H73" s="144"/>
     </row>
     <row r="74" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B74" s="36" t="s">
@@ -5592,22 +5591,22 @@
       <c r="D74" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E74" s="144">
+      <c r="E74" s="133">
         <v>143</v>
       </c>
       <c r="F74" s="58" t="s">
-        <v>198</v>
+        <v>430</v>
       </c>
       <c r="G74" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="H74" s="133" t="s">
-        <v>417</v>
+      <c r="H74" s="142" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="75" spans="2:12" ht="15.75" customHeight="1">
       <c r="B75" s="38" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C75" s="49">
         <v>70</v>
@@ -5615,18 +5614,18 @@
       <c r="D75" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E75" s="145"/>
+      <c r="E75" s="134"/>
       <c r="F75" s="56" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="G75" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="H75" s="134"/>
+      <c r="H75" s="143"/>
     </row>
     <row r="76" spans="2:12" ht="15.75" customHeight="1">
       <c r="B76" s="38" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="C76" s="49">
         <v>110</v>
@@ -5634,18 +5633,18 @@
       <c r="D76" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E76" s="145"/>
+      <c r="E76" s="134"/>
       <c r="F76" s="56" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="G76" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H76" s="134"/>
+      <c r="H76" s="143"/>
     </row>
     <row r="77" spans="2:12" ht="15.75" customHeight="1">
       <c r="B77" s="38" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="C77" s="49">
         <v>35</v>
@@ -5653,18 +5652,18 @@
       <c r="D77" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E77" s="145"/>
+      <c r="E77" s="134"/>
       <c r="F77" s="56" t="s">
-        <v>201</v>
+        <v>431</v>
       </c>
       <c r="G77" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H77" s="134"/>
+      <c r="H77" s="143"/>
     </row>
     <row r="78" spans="2:12" ht="15.75" customHeight="1">
       <c r="B78" s="38" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="C78" s="49">
         <v>95</v>
@@ -5672,18 +5671,18 @@
       <c r="D78" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E78" s="145"/>
+      <c r="E78" s="134"/>
       <c r="F78" s="56" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="G78" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H78" s="134"/>
+      <c r="H78" s="143"/>
     </row>
     <row r="79" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B79" s="51" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="C79" s="52">
         <v>12</v>
@@ -5691,14 +5690,14 @@
       <c r="D79" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E79" s="148"/>
+      <c r="E79" s="135"/>
       <c r="F79" s="57" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="G79" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H79" s="136"/>
+      <c r="H79" s="144"/>
     </row>
     <row r="80" spans="2:12" ht="38.65" thickTop="1">
       <c r="B80" s="40" t="s">
@@ -5710,17 +5709,17 @@
       <c r="D80" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E80" s="144">
+      <c r="E80" s="133">
         <v>112</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="G80" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="H80" s="133" t="s">
-        <v>417</v>
+      <c r="H80" s="142" t="s">
+        <v>407</v>
       </c>
       <c r="I80" s="29"/>
       <c r="J80" s="29"/>
@@ -5729,7 +5728,7 @@
     </row>
     <row r="81" spans="2:12" ht="15.75" customHeight="1">
       <c r="B81" s="44" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C81" s="14">
         <v>60</v>
@@ -5737,14 +5736,14 @@
       <c r="D81" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E81" s="145"/>
+      <c r="E81" s="134"/>
       <c r="F81" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G81" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H81" s="134"/>
+      <c r="H81" s="143"/>
       <c r="I81" s="29"/>
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
@@ -5752,7 +5751,7 @@
     </row>
     <row r="82" spans="2:12" ht="15.75" customHeight="1">
       <c r="B82" s="44" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C82" s="14">
         <v>100</v>
@@ -5760,14 +5759,14 @@
       <c r="D82" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E82" s="145"/>
+      <c r="E82" s="134"/>
       <c r="F82" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G82" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H82" s="134"/>
+      <c r="H82" s="143"/>
       <c r="I82" s="29"/>
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
@@ -5783,14 +5782,14 @@
       <c r="D83" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E83" s="145"/>
+      <c r="E83" s="134"/>
       <c r="F83" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G83" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H83" s="134"/>
+      <c r="H83" s="143"/>
       <c r="I83" s="29"/>
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
@@ -5798,7 +5797,7 @@
     </row>
     <row r="84" spans="2:12" ht="15.75" customHeight="1">
       <c r="B84" s="44" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="C84" s="14">
         <v>90</v>
@@ -5806,14 +5805,14 @@
       <c r="D84" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E84" s="145"/>
+      <c r="E84" s="134"/>
       <c r="F84" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G84" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H84" s="134"/>
+      <c r="H84" s="143"/>
       <c r="I84" s="29"/>
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
@@ -5821,7 +5820,7 @@
     </row>
     <row r="85" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B85" s="60" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C85" s="24">
         <v>20</v>
@@ -5829,14 +5828,14 @@
       <c r="D85" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E85" s="146"/>
+      <c r="E85" s="136"/>
       <c r="F85" s="26" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="G85" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H85" s="136"/>
+      <c r="H85" s="144"/>
       <c r="I85" s="29"/>
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
@@ -5852,7 +5851,7 @@
       <c r="D86" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E86" s="149">
+      <c r="E86" s="137">
         <v>125</v>
       </c>
       <c r="F86" s="11" t="s">
@@ -5861,8 +5860,8 @@
       <c r="G86" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H86" s="133" t="s">
-        <v>416</v>
+      <c r="H86" s="142" t="s">
+        <v>406</v>
       </c>
       <c r="I86" s="29"/>
       <c r="J86" s="29"/>
@@ -5879,14 +5878,14 @@
       <c r="D87" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E87" s="145"/>
+      <c r="E87" s="134"/>
       <c r="F87" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G87" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H87" s="134"/>
+      <c r="H87" s="143"/>
       <c r="I87" s="29"/>
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
@@ -5902,14 +5901,14 @@
       <c r="D88" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E88" s="145"/>
+      <c r="E88" s="134"/>
       <c r="F88" s="15" t="s">
         <v>62</v>
       </c>
       <c r="G88" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H88" s="134"/>
+      <c r="H88" s="143"/>
       <c r="I88" s="29"/>
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
@@ -5917,7 +5916,7 @@
     </row>
     <row r="89" spans="2:12" ht="15.75" customHeight="1">
       <c r="B89" s="13" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="C89" s="14">
         <v>50</v>
@@ -5925,14 +5924,14 @@
       <c r="D89" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E89" s="145"/>
+      <c r="E89" s="134"/>
       <c r="F89" s="15" t="s">
         <v>63</v>
       </c>
       <c r="G89" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H89" s="134"/>
+      <c r="H89" s="143"/>
       <c r="I89" s="29"/>
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
@@ -5940,7 +5939,7 @@
     </row>
     <row r="90" spans="2:12" ht="15.75" customHeight="1">
       <c r="B90" s="13" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C90" s="14">
         <v>120</v>
@@ -5948,14 +5947,14 @@
       <c r="D90" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E90" s="145"/>
+      <c r="E90" s="134"/>
       <c r="F90" s="15" t="s">
         <v>64</v>
       </c>
       <c r="G90" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H90" s="134"/>
+      <c r="H90" s="143"/>
       <c r="I90" s="29"/>
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
@@ -5963,7 +5962,7 @@
     </row>
     <row r="91" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B91" s="16" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="C91" s="17">
         <v>30</v>
@@ -5971,14 +5970,14 @@
       <c r="D91" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E91" s="148"/>
+      <c r="E91" s="135"/>
       <c r="F91" s="19" t="s">
         <v>65</v>
       </c>
       <c r="G91" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H91" s="136"/>
+      <c r="H91" s="144"/>
       <c r="I91" s="29"/>
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
@@ -5986,30 +5985,30 @@
     </row>
     <row r="92" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B92" s="61" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C92" s="22">
         <v>440</v>
       </c>
       <c r="D92" s="62" t="s">
-        <v>332</v>
-      </c>
-      <c r="E92" s="144">
+        <v>322</v>
+      </c>
+      <c r="E92" s="133">
         <v>125</v>
       </c>
       <c r="F92" s="47" t="s">
         <v>66</v>
       </c>
       <c r="G92" s="48" t="s">
-        <v>335</v>
-      </c>
-      <c r="H92" s="140" t="s">
-        <v>421</v>
+        <v>325</v>
+      </c>
+      <c r="H92" s="145" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="93" spans="2:12" ht="15.75" customHeight="1">
       <c r="B93" s="44" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C93" s="14">
         <v>80</v>
@@ -6017,18 +6016,18 @@
       <c r="D93" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="E93" s="145"/>
+      <c r="E93" s="134"/>
       <c r="F93" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H93" s="138"/>
+      <c r="H93" s="146"/>
     </row>
     <row r="94" spans="2:12" ht="15.75" customHeight="1">
       <c r="B94" s="44" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="C94" s="14">
         <v>140</v>
@@ -6036,18 +6035,18 @@
       <c r="D94" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="E94" s="145"/>
+      <c r="E94" s="134"/>
       <c r="F94" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G94" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H94" s="138"/>
+      <c r="H94" s="146"/>
     </row>
     <row r="95" spans="2:12" ht="15.75" customHeight="1">
       <c r="B95" s="44" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C95" s="14">
         <v>55</v>
@@ -6055,18 +6054,18 @@
       <c r="D95" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="E95" s="145"/>
+      <c r="E95" s="134"/>
       <c r="F95" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G95" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H95" s="138"/>
+      <c r="H95" s="146"/>
     </row>
     <row r="96" spans="2:12" ht="15.75" customHeight="1">
       <c r="B96" s="44" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C96" s="14">
         <v>130</v>
@@ -6074,18 +6073,18 @@
       <c r="D96" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="E96" s="145"/>
+      <c r="E96" s="134"/>
       <c r="F96" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G96" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H96" s="138"/>
+      <c r="H96" s="146"/>
     </row>
     <row r="97" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B97" s="64" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C97" s="17">
         <v>35</v>
@@ -6093,14 +6092,14 @@
       <c r="D97" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="E97" s="148"/>
+      <c r="E97" s="135"/>
       <c r="F97" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G97" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H97" s="139"/>
+      <c r="H97" s="147"/>
     </row>
     <row r="98" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B98" s="36" t="s">
@@ -6112,17 +6111,17 @@
       <c r="D98" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E98" s="144">
+      <c r="E98" s="133">
         <v>125</v>
       </c>
       <c r="F98" s="58" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="G98" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="H98" s="133" t="s">
-        <v>417</v>
+      <c r="H98" s="142" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="99" spans="2:8" ht="15.75" customHeight="1">
@@ -6135,18 +6134,18 @@
       <c r="D99" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E99" s="145"/>
+      <c r="E99" s="134"/>
       <c r="F99" s="56" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="G99" s="54" t="s">
-        <v>245</v>
-      </c>
-      <c r="H99" s="134"/>
+        <v>235</v>
+      </c>
+      <c r="H99" s="143"/>
     </row>
     <row r="100" spans="2:8" ht="15.75" customHeight="1">
       <c r="B100" s="38" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C100" s="14">
         <v>140</v>
@@ -6154,18 +6153,18 @@
       <c r="D100" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E100" s="145"/>
+      <c r="E100" s="134"/>
       <c r="F100" s="56" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="G100" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H100" s="134"/>
+      <c r="H100" s="143"/>
     </row>
     <row r="101" spans="2:8" ht="15.75" customHeight="1">
       <c r="B101" s="38" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C101" s="14">
         <v>55</v>
@@ -6173,18 +6172,18 @@
       <c r="D101" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E101" s="145"/>
+      <c r="E101" s="134"/>
       <c r="F101" s="56" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="G101" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H101" s="134"/>
+      <c r="H101" s="143"/>
     </row>
     <row r="102" spans="2:8" ht="15.75" customHeight="1">
       <c r="B102" s="38" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C102" s="14">
         <v>130</v>
@@ -6192,18 +6191,18 @@
       <c r="D102" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E102" s="145"/>
+      <c r="E102" s="134"/>
       <c r="F102" s="56" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="G102" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H102" s="134"/>
+      <c r="H102" s="143"/>
     </row>
     <row r="103" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B103" s="51" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C103" s="17">
         <v>40</v>
@@ -6211,18 +6210,18 @@
       <c r="D103" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E103" s="148"/>
+      <c r="E103" s="135"/>
       <c r="F103" s="57" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="G103" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="H103" s="136"/>
+      <c r="H103" s="144"/>
     </row>
     <row r="104" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B104" s="61" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C104" s="22">
         <v>450</v>
@@ -6230,7 +6229,7 @@
       <c r="D104" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E104" s="144">
+      <c r="E104" s="133">
         <v>125</v>
       </c>
       <c r="F104" s="31" t="s">
@@ -6239,8 +6238,8 @@
       <c r="G104" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="H104" s="133" t="s">
-        <v>417</v>
+      <c r="H104" s="142" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="105" spans="2:8" ht="15.75" customHeight="1">
@@ -6253,18 +6252,18 @@
       <c r="D105" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E105" s="145"/>
+      <c r="E105" s="134"/>
       <c r="F105" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G105" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H105" s="134"/>
+      <c r="H105" s="143"/>
     </row>
     <row r="106" spans="2:8" ht="15.75" customHeight="1">
       <c r="B106" s="44" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="C106" s="14">
         <v>140</v>
@@ -6272,14 +6271,14 @@
       <c r="D106" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E106" s="145"/>
+      <c r="E106" s="134"/>
       <c r="F106" s="15" t="s">
         <v>62</v>
       </c>
       <c r="G106" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H106" s="134"/>
+      <c r="H106" s="143"/>
     </row>
     <row r="107" spans="2:8" ht="15.75" customHeight="1">
       <c r="B107" s="44" t="s">
@@ -6291,18 +6290,18 @@
       <c r="D107" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E107" s="145"/>
+      <c r="E107" s="134"/>
       <c r="F107" s="15" t="s">
         <v>75</v>
       </c>
       <c r="G107" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H107" s="134"/>
+      <c r="H107" s="143"/>
     </row>
     <row r="108" spans="2:8" ht="15.75" customHeight="1">
       <c r="B108" s="44" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C108" s="14">
         <v>130</v>
@@ -6310,18 +6309,18 @@
       <c r="D108" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E108" s="145"/>
+      <c r="E108" s="134"/>
       <c r="F108" s="15" t="s">
         <v>64</v>
       </c>
       <c r="G108" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H108" s="134"/>
+      <c r="H108" s="143"/>
     </row>
     <row r="109" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B109" s="66" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C109" s="33">
         <v>40</v>
@@ -6329,18 +6328,18 @@
       <c r="D109" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E109" s="146"/>
+      <c r="E109" s="136"/>
       <c r="F109" s="34" t="s">
         <v>65</v>
       </c>
       <c r="G109" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="H109" s="136"/>
+      <c r="H109" s="144"/>
     </row>
     <row r="110" spans="2:8" ht="25.5" customHeight="1" thickTop="1">
       <c r="B110" s="36" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="C110" s="22">
         <v>450</v>
@@ -6348,22 +6347,22 @@
       <c r="D110" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E110" s="144">
+      <c r="E110" s="133">
         <v>125</v>
       </c>
       <c r="F110" s="72" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="G110" s="37" t="s">
-        <v>370</v>
-      </c>
-      <c r="H110" s="133" t="s">
-        <v>417</v>
+        <v>360</v>
+      </c>
+      <c r="H110" s="142" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="111" spans="2:8" ht="15.75" customHeight="1">
       <c r="B111" s="38" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C111" s="14">
         <v>80</v>
@@ -6371,18 +6370,18 @@
       <c r="D111" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E111" s="145"/>
+      <c r="E111" s="134"/>
       <c r="F111" s="56" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="G111" s="54" t="s">
-        <v>369</v>
-      </c>
-      <c r="H111" s="134"/>
+        <v>359</v>
+      </c>
+      <c r="H111" s="143"/>
     </row>
     <row r="112" spans="2:8" ht="15.75" customHeight="1">
       <c r="B112" s="38" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C112" s="14">
         <v>140</v>
@@ -6390,18 +6389,18 @@
       <c r="D112" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E112" s="145"/>
+      <c r="E112" s="134"/>
       <c r="F112" s="56" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="G112" s="54" t="s">
-        <v>373</v>
-      </c>
-      <c r="H112" s="134"/>
+        <v>363</v>
+      </c>
+      <c r="H112" s="143"/>
     </row>
     <row r="113" spans="2:12" ht="15.75" customHeight="1">
       <c r="B113" s="38" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="C113" s="14">
         <v>60</v>
@@ -6409,18 +6408,18 @@
       <c r="D113" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E113" s="145"/>
+      <c r="E113" s="134"/>
       <c r="F113" s="56" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="G113" s="54" t="s">
-        <v>369</v>
-      </c>
-      <c r="H113" s="134"/>
+        <v>359</v>
+      </c>
+      <c r="H113" s="143"/>
     </row>
     <row r="114" spans="2:12" ht="15.75" customHeight="1">
       <c r="B114" s="38" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="C114" s="14">
         <v>130</v>
@@ -6428,18 +6427,18 @@
       <c r="D114" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E114" s="145"/>
+      <c r="E114" s="134"/>
       <c r="F114" s="56" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="G114" s="54" t="s">
-        <v>369</v>
-      </c>
-      <c r="H114" s="134"/>
+        <v>359</v>
+      </c>
+      <c r="H114" s="143"/>
     </row>
     <row r="115" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B115" s="51" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="C115" s="17">
         <v>40</v>
@@ -6447,18 +6446,18 @@
       <c r="D115" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E115" s="148"/>
+      <c r="E115" s="135"/>
       <c r="F115" s="57" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="G115" s="54" t="s">
-        <v>379</v>
-      </c>
-      <c r="H115" s="136"/>
+        <v>369</v>
+      </c>
+      <c r="H115" s="144"/>
     </row>
     <row r="116" spans="2:12" ht="25.9" thickTop="1">
       <c r="B116" s="68" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C116" s="22">
         <v>630</v>
@@ -6466,17 +6465,17 @@
       <c r="D116" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E116" s="144">
+      <c r="E116" s="133">
         <v>143</v>
       </c>
       <c r="F116" s="31" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="G116" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="H116" s="133" t="s">
-        <v>428</v>
+      <c r="H116" s="142" t="s">
+        <v>418</v>
       </c>
       <c r="I116" s="29"/>
       <c r="J116" s="29"/>
@@ -6485,7 +6484,7 @@
     </row>
     <row r="117" spans="2:12" ht="15.75" customHeight="1">
       <c r="B117" s="70" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C117" s="14">
         <v>110</v>
@@ -6493,14 +6492,14 @@
       <c r="D117" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E117" s="145"/>
+      <c r="E117" s="134"/>
       <c r="F117" s="15" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="G117" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H117" s="134"/>
+      <c r="H117" s="143"/>
       <c r="I117" s="29"/>
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
@@ -6508,7 +6507,7 @@
     </row>
     <row r="118" spans="2:12" ht="15.75" customHeight="1">
       <c r="B118" s="70" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="C118" s="14">
         <v>190</v>
@@ -6516,14 +6515,14 @@
       <c r="D118" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E118" s="145"/>
+      <c r="E118" s="134"/>
       <c r="F118" s="15" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="G118" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H118" s="134"/>
+      <c r="H118" s="143"/>
       <c r="I118" s="29"/>
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
@@ -6531,7 +6530,7 @@
     </row>
     <row r="119" spans="2:12" ht="15.75" customHeight="1">
       <c r="B119" s="70" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C119" s="14">
         <v>90</v>
@@ -6539,14 +6538,14 @@
       <c r="D119" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E119" s="145"/>
+      <c r="E119" s="134"/>
       <c r="F119" s="15" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="G119" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H119" s="134"/>
+      <c r="H119" s="143"/>
       <c r="I119" s="29"/>
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
@@ -6554,7 +6553,7 @@
     </row>
     <row r="120" spans="2:12" ht="15.75" customHeight="1">
       <c r="B120" s="70" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="C120" s="14">
         <v>180</v>
@@ -6562,14 +6561,14 @@
       <c r="D120" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E120" s="145"/>
+      <c r="E120" s="134"/>
       <c r="F120" s="15" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="G120" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H120" s="134"/>
+      <c r="H120" s="143"/>
       <c r="I120" s="29"/>
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
@@ -6577,7 +6576,7 @@
     </row>
     <row r="121" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B121" s="71" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="C121" s="24">
         <v>60</v>
@@ -6585,14 +6584,14 @@
       <c r="D121" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E121" s="146"/>
+      <c r="E121" s="136"/>
       <c r="F121" s="26" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="G121" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="H121" s="136"/>
+      <c r="H121" s="144"/>
       <c r="I121" s="29"/>
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
@@ -6608,17 +6607,17 @@
       <c r="D122" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E122" s="144">
+      <c r="E122" s="133">
         <v>125</v>
       </c>
       <c r="F122" s="72" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="G122" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="H122" s="133" t="s">
-        <v>417</v>
+      <c r="H122" s="142" t="s">
+        <v>407</v>
       </c>
       <c r="I122" s="29"/>
       <c r="J122" s="29"/>
@@ -6635,14 +6634,14 @@
       <c r="D123" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E123" s="145"/>
+      <c r="E123" s="134"/>
       <c r="F123" s="56" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="G123" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H123" s="134"/>
+      <c r="H123" s="143"/>
       <c r="I123" s="29"/>
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
@@ -6658,14 +6657,14 @@
       <c r="D124" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E124" s="145"/>
+      <c r="E124" s="134"/>
       <c r="F124" s="56" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="G124" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H124" s="134"/>
+      <c r="H124" s="143"/>
       <c r="I124" s="29"/>
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
@@ -6681,14 +6680,14 @@
       <c r="D125" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E125" s="145"/>
+      <c r="E125" s="134"/>
       <c r="F125" s="56" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="G125" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H125" s="134"/>
+      <c r="H125" s="143"/>
       <c r="I125" s="29"/>
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
@@ -6704,14 +6703,14 @@
       <c r="D126" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E126" s="145"/>
+      <c r="E126" s="134"/>
       <c r="F126" s="56" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="G126" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H126" s="134"/>
+      <c r="H126" s="143"/>
       <c r="I126" s="29"/>
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
@@ -6719,7 +6718,7 @@
     </row>
     <row r="127" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B127" s="39" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="C127" s="24">
         <v>60</v>
@@ -6727,14 +6726,14 @@
       <c r="D127" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E127" s="146"/>
+      <c r="E127" s="136"/>
       <c r="F127" s="73" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="G127" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="H127" s="136"/>
+      <c r="H127" s="144"/>
       <c r="I127" s="29"/>
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
@@ -6750,17 +6749,17 @@
       <c r="D128" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E128" s="144">
+      <c r="E128" s="133">
         <v>143</v>
       </c>
       <c r="F128" s="72" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="G128" s="48" t="s">
         <v>84</v>
       </c>
-      <c r="H128" s="133" t="s">
-        <v>417</v>
+      <c r="H128" s="142" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="129" spans="2:12" ht="15.75" customHeight="1">
@@ -6773,18 +6772,18 @@
       <c r="D129" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E129" s="145"/>
+      <c r="E129" s="134"/>
       <c r="F129" s="56" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="G129" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="H129" s="134"/>
+      <c r="H129" s="143"/>
     </row>
     <row r="130" spans="2:12" ht="15.75" customHeight="1">
       <c r="B130" s="70" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="C130" s="14">
         <v>190</v>
@@ -6792,18 +6791,18 @@
       <c r="D130" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E130" s="145"/>
+      <c r="E130" s="134"/>
       <c r="F130" s="56" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="G130" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H130" s="134"/>
+      <c r="H130" s="143"/>
     </row>
     <row r="131" spans="2:12" ht="15.75" customHeight="1">
       <c r="B131" s="74" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="C131" s="14">
         <v>90</v>
@@ -6811,18 +6810,18 @@
       <c r="D131" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E131" s="145"/>
+      <c r="E131" s="134"/>
       <c r="F131" s="56" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="G131" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H131" s="134"/>
+      <c r="H131" s="143"/>
     </row>
     <row r="132" spans="2:12" ht="15.75" customHeight="1">
       <c r="B132" s="74" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C132" s="14">
         <v>180</v>
@@ -6830,18 +6829,18 @@
       <c r="D132" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E132" s="145"/>
+      <c r="E132" s="134"/>
       <c r="F132" s="56" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="G132" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H132" s="134"/>
+      <c r="H132" s="143"/>
     </row>
     <row r="133" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B133" s="71" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="C133" s="24">
         <v>60</v>
@@ -6849,14 +6848,14 @@
       <c r="D133" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E133" s="146"/>
+      <c r="E133" s="136"/>
       <c r="F133" s="73" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="G133" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="H133" s="136"/>
+      <c r="H133" s="144"/>
     </row>
     <row r="134" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B134" s="75" t="s">
@@ -6868,17 +6867,17 @@
       <c r="D134" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E134" s="147">
+      <c r="E134" s="138">
         <v>143</v>
       </c>
       <c r="F134" s="28" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="G134" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H134" s="133" t="s">
-        <v>416</v>
+      <c r="H134" s="142" t="s">
+        <v>406</v>
       </c>
       <c r="I134" s="29"/>
       <c r="J134" s="29"/>
@@ -6895,14 +6894,14 @@
       <c r="D135" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E135" s="145"/>
+      <c r="E135" s="134"/>
       <c r="F135" s="15" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="G135" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H135" s="134"/>
+      <c r="H135" s="143"/>
       <c r="I135" s="29"/>
       <c r="J135" s="29"/>
       <c r="K135" s="29"/>
@@ -6918,14 +6917,14 @@
       <c r="D136" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E136" s="145"/>
+      <c r="E136" s="134"/>
       <c r="F136" s="15" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="G136" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H136" s="134"/>
+      <c r="H136" s="143"/>
       <c r="I136" s="29"/>
       <c r="J136" s="29"/>
       <c r="K136" s="29"/>
@@ -6933,7 +6932,7 @@
     </row>
     <row r="137" spans="2:12" ht="15.75" customHeight="1">
       <c r="B137" s="44" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="C137" s="14">
         <v>80</v>
@@ -6941,14 +6940,14 @@
       <c r="D137" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E137" s="145"/>
+      <c r="E137" s="134"/>
       <c r="F137" s="15" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="G137" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H137" s="134"/>
+      <c r="H137" s="143"/>
       <c r="I137" s="29"/>
       <c r="J137" s="29"/>
       <c r="K137" s="29"/>
@@ -6956,7 +6955,7 @@
     </row>
     <row r="138" spans="2:12" ht="15.75" customHeight="1">
       <c r="B138" s="44" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="C138" s="14">
         <v>170</v>
@@ -6964,14 +6963,14 @@
       <c r="D138" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E138" s="145"/>
+      <c r="E138" s="134"/>
       <c r="F138" s="15" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="G138" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H138" s="134"/>
+      <c r="H138" s="143"/>
       <c r="I138" s="29"/>
       <c r="J138" s="29"/>
       <c r="K138" s="29"/>
@@ -6987,14 +6986,14 @@
       <c r="D139" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E139" s="148"/>
+      <c r="E139" s="135"/>
       <c r="F139" s="19" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="G139" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H139" s="136"/>
+      <c r="H139" s="144"/>
       <c r="I139" s="29"/>
       <c r="J139" s="29"/>
       <c r="K139" s="29"/>
@@ -7010,17 +7009,17 @@
       <c r="D140" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E140" s="144">
+      <c r="E140" s="133">
         <v>143</v>
       </c>
       <c r="F140" s="31" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="G140" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="H140" s="133" t="s">
-        <v>417</v>
+      <c r="H140" s="142" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="141" spans="2:12" ht="15.75" customHeight="1">
@@ -7033,18 +7032,18 @@
       <c r="D141" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E141" s="145"/>
+      <c r="E141" s="134"/>
       <c r="F141" s="15" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="G141" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="H141" s="134"/>
+      <c r="H141" s="143"/>
     </row>
     <row r="142" spans="2:12" ht="15.75" customHeight="1">
       <c r="B142" s="44" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C142" s="14">
         <v>180</v>
@@ -7052,14 +7051,14 @@
       <c r="D142" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E142" s="145"/>
+      <c r="E142" s="134"/>
       <c r="F142" s="15" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="G142" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="H142" s="134"/>
+      <c r="H142" s="143"/>
     </row>
     <row r="143" spans="2:12" ht="15.75" customHeight="1">
       <c r="B143" s="44" t="s">
@@ -7071,18 +7070,18 @@
       <c r="D143" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E143" s="145"/>
+      <c r="E143" s="134"/>
       <c r="F143" s="15" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="G143" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="H143" s="134"/>
+      <c r="H143" s="143"/>
     </row>
     <row r="144" spans="2:12" ht="15.75" customHeight="1">
       <c r="B144" s="44" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C144" s="14">
         <v>170</v>
@@ -7090,18 +7089,18 @@
       <c r="D144" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E144" s="145"/>
+      <c r="E144" s="134"/>
       <c r="F144" s="15" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="G144" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="H144" s="134"/>
+      <c r="H144" s="143"/>
     </row>
     <row r="145" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B145" s="64" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="C145" s="17">
         <v>50</v>
@@ -7109,41 +7108,41 @@
       <c r="D145" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E145" s="148"/>
+      <c r="E145" s="135"/>
       <c r="F145" s="19" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="G145" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="H145" s="136"/>
+      <c r="H145" s="144"/>
     </row>
     <row r="146" spans="1:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B146" s="112" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="C146" s="22">
         <v>615</v>
       </c>
       <c r="D146" s="79" t="s">
-        <v>333</v>
-      </c>
-      <c r="E146" s="144">
+        <v>323</v>
+      </c>
+      <c r="E146" s="133">
         <v>143</v>
       </c>
       <c r="F146" s="47" t="s">
         <v>66</v>
       </c>
       <c r="G146" s="48" t="s">
-        <v>334</v>
-      </c>
-      <c r="H146" s="140" t="s">
-        <v>421</v>
+        <v>324</v>
+      </c>
+      <c r="H146" s="145" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:12" ht="15.75" customHeight="1">
       <c r="B147" s="44" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="C147" s="14">
         <v>105</v>
@@ -7151,18 +7150,18 @@
       <c r="D147" s="80" t="s">
         <v>99</v>
       </c>
-      <c r="E147" s="145"/>
+      <c r="E147" s="134"/>
       <c r="F147" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G147" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H147" s="138"/>
+      <c r="H147" s="146"/>
     </row>
     <row r="148" spans="1:12" ht="15.75" customHeight="1">
       <c r="B148" s="44" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="C148" s="14">
         <v>190</v>
@@ -7170,18 +7169,18 @@
       <c r="D148" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="E148" s="145"/>
+      <c r="E148" s="134"/>
       <c r="F148" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G148" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H148" s="138"/>
+      <c r="H148" s="146"/>
     </row>
     <row r="149" spans="1:12" ht="15.75" customHeight="1">
       <c r="B149" s="44" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="C149" s="14">
         <v>85</v>
@@ -7189,18 +7188,18 @@
       <c r="D149" s="80" t="s">
         <v>99</v>
       </c>
-      <c r="E149" s="145"/>
+      <c r="E149" s="134"/>
       <c r="F149" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G149" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H149" s="138"/>
+      <c r="H149" s="146"/>
     </row>
     <row r="150" spans="1:12" ht="15.75" customHeight="1">
       <c r="B150" s="44" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="C150" s="14">
         <v>180</v>
@@ -7208,18 +7207,18 @@
       <c r="D150" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="E150" s="145"/>
+      <c r="E150" s="134"/>
       <c r="F150" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G150" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H150" s="138"/>
+      <c r="H150" s="146"/>
     </row>
     <row r="151" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B151" s="64" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="C151" s="17">
         <v>55</v>
@@ -7227,131 +7226,131 @@
       <c r="D151" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="E151" s="148"/>
+      <c r="E151" s="135"/>
       <c r="F151" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G151" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H151" s="139"/>
+      <c r="H151" s="147"/>
     </row>
     <row r="152" spans="1:12" ht="13.5" thickTop="1">
       <c r="A152" s="111"/>
       <c r="B152" s="110" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="C152" s="22">
         <v>615</v>
       </c>
       <c r="D152" s="109" t="s">
-        <v>392</v>
-      </c>
-      <c r="E152" s="144">
+        <v>382</v>
+      </c>
+      <c r="E152" s="133">
         <v>143</v>
       </c>
       <c r="F152" s="47" t="s">
         <v>66</v>
       </c>
       <c r="G152" s="114" t="s">
-        <v>388</v>
-      </c>
-      <c r="H152" s="140" t="s">
-        <v>421</v>
+        <v>378</v>
+      </c>
+      <c r="H152" s="145" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="153" spans="1:12" ht="15.75" customHeight="1">
       <c r="B153" s="113" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C153" s="14">
         <v>105</v>
       </c>
       <c r="D153" s="109" t="s">
-        <v>385</v>
-      </c>
-      <c r="E153" s="145"/>
+        <v>375</v>
+      </c>
+      <c r="E153" s="134"/>
       <c r="F153" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G153" s="12"/>
-      <c r="H153" s="138"/>
+      <c r="H153" s="146"/>
     </row>
     <row r="154" spans="1:12" ht="15.75" customHeight="1">
       <c r="B154" s="113" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C154" s="14">
         <v>190</v>
       </c>
       <c r="D154" s="109" t="s">
-        <v>387</v>
-      </c>
-      <c r="E154" s="145"/>
+        <v>377</v>
+      </c>
+      <c r="E154" s="134"/>
       <c r="F154" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G154" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H154" s="138"/>
+      <c r="H154" s="146"/>
     </row>
     <row r="155" spans="1:12" ht="15.75" customHeight="1">
       <c r="B155" s="113" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C155" s="14">
         <v>85</v>
       </c>
       <c r="D155" s="109" t="s">
-        <v>385</v>
-      </c>
-      <c r="E155" s="145"/>
+        <v>375</v>
+      </c>
+      <c r="E155" s="134"/>
       <c r="F155" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G155" s="12"/>
-      <c r="H155" s="138"/>
+      <c r="H155" s="146"/>
     </row>
     <row r="156" spans="1:12" ht="15.75" customHeight="1">
       <c r="B156" s="113" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C156" s="14">
         <v>180</v>
       </c>
       <c r="D156" s="109" t="s">
-        <v>387</v>
-      </c>
-      <c r="E156" s="145"/>
+        <v>377</v>
+      </c>
+      <c r="E156" s="134"/>
       <c r="F156" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G156" s="12"/>
-      <c r="H156" s="138"/>
+      <c r="H156" s="146"/>
     </row>
     <row r="157" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B157" s="116" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="C157" s="17">
         <v>55</v>
       </c>
       <c r="D157" s="109" t="s">
-        <v>385</v>
-      </c>
-      <c r="E157" s="148"/>
+        <v>375</v>
+      </c>
+      <c r="E157" s="135"/>
       <c r="F157" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G157" s="115" t="s">
         <v>46</v>
       </c>
-      <c r="H157" s="139"/>
+      <c r="H157" s="147"/>
     </row>
     <row r="158" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B158" s="82" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C158" s="22">
         <v>580</v>
@@ -7359,17 +7358,17 @@
       <c r="D158" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E158" s="144">
+      <c r="E158" s="133">
         <v>167</v>
       </c>
       <c r="F158" s="31" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="G158" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H158" s="133" t="s">
-        <v>417</v>
+      <c r="H158" s="142" t="s">
+        <v>407</v>
       </c>
       <c r="I158" s="29"/>
       <c r="J158" s="29"/>
@@ -7378,7 +7377,7 @@
     </row>
     <row r="159" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B159" s="84" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C159" s="14">
         <v>100</v>
@@ -7386,14 +7385,14 @@
       <c r="D159" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E159" s="145"/>
+      <c r="E159" s="134"/>
       <c r="F159" s="15" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="G159" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H159" s="134"/>
+      <c r="H159" s="143"/>
       <c r="I159" s="29"/>
       <c r="J159" s="29"/>
       <c r="K159" s="29"/>
@@ -7401,7 +7400,7 @@
     </row>
     <row r="160" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B160" s="84" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="C160" s="14">
         <v>180</v>
@@ -7409,14 +7408,14 @@
       <c r="D160" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E160" s="145"/>
+      <c r="E160" s="134"/>
       <c r="F160" s="15" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="G160" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H160" s="134"/>
+      <c r="H160" s="143"/>
       <c r="I160" s="29"/>
       <c r="J160" s="29"/>
       <c r="K160" s="29"/>
@@ -7424,7 +7423,7 @@
     </row>
     <row r="161" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B161" s="84" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="C161" s="14">
         <v>80</v>
@@ -7432,14 +7431,14 @@
       <c r="D161" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E161" s="145"/>
+      <c r="E161" s="134"/>
       <c r="F161" s="15" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G161" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H161" s="134"/>
+      <c r="H161" s="143"/>
       <c r="I161" s="29"/>
       <c r="J161" s="29"/>
       <c r="K161" s="29"/>
@@ -7447,7 +7446,7 @@
     </row>
     <row r="162" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B162" s="84" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="C162" s="14">
         <v>170</v>
@@ -7455,14 +7454,14 @@
       <c r="D162" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E162" s="145"/>
+      <c r="E162" s="134"/>
       <c r="F162" s="15" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="G162" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H162" s="134"/>
+      <c r="H162" s="143"/>
       <c r="I162" s="29"/>
       <c r="J162" s="29"/>
       <c r="K162" s="29"/>
@@ -7470,7 +7469,7 @@
     </row>
     <row r="163" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B163" s="85" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C163" s="17">
         <v>50</v>
@@ -7478,14 +7477,14 @@
       <c r="D163" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E163" s="148"/>
+      <c r="E163" s="135"/>
       <c r="F163" s="19" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="G163" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="H163" s="136"/>
+      <c r="H163" s="144"/>
       <c r="I163" s="29"/>
       <c r="J163" s="29"/>
       <c r="K163" s="29"/>
@@ -7501,17 +7500,17 @@
       <c r="D164" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E164" s="144">
+      <c r="E164" s="133">
         <v>125</v>
       </c>
       <c r="F164" s="58" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="G164" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="H164" s="133" t="s">
-        <v>417</v>
+      <c r="H164" s="142" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="165" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
@@ -7524,18 +7523,18 @@
       <c r="D165" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E165" s="145"/>
+      <c r="E165" s="134"/>
       <c r="F165" s="56" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G165" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H165" s="134"/>
+      <c r="H165" s="143"/>
     </row>
     <row r="166" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B166" s="38" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="C166" s="14">
         <v>180</v>
@@ -7543,14 +7542,14 @@
       <c r="D166" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E166" s="145"/>
+      <c r="E166" s="134"/>
       <c r="F166" s="56" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="G166" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H166" s="134"/>
+      <c r="H166" s="143"/>
     </row>
     <row r="167" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B167" s="38" t="s">
@@ -7562,18 +7561,18 @@
       <c r="D167" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E167" s="145"/>
+      <c r="E167" s="134"/>
       <c r="F167" s="56" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="G167" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H167" s="134"/>
+      <c r="H167" s="143"/>
     </row>
     <row r="168" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B168" s="87" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="C168" s="14">
         <v>170</v>
@@ -7581,18 +7580,18 @@
       <c r="D168" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E168" s="145"/>
+      <c r="E168" s="134"/>
       <c r="F168" s="56" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G168" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H168" s="134"/>
+      <c r="H168" s="143"/>
     </row>
     <row r="169" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B169" s="51" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="C169" s="17">
         <v>50</v>
@@ -7600,18 +7599,18 @@
       <c r="D169" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E169" s="148"/>
+      <c r="E169" s="135"/>
       <c r="F169" s="57" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="G169" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H169" s="136"/>
+      <c r="H169" s="144"/>
     </row>
     <row r="170" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B170" s="40" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="C170" s="9">
         <v>580</v>
@@ -7619,7 +7618,7 @@
       <c r="D170" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E170" s="149">
+      <c r="E170" s="137">
         <v>200</v>
       </c>
       <c r="F170" s="50" t="s">
@@ -7628,8 +7627,8 @@
       <c r="G170" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H170" s="133" t="s">
-        <v>422</v>
+      <c r="H170" s="142" t="s">
+        <v>412</v>
       </c>
       <c r="I170" s="29"/>
       <c r="J170" s="29"/>
@@ -7638,7 +7637,7 @@
     </row>
     <row r="171" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B171" s="44" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="C171" s="14">
         <v>100</v>
@@ -7646,14 +7645,14 @@
       <c r="D171" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E171" s="145"/>
+      <c r="E171" s="134"/>
       <c r="F171" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G171" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="H171" s="134"/>
+      <c r="H171" s="143"/>
       <c r="I171" s="29"/>
       <c r="J171" s="29"/>
       <c r="K171" s="29"/>
@@ -7661,7 +7660,7 @@
     </row>
     <row r="172" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B172" s="44" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C172" s="14">
         <v>180</v>
@@ -7669,14 +7668,14 @@
       <c r="D172" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E172" s="145"/>
+      <c r="E172" s="134"/>
       <c r="F172" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G172" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="H172" s="134"/>
+      <c r="H172" s="143"/>
       <c r="I172" s="29"/>
       <c r="J172" s="29"/>
       <c r="K172" s="29"/>
@@ -7684,7 +7683,7 @@
     </row>
     <row r="173" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B173" s="44" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="C173" s="14">
         <v>80</v>
@@ -7692,14 +7691,14 @@
       <c r="D173" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E173" s="145"/>
+      <c r="E173" s="134"/>
       <c r="F173" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G173" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="H173" s="134"/>
+      <c r="H173" s="143"/>
       <c r="I173" s="29"/>
       <c r="J173" s="29"/>
       <c r="K173" s="29"/>
@@ -7707,7 +7706,7 @@
     </row>
     <row r="174" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B174" s="44" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="C174" s="14">
         <v>170</v>
@@ -7715,14 +7714,14 @@
       <c r="D174" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E174" s="145"/>
+      <c r="E174" s="134"/>
       <c r="F174" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G174" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="H174" s="134"/>
+      <c r="H174" s="143"/>
       <c r="I174" s="29"/>
       <c r="J174" s="29"/>
       <c r="K174" s="29"/>
@@ -7730,7 +7729,7 @@
     </row>
     <row r="175" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B175" s="60" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="C175" s="24">
         <v>50</v>
@@ -7738,14 +7737,14 @@
       <c r="D175" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E175" s="146"/>
+      <c r="E175" s="136"/>
       <c r="F175" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G175" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="H175" s="136"/>
+      <c r="H175" s="144"/>
       <c r="I175" s="29"/>
       <c r="J175" s="29"/>
       <c r="K175" s="29"/>
@@ -7761,17 +7760,17 @@
       <c r="D176" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E176" s="144">
+      <c r="E176" s="133">
         <v>125</v>
       </c>
       <c r="F176" s="58" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="G176" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="H176" s="133" t="s">
-        <v>417</v>
+      <c r="H176" s="142" t="s">
+        <v>407</v>
       </c>
       <c r="I176" s="29"/>
       <c r="J176" s="29"/>
@@ -7788,14 +7787,14 @@
       <c r="D177" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E177" s="145"/>
+      <c r="E177" s="134"/>
       <c r="F177" s="56" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="G177" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="H177" s="134"/>
+      <c r="H177" s="143"/>
       <c r="I177" s="29"/>
       <c r="J177" s="29"/>
       <c r="K177" s="29"/>
@@ -7811,14 +7810,14 @@
       <c r="D178" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E178" s="145"/>
+      <c r="E178" s="134"/>
       <c r="F178" s="56" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="G178" s="78" t="s">
         <v>113</v>
       </c>
-      <c r="H178" s="134"/>
+      <c r="H178" s="143"/>
       <c r="I178" s="29"/>
       <c r="J178" s="29"/>
       <c r="K178" s="29"/>
@@ -7834,14 +7833,14 @@
       <c r="D179" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E179" s="145"/>
+      <c r="E179" s="134"/>
       <c r="F179" s="56" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="G179" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="H179" s="134"/>
+      <c r="H179" s="143"/>
       <c r="I179" s="29"/>
       <c r="J179" s="29"/>
       <c r="K179" s="29"/>
@@ -7849,7 +7848,7 @@
     </row>
     <row r="180" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B180" s="38" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="C180" s="14">
         <v>170</v>
@@ -7857,14 +7856,14 @@
       <c r="D180" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E180" s="145"/>
+      <c r="E180" s="134"/>
       <c r="F180" s="56" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="G180" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="H180" s="134"/>
+      <c r="H180" s="143"/>
       <c r="I180" s="29"/>
       <c r="J180" s="29"/>
       <c r="K180" s="29"/>
@@ -7872,7 +7871,7 @@
     </row>
     <row r="181" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B181" s="51" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="C181" s="17">
         <v>50</v>
@@ -7880,14 +7879,14 @@
       <c r="D181" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E181" s="148"/>
+      <c r="E181" s="135"/>
       <c r="F181" s="88" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="G181" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="H181" s="136"/>
+      <c r="H181" s="144"/>
       <c r="I181" s="29"/>
       <c r="J181" s="29"/>
       <c r="K181" s="29"/>
@@ -7903,17 +7902,17 @@
       <c r="D182" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E182" s="147">
+      <c r="E182" s="138">
         <v>167</v>
       </c>
       <c r="F182" s="28" t="s">
+        <v>316</v>
+      </c>
+      <c r="G182" s="54" t="s">
         <v>326</v>
       </c>
-      <c r="G182" s="54" t="s">
-        <v>336</v>
-      </c>
-      <c r="H182" s="133" t="s">
-        <v>416</v>
+      <c r="H182" s="142" t="s">
+        <v>406</v>
       </c>
       <c r="I182" s="29"/>
       <c r="J182" s="29"/>
@@ -7930,14 +7929,14 @@
       <c r="D183" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E183" s="145"/>
+      <c r="E183" s="134"/>
       <c r="F183" s="15" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="G183" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H183" s="134"/>
+      <c r="H183" s="143"/>
       <c r="I183" s="29"/>
       <c r="J183" s="29"/>
       <c r="K183" s="29"/>
@@ -7953,18 +7952,18 @@
       <c r="D184" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E184" s="145"/>
+      <c r="E184" s="134"/>
       <c r="F184" s="15" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="G184" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H184" s="134"/>
+      <c r="H184" s="143"/>
     </row>
     <row r="185" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B185" s="42" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C185" s="14">
         <v>120</v>
@@ -7972,14 +7971,14 @@
       <c r="D185" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E185" s="145"/>
+      <c r="E185" s="134"/>
       <c r="F185" s="15" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="G185" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H185" s="134"/>
+      <c r="H185" s="143"/>
     </row>
     <row r="186" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B186" s="44" t="s">
@@ -7991,14 +7990,14 @@
       <c r="D186" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E186" s="145"/>
+      <c r="E186" s="134"/>
       <c r="F186" s="15" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="G186" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H186" s="134"/>
+      <c r="H186" s="143"/>
       <c r="I186" s="29"/>
       <c r="J186" s="29"/>
       <c r="K186" s="29"/>
@@ -8006,7 +8005,7 @@
     </row>
     <row r="187" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B187" s="64" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C187" s="17">
         <v>80</v>
@@ -8014,14 +8013,14 @@
       <c r="D187" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E187" s="148"/>
+      <c r="E187" s="135"/>
       <c r="F187" s="19" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="G187" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="H187" s="135"/>
+      <c r="H187" s="148"/>
       <c r="I187" s="29"/>
       <c r="J187" s="29"/>
       <c r="K187" s="29"/>
@@ -8037,17 +8036,17 @@
       <c r="D188" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E188" s="144">
+      <c r="E188" s="133">
         <v>167</v>
       </c>
       <c r="F188" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G188" s="54" t="s">
-        <v>331</v>
-      </c>
-      <c r="H188" s="133" t="s">
-        <v>429</v>
+        <v>321</v>
+      </c>
+      <c r="H188" s="142" t="s">
+        <v>419</v>
       </c>
       <c r="I188" s="29"/>
       <c r="J188" s="29"/>
@@ -8056,7 +8055,7 @@
     </row>
     <row r="189" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B189" s="44" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="C189" s="14">
         <v>160</v>
@@ -8064,14 +8063,14 @@
       <c r="D189" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E189" s="145"/>
+      <c r="E189" s="134"/>
       <c r="F189" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G189" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H189" s="134"/>
+      <c r="H189" s="143"/>
       <c r="I189" s="29"/>
       <c r="J189" s="29"/>
       <c r="K189" s="29"/>
@@ -8079,7 +8078,7 @@
     </row>
     <row r="190" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B190" s="44" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="C190" s="14">
         <v>270</v>
@@ -8087,14 +8086,14 @@
       <c r="D190" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E190" s="145"/>
+      <c r="E190" s="134"/>
       <c r="F190" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G190" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H190" s="134"/>
+      <c r="H190" s="143"/>
       <c r="I190" s="29"/>
       <c r="J190" s="29"/>
       <c r="K190" s="29"/>
@@ -8110,14 +8109,14 @@
       <c r="D191" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E191" s="145"/>
+      <c r="E191" s="134"/>
       <c r="F191" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G191" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H191" s="134"/>
+      <c r="H191" s="143"/>
       <c r="I191" s="29"/>
       <c r="J191" s="29"/>
       <c r="K191" s="29"/>
@@ -8125,7 +8124,7 @@
     </row>
     <row r="192" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B192" s="44" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="C192" s="14">
         <v>260</v>
@@ -8133,14 +8132,14 @@
       <c r="D192" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E192" s="145"/>
+      <c r="E192" s="134"/>
       <c r="F192" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G192" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H192" s="134"/>
+      <c r="H192" s="143"/>
       <c r="I192" s="29"/>
       <c r="J192" s="29"/>
       <c r="K192" s="29"/>
@@ -8148,7 +8147,7 @@
     </row>
     <row r="193" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B193" s="60" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C193" s="24">
         <v>95</v>
@@ -8156,14 +8155,14 @@
       <c r="D193" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E193" s="146"/>
+      <c r="E193" s="136"/>
       <c r="F193" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G193" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="H193" s="135"/>
+      <c r="H193" s="148"/>
       <c r="I193" s="29"/>
       <c r="J193" s="29"/>
       <c r="K193" s="29"/>
@@ -8179,7 +8178,7 @@
       <c r="D194" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E194" s="144">
+      <c r="E194" s="133">
         <v>143</v>
       </c>
       <c r="F194" s="72" t="s">
@@ -8188,13 +8187,13 @@
       <c r="G194" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="H194" s="133" t="s">
-        <v>417</v>
+      <c r="H194" s="142" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="195" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B195" s="38" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C195" s="14">
         <v>140</v>
@@ -8202,18 +8201,18 @@
       <c r="D195" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E195" s="145"/>
+      <c r="E195" s="134"/>
       <c r="F195" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G195" s="54" t="s">
         <v>125</v>
       </c>
-      <c r="H195" s="134"/>
+      <c r="H195" s="143"/>
     </row>
     <row r="196" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B196" s="38" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C196" s="14">
         <v>240</v>
@@ -8221,18 +8220,18 @@
       <c r="D196" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E196" s="145"/>
+      <c r="E196" s="134"/>
       <c r="F196" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G196" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H196" s="134"/>
+      <c r="H196" s="143"/>
     </row>
     <row r="197" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B197" s="38" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C197" s="14">
         <v>120</v>
@@ -8240,18 +8239,18 @@
       <c r="D197" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E197" s="145"/>
+      <c r="E197" s="134"/>
       <c r="F197" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G197" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H197" s="134"/>
+      <c r="H197" s="143"/>
     </row>
     <row r="198" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B198" s="38" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C198" s="14">
         <v>230</v>
@@ -8259,18 +8258,18 @@
       <c r="D198" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E198" s="145"/>
+      <c r="E198" s="134"/>
       <c r="F198" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G198" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H198" s="134"/>
+      <c r="H198" s="143"/>
     </row>
     <row r="199" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B199" s="39" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="C199" s="24">
         <v>80</v>
@@ -8278,14 +8277,14 @@
       <c r="D199" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E199" s="146"/>
+      <c r="E199" s="136"/>
       <c r="F199" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G199" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="H199" s="136"/>
+      <c r="H199" s="144"/>
     </row>
     <row r="200" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B200" s="68" t="s">
@@ -8298,15 +8297,15 @@
       <c r="D200" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E200" s="144">
+      <c r="E200" s="133">
         <v>233</v>
       </c>
       <c r="F200" s="72"/>
       <c r="G200" s="48" t="s">
-        <v>344</v>
-      </c>
-      <c r="H200" s="137" t="s">
-        <v>419</v>
+        <v>334</v>
+      </c>
+      <c r="H200" s="149" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="201" spans="2:12" ht="15.75" customHeight="1">
@@ -8319,14 +8318,14 @@
       <c r="D201" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E201" s="145"/>
+      <c r="E201" s="134"/>
       <c r="F201" s="50"/>
       <c r="G201" s="12"/>
-      <c r="H201" s="138"/>
+      <c r="H201" s="146"/>
     </row>
     <row r="202" spans="2:12" ht="15.75" customHeight="1">
       <c r="B202" s="70" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="C202" s="14">
         <v>270</v>
@@ -8334,12 +8333,12 @@
       <c r="D202" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E202" s="145"/>
+      <c r="E202" s="134"/>
       <c r="F202" s="50"/>
       <c r="G202" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H202" s="138"/>
+      <c r="H202" s="146"/>
     </row>
     <row r="203" spans="2:12" ht="15.75" customHeight="1">
       <c r="B203" s="70" t="s">
@@ -8351,16 +8350,16 @@
       <c r="D203" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E203" s="145"/>
+      <c r="E203" s="134"/>
       <c r="F203" s="50"/>
       <c r="G203" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H203" s="138"/>
+      <c r="H203" s="146"/>
     </row>
     <row r="204" spans="2:12" ht="15.75" customHeight="1">
       <c r="B204" s="70" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C204" s="14">
         <v>260</v>
@@ -8368,16 +8367,16 @@
       <c r="D204" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E204" s="145"/>
+      <c r="E204" s="134"/>
       <c r="F204" s="50"/>
       <c r="G204" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H204" s="138"/>
+      <c r="H204" s="146"/>
     </row>
     <row r="205" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B205" s="71" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="C205" s="24">
         <v>95</v>
@@ -8385,16 +8384,16 @@
       <c r="D205" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E205" s="146"/>
+      <c r="E205" s="136"/>
       <c r="F205" s="89"/>
       <c r="G205" s="90" t="s">
         <v>120</v>
       </c>
-      <c r="H205" s="139"/>
+      <c r="H205" s="147"/>
     </row>
     <row r="206" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B206" s="117" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="C206" s="22">
         <v>1110</v>
@@ -8402,22 +8401,22 @@
       <c r="D206" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E206" s="144">
+      <c r="E206" s="133">
         <v>167</v>
       </c>
       <c r="F206" s="127" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="G206" s="114" t="s">
-        <v>395</v>
-      </c>
-      <c r="H206" s="133" t="s">
-        <v>417</v>
+        <v>385</v>
+      </c>
+      <c r="H206" s="142" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="207" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B207" s="74" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="C207" s="14">
         <v>200</v>
@@ -8425,18 +8424,18 @@
       <c r="D207" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E207" s="145"/>
+      <c r="E207" s="134"/>
       <c r="F207" s="127" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="G207" s="119" t="s">
-        <v>397</v>
-      </c>
-      <c r="H207" s="134"/>
+        <v>387</v>
+      </c>
+      <c r="H207" s="143"/>
     </row>
     <row r="208" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B208" s="125" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C208" s="14">
         <v>300</v>
@@ -8444,18 +8443,18 @@
       <c r="D208" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E208" s="145"/>
+      <c r="E208" s="134"/>
       <c r="F208" s="127" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="G208" s="120" t="s">
-        <v>396</v>
-      </c>
-      <c r="H208" s="134"/>
+        <v>386</v>
+      </c>
+      <c r="H208" s="143"/>
     </row>
     <row r="209" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B209" s="125" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="C209" s="14">
         <v>180</v>
@@ -8463,18 +8462,18 @@
       <c r="D209" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E209" s="145"/>
+      <c r="E209" s="134"/>
       <c r="F209" s="127" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="G209" s="119" t="s">
-        <v>397</v>
-      </c>
-      <c r="H209" s="134"/>
+        <v>387</v>
+      </c>
+      <c r="H209" s="143"/>
     </row>
     <row r="210" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B210" s="125" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="C210" s="14">
         <v>290</v>
@@ -8482,18 +8481,18 @@
       <c r="D210" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E210" s="145"/>
+      <c r="E210" s="134"/>
       <c r="F210" s="127" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="G210" s="122" t="s">
-        <v>397</v>
-      </c>
-      <c r="H210" s="134"/>
+        <v>387</v>
+      </c>
+      <c r="H210" s="143"/>
     </row>
     <row r="211" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B211" s="126" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="C211" s="24">
         <v>140</v>
@@ -8501,18 +8500,18 @@
       <c r="D211" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E211" s="146"/>
+      <c r="E211" s="136"/>
       <c r="F211" s="127" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="G211" s="121" t="s">
-        <v>397</v>
-      </c>
-      <c r="H211" s="136"/>
+        <v>387</v>
+      </c>
+      <c r="H211" s="144"/>
     </row>
     <row r="212" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B212" s="117" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C212" s="22">
         <f>C213+C214+C215+C216+C217</f>
@@ -8521,22 +8520,22 @@
       <c r="D212" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E212" s="141">
+      <c r="E212" s="139">
         <v>167</v>
       </c>
       <c r="F212" s="127" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="G212" s="114" t="s">
-        <v>404</v>
-      </c>
-      <c r="H212" s="133" t="s">
-        <v>417</v>
+        <v>394</v>
+      </c>
+      <c r="H212" s="142" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="213" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B213" s="74" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="C213" s="14">
         <v>200</v>
@@ -8544,18 +8543,18 @@
       <c r="D213" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E213" s="142"/>
+      <c r="E213" s="140"/>
       <c r="F213" s="127" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="G213" s="118" t="s">
-        <v>406</v>
-      </c>
-      <c r="H213" s="134"/>
+        <v>396</v>
+      </c>
+      <c r="H213" s="143"/>
     </row>
     <row r="214" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B214" s="125" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C214" s="14">
         <v>300</v>
@@ -8563,18 +8562,18 @@
       <c r="D214" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E214" s="142"/>
+      <c r="E214" s="140"/>
       <c r="F214" s="127" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="G214" s="118" t="s">
-        <v>408</v>
-      </c>
-      <c r="H214" s="134"/>
+        <v>398</v>
+      </c>
+      <c r="H214" s="143"/>
     </row>
     <row r="215" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B215" s="125" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="C215" s="14">
         <v>180</v>
@@ -8582,18 +8581,18 @@
       <c r="D215" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E215" s="142"/>
+      <c r="E215" s="140"/>
       <c r="F215" s="127" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="G215" s="118" t="s">
-        <v>406</v>
-      </c>
-      <c r="H215" s="134"/>
+        <v>396</v>
+      </c>
+      <c r="H215" s="143"/>
     </row>
     <row r="216" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B216" s="125" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="C216" s="14">
         <v>290</v>
@@ -8601,18 +8600,18 @@
       <c r="D216" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E216" s="142"/>
+      <c r="E216" s="140"/>
       <c r="F216" s="127" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="G216" s="118" t="s">
-        <v>406</v>
-      </c>
-      <c r="H216" s="134"/>
+        <v>396</v>
+      </c>
+      <c r="H216" s="143"/>
     </row>
     <row r="217" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B217" s="126" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C217" s="123">
         <v>140</v>
@@ -8620,14 +8619,14 @@
       <c r="D217" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="E217" s="143"/>
+      <c r="E217" s="141"/>
       <c r="F217" s="127" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="G217" s="119" t="s">
-        <v>409</v>
-      </c>
-      <c r="H217" s="136"/>
+        <v>399</v>
+      </c>
+      <c r="H217" s="144"/>
     </row>
     <row r="218" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B218" s="91" t="s">
@@ -8643,13 +8642,13 @@
         <v>100</v>
       </c>
       <c r="F218" s="94" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="G218" s="59" t="s">
         <v>17</v>
       </c>
       <c r="H218" s="128" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
     </row>
     <row r="219" spans="2:8" ht="15.75" customHeight="1">
@@ -8672,12 +8671,12 @@
         <v>7</v>
       </c>
       <c r="H219" s="128" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
     </row>
     <row r="220" spans="2:8" ht="15.75" customHeight="1">
       <c r="B220" s="44" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="C220" s="14">
         <v>30</v>
@@ -8695,7 +8694,7 @@
         <v>7</v>
       </c>
       <c r="H220" s="129" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
     </row>
     <row r="221" spans="2:8" ht="15.75" customHeight="1">
@@ -8712,18 +8711,18 @@
         <v>100</v>
       </c>
       <c r="F221" s="15" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="G221" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H221" s="128" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
     </row>
     <row r="222" spans="2:8" ht="15.75" customHeight="1">
       <c r="B222" s="13" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="C222" s="14">
         <v>58</v>
@@ -8735,18 +8734,18 @@
         <v>100</v>
       </c>
       <c r="F222" s="96" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="G222" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H222" s="128" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
     </row>
     <row r="223" spans="2:8" ht="15.75" customHeight="1">
       <c r="B223" s="38" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="C223" s="14">
         <v>60</v>
@@ -8764,7 +8763,7 @@
         <v>132</v>
       </c>
       <c r="H223" s="130" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
     </row>
     <row r="224" spans="2:8" ht="15.75" customHeight="1">
@@ -8787,7 +8786,7 @@
         <v>7</v>
       </c>
       <c r="H224" s="128" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
     </row>
     <row r="225" spans="2:8" ht="15.75" customHeight="1">
@@ -8810,12 +8809,12 @@
         <v>7</v>
       </c>
       <c r="H225" s="128" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
     </row>
     <row r="226" spans="2:8" ht="15.75" customHeight="1">
       <c r="B226" s="97" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="C226" s="14">
         <v>100</v>
@@ -8833,7 +8832,7 @@
         <v>7</v>
       </c>
       <c r="H226" s="128" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
     </row>
     <row r="227" spans="2:8" ht="15.75" customHeight="1">
@@ -8850,13 +8849,13 @@
         <v>143</v>
       </c>
       <c r="F227" s="15" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="G227" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H227" s="128" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
     </row>
     <row r="228" spans="2:8" ht="15.75" customHeight="1">
@@ -8879,7 +8878,7 @@
         <v>45</v>
       </c>
       <c r="H228" s="128" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
     </row>
     <row r="229" spans="2:8" ht="15.75" customHeight="1">
@@ -8902,12 +8901,12 @@
         <v>7</v>
       </c>
       <c r="H229" s="129" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
     </row>
     <row r="230" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B230" s="131" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="C230" s="24">
         <v>200</v>
@@ -8925,7 +8924,7 @@
         <v>140</v>
       </c>
       <c r="H230" s="132" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
     </row>
     <row r="231" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
@@ -13792,38 +13791,30 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="72">
-    <mergeCell ref="E140:E145"/>
-    <mergeCell ref="E146:E151"/>
-    <mergeCell ref="E158:E163"/>
-    <mergeCell ref="E194:E199"/>
-    <mergeCell ref="E200:E205"/>
-    <mergeCell ref="E164:E169"/>
-    <mergeCell ref="E170:E175"/>
-    <mergeCell ref="E176:E181"/>
-    <mergeCell ref="E182:E187"/>
-    <mergeCell ref="E188:E193"/>
-    <mergeCell ref="E152:E157"/>
-    <mergeCell ref="E92:E97"/>
-    <mergeCell ref="E98:E103"/>
-    <mergeCell ref="E104:E109"/>
-    <mergeCell ref="E116:E121"/>
-    <mergeCell ref="E122:E127"/>
-    <mergeCell ref="E110:E115"/>
-    <mergeCell ref="E62:E67"/>
-    <mergeCell ref="E68:E73"/>
-    <mergeCell ref="E74:E79"/>
-    <mergeCell ref="E80:E85"/>
-    <mergeCell ref="E86:E91"/>
-    <mergeCell ref="E32:E37"/>
-    <mergeCell ref="E38:E43"/>
-    <mergeCell ref="E44:E49"/>
-    <mergeCell ref="E50:E55"/>
-    <mergeCell ref="E56:E61"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="E8:E13"/>
-    <mergeCell ref="E14:E19"/>
-    <mergeCell ref="E20:E25"/>
-    <mergeCell ref="E26:E31"/>
+    <mergeCell ref="H188:H193"/>
+    <mergeCell ref="H194:H199"/>
+    <mergeCell ref="H200:H205"/>
+    <mergeCell ref="H206:H211"/>
+    <mergeCell ref="H92:H97"/>
+    <mergeCell ref="H98:H103"/>
+    <mergeCell ref="H104:H109"/>
+    <mergeCell ref="H110:H115"/>
+    <mergeCell ref="H116:H121"/>
+    <mergeCell ref="H62:H67"/>
+    <mergeCell ref="H68:H73"/>
+    <mergeCell ref="H74:H79"/>
+    <mergeCell ref="H80:H85"/>
+    <mergeCell ref="H86:H91"/>
+    <mergeCell ref="H32:H37"/>
+    <mergeCell ref="H38:H43"/>
+    <mergeCell ref="H44:H49"/>
+    <mergeCell ref="H50:H55"/>
+    <mergeCell ref="H56:H61"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="H8:H13"/>
+    <mergeCell ref="H14:H19"/>
+    <mergeCell ref="H20:H25"/>
+    <mergeCell ref="H26:H31"/>
     <mergeCell ref="E212:E217"/>
     <mergeCell ref="E206:E211"/>
     <mergeCell ref="H122:H127"/>
@@ -13840,30 +13831,38 @@
     <mergeCell ref="E134:E139"/>
     <mergeCell ref="H212:H217"/>
     <mergeCell ref="H182:H187"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="H8:H13"/>
-    <mergeCell ref="H14:H19"/>
-    <mergeCell ref="H20:H25"/>
-    <mergeCell ref="H26:H31"/>
-    <mergeCell ref="H32:H37"/>
-    <mergeCell ref="H38:H43"/>
-    <mergeCell ref="H44:H49"/>
-    <mergeCell ref="H50:H55"/>
-    <mergeCell ref="H56:H61"/>
-    <mergeCell ref="H62:H67"/>
-    <mergeCell ref="H68:H73"/>
-    <mergeCell ref="H74:H79"/>
-    <mergeCell ref="H80:H85"/>
-    <mergeCell ref="H86:H91"/>
-    <mergeCell ref="H188:H193"/>
-    <mergeCell ref="H194:H199"/>
-    <mergeCell ref="H200:H205"/>
-    <mergeCell ref="H206:H211"/>
-    <mergeCell ref="H92:H97"/>
-    <mergeCell ref="H98:H103"/>
-    <mergeCell ref="H104:H109"/>
-    <mergeCell ref="H110:H115"/>
-    <mergeCell ref="H116:H121"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="E8:E13"/>
+    <mergeCell ref="E14:E19"/>
+    <mergeCell ref="E20:E25"/>
+    <mergeCell ref="E26:E31"/>
+    <mergeCell ref="E32:E37"/>
+    <mergeCell ref="E38:E43"/>
+    <mergeCell ref="E44:E49"/>
+    <mergeCell ref="E50:E55"/>
+    <mergeCell ref="E56:E61"/>
+    <mergeCell ref="E62:E67"/>
+    <mergeCell ref="E68:E73"/>
+    <mergeCell ref="E74:E79"/>
+    <mergeCell ref="E80:E85"/>
+    <mergeCell ref="E86:E91"/>
+    <mergeCell ref="E92:E97"/>
+    <mergeCell ref="E98:E103"/>
+    <mergeCell ref="E104:E109"/>
+    <mergeCell ref="E116:E121"/>
+    <mergeCell ref="E122:E127"/>
+    <mergeCell ref="E110:E115"/>
+    <mergeCell ref="E140:E145"/>
+    <mergeCell ref="E146:E151"/>
+    <mergeCell ref="E158:E163"/>
+    <mergeCell ref="E194:E199"/>
+    <mergeCell ref="E200:E205"/>
+    <mergeCell ref="E164:E169"/>
+    <mergeCell ref="E170:E175"/>
+    <mergeCell ref="E176:E181"/>
+    <mergeCell ref="E182:E187"/>
+    <mergeCell ref="E188:E193"/>
+    <mergeCell ref="E152:E157"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-source/护甲数据.xlsx
+++ b/data-source/护甲数据.xlsx
@@ -3702,46 +3702,46 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4069,7 +4069,7 @@
       <c r="D2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="137">
+      <c r="E2" s="149">
         <v>91</v>
       </c>
       <c r="F2" s="11" t="s">
@@ -4078,7 +4078,7 @@
       <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="142" t="s">
+      <c r="H2" s="133" t="s">
         <v>406</v>
       </c>
     </row>
@@ -4092,14 +4092,14 @@
       <c r="D3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="134"/>
+      <c r="E3" s="145"/>
       <c r="F3" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="143"/>
+      <c r="H3" s="134"/>
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1">
       <c r="B4" s="13" t="s">
@@ -4111,14 +4111,14 @@
       <c r="D4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="134"/>
+      <c r="E4" s="145"/>
       <c r="F4" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="143"/>
+      <c r="H4" s="134"/>
     </row>
     <row r="5" spans="2:8" ht="15.75" customHeight="1">
       <c r="B5" s="13" t="s">
@@ -4130,14 +4130,14 @@
       <c r="D5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="134"/>
+      <c r="E5" s="145"/>
       <c r="F5" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="143"/>
+      <c r="H5" s="134"/>
     </row>
     <row r="6" spans="2:8" ht="15.75" customHeight="1">
       <c r="B6" s="13" t="s">
@@ -4149,14 +4149,14 @@
       <c r="D6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="134"/>
+      <c r="E6" s="145"/>
       <c r="F6" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="143"/>
+      <c r="H6" s="134"/>
     </row>
     <row r="7" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B7" s="16" t="s">
@@ -4168,14 +4168,14 @@
       <c r="D7" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="135"/>
+      <c r="E7" s="148"/>
       <c r="F7" s="19" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="144"/>
+      <c r="H7" s="136"/>
     </row>
     <row r="8" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B8" s="21" t="s">
@@ -4187,7 +4187,7 @@
       <c r="D8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="133">
+      <c r="E8" s="144">
         <v>91</v>
       </c>
       <c r="F8" s="11" t="s">
@@ -4196,7 +4196,7 @@
       <c r="G8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="142" t="s">
+      <c r="H8" s="133" t="s">
         <v>407</v>
       </c>
     </row>
@@ -4210,14 +4210,14 @@
       <c r="D9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="134"/>
+      <c r="E9" s="145"/>
       <c r="F9" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="143"/>
+      <c r="H9" s="134"/>
     </row>
     <row r="10" spans="2:8" ht="15.75" customHeight="1">
       <c r="B10" s="13" t="s">
@@ -4229,14 +4229,14 @@
       <c r="D10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="134"/>
+      <c r="E10" s="145"/>
       <c r="F10" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="143"/>
+      <c r="H10" s="134"/>
     </row>
     <row r="11" spans="2:8" ht="15.75" customHeight="1">
       <c r="B11" s="13" t="s">
@@ -4248,14 +4248,14 @@
       <c r="D11" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="134"/>
+      <c r="E11" s="145"/>
       <c r="F11" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="143"/>
+      <c r="H11" s="134"/>
     </row>
     <row r="12" spans="2:8" ht="15.75" customHeight="1">
       <c r="B12" s="13" t="s">
@@ -4267,14 +4267,14 @@
       <c r="D12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="134"/>
+      <c r="E12" s="145"/>
       <c r="F12" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="143"/>
+      <c r="H12" s="134"/>
     </row>
     <row r="13" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B13" s="23" t="s">
@@ -4286,14 +4286,14 @@
       <c r="D13" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="136"/>
+      <c r="E13" s="146"/>
       <c r="F13" s="26" t="s">
         <v>9</v>
       </c>
       <c r="G13" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="144"/>
+      <c r="H13" s="136"/>
     </row>
     <row r="14" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B14" s="8" t="s">
@@ -4305,7 +4305,7 @@
       <c r="D14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="138">
+      <c r="E14" s="147">
         <v>100</v>
       </c>
       <c r="F14" s="28" t="s">
@@ -4314,7 +4314,7 @@
       <c r="G14" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="142" t="s">
+      <c r="H14" s="133" t="s">
         <v>406</v>
       </c>
     </row>
@@ -4328,14 +4328,14 @@
       <c r="D15" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="134"/>
+      <c r="E15" s="145"/>
       <c r="F15" s="15" t="s">
         <v>338</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H15" s="143"/>
+      <c r="H15" s="134"/>
     </row>
     <row r="16" spans="2:8" ht="15.75" customHeight="1">
       <c r="B16" s="13" t="s">
@@ -4347,14 +4347,14 @@
       <c r="D16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="134"/>
+      <c r="E16" s="145"/>
       <c r="F16" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="143"/>
+      <c r="H16" s="134"/>
     </row>
     <row r="17" spans="2:12" ht="15.75" customHeight="1">
       <c r="B17" s="13" t="s">
@@ -4366,14 +4366,14 @@
       <c r="D17" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="134"/>
+      <c r="E17" s="145"/>
       <c r="F17" s="15" t="s">
         <v>340</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H17" s="143"/>
+      <c r="H17" s="134"/>
       <c r="I17" s="29"/>
       <c r="J17" s="29"/>
       <c r="K17" s="29"/>
@@ -4389,14 +4389,14 @@
       <c r="D18" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="134"/>
+      <c r="E18" s="145"/>
       <c r="F18" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="143"/>
+      <c r="H18" s="134"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
       <c r="K18" s="29"/>
@@ -4412,14 +4412,14 @@
       <c r="D19" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="135"/>
+      <c r="E19" s="148"/>
       <c r="F19" s="19" t="s">
         <v>341</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="144"/>
+      <c r="H19" s="136"/>
       <c r="I19" s="29"/>
       <c r="J19" s="29"/>
       <c r="K19" s="29"/>
@@ -4435,7 +4435,7 @@
       <c r="D20" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="133">
+      <c r="E20" s="144">
         <v>100</v>
       </c>
       <c r="F20" s="11" t="s">
@@ -4444,7 +4444,7 @@
       <c r="G20" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="H20" s="142" t="s">
+      <c r="H20" s="133" t="s">
         <v>408</v>
       </c>
     </row>
@@ -4458,14 +4458,14 @@
       <c r="D21" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="134"/>
+      <c r="E21" s="145"/>
       <c r="F21" s="15" t="s">
         <v>338</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H21" s="143"/>
+      <c r="H21" s="134"/>
     </row>
     <row r="22" spans="2:12" ht="15.75" customHeight="1">
       <c r="B22" s="13" t="s">
@@ -4477,14 +4477,14 @@
       <c r="D22" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="134"/>
+      <c r="E22" s="145"/>
       <c r="F22" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H22" s="143"/>
+      <c r="H22" s="134"/>
     </row>
     <row r="23" spans="2:12" ht="15.75" customHeight="1">
       <c r="B23" s="13" t="s">
@@ -4496,14 +4496,14 @@
       <c r="D23" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="134"/>
+      <c r="E23" s="145"/>
       <c r="F23" s="15" t="s">
         <v>340</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H23" s="143"/>
+      <c r="H23" s="134"/>
     </row>
     <row r="24" spans="2:12" ht="15.75" customHeight="1">
       <c r="B24" s="13" t="s">
@@ -4515,14 +4515,14 @@
       <c r="D24" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="134"/>
+      <c r="E24" s="145"/>
       <c r="F24" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H24" s="143"/>
+      <c r="H24" s="134"/>
     </row>
     <row r="25" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B25" s="107" t="s">
@@ -4534,14 +4534,14 @@
       <c r="D25" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="135"/>
+      <c r="E25" s="148"/>
       <c r="F25" s="19" t="s">
         <v>341</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H25" s="144"/>
+      <c r="H25" s="136"/>
     </row>
     <row r="26" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B26" s="21" t="s">
@@ -4553,7 +4553,7 @@
       <c r="D26" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="133">
+      <c r="E26" s="144">
         <v>100</v>
       </c>
       <c r="F26" s="31" t="s">
@@ -4562,7 +4562,7 @@
       <c r="G26" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H26" s="142" t="s">
+      <c r="H26" s="133" t="s">
         <v>407</v>
       </c>
     </row>
@@ -4576,14 +4576,14 @@
       <c r="D27" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="134"/>
+      <c r="E27" s="145"/>
       <c r="F27" s="15" t="s">
         <v>338</v>
       </c>
       <c r="G27" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H27" s="143"/>
+      <c r="H27" s="134"/>
     </row>
     <row r="28" spans="2:12" ht="15.75" customHeight="1">
       <c r="B28" s="13" t="s">
@@ -4595,14 +4595,14 @@
       <c r="D28" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="134"/>
+      <c r="E28" s="145"/>
       <c r="F28" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H28" s="143"/>
+      <c r="H28" s="134"/>
     </row>
     <row r="29" spans="2:12" ht="15.75" customHeight="1">
       <c r="B29" s="13" t="s">
@@ -4614,14 +4614,14 @@
       <c r="D29" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="134"/>
+      <c r="E29" s="145"/>
       <c r="F29" s="15" t="s">
         <v>340</v>
       </c>
       <c r="G29" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H29" s="143"/>
+      <c r="H29" s="134"/>
     </row>
     <row r="30" spans="2:12" ht="15.75" customHeight="1">
       <c r="B30" s="13" t="s">
@@ -4633,14 +4633,14 @@
       <c r="D30" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="134"/>
+      <c r="E30" s="145"/>
       <c r="F30" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H30" s="143"/>
+      <c r="H30" s="134"/>
     </row>
     <row r="31" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B31" s="32" t="s">
@@ -4652,14 +4652,14 @@
       <c r="D31" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="136"/>
+      <c r="E31" s="146"/>
       <c r="F31" s="34" t="s">
         <v>341</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H31" s="144"/>
+      <c r="H31" s="136"/>
     </row>
     <row r="32" spans="2:12" ht="25.9" thickTop="1">
       <c r="B32" s="36" t="s">
@@ -4671,7 +4671,7 @@
       <c r="D32" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="133">
+      <c r="E32" s="144">
         <v>112</v>
       </c>
       <c r="F32" s="31" t="s">
@@ -4680,7 +4680,7 @@
       <c r="G32" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="H32" s="142" t="s">
+      <c r="H32" s="133" t="s">
         <v>407</v>
       </c>
       <c r="I32" s="29"/>
@@ -4698,14 +4698,14 @@
       <c r="D33" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="134"/>
+      <c r="E33" s="145"/>
       <c r="F33" s="15" t="s">
         <v>343</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H33" s="143"/>
+      <c r="H33" s="134"/>
       <c r="I33" s="29"/>
       <c r="J33" s="29"/>
       <c r="K33" s="29"/>
@@ -4721,14 +4721,14 @@
       <c r="D34" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="134"/>
+      <c r="E34" s="145"/>
       <c r="F34" s="15" t="s">
         <v>344</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="143"/>
+      <c r="H34" s="134"/>
       <c r="I34" s="29"/>
       <c r="J34" s="29"/>
       <c r="K34" s="29"/>
@@ -4744,14 +4744,14 @@
       <c r="D35" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="134"/>
+      <c r="E35" s="145"/>
       <c r="F35" s="15" t="s">
         <v>345</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H35" s="143"/>
+      <c r="H35" s="134"/>
       <c r="I35" s="29"/>
       <c r="J35" s="29"/>
       <c r="K35" s="29"/>
@@ -4767,14 +4767,14 @@
       <c r="D36" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="134"/>
+      <c r="E36" s="145"/>
       <c r="F36" s="15" t="s">
         <v>346</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H36" s="143"/>
+      <c r="H36" s="134"/>
       <c r="I36" s="29"/>
       <c r="J36" s="29"/>
       <c r="K36" s="29"/>
@@ -4790,14 +4790,14 @@
       <c r="D37" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E37" s="136"/>
+      <c r="E37" s="146"/>
       <c r="F37" s="26" t="s">
         <v>347</v>
       </c>
       <c r="G37" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="H37" s="144"/>
+      <c r="H37" s="136"/>
       <c r="I37" s="29"/>
       <c r="J37" s="29"/>
       <c r="K37" s="29"/>
@@ -4813,7 +4813,7 @@
       <c r="D38" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="133">
+      <c r="E38" s="144">
         <v>100</v>
       </c>
       <c r="F38" s="11" t="s">
@@ -4822,7 +4822,7 @@
       <c r="G38" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="H38" s="142" t="s">
+      <c r="H38" s="133" t="s">
         <v>407</v>
       </c>
       <c r="I38" s="29"/>
@@ -4840,14 +4840,14 @@
       <c r="D39" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E39" s="134"/>
+      <c r="E39" s="145"/>
       <c r="F39" s="15" t="s">
         <v>338</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H39" s="143"/>
+      <c r="H39" s="134"/>
       <c r="I39" s="29"/>
       <c r="J39" s="29"/>
       <c r="K39" s="29"/>
@@ -4863,14 +4863,14 @@
       <c r="D40" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E40" s="134"/>
+      <c r="E40" s="145"/>
       <c r="F40" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G40" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H40" s="143"/>
+      <c r="H40" s="134"/>
       <c r="I40" s="29"/>
       <c r="J40" s="29"/>
       <c r="K40" s="29"/>
@@ -4886,14 +4886,14 @@
       <c r="D41" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E41" s="134"/>
+      <c r="E41" s="145"/>
       <c r="F41" s="15" t="s">
         <v>340</v>
       </c>
       <c r="G41" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H41" s="143"/>
+      <c r="H41" s="134"/>
       <c r="I41" s="29"/>
       <c r="J41" s="29"/>
       <c r="K41" s="29"/>
@@ -4909,14 +4909,14 @@
       <c r="D42" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E42" s="134"/>
+      <c r="E42" s="145"/>
       <c r="F42" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G42" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="143"/>
+      <c r="H42" s="134"/>
       <c r="I42" s="29"/>
       <c r="J42" s="29"/>
       <c r="K42" s="29"/>
@@ -4932,14 +4932,14 @@
       <c r="D43" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E43" s="136"/>
+      <c r="E43" s="146"/>
       <c r="F43" s="26" t="s">
         <v>341</v>
       </c>
       <c r="G43" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="H43" s="144"/>
+      <c r="H43" s="136"/>
       <c r="I43" s="29"/>
       <c r="J43" s="29"/>
       <c r="K43" s="29"/>
@@ -4955,7 +4955,7 @@
       <c r="D44" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E44" s="137">
+      <c r="E44" s="149">
         <v>112</v>
       </c>
       <c r="F44" s="11" t="s">
@@ -4964,7 +4964,7 @@
       <c r="G44" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H44" s="142" t="s">
+      <c r="H44" s="133" t="s">
         <v>406</v>
       </c>
       <c r="I44" s="29"/>
@@ -4982,14 +4982,14 @@
       <c r="D45" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E45" s="134"/>
+      <c r="E45" s="145"/>
       <c r="F45" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G45" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H45" s="143"/>
+      <c r="H45" s="134"/>
       <c r="I45" s="29"/>
       <c r="J45" s="29"/>
       <c r="K45" s="29"/>
@@ -5005,14 +5005,14 @@
       <c r="D46" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E46" s="134"/>
+      <c r="E46" s="145"/>
       <c r="F46" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G46" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H46" s="143"/>
+      <c r="H46" s="134"/>
       <c r="I46" s="29"/>
       <c r="J46" s="29"/>
       <c r="K46" s="29"/>
@@ -5028,14 +5028,14 @@
       <c r="D47" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E47" s="134"/>
+      <c r="E47" s="145"/>
       <c r="F47" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G47" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H47" s="143"/>
+      <c r="H47" s="134"/>
       <c r="I47" s="29"/>
       <c r="J47" s="29"/>
       <c r="K47" s="29"/>
@@ -5051,14 +5051,14 @@
       <c r="D48" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E48" s="134"/>
+      <c r="E48" s="145"/>
       <c r="F48" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G48" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H48" s="143"/>
+      <c r="H48" s="134"/>
       <c r="I48" s="29"/>
       <c r="J48" s="29"/>
       <c r="K48" s="29"/>
@@ -5074,14 +5074,14 @@
       <c r="D49" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E49" s="135"/>
+      <c r="E49" s="148"/>
       <c r="F49" s="19" t="s">
         <v>349</v>
       </c>
       <c r="G49" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H49" s="144"/>
+      <c r="H49" s="136"/>
       <c r="I49" s="29"/>
       <c r="J49" s="29"/>
       <c r="K49" s="29"/>
@@ -5097,7 +5097,7 @@
       <c r="D50" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E50" s="133">
+      <c r="E50" s="144">
         <v>112</v>
       </c>
       <c r="F50" s="15" t="s">
@@ -5106,7 +5106,7 @@
       <c r="G50" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H50" s="142" t="s">
+      <c r="H50" s="133" t="s">
         <v>409</v>
       </c>
     </row>
@@ -5120,14 +5120,14 @@
       <c r="D51" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E51" s="134"/>
+      <c r="E51" s="145"/>
       <c r="F51" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G51" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H51" s="143"/>
+      <c r="H51" s="134"/>
     </row>
     <row r="52" spans="2:12" ht="15.75" customHeight="1">
       <c r="B52" s="13" t="s">
@@ -5139,14 +5139,14 @@
       <c r="D52" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E52" s="134"/>
+      <c r="E52" s="145"/>
       <c r="F52" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G52" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H52" s="143"/>
+      <c r="H52" s="134"/>
     </row>
     <row r="53" spans="2:12" ht="15.75" customHeight="1">
       <c r="B53" s="13" t="s">
@@ -5158,14 +5158,14 @@
       <c r="D53" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E53" s="134"/>
+      <c r="E53" s="145"/>
       <c r="F53" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G53" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H53" s="143"/>
+      <c r="H53" s="134"/>
     </row>
     <row r="54" spans="2:12" ht="15.75" customHeight="1">
       <c r="B54" s="13" t="s">
@@ -5177,14 +5177,14 @@
       <c r="D54" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E54" s="134"/>
+      <c r="E54" s="145"/>
       <c r="F54" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H54" s="143"/>
+      <c r="H54" s="134"/>
     </row>
     <row r="55" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B55" s="16" t="s">
@@ -5196,14 +5196,14 @@
       <c r="D55" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E55" s="135"/>
+      <c r="E55" s="148"/>
       <c r="F55" s="19" t="s">
         <v>349</v>
       </c>
       <c r="G55" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H55" s="144"/>
+      <c r="H55" s="136"/>
     </row>
     <row r="56" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B56" s="36" t="s">
@@ -5215,7 +5215,7 @@
       <c r="D56" s="63" t="s">
         <v>182</v>
       </c>
-      <c r="E56" s="133">
+      <c r="E56" s="144">
         <v>112</v>
       </c>
       <c r="F56" s="47" t="s">
@@ -5224,7 +5224,7 @@
       <c r="G56" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="H56" s="142" t="s">
+      <c r="H56" s="133" t="s">
         <v>410</v>
       </c>
     </row>
@@ -5238,14 +5238,14 @@
       <c r="D57" s="63" t="s">
         <v>180</v>
       </c>
-      <c r="E57" s="134"/>
+      <c r="E57" s="145"/>
       <c r="F57" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G57" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H57" s="143"/>
+      <c r="H57" s="134"/>
     </row>
     <row r="58" spans="2:12" ht="15.75" customHeight="1">
       <c r="B58" s="38" t="s">
@@ -5257,14 +5257,14 @@
       <c r="D58" s="63" t="s">
         <v>181</v>
       </c>
-      <c r="E58" s="134"/>
+      <c r="E58" s="145"/>
       <c r="F58" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G58" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H58" s="143"/>
+      <c r="H58" s="134"/>
     </row>
     <row r="59" spans="2:12" ht="15.75" customHeight="1">
       <c r="B59" s="38" t="s">
@@ -5276,14 +5276,14 @@
       <c r="D59" s="63" t="s">
         <v>180</v>
       </c>
-      <c r="E59" s="134"/>
+      <c r="E59" s="145"/>
       <c r="F59" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G59" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H59" s="143"/>
+      <c r="H59" s="134"/>
     </row>
     <row r="60" spans="2:12" ht="15.75" customHeight="1">
       <c r="B60" s="38" t="s">
@@ -5295,14 +5295,14 @@
       <c r="D60" s="63" t="s">
         <v>181</v>
       </c>
-      <c r="E60" s="134"/>
+      <c r="E60" s="145"/>
       <c r="F60" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G60" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H60" s="143"/>
+      <c r="H60" s="134"/>
     </row>
     <row r="61" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B61" s="51" t="s">
@@ -5314,14 +5314,14 @@
       <c r="D61" s="63" t="s">
         <v>180</v>
       </c>
-      <c r="E61" s="135"/>
+      <c r="E61" s="148"/>
       <c r="F61" s="53" t="s">
         <v>7</v>
       </c>
       <c r="G61" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H61" s="144"/>
+      <c r="H61" s="136"/>
     </row>
     <row r="62" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B62" s="36" t="s">
@@ -5333,7 +5333,7 @@
       <c r="D62" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E62" s="133">
+      <c r="E62" s="144">
         <v>143</v>
       </c>
       <c r="F62" s="31" t="s">
@@ -5342,7 +5342,7 @@
       <c r="G62" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="H62" s="142" t="s">
+      <c r="H62" s="133" t="s">
         <v>407</v>
       </c>
       <c r="I62" s="29"/>
@@ -5360,14 +5360,14 @@
       <c r="D63" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E63" s="134"/>
+      <c r="E63" s="145"/>
       <c r="F63" s="15" t="s">
         <v>423</v>
       </c>
       <c r="G63" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H63" s="143"/>
+      <c r="H63" s="134"/>
       <c r="I63" s="29"/>
       <c r="J63" s="29"/>
       <c r="K63" s="29"/>
@@ -5383,14 +5383,14 @@
       <c r="D64" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E64" s="134"/>
+      <c r="E64" s="145"/>
       <c r="F64" s="15" t="s">
         <v>424</v>
       </c>
       <c r="G64" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H64" s="143"/>
+      <c r="H64" s="134"/>
       <c r="I64" s="29"/>
       <c r="J64" s="29"/>
       <c r="K64" s="29"/>
@@ -5406,14 +5406,14 @@
       <c r="D65" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E65" s="134"/>
+      <c r="E65" s="145"/>
       <c r="F65" s="15" t="s">
         <v>425</v>
       </c>
       <c r="G65" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H65" s="143"/>
+      <c r="H65" s="134"/>
       <c r="I65" s="29"/>
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
@@ -5429,14 +5429,14 @@
       <c r="D66" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E66" s="134"/>
+      <c r="E66" s="145"/>
       <c r="F66" s="15" t="s">
         <v>426</v>
       </c>
       <c r="G66" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H66" s="143"/>
+      <c r="H66" s="134"/>
       <c r="I66" s="29"/>
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
@@ -5450,14 +5450,14 @@
         <v>12</v>
       </c>
       <c r="D67" s="18"/>
-      <c r="E67" s="135"/>
+      <c r="E67" s="148"/>
       <c r="F67" s="19" t="s">
         <v>427</v>
       </c>
       <c r="G67" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H67" s="144"/>
+      <c r="H67" s="136"/>
       <c r="I67" s="29"/>
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
@@ -5473,7 +5473,7 @@
       <c r="D68" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E68" s="133">
+      <c r="E68" s="144">
         <v>143</v>
       </c>
       <c r="F68" s="31" t="s">
@@ -5482,7 +5482,7 @@
       <c r="G68" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="H68" s="142" t="s">
+      <c r="H68" s="133" t="s">
         <v>407</v>
       </c>
     </row>
@@ -5496,14 +5496,14 @@
       <c r="D69" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E69" s="134"/>
+      <c r="E69" s="145"/>
       <c r="F69" s="56" t="s">
         <v>201</v>
       </c>
       <c r="G69" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="H69" s="143"/>
+      <c r="H69" s="134"/>
     </row>
     <row r="70" spans="2:12" ht="15.75" customHeight="1">
       <c r="B70" s="38" t="s">
@@ -5515,14 +5515,14 @@
       <c r="D70" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E70" s="134"/>
+      <c r="E70" s="145"/>
       <c r="F70" s="15" t="s">
         <v>202</v>
       </c>
       <c r="G70" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H70" s="143"/>
+      <c r="H70" s="134"/>
     </row>
     <row r="71" spans="2:12" ht="15.75" customHeight="1">
       <c r="B71" s="38" t="s">
@@ -5534,14 +5534,14 @@
       <c r="D71" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E71" s="134"/>
+      <c r="E71" s="145"/>
       <c r="F71" s="56" t="s">
         <v>429</v>
       </c>
       <c r="G71" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H71" s="143"/>
+      <c r="H71" s="134"/>
     </row>
     <row r="72" spans="2:12" ht="15.75" customHeight="1">
       <c r="B72" s="38" t="s">
@@ -5553,14 +5553,14 @@
       <c r="D72" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E72" s="134"/>
+      <c r="E72" s="145"/>
       <c r="F72" s="15" t="s">
         <v>203</v>
       </c>
       <c r="G72" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H72" s="143"/>
+      <c r="H72" s="134"/>
     </row>
     <row r="73" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B73" s="51" t="s">
@@ -5572,14 +5572,14 @@
       <c r="D73" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E73" s="135"/>
+      <c r="E73" s="148"/>
       <c r="F73" s="57" t="s">
         <v>204</v>
       </c>
       <c r="G73" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H73" s="144"/>
+      <c r="H73" s="136"/>
     </row>
     <row r="74" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B74" s="36" t="s">
@@ -5591,7 +5591,7 @@
       <c r="D74" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E74" s="133">
+      <c r="E74" s="144">
         <v>143</v>
       </c>
       <c r="F74" s="58" t="s">
@@ -5600,7 +5600,7 @@
       <c r="G74" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="H74" s="142" t="s">
+      <c r="H74" s="133" t="s">
         <v>407</v>
       </c>
     </row>
@@ -5614,14 +5614,14 @@
       <c r="D75" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E75" s="134"/>
+      <c r="E75" s="145"/>
       <c r="F75" s="56" t="s">
         <v>192</v>
       </c>
       <c r="G75" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="H75" s="143"/>
+      <c r="H75" s="134"/>
     </row>
     <row r="76" spans="2:12" ht="15.75" customHeight="1">
       <c r="B76" s="38" t="s">
@@ -5633,14 +5633,14 @@
       <c r="D76" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E76" s="134"/>
+      <c r="E76" s="145"/>
       <c r="F76" s="56" t="s">
         <v>193</v>
       </c>
       <c r="G76" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H76" s="143"/>
+      <c r="H76" s="134"/>
     </row>
     <row r="77" spans="2:12" ht="15.75" customHeight="1">
       <c r="B77" s="38" t="s">
@@ -5652,14 +5652,14 @@
       <c r="D77" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E77" s="134"/>
+      <c r="E77" s="145"/>
       <c r="F77" s="56" t="s">
         <v>431</v>
       </c>
       <c r="G77" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H77" s="143"/>
+      <c r="H77" s="134"/>
     </row>
     <row r="78" spans="2:12" ht="15.75" customHeight="1">
       <c r="B78" s="38" t="s">
@@ -5671,14 +5671,14 @@
       <c r="D78" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E78" s="134"/>
+      <c r="E78" s="145"/>
       <c r="F78" s="56" t="s">
         <v>194</v>
       </c>
       <c r="G78" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H78" s="143"/>
+      <c r="H78" s="134"/>
     </row>
     <row r="79" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B79" s="51" t="s">
@@ -5690,14 +5690,14 @@
       <c r="D79" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E79" s="135"/>
+      <c r="E79" s="148"/>
       <c r="F79" s="57" t="s">
         <v>192</v>
       </c>
       <c r="G79" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H79" s="144"/>
+      <c r="H79" s="136"/>
     </row>
     <row r="80" spans="2:12" ht="38.65" thickTop="1">
       <c r="B80" s="40" t="s">
@@ -5709,7 +5709,7 @@
       <c r="D80" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E80" s="133">
+      <c r="E80" s="144">
         <v>112</v>
       </c>
       <c r="F80" s="11" t="s">
@@ -5718,7 +5718,7 @@
       <c r="G80" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="H80" s="142" t="s">
+      <c r="H80" s="133" t="s">
         <v>407</v>
       </c>
       <c r="I80" s="29"/>
@@ -5736,14 +5736,14 @@
       <c r="D81" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E81" s="134"/>
+      <c r="E81" s="145"/>
       <c r="F81" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G81" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H81" s="143"/>
+      <c r="H81" s="134"/>
       <c r="I81" s="29"/>
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
@@ -5759,14 +5759,14 @@
       <c r="D82" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E82" s="134"/>
+      <c r="E82" s="145"/>
       <c r="F82" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G82" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H82" s="143"/>
+      <c r="H82" s="134"/>
       <c r="I82" s="29"/>
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
@@ -5782,14 +5782,14 @@
       <c r="D83" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E83" s="134"/>
+      <c r="E83" s="145"/>
       <c r="F83" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G83" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H83" s="143"/>
+      <c r="H83" s="134"/>
       <c r="I83" s="29"/>
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
@@ -5805,14 +5805,14 @@
       <c r="D84" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E84" s="134"/>
+      <c r="E84" s="145"/>
       <c r="F84" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G84" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H84" s="143"/>
+      <c r="H84" s="134"/>
       <c r="I84" s="29"/>
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
@@ -5828,14 +5828,14 @@
       <c r="D85" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E85" s="136"/>
+      <c r="E85" s="146"/>
       <c r="F85" s="26" t="s">
         <v>350</v>
       </c>
       <c r="G85" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H85" s="144"/>
+      <c r="H85" s="136"/>
       <c r="I85" s="29"/>
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
@@ -5851,7 +5851,7 @@
       <c r="D86" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E86" s="137">
+      <c r="E86" s="149">
         <v>125</v>
       </c>
       <c r="F86" s="11" t="s">
@@ -5860,7 +5860,7 @@
       <c r="G86" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H86" s="142" t="s">
+      <c r="H86" s="133" t="s">
         <v>406</v>
       </c>
       <c r="I86" s="29"/>
@@ -5878,14 +5878,14 @@
       <c r="D87" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E87" s="134"/>
+      <c r="E87" s="145"/>
       <c r="F87" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G87" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H87" s="143"/>
+      <c r="H87" s="134"/>
       <c r="I87" s="29"/>
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
@@ -5901,14 +5901,14 @@
       <c r="D88" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E88" s="134"/>
+      <c r="E88" s="145"/>
       <c r="F88" s="15" t="s">
         <v>62</v>
       </c>
       <c r="G88" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H88" s="143"/>
+      <c r="H88" s="134"/>
       <c r="I88" s="29"/>
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
@@ -5924,14 +5924,14 @@
       <c r="D89" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E89" s="134"/>
+      <c r="E89" s="145"/>
       <c r="F89" s="15" t="s">
         <v>63</v>
       </c>
       <c r="G89" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H89" s="143"/>
+      <c r="H89" s="134"/>
       <c r="I89" s="29"/>
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
@@ -5947,14 +5947,14 @@
       <c r="D90" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E90" s="134"/>
+      <c r="E90" s="145"/>
       <c r="F90" s="15" t="s">
         <v>64</v>
       </c>
       <c r="G90" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H90" s="143"/>
+      <c r="H90" s="134"/>
       <c r="I90" s="29"/>
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
@@ -5970,14 +5970,14 @@
       <c r="D91" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E91" s="135"/>
+      <c r="E91" s="148"/>
       <c r="F91" s="19" t="s">
         <v>65</v>
       </c>
       <c r="G91" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H91" s="144"/>
+      <c r="H91" s="136"/>
       <c r="I91" s="29"/>
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
@@ -5993,7 +5993,7 @@
       <c r="D92" s="62" t="s">
         <v>322</v>
       </c>
-      <c r="E92" s="133">
+      <c r="E92" s="144">
         <v>125</v>
       </c>
       <c r="F92" s="47" t="s">
@@ -6002,7 +6002,7 @@
       <c r="G92" s="48" t="s">
         <v>325</v>
       </c>
-      <c r="H92" s="145" t="s">
+      <c r="H92" s="140" t="s">
         <v>411</v>
       </c>
     </row>
@@ -6016,14 +6016,14 @@
       <c r="D93" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="E93" s="134"/>
+      <c r="E93" s="145"/>
       <c r="F93" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H93" s="146"/>
+      <c r="H93" s="138"/>
     </row>
     <row r="94" spans="2:12" ht="15.75" customHeight="1">
       <c r="B94" s="44" t="s">
@@ -6035,14 +6035,14 @@
       <c r="D94" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="E94" s="134"/>
+      <c r="E94" s="145"/>
       <c r="F94" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G94" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H94" s="146"/>
+      <c r="H94" s="138"/>
     </row>
     <row r="95" spans="2:12" ht="15.75" customHeight="1">
       <c r="B95" s="44" t="s">
@@ -6054,14 +6054,14 @@
       <c r="D95" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="E95" s="134"/>
+      <c r="E95" s="145"/>
       <c r="F95" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G95" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H95" s="146"/>
+      <c r="H95" s="138"/>
     </row>
     <row r="96" spans="2:12" ht="15.75" customHeight="1">
       <c r="B96" s="44" t="s">
@@ -6073,14 +6073,14 @@
       <c r="D96" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="E96" s="134"/>
+      <c r="E96" s="145"/>
       <c r="F96" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G96" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H96" s="146"/>
+      <c r="H96" s="138"/>
     </row>
     <row r="97" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B97" s="64" t="s">
@@ -6092,14 +6092,14 @@
       <c r="D97" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="E97" s="135"/>
+      <c r="E97" s="148"/>
       <c r="F97" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G97" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H97" s="147"/>
+      <c r="H97" s="139"/>
     </row>
     <row r="98" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B98" s="36" t="s">
@@ -6111,7 +6111,7 @@
       <c r="D98" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E98" s="133">
+      <c r="E98" s="144">
         <v>125</v>
       </c>
       <c r="F98" s="58" t="s">
@@ -6120,7 +6120,7 @@
       <c r="G98" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="H98" s="142" t="s">
+      <c r="H98" s="133" t="s">
         <v>407</v>
       </c>
     </row>
@@ -6134,14 +6134,14 @@
       <c r="D99" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E99" s="134"/>
+      <c r="E99" s="145"/>
       <c r="F99" s="56" t="s">
         <v>241</v>
       </c>
       <c r="G99" s="54" t="s">
         <v>235</v>
       </c>
-      <c r="H99" s="143"/>
+      <c r="H99" s="134"/>
     </row>
     <row r="100" spans="2:8" ht="15.75" customHeight="1">
       <c r="B100" s="38" t="s">
@@ -6153,14 +6153,14 @@
       <c r="D100" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E100" s="134"/>
+      <c r="E100" s="145"/>
       <c r="F100" s="56" t="s">
         <v>242</v>
       </c>
       <c r="G100" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H100" s="143"/>
+      <c r="H100" s="134"/>
     </row>
     <row r="101" spans="2:8" ht="15.75" customHeight="1">
       <c r="B101" s="38" t="s">
@@ -6172,14 +6172,14 @@
       <c r="D101" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E101" s="134"/>
+      <c r="E101" s="145"/>
       <c r="F101" s="56" t="s">
         <v>243</v>
       </c>
       <c r="G101" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H101" s="143"/>
+      <c r="H101" s="134"/>
     </row>
     <row r="102" spans="2:8" ht="15.75" customHeight="1">
       <c r="B102" s="38" t="s">
@@ -6191,14 +6191,14 @@
       <c r="D102" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E102" s="134"/>
+      <c r="E102" s="145"/>
       <c r="F102" s="56" t="s">
         <v>244</v>
       </c>
       <c r="G102" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H102" s="143"/>
+      <c r="H102" s="134"/>
     </row>
     <row r="103" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B103" s="51" t="s">
@@ -6210,14 +6210,14 @@
       <c r="D103" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E103" s="135"/>
+      <c r="E103" s="148"/>
       <c r="F103" s="57" t="s">
         <v>245</v>
       </c>
       <c r="G103" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="H103" s="144"/>
+      <c r="H103" s="136"/>
     </row>
     <row r="104" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B104" s="61" t="s">
@@ -6229,7 +6229,7 @@
       <c r="D104" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E104" s="133">
+      <c r="E104" s="144">
         <v>125</v>
       </c>
       <c r="F104" s="31" t="s">
@@ -6238,7 +6238,7 @@
       <c r="G104" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="H104" s="142" t="s">
+      <c r="H104" s="133" t="s">
         <v>407</v>
       </c>
     </row>
@@ -6252,14 +6252,14 @@
       <c r="D105" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E105" s="134"/>
+      <c r="E105" s="145"/>
       <c r="F105" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G105" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H105" s="143"/>
+      <c r="H105" s="134"/>
     </row>
     <row r="106" spans="2:8" ht="15.75" customHeight="1">
       <c r="B106" s="44" t="s">
@@ -6271,14 +6271,14 @@
       <c r="D106" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E106" s="134"/>
+      <c r="E106" s="145"/>
       <c r="F106" s="15" t="s">
         <v>62</v>
       </c>
       <c r="G106" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H106" s="143"/>
+      <c r="H106" s="134"/>
     </row>
     <row r="107" spans="2:8" ht="15.75" customHeight="1">
       <c r="B107" s="44" t="s">
@@ -6290,14 +6290,14 @@
       <c r="D107" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E107" s="134"/>
+      <c r="E107" s="145"/>
       <c r="F107" s="15" t="s">
         <v>75</v>
       </c>
       <c r="G107" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H107" s="143"/>
+      <c r="H107" s="134"/>
     </row>
     <row r="108" spans="2:8" ht="15.75" customHeight="1">
       <c r="B108" s="44" t="s">
@@ -6309,14 +6309,14 @@
       <c r="D108" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E108" s="134"/>
+      <c r="E108" s="145"/>
       <c r="F108" s="15" t="s">
         <v>64</v>
       </c>
       <c r="G108" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H108" s="143"/>
+      <c r="H108" s="134"/>
     </row>
     <row r="109" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B109" s="66" t="s">
@@ -6328,14 +6328,14 @@
       <c r="D109" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E109" s="136"/>
+      <c r="E109" s="146"/>
       <c r="F109" s="34" t="s">
         <v>65</v>
       </c>
       <c r="G109" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="H109" s="144"/>
+      <c r="H109" s="136"/>
     </row>
     <row r="110" spans="2:8" ht="25.5" customHeight="1" thickTop="1">
       <c r="B110" s="36" t="s">
@@ -6347,7 +6347,7 @@
       <c r="D110" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E110" s="133">
+      <c r="E110" s="144">
         <v>125</v>
       </c>
       <c r="F110" s="72" t="s">
@@ -6356,7 +6356,7 @@
       <c r="G110" s="37" t="s">
         <v>360</v>
       </c>
-      <c r="H110" s="142" t="s">
+      <c r="H110" s="133" t="s">
         <v>407</v>
       </c>
     </row>
@@ -6370,14 +6370,14 @@
       <c r="D111" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E111" s="134"/>
+      <c r="E111" s="145"/>
       <c r="F111" s="56" t="s">
         <v>362</v>
       </c>
       <c r="G111" s="54" t="s">
         <v>359</v>
       </c>
-      <c r="H111" s="143"/>
+      <c r="H111" s="134"/>
     </row>
     <row r="112" spans="2:8" ht="15.75" customHeight="1">
       <c r="B112" s="38" t="s">
@@ -6389,14 +6389,14 @@
       <c r="D112" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E112" s="134"/>
+      <c r="E112" s="145"/>
       <c r="F112" s="56" t="s">
         <v>358</v>
       </c>
       <c r="G112" s="54" t="s">
         <v>363</v>
       </c>
-      <c r="H112" s="143"/>
+      <c r="H112" s="134"/>
     </row>
     <row r="113" spans="2:12" ht="15.75" customHeight="1">
       <c r="B113" s="38" t="s">
@@ -6408,14 +6408,14 @@
       <c r="D113" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E113" s="134"/>
+      <c r="E113" s="145"/>
       <c r="F113" s="56" t="s">
         <v>365</v>
       </c>
       <c r="G113" s="54" t="s">
         <v>359</v>
       </c>
-      <c r="H113" s="143"/>
+      <c r="H113" s="134"/>
     </row>
     <row r="114" spans="2:12" ht="15.75" customHeight="1">
       <c r="B114" s="38" t="s">
@@ -6427,14 +6427,14 @@
       <c r="D114" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E114" s="134"/>
+      <c r="E114" s="145"/>
       <c r="F114" s="56" t="s">
         <v>367</v>
       </c>
       <c r="G114" s="54" t="s">
         <v>359</v>
       </c>
-      <c r="H114" s="143"/>
+      <c r="H114" s="134"/>
     </row>
     <row r="115" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B115" s="51" t="s">
@@ -6446,14 +6446,14 @@
       <c r="D115" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E115" s="135"/>
+      <c r="E115" s="148"/>
       <c r="F115" s="57" t="s">
         <v>370</v>
       </c>
       <c r="G115" s="54" t="s">
         <v>369</v>
       </c>
-      <c r="H115" s="144"/>
+      <c r="H115" s="136"/>
     </row>
     <row r="116" spans="2:12" ht="25.9" thickTop="1">
       <c r="B116" s="68" t="s">
@@ -6465,7 +6465,7 @@
       <c r="D116" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E116" s="133">
+      <c r="E116" s="144">
         <v>143</v>
       </c>
       <c r="F116" s="31" t="s">
@@ -6474,7 +6474,7 @@
       <c r="G116" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="H116" s="142" t="s">
+      <c r="H116" s="133" t="s">
         <v>418</v>
       </c>
       <c r="I116" s="29"/>
@@ -6492,14 +6492,14 @@
       <c r="D117" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E117" s="134"/>
+      <c r="E117" s="145"/>
       <c r="F117" s="15" t="s">
         <v>253</v>
       </c>
       <c r="G117" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H117" s="143"/>
+      <c r="H117" s="134"/>
       <c r="I117" s="29"/>
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
@@ -6515,14 +6515,14 @@
       <c r="D118" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E118" s="134"/>
+      <c r="E118" s="145"/>
       <c r="F118" s="15" t="s">
         <v>254</v>
       </c>
       <c r="G118" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H118" s="143"/>
+      <c r="H118" s="134"/>
       <c r="I118" s="29"/>
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
@@ -6538,14 +6538,14 @@
       <c r="D119" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E119" s="134"/>
+      <c r="E119" s="145"/>
       <c r="F119" s="15" t="s">
         <v>255</v>
       </c>
       <c r="G119" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H119" s="143"/>
+      <c r="H119" s="134"/>
       <c r="I119" s="29"/>
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
@@ -6561,14 +6561,14 @@
       <c r="D120" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E120" s="134"/>
+      <c r="E120" s="145"/>
       <c r="F120" s="15" t="s">
         <v>256</v>
       </c>
       <c r="G120" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H120" s="143"/>
+      <c r="H120" s="134"/>
       <c r="I120" s="29"/>
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
@@ -6584,14 +6584,14 @@
       <c r="D121" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E121" s="136"/>
+      <c r="E121" s="146"/>
       <c r="F121" s="26" t="s">
         <v>257</v>
       </c>
       <c r="G121" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="H121" s="144"/>
+      <c r="H121" s="136"/>
       <c r="I121" s="29"/>
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
@@ -6607,7 +6607,7 @@
       <c r="D122" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E122" s="133">
+      <c r="E122" s="144">
         <v>125</v>
       </c>
       <c r="F122" s="72" t="s">
@@ -6616,7 +6616,7 @@
       <c r="G122" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="H122" s="142" t="s">
+      <c r="H122" s="133" t="s">
         <v>407</v>
       </c>
       <c r="I122" s="29"/>
@@ -6634,14 +6634,14 @@
       <c r="D123" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E123" s="134"/>
+      <c r="E123" s="145"/>
       <c r="F123" s="56" t="s">
         <v>259</v>
       </c>
       <c r="G123" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H123" s="143"/>
+      <c r="H123" s="134"/>
       <c r="I123" s="29"/>
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
@@ -6657,14 +6657,14 @@
       <c r="D124" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E124" s="134"/>
+      <c r="E124" s="145"/>
       <c r="F124" s="56" t="s">
         <v>260</v>
       </c>
       <c r="G124" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H124" s="143"/>
+      <c r="H124" s="134"/>
       <c r="I124" s="29"/>
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
@@ -6680,14 +6680,14 @@
       <c r="D125" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E125" s="134"/>
+      <c r="E125" s="145"/>
       <c r="F125" s="56" t="s">
         <v>261</v>
       </c>
       <c r="G125" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H125" s="143"/>
+      <c r="H125" s="134"/>
       <c r="I125" s="29"/>
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
@@ -6703,14 +6703,14 @@
       <c r="D126" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E126" s="134"/>
+      <c r="E126" s="145"/>
       <c r="F126" s="56" t="s">
         <v>262</v>
       </c>
       <c r="G126" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H126" s="143"/>
+      <c r="H126" s="134"/>
       <c r="I126" s="29"/>
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
@@ -6726,14 +6726,14 @@
       <c r="D127" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E127" s="136"/>
+      <c r="E127" s="146"/>
       <c r="F127" s="73" t="s">
         <v>263</v>
       </c>
       <c r="G127" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="H127" s="144"/>
+      <c r="H127" s="136"/>
       <c r="I127" s="29"/>
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
@@ -6749,7 +6749,7 @@
       <c r="D128" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E128" s="133">
+      <c r="E128" s="144">
         <v>143</v>
       </c>
       <c r="F128" s="72" t="s">
@@ -6758,7 +6758,7 @@
       <c r="G128" s="48" t="s">
         <v>84</v>
       </c>
-      <c r="H128" s="142" t="s">
+      <c r="H128" s="133" t="s">
         <v>407</v>
       </c>
     </row>
@@ -6772,14 +6772,14 @@
       <c r="D129" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E129" s="134"/>
+      <c r="E129" s="145"/>
       <c r="F129" s="56" t="s">
         <v>268</v>
       </c>
       <c r="G129" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="H129" s="143"/>
+      <c r="H129" s="134"/>
     </row>
     <row r="130" spans="2:12" ht="15.75" customHeight="1">
       <c r="B130" s="70" t="s">
@@ -6791,14 +6791,14 @@
       <c r="D130" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E130" s="134"/>
+      <c r="E130" s="145"/>
       <c r="F130" s="56" t="s">
         <v>269</v>
       </c>
       <c r="G130" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H130" s="143"/>
+      <c r="H130" s="134"/>
     </row>
     <row r="131" spans="2:12" ht="15.75" customHeight="1">
       <c r="B131" s="74" t="s">
@@ -6810,14 +6810,14 @@
       <c r="D131" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E131" s="134"/>
+      <c r="E131" s="145"/>
       <c r="F131" s="56" t="s">
         <v>270</v>
       </c>
       <c r="G131" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H131" s="143"/>
+      <c r="H131" s="134"/>
     </row>
     <row r="132" spans="2:12" ht="15.75" customHeight="1">
       <c r="B132" s="74" t="s">
@@ -6829,14 +6829,14 @@
       <c r="D132" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E132" s="134"/>
+      <c r="E132" s="145"/>
       <c r="F132" s="56" t="s">
         <v>271</v>
       </c>
       <c r="G132" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H132" s="143"/>
+      <c r="H132" s="134"/>
     </row>
     <row r="133" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B133" s="71" t="s">
@@ -6848,14 +6848,14 @@
       <c r="D133" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E133" s="136"/>
+      <c r="E133" s="146"/>
       <c r="F133" s="73" t="s">
         <v>272</v>
       </c>
       <c r="G133" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="H133" s="144"/>
+      <c r="H133" s="136"/>
     </row>
     <row r="134" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B134" s="75" t="s">
@@ -6867,7 +6867,7 @@
       <c r="D134" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E134" s="138">
+      <c r="E134" s="147">
         <v>143</v>
       </c>
       <c r="F134" s="28" t="s">
@@ -6876,7 +6876,7 @@
       <c r="G134" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H134" s="142" t="s">
+      <c r="H134" s="133" t="s">
         <v>406</v>
       </c>
       <c r="I134" s="29"/>
@@ -6894,14 +6894,14 @@
       <c r="D135" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E135" s="134"/>
+      <c r="E135" s="145"/>
       <c r="F135" s="15" t="s">
         <v>274</v>
       </c>
       <c r="G135" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H135" s="143"/>
+      <c r="H135" s="134"/>
       <c r="I135" s="29"/>
       <c r="J135" s="29"/>
       <c r="K135" s="29"/>
@@ -6917,14 +6917,14 @@
       <c r="D136" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E136" s="134"/>
+      <c r="E136" s="145"/>
       <c r="F136" s="15" t="s">
         <v>275</v>
       </c>
       <c r="G136" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H136" s="143"/>
+      <c r="H136" s="134"/>
       <c r="I136" s="29"/>
       <c r="J136" s="29"/>
       <c r="K136" s="29"/>
@@ -6940,14 +6940,14 @@
       <c r="D137" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E137" s="134"/>
+      <c r="E137" s="145"/>
       <c r="F137" s="15" t="s">
         <v>276</v>
       </c>
       <c r="G137" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H137" s="143"/>
+      <c r="H137" s="134"/>
       <c r="I137" s="29"/>
       <c r="J137" s="29"/>
       <c r="K137" s="29"/>
@@ -6963,14 +6963,14 @@
       <c r="D138" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E138" s="134"/>
+      <c r="E138" s="145"/>
       <c r="F138" s="15" t="s">
         <v>277</v>
       </c>
       <c r="G138" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H138" s="143"/>
+      <c r="H138" s="134"/>
       <c r="I138" s="29"/>
       <c r="J138" s="29"/>
       <c r="K138" s="29"/>
@@ -6986,14 +6986,14 @@
       <c r="D139" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E139" s="135"/>
+      <c r="E139" s="148"/>
       <c r="F139" s="19" t="s">
         <v>278</v>
       </c>
       <c r="G139" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H139" s="144"/>
+      <c r="H139" s="136"/>
       <c r="I139" s="29"/>
       <c r="J139" s="29"/>
       <c r="K139" s="29"/>
@@ -7009,7 +7009,7 @@
       <c r="D140" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E140" s="133">
+      <c r="E140" s="144">
         <v>143</v>
       </c>
       <c r="F140" s="31" t="s">
@@ -7018,7 +7018,7 @@
       <c r="G140" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="H140" s="142" t="s">
+      <c r="H140" s="133" t="s">
         <v>407</v>
       </c>
     </row>
@@ -7032,14 +7032,14 @@
       <c r="D141" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E141" s="134"/>
+      <c r="E141" s="145"/>
       <c r="F141" s="15" t="s">
         <v>274</v>
       </c>
       <c r="G141" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="H141" s="143"/>
+      <c r="H141" s="134"/>
     </row>
     <row r="142" spans="2:12" ht="15.75" customHeight="1">
       <c r="B142" s="44" t="s">
@@ -7051,14 +7051,14 @@
       <c r="D142" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E142" s="134"/>
+      <c r="E142" s="145"/>
       <c r="F142" s="15" t="s">
         <v>275</v>
       </c>
       <c r="G142" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="H142" s="143"/>
+      <c r="H142" s="134"/>
     </row>
     <row r="143" spans="2:12" ht="15.75" customHeight="1">
       <c r="B143" s="44" t="s">
@@ -7070,14 +7070,14 @@
       <c r="D143" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E143" s="134"/>
+      <c r="E143" s="145"/>
       <c r="F143" s="15" t="s">
         <v>276</v>
       </c>
       <c r="G143" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="H143" s="143"/>
+      <c r="H143" s="134"/>
     </row>
     <row r="144" spans="2:12" ht="15.75" customHeight="1">
       <c r="B144" s="44" t="s">
@@ -7089,14 +7089,14 @@
       <c r="D144" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E144" s="134"/>
+      <c r="E144" s="145"/>
       <c r="F144" s="15" t="s">
         <v>277</v>
       </c>
       <c r="G144" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="H144" s="143"/>
+      <c r="H144" s="134"/>
     </row>
     <row r="145" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B145" s="64" t="s">
@@ -7108,14 +7108,14 @@
       <c r="D145" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E145" s="135"/>
+      <c r="E145" s="148"/>
       <c r="F145" s="19" t="s">
         <v>278</v>
       </c>
       <c r="G145" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="H145" s="144"/>
+      <c r="H145" s="136"/>
     </row>
     <row r="146" spans="1:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B146" s="112" t="s">
@@ -7127,7 +7127,7 @@
       <c r="D146" s="79" t="s">
         <v>323</v>
       </c>
-      <c r="E146" s="133">
+      <c r="E146" s="144">
         <v>143</v>
       </c>
       <c r="F146" s="47" t="s">
@@ -7136,7 +7136,7 @@
       <c r="G146" s="48" t="s">
         <v>324</v>
       </c>
-      <c r="H146" s="145" t="s">
+      <c r="H146" s="140" t="s">
         <v>411</v>
       </c>
     </row>
@@ -7150,14 +7150,14 @@
       <c r="D147" s="80" t="s">
         <v>99</v>
       </c>
-      <c r="E147" s="134"/>
+      <c r="E147" s="145"/>
       <c r="F147" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G147" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H147" s="146"/>
+      <c r="H147" s="138"/>
     </row>
     <row r="148" spans="1:12" ht="15.75" customHeight="1">
       <c r="B148" s="44" t="s">
@@ -7169,14 +7169,14 @@
       <c r="D148" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="E148" s="134"/>
+      <c r="E148" s="145"/>
       <c r="F148" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G148" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H148" s="146"/>
+      <c r="H148" s="138"/>
     </row>
     <row r="149" spans="1:12" ht="15.75" customHeight="1">
       <c r="B149" s="44" t="s">
@@ -7188,14 +7188,14 @@
       <c r="D149" s="80" t="s">
         <v>99</v>
       </c>
-      <c r="E149" s="134"/>
+      <c r="E149" s="145"/>
       <c r="F149" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G149" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H149" s="146"/>
+      <c r="H149" s="138"/>
     </row>
     <row r="150" spans="1:12" ht="15.75" customHeight="1">
       <c r="B150" s="44" t="s">
@@ -7207,14 +7207,14 @@
       <c r="D150" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="E150" s="134"/>
+      <c r="E150" s="145"/>
       <c r="F150" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G150" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H150" s="146"/>
+      <c r="H150" s="138"/>
     </row>
     <row r="151" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B151" s="64" t="s">
@@ -7226,14 +7226,14 @@
       <c r="D151" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="E151" s="135"/>
+      <c r="E151" s="148"/>
       <c r="F151" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G151" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H151" s="147"/>
+      <c r="H151" s="139"/>
     </row>
     <row r="152" spans="1:12" ht="13.5" thickTop="1">
       <c r="A152" s="111"/>
@@ -7246,7 +7246,7 @@
       <c r="D152" s="109" t="s">
         <v>382</v>
       </c>
-      <c r="E152" s="133">
+      <c r="E152" s="144">
         <v>143</v>
       </c>
       <c r="F152" s="47" t="s">
@@ -7255,7 +7255,7 @@
       <c r="G152" s="114" t="s">
         <v>378</v>
       </c>
-      <c r="H152" s="145" t="s">
+      <c r="H152" s="140" t="s">
         <v>411</v>
       </c>
     </row>
@@ -7269,12 +7269,12 @@
       <c r="D153" s="109" t="s">
         <v>375</v>
       </c>
-      <c r="E153" s="134"/>
+      <c r="E153" s="145"/>
       <c r="F153" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G153" s="12"/>
-      <c r="H153" s="146"/>
+      <c r="H153" s="138"/>
     </row>
     <row r="154" spans="1:12" ht="15.75" customHeight="1">
       <c r="B154" s="113" t="s">
@@ -7286,14 +7286,14 @@
       <c r="D154" s="109" t="s">
         <v>377</v>
       </c>
-      <c r="E154" s="134"/>
+      <c r="E154" s="145"/>
       <c r="F154" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G154" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H154" s="146"/>
+      <c r="H154" s="138"/>
     </row>
     <row r="155" spans="1:12" ht="15.75" customHeight="1">
       <c r="B155" s="113" t="s">
@@ -7305,12 +7305,12 @@
       <c r="D155" s="109" t="s">
         <v>375</v>
       </c>
-      <c r="E155" s="134"/>
+      <c r="E155" s="145"/>
       <c r="F155" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G155" s="12"/>
-      <c r="H155" s="146"/>
+      <c r="H155" s="138"/>
     </row>
     <row r="156" spans="1:12" ht="15.75" customHeight="1">
       <c r="B156" s="113" t="s">
@@ -7322,12 +7322,12 @@
       <c r="D156" s="109" t="s">
         <v>377</v>
       </c>
-      <c r="E156" s="134"/>
+      <c r="E156" s="145"/>
       <c r="F156" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G156" s="12"/>
-      <c r="H156" s="146"/>
+      <c r="H156" s="138"/>
     </row>
     <row r="157" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B157" s="116" t="s">
@@ -7339,14 +7339,14 @@
       <c r="D157" s="109" t="s">
         <v>375</v>
       </c>
-      <c r="E157" s="135"/>
+      <c r="E157" s="148"/>
       <c r="F157" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G157" s="115" t="s">
         <v>46</v>
       </c>
-      <c r="H157" s="147"/>
+      <c r="H157" s="139"/>
     </row>
     <row r="158" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B158" s="82" t="s">
@@ -7358,7 +7358,7 @@
       <c r="D158" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E158" s="133">
+      <c r="E158" s="144">
         <v>167</v>
       </c>
       <c r="F158" s="31" t="s">
@@ -7367,7 +7367,7 @@
       <c r="G158" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H158" s="142" t="s">
+      <c r="H158" s="133" t="s">
         <v>407</v>
       </c>
       <c r="I158" s="29"/>
@@ -7385,14 +7385,14 @@
       <c r="D159" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E159" s="134"/>
+      <c r="E159" s="145"/>
       <c r="F159" s="15" t="s">
         <v>274</v>
       </c>
       <c r="G159" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H159" s="143"/>
+      <c r="H159" s="134"/>
       <c r="I159" s="29"/>
       <c r="J159" s="29"/>
       <c r="K159" s="29"/>
@@ -7408,14 +7408,14 @@
       <c r="D160" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E160" s="134"/>
+      <c r="E160" s="145"/>
       <c r="F160" s="15" t="s">
         <v>279</v>
       </c>
       <c r="G160" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H160" s="143"/>
+      <c r="H160" s="134"/>
       <c r="I160" s="29"/>
       <c r="J160" s="29"/>
       <c r="K160" s="29"/>
@@ -7431,14 +7431,14 @@
       <c r="D161" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E161" s="134"/>
+      <c r="E161" s="145"/>
       <c r="F161" s="15" t="s">
         <v>280</v>
       </c>
       <c r="G161" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H161" s="143"/>
+      <c r="H161" s="134"/>
       <c r="I161" s="29"/>
       <c r="J161" s="29"/>
       <c r="K161" s="29"/>
@@ -7454,14 +7454,14 @@
       <c r="D162" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E162" s="134"/>
+      <c r="E162" s="145"/>
       <c r="F162" s="15" t="s">
         <v>281</v>
       </c>
       <c r="G162" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H162" s="143"/>
+      <c r="H162" s="134"/>
       <c r="I162" s="29"/>
       <c r="J162" s="29"/>
       <c r="K162" s="29"/>
@@ -7477,14 +7477,14 @@
       <c r="D163" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E163" s="135"/>
+      <c r="E163" s="148"/>
       <c r="F163" s="19" t="s">
         <v>282</v>
       </c>
       <c r="G163" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="H163" s="144"/>
+      <c r="H163" s="136"/>
       <c r="I163" s="29"/>
       <c r="J163" s="29"/>
       <c r="K163" s="29"/>
@@ -7500,7 +7500,7 @@
       <c r="D164" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E164" s="133">
+      <c r="E164" s="144">
         <v>125</v>
       </c>
       <c r="F164" s="58" t="s">
@@ -7509,7 +7509,7 @@
       <c r="G164" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="H164" s="142" t="s">
+      <c r="H164" s="133" t="s">
         <v>407</v>
       </c>
     </row>
@@ -7523,14 +7523,14 @@
       <c r="D165" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E165" s="134"/>
+      <c r="E165" s="145"/>
       <c r="F165" s="56" t="s">
         <v>196</v>
       </c>
       <c r="G165" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H165" s="143"/>
+      <c r="H165" s="134"/>
     </row>
     <row r="166" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B166" s="38" t="s">
@@ -7542,14 +7542,14 @@
       <c r="D166" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E166" s="134"/>
+      <c r="E166" s="145"/>
       <c r="F166" s="56" t="s">
         <v>197</v>
       </c>
       <c r="G166" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H166" s="143"/>
+      <c r="H166" s="134"/>
     </row>
     <row r="167" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B167" s="38" t="s">
@@ -7561,14 +7561,14 @@
       <c r="D167" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E167" s="134"/>
+      <c r="E167" s="145"/>
       <c r="F167" s="56" t="s">
         <v>198</v>
       </c>
       <c r="G167" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H167" s="143"/>
+      <c r="H167" s="134"/>
     </row>
     <row r="168" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B168" s="87" t="s">
@@ -7580,14 +7580,14 @@
       <c r="D168" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E168" s="134"/>
+      <c r="E168" s="145"/>
       <c r="F168" s="56" t="s">
         <v>199</v>
       </c>
       <c r="G168" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H168" s="143"/>
+      <c r="H168" s="134"/>
     </row>
     <row r="169" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B169" s="51" t="s">
@@ -7599,14 +7599,14 @@
       <c r="D169" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E169" s="135"/>
+      <c r="E169" s="148"/>
       <c r="F169" s="57" t="s">
         <v>200</v>
       </c>
       <c r="G169" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H169" s="144"/>
+      <c r="H169" s="136"/>
     </row>
     <row r="170" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B170" s="40" t="s">
@@ -7618,7 +7618,7 @@
       <c r="D170" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E170" s="137">
+      <c r="E170" s="149">
         <v>200</v>
       </c>
       <c r="F170" s="50" t="s">
@@ -7627,7 +7627,7 @@
       <c r="G170" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H170" s="142" t="s">
+      <c r="H170" s="133" t="s">
         <v>412</v>
       </c>
       <c r="I170" s="29"/>
@@ -7645,14 +7645,14 @@
       <c r="D171" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E171" s="134"/>
+      <c r="E171" s="145"/>
       <c r="F171" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G171" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="H171" s="143"/>
+      <c r="H171" s="134"/>
       <c r="I171" s="29"/>
       <c r="J171" s="29"/>
       <c r="K171" s="29"/>
@@ -7668,14 +7668,14 @@
       <c r="D172" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E172" s="134"/>
+      <c r="E172" s="145"/>
       <c r="F172" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G172" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="H172" s="143"/>
+      <c r="H172" s="134"/>
       <c r="I172" s="29"/>
       <c r="J172" s="29"/>
       <c r="K172" s="29"/>
@@ -7691,14 +7691,14 @@
       <c r="D173" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E173" s="134"/>
+      <c r="E173" s="145"/>
       <c r="F173" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G173" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="H173" s="143"/>
+      <c r="H173" s="134"/>
       <c r="I173" s="29"/>
       <c r="J173" s="29"/>
       <c r="K173" s="29"/>
@@ -7714,14 +7714,14 @@
       <c r="D174" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E174" s="134"/>
+      <c r="E174" s="145"/>
       <c r="F174" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G174" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="H174" s="143"/>
+      <c r="H174" s="134"/>
       <c r="I174" s="29"/>
       <c r="J174" s="29"/>
       <c r="K174" s="29"/>
@@ -7737,14 +7737,14 @@
       <c r="D175" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E175" s="136"/>
+      <c r="E175" s="146"/>
       <c r="F175" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G175" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="H175" s="144"/>
+      <c r="H175" s="136"/>
       <c r="I175" s="29"/>
       <c r="J175" s="29"/>
       <c r="K175" s="29"/>
@@ -7760,7 +7760,7 @@
       <c r="D176" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E176" s="133">
+      <c r="E176" s="144">
         <v>125</v>
       </c>
       <c r="F176" s="58" t="s">
@@ -7769,7 +7769,7 @@
       <c r="G176" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="H176" s="142" t="s">
+      <c r="H176" s="133" t="s">
         <v>407</v>
       </c>
       <c r="I176" s="29"/>
@@ -7787,14 +7787,14 @@
       <c r="D177" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E177" s="134"/>
+      <c r="E177" s="145"/>
       <c r="F177" s="56" t="s">
         <v>284</v>
       </c>
       <c r="G177" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="H177" s="143"/>
+      <c r="H177" s="134"/>
       <c r="I177" s="29"/>
       <c r="J177" s="29"/>
       <c r="K177" s="29"/>
@@ -7810,14 +7810,14 @@
       <c r="D178" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E178" s="134"/>
+      <c r="E178" s="145"/>
       <c r="F178" s="56" t="s">
         <v>285</v>
       </c>
       <c r="G178" s="78" t="s">
         <v>113</v>
       </c>
-      <c r="H178" s="143"/>
+      <c r="H178" s="134"/>
       <c r="I178" s="29"/>
       <c r="J178" s="29"/>
       <c r="K178" s="29"/>
@@ -7833,14 +7833,14 @@
       <c r="D179" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E179" s="134"/>
+      <c r="E179" s="145"/>
       <c r="F179" s="56" t="s">
         <v>286</v>
       </c>
       <c r="G179" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="H179" s="143"/>
+      <c r="H179" s="134"/>
       <c r="I179" s="29"/>
       <c r="J179" s="29"/>
       <c r="K179" s="29"/>
@@ -7856,14 +7856,14 @@
       <c r="D180" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E180" s="134"/>
+      <c r="E180" s="145"/>
       <c r="F180" s="56" t="s">
         <v>287</v>
       </c>
       <c r="G180" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="H180" s="143"/>
+      <c r="H180" s="134"/>
       <c r="I180" s="29"/>
       <c r="J180" s="29"/>
       <c r="K180" s="29"/>
@@ -7879,14 +7879,14 @@
       <c r="D181" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E181" s="135"/>
+      <c r="E181" s="148"/>
       <c r="F181" s="88" t="s">
         <v>288</v>
       </c>
       <c r="G181" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="H181" s="144"/>
+      <c r="H181" s="136"/>
       <c r="I181" s="29"/>
       <c r="J181" s="29"/>
       <c r="K181" s="29"/>
@@ -7902,7 +7902,7 @@
       <c r="D182" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E182" s="138">
+      <c r="E182" s="147">
         <v>167</v>
       </c>
       <c r="F182" s="28" t="s">
@@ -7911,7 +7911,7 @@
       <c r="G182" s="54" t="s">
         <v>326</v>
       </c>
-      <c r="H182" s="142" t="s">
+      <c r="H182" s="133" t="s">
         <v>406</v>
       </c>
       <c r="I182" s="29"/>
@@ -7929,14 +7929,14 @@
       <c r="D183" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E183" s="134"/>
+      <c r="E183" s="145"/>
       <c r="F183" s="15" t="s">
         <v>312</v>
       </c>
       <c r="G183" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H183" s="143"/>
+      <c r="H183" s="134"/>
       <c r="I183" s="29"/>
       <c r="J183" s="29"/>
       <c r="K183" s="29"/>
@@ -7952,14 +7952,14 @@
       <c r="D184" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E184" s="134"/>
+      <c r="E184" s="145"/>
       <c r="F184" s="15" t="s">
         <v>313</v>
       </c>
       <c r="G184" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H184" s="143"/>
+      <c r="H184" s="134"/>
     </row>
     <row r="185" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B185" s="42" t="s">
@@ -7971,14 +7971,14 @@
       <c r="D185" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E185" s="134"/>
+      <c r="E185" s="145"/>
       <c r="F185" s="15" t="s">
         <v>314</v>
       </c>
       <c r="G185" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H185" s="143"/>
+      <c r="H185" s="134"/>
     </row>
     <row r="186" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B186" s="44" t="s">
@@ -7990,14 +7990,14 @@
       <c r="D186" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E186" s="134"/>
+      <c r="E186" s="145"/>
       <c r="F186" s="15" t="s">
         <v>313</v>
       </c>
       <c r="G186" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H186" s="143"/>
+      <c r="H186" s="134"/>
       <c r="I186" s="29"/>
       <c r="J186" s="29"/>
       <c r="K186" s="29"/>
@@ -8013,14 +8013,14 @@
       <c r="D187" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E187" s="135"/>
+      <c r="E187" s="148"/>
       <c r="F187" s="19" t="s">
         <v>315</v>
       </c>
       <c r="G187" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="H187" s="148"/>
+      <c r="H187" s="135"/>
       <c r="I187" s="29"/>
       <c r="J187" s="29"/>
       <c r="K187" s="29"/>
@@ -8036,7 +8036,7 @@
       <c r="D188" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E188" s="133">
+      <c r="E188" s="144">
         <v>167</v>
       </c>
       <c r="F188" s="50" t="s">
@@ -8045,7 +8045,7 @@
       <c r="G188" s="54" t="s">
         <v>321</v>
       </c>
-      <c r="H188" s="142" t="s">
+      <c r="H188" s="133" t="s">
         <v>419</v>
       </c>
       <c r="I188" s="29"/>
@@ -8063,14 +8063,14 @@
       <c r="D189" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E189" s="134"/>
+      <c r="E189" s="145"/>
       <c r="F189" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G189" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H189" s="143"/>
+      <c r="H189" s="134"/>
       <c r="I189" s="29"/>
       <c r="J189" s="29"/>
       <c r="K189" s="29"/>
@@ -8086,14 +8086,14 @@
       <c r="D190" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E190" s="134"/>
+      <c r="E190" s="145"/>
       <c r="F190" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G190" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H190" s="143"/>
+      <c r="H190" s="134"/>
       <c r="I190" s="29"/>
       <c r="J190" s="29"/>
       <c r="K190" s="29"/>
@@ -8109,14 +8109,14 @@
       <c r="D191" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E191" s="134"/>
+      <c r="E191" s="145"/>
       <c r="F191" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G191" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H191" s="143"/>
+      <c r="H191" s="134"/>
       <c r="I191" s="29"/>
       <c r="J191" s="29"/>
       <c r="K191" s="29"/>
@@ -8132,14 +8132,14 @@
       <c r="D192" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E192" s="134"/>
+      <c r="E192" s="145"/>
       <c r="F192" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G192" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H192" s="143"/>
+      <c r="H192" s="134"/>
       <c r="I192" s="29"/>
       <c r="J192" s="29"/>
       <c r="K192" s="29"/>
@@ -8155,14 +8155,14 @@
       <c r="D193" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E193" s="136"/>
+      <c r="E193" s="146"/>
       <c r="F193" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G193" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="H193" s="148"/>
+      <c r="H193" s="135"/>
       <c r="I193" s="29"/>
       <c r="J193" s="29"/>
       <c r="K193" s="29"/>
@@ -8178,7 +8178,7 @@
       <c r="D194" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E194" s="133">
+      <c r="E194" s="144">
         <v>143</v>
       </c>
       <c r="F194" s="72" t="s">
@@ -8187,7 +8187,7 @@
       <c r="G194" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="H194" s="142" t="s">
+      <c r="H194" s="133" t="s">
         <v>407</v>
       </c>
     </row>
@@ -8201,14 +8201,14 @@
       <c r="D195" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E195" s="134"/>
+      <c r="E195" s="145"/>
       <c r="F195" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G195" s="54" t="s">
         <v>125</v>
       </c>
-      <c r="H195" s="143"/>
+      <c r="H195" s="134"/>
     </row>
     <row r="196" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B196" s="38" t="s">
@@ -8220,14 +8220,14 @@
       <c r="D196" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E196" s="134"/>
+      <c r="E196" s="145"/>
       <c r="F196" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G196" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H196" s="143"/>
+      <c r="H196" s="134"/>
     </row>
     <row r="197" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B197" s="38" t="s">
@@ -8239,14 +8239,14 @@
       <c r="D197" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E197" s="134"/>
+      <c r="E197" s="145"/>
       <c r="F197" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G197" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H197" s="143"/>
+      <c r="H197" s="134"/>
     </row>
     <row r="198" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B198" s="38" t="s">
@@ -8258,14 +8258,14 @@
       <c r="D198" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E198" s="134"/>
+      <c r="E198" s="145"/>
       <c r="F198" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G198" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H198" s="143"/>
+      <c r="H198" s="134"/>
     </row>
     <row r="199" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B199" s="39" t="s">
@@ -8277,14 +8277,14 @@
       <c r="D199" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E199" s="136"/>
+      <c r="E199" s="146"/>
       <c r="F199" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G199" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="H199" s="144"/>
+      <c r="H199" s="136"/>
     </row>
     <row r="200" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B200" s="68" t="s">
@@ -8297,14 +8297,14 @@
       <c r="D200" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E200" s="133">
+      <c r="E200" s="144">
         <v>233</v>
       </c>
       <c r="F200" s="72"/>
       <c r="G200" s="48" t="s">
         <v>334</v>
       </c>
-      <c r="H200" s="149" t="s">
+      <c r="H200" s="137" t="s">
         <v>409</v>
       </c>
     </row>
@@ -8318,10 +8318,10 @@
       <c r="D201" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E201" s="134"/>
+      <c r="E201" s="145"/>
       <c r="F201" s="50"/>
       <c r="G201" s="12"/>
-      <c r="H201" s="146"/>
+      <c r="H201" s="138"/>
     </row>
     <row r="202" spans="2:12" ht="15.75" customHeight="1">
       <c r="B202" s="70" t="s">
@@ -8333,12 +8333,12 @@
       <c r="D202" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E202" s="134"/>
+      <c r="E202" s="145"/>
       <c r="F202" s="50"/>
       <c r="G202" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H202" s="146"/>
+      <c r="H202" s="138"/>
     </row>
     <row r="203" spans="2:12" ht="15.75" customHeight="1">
       <c r="B203" s="70" t="s">
@@ -8350,12 +8350,12 @@
       <c r="D203" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E203" s="134"/>
+      <c r="E203" s="145"/>
       <c r="F203" s="50"/>
       <c r="G203" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H203" s="146"/>
+      <c r="H203" s="138"/>
     </row>
     <row r="204" spans="2:12" ht="15.75" customHeight="1">
       <c r="B204" s="70" t="s">
@@ -8367,12 +8367,12 @@
       <c r="D204" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E204" s="134"/>
+      <c r="E204" s="145"/>
       <c r="F204" s="50"/>
       <c r="G204" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H204" s="146"/>
+      <c r="H204" s="138"/>
     </row>
     <row r="205" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B205" s="71" t="s">
@@ -8384,12 +8384,12 @@
       <c r="D205" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E205" s="136"/>
+      <c r="E205" s="146"/>
       <c r="F205" s="89"/>
       <c r="G205" s="90" t="s">
         <v>120</v>
       </c>
-      <c r="H205" s="147"/>
+      <c r="H205" s="139"/>
     </row>
     <row r="206" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B206" s="117" t="s">
@@ -8401,7 +8401,7 @@
       <c r="D206" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E206" s="133">
+      <c r="E206" s="144">
         <v>167</v>
       </c>
       <c r="F206" s="127" t="s">
@@ -8410,7 +8410,7 @@
       <c r="G206" s="114" t="s">
         <v>385</v>
       </c>
-      <c r="H206" s="142" t="s">
+      <c r="H206" s="133" t="s">
         <v>407</v>
       </c>
     </row>
@@ -8424,14 +8424,14 @@
       <c r="D207" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E207" s="134"/>
+      <c r="E207" s="145"/>
       <c r="F207" s="127" t="s">
         <v>312</v>
       </c>
       <c r="G207" s="119" t="s">
         <v>387</v>
       </c>
-      <c r="H207" s="143"/>
+      <c r="H207" s="134"/>
     </row>
     <row r="208" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B208" s="125" t="s">
@@ -8443,14 +8443,14 @@
       <c r="D208" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E208" s="134"/>
+      <c r="E208" s="145"/>
       <c r="F208" s="127" t="s">
         <v>313</v>
       </c>
       <c r="G208" s="120" t="s">
         <v>386</v>
       </c>
-      <c r="H208" s="143"/>
+      <c r="H208" s="134"/>
     </row>
     <row r="209" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B209" s="125" t="s">
@@ -8462,14 +8462,14 @@
       <c r="D209" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E209" s="134"/>
+      <c r="E209" s="145"/>
       <c r="F209" s="127" t="s">
         <v>314</v>
       </c>
       <c r="G209" s="119" t="s">
         <v>387</v>
       </c>
-      <c r="H209" s="143"/>
+      <c r="H209" s="134"/>
     </row>
     <row r="210" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B210" s="125" t="s">
@@ -8481,14 +8481,14 @@
       <c r="D210" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E210" s="134"/>
+      <c r="E210" s="145"/>
       <c r="F210" s="127" t="s">
         <v>313</v>
       </c>
       <c r="G210" s="122" t="s">
         <v>387</v>
       </c>
-      <c r="H210" s="143"/>
+      <c r="H210" s="134"/>
     </row>
     <row r="211" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B211" s="126" t="s">
@@ -8500,14 +8500,14 @@
       <c r="D211" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E211" s="136"/>
+      <c r="E211" s="146"/>
       <c r="F211" s="127" t="s">
         <v>315</v>
       </c>
       <c r="G211" s="121" t="s">
         <v>387</v>
       </c>
-      <c r="H211" s="144"/>
+      <c r="H211" s="136"/>
     </row>
     <row r="212" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B212" s="117" t="s">
@@ -8520,7 +8520,7 @@
       <c r="D212" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E212" s="139">
+      <c r="E212" s="141">
         <v>167</v>
       </c>
       <c r="F212" s="127" t="s">
@@ -8529,7 +8529,7 @@
       <c r="G212" s="114" t="s">
         <v>394</v>
       </c>
-      <c r="H212" s="142" t="s">
+      <c r="H212" s="133" t="s">
         <v>407</v>
       </c>
     </row>
@@ -8543,14 +8543,14 @@
       <c r="D213" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E213" s="140"/>
+      <c r="E213" s="142"/>
       <c r="F213" s="127" t="s">
         <v>403</v>
       </c>
       <c r="G213" s="118" t="s">
         <v>396</v>
       </c>
-      <c r="H213" s="143"/>
+      <c r="H213" s="134"/>
     </row>
     <row r="214" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B214" s="125" t="s">
@@ -8562,14 +8562,14 @@
       <c r="D214" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E214" s="140"/>
+      <c r="E214" s="142"/>
       <c r="F214" s="127" t="s">
         <v>313</v>
       </c>
       <c r="G214" s="118" t="s">
         <v>398</v>
       </c>
-      <c r="H214" s="143"/>
+      <c r="H214" s="134"/>
     </row>
     <row r="215" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B215" s="125" t="s">
@@ -8581,14 +8581,14 @@
       <c r="D215" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E215" s="140"/>
+      <c r="E215" s="142"/>
       <c r="F215" s="127" t="s">
         <v>314</v>
       </c>
       <c r="G215" s="118" t="s">
         <v>396</v>
       </c>
-      <c r="H215" s="143"/>
+      <c r="H215" s="134"/>
     </row>
     <row r="216" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B216" s="125" t="s">
@@ -8600,14 +8600,14 @@
       <c r="D216" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E216" s="140"/>
+      <c r="E216" s="142"/>
       <c r="F216" s="127" t="s">
         <v>313</v>
       </c>
       <c r="G216" s="118" t="s">
         <v>396</v>
       </c>
-      <c r="H216" s="143"/>
+      <c r="H216" s="134"/>
     </row>
     <row r="217" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B217" s="126" t="s">
@@ -8619,14 +8619,14 @@
       <c r="D217" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="E217" s="141"/>
+      <c r="E217" s="143"/>
       <c r="F217" s="127" t="s">
         <v>315</v>
       </c>
       <c r="G217" s="119" t="s">
         <v>399</v>
       </c>
-      <c r="H217" s="144"/>
+      <c r="H217" s="136"/>
     </row>
     <row r="218" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B218" s="91" t="s">
@@ -13791,30 +13791,38 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="72">
-    <mergeCell ref="H188:H193"/>
-    <mergeCell ref="H194:H199"/>
-    <mergeCell ref="H200:H205"/>
-    <mergeCell ref="H206:H211"/>
-    <mergeCell ref="H92:H97"/>
-    <mergeCell ref="H98:H103"/>
-    <mergeCell ref="H104:H109"/>
-    <mergeCell ref="H110:H115"/>
-    <mergeCell ref="H116:H121"/>
-    <mergeCell ref="H62:H67"/>
-    <mergeCell ref="H68:H73"/>
-    <mergeCell ref="H74:H79"/>
-    <mergeCell ref="H80:H85"/>
-    <mergeCell ref="H86:H91"/>
-    <mergeCell ref="H32:H37"/>
-    <mergeCell ref="H38:H43"/>
-    <mergeCell ref="H44:H49"/>
-    <mergeCell ref="H50:H55"/>
-    <mergeCell ref="H56:H61"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="H8:H13"/>
-    <mergeCell ref="H14:H19"/>
-    <mergeCell ref="H20:H25"/>
-    <mergeCell ref="H26:H31"/>
+    <mergeCell ref="E140:E145"/>
+    <mergeCell ref="E146:E151"/>
+    <mergeCell ref="E158:E163"/>
+    <mergeCell ref="E194:E199"/>
+    <mergeCell ref="E200:E205"/>
+    <mergeCell ref="E164:E169"/>
+    <mergeCell ref="E170:E175"/>
+    <mergeCell ref="E176:E181"/>
+    <mergeCell ref="E182:E187"/>
+    <mergeCell ref="E188:E193"/>
+    <mergeCell ref="E152:E157"/>
+    <mergeCell ref="E92:E97"/>
+    <mergeCell ref="E98:E103"/>
+    <mergeCell ref="E104:E109"/>
+    <mergeCell ref="E116:E121"/>
+    <mergeCell ref="E122:E127"/>
+    <mergeCell ref="E110:E115"/>
+    <mergeCell ref="E62:E67"/>
+    <mergeCell ref="E68:E73"/>
+    <mergeCell ref="E74:E79"/>
+    <mergeCell ref="E80:E85"/>
+    <mergeCell ref="E86:E91"/>
+    <mergeCell ref="E32:E37"/>
+    <mergeCell ref="E38:E43"/>
+    <mergeCell ref="E44:E49"/>
+    <mergeCell ref="E50:E55"/>
+    <mergeCell ref="E56:E61"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="E8:E13"/>
+    <mergeCell ref="E14:E19"/>
+    <mergeCell ref="E20:E25"/>
+    <mergeCell ref="E26:E31"/>
     <mergeCell ref="E212:E217"/>
     <mergeCell ref="E206:E211"/>
     <mergeCell ref="H122:H127"/>
@@ -13831,38 +13839,30 @@
     <mergeCell ref="E134:E139"/>
     <mergeCell ref="H212:H217"/>
     <mergeCell ref="H182:H187"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="E8:E13"/>
-    <mergeCell ref="E14:E19"/>
-    <mergeCell ref="E20:E25"/>
-    <mergeCell ref="E26:E31"/>
-    <mergeCell ref="E32:E37"/>
-    <mergeCell ref="E38:E43"/>
-    <mergeCell ref="E44:E49"/>
-    <mergeCell ref="E50:E55"/>
-    <mergeCell ref="E56:E61"/>
-    <mergeCell ref="E62:E67"/>
-    <mergeCell ref="E68:E73"/>
-    <mergeCell ref="E74:E79"/>
-    <mergeCell ref="E80:E85"/>
-    <mergeCell ref="E86:E91"/>
-    <mergeCell ref="E92:E97"/>
-    <mergeCell ref="E98:E103"/>
-    <mergeCell ref="E104:E109"/>
-    <mergeCell ref="E116:E121"/>
-    <mergeCell ref="E122:E127"/>
-    <mergeCell ref="E110:E115"/>
-    <mergeCell ref="E140:E145"/>
-    <mergeCell ref="E146:E151"/>
-    <mergeCell ref="E158:E163"/>
-    <mergeCell ref="E194:E199"/>
-    <mergeCell ref="E200:E205"/>
-    <mergeCell ref="E164:E169"/>
-    <mergeCell ref="E170:E175"/>
-    <mergeCell ref="E176:E181"/>
-    <mergeCell ref="E182:E187"/>
-    <mergeCell ref="E188:E193"/>
-    <mergeCell ref="E152:E157"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="H8:H13"/>
+    <mergeCell ref="H14:H19"/>
+    <mergeCell ref="H20:H25"/>
+    <mergeCell ref="H26:H31"/>
+    <mergeCell ref="H32:H37"/>
+    <mergeCell ref="H38:H43"/>
+    <mergeCell ref="H44:H49"/>
+    <mergeCell ref="H50:H55"/>
+    <mergeCell ref="H56:H61"/>
+    <mergeCell ref="H62:H67"/>
+    <mergeCell ref="H68:H73"/>
+    <mergeCell ref="H74:H79"/>
+    <mergeCell ref="H80:H85"/>
+    <mergeCell ref="H86:H91"/>
+    <mergeCell ref="H188:H193"/>
+    <mergeCell ref="H194:H199"/>
+    <mergeCell ref="H200:H205"/>
+    <mergeCell ref="H206:H211"/>
+    <mergeCell ref="H92:H97"/>
+    <mergeCell ref="H98:H103"/>
+    <mergeCell ref="H104:H109"/>
+    <mergeCell ref="H110:H115"/>
+    <mergeCell ref="H116:H121"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-source/护甲数据.xlsx
+++ b/data-source/护甲数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FED9E47-7AEC-4546-97D3-2026395D4826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFB7423-1C91-47A7-AACD-486F500E9410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3702,46 +3702,46 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4069,7 +4069,7 @@
       <c r="D2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="149">
+      <c r="E2" s="137">
         <v>91</v>
       </c>
       <c r="F2" s="11" t="s">
@@ -4078,7 +4078,7 @@
       <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="133" t="s">
+      <c r="H2" s="142" t="s">
         <v>406</v>
       </c>
     </row>
@@ -4092,14 +4092,14 @@
       <c r="D3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="145"/>
+      <c r="E3" s="134"/>
       <c r="F3" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="134"/>
+      <c r="H3" s="143"/>
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1">
       <c r="B4" s="13" t="s">
@@ -4111,14 +4111,14 @@
       <c r="D4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="145"/>
+      <c r="E4" s="134"/>
       <c r="F4" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="134"/>
+      <c r="H4" s="143"/>
     </row>
     <row r="5" spans="2:8" ht="15.75" customHeight="1">
       <c r="B5" s="13" t="s">
@@ -4130,14 +4130,14 @@
       <c r="D5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="145"/>
+      <c r="E5" s="134"/>
       <c r="F5" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="134"/>
+      <c r="H5" s="143"/>
     </row>
     <row r="6" spans="2:8" ht="15.75" customHeight="1">
       <c r="B6" s="13" t="s">
@@ -4149,14 +4149,14 @@
       <c r="D6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="145"/>
+      <c r="E6" s="134"/>
       <c r="F6" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="134"/>
+      <c r="H6" s="143"/>
     </row>
     <row r="7" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B7" s="16" t="s">
@@ -4168,14 +4168,14 @@
       <c r="D7" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="148"/>
+      <c r="E7" s="135"/>
       <c r="F7" s="19" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="136"/>
+      <c r="H7" s="144"/>
     </row>
     <row r="8" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B8" s="21" t="s">
@@ -4187,7 +4187,7 @@
       <c r="D8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="144">
+      <c r="E8" s="133">
         <v>91</v>
       </c>
       <c r="F8" s="11" t="s">
@@ -4196,7 +4196,7 @@
       <c r="G8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="133" t="s">
+      <c r="H8" s="142" t="s">
         <v>407</v>
       </c>
     </row>
@@ -4210,14 +4210,14 @@
       <c r="D9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="145"/>
+      <c r="E9" s="134"/>
       <c r="F9" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="134"/>
+      <c r="H9" s="143"/>
     </row>
     <row r="10" spans="2:8" ht="15.75" customHeight="1">
       <c r="B10" s="13" t="s">
@@ -4229,14 +4229,14 @@
       <c r="D10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="145"/>
+      <c r="E10" s="134"/>
       <c r="F10" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="134"/>
+      <c r="H10" s="143"/>
     </row>
     <row r="11" spans="2:8" ht="15.75" customHeight="1">
       <c r="B11" s="13" t="s">
@@ -4248,14 +4248,14 @@
       <c r="D11" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="145"/>
+      <c r="E11" s="134"/>
       <c r="F11" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="134"/>
+      <c r="H11" s="143"/>
     </row>
     <row r="12" spans="2:8" ht="15.75" customHeight="1">
       <c r="B12" s="13" t="s">
@@ -4267,14 +4267,14 @@
       <c r="D12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="145"/>
+      <c r="E12" s="134"/>
       <c r="F12" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="134"/>
+      <c r="H12" s="143"/>
     </row>
     <row r="13" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B13" s="23" t="s">
@@ -4286,14 +4286,14 @@
       <c r="D13" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="146"/>
+      <c r="E13" s="136"/>
       <c r="F13" s="26" t="s">
         <v>9</v>
       </c>
       <c r="G13" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="136"/>
+      <c r="H13" s="144"/>
     </row>
     <row r="14" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B14" s="8" t="s">
@@ -4305,7 +4305,7 @@
       <c r="D14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="147">
+      <c r="E14" s="138">
         <v>100</v>
       </c>
       <c r="F14" s="28" t="s">
@@ -4314,7 +4314,7 @@
       <c r="G14" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="133" t="s">
+      <c r="H14" s="142" t="s">
         <v>406</v>
       </c>
     </row>
@@ -4328,14 +4328,14 @@
       <c r="D15" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="145"/>
+      <c r="E15" s="134"/>
       <c r="F15" s="15" t="s">
         <v>338</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H15" s="134"/>
+      <c r="H15" s="143"/>
     </row>
     <row r="16" spans="2:8" ht="15.75" customHeight="1">
       <c r="B16" s="13" t="s">
@@ -4347,14 +4347,14 @@
       <c r="D16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="145"/>
+      <c r="E16" s="134"/>
       <c r="F16" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="134"/>
+      <c r="H16" s="143"/>
     </row>
     <row r="17" spans="2:12" ht="15.75" customHeight="1">
       <c r="B17" s="13" t="s">
@@ -4366,14 +4366,14 @@
       <c r="D17" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="145"/>
+      <c r="E17" s="134"/>
       <c r="F17" s="15" t="s">
         <v>340</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H17" s="134"/>
+      <c r="H17" s="143"/>
       <c r="I17" s="29"/>
       <c r="J17" s="29"/>
       <c r="K17" s="29"/>
@@ -4389,14 +4389,14 @@
       <c r="D18" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="145"/>
+      <c r="E18" s="134"/>
       <c r="F18" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="134"/>
+      <c r="H18" s="143"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
       <c r="K18" s="29"/>
@@ -4412,14 +4412,14 @@
       <c r="D19" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="148"/>
+      <c r="E19" s="135"/>
       <c r="F19" s="19" t="s">
         <v>341</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="136"/>
+      <c r="H19" s="144"/>
       <c r="I19" s="29"/>
       <c r="J19" s="29"/>
       <c r="K19" s="29"/>
@@ -4435,7 +4435,7 @@
       <c r="D20" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="144">
+      <c r="E20" s="133">
         <v>100</v>
       </c>
       <c r="F20" s="11" t="s">
@@ -4444,7 +4444,7 @@
       <c r="G20" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="H20" s="133" t="s">
+      <c r="H20" s="142" t="s">
         <v>408</v>
       </c>
     </row>
@@ -4458,14 +4458,14 @@
       <c r="D21" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="145"/>
+      <c r="E21" s="134"/>
       <c r="F21" s="15" t="s">
         <v>338</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H21" s="134"/>
+      <c r="H21" s="143"/>
     </row>
     <row r="22" spans="2:12" ht="15.75" customHeight="1">
       <c r="B22" s="13" t="s">
@@ -4477,14 +4477,14 @@
       <c r="D22" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="145"/>
+      <c r="E22" s="134"/>
       <c r="F22" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H22" s="134"/>
+      <c r="H22" s="143"/>
     </row>
     <row r="23" spans="2:12" ht="15.75" customHeight="1">
       <c r="B23" s="13" t="s">
@@ -4496,14 +4496,14 @@
       <c r="D23" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="145"/>
+      <c r="E23" s="134"/>
       <c r="F23" s="15" t="s">
         <v>340</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H23" s="134"/>
+      <c r="H23" s="143"/>
     </row>
     <row r="24" spans="2:12" ht="15.75" customHeight="1">
       <c r="B24" s="13" t="s">
@@ -4515,14 +4515,14 @@
       <c r="D24" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="145"/>
+      <c r="E24" s="134"/>
       <c r="F24" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H24" s="134"/>
+      <c r="H24" s="143"/>
     </row>
     <row r="25" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B25" s="107" t="s">
@@ -4534,14 +4534,14 @@
       <c r="D25" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="148"/>
+      <c r="E25" s="135"/>
       <c r="F25" s="19" t="s">
         <v>341</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H25" s="136"/>
+      <c r="H25" s="144"/>
     </row>
     <row r="26" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B26" s="21" t="s">
@@ -4553,7 +4553,7 @@
       <c r="D26" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="144">
+      <c r="E26" s="133">
         <v>100</v>
       </c>
       <c r="F26" s="31" t="s">
@@ -4562,7 +4562,7 @@
       <c r="G26" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H26" s="133" t="s">
+      <c r="H26" s="142" t="s">
         <v>407</v>
       </c>
     </row>
@@ -4576,14 +4576,14 @@
       <c r="D27" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="145"/>
+      <c r="E27" s="134"/>
       <c r="F27" s="15" t="s">
         <v>338</v>
       </c>
       <c r="G27" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H27" s="134"/>
+      <c r="H27" s="143"/>
     </row>
     <row r="28" spans="2:12" ht="15.75" customHeight="1">
       <c r="B28" s="13" t="s">
@@ -4595,14 +4595,14 @@
       <c r="D28" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="145"/>
+      <c r="E28" s="134"/>
       <c r="F28" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H28" s="134"/>
+      <c r="H28" s="143"/>
     </row>
     <row r="29" spans="2:12" ht="15.75" customHeight="1">
       <c r="B29" s="13" t="s">
@@ -4614,14 +4614,14 @@
       <c r="D29" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="145"/>
+      <c r="E29" s="134"/>
       <c r="F29" s="15" t="s">
         <v>340</v>
       </c>
       <c r="G29" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H29" s="134"/>
+      <c r="H29" s="143"/>
     </row>
     <row r="30" spans="2:12" ht="15.75" customHeight="1">
       <c r="B30" s="13" t="s">
@@ -4633,14 +4633,14 @@
       <c r="D30" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="145"/>
+      <c r="E30" s="134"/>
       <c r="F30" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H30" s="134"/>
+      <c r="H30" s="143"/>
     </row>
     <row r="31" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B31" s="32" t="s">
@@ -4652,14 +4652,14 @@
       <c r="D31" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="146"/>
+      <c r="E31" s="136"/>
       <c r="F31" s="34" t="s">
         <v>341</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H31" s="136"/>
+      <c r="H31" s="144"/>
     </row>
     <row r="32" spans="2:12" ht="25.9" thickTop="1">
       <c r="B32" s="36" t="s">
@@ -4671,7 +4671,7 @@
       <c r="D32" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="144">
+      <c r="E32" s="133">
         <v>112</v>
       </c>
       <c r="F32" s="31" t="s">
@@ -4680,7 +4680,7 @@
       <c r="G32" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="H32" s="133" t="s">
+      <c r="H32" s="142" t="s">
         <v>407</v>
       </c>
       <c r="I32" s="29"/>
@@ -4698,14 +4698,14 @@
       <c r="D33" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="145"/>
+      <c r="E33" s="134"/>
       <c r="F33" s="15" t="s">
         <v>343</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H33" s="134"/>
+      <c r="H33" s="143"/>
       <c r="I33" s="29"/>
       <c r="J33" s="29"/>
       <c r="K33" s="29"/>
@@ -4721,14 +4721,14 @@
       <c r="D34" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="145"/>
+      <c r="E34" s="134"/>
       <c r="F34" s="15" t="s">
         <v>344</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="134"/>
+      <c r="H34" s="143"/>
       <c r="I34" s="29"/>
       <c r="J34" s="29"/>
       <c r="K34" s="29"/>
@@ -4744,14 +4744,14 @@
       <c r="D35" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="145"/>
+      <c r="E35" s="134"/>
       <c r="F35" s="15" t="s">
         <v>345</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H35" s="134"/>
+      <c r="H35" s="143"/>
       <c r="I35" s="29"/>
       <c r="J35" s="29"/>
       <c r="K35" s="29"/>
@@ -4767,14 +4767,14 @@
       <c r="D36" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="145"/>
+      <c r="E36" s="134"/>
       <c r="F36" s="15" t="s">
         <v>346</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H36" s="134"/>
+      <c r="H36" s="143"/>
       <c r="I36" s="29"/>
       <c r="J36" s="29"/>
       <c r="K36" s="29"/>
@@ -4790,14 +4790,14 @@
       <c r="D37" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E37" s="146"/>
+      <c r="E37" s="136"/>
       <c r="F37" s="26" t="s">
         <v>347</v>
       </c>
       <c r="G37" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="H37" s="136"/>
+      <c r="H37" s="144"/>
       <c r="I37" s="29"/>
       <c r="J37" s="29"/>
       <c r="K37" s="29"/>
@@ -4813,7 +4813,7 @@
       <c r="D38" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="144">
+      <c r="E38" s="133">
         <v>100</v>
       </c>
       <c r="F38" s="11" t="s">
@@ -4822,7 +4822,7 @@
       <c r="G38" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="H38" s="133" t="s">
+      <c r="H38" s="142" t="s">
         <v>407</v>
       </c>
       <c r="I38" s="29"/>
@@ -4840,14 +4840,14 @@
       <c r="D39" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E39" s="145"/>
+      <c r="E39" s="134"/>
       <c r="F39" s="15" t="s">
         <v>338</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H39" s="134"/>
+      <c r="H39" s="143"/>
       <c r="I39" s="29"/>
       <c r="J39" s="29"/>
       <c r="K39" s="29"/>
@@ -4863,14 +4863,14 @@
       <c r="D40" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E40" s="145"/>
+      <c r="E40" s="134"/>
       <c r="F40" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G40" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H40" s="134"/>
+      <c r="H40" s="143"/>
       <c r="I40" s="29"/>
       <c r="J40" s="29"/>
       <c r="K40" s="29"/>
@@ -4886,14 +4886,14 @@
       <c r="D41" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E41" s="145"/>
+      <c r="E41" s="134"/>
       <c r="F41" s="15" t="s">
         <v>340</v>
       </c>
       <c r="G41" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H41" s="134"/>
+      <c r="H41" s="143"/>
       <c r="I41" s="29"/>
       <c r="J41" s="29"/>
       <c r="K41" s="29"/>
@@ -4909,14 +4909,14 @@
       <c r="D42" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E42" s="145"/>
+      <c r="E42" s="134"/>
       <c r="F42" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G42" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="134"/>
+      <c r="H42" s="143"/>
       <c r="I42" s="29"/>
       <c r="J42" s="29"/>
       <c r="K42" s="29"/>
@@ -4932,14 +4932,14 @@
       <c r="D43" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E43" s="146"/>
+      <c r="E43" s="136"/>
       <c r="F43" s="26" t="s">
         <v>341</v>
       </c>
       <c r="G43" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="H43" s="136"/>
+      <c r="H43" s="144"/>
       <c r="I43" s="29"/>
       <c r="J43" s="29"/>
       <c r="K43" s="29"/>
@@ -4955,7 +4955,7 @@
       <c r="D44" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E44" s="149">
+      <c r="E44" s="137">
         <v>112</v>
       </c>
       <c r="F44" s="11" t="s">
@@ -4964,7 +4964,7 @@
       <c r="G44" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H44" s="133" t="s">
+      <c r="H44" s="142" t="s">
         <v>406</v>
       </c>
       <c r="I44" s="29"/>
@@ -4982,14 +4982,14 @@
       <c r="D45" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E45" s="145"/>
+      <c r="E45" s="134"/>
       <c r="F45" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G45" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H45" s="134"/>
+      <c r="H45" s="143"/>
       <c r="I45" s="29"/>
       <c r="J45" s="29"/>
       <c r="K45" s="29"/>
@@ -5005,14 +5005,14 @@
       <c r="D46" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E46" s="145"/>
+      <c r="E46" s="134"/>
       <c r="F46" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G46" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H46" s="134"/>
+      <c r="H46" s="143"/>
       <c r="I46" s="29"/>
       <c r="J46" s="29"/>
       <c r="K46" s="29"/>
@@ -5028,14 +5028,14 @@
       <c r="D47" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E47" s="145"/>
+      <c r="E47" s="134"/>
       <c r="F47" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G47" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H47" s="134"/>
+      <c r="H47" s="143"/>
       <c r="I47" s="29"/>
       <c r="J47" s="29"/>
       <c r="K47" s="29"/>
@@ -5051,14 +5051,14 @@
       <c r="D48" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E48" s="145"/>
+      <c r="E48" s="134"/>
       <c r="F48" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G48" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H48" s="134"/>
+      <c r="H48" s="143"/>
       <c r="I48" s="29"/>
       <c r="J48" s="29"/>
       <c r="K48" s="29"/>
@@ -5074,14 +5074,14 @@
       <c r="D49" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E49" s="148"/>
+      <c r="E49" s="135"/>
       <c r="F49" s="19" t="s">
         <v>349</v>
       </c>
       <c r="G49" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H49" s="136"/>
+      <c r="H49" s="144"/>
       <c r="I49" s="29"/>
       <c r="J49" s="29"/>
       <c r="K49" s="29"/>
@@ -5097,7 +5097,7 @@
       <c r="D50" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E50" s="144">
+      <c r="E50" s="133">
         <v>112</v>
       </c>
       <c r="F50" s="15" t="s">
@@ -5106,7 +5106,7 @@
       <c r="G50" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H50" s="133" t="s">
+      <c r="H50" s="142" t="s">
         <v>409</v>
       </c>
     </row>
@@ -5120,14 +5120,14 @@
       <c r="D51" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E51" s="145"/>
+      <c r="E51" s="134"/>
       <c r="F51" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G51" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H51" s="134"/>
+      <c r="H51" s="143"/>
     </row>
     <row r="52" spans="2:12" ht="15.75" customHeight="1">
       <c r="B52" s="13" t="s">
@@ -5139,14 +5139,14 @@
       <c r="D52" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E52" s="145"/>
+      <c r="E52" s="134"/>
       <c r="F52" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G52" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H52" s="134"/>
+      <c r="H52" s="143"/>
     </row>
     <row r="53" spans="2:12" ht="15.75" customHeight="1">
       <c r="B53" s="13" t="s">
@@ -5158,14 +5158,14 @@
       <c r="D53" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E53" s="145"/>
+      <c r="E53" s="134"/>
       <c r="F53" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G53" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H53" s="134"/>
+      <c r="H53" s="143"/>
     </row>
     <row r="54" spans="2:12" ht="15.75" customHeight="1">
       <c r="B54" s="13" t="s">
@@ -5177,14 +5177,14 @@
       <c r="D54" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E54" s="145"/>
+      <c r="E54" s="134"/>
       <c r="F54" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H54" s="134"/>
+      <c r="H54" s="143"/>
     </row>
     <row r="55" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B55" s="16" t="s">
@@ -5196,14 +5196,14 @@
       <c r="D55" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E55" s="148"/>
+      <c r="E55" s="135"/>
       <c r="F55" s="19" t="s">
         <v>349</v>
       </c>
       <c r="G55" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H55" s="136"/>
+      <c r="H55" s="144"/>
     </row>
     <row r="56" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B56" s="36" t="s">
@@ -5215,7 +5215,7 @@
       <c r="D56" s="63" t="s">
         <v>182</v>
       </c>
-      <c r="E56" s="144">
+      <c r="E56" s="133">
         <v>112</v>
       </c>
       <c r="F56" s="47" t="s">
@@ -5224,7 +5224,7 @@
       <c r="G56" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="H56" s="133" t="s">
+      <c r="H56" s="142" t="s">
         <v>410</v>
       </c>
     </row>
@@ -5238,14 +5238,14 @@
       <c r="D57" s="63" t="s">
         <v>180</v>
       </c>
-      <c r="E57" s="145"/>
+      <c r="E57" s="134"/>
       <c r="F57" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G57" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H57" s="134"/>
+      <c r="H57" s="143"/>
     </row>
     <row r="58" spans="2:12" ht="15.75" customHeight="1">
       <c r="B58" s="38" t="s">
@@ -5257,14 +5257,14 @@
       <c r="D58" s="63" t="s">
         <v>181</v>
       </c>
-      <c r="E58" s="145"/>
+      <c r="E58" s="134"/>
       <c r="F58" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G58" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H58" s="134"/>
+      <c r="H58" s="143"/>
     </row>
     <row r="59" spans="2:12" ht="15.75" customHeight="1">
       <c r="B59" s="38" t="s">
@@ -5276,14 +5276,14 @@
       <c r="D59" s="63" t="s">
         <v>180</v>
       </c>
-      <c r="E59" s="145"/>
+      <c r="E59" s="134"/>
       <c r="F59" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G59" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H59" s="134"/>
+      <c r="H59" s="143"/>
     </row>
     <row r="60" spans="2:12" ht="15.75" customHeight="1">
       <c r="B60" s="38" t="s">
@@ -5295,14 +5295,14 @@
       <c r="D60" s="63" t="s">
         <v>181</v>
       </c>
-      <c r="E60" s="145"/>
+      <c r="E60" s="134"/>
       <c r="F60" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G60" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H60" s="134"/>
+      <c r="H60" s="143"/>
     </row>
     <row r="61" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B61" s="51" t="s">
@@ -5314,14 +5314,14 @@
       <c r="D61" s="63" t="s">
         <v>180</v>
       </c>
-      <c r="E61" s="148"/>
+      <c r="E61" s="135"/>
       <c r="F61" s="53" t="s">
         <v>7</v>
       </c>
       <c r="G61" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H61" s="136"/>
+      <c r="H61" s="144"/>
     </row>
     <row r="62" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B62" s="36" t="s">
@@ -5333,7 +5333,7 @@
       <c r="D62" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E62" s="144">
+      <c r="E62" s="133">
         <v>143</v>
       </c>
       <c r="F62" s="31" t="s">
@@ -5342,7 +5342,7 @@
       <c r="G62" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="H62" s="133" t="s">
+      <c r="H62" s="142" t="s">
         <v>407</v>
       </c>
       <c r="I62" s="29"/>
@@ -5360,14 +5360,14 @@
       <c r="D63" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E63" s="145"/>
+      <c r="E63" s="134"/>
       <c r="F63" s="15" t="s">
         <v>423</v>
       </c>
       <c r="G63" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H63" s="134"/>
+      <c r="H63" s="143"/>
       <c r="I63" s="29"/>
       <c r="J63" s="29"/>
       <c r="K63" s="29"/>
@@ -5383,14 +5383,14 @@
       <c r="D64" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E64" s="145"/>
+      <c r="E64" s="134"/>
       <c r="F64" s="15" t="s">
         <v>424</v>
       </c>
       <c r="G64" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H64" s="134"/>
+      <c r="H64" s="143"/>
       <c r="I64" s="29"/>
       <c r="J64" s="29"/>
       <c r="K64" s="29"/>
@@ -5406,14 +5406,14 @@
       <c r="D65" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E65" s="145"/>
+      <c r="E65" s="134"/>
       <c r="F65" s="15" t="s">
         <v>425</v>
       </c>
       <c r="G65" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H65" s="134"/>
+      <c r="H65" s="143"/>
       <c r="I65" s="29"/>
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
@@ -5429,14 +5429,14 @@
       <c r="D66" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E66" s="145"/>
+      <c r="E66" s="134"/>
       <c r="F66" s="15" t="s">
         <v>426</v>
       </c>
       <c r="G66" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H66" s="134"/>
+      <c r="H66" s="143"/>
       <c r="I66" s="29"/>
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
@@ -5450,14 +5450,14 @@
         <v>12</v>
       </c>
       <c r="D67" s="18"/>
-      <c r="E67" s="148"/>
+      <c r="E67" s="135"/>
       <c r="F67" s="19" t="s">
         <v>427</v>
       </c>
       <c r="G67" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H67" s="136"/>
+      <c r="H67" s="144"/>
       <c r="I67" s="29"/>
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
@@ -5473,7 +5473,7 @@
       <c r="D68" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E68" s="144">
+      <c r="E68" s="133">
         <v>143</v>
       </c>
       <c r="F68" s="31" t="s">
@@ -5482,7 +5482,7 @@
       <c r="G68" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="H68" s="133" t="s">
+      <c r="H68" s="142" t="s">
         <v>407</v>
       </c>
     </row>
@@ -5496,14 +5496,14 @@
       <c r="D69" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E69" s="145"/>
+      <c r="E69" s="134"/>
       <c r="F69" s="56" t="s">
         <v>201</v>
       </c>
       <c r="G69" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="H69" s="134"/>
+      <c r="H69" s="143"/>
     </row>
     <row r="70" spans="2:12" ht="15.75" customHeight="1">
       <c r="B70" s="38" t="s">
@@ -5515,14 +5515,14 @@
       <c r="D70" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E70" s="145"/>
+      <c r="E70" s="134"/>
       <c r="F70" s="15" t="s">
         <v>202</v>
       </c>
       <c r="G70" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H70" s="134"/>
+      <c r="H70" s="143"/>
     </row>
     <row r="71" spans="2:12" ht="15.75" customHeight="1">
       <c r="B71" s="38" t="s">
@@ -5534,14 +5534,14 @@
       <c r="D71" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E71" s="145"/>
+      <c r="E71" s="134"/>
       <c r="F71" s="56" t="s">
         <v>429</v>
       </c>
       <c r="G71" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H71" s="134"/>
+      <c r="H71" s="143"/>
     </row>
     <row r="72" spans="2:12" ht="15.75" customHeight="1">
       <c r="B72" s="38" t="s">
@@ -5553,14 +5553,14 @@
       <c r="D72" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E72" s="145"/>
+      <c r="E72" s="134"/>
       <c r="F72" s="15" t="s">
         <v>203</v>
       </c>
       <c r="G72" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H72" s="134"/>
+      <c r="H72" s="143"/>
     </row>
     <row r="73" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B73" s="51" t="s">
@@ -5572,14 +5572,14 @@
       <c r="D73" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E73" s="148"/>
+      <c r="E73" s="135"/>
       <c r="F73" s="57" t="s">
         <v>204</v>
       </c>
       <c r="G73" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H73" s="136"/>
+      <c r="H73" s="144"/>
     </row>
     <row r="74" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B74" s="36" t="s">
@@ -5591,7 +5591,7 @@
       <c r="D74" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E74" s="144">
+      <c r="E74" s="133">
         <v>143</v>
       </c>
       <c r="F74" s="58" t="s">
@@ -5600,7 +5600,7 @@
       <c r="G74" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="H74" s="133" t="s">
+      <c r="H74" s="142" t="s">
         <v>407</v>
       </c>
     </row>
@@ -5614,14 +5614,14 @@
       <c r="D75" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E75" s="145"/>
+      <c r="E75" s="134"/>
       <c r="F75" s="56" t="s">
         <v>192</v>
       </c>
       <c r="G75" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="H75" s="134"/>
+      <c r="H75" s="143"/>
     </row>
     <row r="76" spans="2:12" ht="15.75" customHeight="1">
       <c r="B76" s="38" t="s">
@@ -5633,14 +5633,14 @@
       <c r="D76" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E76" s="145"/>
+      <c r="E76" s="134"/>
       <c r="F76" s="56" t="s">
         <v>193</v>
       </c>
       <c r="G76" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H76" s="134"/>
+      <c r="H76" s="143"/>
     </row>
     <row r="77" spans="2:12" ht="15.75" customHeight="1">
       <c r="B77" s="38" t="s">
@@ -5652,14 +5652,14 @@
       <c r="D77" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E77" s="145"/>
+      <c r="E77" s="134"/>
       <c r="F77" s="56" t="s">
         <v>431</v>
       </c>
       <c r="G77" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H77" s="134"/>
+      <c r="H77" s="143"/>
     </row>
     <row r="78" spans="2:12" ht="15.75" customHeight="1">
       <c r="B78" s="38" t="s">
@@ -5671,14 +5671,14 @@
       <c r="D78" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E78" s="145"/>
+      <c r="E78" s="134"/>
       <c r="F78" s="56" t="s">
         <v>194</v>
       </c>
       <c r="G78" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H78" s="134"/>
+      <c r="H78" s="143"/>
     </row>
     <row r="79" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B79" s="51" t="s">
@@ -5690,14 +5690,14 @@
       <c r="D79" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E79" s="148"/>
+      <c r="E79" s="135"/>
       <c r="F79" s="57" t="s">
         <v>192</v>
       </c>
       <c r="G79" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H79" s="136"/>
+      <c r="H79" s="144"/>
     </row>
     <row r="80" spans="2:12" ht="38.65" thickTop="1">
       <c r="B80" s="40" t="s">
@@ -5709,7 +5709,7 @@
       <c r="D80" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E80" s="144">
+      <c r="E80" s="133">
         <v>112</v>
       </c>
       <c r="F80" s="11" t="s">
@@ -5718,7 +5718,7 @@
       <c r="G80" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="H80" s="133" t="s">
+      <c r="H80" s="142" t="s">
         <v>407</v>
       </c>
       <c r="I80" s="29"/>
@@ -5736,14 +5736,14 @@
       <c r="D81" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E81" s="145"/>
+      <c r="E81" s="134"/>
       <c r="F81" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G81" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H81" s="134"/>
+      <c r="H81" s="143"/>
       <c r="I81" s="29"/>
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
@@ -5759,14 +5759,14 @@
       <c r="D82" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E82" s="145"/>
+      <c r="E82" s="134"/>
       <c r="F82" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G82" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H82" s="134"/>
+      <c r="H82" s="143"/>
       <c r="I82" s="29"/>
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
@@ -5782,14 +5782,14 @@
       <c r="D83" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E83" s="145"/>
+      <c r="E83" s="134"/>
       <c r="F83" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G83" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H83" s="134"/>
+      <c r="H83" s="143"/>
       <c r="I83" s="29"/>
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
@@ -5805,14 +5805,14 @@
       <c r="D84" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E84" s="145"/>
+      <c r="E84" s="134"/>
       <c r="F84" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G84" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H84" s="134"/>
+      <c r="H84" s="143"/>
       <c r="I84" s="29"/>
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
@@ -5828,14 +5828,14 @@
       <c r="D85" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E85" s="146"/>
+      <c r="E85" s="136"/>
       <c r="F85" s="26" t="s">
         <v>350</v>
       </c>
       <c r="G85" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H85" s="136"/>
+      <c r="H85" s="144"/>
       <c r="I85" s="29"/>
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
@@ -5851,7 +5851,7 @@
       <c r="D86" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E86" s="149">
+      <c r="E86" s="137">
         <v>125</v>
       </c>
       <c r="F86" s="11" t="s">
@@ -5860,7 +5860,7 @@
       <c r="G86" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H86" s="133" t="s">
+      <c r="H86" s="142" t="s">
         <v>406</v>
       </c>
       <c r="I86" s="29"/>
@@ -5878,14 +5878,14 @@
       <c r="D87" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E87" s="145"/>
+      <c r="E87" s="134"/>
       <c r="F87" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G87" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H87" s="134"/>
+      <c r="H87" s="143"/>
       <c r="I87" s="29"/>
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
@@ -5901,14 +5901,14 @@
       <c r="D88" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E88" s="145"/>
+      <c r="E88" s="134"/>
       <c r="F88" s="15" t="s">
         <v>62</v>
       </c>
       <c r="G88" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H88" s="134"/>
+      <c r="H88" s="143"/>
       <c r="I88" s="29"/>
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
@@ -5924,14 +5924,14 @@
       <c r="D89" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E89" s="145"/>
+      <c r="E89" s="134"/>
       <c r="F89" s="15" t="s">
         <v>63</v>
       </c>
       <c r="G89" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H89" s="134"/>
+      <c r="H89" s="143"/>
       <c r="I89" s="29"/>
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
@@ -5947,14 +5947,14 @@
       <c r="D90" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E90" s="145"/>
+      <c r="E90" s="134"/>
       <c r="F90" s="15" t="s">
         <v>64</v>
       </c>
       <c r="G90" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H90" s="134"/>
+      <c r="H90" s="143"/>
       <c r="I90" s="29"/>
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
@@ -5970,14 +5970,14 @@
       <c r="D91" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E91" s="148"/>
+      <c r="E91" s="135"/>
       <c r="F91" s="19" t="s">
         <v>65</v>
       </c>
       <c r="G91" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H91" s="136"/>
+      <c r="H91" s="144"/>
       <c r="I91" s="29"/>
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
@@ -5993,7 +5993,7 @@
       <c r="D92" s="62" t="s">
         <v>322</v>
       </c>
-      <c r="E92" s="144">
+      <c r="E92" s="133">
         <v>125</v>
       </c>
       <c r="F92" s="47" t="s">
@@ -6002,7 +6002,7 @@
       <c r="G92" s="48" t="s">
         <v>325</v>
       </c>
-      <c r="H92" s="140" t="s">
+      <c r="H92" s="145" t="s">
         <v>411</v>
       </c>
     </row>
@@ -6016,14 +6016,14 @@
       <c r="D93" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="E93" s="145"/>
+      <c r="E93" s="134"/>
       <c r="F93" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H93" s="138"/>
+      <c r="H93" s="146"/>
     </row>
     <row r="94" spans="2:12" ht="15.75" customHeight="1">
       <c r="B94" s="44" t="s">
@@ -6035,14 +6035,14 @@
       <c r="D94" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="E94" s="145"/>
+      <c r="E94" s="134"/>
       <c r="F94" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G94" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H94" s="138"/>
+      <c r="H94" s="146"/>
     </row>
     <row r="95" spans="2:12" ht="15.75" customHeight="1">
       <c r="B95" s="44" t="s">
@@ -6054,14 +6054,14 @@
       <c r="D95" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="E95" s="145"/>
+      <c r="E95" s="134"/>
       <c r="F95" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G95" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H95" s="138"/>
+      <c r="H95" s="146"/>
     </row>
     <row r="96" spans="2:12" ht="15.75" customHeight="1">
       <c r="B96" s="44" t="s">
@@ -6073,14 +6073,14 @@
       <c r="D96" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="E96" s="145"/>
+      <c r="E96" s="134"/>
       <c r="F96" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G96" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H96" s="138"/>
+      <c r="H96" s="146"/>
     </row>
     <row r="97" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B97" s="64" t="s">
@@ -6092,14 +6092,14 @@
       <c r="D97" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="E97" s="148"/>
+      <c r="E97" s="135"/>
       <c r="F97" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G97" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H97" s="139"/>
+      <c r="H97" s="147"/>
     </row>
     <row r="98" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B98" s="36" t="s">
@@ -6111,7 +6111,7 @@
       <c r="D98" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E98" s="144">
+      <c r="E98" s="133">
         <v>125</v>
       </c>
       <c r="F98" s="58" t="s">
@@ -6120,7 +6120,7 @@
       <c r="G98" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="H98" s="133" t="s">
+      <c r="H98" s="142" t="s">
         <v>407</v>
       </c>
     </row>
@@ -6134,14 +6134,14 @@
       <c r="D99" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E99" s="145"/>
+      <c r="E99" s="134"/>
       <c r="F99" s="56" t="s">
         <v>241</v>
       </c>
       <c r="G99" s="54" t="s">
         <v>235</v>
       </c>
-      <c r="H99" s="134"/>
+      <c r="H99" s="143"/>
     </row>
     <row r="100" spans="2:8" ht="15.75" customHeight="1">
       <c r="B100" s="38" t="s">
@@ -6153,14 +6153,14 @@
       <c r="D100" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E100" s="145"/>
+      <c r="E100" s="134"/>
       <c r="F100" s="56" t="s">
         <v>242</v>
       </c>
       <c r="G100" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H100" s="134"/>
+      <c r="H100" s="143"/>
     </row>
     <row r="101" spans="2:8" ht="15.75" customHeight="1">
       <c r="B101" s="38" t="s">
@@ -6172,14 +6172,14 @@
       <c r="D101" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E101" s="145"/>
+      <c r="E101" s="134"/>
       <c r="F101" s="56" t="s">
         <v>243</v>
       </c>
       <c r="G101" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H101" s="134"/>
+      <c r="H101" s="143"/>
     </row>
     <row r="102" spans="2:8" ht="15.75" customHeight="1">
       <c r="B102" s="38" t="s">
@@ -6191,14 +6191,14 @@
       <c r="D102" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E102" s="145"/>
+      <c r="E102" s="134"/>
       <c r="F102" s="56" t="s">
         <v>244</v>
       </c>
       <c r="G102" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H102" s="134"/>
+      <c r="H102" s="143"/>
     </row>
     <row r="103" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B103" s="51" t="s">
@@ -6210,14 +6210,14 @@
       <c r="D103" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E103" s="148"/>
+      <c r="E103" s="135"/>
       <c r="F103" s="57" t="s">
         <v>245</v>
       </c>
       <c r="G103" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="H103" s="136"/>
+      <c r="H103" s="144"/>
     </row>
     <row r="104" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B104" s="61" t="s">
@@ -6229,7 +6229,7 @@
       <c r="D104" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E104" s="144">
+      <c r="E104" s="133">
         <v>125</v>
       </c>
       <c r="F104" s="31" t="s">
@@ -6238,7 +6238,7 @@
       <c r="G104" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="H104" s="133" t="s">
+      <c r="H104" s="142" t="s">
         <v>407</v>
       </c>
     </row>
@@ -6252,14 +6252,14 @@
       <c r="D105" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E105" s="145"/>
+      <c r="E105" s="134"/>
       <c r="F105" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G105" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H105" s="134"/>
+      <c r="H105" s="143"/>
     </row>
     <row r="106" spans="2:8" ht="15.75" customHeight="1">
       <c r="B106" s="44" t="s">
@@ -6271,14 +6271,14 @@
       <c r="D106" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E106" s="145"/>
+      <c r="E106" s="134"/>
       <c r="F106" s="15" t="s">
         <v>62</v>
       </c>
       <c r="G106" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H106" s="134"/>
+      <c r="H106" s="143"/>
     </row>
     <row r="107" spans="2:8" ht="15.75" customHeight="1">
       <c r="B107" s="44" t="s">
@@ -6290,14 +6290,14 @@
       <c r="D107" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E107" s="145"/>
+      <c r="E107" s="134"/>
       <c r="F107" s="15" t="s">
         <v>75</v>
       </c>
       <c r="G107" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H107" s="134"/>
+      <c r="H107" s="143"/>
     </row>
     <row r="108" spans="2:8" ht="15.75" customHeight="1">
       <c r="B108" s="44" t="s">
@@ -6309,14 +6309,14 @@
       <c r="D108" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E108" s="145"/>
+      <c r="E108" s="134"/>
       <c r="F108" s="15" t="s">
         <v>64</v>
       </c>
       <c r="G108" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H108" s="134"/>
+      <c r="H108" s="143"/>
     </row>
     <row r="109" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B109" s="66" t="s">
@@ -6328,14 +6328,14 @@
       <c r="D109" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E109" s="146"/>
+      <c r="E109" s="136"/>
       <c r="F109" s="34" t="s">
         <v>65</v>
       </c>
       <c r="G109" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="H109" s="136"/>
+      <c r="H109" s="144"/>
     </row>
     <row r="110" spans="2:8" ht="25.5" customHeight="1" thickTop="1">
       <c r="B110" s="36" t="s">
@@ -6347,7 +6347,7 @@
       <c r="D110" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E110" s="144">
+      <c r="E110" s="133">
         <v>125</v>
       </c>
       <c r="F110" s="72" t="s">
@@ -6356,7 +6356,7 @@
       <c r="G110" s="37" t="s">
         <v>360</v>
       </c>
-      <c r="H110" s="133" t="s">
+      <c r="H110" s="142" t="s">
         <v>407</v>
       </c>
     </row>
@@ -6370,14 +6370,14 @@
       <c r="D111" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E111" s="145"/>
+      <c r="E111" s="134"/>
       <c r="F111" s="56" t="s">
         <v>362</v>
       </c>
       <c r="G111" s="54" t="s">
         <v>359</v>
       </c>
-      <c r="H111" s="134"/>
+      <c r="H111" s="143"/>
     </row>
     <row r="112" spans="2:8" ht="15.75" customHeight="1">
       <c r="B112" s="38" t="s">
@@ -6389,14 +6389,14 @@
       <c r="D112" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E112" s="145"/>
+      <c r="E112" s="134"/>
       <c r="F112" s="56" t="s">
         <v>358</v>
       </c>
       <c r="G112" s="54" t="s">
         <v>363</v>
       </c>
-      <c r="H112" s="134"/>
+      <c r="H112" s="143"/>
     </row>
     <row r="113" spans="2:12" ht="15.75" customHeight="1">
       <c r="B113" s="38" t="s">
@@ -6408,14 +6408,14 @@
       <c r="D113" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E113" s="145"/>
+      <c r="E113" s="134"/>
       <c r="F113" s="56" t="s">
         <v>365</v>
       </c>
       <c r="G113" s="54" t="s">
         <v>359</v>
       </c>
-      <c r="H113" s="134"/>
+      <c r="H113" s="143"/>
     </row>
     <row r="114" spans="2:12" ht="15.75" customHeight="1">
       <c r="B114" s="38" t="s">
@@ -6427,14 +6427,14 @@
       <c r="D114" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E114" s="145"/>
+      <c r="E114" s="134"/>
       <c r="F114" s="56" t="s">
         <v>367</v>
       </c>
       <c r="G114" s="54" t="s">
         <v>359</v>
       </c>
-      <c r="H114" s="134"/>
+      <c r="H114" s="143"/>
     </row>
     <row r="115" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B115" s="51" t="s">
@@ -6446,14 +6446,14 @@
       <c r="D115" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E115" s="148"/>
+      <c r="E115" s="135"/>
       <c r="F115" s="57" t="s">
         <v>370</v>
       </c>
       <c r="G115" s="54" t="s">
         <v>369</v>
       </c>
-      <c r="H115" s="136"/>
+      <c r="H115" s="144"/>
     </row>
     <row r="116" spans="2:12" ht="25.9" thickTop="1">
       <c r="B116" s="68" t="s">
@@ -6465,7 +6465,7 @@
       <c r="D116" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E116" s="144">
+      <c r="E116" s="133">
         <v>143</v>
       </c>
       <c r="F116" s="31" t="s">
@@ -6474,7 +6474,7 @@
       <c r="G116" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="H116" s="133" t="s">
+      <c r="H116" s="142" t="s">
         <v>418</v>
       </c>
       <c r="I116" s="29"/>
@@ -6492,14 +6492,14 @@
       <c r="D117" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E117" s="145"/>
+      <c r="E117" s="134"/>
       <c r="F117" s="15" t="s">
         <v>253</v>
       </c>
       <c r="G117" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H117" s="134"/>
+      <c r="H117" s="143"/>
       <c r="I117" s="29"/>
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
@@ -6515,14 +6515,14 @@
       <c r="D118" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E118" s="145"/>
+      <c r="E118" s="134"/>
       <c r="F118" s="15" t="s">
         <v>254</v>
       </c>
       <c r="G118" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H118" s="134"/>
+      <c r="H118" s="143"/>
       <c r="I118" s="29"/>
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
@@ -6538,14 +6538,14 @@
       <c r="D119" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E119" s="145"/>
+      <c r="E119" s="134"/>
       <c r="F119" s="15" t="s">
         <v>255</v>
       </c>
       <c r="G119" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H119" s="134"/>
+      <c r="H119" s="143"/>
       <c r="I119" s="29"/>
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
@@ -6561,14 +6561,14 @@
       <c r="D120" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E120" s="145"/>
+      <c r="E120" s="134"/>
       <c r="F120" s="15" t="s">
         <v>256</v>
       </c>
       <c r="G120" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H120" s="134"/>
+      <c r="H120" s="143"/>
       <c r="I120" s="29"/>
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
@@ -6584,14 +6584,14 @@
       <c r="D121" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E121" s="146"/>
+      <c r="E121" s="136"/>
       <c r="F121" s="26" t="s">
         <v>257</v>
       </c>
       <c r="G121" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="H121" s="136"/>
+      <c r="H121" s="144"/>
       <c r="I121" s="29"/>
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
@@ -6607,7 +6607,7 @@
       <c r="D122" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E122" s="144">
+      <c r="E122" s="133">
         <v>125</v>
       </c>
       <c r="F122" s="72" t="s">
@@ -6616,7 +6616,7 @@
       <c r="G122" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="H122" s="133" t="s">
+      <c r="H122" s="142" t="s">
         <v>407</v>
       </c>
       <c r="I122" s="29"/>
@@ -6634,14 +6634,14 @@
       <c r="D123" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E123" s="145"/>
+      <c r="E123" s="134"/>
       <c r="F123" s="56" t="s">
         <v>259</v>
       </c>
       <c r="G123" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H123" s="134"/>
+      <c r="H123" s="143"/>
       <c r="I123" s="29"/>
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
@@ -6657,14 +6657,14 @@
       <c r="D124" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E124" s="145"/>
+      <c r="E124" s="134"/>
       <c r="F124" s="56" t="s">
         <v>260</v>
       </c>
       <c r="G124" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H124" s="134"/>
+      <c r="H124" s="143"/>
       <c r="I124" s="29"/>
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
@@ -6680,14 +6680,14 @@
       <c r="D125" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E125" s="145"/>
+      <c r="E125" s="134"/>
       <c r="F125" s="56" t="s">
         <v>261</v>
       </c>
       <c r="G125" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H125" s="134"/>
+      <c r="H125" s="143"/>
       <c r="I125" s="29"/>
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
@@ -6703,14 +6703,14 @@
       <c r="D126" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E126" s="145"/>
+      <c r="E126" s="134"/>
       <c r="F126" s="56" t="s">
         <v>262</v>
       </c>
       <c r="G126" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H126" s="134"/>
+      <c r="H126" s="143"/>
       <c r="I126" s="29"/>
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
@@ -6726,14 +6726,14 @@
       <c r="D127" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E127" s="146"/>
+      <c r="E127" s="136"/>
       <c r="F127" s="73" t="s">
         <v>263</v>
       </c>
       <c r="G127" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="H127" s="136"/>
+      <c r="H127" s="144"/>
       <c r="I127" s="29"/>
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
@@ -6749,7 +6749,7 @@
       <c r="D128" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E128" s="144">
+      <c r="E128" s="133">
         <v>143</v>
       </c>
       <c r="F128" s="72" t="s">
@@ -6758,7 +6758,7 @@
       <c r="G128" s="48" t="s">
         <v>84</v>
       </c>
-      <c r="H128" s="133" t="s">
+      <c r="H128" s="142" t="s">
         <v>407</v>
       </c>
     </row>
@@ -6772,14 +6772,14 @@
       <c r="D129" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E129" s="145"/>
+      <c r="E129" s="134"/>
       <c r="F129" s="56" t="s">
         <v>268</v>
       </c>
       <c r="G129" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="H129" s="134"/>
+      <c r="H129" s="143"/>
     </row>
     <row r="130" spans="2:12" ht="15.75" customHeight="1">
       <c r="B130" s="70" t="s">
@@ -6791,14 +6791,14 @@
       <c r="D130" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E130" s="145"/>
+      <c r="E130" s="134"/>
       <c r="F130" s="56" t="s">
         <v>269</v>
       </c>
       <c r="G130" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H130" s="134"/>
+      <c r="H130" s="143"/>
     </row>
     <row r="131" spans="2:12" ht="15.75" customHeight="1">
       <c r="B131" s="74" t="s">
@@ -6810,14 +6810,14 @@
       <c r="D131" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E131" s="145"/>
+      <c r="E131" s="134"/>
       <c r="F131" s="56" t="s">
         <v>270</v>
       </c>
       <c r="G131" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H131" s="134"/>
+      <c r="H131" s="143"/>
     </row>
     <row r="132" spans="2:12" ht="15.75" customHeight="1">
       <c r="B132" s="74" t="s">
@@ -6829,14 +6829,14 @@
       <c r="D132" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E132" s="145"/>
+      <c r="E132" s="134"/>
       <c r="F132" s="56" t="s">
         <v>271</v>
       </c>
       <c r="G132" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H132" s="134"/>
+      <c r="H132" s="143"/>
     </row>
     <row r="133" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B133" s="71" t="s">
@@ -6848,14 +6848,14 @@
       <c r="D133" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E133" s="146"/>
+      <c r="E133" s="136"/>
       <c r="F133" s="73" t="s">
         <v>272</v>
       </c>
       <c r="G133" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="H133" s="136"/>
+      <c r="H133" s="144"/>
     </row>
     <row r="134" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B134" s="75" t="s">
@@ -6867,7 +6867,7 @@
       <c r="D134" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E134" s="147">
+      <c r="E134" s="138">
         <v>143</v>
       </c>
       <c r="F134" s="28" t="s">
@@ -6876,7 +6876,7 @@
       <c r="G134" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H134" s="133" t="s">
+      <c r="H134" s="142" t="s">
         <v>406</v>
       </c>
       <c r="I134" s="29"/>
@@ -6894,14 +6894,14 @@
       <c r="D135" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E135" s="145"/>
+      <c r="E135" s="134"/>
       <c r="F135" s="15" t="s">
         <v>274</v>
       </c>
       <c r="G135" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H135" s="134"/>
+      <c r="H135" s="143"/>
       <c r="I135" s="29"/>
       <c r="J135" s="29"/>
       <c r="K135" s="29"/>
@@ -6917,14 +6917,14 @@
       <c r="D136" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E136" s="145"/>
+      <c r="E136" s="134"/>
       <c r="F136" s="15" t="s">
         <v>275</v>
       </c>
       <c r="G136" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H136" s="134"/>
+      <c r="H136" s="143"/>
       <c r="I136" s="29"/>
       <c r="J136" s="29"/>
       <c r="K136" s="29"/>
@@ -6940,14 +6940,14 @@
       <c r="D137" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E137" s="145"/>
+      <c r="E137" s="134"/>
       <c r="F137" s="15" t="s">
         <v>276</v>
       </c>
       <c r="G137" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H137" s="134"/>
+      <c r="H137" s="143"/>
       <c r="I137" s="29"/>
       <c r="J137" s="29"/>
       <c r="K137" s="29"/>
@@ -6963,14 +6963,14 @@
       <c r="D138" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E138" s="145"/>
+      <c r="E138" s="134"/>
       <c r="F138" s="15" t="s">
         <v>277</v>
       </c>
       <c r="G138" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H138" s="134"/>
+      <c r="H138" s="143"/>
       <c r="I138" s="29"/>
       <c r="J138" s="29"/>
       <c r="K138" s="29"/>
@@ -6986,14 +6986,14 @@
       <c r="D139" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E139" s="148"/>
+      <c r="E139" s="135"/>
       <c r="F139" s="19" t="s">
         <v>278</v>
       </c>
       <c r="G139" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H139" s="136"/>
+      <c r="H139" s="144"/>
       <c r="I139" s="29"/>
       <c r="J139" s="29"/>
       <c r="K139" s="29"/>
@@ -7009,7 +7009,7 @@
       <c r="D140" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E140" s="144">
+      <c r="E140" s="133">
         <v>143</v>
       </c>
       <c r="F140" s="31" t="s">
@@ -7018,7 +7018,7 @@
       <c r="G140" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="H140" s="133" t="s">
+      <c r="H140" s="142" t="s">
         <v>407</v>
       </c>
     </row>
@@ -7032,14 +7032,14 @@
       <c r="D141" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E141" s="145"/>
+      <c r="E141" s="134"/>
       <c r="F141" s="15" t="s">
         <v>274</v>
       </c>
       <c r="G141" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="H141" s="134"/>
+      <c r="H141" s="143"/>
     </row>
     <row r="142" spans="2:12" ht="15.75" customHeight="1">
       <c r="B142" s="44" t="s">
@@ -7051,14 +7051,14 @@
       <c r="D142" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E142" s="145"/>
+      <c r="E142" s="134"/>
       <c r="F142" s="15" t="s">
         <v>275</v>
       </c>
       <c r="G142" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="H142" s="134"/>
+      <c r="H142" s="143"/>
     </row>
     <row r="143" spans="2:12" ht="15.75" customHeight="1">
       <c r="B143" s="44" t="s">
@@ -7070,14 +7070,14 @@
       <c r="D143" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E143" s="145"/>
+      <c r="E143" s="134"/>
       <c r="F143" s="15" t="s">
         <v>276</v>
       </c>
       <c r="G143" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="H143" s="134"/>
+      <c r="H143" s="143"/>
     </row>
     <row r="144" spans="2:12" ht="15.75" customHeight="1">
       <c r="B144" s="44" t="s">
@@ -7089,14 +7089,14 @@
       <c r="D144" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E144" s="145"/>
+      <c r="E144" s="134"/>
       <c r="F144" s="15" t="s">
         <v>277</v>
       </c>
       <c r="G144" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="H144" s="134"/>
+      <c r="H144" s="143"/>
     </row>
     <row r="145" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B145" s="64" t="s">
@@ -7108,14 +7108,14 @@
       <c r="D145" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E145" s="148"/>
+      <c r="E145" s="135"/>
       <c r="F145" s="19" t="s">
         <v>278</v>
       </c>
       <c r="G145" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="H145" s="136"/>
+      <c r="H145" s="144"/>
     </row>
     <row r="146" spans="1:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B146" s="112" t="s">
@@ -7127,7 +7127,7 @@
       <c r="D146" s="79" t="s">
         <v>323</v>
       </c>
-      <c r="E146" s="144">
+      <c r="E146" s="133">
         <v>143</v>
       </c>
       <c r="F146" s="47" t="s">
@@ -7136,7 +7136,7 @@
       <c r="G146" s="48" t="s">
         <v>324</v>
       </c>
-      <c r="H146" s="140" t="s">
+      <c r="H146" s="145" t="s">
         <v>411</v>
       </c>
     </row>
@@ -7150,14 +7150,14 @@
       <c r="D147" s="80" t="s">
         <v>99</v>
       </c>
-      <c r="E147" s="145"/>
+      <c r="E147" s="134"/>
       <c r="F147" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G147" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H147" s="138"/>
+      <c r="H147" s="146"/>
     </row>
     <row r="148" spans="1:12" ht="15.75" customHeight="1">
       <c r="B148" s="44" t="s">
@@ -7169,14 +7169,14 @@
       <c r="D148" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="E148" s="145"/>
+      <c r="E148" s="134"/>
       <c r="F148" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G148" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H148" s="138"/>
+      <c r="H148" s="146"/>
     </row>
     <row r="149" spans="1:12" ht="15.75" customHeight="1">
       <c r="B149" s="44" t="s">
@@ -7188,14 +7188,14 @@
       <c r="D149" s="80" t="s">
         <v>99</v>
       </c>
-      <c r="E149" s="145"/>
+      <c r="E149" s="134"/>
       <c r="F149" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G149" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H149" s="138"/>
+      <c r="H149" s="146"/>
     </row>
     <row r="150" spans="1:12" ht="15.75" customHeight="1">
       <c r="B150" s="44" t="s">
@@ -7207,14 +7207,14 @@
       <c r="D150" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="E150" s="145"/>
+      <c r="E150" s="134"/>
       <c r="F150" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G150" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H150" s="138"/>
+      <c r="H150" s="146"/>
     </row>
     <row r="151" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B151" s="64" t="s">
@@ -7226,14 +7226,14 @@
       <c r="D151" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="E151" s="148"/>
+      <c r="E151" s="135"/>
       <c r="F151" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G151" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H151" s="139"/>
+      <c r="H151" s="147"/>
     </row>
     <row r="152" spans="1:12" ht="13.5" thickTop="1">
       <c r="A152" s="111"/>
@@ -7246,7 +7246,7 @@
       <c r="D152" s="109" t="s">
         <v>382</v>
       </c>
-      <c r="E152" s="144">
+      <c r="E152" s="133">
         <v>143</v>
       </c>
       <c r="F152" s="47" t="s">
@@ -7255,7 +7255,7 @@
       <c r="G152" s="114" t="s">
         <v>378</v>
       </c>
-      <c r="H152" s="140" t="s">
+      <c r="H152" s="145" t="s">
         <v>411</v>
       </c>
     </row>
@@ -7269,12 +7269,12 @@
       <c r="D153" s="109" t="s">
         <v>375</v>
       </c>
-      <c r="E153" s="145"/>
+      <c r="E153" s="134"/>
       <c r="F153" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G153" s="12"/>
-      <c r="H153" s="138"/>
+      <c r="H153" s="146"/>
     </row>
     <row r="154" spans="1:12" ht="15.75" customHeight="1">
       <c r="B154" s="113" t="s">
@@ -7286,14 +7286,14 @@
       <c r="D154" s="109" t="s">
         <v>377</v>
       </c>
-      <c r="E154" s="145"/>
+      <c r="E154" s="134"/>
       <c r="F154" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G154" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H154" s="138"/>
+      <c r="H154" s="146"/>
     </row>
     <row r="155" spans="1:12" ht="15.75" customHeight="1">
       <c r="B155" s="113" t="s">
@@ -7305,12 +7305,12 @@
       <c r="D155" s="109" t="s">
         <v>375</v>
       </c>
-      <c r="E155" s="145"/>
+      <c r="E155" s="134"/>
       <c r="F155" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G155" s="12"/>
-      <c r="H155" s="138"/>
+      <c r="H155" s="146"/>
     </row>
     <row r="156" spans="1:12" ht="15.75" customHeight="1">
       <c r="B156" s="113" t="s">
@@ -7322,12 +7322,12 @@
       <c r="D156" s="109" t="s">
         <v>377</v>
       </c>
-      <c r="E156" s="145"/>
+      <c r="E156" s="134"/>
       <c r="F156" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G156" s="12"/>
-      <c r="H156" s="138"/>
+      <c r="H156" s="146"/>
     </row>
     <row r="157" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B157" s="116" t="s">
@@ -7339,14 +7339,14 @@
       <c r="D157" s="109" t="s">
         <v>375</v>
       </c>
-      <c r="E157" s="148"/>
+      <c r="E157" s="135"/>
       <c r="F157" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G157" s="115" t="s">
         <v>46</v>
       </c>
-      <c r="H157" s="139"/>
+      <c r="H157" s="147"/>
     </row>
     <row r="158" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B158" s="82" t="s">
@@ -7358,7 +7358,7 @@
       <c r="D158" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E158" s="144">
+      <c r="E158" s="133">
         <v>167</v>
       </c>
       <c r="F158" s="31" t="s">
@@ -7367,7 +7367,7 @@
       <c r="G158" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H158" s="133" t="s">
+      <c r="H158" s="142" t="s">
         <v>407</v>
       </c>
       <c r="I158" s="29"/>
@@ -7385,14 +7385,14 @@
       <c r="D159" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E159" s="145"/>
+      <c r="E159" s="134"/>
       <c r="F159" s="15" t="s">
         <v>274</v>
       </c>
       <c r="G159" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H159" s="134"/>
+      <c r="H159" s="143"/>
       <c r="I159" s="29"/>
       <c r="J159" s="29"/>
       <c r="K159" s="29"/>
@@ -7408,14 +7408,14 @@
       <c r="D160" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E160" s="145"/>
+      <c r="E160" s="134"/>
       <c r="F160" s="15" t="s">
         <v>279</v>
       </c>
       <c r="G160" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H160" s="134"/>
+      <c r="H160" s="143"/>
       <c r="I160" s="29"/>
       <c r="J160" s="29"/>
       <c r="K160" s="29"/>
@@ -7431,14 +7431,14 @@
       <c r="D161" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E161" s="145"/>
+      <c r="E161" s="134"/>
       <c r="F161" s="15" t="s">
         <v>280</v>
       </c>
       <c r="G161" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H161" s="134"/>
+      <c r="H161" s="143"/>
       <c r="I161" s="29"/>
       <c r="J161" s="29"/>
       <c r="K161" s="29"/>
@@ -7454,14 +7454,14 @@
       <c r="D162" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E162" s="145"/>
+      <c r="E162" s="134"/>
       <c r="F162" s="15" t="s">
         <v>281</v>
       </c>
       <c r="G162" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H162" s="134"/>
+      <c r="H162" s="143"/>
       <c r="I162" s="29"/>
       <c r="J162" s="29"/>
       <c r="K162" s="29"/>
@@ -7477,14 +7477,14 @@
       <c r="D163" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E163" s="148"/>
+      <c r="E163" s="135"/>
       <c r="F163" s="19" t="s">
         <v>282</v>
       </c>
       <c r="G163" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="H163" s="136"/>
+      <c r="H163" s="144"/>
       <c r="I163" s="29"/>
       <c r="J163" s="29"/>
       <c r="K163" s="29"/>
@@ -7500,7 +7500,7 @@
       <c r="D164" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E164" s="144">
+      <c r="E164" s="133">
         <v>125</v>
       </c>
       <c r="F164" s="58" t="s">
@@ -7509,7 +7509,7 @@
       <c r="G164" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="H164" s="133" t="s">
+      <c r="H164" s="142" t="s">
         <v>407</v>
       </c>
     </row>
@@ -7523,14 +7523,14 @@
       <c r="D165" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E165" s="145"/>
+      <c r="E165" s="134"/>
       <c r="F165" s="56" t="s">
         <v>196</v>
       </c>
       <c r="G165" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H165" s="134"/>
+      <c r="H165" s="143"/>
     </row>
     <row r="166" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B166" s="38" t="s">
@@ -7542,14 +7542,14 @@
       <c r="D166" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E166" s="145"/>
+      <c r="E166" s="134"/>
       <c r="F166" s="56" t="s">
         <v>197</v>
       </c>
       <c r="G166" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H166" s="134"/>
+      <c r="H166" s="143"/>
     </row>
     <row r="167" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B167" s="38" t="s">
@@ -7561,14 +7561,14 @@
       <c r="D167" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E167" s="145"/>
+      <c r="E167" s="134"/>
       <c r="F167" s="56" t="s">
         <v>198</v>
       </c>
       <c r="G167" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H167" s="134"/>
+      <c r="H167" s="143"/>
     </row>
     <row r="168" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B168" s="87" t="s">
@@ -7580,14 +7580,14 @@
       <c r="D168" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E168" s="145"/>
+      <c r="E168" s="134"/>
       <c r="F168" s="56" t="s">
         <v>199</v>
       </c>
       <c r="G168" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H168" s="134"/>
+      <c r="H168" s="143"/>
     </row>
     <row r="169" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B169" s="51" t="s">
@@ -7599,14 +7599,14 @@
       <c r="D169" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E169" s="148"/>
+      <c r="E169" s="135"/>
       <c r="F169" s="57" t="s">
         <v>200</v>
       </c>
       <c r="G169" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H169" s="136"/>
+      <c r="H169" s="144"/>
     </row>
     <row r="170" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B170" s="40" t="s">
@@ -7618,7 +7618,7 @@
       <c r="D170" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E170" s="149">
+      <c r="E170" s="137">
         <v>200</v>
       </c>
       <c r="F170" s="50" t="s">
@@ -7627,7 +7627,7 @@
       <c r="G170" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H170" s="133" t="s">
+      <c r="H170" s="142" t="s">
         <v>412</v>
       </c>
       <c r="I170" s="29"/>
@@ -7645,14 +7645,14 @@
       <c r="D171" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E171" s="145"/>
+      <c r="E171" s="134"/>
       <c r="F171" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G171" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="H171" s="134"/>
+      <c r="H171" s="143"/>
       <c r="I171" s="29"/>
       <c r="J171" s="29"/>
       <c r="K171" s="29"/>
@@ -7668,14 +7668,14 @@
       <c r="D172" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E172" s="145"/>
+      <c r="E172" s="134"/>
       <c r="F172" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G172" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="H172" s="134"/>
+      <c r="H172" s="143"/>
       <c r="I172" s="29"/>
       <c r="J172" s="29"/>
       <c r="K172" s="29"/>
@@ -7691,14 +7691,14 @@
       <c r="D173" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E173" s="145"/>
+      <c r="E173" s="134"/>
       <c r="F173" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G173" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="H173" s="134"/>
+      <c r="H173" s="143"/>
       <c r="I173" s="29"/>
       <c r="J173" s="29"/>
       <c r="K173" s="29"/>
@@ -7714,14 +7714,14 @@
       <c r="D174" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E174" s="145"/>
+      <c r="E174" s="134"/>
       <c r="F174" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G174" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="H174" s="134"/>
+      <c r="H174" s="143"/>
       <c r="I174" s="29"/>
       <c r="J174" s="29"/>
       <c r="K174" s="29"/>
@@ -7737,14 +7737,14 @@
       <c r="D175" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E175" s="146"/>
+      <c r="E175" s="136"/>
       <c r="F175" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G175" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="H175" s="136"/>
+      <c r="H175" s="144"/>
       <c r="I175" s="29"/>
       <c r="J175" s="29"/>
       <c r="K175" s="29"/>
@@ -7760,7 +7760,7 @@
       <c r="D176" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E176" s="144">
+      <c r="E176" s="133">
         <v>125</v>
       </c>
       <c r="F176" s="58" t="s">
@@ -7769,7 +7769,7 @@
       <c r="G176" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="H176" s="133" t="s">
+      <c r="H176" s="142" t="s">
         <v>407</v>
       </c>
       <c r="I176" s="29"/>
@@ -7787,14 +7787,14 @@
       <c r="D177" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E177" s="145"/>
+      <c r="E177" s="134"/>
       <c r="F177" s="56" t="s">
         <v>284</v>
       </c>
       <c r="G177" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="H177" s="134"/>
+      <c r="H177" s="143"/>
       <c r="I177" s="29"/>
       <c r="J177" s="29"/>
       <c r="K177" s="29"/>
@@ -7810,14 +7810,14 @@
       <c r="D178" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E178" s="145"/>
+      <c r="E178" s="134"/>
       <c r="F178" s="56" t="s">
         <v>285</v>
       </c>
       <c r="G178" s="78" t="s">
         <v>113</v>
       </c>
-      <c r="H178" s="134"/>
+      <c r="H178" s="143"/>
       <c r="I178" s="29"/>
       <c r="J178" s="29"/>
       <c r="K178" s="29"/>
@@ -7833,14 +7833,14 @@
       <c r="D179" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E179" s="145"/>
+      <c r="E179" s="134"/>
       <c r="F179" s="56" t="s">
         <v>286</v>
       </c>
       <c r="G179" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="H179" s="134"/>
+      <c r="H179" s="143"/>
       <c r="I179" s="29"/>
       <c r="J179" s="29"/>
       <c r="K179" s="29"/>
@@ -7856,14 +7856,14 @@
       <c r="D180" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E180" s="145"/>
+      <c r="E180" s="134"/>
       <c r="F180" s="56" t="s">
         <v>287</v>
       </c>
       <c r="G180" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="H180" s="134"/>
+      <c r="H180" s="143"/>
       <c r="I180" s="29"/>
       <c r="J180" s="29"/>
       <c r="K180" s="29"/>
@@ -7879,14 +7879,14 @@
       <c r="D181" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E181" s="148"/>
+      <c r="E181" s="135"/>
       <c r="F181" s="88" t="s">
         <v>288</v>
       </c>
       <c r="G181" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="H181" s="136"/>
+      <c r="H181" s="144"/>
       <c r="I181" s="29"/>
       <c r="J181" s="29"/>
       <c r="K181" s="29"/>
@@ -7902,7 +7902,7 @@
       <c r="D182" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E182" s="147">
+      <c r="E182" s="138">
         <v>167</v>
       </c>
       <c r="F182" s="28" t="s">
@@ -7911,7 +7911,7 @@
       <c r="G182" s="54" t="s">
         <v>326</v>
       </c>
-      <c r="H182" s="133" t="s">
+      <c r="H182" s="142" t="s">
         <v>406</v>
       </c>
       <c r="I182" s="29"/>
@@ -7929,14 +7929,14 @@
       <c r="D183" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E183" s="145"/>
+      <c r="E183" s="134"/>
       <c r="F183" s="15" t="s">
         <v>312</v>
       </c>
       <c r="G183" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H183" s="134"/>
+      <c r="H183" s="143"/>
       <c r="I183" s="29"/>
       <c r="J183" s="29"/>
       <c r="K183" s="29"/>
@@ -7952,14 +7952,14 @@
       <c r="D184" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E184" s="145"/>
+      <c r="E184" s="134"/>
       <c r="F184" s="15" t="s">
         <v>313</v>
       </c>
       <c r="G184" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H184" s="134"/>
+      <c r="H184" s="143"/>
     </row>
     <row r="185" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B185" s="42" t="s">
@@ -7971,14 +7971,14 @@
       <c r="D185" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E185" s="145"/>
+      <c r="E185" s="134"/>
       <c r="F185" s="15" t="s">
         <v>314</v>
       </c>
       <c r="G185" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H185" s="134"/>
+      <c r="H185" s="143"/>
     </row>
     <row r="186" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B186" s="44" t="s">
@@ -7990,14 +7990,14 @@
       <c r="D186" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E186" s="145"/>
+      <c r="E186" s="134"/>
       <c r="F186" s="15" t="s">
         <v>313</v>
       </c>
       <c r="G186" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H186" s="134"/>
+      <c r="H186" s="143"/>
       <c r="I186" s="29"/>
       <c r="J186" s="29"/>
       <c r="K186" s="29"/>
@@ -8013,14 +8013,14 @@
       <c r="D187" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E187" s="148"/>
+      <c r="E187" s="135"/>
       <c r="F187" s="19" t="s">
         <v>315</v>
       </c>
       <c r="G187" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="H187" s="135"/>
+      <c r="H187" s="148"/>
       <c r="I187" s="29"/>
       <c r="J187" s="29"/>
       <c r="K187" s="29"/>
@@ -8036,7 +8036,7 @@
       <c r="D188" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E188" s="144">
+      <c r="E188" s="133">
         <v>167</v>
       </c>
       <c r="F188" s="50" t="s">
@@ -8045,7 +8045,7 @@
       <c r="G188" s="54" t="s">
         <v>321</v>
       </c>
-      <c r="H188" s="133" t="s">
+      <c r="H188" s="142" t="s">
         <v>419</v>
       </c>
       <c r="I188" s="29"/>
@@ -8063,14 +8063,14 @@
       <c r="D189" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E189" s="145"/>
+      <c r="E189" s="134"/>
       <c r="F189" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G189" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H189" s="134"/>
+      <c r="H189" s="143"/>
       <c r="I189" s="29"/>
       <c r="J189" s="29"/>
       <c r="K189" s="29"/>
@@ -8086,14 +8086,14 @@
       <c r="D190" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E190" s="145"/>
+      <c r="E190" s="134"/>
       <c r="F190" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G190" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H190" s="134"/>
+      <c r="H190" s="143"/>
       <c r="I190" s="29"/>
       <c r="J190" s="29"/>
       <c r="K190" s="29"/>
@@ -8109,14 +8109,14 @@
       <c r="D191" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E191" s="145"/>
+      <c r="E191" s="134"/>
       <c r="F191" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G191" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H191" s="134"/>
+      <c r="H191" s="143"/>
       <c r="I191" s="29"/>
       <c r="J191" s="29"/>
       <c r="K191" s="29"/>
@@ -8132,14 +8132,14 @@
       <c r="D192" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E192" s="145"/>
+      <c r="E192" s="134"/>
       <c r="F192" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G192" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H192" s="134"/>
+      <c r="H192" s="143"/>
       <c r="I192" s="29"/>
       <c r="J192" s="29"/>
       <c r="K192" s="29"/>
@@ -8155,14 +8155,14 @@
       <c r="D193" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E193" s="146"/>
+      <c r="E193" s="136"/>
       <c r="F193" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G193" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="H193" s="135"/>
+      <c r="H193" s="148"/>
       <c r="I193" s="29"/>
       <c r="J193" s="29"/>
       <c r="K193" s="29"/>
@@ -8178,7 +8178,7 @@
       <c r="D194" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E194" s="144">
+      <c r="E194" s="133">
         <v>143</v>
       </c>
       <c r="F194" s="72" t="s">
@@ -8187,7 +8187,7 @@
       <c r="G194" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="H194" s="133" t="s">
+      <c r="H194" s="142" t="s">
         <v>407</v>
       </c>
     </row>
@@ -8201,14 +8201,14 @@
       <c r="D195" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E195" s="145"/>
+      <c r="E195" s="134"/>
       <c r="F195" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G195" s="54" t="s">
         <v>125</v>
       </c>
-      <c r="H195" s="134"/>
+      <c r="H195" s="143"/>
     </row>
     <row r="196" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B196" s="38" t="s">
@@ -8220,14 +8220,14 @@
       <c r="D196" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E196" s="145"/>
+      <c r="E196" s="134"/>
       <c r="F196" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G196" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H196" s="134"/>
+      <c r="H196" s="143"/>
     </row>
     <row r="197" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B197" s="38" t="s">
@@ -8239,14 +8239,14 @@
       <c r="D197" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E197" s="145"/>
+      <c r="E197" s="134"/>
       <c r="F197" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G197" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H197" s="134"/>
+      <c r="H197" s="143"/>
     </row>
     <row r="198" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B198" s="38" t="s">
@@ -8258,14 +8258,14 @@
       <c r="D198" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E198" s="145"/>
+      <c r="E198" s="134"/>
       <c r="F198" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G198" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H198" s="134"/>
+      <c r="H198" s="143"/>
     </row>
     <row r="199" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B199" s="39" t="s">
@@ -8277,34 +8277,33 @@
       <c r="D199" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E199" s="146"/>
+      <c r="E199" s="136"/>
       <c r="F199" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G199" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="H199" s="136"/>
+      <c r="H199" s="144"/>
     </row>
     <row r="200" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B200" s="68" t="s">
         <v>126</v>
       </c>
       <c r="C200" s="22">
-        <f>925+600</f>
         <v>1525</v>
       </c>
       <c r="D200" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E200" s="144">
+      <c r="E200" s="133">
         <v>233</v>
       </c>
       <c r="F200" s="72"/>
       <c r="G200" s="48" t="s">
         <v>334</v>
       </c>
-      <c r="H200" s="137" t="s">
+      <c r="H200" s="149" t="s">
         <v>409</v>
       </c>
     </row>
@@ -8318,10 +8317,10 @@
       <c r="D201" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E201" s="145"/>
+      <c r="E201" s="134"/>
       <c r="F201" s="50"/>
       <c r="G201" s="12"/>
-      <c r="H201" s="138"/>
+      <c r="H201" s="146"/>
     </row>
     <row r="202" spans="2:12" ht="15.75" customHeight="1">
       <c r="B202" s="70" t="s">
@@ -8333,12 +8332,12 @@
       <c r="D202" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E202" s="145"/>
+      <c r="E202" s="134"/>
       <c r="F202" s="50"/>
       <c r="G202" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H202" s="138"/>
+      <c r="H202" s="146"/>
     </row>
     <row r="203" spans="2:12" ht="15.75" customHeight="1">
       <c r="B203" s="70" t="s">
@@ -8350,12 +8349,12 @@
       <c r="D203" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E203" s="145"/>
+      <c r="E203" s="134"/>
       <c r="F203" s="50"/>
       <c r="G203" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H203" s="138"/>
+      <c r="H203" s="146"/>
     </row>
     <row r="204" spans="2:12" ht="15.75" customHeight="1">
       <c r="B204" s="70" t="s">
@@ -8367,12 +8366,12 @@
       <c r="D204" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E204" s="145"/>
+      <c r="E204" s="134"/>
       <c r="F204" s="50"/>
       <c r="G204" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H204" s="138"/>
+      <c r="H204" s="146"/>
     </row>
     <row r="205" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B205" s="71" t="s">
@@ -8384,12 +8383,12 @@
       <c r="D205" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E205" s="146"/>
+      <c r="E205" s="136"/>
       <c r="F205" s="89"/>
       <c r="G205" s="90" t="s">
         <v>120</v>
       </c>
-      <c r="H205" s="139"/>
+      <c r="H205" s="147"/>
     </row>
     <row r="206" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B206" s="117" t="s">
@@ -8401,7 +8400,7 @@
       <c r="D206" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E206" s="144">
+      <c r="E206" s="133">
         <v>167</v>
       </c>
       <c r="F206" s="127" t="s">
@@ -8410,7 +8409,7 @@
       <c r="G206" s="114" t="s">
         <v>385</v>
       </c>
-      <c r="H206" s="133" t="s">
+      <c r="H206" s="142" t="s">
         <v>407</v>
       </c>
     </row>
@@ -8424,14 +8423,14 @@
       <c r="D207" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E207" s="145"/>
+      <c r="E207" s="134"/>
       <c r="F207" s="127" t="s">
         <v>312</v>
       </c>
       <c r="G207" s="119" t="s">
         <v>387</v>
       </c>
-      <c r="H207" s="134"/>
+      <c r="H207" s="143"/>
     </row>
     <row r="208" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B208" s="125" t="s">
@@ -8443,14 +8442,14 @@
       <c r="D208" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E208" s="145"/>
+      <c r="E208" s="134"/>
       <c r="F208" s="127" t="s">
         <v>313</v>
       </c>
       <c r="G208" s="120" t="s">
         <v>386</v>
       </c>
-      <c r="H208" s="134"/>
+      <c r="H208" s="143"/>
     </row>
     <row r="209" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B209" s="125" t="s">
@@ -8462,14 +8461,14 @@
       <c r="D209" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E209" s="145"/>
+      <c r="E209" s="134"/>
       <c r="F209" s="127" t="s">
         <v>314</v>
       </c>
       <c r="G209" s="119" t="s">
         <v>387</v>
       </c>
-      <c r="H209" s="134"/>
+      <c r="H209" s="143"/>
     </row>
     <row r="210" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B210" s="125" t="s">
@@ -8481,14 +8480,14 @@
       <c r="D210" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E210" s="145"/>
+      <c r="E210" s="134"/>
       <c r="F210" s="127" t="s">
         <v>313</v>
       </c>
       <c r="G210" s="122" t="s">
         <v>387</v>
       </c>
-      <c r="H210" s="134"/>
+      <c r="H210" s="143"/>
     </row>
     <row r="211" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B211" s="126" t="s">
@@ -8500,27 +8499,26 @@
       <c r="D211" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E211" s="146"/>
+      <c r="E211" s="136"/>
       <c r="F211" s="127" t="s">
         <v>315</v>
       </c>
       <c r="G211" s="121" t="s">
         <v>387</v>
       </c>
-      <c r="H211" s="136"/>
+      <c r="H211" s="144"/>
     </row>
     <row r="212" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B212" s="117" t="s">
         <v>393</v>
       </c>
       <c r="C212" s="22">
-        <f>C213+C214+C215+C216+C217</f>
         <v>1110</v>
       </c>
       <c r="D212" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E212" s="141">
+      <c r="E212" s="139">
         <v>167</v>
       </c>
       <c r="F212" s="127" t="s">
@@ -8529,7 +8527,7 @@
       <c r="G212" s="114" t="s">
         <v>394</v>
       </c>
-      <c r="H212" s="133" t="s">
+      <c r="H212" s="142" t="s">
         <v>407</v>
       </c>
     </row>
@@ -8543,14 +8541,14 @@
       <c r="D213" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E213" s="142"/>
+      <c r="E213" s="140"/>
       <c r="F213" s="127" t="s">
         <v>403</v>
       </c>
       <c r="G213" s="118" t="s">
         <v>396</v>
       </c>
-      <c r="H213" s="134"/>
+      <c r="H213" s="143"/>
     </row>
     <row r="214" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B214" s="125" t="s">
@@ -8562,14 +8560,14 @@
       <c r="D214" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E214" s="142"/>
+      <c r="E214" s="140"/>
       <c r="F214" s="127" t="s">
         <v>313</v>
       </c>
       <c r="G214" s="118" t="s">
         <v>398</v>
       </c>
-      <c r="H214" s="134"/>
+      <c r="H214" s="143"/>
     </row>
     <row r="215" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B215" s="125" t="s">
@@ -8581,14 +8579,14 @@
       <c r="D215" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E215" s="142"/>
+      <c r="E215" s="140"/>
       <c r="F215" s="127" t="s">
         <v>314</v>
       </c>
       <c r="G215" s="118" t="s">
         <v>396</v>
       </c>
-      <c r="H215" s="134"/>
+      <c r="H215" s="143"/>
     </row>
     <row r="216" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B216" s="125" t="s">
@@ -8600,14 +8598,14 @@
       <c r="D216" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E216" s="142"/>
+      <c r="E216" s="140"/>
       <c r="F216" s="127" t="s">
         <v>313</v>
       </c>
       <c r="G216" s="118" t="s">
         <v>396</v>
       </c>
-      <c r="H216" s="134"/>
+      <c r="H216" s="143"/>
     </row>
     <row r="217" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B217" s="126" t="s">
@@ -8619,14 +8617,14 @@
       <c r="D217" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="E217" s="143"/>
+      <c r="E217" s="141"/>
       <c r="F217" s="127" t="s">
         <v>315</v>
       </c>
       <c r="G217" s="119" t="s">
         <v>399</v>
       </c>
-      <c r="H217" s="136"/>
+      <c r="H217" s="144"/>
     </row>
     <row r="218" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B218" s="91" t="s">
@@ -13791,38 +13789,30 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="72">
-    <mergeCell ref="E140:E145"/>
-    <mergeCell ref="E146:E151"/>
-    <mergeCell ref="E158:E163"/>
-    <mergeCell ref="E194:E199"/>
-    <mergeCell ref="E200:E205"/>
-    <mergeCell ref="E164:E169"/>
-    <mergeCell ref="E170:E175"/>
-    <mergeCell ref="E176:E181"/>
-    <mergeCell ref="E182:E187"/>
-    <mergeCell ref="E188:E193"/>
-    <mergeCell ref="E152:E157"/>
-    <mergeCell ref="E92:E97"/>
-    <mergeCell ref="E98:E103"/>
-    <mergeCell ref="E104:E109"/>
-    <mergeCell ref="E116:E121"/>
-    <mergeCell ref="E122:E127"/>
-    <mergeCell ref="E110:E115"/>
-    <mergeCell ref="E62:E67"/>
-    <mergeCell ref="E68:E73"/>
-    <mergeCell ref="E74:E79"/>
-    <mergeCell ref="E80:E85"/>
-    <mergeCell ref="E86:E91"/>
-    <mergeCell ref="E32:E37"/>
-    <mergeCell ref="E38:E43"/>
-    <mergeCell ref="E44:E49"/>
-    <mergeCell ref="E50:E55"/>
-    <mergeCell ref="E56:E61"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="E8:E13"/>
-    <mergeCell ref="E14:E19"/>
-    <mergeCell ref="E20:E25"/>
-    <mergeCell ref="E26:E31"/>
+    <mergeCell ref="H188:H193"/>
+    <mergeCell ref="H194:H199"/>
+    <mergeCell ref="H200:H205"/>
+    <mergeCell ref="H206:H211"/>
+    <mergeCell ref="H92:H97"/>
+    <mergeCell ref="H98:H103"/>
+    <mergeCell ref="H104:H109"/>
+    <mergeCell ref="H110:H115"/>
+    <mergeCell ref="H116:H121"/>
+    <mergeCell ref="H62:H67"/>
+    <mergeCell ref="H68:H73"/>
+    <mergeCell ref="H74:H79"/>
+    <mergeCell ref="H80:H85"/>
+    <mergeCell ref="H86:H91"/>
+    <mergeCell ref="H32:H37"/>
+    <mergeCell ref="H38:H43"/>
+    <mergeCell ref="H44:H49"/>
+    <mergeCell ref="H50:H55"/>
+    <mergeCell ref="H56:H61"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="H8:H13"/>
+    <mergeCell ref="H14:H19"/>
+    <mergeCell ref="H20:H25"/>
+    <mergeCell ref="H26:H31"/>
     <mergeCell ref="E212:E217"/>
     <mergeCell ref="E206:E211"/>
     <mergeCell ref="H122:H127"/>
@@ -13839,30 +13829,38 @@
     <mergeCell ref="E134:E139"/>
     <mergeCell ref="H212:H217"/>
     <mergeCell ref="H182:H187"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="H8:H13"/>
-    <mergeCell ref="H14:H19"/>
-    <mergeCell ref="H20:H25"/>
-    <mergeCell ref="H26:H31"/>
-    <mergeCell ref="H32:H37"/>
-    <mergeCell ref="H38:H43"/>
-    <mergeCell ref="H44:H49"/>
-    <mergeCell ref="H50:H55"/>
-    <mergeCell ref="H56:H61"/>
-    <mergeCell ref="H62:H67"/>
-    <mergeCell ref="H68:H73"/>
-    <mergeCell ref="H74:H79"/>
-    <mergeCell ref="H80:H85"/>
-    <mergeCell ref="H86:H91"/>
-    <mergeCell ref="H188:H193"/>
-    <mergeCell ref="H194:H199"/>
-    <mergeCell ref="H200:H205"/>
-    <mergeCell ref="H206:H211"/>
-    <mergeCell ref="H92:H97"/>
-    <mergeCell ref="H98:H103"/>
-    <mergeCell ref="H104:H109"/>
-    <mergeCell ref="H110:H115"/>
-    <mergeCell ref="H116:H121"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="E8:E13"/>
+    <mergeCell ref="E14:E19"/>
+    <mergeCell ref="E20:E25"/>
+    <mergeCell ref="E26:E31"/>
+    <mergeCell ref="E32:E37"/>
+    <mergeCell ref="E38:E43"/>
+    <mergeCell ref="E44:E49"/>
+    <mergeCell ref="E50:E55"/>
+    <mergeCell ref="E56:E61"/>
+    <mergeCell ref="E62:E67"/>
+    <mergeCell ref="E68:E73"/>
+    <mergeCell ref="E74:E79"/>
+    <mergeCell ref="E80:E85"/>
+    <mergeCell ref="E86:E91"/>
+    <mergeCell ref="E92:E97"/>
+    <mergeCell ref="E98:E103"/>
+    <mergeCell ref="E104:E109"/>
+    <mergeCell ref="E116:E121"/>
+    <mergeCell ref="E122:E127"/>
+    <mergeCell ref="E110:E115"/>
+    <mergeCell ref="E140:E145"/>
+    <mergeCell ref="E146:E151"/>
+    <mergeCell ref="E158:E163"/>
+    <mergeCell ref="E194:E199"/>
+    <mergeCell ref="E200:E205"/>
+    <mergeCell ref="E164:E169"/>
+    <mergeCell ref="E170:E175"/>
+    <mergeCell ref="E176:E181"/>
+    <mergeCell ref="E182:E187"/>
+    <mergeCell ref="E188:E193"/>
+    <mergeCell ref="E152:E157"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-source/护甲数据.xlsx
+++ b/data-source/护甲数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFB7423-1C91-47A7-AACD-486F500E9410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3451394-E046-4CD8-A45C-A1E9925A47F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2118,9 +2118,6 @@
     <t>头狼的裤子</t>
   </si>
   <si>
-    <t>厚布14；布料16；青铜锭：3；铜锭7；恐狼牙：20</t>
-  </si>
-  <si>
     <t>头狼的靴子</t>
   </si>
   <si>
@@ -2350,6 +2347,9 @@
   </si>
   <si>
     <t>硬化铆钉：2；魔法皮革：3；碎铜片：4；厚布：4</t>
+  </si>
+  <si>
+    <t>厚布：14；布料：16；青铜锭：3；铜锭：7；恐狼牙：20</t>
   </si>
 </sst>
 </file>
@@ -3702,46 +3702,46 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4056,7 +4056,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
@@ -4069,7 +4069,7 @@
       <c r="D2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="137">
+      <c r="E2" s="149">
         <v>91</v>
       </c>
       <c r="F2" s="11" t="s">
@@ -4078,8 +4078,8 @@
       <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="142" t="s">
-        <v>406</v>
+      <c r="H2" s="133" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="15.75" customHeight="1">
@@ -4092,14 +4092,14 @@
       <c r="D3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="134"/>
+      <c r="E3" s="145"/>
       <c r="F3" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="143"/>
+      <c r="H3" s="134"/>
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1">
       <c r="B4" s="13" t="s">
@@ -4111,14 +4111,14 @@
       <c r="D4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="134"/>
+      <c r="E4" s="145"/>
       <c r="F4" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="143"/>
+      <c r="H4" s="134"/>
     </row>
     <row r="5" spans="2:8" ht="15.75" customHeight="1">
       <c r="B5" s="13" t="s">
@@ -4130,14 +4130,14 @@
       <c r="D5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="134"/>
+      <c r="E5" s="145"/>
       <c r="F5" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="143"/>
+      <c r="H5" s="134"/>
     </row>
     <row r="6" spans="2:8" ht="15.75" customHeight="1">
       <c r="B6" s="13" t="s">
@@ -4149,14 +4149,14 @@
       <c r="D6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="134"/>
+      <c r="E6" s="145"/>
       <c r="F6" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="143"/>
+      <c r="H6" s="134"/>
     </row>
     <row r="7" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B7" s="16" t="s">
@@ -4168,14 +4168,14 @@
       <c r="D7" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="135"/>
+      <c r="E7" s="148"/>
       <c r="F7" s="19" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="144"/>
+      <c r="H7" s="136"/>
     </row>
     <row r="8" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B8" s="21" t="s">
@@ -4187,7 +4187,7 @@
       <c r="D8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="133">
+      <c r="E8" s="144">
         <v>91</v>
       </c>
       <c r="F8" s="11" t="s">
@@ -4196,8 +4196,8 @@
       <c r="G8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="142" t="s">
-        <v>407</v>
+      <c r="H8" s="133" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15.75" customHeight="1">
@@ -4210,14 +4210,14 @@
       <c r="D9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="134"/>
+      <c r="E9" s="145"/>
       <c r="F9" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="143"/>
+      <c r="H9" s="134"/>
     </row>
     <row r="10" spans="2:8" ht="15.75" customHeight="1">
       <c r="B10" s="13" t="s">
@@ -4229,14 +4229,14 @@
       <c r="D10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="134"/>
+      <c r="E10" s="145"/>
       <c r="F10" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="143"/>
+      <c r="H10" s="134"/>
     </row>
     <row r="11" spans="2:8" ht="15.75" customHeight="1">
       <c r="B11" s="13" t="s">
@@ -4248,14 +4248,14 @@
       <c r="D11" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="134"/>
+      <c r="E11" s="145"/>
       <c r="F11" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="143"/>
+      <c r="H11" s="134"/>
     </row>
     <row r="12" spans="2:8" ht="15.75" customHeight="1">
       <c r="B12" s="13" t="s">
@@ -4267,14 +4267,14 @@
       <c r="D12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="134"/>
+      <c r="E12" s="145"/>
       <c r="F12" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="143"/>
+      <c r="H12" s="134"/>
     </row>
     <row r="13" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B13" s="23" t="s">
@@ -4286,14 +4286,14 @@
       <c r="D13" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="136"/>
+      <c r="E13" s="146"/>
       <c r="F13" s="26" t="s">
         <v>9</v>
       </c>
       <c r="G13" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="144"/>
+      <c r="H13" s="136"/>
     </row>
     <row r="14" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B14" s="8" t="s">
@@ -4305,7 +4305,7 @@
       <c r="D14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="138">
+      <c r="E14" s="147">
         <v>100</v>
       </c>
       <c r="F14" s="28" t="s">
@@ -4314,8 +4314,8 @@
       <c r="G14" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="142" t="s">
-        <v>406</v>
+      <c r="H14" s="133" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15.75" customHeight="1">
@@ -4328,14 +4328,14 @@
       <c r="D15" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="134"/>
+      <c r="E15" s="145"/>
       <c r="F15" s="15" t="s">
         <v>338</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H15" s="143"/>
+      <c r="H15" s="134"/>
     </row>
     <row r="16" spans="2:8" ht="15.75" customHeight="1">
       <c r="B16" s="13" t="s">
@@ -4347,14 +4347,14 @@
       <c r="D16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="134"/>
+      <c r="E16" s="145"/>
       <c r="F16" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="143"/>
+      <c r="H16" s="134"/>
     </row>
     <row r="17" spans="2:12" ht="15.75" customHeight="1">
       <c r="B17" s="13" t="s">
@@ -4366,14 +4366,14 @@
       <c r="D17" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="134"/>
+      <c r="E17" s="145"/>
       <c r="F17" s="15" t="s">
         <v>340</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H17" s="143"/>
+      <c r="H17" s="134"/>
       <c r="I17" s="29"/>
       <c r="J17" s="29"/>
       <c r="K17" s="29"/>
@@ -4389,14 +4389,14 @@
       <c r="D18" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="134"/>
+      <c r="E18" s="145"/>
       <c r="F18" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="143"/>
+      <c r="H18" s="134"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
       <c r="K18" s="29"/>
@@ -4412,14 +4412,14 @@
       <c r="D19" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="135"/>
+      <c r="E19" s="148"/>
       <c r="F19" s="19" t="s">
         <v>341</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="144"/>
+      <c r="H19" s="136"/>
       <c r="I19" s="29"/>
       <c r="J19" s="29"/>
       <c r="K19" s="29"/>
@@ -4435,7 +4435,7 @@
       <c r="D20" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="133">
+      <c r="E20" s="144">
         <v>100</v>
       </c>
       <c r="F20" s="11" t="s">
@@ -4444,8 +4444,8 @@
       <c r="G20" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="H20" s="142" t="s">
-        <v>408</v>
+      <c r="H20" s="133" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="15.75" customHeight="1">
@@ -4458,14 +4458,14 @@
       <c r="D21" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="134"/>
+      <c r="E21" s="145"/>
       <c r="F21" s="15" t="s">
         <v>338</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H21" s="143"/>
+      <c r="H21" s="134"/>
     </row>
     <row r="22" spans="2:12" ht="15.75" customHeight="1">
       <c r="B22" s="13" t="s">
@@ -4477,14 +4477,14 @@
       <c r="D22" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="134"/>
+      <c r="E22" s="145"/>
       <c r="F22" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H22" s="143"/>
+      <c r="H22" s="134"/>
     </row>
     <row r="23" spans="2:12" ht="15.75" customHeight="1">
       <c r="B23" s="13" t="s">
@@ -4496,14 +4496,14 @@
       <c r="D23" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="134"/>
+      <c r="E23" s="145"/>
       <c r="F23" s="15" t="s">
         <v>340</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H23" s="143"/>
+      <c r="H23" s="134"/>
     </row>
     <row r="24" spans="2:12" ht="15.75" customHeight="1">
       <c r="B24" s="13" t="s">
@@ -4515,14 +4515,14 @@
       <c r="D24" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="134"/>
+      <c r="E24" s="145"/>
       <c r="F24" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H24" s="143"/>
+      <c r="H24" s="134"/>
     </row>
     <row r="25" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B25" s="107" t="s">
@@ -4534,14 +4534,14 @@
       <c r="D25" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="135"/>
+      <c r="E25" s="148"/>
       <c r="F25" s="19" t="s">
         <v>341</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H25" s="144"/>
+      <c r="H25" s="136"/>
     </row>
     <row r="26" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B26" s="21" t="s">
@@ -4553,7 +4553,7 @@
       <c r="D26" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="133">
+      <c r="E26" s="144">
         <v>100</v>
       </c>
       <c r="F26" s="31" t="s">
@@ -4562,8 +4562,8 @@
       <c r="G26" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H26" s="142" t="s">
-        <v>407</v>
+      <c r="H26" s="133" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="27" spans="2:12" ht="15.75" customHeight="1">
@@ -4576,14 +4576,14 @@
       <c r="D27" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="134"/>
+      <c r="E27" s="145"/>
       <c r="F27" s="15" t="s">
         <v>338</v>
       </c>
       <c r="G27" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H27" s="143"/>
+      <c r="H27" s="134"/>
     </row>
     <row r="28" spans="2:12" ht="15.75" customHeight="1">
       <c r="B28" s="13" t="s">
@@ -4595,14 +4595,14 @@
       <c r="D28" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="134"/>
+      <c r="E28" s="145"/>
       <c r="F28" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H28" s="143"/>
+      <c r="H28" s="134"/>
     </row>
     <row r="29" spans="2:12" ht="15.75" customHeight="1">
       <c r="B29" s="13" t="s">
@@ -4614,14 +4614,14 @@
       <c r="D29" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="134"/>
+      <c r="E29" s="145"/>
       <c r="F29" s="15" t="s">
         <v>340</v>
       </c>
       <c r="G29" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H29" s="143"/>
+      <c r="H29" s="134"/>
     </row>
     <row r="30" spans="2:12" ht="15.75" customHeight="1">
       <c r="B30" s="13" t="s">
@@ -4633,14 +4633,14 @@
       <c r="D30" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="134"/>
+      <c r="E30" s="145"/>
       <c r="F30" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H30" s="143"/>
+      <c r="H30" s="134"/>
     </row>
     <row r="31" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B31" s="32" t="s">
@@ -4652,14 +4652,14 @@
       <c r="D31" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="136"/>
+      <c r="E31" s="146"/>
       <c r="F31" s="34" t="s">
         <v>341</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H31" s="144"/>
+      <c r="H31" s="136"/>
     </row>
     <row r="32" spans="2:12" ht="25.9" thickTop="1">
       <c r="B32" s="36" t="s">
@@ -4671,7 +4671,7 @@
       <c r="D32" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="133">
+      <c r="E32" s="144">
         <v>112</v>
       </c>
       <c r="F32" s="31" t="s">
@@ -4680,8 +4680,8 @@
       <c r="G32" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="H32" s="142" t="s">
-        <v>407</v>
+      <c r="H32" s="133" t="s">
+        <v>406</v>
       </c>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -4698,14 +4698,14 @@
       <c r="D33" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="134"/>
+      <c r="E33" s="145"/>
       <c r="F33" s="15" t="s">
         <v>343</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H33" s="143"/>
+      <c r="H33" s="134"/>
       <c r="I33" s="29"/>
       <c r="J33" s="29"/>
       <c r="K33" s="29"/>
@@ -4721,14 +4721,14 @@
       <c r="D34" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="134"/>
+      <c r="E34" s="145"/>
       <c r="F34" s="15" t="s">
         <v>344</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="143"/>
+      <c r="H34" s="134"/>
       <c r="I34" s="29"/>
       <c r="J34" s="29"/>
       <c r="K34" s="29"/>
@@ -4744,14 +4744,14 @@
       <c r="D35" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="134"/>
+      <c r="E35" s="145"/>
       <c r="F35" s="15" t="s">
         <v>345</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H35" s="143"/>
+      <c r="H35" s="134"/>
       <c r="I35" s="29"/>
       <c r="J35" s="29"/>
       <c r="K35" s="29"/>
@@ -4767,14 +4767,14 @@
       <c r="D36" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="134"/>
+      <c r="E36" s="145"/>
       <c r="F36" s="15" t="s">
         <v>346</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H36" s="143"/>
+      <c r="H36" s="134"/>
       <c r="I36" s="29"/>
       <c r="J36" s="29"/>
       <c r="K36" s="29"/>
@@ -4790,14 +4790,14 @@
       <c r="D37" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E37" s="136"/>
+      <c r="E37" s="146"/>
       <c r="F37" s="26" t="s">
         <v>347</v>
       </c>
       <c r="G37" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="H37" s="144"/>
+      <c r="H37" s="136"/>
       <c r="I37" s="29"/>
       <c r="J37" s="29"/>
       <c r="K37" s="29"/>
@@ -4813,7 +4813,7 @@
       <c r="D38" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="133">
+      <c r="E38" s="144">
         <v>100</v>
       </c>
       <c r="F38" s="11" t="s">
@@ -4822,8 +4822,8 @@
       <c r="G38" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="H38" s="142" t="s">
-        <v>407</v>
+      <c r="H38" s="133" t="s">
+        <v>406</v>
       </c>
       <c r="I38" s="29"/>
       <c r="J38" s="29"/>
@@ -4840,14 +4840,14 @@
       <c r="D39" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E39" s="134"/>
+      <c r="E39" s="145"/>
       <c r="F39" s="15" t="s">
         <v>338</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H39" s="143"/>
+      <c r="H39" s="134"/>
       <c r="I39" s="29"/>
       <c r="J39" s="29"/>
       <c r="K39" s="29"/>
@@ -4863,14 +4863,14 @@
       <c r="D40" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E40" s="134"/>
+      <c r="E40" s="145"/>
       <c r="F40" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G40" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H40" s="143"/>
+      <c r="H40" s="134"/>
       <c r="I40" s="29"/>
       <c r="J40" s="29"/>
       <c r="K40" s="29"/>
@@ -4886,14 +4886,14 @@
       <c r="D41" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E41" s="134"/>
+      <c r="E41" s="145"/>
       <c r="F41" s="15" t="s">
         <v>340</v>
       </c>
       <c r="G41" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H41" s="143"/>
+      <c r="H41" s="134"/>
       <c r="I41" s="29"/>
       <c r="J41" s="29"/>
       <c r="K41" s="29"/>
@@ -4909,14 +4909,14 @@
       <c r="D42" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E42" s="134"/>
+      <c r="E42" s="145"/>
       <c r="F42" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G42" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="143"/>
+      <c r="H42" s="134"/>
       <c r="I42" s="29"/>
       <c r="J42" s="29"/>
       <c r="K42" s="29"/>
@@ -4932,14 +4932,14 @@
       <c r="D43" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E43" s="136"/>
+      <c r="E43" s="146"/>
       <c r="F43" s="26" t="s">
         <v>341</v>
       </c>
       <c r="G43" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="H43" s="144"/>
+      <c r="H43" s="136"/>
       <c r="I43" s="29"/>
       <c r="J43" s="29"/>
       <c r="K43" s="29"/>
@@ -4955,7 +4955,7 @@
       <c r="D44" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E44" s="137">
+      <c r="E44" s="149">
         <v>112</v>
       </c>
       <c r="F44" s="11" t="s">
@@ -4964,8 +4964,8 @@
       <c r="G44" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H44" s="142" t="s">
-        <v>406</v>
+      <c r="H44" s="133" t="s">
+        <v>405</v>
       </c>
       <c r="I44" s="29"/>
       <c r="J44" s="29"/>
@@ -4982,14 +4982,14 @@
       <c r="D45" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E45" s="134"/>
+      <c r="E45" s="145"/>
       <c r="F45" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G45" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H45" s="143"/>
+      <c r="H45" s="134"/>
       <c r="I45" s="29"/>
       <c r="J45" s="29"/>
       <c r="K45" s="29"/>
@@ -5005,14 +5005,14 @@
       <c r="D46" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E46" s="134"/>
+      <c r="E46" s="145"/>
       <c r="F46" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G46" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H46" s="143"/>
+      <c r="H46" s="134"/>
       <c r="I46" s="29"/>
       <c r="J46" s="29"/>
       <c r="K46" s="29"/>
@@ -5028,14 +5028,14 @@
       <c r="D47" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E47" s="134"/>
+      <c r="E47" s="145"/>
       <c r="F47" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G47" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H47" s="143"/>
+      <c r="H47" s="134"/>
       <c r="I47" s="29"/>
       <c r="J47" s="29"/>
       <c r="K47" s="29"/>
@@ -5051,14 +5051,14 @@
       <c r="D48" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E48" s="134"/>
+      <c r="E48" s="145"/>
       <c r="F48" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G48" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H48" s="143"/>
+      <c r="H48" s="134"/>
       <c r="I48" s="29"/>
       <c r="J48" s="29"/>
       <c r="K48" s="29"/>
@@ -5074,14 +5074,14 @@
       <c r="D49" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E49" s="135"/>
+      <c r="E49" s="148"/>
       <c r="F49" s="19" t="s">
         <v>349</v>
       </c>
       <c r="G49" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H49" s="144"/>
+      <c r="H49" s="136"/>
       <c r="I49" s="29"/>
       <c r="J49" s="29"/>
       <c r="K49" s="29"/>
@@ -5097,7 +5097,7 @@
       <c r="D50" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E50" s="133">
+      <c r="E50" s="144">
         <v>112</v>
       </c>
       <c r="F50" s="15" t="s">
@@ -5106,8 +5106,8 @@
       <c r="G50" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H50" s="142" t="s">
-        <v>409</v>
+      <c r="H50" s="133" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="51" spans="2:12" ht="15.75" customHeight="1">
@@ -5120,14 +5120,14 @@
       <c r="D51" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E51" s="134"/>
+      <c r="E51" s="145"/>
       <c r="F51" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G51" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H51" s="143"/>
+      <c r="H51" s="134"/>
     </row>
     <row r="52" spans="2:12" ht="15.75" customHeight="1">
       <c r="B52" s="13" t="s">
@@ -5139,14 +5139,14 @@
       <c r="D52" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E52" s="134"/>
+      <c r="E52" s="145"/>
       <c r="F52" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G52" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H52" s="143"/>
+      <c r="H52" s="134"/>
     </row>
     <row r="53" spans="2:12" ht="15.75" customHeight="1">
       <c r="B53" s="13" t="s">
@@ -5158,14 +5158,14 @@
       <c r="D53" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E53" s="134"/>
+      <c r="E53" s="145"/>
       <c r="F53" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G53" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H53" s="143"/>
+      <c r="H53" s="134"/>
     </row>
     <row r="54" spans="2:12" ht="15.75" customHeight="1">
       <c r="B54" s="13" t="s">
@@ -5177,14 +5177,14 @@
       <c r="D54" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E54" s="134"/>
+      <c r="E54" s="145"/>
       <c r="F54" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H54" s="143"/>
+      <c r="H54" s="134"/>
     </row>
     <row r="55" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B55" s="16" t="s">
@@ -5196,14 +5196,14 @@
       <c r="D55" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E55" s="135"/>
+      <c r="E55" s="148"/>
       <c r="F55" s="19" t="s">
         <v>349</v>
       </c>
       <c r="G55" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H55" s="144"/>
+      <c r="H55" s="136"/>
     </row>
     <row r="56" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B56" s="36" t="s">
@@ -5215,7 +5215,7 @@
       <c r="D56" s="63" t="s">
         <v>182</v>
       </c>
-      <c r="E56" s="133">
+      <c r="E56" s="144">
         <v>112</v>
       </c>
       <c r="F56" s="47" t="s">
@@ -5224,8 +5224,8 @@
       <c r="G56" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="H56" s="142" t="s">
-        <v>410</v>
+      <c r="H56" s="133" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="57" spans="2:12" ht="15.75" customHeight="1">
@@ -5238,14 +5238,14 @@
       <c r="D57" s="63" t="s">
         <v>180</v>
       </c>
-      <c r="E57" s="134"/>
+      <c r="E57" s="145"/>
       <c r="F57" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G57" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H57" s="143"/>
+      <c r="H57" s="134"/>
     </row>
     <row r="58" spans="2:12" ht="15.75" customHeight="1">
       <c r="B58" s="38" t="s">
@@ -5257,14 +5257,14 @@
       <c r="D58" s="63" t="s">
         <v>181</v>
       </c>
-      <c r="E58" s="134"/>
+      <c r="E58" s="145"/>
       <c r="F58" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G58" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H58" s="143"/>
+      <c r="H58" s="134"/>
     </row>
     <row r="59" spans="2:12" ht="15.75" customHeight="1">
       <c r="B59" s="38" t="s">
@@ -5276,14 +5276,14 @@
       <c r="D59" s="63" t="s">
         <v>180</v>
       </c>
-      <c r="E59" s="134"/>
+      <c r="E59" s="145"/>
       <c r="F59" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G59" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H59" s="143"/>
+      <c r="H59" s="134"/>
     </row>
     <row r="60" spans="2:12" ht="15.75" customHeight="1">
       <c r="B60" s="38" t="s">
@@ -5295,14 +5295,14 @@
       <c r="D60" s="63" t="s">
         <v>181</v>
       </c>
-      <c r="E60" s="134"/>
+      <c r="E60" s="145"/>
       <c r="F60" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G60" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H60" s="143"/>
+      <c r="H60" s="134"/>
     </row>
     <row r="61" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B61" s="51" t="s">
@@ -5314,14 +5314,14 @@
       <c r="D61" s="63" t="s">
         <v>180</v>
       </c>
-      <c r="E61" s="135"/>
+      <c r="E61" s="148"/>
       <c r="F61" s="53" t="s">
         <v>7</v>
       </c>
       <c r="G61" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H61" s="144"/>
+      <c r="H61" s="136"/>
     </row>
     <row r="62" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B62" s="36" t="s">
@@ -5333,17 +5333,17 @@
       <c r="D62" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E62" s="133">
+      <c r="E62" s="144">
         <v>143</v>
       </c>
       <c r="F62" s="31" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G62" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="H62" s="142" t="s">
-        <v>407</v>
+      <c r="H62" s="133" t="s">
+        <v>406</v>
       </c>
       <c r="I62" s="29"/>
       <c r="J62" s="29"/>
@@ -5360,14 +5360,14 @@
       <c r="D63" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E63" s="134"/>
+      <c r="E63" s="145"/>
       <c r="F63" s="15" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G63" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H63" s="143"/>
+      <c r="H63" s="134"/>
       <c r="I63" s="29"/>
       <c r="J63" s="29"/>
       <c r="K63" s="29"/>
@@ -5383,14 +5383,14 @@
       <c r="D64" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E64" s="134"/>
+      <c r="E64" s="145"/>
       <c r="F64" s="15" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G64" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H64" s="143"/>
+      <c r="H64" s="134"/>
       <c r="I64" s="29"/>
       <c r="J64" s="29"/>
       <c r="K64" s="29"/>
@@ -5406,14 +5406,14 @@
       <c r="D65" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E65" s="134"/>
+      <c r="E65" s="145"/>
       <c r="F65" s="15" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G65" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H65" s="143"/>
+      <c r="H65" s="134"/>
       <c r="I65" s="29"/>
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
@@ -5429,14 +5429,14 @@
       <c r="D66" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E66" s="134"/>
+      <c r="E66" s="145"/>
       <c r="F66" s="15" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G66" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H66" s="143"/>
+      <c r="H66" s="134"/>
       <c r="I66" s="29"/>
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
@@ -5450,14 +5450,14 @@
         <v>12</v>
       </c>
       <c r="D67" s="18"/>
-      <c r="E67" s="135"/>
+      <c r="E67" s="148"/>
       <c r="F67" s="19" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G67" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H67" s="144"/>
+      <c r="H67" s="136"/>
       <c r="I67" s="29"/>
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
@@ -5473,17 +5473,17 @@
       <c r="D68" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E68" s="133">
+      <c r="E68" s="144">
         <v>143</v>
       </c>
       <c r="F68" s="31" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G68" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="H68" s="142" t="s">
-        <v>407</v>
+      <c r="H68" s="133" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="69" spans="2:12" ht="15.75" customHeight="1">
@@ -5496,14 +5496,14 @@
       <c r="D69" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E69" s="134"/>
+      <c r="E69" s="145"/>
       <c r="F69" s="56" t="s">
         <v>201</v>
       </c>
       <c r="G69" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="H69" s="143"/>
+      <c r="H69" s="134"/>
     </row>
     <row r="70" spans="2:12" ht="15.75" customHeight="1">
       <c r="B70" s="38" t="s">
@@ -5515,14 +5515,14 @@
       <c r="D70" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E70" s="134"/>
+      <c r="E70" s="145"/>
       <c r="F70" s="15" t="s">
         <v>202</v>
       </c>
       <c r="G70" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H70" s="143"/>
+      <c r="H70" s="134"/>
     </row>
     <row r="71" spans="2:12" ht="15.75" customHeight="1">
       <c r="B71" s="38" t="s">
@@ -5534,14 +5534,14 @@
       <c r="D71" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E71" s="134"/>
+      <c r="E71" s="145"/>
       <c r="F71" s="56" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G71" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H71" s="143"/>
+      <c r="H71" s="134"/>
     </row>
     <row r="72" spans="2:12" ht="15.75" customHeight="1">
       <c r="B72" s="38" t="s">
@@ -5553,14 +5553,14 @@
       <c r="D72" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E72" s="134"/>
+      <c r="E72" s="145"/>
       <c r="F72" s="15" t="s">
         <v>203</v>
       </c>
       <c r="G72" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H72" s="143"/>
+      <c r="H72" s="134"/>
     </row>
     <row r="73" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B73" s="51" t="s">
@@ -5572,14 +5572,14 @@
       <c r="D73" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E73" s="135"/>
+      <c r="E73" s="148"/>
       <c r="F73" s="57" t="s">
         <v>204</v>
       </c>
       <c r="G73" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H73" s="144"/>
+      <c r="H73" s="136"/>
     </row>
     <row r="74" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B74" s="36" t="s">
@@ -5591,17 +5591,17 @@
       <c r="D74" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E74" s="133">
+      <c r="E74" s="144">
         <v>143</v>
       </c>
       <c r="F74" s="58" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G74" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="H74" s="142" t="s">
-        <v>407</v>
+      <c r="H74" s="133" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="75" spans="2:12" ht="15.75" customHeight="1">
@@ -5614,14 +5614,14 @@
       <c r="D75" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E75" s="134"/>
+      <c r="E75" s="145"/>
       <c r="F75" s="56" t="s">
         <v>192</v>
       </c>
       <c r="G75" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="H75" s="143"/>
+      <c r="H75" s="134"/>
     </row>
     <row r="76" spans="2:12" ht="15.75" customHeight="1">
       <c r="B76" s="38" t="s">
@@ -5633,14 +5633,14 @@
       <c r="D76" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E76" s="134"/>
+      <c r="E76" s="145"/>
       <c r="F76" s="56" t="s">
         <v>193</v>
       </c>
       <c r="G76" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H76" s="143"/>
+      <c r="H76" s="134"/>
     </row>
     <row r="77" spans="2:12" ht="15.75" customHeight="1">
       <c r="B77" s="38" t="s">
@@ -5652,14 +5652,14 @@
       <c r="D77" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E77" s="134"/>
+      <c r="E77" s="145"/>
       <c r="F77" s="56" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G77" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H77" s="143"/>
+      <c r="H77" s="134"/>
     </row>
     <row r="78" spans="2:12" ht="15.75" customHeight="1">
       <c r="B78" s="38" t="s">
@@ -5671,14 +5671,14 @@
       <c r="D78" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E78" s="134"/>
+      <c r="E78" s="145"/>
       <c r="F78" s="56" t="s">
         <v>194</v>
       </c>
       <c r="G78" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H78" s="143"/>
+      <c r="H78" s="134"/>
     </row>
     <row r="79" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B79" s="51" t="s">
@@ -5690,14 +5690,14 @@
       <c r="D79" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E79" s="135"/>
+      <c r="E79" s="148"/>
       <c r="F79" s="57" t="s">
         <v>192</v>
       </c>
       <c r="G79" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H79" s="144"/>
+      <c r="H79" s="136"/>
     </row>
     <row r="80" spans="2:12" ht="38.65" thickTop="1">
       <c r="B80" s="40" t="s">
@@ -5709,7 +5709,7 @@
       <c r="D80" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E80" s="133">
+      <c r="E80" s="144">
         <v>112</v>
       </c>
       <c r="F80" s="11" t="s">
@@ -5718,8 +5718,8 @@
       <c r="G80" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="H80" s="142" t="s">
-        <v>407</v>
+      <c r="H80" s="133" t="s">
+        <v>406</v>
       </c>
       <c r="I80" s="29"/>
       <c r="J80" s="29"/>
@@ -5736,14 +5736,14 @@
       <c r="D81" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E81" s="134"/>
+      <c r="E81" s="145"/>
       <c r="F81" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G81" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H81" s="143"/>
+      <c r="H81" s="134"/>
       <c r="I81" s="29"/>
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
@@ -5759,14 +5759,14 @@
       <c r="D82" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E82" s="134"/>
+      <c r="E82" s="145"/>
       <c r="F82" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G82" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H82" s="143"/>
+      <c r="H82" s="134"/>
       <c r="I82" s="29"/>
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
@@ -5782,14 +5782,14 @@
       <c r="D83" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E83" s="134"/>
+      <c r="E83" s="145"/>
       <c r="F83" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G83" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H83" s="143"/>
+      <c r="H83" s="134"/>
       <c r="I83" s="29"/>
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
@@ -5805,14 +5805,14 @@
       <c r="D84" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E84" s="134"/>
+      <c r="E84" s="145"/>
       <c r="F84" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G84" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H84" s="143"/>
+      <c r="H84" s="134"/>
       <c r="I84" s="29"/>
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
@@ -5828,14 +5828,14 @@
       <c r="D85" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E85" s="136"/>
+      <c r="E85" s="146"/>
       <c r="F85" s="26" t="s">
         <v>350</v>
       </c>
       <c r="G85" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H85" s="144"/>
+      <c r="H85" s="136"/>
       <c r="I85" s="29"/>
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
@@ -5851,7 +5851,7 @@
       <c r="D86" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E86" s="137">
+      <c r="E86" s="149">
         <v>125</v>
       </c>
       <c r="F86" s="11" t="s">
@@ -5860,8 +5860,8 @@
       <c r="G86" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H86" s="142" t="s">
-        <v>406</v>
+      <c r="H86" s="133" t="s">
+        <v>405</v>
       </c>
       <c r="I86" s="29"/>
       <c r="J86" s="29"/>
@@ -5878,14 +5878,14 @@
       <c r="D87" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E87" s="134"/>
+      <c r="E87" s="145"/>
       <c r="F87" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G87" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H87" s="143"/>
+      <c r="H87" s="134"/>
       <c r="I87" s="29"/>
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
@@ -5901,14 +5901,14 @@
       <c r="D88" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E88" s="134"/>
+      <c r="E88" s="145"/>
       <c r="F88" s="15" t="s">
         <v>62</v>
       </c>
       <c r="G88" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H88" s="143"/>
+      <c r="H88" s="134"/>
       <c r="I88" s="29"/>
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
@@ -5924,14 +5924,14 @@
       <c r="D89" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E89" s="134"/>
+      <c r="E89" s="145"/>
       <c r="F89" s="15" t="s">
         <v>63</v>
       </c>
       <c r="G89" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H89" s="143"/>
+      <c r="H89" s="134"/>
       <c r="I89" s="29"/>
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
@@ -5947,14 +5947,14 @@
       <c r="D90" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E90" s="134"/>
+      <c r="E90" s="145"/>
       <c r="F90" s="15" t="s">
         <v>64</v>
       </c>
       <c r="G90" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H90" s="143"/>
+      <c r="H90" s="134"/>
       <c r="I90" s="29"/>
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
@@ -5970,14 +5970,14 @@
       <c r="D91" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E91" s="135"/>
+      <c r="E91" s="148"/>
       <c r="F91" s="19" t="s">
         <v>65</v>
       </c>
       <c r="G91" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H91" s="144"/>
+      <c r="H91" s="136"/>
       <c r="I91" s="29"/>
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
@@ -5993,7 +5993,7 @@
       <c r="D92" s="62" t="s">
         <v>322</v>
       </c>
-      <c r="E92" s="133">
+      <c r="E92" s="144">
         <v>125</v>
       </c>
       <c r="F92" s="47" t="s">
@@ -6002,8 +6002,8 @@
       <c r="G92" s="48" t="s">
         <v>325</v>
       </c>
-      <c r="H92" s="145" t="s">
-        <v>411</v>
+      <c r="H92" s="140" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="93" spans="2:12" ht="15.75" customHeight="1">
@@ -6016,14 +6016,14 @@
       <c r="D93" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="E93" s="134"/>
+      <c r="E93" s="145"/>
       <c r="F93" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H93" s="146"/>
+      <c r="H93" s="138"/>
     </row>
     <row r="94" spans="2:12" ht="15.75" customHeight="1">
       <c r="B94" s="44" t="s">
@@ -6035,14 +6035,14 @@
       <c r="D94" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="E94" s="134"/>
+      <c r="E94" s="145"/>
       <c r="F94" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G94" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H94" s="146"/>
+      <c r="H94" s="138"/>
     </row>
     <row r="95" spans="2:12" ht="15.75" customHeight="1">
       <c r="B95" s="44" t="s">
@@ -6054,14 +6054,14 @@
       <c r="D95" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="E95" s="134"/>
+      <c r="E95" s="145"/>
       <c r="F95" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G95" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H95" s="146"/>
+      <c r="H95" s="138"/>
     </row>
     <row r="96" spans="2:12" ht="15.75" customHeight="1">
       <c r="B96" s="44" t="s">
@@ -6073,14 +6073,14 @@
       <c r="D96" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="E96" s="134"/>
+      <c r="E96" s="145"/>
       <c r="F96" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G96" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H96" s="146"/>
+      <c r="H96" s="138"/>
     </row>
     <row r="97" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B97" s="64" t="s">
@@ -6092,14 +6092,14 @@
       <c r="D97" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="E97" s="135"/>
+      <c r="E97" s="148"/>
       <c r="F97" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G97" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H97" s="147"/>
+      <c r="H97" s="139"/>
     </row>
     <row r="98" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B98" s="36" t="s">
@@ -6111,7 +6111,7 @@
       <c r="D98" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E98" s="133">
+      <c r="E98" s="144">
         <v>125</v>
       </c>
       <c r="F98" s="58" t="s">
@@ -6120,8 +6120,8 @@
       <c r="G98" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="H98" s="142" t="s">
-        <v>407</v>
+      <c r="H98" s="133" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="99" spans="2:8" ht="15.75" customHeight="1">
@@ -6134,14 +6134,14 @@
       <c r="D99" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E99" s="134"/>
+      <c r="E99" s="145"/>
       <c r="F99" s="56" t="s">
         <v>241</v>
       </c>
       <c r="G99" s="54" t="s">
         <v>235</v>
       </c>
-      <c r="H99" s="143"/>
+      <c r="H99" s="134"/>
     </row>
     <row r="100" spans="2:8" ht="15.75" customHeight="1">
       <c r="B100" s="38" t="s">
@@ -6153,14 +6153,14 @@
       <c r="D100" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E100" s="134"/>
+      <c r="E100" s="145"/>
       <c r="F100" s="56" t="s">
         <v>242</v>
       </c>
       <c r="G100" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H100" s="143"/>
+      <c r="H100" s="134"/>
     </row>
     <row r="101" spans="2:8" ht="15.75" customHeight="1">
       <c r="B101" s="38" t="s">
@@ -6172,14 +6172,14 @@
       <c r="D101" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E101" s="134"/>
+      <c r="E101" s="145"/>
       <c r="F101" s="56" t="s">
         <v>243</v>
       </c>
       <c r="G101" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H101" s="143"/>
+      <c r="H101" s="134"/>
     </row>
     <row r="102" spans="2:8" ht="15.75" customHeight="1">
       <c r="B102" s="38" t="s">
@@ -6191,14 +6191,14 @@
       <c r="D102" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E102" s="134"/>
+      <c r="E102" s="145"/>
       <c r="F102" s="56" t="s">
         <v>244</v>
       </c>
       <c r="G102" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H102" s="143"/>
+      <c r="H102" s="134"/>
     </row>
     <row r="103" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B103" s="51" t="s">
@@ -6210,14 +6210,14 @@
       <c r="D103" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E103" s="135"/>
+      <c r="E103" s="148"/>
       <c r="F103" s="57" t="s">
         <v>245</v>
       </c>
       <c r="G103" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="H103" s="144"/>
+      <c r="H103" s="136"/>
     </row>
     <row r="104" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B104" s="61" t="s">
@@ -6229,7 +6229,7 @@
       <c r="D104" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E104" s="133">
+      <c r="E104" s="144">
         <v>125</v>
       </c>
       <c r="F104" s="31" t="s">
@@ -6238,8 +6238,8 @@
       <c r="G104" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="H104" s="142" t="s">
-        <v>407</v>
+      <c r="H104" s="133" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="105" spans="2:8" ht="15.75" customHeight="1">
@@ -6252,14 +6252,14 @@
       <c r="D105" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E105" s="134"/>
+      <c r="E105" s="145"/>
       <c r="F105" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G105" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H105" s="143"/>
+      <c r="H105" s="134"/>
     </row>
     <row r="106" spans="2:8" ht="15.75" customHeight="1">
       <c r="B106" s="44" t="s">
@@ -6271,14 +6271,14 @@
       <c r="D106" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E106" s="134"/>
+      <c r="E106" s="145"/>
       <c r="F106" s="15" t="s">
         <v>62</v>
       </c>
       <c r="G106" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H106" s="143"/>
+      <c r="H106" s="134"/>
     </row>
     <row r="107" spans="2:8" ht="15.75" customHeight="1">
       <c r="B107" s="44" t="s">
@@ -6290,14 +6290,14 @@
       <c r="D107" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E107" s="134"/>
+      <c r="E107" s="145"/>
       <c r="F107" s="15" t="s">
         <v>75</v>
       </c>
       <c r="G107" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H107" s="143"/>
+      <c r="H107" s="134"/>
     </row>
     <row r="108" spans="2:8" ht="15.75" customHeight="1">
       <c r="B108" s="44" t="s">
@@ -6309,14 +6309,14 @@
       <c r="D108" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E108" s="134"/>
+      <c r="E108" s="145"/>
       <c r="F108" s="15" t="s">
         <v>64</v>
       </c>
       <c r="G108" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H108" s="143"/>
+      <c r="H108" s="134"/>
     </row>
     <row r="109" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B109" s="66" t="s">
@@ -6328,14 +6328,14 @@
       <c r="D109" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E109" s="136"/>
+      <c r="E109" s="146"/>
       <c r="F109" s="34" t="s">
         <v>65</v>
       </c>
       <c r="G109" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="H109" s="144"/>
+      <c r="H109" s="136"/>
     </row>
     <row r="110" spans="2:8" ht="25.5" customHeight="1" thickTop="1">
       <c r="B110" s="36" t="s">
@@ -6347,17 +6347,17 @@
       <c r="D110" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E110" s="133">
+      <c r="E110" s="144">
         <v>125</v>
       </c>
       <c r="F110" s="72" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G110" s="37" t="s">
         <v>360</v>
       </c>
-      <c r="H110" s="142" t="s">
-        <v>407</v>
+      <c r="H110" s="133" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="111" spans="2:8" ht="15.75" customHeight="1">
@@ -6370,14 +6370,14 @@
       <c r="D111" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E111" s="134"/>
+      <c r="E111" s="145"/>
       <c r="F111" s="56" t="s">
         <v>362</v>
       </c>
       <c r="G111" s="54" t="s">
         <v>359</v>
       </c>
-      <c r="H111" s="143"/>
+      <c r="H111" s="134"/>
     </row>
     <row r="112" spans="2:8" ht="15.75" customHeight="1">
       <c r="B112" s="38" t="s">
@@ -6389,14 +6389,14 @@
       <c r="D112" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E112" s="134"/>
+      <c r="E112" s="145"/>
       <c r="F112" s="56" t="s">
         <v>358</v>
       </c>
       <c r="G112" s="54" t="s">
         <v>363</v>
       </c>
-      <c r="H112" s="143"/>
+      <c r="H112" s="134"/>
     </row>
     <row r="113" spans="2:12" ht="15.75" customHeight="1">
       <c r="B113" s="38" t="s">
@@ -6408,14 +6408,14 @@
       <c r="D113" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E113" s="134"/>
+      <c r="E113" s="145"/>
       <c r="F113" s="56" t="s">
         <v>365</v>
       </c>
       <c r="G113" s="54" t="s">
         <v>359</v>
       </c>
-      <c r="H113" s="143"/>
+      <c r="H113" s="134"/>
     </row>
     <row r="114" spans="2:12" ht="15.75" customHeight="1">
       <c r="B114" s="38" t="s">
@@ -6427,18 +6427,18 @@
       <c r="D114" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E114" s="134"/>
+      <c r="E114" s="145"/>
       <c r="F114" s="56" t="s">
-        <v>367</v>
+        <v>431</v>
       </c>
       <c r="G114" s="54" t="s">
         <v>359</v>
       </c>
-      <c r="H114" s="143"/>
+      <c r="H114" s="134"/>
     </row>
     <row r="115" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B115" s="51" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C115" s="17">
         <v>40</v>
@@ -6446,14 +6446,14 @@
       <c r="D115" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E115" s="135"/>
+      <c r="E115" s="148"/>
       <c r="F115" s="57" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G115" s="54" t="s">
-        <v>369</v>
-      </c>
-      <c r="H115" s="144"/>
+        <v>368</v>
+      </c>
+      <c r="H115" s="136"/>
     </row>
     <row r="116" spans="2:12" ht="25.9" thickTop="1">
       <c r="B116" s="68" t="s">
@@ -6465,7 +6465,7 @@
       <c r="D116" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E116" s="133">
+      <c r="E116" s="144">
         <v>143</v>
       </c>
       <c r="F116" s="31" t="s">
@@ -6474,8 +6474,8 @@
       <c r="G116" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="H116" s="142" t="s">
-        <v>418</v>
+      <c r="H116" s="133" t="s">
+        <v>417</v>
       </c>
       <c r="I116" s="29"/>
       <c r="J116" s="29"/>
@@ -6492,14 +6492,14 @@
       <c r="D117" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E117" s="134"/>
+      <c r="E117" s="145"/>
       <c r="F117" s="15" t="s">
         <v>253</v>
       </c>
       <c r="G117" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H117" s="143"/>
+      <c r="H117" s="134"/>
       <c r="I117" s="29"/>
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
@@ -6515,14 +6515,14 @@
       <c r="D118" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E118" s="134"/>
+      <c r="E118" s="145"/>
       <c r="F118" s="15" t="s">
         <v>254</v>
       </c>
       <c r="G118" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H118" s="143"/>
+      <c r="H118" s="134"/>
       <c r="I118" s="29"/>
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
@@ -6538,14 +6538,14 @@
       <c r="D119" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E119" s="134"/>
+      <c r="E119" s="145"/>
       <c r="F119" s="15" t="s">
         <v>255</v>
       </c>
       <c r="G119" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H119" s="143"/>
+      <c r="H119" s="134"/>
       <c r="I119" s="29"/>
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
@@ -6561,14 +6561,14 @@
       <c r="D120" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E120" s="134"/>
+      <c r="E120" s="145"/>
       <c r="F120" s="15" t="s">
         <v>256</v>
       </c>
       <c r="G120" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H120" s="143"/>
+      <c r="H120" s="134"/>
       <c r="I120" s="29"/>
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
@@ -6584,14 +6584,14 @@
       <c r="D121" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E121" s="136"/>
+      <c r="E121" s="146"/>
       <c r="F121" s="26" t="s">
         <v>257</v>
       </c>
       <c r="G121" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="H121" s="144"/>
+      <c r="H121" s="136"/>
       <c r="I121" s="29"/>
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
@@ -6607,7 +6607,7 @@
       <c r="D122" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E122" s="133">
+      <c r="E122" s="144">
         <v>125</v>
       </c>
       <c r="F122" s="72" t="s">
@@ -6616,8 +6616,8 @@
       <c r="G122" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="H122" s="142" t="s">
-        <v>407</v>
+      <c r="H122" s="133" t="s">
+        <v>406</v>
       </c>
       <c r="I122" s="29"/>
       <c r="J122" s="29"/>
@@ -6634,14 +6634,14 @@
       <c r="D123" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E123" s="134"/>
+      <c r="E123" s="145"/>
       <c r="F123" s="56" t="s">
         <v>259</v>
       </c>
       <c r="G123" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H123" s="143"/>
+      <c r="H123" s="134"/>
       <c r="I123" s="29"/>
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
@@ -6657,14 +6657,14 @@
       <c r="D124" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E124" s="134"/>
+      <c r="E124" s="145"/>
       <c r="F124" s="56" t="s">
         <v>260</v>
       </c>
       <c r="G124" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H124" s="143"/>
+      <c r="H124" s="134"/>
       <c r="I124" s="29"/>
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
@@ -6680,14 +6680,14 @@
       <c r="D125" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E125" s="134"/>
+      <c r="E125" s="145"/>
       <c r="F125" s="56" t="s">
         <v>261</v>
       </c>
       <c r="G125" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H125" s="143"/>
+      <c r="H125" s="134"/>
       <c r="I125" s="29"/>
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
@@ -6703,14 +6703,14 @@
       <c r="D126" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E126" s="134"/>
+      <c r="E126" s="145"/>
       <c r="F126" s="56" t="s">
         <v>262</v>
       </c>
       <c r="G126" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H126" s="143"/>
+      <c r="H126" s="134"/>
       <c r="I126" s="29"/>
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
@@ -6726,14 +6726,14 @@
       <c r="D127" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E127" s="136"/>
+      <c r="E127" s="146"/>
       <c r="F127" s="73" t="s">
         <v>263</v>
       </c>
       <c r="G127" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="H127" s="144"/>
+      <c r="H127" s="136"/>
       <c r="I127" s="29"/>
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
@@ -6749,7 +6749,7 @@
       <c r="D128" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E128" s="133">
+      <c r="E128" s="144">
         <v>143</v>
       </c>
       <c r="F128" s="72" t="s">
@@ -6758,8 +6758,8 @@
       <c r="G128" s="48" t="s">
         <v>84</v>
       </c>
-      <c r="H128" s="142" t="s">
-        <v>407</v>
+      <c r="H128" s="133" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="129" spans="2:12" ht="15.75" customHeight="1">
@@ -6772,14 +6772,14 @@
       <c r="D129" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E129" s="134"/>
+      <c r="E129" s="145"/>
       <c r="F129" s="56" t="s">
         <v>268</v>
       </c>
       <c r="G129" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="H129" s="143"/>
+      <c r="H129" s="134"/>
     </row>
     <row r="130" spans="2:12" ht="15.75" customHeight="1">
       <c r="B130" s="70" t="s">
@@ -6791,14 +6791,14 @@
       <c r="D130" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E130" s="134"/>
+      <c r="E130" s="145"/>
       <c r="F130" s="56" t="s">
         <v>269</v>
       </c>
       <c r="G130" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H130" s="143"/>
+      <c r="H130" s="134"/>
     </row>
     <row r="131" spans="2:12" ht="15.75" customHeight="1">
       <c r="B131" s="74" t="s">
@@ -6810,14 +6810,14 @@
       <c r="D131" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E131" s="134"/>
+      <c r="E131" s="145"/>
       <c r="F131" s="56" t="s">
         <v>270</v>
       </c>
       <c r="G131" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H131" s="143"/>
+      <c r="H131" s="134"/>
     </row>
     <row r="132" spans="2:12" ht="15.75" customHeight="1">
       <c r="B132" s="74" t="s">
@@ -6829,14 +6829,14 @@
       <c r="D132" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E132" s="134"/>
+      <c r="E132" s="145"/>
       <c r="F132" s="56" t="s">
         <v>271</v>
       </c>
       <c r="G132" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H132" s="143"/>
+      <c r="H132" s="134"/>
     </row>
     <row r="133" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B133" s="71" t="s">
@@ -6848,14 +6848,14 @@
       <c r="D133" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E133" s="136"/>
+      <c r="E133" s="146"/>
       <c r="F133" s="73" t="s">
         <v>272</v>
       </c>
       <c r="G133" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="H133" s="144"/>
+      <c r="H133" s="136"/>
     </row>
     <row r="134" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B134" s="75" t="s">
@@ -6867,7 +6867,7 @@
       <c r="D134" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E134" s="138">
+      <c r="E134" s="147">
         <v>143</v>
       </c>
       <c r="F134" s="28" t="s">
@@ -6876,8 +6876,8 @@
       <c r="G134" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H134" s="142" t="s">
-        <v>406</v>
+      <c r="H134" s="133" t="s">
+        <v>405</v>
       </c>
       <c r="I134" s="29"/>
       <c r="J134" s="29"/>
@@ -6894,14 +6894,14 @@
       <c r="D135" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E135" s="134"/>
+      <c r="E135" s="145"/>
       <c r="F135" s="15" t="s">
         <v>274</v>
       </c>
       <c r="G135" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H135" s="143"/>
+      <c r="H135" s="134"/>
       <c r="I135" s="29"/>
       <c r="J135" s="29"/>
       <c r="K135" s="29"/>
@@ -6917,14 +6917,14 @@
       <c r="D136" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E136" s="134"/>
+      <c r="E136" s="145"/>
       <c r="F136" s="15" t="s">
         <v>275</v>
       </c>
       <c r="G136" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H136" s="143"/>
+      <c r="H136" s="134"/>
       <c r="I136" s="29"/>
       <c r="J136" s="29"/>
       <c r="K136" s="29"/>
@@ -6940,14 +6940,14 @@
       <c r="D137" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E137" s="134"/>
+      <c r="E137" s="145"/>
       <c r="F137" s="15" t="s">
         <v>276</v>
       </c>
       <c r="G137" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H137" s="143"/>
+      <c r="H137" s="134"/>
       <c r="I137" s="29"/>
       <c r="J137" s="29"/>
       <c r="K137" s="29"/>
@@ -6963,14 +6963,14 @@
       <c r="D138" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E138" s="134"/>
+      <c r="E138" s="145"/>
       <c r="F138" s="15" t="s">
         <v>277</v>
       </c>
       <c r="G138" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H138" s="143"/>
+      <c r="H138" s="134"/>
       <c r="I138" s="29"/>
       <c r="J138" s="29"/>
       <c r="K138" s="29"/>
@@ -6986,14 +6986,14 @@
       <c r="D139" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E139" s="135"/>
+      <c r="E139" s="148"/>
       <c r="F139" s="19" t="s">
         <v>278</v>
       </c>
       <c r="G139" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H139" s="144"/>
+      <c r="H139" s="136"/>
       <c r="I139" s="29"/>
       <c r="J139" s="29"/>
       <c r="K139" s="29"/>
@@ -7009,7 +7009,7 @@
       <c r="D140" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E140" s="133">
+      <c r="E140" s="144">
         <v>143</v>
       </c>
       <c r="F140" s="31" t="s">
@@ -7018,8 +7018,8 @@
       <c r="G140" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="H140" s="142" t="s">
-        <v>407</v>
+      <c r="H140" s="133" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="2:12" ht="15.75" customHeight="1">
@@ -7032,14 +7032,14 @@
       <c r="D141" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E141" s="134"/>
+      <c r="E141" s="145"/>
       <c r="F141" s="15" t="s">
         <v>274</v>
       </c>
       <c r="G141" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="H141" s="143"/>
+      <c r="H141" s="134"/>
     </row>
     <row r="142" spans="2:12" ht="15.75" customHeight="1">
       <c r="B142" s="44" t="s">
@@ -7051,14 +7051,14 @@
       <c r="D142" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E142" s="134"/>
+      <c r="E142" s="145"/>
       <c r="F142" s="15" t="s">
         <v>275</v>
       </c>
       <c r="G142" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="H142" s="143"/>
+      <c r="H142" s="134"/>
     </row>
     <row r="143" spans="2:12" ht="15.75" customHeight="1">
       <c r="B143" s="44" t="s">
@@ -7070,14 +7070,14 @@
       <c r="D143" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E143" s="134"/>
+      <c r="E143" s="145"/>
       <c r="F143" s="15" t="s">
         <v>276</v>
       </c>
       <c r="G143" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="H143" s="143"/>
+      <c r="H143" s="134"/>
     </row>
     <row r="144" spans="2:12" ht="15.75" customHeight="1">
       <c r="B144" s="44" t="s">
@@ -7089,14 +7089,14 @@
       <c r="D144" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E144" s="134"/>
+      <c r="E144" s="145"/>
       <c r="F144" s="15" t="s">
         <v>277</v>
       </c>
       <c r="G144" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="H144" s="143"/>
+      <c r="H144" s="134"/>
     </row>
     <row r="145" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B145" s="64" t="s">
@@ -7108,18 +7108,18 @@
       <c r="D145" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E145" s="135"/>
+      <c r="E145" s="148"/>
       <c r="F145" s="19" t="s">
         <v>278</v>
       </c>
       <c r="G145" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="H145" s="144"/>
+      <c r="H145" s="136"/>
     </row>
     <row r="146" spans="1:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B146" s="112" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C146" s="22">
         <v>615</v>
@@ -7127,7 +7127,7 @@
       <c r="D146" s="79" t="s">
         <v>323</v>
       </c>
-      <c r="E146" s="133">
+      <c r="E146" s="144">
         <v>143</v>
       </c>
       <c r="F146" s="47" t="s">
@@ -7136,8 +7136,8 @@
       <c r="G146" s="48" t="s">
         <v>324</v>
       </c>
-      <c r="H146" s="145" t="s">
-        <v>411</v>
+      <c r="H146" s="140" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:12" ht="15.75" customHeight="1">
@@ -7150,14 +7150,14 @@
       <c r="D147" s="80" t="s">
         <v>99</v>
       </c>
-      <c r="E147" s="134"/>
+      <c r="E147" s="145"/>
       <c r="F147" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G147" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H147" s="146"/>
+      <c r="H147" s="138"/>
     </row>
     <row r="148" spans="1:12" ht="15.75" customHeight="1">
       <c r="B148" s="44" t="s">
@@ -7169,14 +7169,14 @@
       <c r="D148" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="E148" s="134"/>
+      <c r="E148" s="145"/>
       <c r="F148" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G148" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H148" s="146"/>
+      <c r="H148" s="138"/>
     </row>
     <row r="149" spans="1:12" ht="15.75" customHeight="1">
       <c r="B149" s="44" t="s">
@@ -7188,14 +7188,14 @@
       <c r="D149" s="80" t="s">
         <v>99</v>
       </c>
-      <c r="E149" s="134"/>
+      <c r="E149" s="145"/>
       <c r="F149" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G149" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H149" s="146"/>
+      <c r="H149" s="138"/>
     </row>
     <row r="150" spans="1:12" ht="15.75" customHeight="1">
       <c r="B150" s="44" t="s">
@@ -7207,14 +7207,14 @@
       <c r="D150" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="E150" s="134"/>
+      <c r="E150" s="145"/>
       <c r="F150" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G150" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H150" s="146"/>
+      <c r="H150" s="138"/>
     </row>
     <row r="151" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B151" s="64" t="s">
@@ -7226,131 +7226,131 @@
       <c r="D151" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="E151" s="135"/>
+      <c r="E151" s="148"/>
       <c r="F151" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G151" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H151" s="147"/>
+      <c r="H151" s="139"/>
     </row>
     <row r="152" spans="1:12" ht="13.5" thickTop="1">
       <c r="A152" s="111"/>
       <c r="B152" s="110" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C152" s="22">
         <v>615</v>
       </c>
       <c r="D152" s="109" t="s">
-        <v>382</v>
-      </c>
-      <c r="E152" s="133">
+        <v>381</v>
+      </c>
+      <c r="E152" s="144">
         <v>143</v>
       </c>
       <c r="F152" s="47" t="s">
         <v>66</v>
       </c>
       <c r="G152" s="114" t="s">
-        <v>378</v>
-      </c>
-      <c r="H152" s="145" t="s">
-        <v>411</v>
+        <v>377</v>
+      </c>
+      <c r="H152" s="140" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="153" spans="1:12" ht="15.75" customHeight="1">
       <c r="B153" s="113" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C153" s="14">
         <v>105</v>
       </c>
       <c r="D153" s="109" t="s">
-        <v>375</v>
-      </c>
-      <c r="E153" s="134"/>
+        <v>374</v>
+      </c>
+      <c r="E153" s="145"/>
       <c r="F153" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G153" s="12"/>
-      <c r="H153" s="146"/>
+      <c r="H153" s="138"/>
     </row>
     <row r="154" spans="1:12" ht="15.75" customHeight="1">
       <c r="B154" s="113" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C154" s="14">
         <v>190</v>
       </c>
       <c r="D154" s="109" t="s">
-        <v>377</v>
-      </c>
-      <c r="E154" s="134"/>
+        <v>376</v>
+      </c>
+      <c r="E154" s="145"/>
       <c r="F154" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G154" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H154" s="146"/>
+      <c r="H154" s="138"/>
     </row>
     <row r="155" spans="1:12" ht="15.75" customHeight="1">
       <c r="B155" s="113" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C155" s="14">
         <v>85</v>
       </c>
       <c r="D155" s="109" t="s">
-        <v>375</v>
-      </c>
-      <c r="E155" s="134"/>
+        <v>374</v>
+      </c>
+      <c r="E155" s="145"/>
       <c r="F155" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G155" s="12"/>
-      <c r="H155" s="146"/>
+      <c r="H155" s="138"/>
     </row>
     <row r="156" spans="1:12" ht="15.75" customHeight="1">
       <c r="B156" s="113" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C156" s="14">
         <v>180</v>
       </c>
       <c r="D156" s="109" t="s">
-        <v>377</v>
-      </c>
-      <c r="E156" s="134"/>
+        <v>376</v>
+      </c>
+      <c r="E156" s="145"/>
       <c r="F156" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G156" s="12"/>
-      <c r="H156" s="146"/>
+      <c r="H156" s="138"/>
     </row>
     <row r="157" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B157" s="116" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C157" s="17">
         <v>55</v>
       </c>
       <c r="D157" s="109" t="s">
-        <v>375</v>
-      </c>
-      <c r="E157" s="135"/>
+        <v>374</v>
+      </c>
+      <c r="E157" s="148"/>
       <c r="F157" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G157" s="115" t="s">
         <v>46</v>
       </c>
-      <c r="H157" s="147"/>
+      <c r="H157" s="139"/>
     </row>
     <row r="158" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B158" s="82" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C158" s="22">
         <v>580</v>
@@ -7358,7 +7358,7 @@
       <c r="D158" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E158" s="133">
+      <c r="E158" s="144">
         <v>167</v>
       </c>
       <c r="F158" s="31" t="s">
@@ -7367,8 +7367,8 @@
       <c r="G158" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H158" s="142" t="s">
-        <v>407</v>
+      <c r="H158" s="133" t="s">
+        <v>406</v>
       </c>
       <c r="I158" s="29"/>
       <c r="J158" s="29"/>
@@ -7385,14 +7385,14 @@
       <c r="D159" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E159" s="134"/>
+      <c r="E159" s="145"/>
       <c r="F159" s="15" t="s">
         <v>274</v>
       </c>
       <c r="G159" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H159" s="143"/>
+      <c r="H159" s="134"/>
       <c r="I159" s="29"/>
       <c r="J159" s="29"/>
       <c r="K159" s="29"/>
@@ -7408,14 +7408,14 @@
       <c r="D160" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E160" s="134"/>
+      <c r="E160" s="145"/>
       <c r="F160" s="15" t="s">
         <v>279</v>
       </c>
       <c r="G160" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H160" s="143"/>
+      <c r="H160" s="134"/>
       <c r="I160" s="29"/>
       <c r="J160" s="29"/>
       <c r="K160" s="29"/>
@@ -7431,14 +7431,14 @@
       <c r="D161" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E161" s="134"/>
+      <c r="E161" s="145"/>
       <c r="F161" s="15" t="s">
         <v>280</v>
       </c>
       <c r="G161" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H161" s="143"/>
+      <c r="H161" s="134"/>
       <c r="I161" s="29"/>
       <c r="J161" s="29"/>
       <c r="K161" s="29"/>
@@ -7454,14 +7454,14 @@
       <c r="D162" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E162" s="134"/>
+      <c r="E162" s="145"/>
       <c r="F162" s="15" t="s">
         <v>281</v>
       </c>
       <c r="G162" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H162" s="143"/>
+      <c r="H162" s="134"/>
       <c r="I162" s="29"/>
       <c r="J162" s="29"/>
       <c r="K162" s="29"/>
@@ -7477,14 +7477,14 @@
       <c r="D163" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E163" s="135"/>
+      <c r="E163" s="148"/>
       <c r="F163" s="19" t="s">
         <v>282</v>
       </c>
       <c r="G163" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="H163" s="144"/>
+      <c r="H163" s="136"/>
       <c r="I163" s="29"/>
       <c r="J163" s="29"/>
       <c r="K163" s="29"/>
@@ -7500,7 +7500,7 @@
       <c r="D164" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E164" s="133">
+      <c r="E164" s="144">
         <v>125</v>
       </c>
       <c r="F164" s="58" t="s">
@@ -7509,8 +7509,8 @@
       <c r="G164" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="H164" s="142" t="s">
-        <v>407</v>
+      <c r="H164" s="133" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="165" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
@@ -7523,14 +7523,14 @@
       <c r="D165" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E165" s="134"/>
+      <c r="E165" s="145"/>
       <c r="F165" s="56" t="s">
         <v>196</v>
       </c>
       <c r="G165" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H165" s="143"/>
+      <c r="H165" s="134"/>
     </row>
     <row r="166" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B166" s="38" t="s">
@@ -7542,14 +7542,14 @@
       <c r="D166" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E166" s="134"/>
+      <c r="E166" s="145"/>
       <c r="F166" s="56" t="s">
         <v>197</v>
       </c>
       <c r="G166" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H166" s="143"/>
+      <c r="H166" s="134"/>
     </row>
     <row r="167" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B167" s="38" t="s">
@@ -7561,14 +7561,14 @@
       <c r="D167" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E167" s="134"/>
+      <c r="E167" s="145"/>
       <c r="F167" s="56" t="s">
         <v>198</v>
       </c>
       <c r="G167" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H167" s="143"/>
+      <c r="H167" s="134"/>
     </row>
     <row r="168" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B168" s="87" t="s">
@@ -7580,14 +7580,14 @@
       <c r="D168" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E168" s="134"/>
+      <c r="E168" s="145"/>
       <c r="F168" s="56" t="s">
         <v>199</v>
       </c>
       <c r="G168" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H168" s="143"/>
+      <c r="H168" s="134"/>
     </row>
     <row r="169" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B169" s="51" t="s">
@@ -7599,18 +7599,18 @@
       <c r="D169" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E169" s="135"/>
+      <c r="E169" s="148"/>
       <c r="F169" s="57" t="s">
         <v>200</v>
       </c>
       <c r="G169" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H169" s="144"/>
+      <c r="H169" s="136"/>
     </row>
     <row r="170" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B170" s="40" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C170" s="9">
         <v>580</v>
@@ -7618,7 +7618,7 @@
       <c r="D170" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E170" s="137">
+      <c r="E170" s="149">
         <v>200</v>
       </c>
       <c r="F170" s="50" t="s">
@@ -7627,8 +7627,8 @@
       <c r="G170" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H170" s="142" t="s">
-        <v>412</v>
+      <c r="H170" s="133" t="s">
+        <v>411</v>
       </c>
       <c r="I170" s="29"/>
       <c r="J170" s="29"/>
@@ -7645,14 +7645,14 @@
       <c r="D171" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E171" s="134"/>
+      <c r="E171" s="145"/>
       <c r="F171" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G171" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="H171" s="143"/>
+      <c r="H171" s="134"/>
       <c r="I171" s="29"/>
       <c r="J171" s="29"/>
       <c r="K171" s="29"/>
@@ -7668,14 +7668,14 @@
       <c r="D172" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E172" s="134"/>
+      <c r="E172" s="145"/>
       <c r="F172" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G172" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="H172" s="143"/>
+      <c r="H172" s="134"/>
       <c r="I172" s="29"/>
       <c r="J172" s="29"/>
       <c r="K172" s="29"/>
@@ -7691,14 +7691,14 @@
       <c r="D173" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E173" s="134"/>
+      <c r="E173" s="145"/>
       <c r="F173" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G173" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="H173" s="143"/>
+      <c r="H173" s="134"/>
       <c r="I173" s="29"/>
       <c r="J173" s="29"/>
       <c r="K173" s="29"/>
@@ -7714,14 +7714,14 @@
       <c r="D174" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E174" s="134"/>
+      <c r="E174" s="145"/>
       <c r="F174" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G174" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="H174" s="143"/>
+      <c r="H174" s="134"/>
       <c r="I174" s="29"/>
       <c r="J174" s="29"/>
       <c r="K174" s="29"/>
@@ -7737,14 +7737,14 @@
       <c r="D175" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E175" s="136"/>
+      <c r="E175" s="146"/>
       <c r="F175" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G175" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="H175" s="144"/>
+      <c r="H175" s="136"/>
       <c r="I175" s="29"/>
       <c r="J175" s="29"/>
       <c r="K175" s="29"/>
@@ -7760,7 +7760,7 @@
       <c r="D176" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E176" s="133">
+      <c r="E176" s="144">
         <v>125</v>
       </c>
       <c r="F176" s="58" t="s">
@@ -7769,8 +7769,8 @@
       <c r="G176" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="H176" s="142" t="s">
-        <v>407</v>
+      <c r="H176" s="133" t="s">
+        <v>406</v>
       </c>
       <c r="I176" s="29"/>
       <c r="J176" s="29"/>
@@ -7787,14 +7787,14 @@
       <c r="D177" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E177" s="134"/>
+      <c r="E177" s="145"/>
       <c r="F177" s="56" t="s">
         <v>284</v>
       </c>
       <c r="G177" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="H177" s="143"/>
+      <c r="H177" s="134"/>
       <c r="I177" s="29"/>
       <c r="J177" s="29"/>
       <c r="K177" s="29"/>
@@ -7810,14 +7810,14 @@
       <c r="D178" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E178" s="134"/>
+      <c r="E178" s="145"/>
       <c r="F178" s="56" t="s">
         <v>285</v>
       </c>
       <c r="G178" s="78" t="s">
         <v>113</v>
       </c>
-      <c r="H178" s="143"/>
+      <c r="H178" s="134"/>
       <c r="I178" s="29"/>
       <c r="J178" s="29"/>
       <c r="K178" s="29"/>
@@ -7833,14 +7833,14 @@
       <c r="D179" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E179" s="134"/>
+      <c r="E179" s="145"/>
       <c r="F179" s="56" t="s">
         <v>286</v>
       </c>
       <c r="G179" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="H179" s="143"/>
+      <c r="H179" s="134"/>
       <c r="I179" s="29"/>
       <c r="J179" s="29"/>
       <c r="K179" s="29"/>
@@ -7856,14 +7856,14 @@
       <c r="D180" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E180" s="134"/>
+      <c r="E180" s="145"/>
       <c r="F180" s="56" t="s">
         <v>287</v>
       </c>
       <c r="G180" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="H180" s="143"/>
+      <c r="H180" s="134"/>
       <c r="I180" s="29"/>
       <c r="J180" s="29"/>
       <c r="K180" s="29"/>
@@ -7879,14 +7879,14 @@
       <c r="D181" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E181" s="135"/>
+      <c r="E181" s="148"/>
       <c r="F181" s="88" t="s">
         <v>288</v>
       </c>
       <c r="G181" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="H181" s="144"/>
+      <c r="H181" s="136"/>
       <c r="I181" s="29"/>
       <c r="J181" s="29"/>
       <c r="K181" s="29"/>
@@ -7902,7 +7902,7 @@
       <c r="D182" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E182" s="138">
+      <c r="E182" s="147">
         <v>167</v>
       </c>
       <c r="F182" s="28" t="s">
@@ -7911,8 +7911,8 @@
       <c r="G182" s="54" t="s">
         <v>326</v>
       </c>
-      <c r="H182" s="142" t="s">
-        <v>406</v>
+      <c r="H182" s="133" t="s">
+        <v>405</v>
       </c>
       <c r="I182" s="29"/>
       <c r="J182" s="29"/>
@@ -7929,14 +7929,14 @@
       <c r="D183" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E183" s="134"/>
+      <c r="E183" s="145"/>
       <c r="F183" s="15" t="s">
         <v>312</v>
       </c>
       <c r="G183" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H183" s="143"/>
+      <c r="H183" s="134"/>
       <c r="I183" s="29"/>
       <c r="J183" s="29"/>
       <c r="K183" s="29"/>
@@ -7952,14 +7952,14 @@
       <c r="D184" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E184" s="134"/>
+      <c r="E184" s="145"/>
       <c r="F184" s="15" t="s">
         <v>313</v>
       </c>
       <c r="G184" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H184" s="143"/>
+      <c r="H184" s="134"/>
     </row>
     <row r="185" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B185" s="42" t="s">
@@ -7971,14 +7971,14 @@
       <c r="D185" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E185" s="134"/>
+      <c r="E185" s="145"/>
       <c r="F185" s="15" t="s">
         <v>314</v>
       </c>
       <c r="G185" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H185" s="143"/>
+      <c r="H185" s="134"/>
     </row>
     <row r="186" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B186" s="44" t="s">
@@ -7990,14 +7990,14 @@
       <c r="D186" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E186" s="134"/>
+      <c r="E186" s="145"/>
       <c r="F186" s="15" t="s">
         <v>313</v>
       </c>
       <c r="G186" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H186" s="143"/>
+      <c r="H186" s="134"/>
       <c r="I186" s="29"/>
       <c r="J186" s="29"/>
       <c r="K186" s="29"/>
@@ -8013,14 +8013,14 @@
       <c r="D187" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E187" s="135"/>
+      <c r="E187" s="148"/>
       <c r="F187" s="19" t="s">
         <v>315</v>
       </c>
       <c r="G187" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="H187" s="148"/>
+      <c r="H187" s="135"/>
       <c r="I187" s="29"/>
       <c r="J187" s="29"/>
       <c r="K187" s="29"/>
@@ -8036,7 +8036,7 @@
       <c r="D188" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E188" s="133">
+      <c r="E188" s="144">
         <v>167</v>
       </c>
       <c r="F188" s="50" t="s">
@@ -8045,8 +8045,8 @@
       <c r="G188" s="54" t="s">
         <v>321</v>
       </c>
-      <c r="H188" s="142" t="s">
-        <v>419</v>
+      <c r="H188" s="133" t="s">
+        <v>418</v>
       </c>
       <c r="I188" s="29"/>
       <c r="J188" s="29"/>
@@ -8063,14 +8063,14 @@
       <c r="D189" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E189" s="134"/>
+      <c r="E189" s="145"/>
       <c r="F189" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G189" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H189" s="143"/>
+      <c r="H189" s="134"/>
       <c r="I189" s="29"/>
       <c r="J189" s="29"/>
       <c r="K189" s="29"/>
@@ -8086,14 +8086,14 @@
       <c r="D190" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E190" s="134"/>
+      <c r="E190" s="145"/>
       <c r="F190" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G190" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H190" s="143"/>
+      <c r="H190" s="134"/>
       <c r="I190" s="29"/>
       <c r="J190" s="29"/>
       <c r="K190" s="29"/>
@@ -8109,14 +8109,14 @@
       <c r="D191" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E191" s="134"/>
+      <c r="E191" s="145"/>
       <c r="F191" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G191" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H191" s="143"/>
+      <c r="H191" s="134"/>
       <c r="I191" s="29"/>
       <c r="J191" s="29"/>
       <c r="K191" s="29"/>
@@ -8132,14 +8132,14 @@
       <c r="D192" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E192" s="134"/>
+      <c r="E192" s="145"/>
       <c r="F192" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G192" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H192" s="143"/>
+      <c r="H192" s="134"/>
       <c r="I192" s="29"/>
       <c r="J192" s="29"/>
       <c r="K192" s="29"/>
@@ -8155,14 +8155,14 @@
       <c r="D193" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E193" s="136"/>
+      <c r="E193" s="146"/>
       <c r="F193" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G193" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="H193" s="148"/>
+      <c r="H193" s="135"/>
       <c r="I193" s="29"/>
       <c r="J193" s="29"/>
       <c r="K193" s="29"/>
@@ -8178,7 +8178,7 @@
       <c r="D194" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E194" s="133">
+      <c r="E194" s="144">
         <v>143</v>
       </c>
       <c r="F194" s="72" t="s">
@@ -8187,8 +8187,8 @@
       <c r="G194" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="H194" s="142" t="s">
-        <v>407</v>
+      <c r="H194" s="133" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="195" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
@@ -8201,14 +8201,14 @@
       <c r="D195" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E195" s="134"/>
+      <c r="E195" s="145"/>
       <c r="F195" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G195" s="54" t="s">
         <v>125</v>
       </c>
-      <c r="H195" s="143"/>
+      <c r="H195" s="134"/>
     </row>
     <row r="196" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B196" s="38" t="s">
@@ -8220,14 +8220,14 @@
       <c r="D196" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E196" s="134"/>
+      <c r="E196" s="145"/>
       <c r="F196" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G196" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H196" s="143"/>
+      <c r="H196" s="134"/>
     </row>
     <row r="197" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B197" s="38" t="s">
@@ -8239,14 +8239,14 @@
       <c r="D197" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E197" s="134"/>
+      <c r="E197" s="145"/>
       <c r="F197" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G197" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H197" s="143"/>
+      <c r="H197" s="134"/>
     </row>
     <row r="198" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B198" s="38" t="s">
@@ -8258,14 +8258,14 @@
       <c r="D198" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E198" s="134"/>
+      <c r="E198" s="145"/>
       <c r="F198" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G198" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H198" s="143"/>
+      <c r="H198" s="134"/>
     </row>
     <row r="199" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B199" s="39" t="s">
@@ -8277,14 +8277,14 @@
       <c r="D199" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E199" s="136"/>
+      <c r="E199" s="146"/>
       <c r="F199" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G199" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="H199" s="144"/>
+      <c r="H199" s="136"/>
     </row>
     <row r="200" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B200" s="68" t="s">
@@ -8296,15 +8296,15 @@
       <c r="D200" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E200" s="133">
+      <c r="E200" s="144">
         <v>233</v>
       </c>
       <c r="F200" s="72"/>
       <c r="G200" s="48" t="s">
         <v>334</v>
       </c>
-      <c r="H200" s="149" t="s">
-        <v>409</v>
+      <c r="H200" s="137" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="201" spans="2:12" ht="15.75" customHeight="1">
@@ -8317,10 +8317,10 @@
       <c r="D201" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E201" s="134"/>
+      <c r="E201" s="145"/>
       <c r="F201" s="50"/>
       <c r="G201" s="12"/>
-      <c r="H201" s="146"/>
+      <c r="H201" s="138"/>
     </row>
     <row r="202" spans="2:12" ht="15.75" customHeight="1">
       <c r="B202" s="70" t="s">
@@ -8332,12 +8332,12 @@
       <c r="D202" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E202" s="134"/>
+      <c r="E202" s="145"/>
       <c r="F202" s="50"/>
       <c r="G202" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H202" s="146"/>
+      <c r="H202" s="138"/>
     </row>
     <row r="203" spans="2:12" ht="15.75" customHeight="1">
       <c r="B203" s="70" t="s">
@@ -8349,12 +8349,12 @@
       <c r="D203" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E203" s="134"/>
+      <c r="E203" s="145"/>
       <c r="F203" s="50"/>
       <c r="G203" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H203" s="146"/>
+      <c r="H203" s="138"/>
     </row>
     <row r="204" spans="2:12" ht="15.75" customHeight="1">
       <c r="B204" s="70" t="s">
@@ -8366,12 +8366,12 @@
       <c r="D204" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E204" s="134"/>
+      <c r="E204" s="145"/>
       <c r="F204" s="50"/>
       <c r="G204" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H204" s="146"/>
+      <c r="H204" s="138"/>
     </row>
     <row r="205" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B205" s="71" t="s">
@@ -8383,16 +8383,16 @@
       <c r="D205" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E205" s="136"/>
+      <c r="E205" s="146"/>
       <c r="F205" s="89"/>
       <c r="G205" s="90" t="s">
         <v>120</v>
       </c>
-      <c r="H205" s="147"/>
+      <c r="H205" s="139"/>
     </row>
     <row r="206" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B206" s="117" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C206" s="22">
         <v>1110</v>
@@ -8400,22 +8400,22 @@
       <c r="D206" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E206" s="133">
+      <c r="E206" s="144">
         <v>167</v>
       </c>
       <c r="F206" s="127" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G206" s="114" t="s">
-        <v>385</v>
-      </c>
-      <c r="H206" s="142" t="s">
-        <v>407</v>
+        <v>384</v>
+      </c>
+      <c r="H206" s="133" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="207" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B207" s="74" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C207" s="14">
         <v>200</v>
@@ -8423,18 +8423,18 @@
       <c r="D207" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E207" s="134"/>
+      <c r="E207" s="145"/>
       <c r="F207" s="127" t="s">
         <v>312</v>
       </c>
       <c r="G207" s="119" t="s">
-        <v>387</v>
-      </c>
-      <c r="H207" s="143"/>
+        <v>386</v>
+      </c>
+      <c r="H207" s="134"/>
     </row>
     <row r="208" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B208" s="125" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C208" s="14">
         <v>300</v>
@@ -8442,18 +8442,18 @@
       <c r="D208" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E208" s="134"/>
+      <c r="E208" s="145"/>
       <c r="F208" s="127" t="s">
         <v>313</v>
       </c>
       <c r="G208" s="120" t="s">
-        <v>386</v>
-      </c>
-      <c r="H208" s="143"/>
+        <v>385</v>
+      </c>
+      <c r="H208" s="134"/>
     </row>
     <row r="209" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B209" s="125" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C209" s="14">
         <v>180</v>
@@ -8461,18 +8461,18 @@
       <c r="D209" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E209" s="134"/>
+      <c r="E209" s="145"/>
       <c r="F209" s="127" t="s">
         <v>314</v>
       </c>
       <c r="G209" s="119" t="s">
-        <v>387</v>
-      </c>
-      <c r="H209" s="143"/>
+        <v>386</v>
+      </c>
+      <c r="H209" s="134"/>
     </row>
     <row r="210" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B210" s="125" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C210" s="14">
         <v>290</v>
@@ -8480,18 +8480,18 @@
       <c r="D210" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E210" s="134"/>
+      <c r="E210" s="145"/>
       <c r="F210" s="127" t="s">
         <v>313</v>
       </c>
       <c r="G210" s="122" t="s">
-        <v>387</v>
-      </c>
-      <c r="H210" s="143"/>
+        <v>386</v>
+      </c>
+      <c r="H210" s="134"/>
     </row>
     <row r="211" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B211" s="126" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C211" s="24">
         <v>140</v>
@@ -8499,18 +8499,18 @@
       <c r="D211" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E211" s="136"/>
+      <c r="E211" s="146"/>
       <c r="F211" s="127" t="s">
         <v>315</v>
       </c>
       <c r="G211" s="121" t="s">
-        <v>387</v>
-      </c>
-      <c r="H211" s="144"/>
+        <v>386</v>
+      </c>
+      <c r="H211" s="136"/>
     </row>
     <row r="212" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B212" s="117" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C212" s="22">
         <v>1110</v>
@@ -8518,22 +8518,22 @@
       <c r="D212" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E212" s="139">
+      <c r="E212" s="141">
         <v>167</v>
       </c>
       <c r="F212" s="127" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G212" s="114" t="s">
-        <v>394</v>
-      </c>
-      <c r="H212" s="142" t="s">
-        <v>407</v>
+        <v>393</v>
+      </c>
+      <c r="H212" s="133" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="213" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B213" s="74" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C213" s="14">
         <v>200</v>
@@ -8541,18 +8541,18 @@
       <c r="D213" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E213" s="140"/>
+      <c r="E213" s="142"/>
       <c r="F213" s="127" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G213" s="118" t="s">
-        <v>396</v>
-      </c>
-      <c r="H213" s="143"/>
+        <v>395</v>
+      </c>
+      <c r="H213" s="134"/>
     </row>
     <row r="214" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B214" s="125" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C214" s="14">
         <v>300</v>
@@ -8560,18 +8560,18 @@
       <c r="D214" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E214" s="140"/>
+      <c r="E214" s="142"/>
       <c r="F214" s="127" t="s">
         <v>313</v>
       </c>
       <c r="G214" s="118" t="s">
-        <v>398</v>
-      </c>
-      <c r="H214" s="143"/>
+        <v>397</v>
+      </c>
+      <c r="H214" s="134"/>
     </row>
     <row r="215" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B215" s="125" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C215" s="14">
         <v>180</v>
@@ -8579,18 +8579,18 @@
       <c r="D215" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E215" s="140"/>
+      <c r="E215" s="142"/>
       <c r="F215" s="127" t="s">
         <v>314</v>
       </c>
       <c r="G215" s="118" t="s">
-        <v>396</v>
-      </c>
-      <c r="H215" s="143"/>
+        <v>395</v>
+      </c>
+      <c r="H215" s="134"/>
     </row>
     <row r="216" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B216" s="125" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C216" s="14">
         <v>290</v>
@@ -8598,18 +8598,18 @@
       <c r="D216" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E216" s="140"/>
+      <c r="E216" s="142"/>
       <c r="F216" s="127" t="s">
         <v>313</v>
       </c>
       <c r="G216" s="118" t="s">
-        <v>396</v>
-      </c>
-      <c r="H216" s="143"/>
+        <v>395</v>
+      </c>
+      <c r="H216" s="134"/>
     </row>
     <row r="217" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B217" s="126" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C217" s="123">
         <v>140</v>
@@ -8617,14 +8617,14 @@
       <c r="D217" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="E217" s="141"/>
+      <c r="E217" s="143"/>
       <c r="F217" s="127" t="s">
         <v>315</v>
       </c>
       <c r="G217" s="119" t="s">
-        <v>399</v>
-      </c>
-      <c r="H217" s="144"/>
+        <v>398</v>
+      </c>
+      <c r="H217" s="136"/>
     </row>
     <row r="218" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B218" s="91" t="s">
@@ -8646,7 +8646,7 @@
         <v>17</v>
       </c>
       <c r="H218" s="128" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="219" spans="2:8" ht="15.75" customHeight="1">
@@ -8669,7 +8669,7 @@
         <v>7</v>
       </c>
       <c r="H219" s="128" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="220" spans="2:8" ht="15.75" customHeight="1">
@@ -8692,7 +8692,7 @@
         <v>7</v>
       </c>
       <c r="H220" s="129" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="221" spans="2:8" ht="15.75" customHeight="1">
@@ -8715,7 +8715,7 @@
         <v>7</v>
       </c>
       <c r="H221" s="128" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="222" spans="2:8" ht="15.75" customHeight="1">
@@ -8738,7 +8738,7 @@
         <v>7</v>
       </c>
       <c r="H222" s="128" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="223" spans="2:8" ht="15.75" customHeight="1">
@@ -8761,7 +8761,7 @@
         <v>132</v>
       </c>
       <c r="H223" s="130" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="224" spans="2:8" ht="15.75" customHeight="1">
@@ -8784,7 +8784,7 @@
         <v>7</v>
       </c>
       <c r="H224" s="128" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="225" spans="2:8" ht="15.75" customHeight="1">
@@ -8807,7 +8807,7 @@
         <v>7</v>
       </c>
       <c r="H225" s="128" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="226" spans="2:8" ht="15.75" customHeight="1">
@@ -8830,7 +8830,7 @@
         <v>7</v>
       </c>
       <c r="H226" s="128" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="227" spans="2:8" ht="15.75" customHeight="1">
@@ -8853,7 +8853,7 @@
         <v>7</v>
       </c>
       <c r="H227" s="128" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="228" spans="2:8" ht="15.75" customHeight="1">
@@ -8876,7 +8876,7 @@
         <v>45</v>
       </c>
       <c r="H228" s="128" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="229" spans="2:8" ht="15.75" customHeight="1">
@@ -8899,12 +8899,12 @@
         <v>7</v>
       </c>
       <c r="H229" s="129" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="230" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B230" s="131" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C230" s="24">
         <v>200</v>
@@ -8922,7 +8922,7 @@
         <v>140</v>
       </c>
       <c r="H230" s="132" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="231" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
@@ -13789,30 +13789,38 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="72">
-    <mergeCell ref="H188:H193"/>
-    <mergeCell ref="H194:H199"/>
-    <mergeCell ref="H200:H205"/>
-    <mergeCell ref="H206:H211"/>
-    <mergeCell ref="H92:H97"/>
-    <mergeCell ref="H98:H103"/>
-    <mergeCell ref="H104:H109"/>
-    <mergeCell ref="H110:H115"/>
-    <mergeCell ref="H116:H121"/>
-    <mergeCell ref="H62:H67"/>
-    <mergeCell ref="H68:H73"/>
-    <mergeCell ref="H74:H79"/>
-    <mergeCell ref="H80:H85"/>
-    <mergeCell ref="H86:H91"/>
-    <mergeCell ref="H32:H37"/>
-    <mergeCell ref="H38:H43"/>
-    <mergeCell ref="H44:H49"/>
-    <mergeCell ref="H50:H55"/>
-    <mergeCell ref="H56:H61"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="H8:H13"/>
-    <mergeCell ref="H14:H19"/>
-    <mergeCell ref="H20:H25"/>
-    <mergeCell ref="H26:H31"/>
+    <mergeCell ref="E140:E145"/>
+    <mergeCell ref="E146:E151"/>
+    <mergeCell ref="E158:E163"/>
+    <mergeCell ref="E194:E199"/>
+    <mergeCell ref="E200:E205"/>
+    <mergeCell ref="E164:E169"/>
+    <mergeCell ref="E170:E175"/>
+    <mergeCell ref="E176:E181"/>
+    <mergeCell ref="E182:E187"/>
+    <mergeCell ref="E188:E193"/>
+    <mergeCell ref="E152:E157"/>
+    <mergeCell ref="E92:E97"/>
+    <mergeCell ref="E98:E103"/>
+    <mergeCell ref="E104:E109"/>
+    <mergeCell ref="E116:E121"/>
+    <mergeCell ref="E122:E127"/>
+    <mergeCell ref="E110:E115"/>
+    <mergeCell ref="E62:E67"/>
+    <mergeCell ref="E68:E73"/>
+    <mergeCell ref="E74:E79"/>
+    <mergeCell ref="E80:E85"/>
+    <mergeCell ref="E86:E91"/>
+    <mergeCell ref="E32:E37"/>
+    <mergeCell ref="E38:E43"/>
+    <mergeCell ref="E44:E49"/>
+    <mergeCell ref="E50:E55"/>
+    <mergeCell ref="E56:E61"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="E8:E13"/>
+    <mergeCell ref="E14:E19"/>
+    <mergeCell ref="E20:E25"/>
+    <mergeCell ref="E26:E31"/>
     <mergeCell ref="E212:E217"/>
     <mergeCell ref="E206:E211"/>
     <mergeCell ref="H122:H127"/>
@@ -13829,38 +13837,30 @@
     <mergeCell ref="E134:E139"/>
     <mergeCell ref="H212:H217"/>
     <mergeCell ref="H182:H187"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="E8:E13"/>
-    <mergeCell ref="E14:E19"/>
-    <mergeCell ref="E20:E25"/>
-    <mergeCell ref="E26:E31"/>
-    <mergeCell ref="E32:E37"/>
-    <mergeCell ref="E38:E43"/>
-    <mergeCell ref="E44:E49"/>
-    <mergeCell ref="E50:E55"/>
-    <mergeCell ref="E56:E61"/>
-    <mergeCell ref="E62:E67"/>
-    <mergeCell ref="E68:E73"/>
-    <mergeCell ref="E74:E79"/>
-    <mergeCell ref="E80:E85"/>
-    <mergeCell ref="E86:E91"/>
-    <mergeCell ref="E92:E97"/>
-    <mergeCell ref="E98:E103"/>
-    <mergeCell ref="E104:E109"/>
-    <mergeCell ref="E116:E121"/>
-    <mergeCell ref="E122:E127"/>
-    <mergeCell ref="E110:E115"/>
-    <mergeCell ref="E140:E145"/>
-    <mergeCell ref="E146:E151"/>
-    <mergeCell ref="E158:E163"/>
-    <mergeCell ref="E194:E199"/>
-    <mergeCell ref="E200:E205"/>
-    <mergeCell ref="E164:E169"/>
-    <mergeCell ref="E170:E175"/>
-    <mergeCell ref="E176:E181"/>
-    <mergeCell ref="E182:E187"/>
-    <mergeCell ref="E188:E193"/>
-    <mergeCell ref="E152:E157"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="H8:H13"/>
+    <mergeCell ref="H14:H19"/>
+    <mergeCell ref="H20:H25"/>
+    <mergeCell ref="H26:H31"/>
+    <mergeCell ref="H32:H37"/>
+    <mergeCell ref="H38:H43"/>
+    <mergeCell ref="H44:H49"/>
+    <mergeCell ref="H50:H55"/>
+    <mergeCell ref="H56:H61"/>
+    <mergeCell ref="H62:H67"/>
+    <mergeCell ref="H68:H73"/>
+    <mergeCell ref="H74:H79"/>
+    <mergeCell ref="H80:H85"/>
+    <mergeCell ref="H86:H91"/>
+    <mergeCell ref="H188:H193"/>
+    <mergeCell ref="H194:H199"/>
+    <mergeCell ref="H200:H205"/>
+    <mergeCell ref="H206:H211"/>
+    <mergeCell ref="H92:H97"/>
+    <mergeCell ref="H98:H103"/>
+    <mergeCell ref="H104:H109"/>
+    <mergeCell ref="H110:H115"/>
+    <mergeCell ref="H116:H121"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-source/护甲数据.xlsx
+++ b/data-source/护甲数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3451394-E046-4CD8-A45C-A1E9925A47F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354C97C5-ADDF-43B1-90EE-4CA2299B01E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -544,9 +544,6 @@
     <t xml:space="preserve">哀悼收割者手套  </t>
   </si>
   <si>
-    <t xml:space="preserve">哀悼收割者马裤  </t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -1576,9 +1573,6 @@
     <t xml:space="preserve">雪原猎人腿甲  </t>
   </si>
   <si>
-    <t xml:space="preserve">哀悼收割者腿甲  </t>
-  </si>
-  <si>
     <t xml:space="preserve">风暴使者腿甲  </t>
   </si>
   <si>
@@ -2350,6 +2344,12 @@
   </si>
   <si>
     <t>厚布：14；布料：16；青铜锭：3；铜锭：7；恐狼牙：20</t>
+  </si>
+  <si>
+    <t>哀悼收割者裤子</t>
+  </si>
+  <si>
+    <t>哀悼收割者靴子</t>
   </si>
 </sst>
 </file>
@@ -3702,46 +3702,46 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4056,7 +4056,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
@@ -4069,22 +4069,22 @@
       <c r="D2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="149">
+      <c r="E2" s="137">
         <v>91</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="133" t="s">
-        <v>405</v>
+      <c r="H2" s="142" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="15.75" customHeight="1">
       <c r="B3" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C3" s="14">
         <v>10</v>
@@ -4092,18 +4092,18 @@
       <c r="D3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="145"/>
+      <c r="E3" s="134"/>
       <c r="F3" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="134"/>
+      <c r="H3" s="143"/>
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1">
       <c r="B4" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C4" s="14">
         <v>25</v>
@@ -4111,18 +4111,18 @@
       <c r="D4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="145"/>
+      <c r="E4" s="134"/>
       <c r="F4" s="15" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="134"/>
+      <c r="H4" s="143"/>
     </row>
     <row r="5" spans="2:8" ht="15.75" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C5" s="14">
         <v>10</v>
@@ -4130,18 +4130,18 @@
       <c r="D5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="145"/>
+      <c r="E5" s="134"/>
       <c r="F5" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="134"/>
+      <c r="H5" s="143"/>
     </row>
     <row r="6" spans="2:8" ht="15.75" customHeight="1">
       <c r="B6" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C6" s="14">
         <v>25</v>
@@ -4149,18 +4149,18 @@
       <c r="D6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="145"/>
+      <c r="E6" s="134"/>
       <c r="F6" s="15" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="134"/>
+      <c r="H6" s="143"/>
     </row>
     <row r="7" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B7" s="16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" s="17">
         <v>0</v>
@@ -4168,14 +4168,14 @@
       <c r="D7" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="148"/>
+      <c r="E7" s="135"/>
       <c r="F7" s="19" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="136"/>
+      <c r="H7" s="144"/>
     </row>
     <row r="8" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B8" s="21" t="s">
@@ -4187,17 +4187,17 @@
       <c r="D8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="144">
+      <c r="E8" s="133">
         <v>91</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="133" t="s">
-        <v>406</v>
+      <c r="H8" s="142" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15.75" customHeight="1">
@@ -4210,14 +4210,14 @@
       <c r="D9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="145"/>
+      <c r="E9" s="134"/>
       <c r="F9" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="134"/>
+      <c r="H9" s="143"/>
     </row>
     <row r="10" spans="2:8" ht="15.75" customHeight="1">
       <c r="B10" s="13" t="s">
@@ -4229,14 +4229,14 @@
       <c r="D10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="145"/>
+      <c r="E10" s="134"/>
       <c r="F10" s="15" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="134"/>
+      <c r="H10" s="143"/>
     </row>
     <row r="11" spans="2:8" ht="15.75" customHeight="1">
       <c r="B11" s="13" t="s">
@@ -4248,18 +4248,18 @@
       <c r="D11" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="145"/>
+      <c r="E11" s="134"/>
       <c r="F11" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="134"/>
+      <c r="H11" s="143"/>
     </row>
     <row r="12" spans="2:8" ht="15.75" customHeight="1">
       <c r="B12" s="13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C12" s="14">
         <v>25</v>
@@ -4267,18 +4267,18 @@
       <c r="D12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="145"/>
+      <c r="E12" s="134"/>
       <c r="F12" s="15" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="134"/>
+      <c r="H12" s="143"/>
     </row>
     <row r="13" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B13" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C13" s="24">
         <v>0</v>
@@ -4286,14 +4286,14 @@
       <c r="D13" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="146"/>
+      <c r="E13" s="136"/>
       <c r="F13" s="26" t="s">
         <v>9</v>
       </c>
       <c r="G13" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="136"/>
+      <c r="H13" s="144"/>
     </row>
     <row r="14" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B14" s="8" t="s">
@@ -4305,22 +4305,22 @@
       <c r="D14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="147">
+      <c r="E14" s="138">
         <v>100</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="133" t="s">
-        <v>405</v>
+      <c r="H14" s="142" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15.75" customHeight="1">
       <c r="B15" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C15" s="14">
         <v>30</v>
@@ -4328,18 +4328,18 @@
       <c r="D15" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="145"/>
+      <c r="E15" s="134"/>
       <c r="F15" s="15" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H15" s="134"/>
+      <c r="H15" s="143"/>
     </row>
     <row r="16" spans="2:8" ht="15.75" customHeight="1">
       <c r="B16" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C16" s="14">
         <v>50</v>
@@ -4347,14 +4347,14 @@
       <c r="D16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="145"/>
+      <c r="E16" s="134"/>
       <c r="F16" s="15" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="134"/>
+      <c r="H16" s="143"/>
     </row>
     <row r="17" spans="2:12" ht="15.75" customHeight="1">
       <c r="B17" s="13" t="s">
@@ -4366,14 +4366,14 @@
       <c r="D17" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="145"/>
+      <c r="E17" s="134"/>
       <c r="F17" s="15" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H17" s="134"/>
+      <c r="H17" s="143"/>
       <c r="I17" s="29"/>
       <c r="J17" s="29"/>
       <c r="K17" s="29"/>
@@ -4381,7 +4381,7 @@
     </row>
     <row r="18" spans="2:12" ht="15.75" customHeight="1">
       <c r="B18" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C18" s="14">
         <v>50</v>
@@ -4389,14 +4389,14 @@
       <c r="D18" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="145"/>
+      <c r="E18" s="134"/>
       <c r="F18" s="15" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="134"/>
+      <c r="H18" s="143"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
       <c r="K18" s="29"/>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="19" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B19" s="16" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C19" s="17">
         <v>0</v>
@@ -4412,14 +4412,14 @@
       <c r="D19" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="148"/>
+      <c r="E19" s="135"/>
       <c r="F19" s="19" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="136"/>
+      <c r="H19" s="144"/>
       <c r="I19" s="29"/>
       <c r="J19" s="29"/>
       <c r="K19" s="29"/>
@@ -4435,22 +4435,22 @@
       <c r="D20" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="144">
+      <c r="E20" s="133">
         <v>100</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G20" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="H20" s="133" t="s">
-        <v>407</v>
+      <c r="H20" s="142" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="15.75" customHeight="1">
       <c r="B21" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C21" s="14">
         <v>30</v>
@@ -4458,18 +4458,18 @@
       <c r="D21" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="145"/>
+      <c r="E21" s="134"/>
       <c r="F21" s="15" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H21" s="134"/>
+      <c r="H21" s="143"/>
     </row>
     <row r="22" spans="2:12" ht="15.75" customHeight="1">
       <c r="B22" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C22" s="14">
         <v>50</v>
@@ -4477,14 +4477,14 @@
       <c r="D22" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="145"/>
+      <c r="E22" s="134"/>
       <c r="F22" s="15" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H22" s="134"/>
+      <c r="H22" s="143"/>
     </row>
     <row r="23" spans="2:12" ht="15.75" customHeight="1">
       <c r="B23" s="13" t="s">
@@ -4496,18 +4496,18 @@
       <c r="D23" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="145"/>
+      <c r="E23" s="134"/>
       <c r="F23" s="15" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H23" s="134"/>
+      <c r="H23" s="143"/>
     </row>
     <row r="24" spans="2:12" ht="15.75" customHeight="1">
       <c r="B24" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C24" s="14">
         <v>50</v>
@@ -4515,18 +4515,18 @@
       <c r="D24" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="145"/>
+      <c r="E24" s="134"/>
       <c r="F24" s="15" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H24" s="134"/>
+      <c r="H24" s="143"/>
     </row>
     <row r="25" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B25" s="107" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C25" s="17">
         <v>0</v>
@@ -4534,14 +4534,14 @@
       <c r="D25" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="148"/>
+      <c r="E25" s="135"/>
       <c r="F25" s="19" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H25" s="136"/>
+      <c r="H25" s="144"/>
     </row>
     <row r="26" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B26" s="21" t="s">
@@ -4553,22 +4553,22 @@
       <c r="D26" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="144">
+      <c r="E26" s="133">
         <v>100</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G26" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H26" s="133" t="s">
-        <v>406</v>
+      <c r="H26" s="142" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="27" spans="2:12" ht="15.75" customHeight="1">
       <c r="B27" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C27" s="14">
         <v>30</v>
@@ -4576,18 +4576,18 @@
       <c r="D27" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="145"/>
+      <c r="E27" s="134"/>
       <c r="F27" s="15" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G27" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H27" s="134"/>
+      <c r="H27" s="143"/>
     </row>
     <row r="28" spans="2:12" ht="15.75" customHeight="1">
       <c r="B28" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C28" s="14">
         <v>50</v>
@@ -4595,18 +4595,18 @@
       <c r="D28" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="145"/>
+      <c r="E28" s="134"/>
       <c r="F28" s="15" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H28" s="134"/>
+      <c r="H28" s="143"/>
     </row>
     <row r="29" spans="2:12" ht="15.75" customHeight="1">
       <c r="B29" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C29" s="14">
         <v>20</v>
@@ -4614,18 +4614,18 @@
       <c r="D29" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="145"/>
+      <c r="E29" s="134"/>
       <c r="F29" s="15" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G29" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H29" s="134"/>
+      <c r="H29" s="143"/>
     </row>
     <row r="30" spans="2:12" ht="15.75" customHeight="1">
       <c r="B30" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C30" s="14">
         <v>50</v>
@@ -4633,18 +4633,18 @@
       <c r="D30" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="145"/>
+      <c r="E30" s="134"/>
       <c r="F30" s="15" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H30" s="134"/>
+      <c r="H30" s="143"/>
     </row>
     <row r="31" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B31" s="32" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C31" s="33">
         <v>0</v>
@@ -4652,14 +4652,14 @@
       <c r="D31" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="146"/>
+      <c r="E31" s="136"/>
       <c r="F31" s="34" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H31" s="136"/>
+      <c r="H31" s="144"/>
     </row>
     <row r="32" spans="2:12" ht="25.9" thickTop="1">
       <c r="B32" s="36" t="s">
@@ -4671,17 +4671,17 @@
       <c r="D32" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="144">
+      <c r="E32" s="133">
         <v>112</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G32" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="H32" s="133" t="s">
-        <v>406</v>
+      <c r="H32" s="142" t="s">
+        <v>404</v>
       </c>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -4690,7 +4690,7 @@
     </row>
     <row r="33" spans="2:12" ht="15.75" customHeight="1">
       <c r="B33" s="87" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C33" s="14">
         <v>40</v>
@@ -4698,14 +4698,14 @@
       <c r="D33" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="145"/>
+      <c r="E33" s="134"/>
       <c r="F33" s="15" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H33" s="134"/>
+      <c r="H33" s="143"/>
       <c r="I33" s="29"/>
       <c r="J33" s="29"/>
       <c r="K33" s="29"/>
@@ -4721,14 +4721,14 @@
       <c r="D34" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="145"/>
+      <c r="E34" s="134"/>
       <c r="F34" s="15" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="134"/>
+      <c r="H34" s="143"/>
       <c r="I34" s="29"/>
       <c r="J34" s="29"/>
       <c r="K34" s="29"/>
@@ -4736,7 +4736,7 @@
     </row>
     <row r="35" spans="2:12" ht="15.75" customHeight="1">
       <c r="B35" s="38" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C35" s="14">
         <v>30</v>
@@ -4744,14 +4744,14 @@
       <c r="D35" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="145"/>
+      <c r="E35" s="134"/>
       <c r="F35" s="15" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H35" s="134"/>
+      <c r="H35" s="143"/>
       <c r="I35" s="29"/>
       <c r="J35" s="29"/>
       <c r="K35" s="29"/>
@@ -4759,7 +4759,7 @@
     </row>
     <row r="36" spans="2:12" ht="15.75" customHeight="1">
       <c r="B36" s="87" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C36" s="14">
         <v>60</v>
@@ -4767,14 +4767,14 @@
       <c r="D36" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="145"/>
+      <c r="E36" s="134"/>
       <c r="F36" s="15" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H36" s="134"/>
+      <c r="H36" s="143"/>
       <c r="I36" s="29"/>
       <c r="J36" s="29"/>
       <c r="K36" s="29"/>
@@ -4782,7 +4782,7 @@
     </row>
     <row r="37" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B37" s="108" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C37" s="24">
         <v>10</v>
@@ -4790,14 +4790,14 @@
       <c r="D37" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E37" s="146"/>
+      <c r="E37" s="136"/>
       <c r="F37" s="26" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G37" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="H37" s="136"/>
+      <c r="H37" s="144"/>
       <c r="I37" s="29"/>
       <c r="J37" s="29"/>
       <c r="K37" s="29"/>
@@ -4813,17 +4813,17 @@
       <c r="D38" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="144">
+      <c r="E38" s="133">
         <v>100</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G38" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="H38" s="133" t="s">
-        <v>406</v>
+      <c r="H38" s="142" t="s">
+        <v>404</v>
       </c>
       <c r="I38" s="29"/>
       <c r="J38" s="29"/>
@@ -4840,14 +4840,14 @@
       <c r="D39" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E39" s="145"/>
+      <c r="E39" s="134"/>
       <c r="F39" s="15" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H39" s="134"/>
+      <c r="H39" s="143"/>
       <c r="I39" s="29"/>
       <c r="J39" s="29"/>
       <c r="K39" s="29"/>
@@ -4863,14 +4863,14 @@
       <c r="D40" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E40" s="145"/>
+      <c r="E40" s="134"/>
       <c r="F40" s="15" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G40" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H40" s="134"/>
+      <c r="H40" s="143"/>
       <c r="I40" s="29"/>
       <c r="J40" s="29"/>
       <c r="K40" s="29"/>
@@ -4886,14 +4886,14 @@
       <c r="D41" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E41" s="145"/>
+      <c r="E41" s="134"/>
       <c r="F41" s="15" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G41" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H41" s="134"/>
+      <c r="H41" s="143"/>
       <c r="I41" s="29"/>
       <c r="J41" s="29"/>
       <c r="K41" s="29"/>
@@ -4901,7 +4901,7 @@
     </row>
     <row r="42" spans="2:12" ht="15.75" customHeight="1">
       <c r="B42" s="44" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C42" s="14">
         <v>50</v>
@@ -4909,14 +4909,14 @@
       <c r="D42" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E42" s="145"/>
+      <c r="E42" s="134"/>
       <c r="F42" s="15" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G42" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="134"/>
+      <c r="H42" s="143"/>
       <c r="I42" s="29"/>
       <c r="J42" s="29"/>
       <c r="K42" s="29"/>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="43" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B43" s="45" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C43" s="24">
         <v>0</v>
@@ -4932,14 +4932,14 @@
       <c r="D43" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E43" s="146"/>
+      <c r="E43" s="136"/>
       <c r="F43" s="26" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G43" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="H43" s="136"/>
+      <c r="H43" s="144"/>
       <c r="I43" s="29"/>
       <c r="J43" s="29"/>
       <c r="K43" s="29"/>
@@ -4955,17 +4955,17 @@
       <c r="D44" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E44" s="149">
+      <c r="E44" s="137">
         <v>112</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G44" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H44" s="133" t="s">
-        <v>405</v>
+      <c r="H44" s="142" t="s">
+        <v>403</v>
       </c>
       <c r="I44" s="29"/>
       <c r="J44" s="29"/>
@@ -4974,7 +4974,7 @@
     </row>
     <row r="45" spans="2:12" ht="15.75" customHeight="1">
       <c r="B45" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C45" s="14">
         <v>50</v>
@@ -4982,14 +4982,14 @@
       <c r="D45" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E45" s="145"/>
+      <c r="E45" s="134"/>
       <c r="F45" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G45" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H45" s="134"/>
+      <c r="H45" s="143"/>
       <c r="I45" s="29"/>
       <c r="J45" s="29"/>
       <c r="K45" s="29"/>
@@ -4997,7 +4997,7 @@
     </row>
     <row r="46" spans="2:12" ht="15.75" customHeight="1">
       <c r="B46" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C46" s="14">
         <v>90</v>
@@ -5005,14 +5005,14 @@
       <c r="D46" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E46" s="145"/>
+      <c r="E46" s="134"/>
       <c r="F46" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G46" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H46" s="134"/>
+      <c r="H46" s="143"/>
       <c r="I46" s="29"/>
       <c r="J46" s="29"/>
       <c r="K46" s="29"/>
@@ -5020,7 +5020,7 @@
     </row>
     <row r="47" spans="2:12" ht="15.75" customHeight="1">
       <c r="B47" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C47" s="14">
         <v>30</v>
@@ -5028,14 +5028,14 @@
       <c r="D47" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E47" s="145"/>
+      <c r="E47" s="134"/>
       <c r="F47" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G47" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H47" s="134"/>
+      <c r="H47" s="143"/>
       <c r="I47" s="29"/>
       <c r="J47" s="29"/>
       <c r="K47" s="29"/>
@@ -5043,7 +5043,7 @@
     </row>
     <row r="48" spans="2:12" ht="15.75" customHeight="1">
       <c r="B48" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C48" s="14">
         <v>80</v>
@@ -5051,14 +5051,14 @@
       <c r="D48" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E48" s="145"/>
+      <c r="E48" s="134"/>
       <c r="F48" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G48" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H48" s="134"/>
+      <c r="H48" s="143"/>
       <c r="I48" s="29"/>
       <c r="J48" s="29"/>
       <c r="K48" s="29"/>
@@ -5066,7 +5066,7 @@
     </row>
     <row r="49" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B49" s="16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C49" s="17">
         <v>10</v>
@@ -5074,14 +5074,14 @@
       <c r="D49" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E49" s="148"/>
+      <c r="E49" s="135"/>
       <c r="F49" s="19" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G49" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H49" s="136"/>
+      <c r="H49" s="144"/>
       <c r="I49" s="29"/>
       <c r="J49" s="29"/>
       <c r="K49" s="29"/>
@@ -5097,17 +5097,17 @@
       <c r="D50" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E50" s="144">
+      <c r="E50" s="133">
         <v>112</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G50" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H50" s="133" t="s">
-        <v>408</v>
+      <c r="H50" s="142" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="51" spans="2:12" ht="15.75" customHeight="1">
@@ -5120,18 +5120,18 @@
       <c r="D51" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E51" s="145"/>
+      <c r="E51" s="134"/>
       <c r="F51" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G51" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H51" s="134"/>
+      <c r="H51" s="143"/>
     </row>
     <row r="52" spans="2:12" ht="15.75" customHeight="1">
       <c r="B52" s="13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C52" s="14">
         <v>90</v>
@@ -5139,18 +5139,18 @@
       <c r="D52" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E52" s="145"/>
+      <c r="E52" s="134"/>
       <c r="F52" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G52" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H52" s="134"/>
+      <c r="H52" s="143"/>
     </row>
     <row r="53" spans="2:12" ht="15.75" customHeight="1">
       <c r="B53" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C53" s="14">
         <v>30</v>
@@ -5158,18 +5158,18 @@
       <c r="D53" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E53" s="145"/>
+      <c r="E53" s="134"/>
       <c r="F53" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G53" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H53" s="134"/>
+      <c r="H53" s="143"/>
     </row>
     <row r="54" spans="2:12" ht="15.75" customHeight="1">
       <c r="B54" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C54" s="14">
         <v>80</v>
@@ -5177,18 +5177,18 @@
       <c r="D54" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E54" s="145"/>
+      <c r="E54" s="134"/>
       <c r="F54" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H54" s="134"/>
+      <c r="H54" s="143"/>
     </row>
     <row r="55" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B55" s="16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C55" s="17">
         <v>10</v>
@@ -5196,14 +5196,14 @@
       <c r="D55" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E55" s="148"/>
+      <c r="E55" s="135"/>
       <c r="F55" s="19" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G55" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H55" s="136"/>
+      <c r="H55" s="144"/>
     </row>
     <row r="56" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B56" s="36" t="s">
@@ -5213,9 +5213,9 @@
         <v>260</v>
       </c>
       <c r="D56" s="63" t="s">
-        <v>182</v>
-      </c>
-      <c r="E56" s="144">
+        <v>181</v>
+      </c>
+      <c r="E56" s="133">
         <v>112</v>
       </c>
       <c r="F56" s="47" t="s">
@@ -5224,104 +5224,104 @@
       <c r="G56" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="H56" s="133" t="s">
-        <v>409</v>
+      <c r="H56" s="142" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="57" spans="2:12" ht="15.75" customHeight="1">
       <c r="B57" s="38" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C57" s="49">
         <v>50</v>
       </c>
       <c r="D57" s="63" t="s">
-        <v>180</v>
-      </c>
-      <c r="E57" s="145"/>
+        <v>179</v>
+      </c>
+      <c r="E57" s="134"/>
       <c r="F57" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G57" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H57" s="134"/>
+      <c r="H57" s="143"/>
     </row>
     <row r="58" spans="2:12" ht="15.75" customHeight="1">
       <c r="B58" s="38" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C58" s="49">
         <v>90</v>
       </c>
       <c r="D58" s="63" t="s">
-        <v>181</v>
-      </c>
-      <c r="E58" s="145"/>
+        <v>180</v>
+      </c>
+      <c r="E58" s="134"/>
       <c r="F58" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G58" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H58" s="134"/>
+      <c r="H58" s="143"/>
     </row>
     <row r="59" spans="2:12" ht="15.75" customHeight="1">
       <c r="B59" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C59" s="49">
         <v>30</v>
       </c>
       <c r="D59" s="63" t="s">
-        <v>180</v>
-      </c>
-      <c r="E59" s="145"/>
+        <v>179</v>
+      </c>
+      <c r="E59" s="134"/>
       <c r="F59" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G59" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H59" s="134"/>
+      <c r="H59" s="143"/>
     </row>
     <row r="60" spans="2:12" ht="15.75" customHeight="1">
       <c r="B60" s="38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C60" s="49">
         <v>80</v>
       </c>
       <c r="D60" s="63" t="s">
-        <v>181</v>
-      </c>
-      <c r="E60" s="145"/>
+        <v>180</v>
+      </c>
+      <c r="E60" s="134"/>
       <c r="F60" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G60" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H60" s="134"/>
+      <c r="H60" s="143"/>
     </row>
     <row r="61" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B61" s="51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C61" s="52">
         <v>10</v>
       </c>
       <c r="D61" s="63" t="s">
-        <v>180</v>
-      </c>
-      <c r="E61" s="148"/>
+        <v>179</v>
+      </c>
+      <c r="E61" s="135"/>
       <c r="F61" s="53" t="s">
         <v>7</v>
       </c>
       <c r="G61" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H61" s="136"/>
+      <c r="H61" s="144"/>
     </row>
     <row r="62" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B62" s="36" t="s">
@@ -5333,17 +5333,17 @@
       <c r="D62" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E62" s="144">
+      <c r="E62" s="133">
         <v>143</v>
       </c>
       <c r="F62" s="31" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="G62" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="H62" s="133" t="s">
-        <v>406</v>
+      <c r="H62" s="142" t="s">
+        <v>404</v>
       </c>
       <c r="I62" s="29"/>
       <c r="J62" s="29"/>
@@ -5352,7 +5352,7 @@
     </row>
     <row r="63" spans="2:12" ht="15.75" customHeight="1">
       <c r="B63" s="38" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C63" s="14">
         <v>60</v>
@@ -5360,14 +5360,14 @@
       <c r="D63" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E63" s="145"/>
+      <c r="E63" s="134"/>
       <c r="F63" s="15" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G63" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H63" s="134"/>
+      <c r="H63" s="143"/>
       <c r="I63" s="29"/>
       <c r="J63" s="29"/>
       <c r="K63" s="29"/>
@@ -5375,7 +5375,7 @@
     </row>
     <row r="64" spans="2:12" ht="15.75" customHeight="1">
       <c r="B64" s="38" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C64" s="14">
         <v>110</v>
@@ -5383,14 +5383,14 @@
       <c r="D64" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E64" s="145"/>
+      <c r="E64" s="134"/>
       <c r="F64" s="15" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G64" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H64" s="134"/>
+      <c r="H64" s="143"/>
       <c r="I64" s="29"/>
       <c r="J64" s="29"/>
       <c r="K64" s="29"/>
@@ -5398,7 +5398,7 @@
     </row>
     <row r="65" spans="2:12" ht="15.75" customHeight="1">
       <c r="B65" s="38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C65" s="14">
         <v>35</v>
@@ -5406,14 +5406,14 @@
       <c r="D65" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E65" s="145"/>
+      <c r="E65" s="134"/>
       <c r="F65" s="15" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="G65" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H65" s="134"/>
+      <c r="H65" s="143"/>
       <c r="I65" s="29"/>
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
@@ -5421,7 +5421,7 @@
     </row>
     <row r="66" spans="2:12" ht="15.75" customHeight="1">
       <c r="B66" s="38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C66" s="14">
         <v>95</v>
@@ -5429,14 +5429,14 @@
       <c r="D66" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E66" s="145"/>
+      <c r="E66" s="134"/>
       <c r="F66" s="15" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G66" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H66" s="134"/>
+      <c r="H66" s="143"/>
       <c r="I66" s="29"/>
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
@@ -5444,20 +5444,20 @@
     </row>
     <row r="67" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B67" s="51" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C67" s="17">
         <v>12</v>
       </c>
       <c r="D67" s="18"/>
-      <c r="E67" s="148"/>
+      <c r="E67" s="135"/>
       <c r="F67" s="19" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G67" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H67" s="136"/>
+      <c r="H67" s="144"/>
       <c r="I67" s="29"/>
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
@@ -5473,17 +5473,17 @@
       <c r="D68" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E68" s="144">
+      <c r="E68" s="133">
         <v>143</v>
       </c>
       <c r="F68" s="31" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="G68" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="H68" s="133" t="s">
-        <v>406</v>
+      <c r="H68" s="142" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="69" spans="2:12" ht="15.75" customHeight="1">
@@ -5496,18 +5496,18 @@
       <c r="D69" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E69" s="145"/>
+      <c r="E69" s="134"/>
       <c r="F69" s="56" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G69" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="H69" s="134"/>
+      <c r="H69" s="143"/>
     </row>
     <row r="70" spans="2:12" ht="15.75" customHeight="1">
       <c r="B70" s="38" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C70" s="14">
         <v>110</v>
@@ -5515,18 +5515,18 @@
       <c r="D70" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E70" s="145"/>
+      <c r="E70" s="134"/>
       <c r="F70" s="15" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G70" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H70" s="134"/>
+      <c r="H70" s="143"/>
     </row>
     <row r="71" spans="2:12" ht="15.75" customHeight="1">
       <c r="B71" s="38" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C71" s="14">
         <v>35</v>
@@ -5534,18 +5534,18 @@
       <c r="D71" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E71" s="145"/>
+      <c r="E71" s="134"/>
       <c r="F71" s="56" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="G71" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H71" s="134"/>
+      <c r="H71" s="143"/>
     </row>
     <row r="72" spans="2:12" ht="15.75" customHeight="1">
       <c r="B72" s="38" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C72" s="14">
         <v>95</v>
@@ -5553,18 +5553,18 @@
       <c r="D72" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E72" s="145"/>
+      <c r="E72" s="134"/>
       <c r="F72" s="15" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G72" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H72" s="134"/>
+      <c r="H72" s="143"/>
     </row>
     <row r="73" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B73" s="51" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C73" s="17">
         <v>12</v>
@@ -5572,14 +5572,14 @@
       <c r="D73" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E73" s="148"/>
+      <c r="E73" s="135"/>
       <c r="F73" s="57" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G73" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H73" s="136"/>
+      <c r="H73" s="144"/>
     </row>
     <row r="74" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B74" s="36" t="s">
@@ -5591,22 +5591,22 @@
       <c r="D74" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E74" s="144">
+      <c r="E74" s="133">
         <v>143</v>
       </c>
       <c r="F74" s="58" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G74" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="H74" s="133" t="s">
-        <v>406</v>
+      <c r="H74" s="142" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="75" spans="2:12" ht="15.75" customHeight="1">
       <c r="B75" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C75" s="49">
         <v>70</v>
@@ -5614,18 +5614,18 @@
       <c r="D75" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E75" s="145"/>
+      <c r="E75" s="134"/>
       <c r="F75" s="56" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G75" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="H75" s="134"/>
+      <c r="H75" s="143"/>
     </row>
     <row r="76" spans="2:12" ht="15.75" customHeight="1">
       <c r="B76" s="38" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C76" s="49">
         <v>110</v>
@@ -5633,18 +5633,18 @@
       <c r="D76" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E76" s="145"/>
+      <c r="E76" s="134"/>
       <c r="F76" s="56" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G76" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H76" s="134"/>
+      <c r="H76" s="143"/>
     </row>
     <row r="77" spans="2:12" ht="15.75" customHeight="1">
       <c r="B77" s="38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C77" s="49">
         <v>35</v>
@@ -5652,18 +5652,18 @@
       <c r="D77" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E77" s="145"/>
+      <c r="E77" s="134"/>
       <c r="F77" s="56" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G77" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H77" s="134"/>
+      <c r="H77" s="143"/>
     </row>
     <row r="78" spans="2:12" ht="15.75" customHeight="1">
       <c r="B78" s="38" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C78" s="49">
         <v>95</v>
@@ -5671,18 +5671,18 @@
       <c r="D78" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E78" s="145"/>
+      <c r="E78" s="134"/>
       <c r="F78" s="56" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G78" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H78" s="134"/>
+      <c r="H78" s="143"/>
     </row>
     <row r="79" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B79" s="51" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C79" s="52">
         <v>12</v>
@@ -5690,14 +5690,14 @@
       <c r="D79" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E79" s="148"/>
+      <c r="E79" s="135"/>
       <c r="F79" s="57" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G79" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H79" s="136"/>
+      <c r="H79" s="144"/>
     </row>
     <row r="80" spans="2:12" ht="38.65" thickTop="1">
       <c r="B80" s="40" t="s">
@@ -5709,17 +5709,17 @@
       <c r="D80" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E80" s="144">
+      <c r="E80" s="133">
         <v>112</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G80" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="H80" s="133" t="s">
-        <v>406</v>
+      <c r="H80" s="142" t="s">
+        <v>404</v>
       </c>
       <c r="I80" s="29"/>
       <c r="J80" s="29"/>
@@ -5728,7 +5728,7 @@
     </row>
     <row r="81" spans="2:12" ht="15.75" customHeight="1">
       <c r="B81" s="44" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C81" s="14">
         <v>60</v>
@@ -5736,14 +5736,14 @@
       <c r="D81" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E81" s="145"/>
+      <c r="E81" s="134"/>
       <c r="F81" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G81" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H81" s="134"/>
+      <c r="H81" s="143"/>
       <c r="I81" s="29"/>
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="82" spans="2:12" ht="15.75" customHeight="1">
       <c r="B82" s="44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C82" s="14">
         <v>100</v>
@@ -5759,14 +5759,14 @@
       <c r="D82" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E82" s="145"/>
+      <c r="E82" s="134"/>
       <c r="F82" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G82" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H82" s="134"/>
+      <c r="H82" s="143"/>
       <c r="I82" s="29"/>
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
@@ -5782,14 +5782,14 @@
       <c r="D83" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E83" s="145"/>
+      <c r="E83" s="134"/>
       <c r="F83" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G83" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H83" s="134"/>
+      <c r="H83" s="143"/>
       <c r="I83" s="29"/>
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
@@ -5797,7 +5797,7 @@
     </row>
     <row r="84" spans="2:12" ht="15.75" customHeight="1">
       <c r="B84" s="44" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C84" s="14">
         <v>90</v>
@@ -5805,14 +5805,14 @@
       <c r="D84" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E84" s="145"/>
+      <c r="E84" s="134"/>
       <c r="F84" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G84" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H84" s="134"/>
+      <c r="H84" s="143"/>
       <c r="I84" s="29"/>
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
@@ -5820,7 +5820,7 @@
     </row>
     <row r="85" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B85" s="60" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C85" s="24">
         <v>20</v>
@@ -5828,14 +5828,14 @@
       <c r="D85" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E85" s="146"/>
+      <c r="E85" s="136"/>
       <c r="F85" s="26" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G85" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H85" s="136"/>
+      <c r="H85" s="144"/>
       <c r="I85" s="29"/>
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
@@ -5851,7 +5851,7 @@
       <c r="D86" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E86" s="149">
+      <c r="E86" s="137">
         <v>125</v>
       </c>
       <c r="F86" s="11" t="s">
@@ -5860,8 +5860,8 @@
       <c r="G86" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H86" s="133" t="s">
-        <v>405</v>
+      <c r="H86" s="142" t="s">
+        <v>403</v>
       </c>
       <c r="I86" s="29"/>
       <c r="J86" s="29"/>
@@ -5878,14 +5878,14 @@
       <c r="D87" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E87" s="145"/>
+      <c r="E87" s="134"/>
       <c r="F87" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G87" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H87" s="134"/>
+      <c r="H87" s="143"/>
       <c r="I87" s="29"/>
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
@@ -5901,14 +5901,14 @@
       <c r="D88" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E88" s="145"/>
+      <c r="E88" s="134"/>
       <c r="F88" s="15" t="s">
         <v>62</v>
       </c>
       <c r="G88" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H88" s="134"/>
+      <c r="H88" s="143"/>
       <c r="I88" s="29"/>
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
@@ -5916,7 +5916,7 @@
     </row>
     <row r="89" spans="2:12" ht="15.75" customHeight="1">
       <c r="B89" s="13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C89" s="14">
         <v>50</v>
@@ -5924,14 +5924,14 @@
       <c r="D89" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E89" s="145"/>
+      <c r="E89" s="134"/>
       <c r="F89" s="15" t="s">
         <v>63</v>
       </c>
       <c r="G89" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H89" s="134"/>
+      <c r="H89" s="143"/>
       <c r="I89" s="29"/>
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
@@ -5939,7 +5939,7 @@
     </row>
     <row r="90" spans="2:12" ht="15.75" customHeight="1">
       <c r="B90" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C90" s="14">
         <v>120</v>
@@ -5947,14 +5947,14 @@
       <c r="D90" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E90" s="145"/>
+      <c r="E90" s="134"/>
       <c r="F90" s="15" t="s">
         <v>64</v>
       </c>
       <c r="G90" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H90" s="134"/>
+      <c r="H90" s="143"/>
       <c r="I90" s="29"/>
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
@@ -5962,7 +5962,7 @@
     </row>
     <row r="91" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B91" s="16" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C91" s="17">
         <v>30</v>
@@ -5970,14 +5970,14 @@
       <c r="D91" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E91" s="148"/>
+      <c r="E91" s="135"/>
       <c r="F91" s="19" t="s">
         <v>65</v>
       </c>
       <c r="G91" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H91" s="136"/>
+      <c r="H91" s="144"/>
       <c r="I91" s="29"/>
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
@@ -5985,30 +5985,30 @@
     </row>
     <row r="92" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B92" s="61" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C92" s="22">
         <v>440</v>
       </c>
       <c r="D92" s="62" t="s">
-        <v>322</v>
-      </c>
-      <c r="E92" s="144">
+        <v>320</v>
+      </c>
+      <c r="E92" s="133">
         <v>125</v>
       </c>
       <c r="F92" s="47" t="s">
         <v>66</v>
       </c>
       <c r="G92" s="48" t="s">
-        <v>325</v>
-      </c>
-      <c r="H92" s="140" t="s">
-        <v>410</v>
+        <v>323</v>
+      </c>
+      <c r="H92" s="145" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="93" spans="2:12" ht="15.75" customHeight="1">
       <c r="B93" s="44" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C93" s="14">
         <v>80</v>
@@ -6016,18 +6016,18 @@
       <c r="D93" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="E93" s="145"/>
+      <c r="E93" s="134"/>
       <c r="F93" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H93" s="138"/>
+      <c r="H93" s="146"/>
     </row>
     <row r="94" spans="2:12" ht="15.75" customHeight="1">
       <c r="B94" s="44" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C94" s="14">
         <v>140</v>
@@ -6035,18 +6035,18 @@
       <c r="D94" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="E94" s="145"/>
+      <c r="E94" s="134"/>
       <c r="F94" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G94" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H94" s="138"/>
+      <c r="H94" s="146"/>
     </row>
     <row r="95" spans="2:12" ht="15.75" customHeight="1">
       <c r="B95" s="44" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C95" s="14">
         <v>55</v>
@@ -6054,18 +6054,18 @@
       <c r="D95" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="E95" s="145"/>
+      <c r="E95" s="134"/>
       <c r="F95" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G95" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H95" s="138"/>
+      <c r="H95" s="146"/>
     </row>
     <row r="96" spans="2:12" ht="15.75" customHeight="1">
       <c r="B96" s="44" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C96" s="14">
         <v>130</v>
@@ -6073,18 +6073,18 @@
       <c r="D96" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="E96" s="145"/>
+      <c r="E96" s="134"/>
       <c r="F96" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G96" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H96" s="138"/>
+      <c r="H96" s="146"/>
     </row>
     <row r="97" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B97" s="64" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C97" s="17">
         <v>35</v>
@@ -6092,14 +6092,14 @@
       <c r="D97" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="E97" s="148"/>
+      <c r="E97" s="135"/>
       <c r="F97" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G97" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H97" s="139"/>
+      <c r="H97" s="147"/>
     </row>
     <row r="98" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B98" s="36" t="s">
@@ -6111,17 +6111,17 @@
       <c r="D98" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E98" s="144">
+      <c r="E98" s="133">
         <v>125</v>
       </c>
       <c r="F98" s="58" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G98" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="H98" s="133" t="s">
-        <v>406</v>
+      <c r="H98" s="142" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="99" spans="2:8" ht="15.75" customHeight="1">
@@ -6134,18 +6134,18 @@
       <c r="D99" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E99" s="145"/>
+      <c r="E99" s="134"/>
       <c r="F99" s="56" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G99" s="54" t="s">
-        <v>235</v>
-      </c>
-      <c r="H99" s="134"/>
+        <v>233</v>
+      </c>
+      <c r="H99" s="143"/>
     </row>
     <row r="100" spans="2:8" ht="15.75" customHeight="1">
       <c r="B100" s="38" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C100" s="14">
         <v>140</v>
@@ -6153,18 +6153,18 @@
       <c r="D100" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E100" s="145"/>
+      <c r="E100" s="134"/>
       <c r="F100" s="56" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G100" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H100" s="134"/>
+      <c r="H100" s="143"/>
     </row>
     <row r="101" spans="2:8" ht="15.75" customHeight="1">
       <c r="B101" s="38" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C101" s="14">
         <v>55</v>
@@ -6172,18 +6172,18 @@
       <c r="D101" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E101" s="145"/>
+      <c r="E101" s="134"/>
       <c r="F101" s="56" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G101" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H101" s="134"/>
+      <c r="H101" s="143"/>
     </row>
     <row r="102" spans="2:8" ht="15.75" customHeight="1">
       <c r="B102" s="38" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C102" s="14">
         <v>130</v>
@@ -6191,18 +6191,18 @@
       <c r="D102" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E102" s="145"/>
+      <c r="E102" s="134"/>
       <c r="F102" s="56" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G102" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H102" s="134"/>
+      <c r="H102" s="143"/>
     </row>
     <row r="103" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B103" s="51" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C103" s="17">
         <v>40</v>
@@ -6210,18 +6210,18 @@
       <c r="D103" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E103" s="148"/>
+      <c r="E103" s="135"/>
       <c r="F103" s="57" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G103" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="H103" s="136"/>
+      <c r="H103" s="144"/>
     </row>
     <row r="104" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B104" s="61" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C104" s="22">
         <v>450</v>
@@ -6229,7 +6229,7 @@
       <c r="D104" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E104" s="144">
+      <c r="E104" s="133">
         <v>125</v>
       </c>
       <c r="F104" s="31" t="s">
@@ -6238,8 +6238,8 @@
       <c r="G104" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="H104" s="133" t="s">
-        <v>406</v>
+      <c r="H104" s="142" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="105" spans="2:8" ht="15.75" customHeight="1">
@@ -6252,18 +6252,18 @@
       <c r="D105" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E105" s="145"/>
+      <c r="E105" s="134"/>
       <c r="F105" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G105" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H105" s="134"/>
+      <c r="H105" s="143"/>
     </row>
     <row r="106" spans="2:8" ht="15.75" customHeight="1">
       <c r="B106" s="44" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C106" s="14">
         <v>140</v>
@@ -6271,14 +6271,14 @@
       <c r="D106" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E106" s="145"/>
+      <c r="E106" s="134"/>
       <c r="F106" s="15" t="s">
         <v>62</v>
       </c>
       <c r="G106" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H106" s="134"/>
+      <c r="H106" s="143"/>
     </row>
     <row r="107" spans="2:8" ht="15.75" customHeight="1">
       <c r="B107" s="44" t="s">
@@ -6290,18 +6290,18 @@
       <c r="D107" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E107" s="145"/>
+      <c r="E107" s="134"/>
       <c r="F107" s="15" t="s">
         <v>75</v>
       </c>
       <c r="G107" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H107" s="134"/>
+      <c r="H107" s="143"/>
     </row>
     <row r="108" spans="2:8" ht="15.75" customHeight="1">
       <c r="B108" s="44" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C108" s="14">
         <v>130</v>
@@ -6309,18 +6309,18 @@
       <c r="D108" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E108" s="145"/>
+      <c r="E108" s="134"/>
       <c r="F108" s="15" t="s">
         <v>64</v>
       </c>
       <c r="G108" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H108" s="134"/>
+      <c r="H108" s="143"/>
     </row>
     <row r="109" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B109" s="66" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C109" s="33">
         <v>40</v>
@@ -6328,18 +6328,18 @@
       <c r="D109" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E109" s="146"/>
+      <c r="E109" s="136"/>
       <c r="F109" s="34" t="s">
         <v>65</v>
       </c>
       <c r="G109" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="H109" s="136"/>
+      <c r="H109" s="144"/>
     </row>
     <row r="110" spans="2:8" ht="25.5" customHeight="1" thickTop="1">
       <c r="B110" s="36" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C110" s="22">
         <v>450</v>
@@ -6347,22 +6347,22 @@
       <c r="D110" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E110" s="144">
+      <c r="E110" s="133">
         <v>125</v>
       </c>
       <c r="F110" s="72" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G110" s="37" t="s">
-        <v>360</v>
-      </c>
-      <c r="H110" s="133" t="s">
-        <v>406</v>
+        <v>358</v>
+      </c>
+      <c r="H110" s="142" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="111" spans="2:8" ht="15.75" customHeight="1">
       <c r="B111" s="38" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C111" s="14">
         <v>80</v>
@@ -6370,18 +6370,18 @@
       <c r="D111" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E111" s="145"/>
+      <c r="E111" s="134"/>
       <c r="F111" s="56" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G111" s="54" t="s">
-        <v>359</v>
-      </c>
-      <c r="H111" s="134"/>
+        <v>357</v>
+      </c>
+      <c r="H111" s="143"/>
     </row>
     <row r="112" spans="2:8" ht="15.75" customHeight="1">
       <c r="B112" s="38" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C112" s="14">
         <v>140</v>
@@ -6389,18 +6389,18 @@
       <c r="D112" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E112" s="145"/>
+      <c r="E112" s="134"/>
       <c r="F112" s="56" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G112" s="54" t="s">
-        <v>363</v>
-      </c>
-      <c r="H112" s="134"/>
+        <v>361</v>
+      </c>
+      <c r="H112" s="143"/>
     </row>
     <row r="113" spans="2:12" ht="15.75" customHeight="1">
       <c r="B113" s="38" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C113" s="14">
         <v>60</v>
@@ -6408,18 +6408,18 @@
       <c r="D113" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E113" s="145"/>
+      <c r="E113" s="134"/>
       <c r="F113" s="56" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G113" s="54" t="s">
-        <v>359</v>
-      </c>
-      <c r="H113" s="134"/>
+        <v>357</v>
+      </c>
+      <c r="H113" s="143"/>
     </row>
     <row r="114" spans="2:12" ht="15.75" customHeight="1">
       <c r="B114" s="38" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C114" s="14">
         <v>130</v>
@@ -6427,18 +6427,18 @@
       <c r="D114" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E114" s="145"/>
+      <c r="E114" s="134"/>
       <c r="F114" s="56" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="G114" s="54" t="s">
-        <v>359</v>
-      </c>
-      <c r="H114" s="134"/>
+        <v>357</v>
+      </c>
+      <c r="H114" s="143"/>
     </row>
     <row r="115" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B115" s="51" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C115" s="17">
         <v>40</v>
@@ -6446,18 +6446,18 @@
       <c r="D115" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E115" s="148"/>
+      <c r="E115" s="135"/>
       <c r="F115" s="57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G115" s="54" t="s">
-        <v>368</v>
-      </c>
-      <c r="H115" s="136"/>
+        <v>366</v>
+      </c>
+      <c r="H115" s="144"/>
     </row>
     <row r="116" spans="2:12" ht="25.9" thickTop="1">
       <c r="B116" s="68" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C116" s="22">
         <v>630</v>
@@ -6465,17 +6465,17 @@
       <c r="D116" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E116" s="144">
+      <c r="E116" s="133">
         <v>143</v>
       </c>
       <c r="F116" s="31" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G116" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="H116" s="133" t="s">
-        <v>417</v>
+      <c r="H116" s="142" t="s">
+        <v>415</v>
       </c>
       <c r="I116" s="29"/>
       <c r="J116" s="29"/>
@@ -6484,7 +6484,7 @@
     </row>
     <row r="117" spans="2:12" ht="15.75" customHeight="1">
       <c r="B117" s="70" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C117" s="14">
         <v>110</v>
@@ -6492,14 +6492,14 @@
       <c r="D117" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E117" s="145"/>
+      <c r="E117" s="134"/>
       <c r="F117" s="15" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G117" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H117" s="134"/>
+      <c r="H117" s="143"/>
       <c r="I117" s="29"/>
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
@@ -6507,7 +6507,7 @@
     </row>
     <row r="118" spans="2:12" ht="15.75" customHeight="1">
       <c r="B118" s="70" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C118" s="14">
         <v>190</v>
@@ -6515,14 +6515,14 @@
       <c r="D118" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E118" s="145"/>
+      <c r="E118" s="134"/>
       <c r="F118" s="15" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G118" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H118" s="134"/>
+      <c r="H118" s="143"/>
       <c r="I118" s="29"/>
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
@@ -6530,7 +6530,7 @@
     </row>
     <row r="119" spans="2:12" ht="15.75" customHeight="1">
       <c r="B119" s="70" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C119" s="14">
         <v>90</v>
@@ -6538,14 +6538,14 @@
       <c r="D119" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E119" s="145"/>
+      <c r="E119" s="134"/>
       <c r="F119" s="15" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G119" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H119" s="134"/>
+      <c r="H119" s="143"/>
       <c r="I119" s="29"/>
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
@@ -6553,7 +6553,7 @@
     </row>
     <row r="120" spans="2:12" ht="15.75" customHeight="1">
       <c r="B120" s="70" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C120" s="14">
         <v>180</v>
@@ -6561,14 +6561,14 @@
       <c r="D120" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E120" s="145"/>
+      <c r="E120" s="134"/>
       <c r="F120" s="15" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G120" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H120" s="134"/>
+      <c r="H120" s="143"/>
       <c r="I120" s="29"/>
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
@@ -6576,7 +6576,7 @@
     </row>
     <row r="121" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B121" s="71" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C121" s="24">
         <v>60</v>
@@ -6584,14 +6584,14 @@
       <c r="D121" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E121" s="146"/>
+      <c r="E121" s="136"/>
       <c r="F121" s="26" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G121" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="H121" s="136"/>
+      <c r="H121" s="144"/>
       <c r="I121" s="29"/>
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
@@ -6607,17 +6607,17 @@
       <c r="D122" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E122" s="144">
+      <c r="E122" s="133">
         <v>125</v>
       </c>
       <c r="F122" s="72" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G122" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="H122" s="133" t="s">
-        <v>406</v>
+      <c r="H122" s="142" t="s">
+        <v>404</v>
       </c>
       <c r="I122" s="29"/>
       <c r="J122" s="29"/>
@@ -6634,14 +6634,14 @@
       <c r="D123" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E123" s="145"/>
+      <c r="E123" s="134"/>
       <c r="F123" s="56" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G123" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H123" s="134"/>
+      <c r="H123" s="143"/>
       <c r="I123" s="29"/>
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
@@ -6657,14 +6657,14 @@
       <c r="D124" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E124" s="145"/>
+      <c r="E124" s="134"/>
       <c r="F124" s="56" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G124" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H124" s="134"/>
+      <c r="H124" s="143"/>
       <c r="I124" s="29"/>
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
@@ -6680,14 +6680,14 @@
       <c r="D125" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E125" s="145"/>
+      <c r="E125" s="134"/>
       <c r="F125" s="56" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G125" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H125" s="134"/>
+      <c r="H125" s="143"/>
       <c r="I125" s="29"/>
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
@@ -6695,7 +6695,7 @@
     </row>
     <row r="126" spans="2:12" ht="15.75" customHeight="1">
       <c r="B126" s="38" t="s">
-        <v>82</v>
+        <v>430</v>
       </c>
       <c r="C126" s="14">
         <v>190</v>
@@ -6703,14 +6703,14 @@
       <c r="D126" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E126" s="145"/>
+      <c r="E126" s="134"/>
       <c r="F126" s="56" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G126" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H126" s="134"/>
+      <c r="H126" s="143"/>
       <c r="I126" s="29"/>
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
@@ -6718,7 +6718,7 @@
     </row>
     <row r="127" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B127" s="39" t="s">
-        <v>218</v>
+        <v>431</v>
       </c>
       <c r="C127" s="24">
         <v>60</v>
@@ -6726,14 +6726,14 @@
       <c r="D127" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E127" s="146"/>
+      <c r="E127" s="136"/>
       <c r="F127" s="73" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G127" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="H127" s="136"/>
+      <c r="H127" s="144"/>
       <c r="I127" s="29"/>
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
@@ -6741,7 +6741,7 @@
     </row>
     <row r="128" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B128" s="68" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C128" s="22">
         <v>630</v>
@@ -6749,22 +6749,22 @@
       <c r="D128" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E128" s="144">
+      <c r="E128" s="133">
         <v>143</v>
       </c>
       <c r="F128" s="72" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G128" s="48" t="s">
-        <v>84</v>
-      </c>
-      <c r="H128" s="133" t="s">
-        <v>406</v>
+        <v>83</v>
+      </c>
+      <c r="H128" s="142" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="129" spans="2:12" ht="15.75" customHeight="1">
       <c r="B129" s="74" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C129" s="14">
         <v>110</v>
@@ -6772,18 +6772,18 @@
       <c r="D129" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E129" s="145"/>
+      <c r="E129" s="134"/>
       <c r="F129" s="56" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G129" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="H129" s="134"/>
+        <v>85</v>
+      </c>
+      <c r="H129" s="143"/>
     </row>
     <row r="130" spans="2:12" ht="15.75" customHeight="1">
       <c r="B130" s="70" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C130" s="14">
         <v>190</v>
@@ -6791,18 +6791,18 @@
       <c r="D130" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E130" s="145"/>
+      <c r="E130" s="134"/>
       <c r="F130" s="56" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G130" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H130" s="134"/>
+      <c r="H130" s="143"/>
     </row>
     <row r="131" spans="2:12" ht="15.75" customHeight="1">
       <c r="B131" s="74" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C131" s="14">
         <v>90</v>
@@ -6810,18 +6810,18 @@
       <c r="D131" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E131" s="145"/>
+      <c r="E131" s="134"/>
       <c r="F131" s="56" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G131" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H131" s="134"/>
+      <c r="H131" s="143"/>
     </row>
     <row r="132" spans="2:12" ht="15.75" customHeight="1">
       <c r="B132" s="74" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C132" s="14">
         <v>180</v>
@@ -6829,18 +6829,18 @@
       <c r="D132" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E132" s="145"/>
+      <c r="E132" s="134"/>
       <c r="F132" s="56" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G132" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H132" s="134"/>
+      <c r="H132" s="143"/>
     </row>
     <row r="133" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B133" s="71" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C133" s="24">
         <v>60</v>
@@ -6848,18 +6848,18 @@
       <c r="D133" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E133" s="146"/>
+      <c r="E133" s="136"/>
       <c r="F133" s="73" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G133" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="H133" s="136"/>
+        <v>86</v>
+      </c>
+      <c r="H133" s="144"/>
     </row>
     <row r="134" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B134" s="75" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C134" s="76">
         <v>580</v>
@@ -6867,17 +6867,17 @@
       <c r="D134" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E134" s="147">
+      <c r="E134" s="138">
         <v>143</v>
       </c>
       <c r="F134" s="28" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G134" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H134" s="133" t="s">
-        <v>405</v>
+      <c r="H134" s="142" t="s">
+        <v>403</v>
       </c>
       <c r="I134" s="29"/>
       <c r="J134" s="29"/>
@@ -6886,7 +6886,7 @@
     </row>
     <row r="135" spans="2:12" ht="15.75" customHeight="1">
       <c r="B135" s="44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C135" s="14">
         <v>100</v>
@@ -6894,14 +6894,14 @@
       <c r="D135" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E135" s="145"/>
+      <c r="E135" s="134"/>
       <c r="F135" s="15" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G135" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H135" s="134"/>
+      <c r="H135" s="143"/>
       <c r="I135" s="29"/>
       <c r="J135" s="29"/>
       <c r="K135" s="29"/>
@@ -6909,7 +6909,7 @@
     </row>
     <row r="136" spans="2:12" ht="15.75" customHeight="1">
       <c r="B136" s="44" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C136" s="14">
         <v>180</v>
@@ -6917,14 +6917,14 @@
       <c r="D136" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E136" s="145"/>
+      <c r="E136" s="134"/>
       <c r="F136" s="15" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G136" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H136" s="134"/>
+      <c r="H136" s="143"/>
       <c r="I136" s="29"/>
       <c r="J136" s="29"/>
       <c r="K136" s="29"/>
@@ -6932,7 +6932,7 @@
     </row>
     <row r="137" spans="2:12" ht="15.75" customHeight="1">
       <c r="B137" s="44" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C137" s="14">
         <v>80</v>
@@ -6940,14 +6940,14 @@
       <c r="D137" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E137" s="145"/>
+      <c r="E137" s="134"/>
       <c r="F137" s="15" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G137" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H137" s="134"/>
+      <c r="H137" s="143"/>
       <c r="I137" s="29"/>
       <c r="J137" s="29"/>
       <c r="K137" s="29"/>
@@ -6955,7 +6955,7 @@
     </row>
     <row r="138" spans="2:12" ht="15.75" customHeight="1">
       <c r="B138" s="44" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C138" s="14">
         <v>170</v>
@@ -6963,14 +6963,14 @@
       <c r="D138" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E138" s="145"/>
+      <c r="E138" s="134"/>
       <c r="F138" s="15" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G138" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H138" s="134"/>
+      <c r="H138" s="143"/>
       <c r="I138" s="29"/>
       <c r="J138" s="29"/>
       <c r="K138" s="29"/>
@@ -6978,7 +6978,7 @@
     </row>
     <row r="139" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B139" s="64" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C139" s="17">
         <v>50</v>
@@ -6986,14 +6986,14 @@
       <c r="D139" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E139" s="148"/>
+      <c r="E139" s="135"/>
       <c r="F139" s="19" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G139" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H139" s="136"/>
+      <c r="H139" s="144"/>
       <c r="I139" s="29"/>
       <c r="J139" s="29"/>
       <c r="K139" s="29"/>
@@ -7001,7 +7001,7 @@
     </row>
     <row r="140" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B140" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C140" s="22">
         <v>580</v>
@@ -7009,22 +7009,22 @@
       <c r="D140" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E140" s="144">
+      <c r="E140" s="133">
         <v>143</v>
       </c>
       <c r="F140" s="31" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G140" s="77" t="s">
-        <v>93</v>
-      </c>
-      <c r="H140" s="133" t="s">
-        <v>406</v>
+        <v>92</v>
+      </c>
+      <c r="H140" s="142" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="2:12" ht="15.75" customHeight="1">
       <c r="B141" s="44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C141" s="14">
         <v>100</v>
@@ -7032,18 +7032,18 @@
       <c r="D141" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E141" s="145"/>
+      <c r="E141" s="134"/>
       <c r="F141" s="15" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G141" s="77" t="s">
-        <v>95</v>
-      </c>
-      <c r="H141" s="134"/>
+        <v>94</v>
+      </c>
+      <c r="H141" s="143"/>
     </row>
     <row r="142" spans="2:12" ht="15.75" customHeight="1">
       <c r="B142" s="44" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C142" s="14">
         <v>180</v>
@@ -7051,18 +7051,18 @@
       <c r="D142" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E142" s="145"/>
+      <c r="E142" s="134"/>
       <c r="F142" s="15" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G142" s="78" t="s">
-        <v>96</v>
-      </c>
-      <c r="H142" s="134"/>
+        <v>95</v>
+      </c>
+      <c r="H142" s="143"/>
     </row>
     <row r="143" spans="2:12" ht="15.75" customHeight="1">
       <c r="B143" s="44" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C143" s="14">
         <v>80</v>
@@ -7070,18 +7070,18 @@
       <c r="D143" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E143" s="145"/>
+      <c r="E143" s="134"/>
       <c r="F143" s="15" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G143" s="77" t="s">
-        <v>95</v>
-      </c>
-      <c r="H143" s="134"/>
+        <v>94</v>
+      </c>
+      <c r="H143" s="143"/>
     </row>
     <row r="144" spans="2:12" ht="15.75" customHeight="1">
       <c r="B144" s="44" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C144" s="14">
         <v>170</v>
@@ -7089,18 +7089,18 @@
       <c r="D144" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E144" s="145"/>
+      <c r="E144" s="134"/>
       <c r="F144" s="15" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G144" s="77" t="s">
-        <v>95</v>
-      </c>
-      <c r="H144" s="134"/>
+        <v>94</v>
+      </c>
+      <c r="H144" s="143"/>
     </row>
     <row r="145" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B145" s="64" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C145" s="17">
         <v>50</v>
@@ -7108,249 +7108,249 @@
       <c r="D145" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E145" s="148"/>
+      <c r="E145" s="135"/>
       <c r="F145" s="19" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G145" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="H145" s="136"/>
+        <v>97</v>
+      </c>
+      <c r="H145" s="144"/>
     </row>
     <row r="146" spans="1:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B146" s="112" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C146" s="22">
         <v>615</v>
       </c>
       <c r="D146" s="79" t="s">
-        <v>323</v>
-      </c>
-      <c r="E146" s="144">
+        <v>321</v>
+      </c>
+      <c r="E146" s="133">
         <v>143</v>
       </c>
       <c r="F146" s="47" t="s">
         <v>66</v>
       </c>
       <c r="G146" s="48" t="s">
-        <v>324</v>
-      </c>
-      <c r="H146" s="140" t="s">
-        <v>410</v>
+        <v>322</v>
+      </c>
+      <c r="H146" s="145" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="147" spans="1:12" ht="15.75" customHeight="1">
       <c r="B147" s="44" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C147" s="14">
         <v>105</v>
       </c>
       <c r="D147" s="80" t="s">
-        <v>99</v>
-      </c>
-      <c r="E147" s="145"/>
+        <v>98</v>
+      </c>
+      <c r="E147" s="134"/>
       <c r="F147" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G147" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H147" s="138"/>
+      <c r="H147" s="146"/>
     </row>
     <row r="148" spans="1:12" ht="15.75" customHeight="1">
       <c r="B148" s="44" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C148" s="14">
         <v>190</v>
       </c>
       <c r="D148" s="80" t="s">
-        <v>100</v>
-      </c>
-      <c r="E148" s="145"/>
+        <v>99</v>
+      </c>
+      <c r="E148" s="134"/>
       <c r="F148" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G148" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H148" s="138"/>
+      <c r="H148" s="146"/>
     </row>
     <row r="149" spans="1:12" ht="15.75" customHeight="1">
       <c r="B149" s="44" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C149" s="14">
         <v>85</v>
       </c>
       <c r="D149" s="80" t="s">
-        <v>99</v>
-      </c>
-      <c r="E149" s="145"/>
+        <v>98</v>
+      </c>
+      <c r="E149" s="134"/>
       <c r="F149" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G149" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H149" s="138"/>
+      <c r="H149" s="146"/>
     </row>
     <row r="150" spans="1:12" ht="15.75" customHeight="1">
       <c r="B150" s="44" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C150" s="14">
         <v>180</v>
       </c>
       <c r="D150" s="80" t="s">
-        <v>100</v>
-      </c>
-      <c r="E150" s="145"/>
+        <v>99</v>
+      </c>
+      <c r="E150" s="134"/>
       <c r="F150" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G150" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H150" s="138"/>
+      <c r="H150" s="146"/>
     </row>
     <row r="151" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B151" s="64" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C151" s="17">
         <v>55</v>
       </c>
       <c r="D151" s="81" t="s">
-        <v>99</v>
-      </c>
-      <c r="E151" s="148"/>
+        <v>98</v>
+      </c>
+      <c r="E151" s="135"/>
       <c r="F151" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G151" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H151" s="139"/>
+      <c r="H151" s="147"/>
     </row>
     <row r="152" spans="1:12" ht="13.5" thickTop="1">
       <c r="A152" s="111"/>
       <c r="B152" s="110" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C152" s="22">
         <v>615</v>
       </c>
       <c r="D152" s="109" t="s">
-        <v>381</v>
-      </c>
-      <c r="E152" s="144">
+        <v>379</v>
+      </c>
+      <c r="E152" s="133">
         <v>143</v>
       </c>
       <c r="F152" s="47" t="s">
         <v>66</v>
       </c>
       <c r="G152" s="114" t="s">
-        <v>377</v>
-      </c>
-      <c r="H152" s="140" t="s">
-        <v>410</v>
+        <v>375</v>
+      </c>
+      <c r="H152" s="145" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="153" spans="1:12" ht="15.75" customHeight="1">
       <c r="B153" s="113" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C153" s="14">
         <v>105</v>
       </c>
       <c r="D153" s="109" t="s">
-        <v>374</v>
-      </c>
-      <c r="E153" s="145"/>
+        <v>372</v>
+      </c>
+      <c r="E153" s="134"/>
       <c r="F153" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G153" s="12"/>
-      <c r="H153" s="138"/>
+      <c r="H153" s="146"/>
     </row>
     <row r="154" spans="1:12" ht="15.75" customHeight="1">
       <c r="B154" s="113" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C154" s="14">
         <v>190</v>
       </c>
       <c r="D154" s="109" t="s">
-        <v>376</v>
-      </c>
-      <c r="E154" s="145"/>
+        <v>374</v>
+      </c>
+      <c r="E154" s="134"/>
       <c r="F154" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G154" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H154" s="138"/>
+      <c r="H154" s="146"/>
     </row>
     <row r="155" spans="1:12" ht="15.75" customHeight="1">
       <c r="B155" s="113" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C155" s="14">
         <v>85</v>
       </c>
       <c r="D155" s="109" t="s">
-        <v>374</v>
-      </c>
-      <c r="E155" s="145"/>
+        <v>372</v>
+      </c>
+      <c r="E155" s="134"/>
       <c r="F155" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G155" s="12"/>
-      <c r="H155" s="138"/>
+      <c r="H155" s="146"/>
     </row>
     <row r="156" spans="1:12" ht="15.75" customHeight="1">
       <c r="B156" s="113" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C156" s="14">
         <v>180</v>
       </c>
       <c r="D156" s="109" t="s">
-        <v>376</v>
-      </c>
-      <c r="E156" s="145"/>
+        <v>374</v>
+      </c>
+      <c r="E156" s="134"/>
       <c r="F156" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G156" s="12"/>
-      <c r="H156" s="138"/>
+      <c r="H156" s="146"/>
     </row>
     <row r="157" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B157" s="116" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C157" s="17">
         <v>55</v>
       </c>
       <c r="D157" s="109" t="s">
-        <v>374</v>
-      </c>
-      <c r="E157" s="148"/>
+        <v>372</v>
+      </c>
+      <c r="E157" s="135"/>
       <c r="F157" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G157" s="115" t="s">
         <v>46</v>
       </c>
-      <c r="H157" s="139"/>
+      <c r="H157" s="147"/>
     </row>
     <row r="158" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B158" s="82" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C158" s="22">
         <v>580</v>
@@ -7358,17 +7358,17 @@
       <c r="D158" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E158" s="144">
+      <c r="E158" s="133">
         <v>167</v>
       </c>
       <c r="F158" s="31" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G158" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H158" s="133" t="s">
-        <v>406</v>
+      <c r="H158" s="142" t="s">
+        <v>404</v>
       </c>
       <c r="I158" s="29"/>
       <c r="J158" s="29"/>
@@ -7377,7 +7377,7 @@
     </row>
     <row r="159" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B159" s="84" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C159" s="14">
         <v>100</v>
@@ -7385,14 +7385,14 @@
       <c r="D159" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E159" s="145"/>
+      <c r="E159" s="134"/>
       <c r="F159" s="15" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G159" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H159" s="134"/>
+      <c r="H159" s="143"/>
       <c r="I159" s="29"/>
       <c r="J159" s="29"/>
       <c r="K159" s="29"/>
@@ -7400,7 +7400,7 @@
     </row>
     <row r="160" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B160" s="84" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C160" s="14">
         <v>180</v>
@@ -7408,14 +7408,14 @@
       <c r="D160" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E160" s="145"/>
+      <c r="E160" s="134"/>
       <c r="F160" s="15" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G160" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H160" s="134"/>
+      <c r="H160" s="143"/>
       <c r="I160" s="29"/>
       <c r="J160" s="29"/>
       <c r="K160" s="29"/>
@@ -7423,7 +7423,7 @@
     </row>
     <row r="161" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B161" s="84" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C161" s="14">
         <v>80</v>
@@ -7431,14 +7431,14 @@
       <c r="D161" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E161" s="145"/>
+      <c r="E161" s="134"/>
       <c r="F161" s="15" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G161" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H161" s="134"/>
+      <c r="H161" s="143"/>
       <c r="I161" s="29"/>
       <c r="J161" s="29"/>
       <c r="K161" s="29"/>
@@ -7446,7 +7446,7 @@
     </row>
     <row r="162" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B162" s="84" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C162" s="14">
         <v>170</v>
@@ -7454,14 +7454,14 @@
       <c r="D162" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E162" s="145"/>
+      <c r="E162" s="134"/>
       <c r="F162" s="15" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G162" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H162" s="134"/>
+      <c r="H162" s="143"/>
       <c r="I162" s="29"/>
       <c r="J162" s="29"/>
       <c r="K162" s="29"/>
@@ -7469,7 +7469,7 @@
     </row>
     <row r="163" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B163" s="85" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C163" s="17">
         <v>50</v>
@@ -7477,14 +7477,14 @@
       <c r="D163" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E163" s="148"/>
+      <c r="E163" s="135"/>
       <c r="F163" s="19" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G163" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="H163" s="136"/>
+      <c r="H163" s="144"/>
       <c r="I163" s="29"/>
       <c r="J163" s="29"/>
       <c r="K163" s="29"/>
@@ -7492,7 +7492,7 @@
     </row>
     <row r="164" spans="2:12" ht="26.25" thickTop="1" thickBot="1">
       <c r="B164" s="36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C164" s="22">
         <v>580</v>
@@ -7500,22 +7500,22 @@
       <c r="D164" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E164" s="144">
+      <c r="E164" s="133">
         <v>125</v>
       </c>
       <c r="F164" s="58" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G164" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="H164" s="133" t="s">
-        <v>406</v>
+        <v>101</v>
+      </c>
+      <c r="H164" s="142" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="165" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B165" s="38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C165" s="14">
         <v>100</v>
@@ -7523,18 +7523,18 @@
       <c r="D165" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E165" s="145"/>
+      <c r="E165" s="134"/>
       <c r="F165" s="56" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G165" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H165" s="134"/>
+      <c r="H165" s="143"/>
     </row>
     <row r="166" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B166" s="38" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C166" s="14">
         <v>180</v>
@@ -7542,18 +7542,18 @@
       <c r="D166" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E166" s="145"/>
+      <c r="E166" s="134"/>
       <c r="F166" s="56" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G166" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H166" s="134"/>
+      <c r="H166" s="143"/>
     </row>
     <row r="167" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B167" s="38" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C167" s="14">
         <v>80</v>
@@ -7561,18 +7561,18 @@
       <c r="D167" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E167" s="145"/>
+      <c r="E167" s="134"/>
       <c r="F167" s="56" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G167" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H167" s="134"/>
+      <c r="H167" s="143"/>
     </row>
     <row r="168" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B168" s="87" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C168" s="14">
         <v>170</v>
@@ -7580,18 +7580,18 @@
       <c r="D168" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E168" s="145"/>
+      <c r="E168" s="134"/>
       <c r="F168" s="56" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G168" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H168" s="134"/>
+      <c r="H168" s="143"/>
     </row>
     <row r="169" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B169" s="51" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C169" s="17">
         <v>50</v>
@@ -7599,18 +7599,18 @@
       <c r="D169" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E169" s="148"/>
+      <c r="E169" s="135"/>
       <c r="F169" s="57" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G169" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H169" s="136"/>
+      <c r="H169" s="144"/>
     </row>
     <row r="170" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B170" s="40" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C170" s="9">
         <v>580</v>
@@ -7618,7 +7618,7 @@
       <c r="D170" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E170" s="149">
+      <c r="E170" s="137">
         <v>200</v>
       </c>
       <c r="F170" s="50" t="s">
@@ -7627,8 +7627,8 @@
       <c r="G170" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H170" s="133" t="s">
-        <v>411</v>
+      <c r="H170" s="142" t="s">
+        <v>409</v>
       </c>
       <c r="I170" s="29"/>
       <c r="J170" s="29"/>
@@ -7637,7 +7637,7 @@
     </row>
     <row r="171" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B171" s="44" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C171" s="14">
         <v>100</v>
@@ -7645,14 +7645,14 @@
       <c r="D171" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E171" s="145"/>
+      <c r="E171" s="134"/>
       <c r="F171" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G171" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="H171" s="134"/>
+        <v>104</v>
+      </c>
+      <c r="H171" s="143"/>
       <c r="I171" s="29"/>
       <c r="J171" s="29"/>
       <c r="K171" s="29"/>
@@ -7660,7 +7660,7 @@
     </row>
     <row r="172" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B172" s="44" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C172" s="14">
         <v>180</v>
@@ -7668,14 +7668,14 @@
       <c r="D172" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E172" s="145"/>
+      <c r="E172" s="134"/>
       <c r="F172" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G172" s="55" t="s">
-        <v>106</v>
-      </c>
-      <c r="H172" s="134"/>
+        <v>105</v>
+      </c>
+      <c r="H172" s="143"/>
       <c r="I172" s="29"/>
       <c r="J172" s="29"/>
       <c r="K172" s="29"/>
@@ -7683,7 +7683,7 @@
     </row>
     <row r="173" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B173" s="44" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C173" s="14">
         <v>80</v>
@@ -7691,14 +7691,14 @@
       <c r="D173" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E173" s="145"/>
+      <c r="E173" s="134"/>
       <c r="F173" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G173" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="H173" s="134"/>
+        <v>104</v>
+      </c>
+      <c r="H173" s="143"/>
       <c r="I173" s="29"/>
       <c r="J173" s="29"/>
       <c r="K173" s="29"/>
@@ -7706,7 +7706,7 @@
     </row>
     <row r="174" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B174" s="44" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C174" s="14">
         <v>170</v>
@@ -7714,14 +7714,14 @@
       <c r="D174" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E174" s="145"/>
+      <c r="E174" s="134"/>
       <c r="F174" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G174" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="H174" s="134"/>
+        <v>104</v>
+      </c>
+      <c r="H174" s="143"/>
       <c r="I174" s="29"/>
       <c r="J174" s="29"/>
       <c r="K174" s="29"/>
@@ -7729,7 +7729,7 @@
     </row>
     <row r="175" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B175" s="60" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C175" s="24">
         <v>50</v>
@@ -7737,14 +7737,14 @@
       <c r="D175" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E175" s="146"/>
+      <c r="E175" s="136"/>
       <c r="F175" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G175" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="H175" s="136"/>
+        <v>106</v>
+      </c>
+      <c r="H175" s="144"/>
       <c r="I175" s="29"/>
       <c r="J175" s="29"/>
       <c r="K175" s="29"/>
@@ -7752,7 +7752,7 @@
     </row>
     <row r="176" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B176" s="36" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C176" s="22">
         <v>580</v>
@@ -7760,17 +7760,17 @@
       <c r="D176" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E176" s="144">
+      <c r="E176" s="133">
         <v>125</v>
       </c>
       <c r="F176" s="58" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G176" s="37" t="s">
-        <v>109</v>
-      </c>
-      <c r="H176" s="133" t="s">
-        <v>406</v>
+        <v>108</v>
+      </c>
+      <c r="H176" s="142" t="s">
+        <v>404</v>
       </c>
       <c r="I176" s="29"/>
       <c r="J176" s="29"/>
@@ -7779,7 +7779,7 @@
     </row>
     <row r="177" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B177" s="38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C177" s="14">
         <v>100</v>
@@ -7787,14 +7787,14 @@
       <c r="D177" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E177" s="145"/>
+      <c r="E177" s="134"/>
       <c r="F177" s="56" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G177" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="H177" s="134"/>
+        <v>110</v>
+      </c>
+      <c r="H177" s="143"/>
       <c r="I177" s="29"/>
       <c r="J177" s="29"/>
       <c r="K177" s="29"/>
@@ -7802,7 +7802,7 @@
     </row>
     <row r="178" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B178" s="87" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C178" s="14">
         <v>180</v>
@@ -7810,14 +7810,14 @@
       <c r="D178" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E178" s="145"/>
+      <c r="E178" s="134"/>
       <c r="F178" s="56" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G178" s="78" t="s">
-        <v>113</v>
-      </c>
-      <c r="H178" s="134"/>
+        <v>112</v>
+      </c>
+      <c r="H178" s="143"/>
       <c r="I178" s="29"/>
       <c r="J178" s="29"/>
       <c r="K178" s="29"/>
@@ -7825,7 +7825,7 @@
     </row>
     <row r="179" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B179" s="38" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C179" s="14">
         <v>80</v>
@@ -7833,14 +7833,14 @@
       <c r="D179" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E179" s="145"/>
+      <c r="E179" s="134"/>
       <c r="F179" s="56" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G179" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="H179" s="134"/>
+        <v>110</v>
+      </c>
+      <c r="H179" s="143"/>
       <c r="I179" s="29"/>
       <c r="J179" s="29"/>
       <c r="K179" s="29"/>
@@ -7848,7 +7848,7 @@
     </row>
     <row r="180" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B180" s="38" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C180" s="14">
         <v>170</v>
@@ -7856,14 +7856,14 @@
       <c r="D180" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E180" s="145"/>
+      <c r="E180" s="134"/>
       <c r="F180" s="56" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G180" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="H180" s="134"/>
+        <v>110</v>
+      </c>
+      <c r="H180" s="143"/>
       <c r="I180" s="29"/>
       <c r="J180" s="29"/>
       <c r="K180" s="29"/>
@@ -7871,7 +7871,7 @@
     </row>
     <row r="181" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B181" s="51" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C181" s="17">
         <v>50</v>
@@ -7879,14 +7879,14 @@
       <c r="D181" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E181" s="148"/>
+      <c r="E181" s="135"/>
       <c r="F181" s="88" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G181" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="H181" s="136"/>
+        <v>114</v>
+      </c>
+      <c r="H181" s="144"/>
       <c r="I181" s="29"/>
       <c r="J181" s="29"/>
       <c r="K181" s="29"/>
@@ -7894,7 +7894,7 @@
     </row>
     <row r="182" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B182" s="75" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C182" s="76">
         <v>1010</v>
@@ -7902,17 +7902,17 @@
       <c r="D182" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E182" s="147">
+      <c r="E182" s="138">
         <v>167</v>
       </c>
       <c r="F182" s="28" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G182" s="54" t="s">
-        <v>326</v>
-      </c>
-      <c r="H182" s="133" t="s">
-        <v>405</v>
+        <v>324</v>
+      </c>
+      <c r="H182" s="142" t="s">
+        <v>403</v>
       </c>
       <c r="I182" s="29"/>
       <c r="J182" s="29"/>
@@ -7921,7 +7921,7 @@
     </row>
     <row r="183" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B183" s="44" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C183" s="14">
         <v>140</v>
@@ -7929,14 +7929,14 @@
       <c r="D183" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E183" s="145"/>
+      <c r="E183" s="134"/>
       <c r="F183" s="15" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G183" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H183" s="134"/>
+      <c r="H183" s="143"/>
       <c r="I183" s="29"/>
       <c r="J183" s="29"/>
       <c r="K183" s="29"/>
@@ -7944,7 +7944,7 @@
     </row>
     <row r="184" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B184" s="42" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C184" s="14">
         <v>240</v>
@@ -7952,18 +7952,18 @@
       <c r="D184" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E184" s="145"/>
+      <c r="E184" s="134"/>
       <c r="F184" s="15" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G184" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H184" s="134"/>
+      <c r="H184" s="143"/>
     </row>
     <row r="185" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B185" s="42" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C185" s="14">
         <v>120</v>
@@ -7971,18 +7971,18 @@
       <c r="D185" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E185" s="145"/>
+      <c r="E185" s="134"/>
       <c r="F185" s="15" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G185" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H185" s="134"/>
+      <c r="H185" s="143"/>
     </row>
     <row r="186" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B186" s="44" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C186" s="14">
         <v>230</v>
@@ -7990,14 +7990,14 @@
       <c r="D186" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E186" s="145"/>
+      <c r="E186" s="134"/>
       <c r="F186" s="15" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G186" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H186" s="134"/>
+      <c r="H186" s="143"/>
       <c r="I186" s="29"/>
       <c r="J186" s="29"/>
       <c r="K186" s="29"/>
@@ -8005,7 +8005,7 @@
     </row>
     <row r="187" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B187" s="64" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C187" s="17">
         <v>80</v>
@@ -8013,14 +8013,14 @@
       <c r="D187" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E187" s="148"/>
+      <c r="E187" s="135"/>
       <c r="F187" s="19" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G187" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="H187" s="135"/>
+        <v>119</v>
+      </c>
+      <c r="H187" s="148"/>
       <c r="I187" s="29"/>
       <c r="J187" s="29"/>
       <c r="K187" s="29"/>
@@ -8028,7 +8028,7 @@
     </row>
     <row r="188" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B188" s="61" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C188" s="22">
         <v>1325</v>
@@ -8036,17 +8036,17 @@
       <c r="D188" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E188" s="144">
+      <c r="E188" s="133">
         <v>167</v>
       </c>
       <c r="F188" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G188" s="54" t="s">
-        <v>321</v>
-      </c>
-      <c r="H188" s="133" t="s">
-        <v>418</v>
+        <v>319</v>
+      </c>
+      <c r="H188" s="142" t="s">
+        <v>416</v>
       </c>
       <c r="I188" s="29"/>
       <c r="J188" s="29"/>
@@ -8055,7 +8055,7 @@
     </row>
     <row r="189" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B189" s="44" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C189" s="14">
         <v>160</v>
@@ -8063,14 +8063,14 @@
       <c r="D189" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E189" s="145"/>
+      <c r="E189" s="134"/>
       <c r="F189" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G189" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H189" s="134"/>
+      <c r="H189" s="143"/>
       <c r="I189" s="29"/>
       <c r="J189" s="29"/>
       <c r="K189" s="29"/>
@@ -8078,7 +8078,7 @@
     </row>
     <row r="190" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B190" s="44" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C190" s="14">
         <v>270</v>
@@ -8086,14 +8086,14 @@
       <c r="D190" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E190" s="145"/>
+      <c r="E190" s="134"/>
       <c r="F190" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G190" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H190" s="134"/>
+      <c r="H190" s="143"/>
       <c r="I190" s="29"/>
       <c r="J190" s="29"/>
       <c r="K190" s="29"/>
@@ -8101,7 +8101,7 @@
     </row>
     <row r="191" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B191" s="44" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C191" s="14">
         <v>140</v>
@@ -8109,14 +8109,14 @@
       <c r="D191" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E191" s="145"/>
+      <c r="E191" s="134"/>
       <c r="F191" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G191" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H191" s="134"/>
+      <c r="H191" s="143"/>
       <c r="I191" s="29"/>
       <c r="J191" s="29"/>
       <c r="K191" s="29"/>
@@ -8124,7 +8124,7 @@
     </row>
     <row r="192" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B192" s="44" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C192" s="14">
         <v>260</v>
@@ -8132,14 +8132,14 @@
       <c r="D192" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E192" s="145"/>
+      <c r="E192" s="134"/>
       <c r="F192" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G192" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H192" s="134"/>
+      <c r="H192" s="143"/>
       <c r="I192" s="29"/>
       <c r="J192" s="29"/>
       <c r="K192" s="29"/>
@@ -8147,7 +8147,7 @@
     </row>
     <row r="193" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B193" s="60" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C193" s="24">
         <v>95</v>
@@ -8155,14 +8155,14 @@
       <c r="D193" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E193" s="146"/>
+      <c r="E193" s="136"/>
       <c r="F193" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G193" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="H193" s="135"/>
+        <v>119</v>
+      </c>
+      <c r="H193" s="148"/>
       <c r="I193" s="29"/>
       <c r="J193" s="29"/>
       <c r="K193" s="29"/>
@@ -8170,7 +8170,7 @@
     </row>
     <row r="194" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B194" s="36" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C194" s="22">
         <v>810</v>
@@ -8178,22 +8178,22 @@
       <c r="D194" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E194" s="144">
+      <c r="E194" s="133">
         <v>143</v>
       </c>
       <c r="F194" s="72" t="s">
         <v>7</v>
       </c>
       <c r="G194" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="H194" s="133" t="s">
-        <v>406</v>
+        <v>123</v>
+      </c>
+      <c r="H194" s="142" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="195" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B195" s="38" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C195" s="14">
         <v>140</v>
@@ -8201,18 +8201,18 @@
       <c r="D195" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E195" s="145"/>
+      <c r="E195" s="134"/>
       <c r="F195" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G195" s="54" t="s">
-        <v>125</v>
-      </c>
-      <c r="H195" s="134"/>
+        <v>124</v>
+      </c>
+      <c r="H195" s="143"/>
     </row>
     <row r="196" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B196" s="38" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C196" s="14">
         <v>240</v>
@@ -8220,18 +8220,18 @@
       <c r="D196" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E196" s="145"/>
+      <c r="E196" s="134"/>
       <c r="F196" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G196" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H196" s="134"/>
+      <c r="H196" s="143"/>
     </row>
     <row r="197" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B197" s="38" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C197" s="14">
         <v>120</v>
@@ -8239,18 +8239,18 @@
       <c r="D197" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E197" s="145"/>
+      <c r="E197" s="134"/>
       <c r="F197" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G197" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H197" s="134"/>
+      <c r="H197" s="143"/>
     </row>
     <row r="198" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B198" s="38" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C198" s="14">
         <v>230</v>
@@ -8258,18 +8258,18 @@
       <c r="D198" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E198" s="145"/>
+      <c r="E198" s="134"/>
       <c r="F198" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G198" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H198" s="134"/>
+      <c r="H198" s="143"/>
     </row>
     <row r="199" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B199" s="39" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C199" s="24">
         <v>80</v>
@@ -8277,18 +8277,18 @@
       <c r="D199" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E199" s="146"/>
+      <c r="E199" s="136"/>
       <c r="F199" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G199" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="H199" s="136"/>
+        <v>119</v>
+      </c>
+      <c r="H199" s="144"/>
     </row>
     <row r="200" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B200" s="68" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C200" s="22">
         <v>1525</v>
@@ -8296,20 +8296,20 @@
       <c r="D200" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E200" s="144">
+      <c r="E200" s="133">
         <v>233</v>
       </c>
       <c r="F200" s="72"/>
       <c r="G200" s="48" t="s">
-        <v>334</v>
-      </c>
-      <c r="H200" s="137" t="s">
-        <v>408</v>
+        <v>332</v>
+      </c>
+      <c r="H200" s="149" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="201" spans="2:12" ht="15.75" customHeight="1">
       <c r="B201" s="74" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C201" s="14">
         <v>160</v>
@@ -8317,14 +8317,14 @@
       <c r="D201" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E201" s="145"/>
+      <c r="E201" s="134"/>
       <c r="F201" s="50"/>
       <c r="G201" s="12"/>
-      <c r="H201" s="138"/>
+      <c r="H201" s="146"/>
     </row>
     <row r="202" spans="2:12" ht="15.75" customHeight="1">
       <c r="B202" s="70" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C202" s="14">
         <v>270</v>
@@ -8332,16 +8332,16 @@
       <c r="D202" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E202" s="145"/>
+      <c r="E202" s="134"/>
       <c r="F202" s="50"/>
       <c r="G202" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H202" s="138"/>
+      <c r="H202" s="146"/>
     </row>
     <row r="203" spans="2:12" ht="15.75" customHeight="1">
       <c r="B203" s="70" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C203" s="14">
         <v>140</v>
@@ -8349,16 +8349,16 @@
       <c r="D203" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E203" s="145"/>
+      <c r="E203" s="134"/>
       <c r="F203" s="50"/>
       <c r="G203" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H203" s="138"/>
+      <c r="H203" s="146"/>
     </row>
     <row r="204" spans="2:12" ht="15.75" customHeight="1">
       <c r="B204" s="70" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C204" s="14">
         <v>260</v>
@@ -8366,16 +8366,16 @@
       <c r="D204" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E204" s="145"/>
+      <c r="E204" s="134"/>
       <c r="F204" s="50"/>
       <c r="G204" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H204" s="138"/>
+      <c r="H204" s="146"/>
     </row>
     <row r="205" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B205" s="71" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C205" s="24">
         <v>95</v>
@@ -8383,16 +8383,16 @@
       <c r="D205" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E205" s="146"/>
+      <c r="E205" s="136"/>
       <c r="F205" s="89"/>
       <c r="G205" s="90" t="s">
-        <v>120</v>
-      </c>
-      <c r="H205" s="139"/>
+        <v>119</v>
+      </c>
+      <c r="H205" s="147"/>
     </row>
     <row r="206" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B206" s="117" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C206" s="22">
         <v>1110</v>
@@ -8400,22 +8400,22 @@
       <c r="D206" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E206" s="144">
+      <c r="E206" s="133">
         <v>167</v>
       </c>
       <c r="F206" s="127" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G206" s="114" t="s">
-        <v>384</v>
-      </c>
-      <c r="H206" s="133" t="s">
-        <v>406</v>
+        <v>382</v>
+      </c>
+      <c r="H206" s="142" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="207" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B207" s="74" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C207" s="14">
         <v>200</v>
@@ -8423,18 +8423,18 @@
       <c r="D207" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E207" s="145"/>
+      <c r="E207" s="134"/>
       <c r="F207" s="127" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G207" s="119" t="s">
-        <v>386</v>
-      </c>
-      <c r="H207" s="134"/>
+        <v>384</v>
+      </c>
+      <c r="H207" s="143"/>
     </row>
     <row r="208" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B208" s="125" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C208" s="14">
         <v>300</v>
@@ -8442,18 +8442,18 @@
       <c r="D208" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E208" s="145"/>
+      <c r="E208" s="134"/>
       <c r="F208" s="127" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G208" s="120" t="s">
-        <v>385</v>
-      </c>
-      <c r="H208" s="134"/>
+        <v>383</v>
+      </c>
+      <c r="H208" s="143"/>
     </row>
     <row r="209" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B209" s="125" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C209" s="14">
         <v>180</v>
@@ -8461,18 +8461,18 @@
       <c r="D209" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E209" s="145"/>
+      <c r="E209" s="134"/>
       <c r="F209" s="127" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G209" s="119" t="s">
-        <v>386</v>
-      </c>
-      <c r="H209" s="134"/>
+        <v>384</v>
+      </c>
+      <c r="H209" s="143"/>
     </row>
     <row r="210" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B210" s="125" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C210" s="14">
         <v>290</v>
@@ -8480,18 +8480,18 @@
       <c r="D210" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E210" s="145"/>
+      <c r="E210" s="134"/>
       <c r="F210" s="127" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G210" s="122" t="s">
-        <v>386</v>
-      </c>
-      <c r="H210" s="134"/>
+        <v>384</v>
+      </c>
+      <c r="H210" s="143"/>
     </row>
     <row r="211" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B211" s="126" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C211" s="24">
         <v>140</v>
@@ -8499,18 +8499,18 @@
       <c r="D211" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E211" s="146"/>
+      <c r="E211" s="136"/>
       <c r="F211" s="127" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G211" s="121" t="s">
-        <v>386</v>
-      </c>
-      <c r="H211" s="136"/>
+        <v>384</v>
+      </c>
+      <c r="H211" s="144"/>
     </row>
     <row r="212" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B212" s="117" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C212" s="22">
         <v>1110</v>
@@ -8518,22 +8518,22 @@
       <c r="D212" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E212" s="141">
+      <c r="E212" s="139">
         <v>167</v>
       </c>
       <c r="F212" s="127" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G212" s="114" t="s">
-        <v>393</v>
-      </c>
-      <c r="H212" s="133" t="s">
-        <v>406</v>
+        <v>391</v>
+      </c>
+      <c r="H212" s="142" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="213" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B213" s="74" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C213" s="14">
         <v>200</v>
@@ -8541,18 +8541,18 @@
       <c r="D213" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E213" s="142"/>
+      <c r="E213" s="140"/>
       <c r="F213" s="127" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="G213" s="118" t="s">
-        <v>395</v>
-      </c>
-      <c r="H213" s="134"/>
+        <v>393</v>
+      </c>
+      <c r="H213" s="143"/>
     </row>
     <row r="214" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B214" s="125" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C214" s="14">
         <v>300</v>
@@ -8560,18 +8560,18 @@
       <c r="D214" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E214" s="142"/>
+      <c r="E214" s="140"/>
       <c r="F214" s="127" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G214" s="118" t="s">
-        <v>397</v>
-      </c>
-      <c r="H214" s="134"/>
+        <v>395</v>
+      </c>
+      <c r="H214" s="143"/>
     </row>
     <row r="215" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B215" s="125" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C215" s="14">
         <v>180</v>
@@ -8579,18 +8579,18 @@
       <c r="D215" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E215" s="142"/>
+      <c r="E215" s="140"/>
       <c r="F215" s="127" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G215" s="118" t="s">
-        <v>395</v>
-      </c>
-      <c r="H215" s="134"/>
+        <v>393</v>
+      </c>
+      <c r="H215" s="143"/>
     </row>
     <row r="216" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B216" s="125" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C216" s="14">
         <v>290</v>
@@ -8598,18 +8598,18 @@
       <c r="D216" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E216" s="142"/>
+      <c r="E216" s="140"/>
       <c r="F216" s="127" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G216" s="118" t="s">
-        <v>395</v>
-      </c>
-      <c r="H216" s="134"/>
+        <v>393</v>
+      </c>
+      <c r="H216" s="143"/>
     </row>
     <row r="217" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B217" s="126" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C217" s="123">
         <v>140</v>
@@ -8617,18 +8617,18 @@
       <c r="D217" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="E217" s="143"/>
+      <c r="E217" s="141"/>
       <c r="F217" s="127" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G217" s="119" t="s">
-        <v>398</v>
-      </c>
-      <c r="H217" s="136"/>
+        <v>396</v>
+      </c>
+      <c r="H217" s="144"/>
     </row>
     <row r="218" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B218" s="91" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C218" s="92">
         <v>5</v>
@@ -8640,18 +8640,18 @@
         <v>100</v>
       </c>
       <c r="F218" s="94" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G218" s="59" t="s">
         <v>17</v>
       </c>
       <c r="H218" s="128" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="219" spans="2:8" ht="15.75" customHeight="1">
       <c r="B219" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C219" s="14">
         <v>12</v>
@@ -8669,12 +8669,12 @@
         <v>7</v>
       </c>
       <c r="H219" s="128" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="220" spans="2:8" ht="15.75" customHeight="1">
       <c r="B220" s="44" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C220" s="14">
         <v>30</v>
@@ -8692,12 +8692,12 @@
         <v>7</v>
       </c>
       <c r="H220" s="129" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="221" spans="2:8" ht="15.75" customHeight="1">
       <c r="B221" s="44" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C221" s="14">
         <v>35</v>
@@ -8709,18 +8709,18 @@
         <v>100</v>
       </c>
       <c r="F221" s="15" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G221" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H221" s="128" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="222" spans="2:8" ht="15.75" customHeight="1">
       <c r="B222" s="13" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C222" s="14">
         <v>58</v>
@@ -8732,18 +8732,18 @@
         <v>100</v>
       </c>
       <c r="F222" s="96" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G222" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H222" s="128" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="223" spans="2:8" ht="15.75" customHeight="1">
       <c r="B223" s="38" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C223" s="14">
         <v>60</v>
@@ -8758,15 +8758,15 @@
         <v>7</v>
       </c>
       <c r="G223" s="54" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H223" s="130" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="224" spans="2:8" ht="15.75" customHeight="1">
       <c r="B224" s="44" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C224" s="14">
         <v>70</v>
@@ -8784,12 +8784,12 @@
         <v>7</v>
       </c>
       <c r="H224" s="128" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="225" spans="2:8" ht="15.75" customHeight="1">
       <c r="B225" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C225" s="14">
         <v>70</v>
@@ -8807,12 +8807,12 @@
         <v>7</v>
       </c>
       <c r="H225" s="128" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="226" spans="2:8" ht="15.75" customHeight="1">
       <c r="B226" s="97" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C226" s="14">
         <v>100</v>
@@ -8830,12 +8830,12 @@
         <v>7</v>
       </c>
       <c r="H226" s="128" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="227" spans="2:8" ht="15.75" customHeight="1">
       <c r="B227" s="44" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C227" s="14">
         <v>115</v>
@@ -8847,18 +8847,18 @@
         <v>143</v>
       </c>
       <c r="F227" s="15" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G227" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H227" s="128" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="228" spans="2:8" ht="15.75" customHeight="1">
       <c r="B228" s="87" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C228" s="14">
         <v>150</v>
@@ -8870,18 +8870,18 @@
         <v>125</v>
       </c>
       <c r="F228" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G228" s="54" t="s">
         <v>45</v>
       </c>
       <c r="H228" s="128" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="229" spans="2:8" ht="15.75" customHeight="1">
       <c r="B229" s="44" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C229" s="14">
         <v>160</v>
@@ -8893,18 +8893,18 @@
         <v>167</v>
       </c>
       <c r="F229" s="56" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G229" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H229" s="129" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="230" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B230" s="131" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C230" s="24">
         <v>200</v>
@@ -8919,10 +8919,10 @@
         <v>7</v>
       </c>
       <c r="G230" s="27" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H230" s="132" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="231" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
@@ -13789,38 +13789,30 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="72">
-    <mergeCell ref="E140:E145"/>
-    <mergeCell ref="E146:E151"/>
-    <mergeCell ref="E158:E163"/>
-    <mergeCell ref="E194:E199"/>
-    <mergeCell ref="E200:E205"/>
-    <mergeCell ref="E164:E169"/>
-    <mergeCell ref="E170:E175"/>
-    <mergeCell ref="E176:E181"/>
-    <mergeCell ref="E182:E187"/>
-    <mergeCell ref="E188:E193"/>
-    <mergeCell ref="E152:E157"/>
-    <mergeCell ref="E92:E97"/>
-    <mergeCell ref="E98:E103"/>
-    <mergeCell ref="E104:E109"/>
-    <mergeCell ref="E116:E121"/>
-    <mergeCell ref="E122:E127"/>
-    <mergeCell ref="E110:E115"/>
-    <mergeCell ref="E62:E67"/>
-    <mergeCell ref="E68:E73"/>
-    <mergeCell ref="E74:E79"/>
-    <mergeCell ref="E80:E85"/>
-    <mergeCell ref="E86:E91"/>
-    <mergeCell ref="E32:E37"/>
-    <mergeCell ref="E38:E43"/>
-    <mergeCell ref="E44:E49"/>
-    <mergeCell ref="E50:E55"/>
-    <mergeCell ref="E56:E61"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="E8:E13"/>
-    <mergeCell ref="E14:E19"/>
-    <mergeCell ref="E20:E25"/>
-    <mergeCell ref="E26:E31"/>
+    <mergeCell ref="H188:H193"/>
+    <mergeCell ref="H194:H199"/>
+    <mergeCell ref="H200:H205"/>
+    <mergeCell ref="H206:H211"/>
+    <mergeCell ref="H92:H97"/>
+    <mergeCell ref="H98:H103"/>
+    <mergeCell ref="H104:H109"/>
+    <mergeCell ref="H110:H115"/>
+    <mergeCell ref="H116:H121"/>
+    <mergeCell ref="H62:H67"/>
+    <mergeCell ref="H68:H73"/>
+    <mergeCell ref="H74:H79"/>
+    <mergeCell ref="H80:H85"/>
+    <mergeCell ref="H86:H91"/>
+    <mergeCell ref="H32:H37"/>
+    <mergeCell ref="H38:H43"/>
+    <mergeCell ref="H44:H49"/>
+    <mergeCell ref="H50:H55"/>
+    <mergeCell ref="H56:H61"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="H8:H13"/>
+    <mergeCell ref="H14:H19"/>
+    <mergeCell ref="H20:H25"/>
+    <mergeCell ref="H26:H31"/>
     <mergeCell ref="E212:E217"/>
     <mergeCell ref="E206:E211"/>
     <mergeCell ref="H122:H127"/>
@@ -13837,30 +13829,38 @@
     <mergeCell ref="E134:E139"/>
     <mergeCell ref="H212:H217"/>
     <mergeCell ref="H182:H187"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="H8:H13"/>
-    <mergeCell ref="H14:H19"/>
-    <mergeCell ref="H20:H25"/>
-    <mergeCell ref="H26:H31"/>
-    <mergeCell ref="H32:H37"/>
-    <mergeCell ref="H38:H43"/>
-    <mergeCell ref="H44:H49"/>
-    <mergeCell ref="H50:H55"/>
-    <mergeCell ref="H56:H61"/>
-    <mergeCell ref="H62:H67"/>
-    <mergeCell ref="H68:H73"/>
-    <mergeCell ref="H74:H79"/>
-    <mergeCell ref="H80:H85"/>
-    <mergeCell ref="H86:H91"/>
-    <mergeCell ref="H188:H193"/>
-    <mergeCell ref="H194:H199"/>
-    <mergeCell ref="H200:H205"/>
-    <mergeCell ref="H206:H211"/>
-    <mergeCell ref="H92:H97"/>
-    <mergeCell ref="H98:H103"/>
-    <mergeCell ref="H104:H109"/>
-    <mergeCell ref="H110:H115"/>
-    <mergeCell ref="H116:H121"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="E8:E13"/>
+    <mergeCell ref="E14:E19"/>
+    <mergeCell ref="E20:E25"/>
+    <mergeCell ref="E26:E31"/>
+    <mergeCell ref="E32:E37"/>
+    <mergeCell ref="E38:E43"/>
+    <mergeCell ref="E44:E49"/>
+    <mergeCell ref="E50:E55"/>
+    <mergeCell ref="E56:E61"/>
+    <mergeCell ref="E62:E67"/>
+    <mergeCell ref="E68:E73"/>
+    <mergeCell ref="E74:E79"/>
+    <mergeCell ref="E80:E85"/>
+    <mergeCell ref="E86:E91"/>
+    <mergeCell ref="E92:E97"/>
+    <mergeCell ref="E98:E103"/>
+    <mergeCell ref="E104:E109"/>
+    <mergeCell ref="E116:E121"/>
+    <mergeCell ref="E122:E127"/>
+    <mergeCell ref="E110:E115"/>
+    <mergeCell ref="E140:E145"/>
+    <mergeCell ref="E146:E151"/>
+    <mergeCell ref="E158:E163"/>
+    <mergeCell ref="E194:E199"/>
+    <mergeCell ref="E200:E205"/>
+    <mergeCell ref="E164:E169"/>
+    <mergeCell ref="E170:E175"/>
+    <mergeCell ref="E176:E181"/>
+    <mergeCell ref="E182:E187"/>
+    <mergeCell ref="E188:E193"/>
+    <mergeCell ref="E152:E157"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-source/护甲数据.xlsx
+++ b/data-source/护甲数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354C97C5-ADDF-43B1-90EE-4CA2299B01E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7473F8-0B25-4F76-900F-BC8450170062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="431">
   <si>
     <t>护甲</t>
   </si>
@@ -607,26 +607,6 @@
   </si>
   <si>
     <t>风暴使者头盔</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>移动速度：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>6</t>
-    </r>
   </si>
   <si>
     <r>
@@ -3702,46 +3682,46 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4056,7 +4036,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
@@ -4069,22 +4049,22 @@
       <c r="D2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="137">
+      <c r="E2" s="149">
         <v>91</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="142" t="s">
-        <v>403</v>
+      <c r="H2" s="133" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="15.75" customHeight="1">
       <c r="B3" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C3" s="14">
         <v>10</v>
@@ -4092,18 +4072,18 @@
       <c r="D3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="134"/>
+      <c r="E3" s="145"/>
       <c r="F3" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="143"/>
+      <c r="H3" s="134"/>
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1">
       <c r="B4" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C4" s="14">
         <v>25</v>
@@ -4111,18 +4091,18 @@
       <c r="D4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="134"/>
+      <c r="E4" s="145"/>
       <c r="F4" s="15" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="143"/>
+      <c r="H4" s="134"/>
     </row>
     <row r="5" spans="2:8" ht="15.75" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C5" s="14">
         <v>10</v>
@@ -4130,18 +4110,18 @@
       <c r="D5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="134"/>
+      <c r="E5" s="145"/>
       <c r="F5" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="143"/>
+      <c r="H5" s="134"/>
     </row>
     <row r="6" spans="2:8" ht="15.75" customHeight="1">
       <c r="B6" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C6" s="14">
         <v>25</v>
@@ -4149,18 +4129,18 @@
       <c r="D6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="134"/>
+      <c r="E6" s="145"/>
       <c r="F6" s="15" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="143"/>
+      <c r="H6" s="134"/>
     </row>
     <row r="7" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B7" s="16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C7" s="17">
         <v>0</v>
@@ -4168,14 +4148,14 @@
       <c r="D7" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="135"/>
+      <c r="E7" s="148"/>
       <c r="F7" s="19" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="144"/>
+      <c r="H7" s="136"/>
     </row>
     <row r="8" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B8" s="21" t="s">
@@ -4187,17 +4167,17 @@
       <c r="D8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="133">
+      <c r="E8" s="144">
         <v>91</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="142" t="s">
-        <v>404</v>
+      <c r="H8" s="133" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15.75" customHeight="1">
@@ -4210,14 +4190,14 @@
       <c r="D9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="134"/>
+      <c r="E9" s="145"/>
       <c r="F9" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="143"/>
+      <c r="H9" s="134"/>
     </row>
     <row r="10" spans="2:8" ht="15.75" customHeight="1">
       <c r="B10" s="13" t="s">
@@ -4229,14 +4209,14 @@
       <c r="D10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="134"/>
+      <c r="E10" s="145"/>
       <c r="F10" s="15" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="143"/>
+      <c r="H10" s="134"/>
     </row>
     <row r="11" spans="2:8" ht="15.75" customHeight="1">
       <c r="B11" s="13" t="s">
@@ -4248,18 +4228,18 @@
       <c r="D11" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="134"/>
+      <c r="E11" s="145"/>
       <c r="F11" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="143"/>
+      <c r="H11" s="134"/>
     </row>
     <row r="12" spans="2:8" ht="15.75" customHeight="1">
       <c r="B12" s="13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C12" s="14">
         <v>25</v>
@@ -4267,18 +4247,18 @@
       <c r="D12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="134"/>
+      <c r="E12" s="145"/>
       <c r="F12" s="15" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="143"/>
+      <c r="H12" s="134"/>
     </row>
     <row r="13" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B13" s="23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C13" s="24">
         <v>0</v>
@@ -4286,14 +4266,14 @@
       <c r="D13" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="136"/>
+      <c r="E13" s="146"/>
       <c r="F13" s="26" t="s">
         <v>9</v>
       </c>
       <c r="G13" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="144"/>
+      <c r="H13" s="136"/>
     </row>
     <row r="14" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B14" s="8" t="s">
@@ -4305,22 +4285,22 @@
       <c r="D14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="138">
+      <c r="E14" s="147">
         <v>100</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="142" t="s">
-        <v>403</v>
+      <c r="H14" s="133" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15.75" customHeight="1">
       <c r="B15" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C15" s="14">
         <v>30</v>
@@ -4328,18 +4308,18 @@
       <c r="D15" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="134"/>
+      <c r="E15" s="145"/>
       <c r="F15" s="15" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H15" s="143"/>
+      <c r="H15" s="134"/>
     </row>
     <row r="16" spans="2:8" ht="15.75" customHeight="1">
       <c r="B16" s="13" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C16" s="14">
         <v>50</v>
@@ -4347,14 +4327,14 @@
       <c r="D16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="134"/>
+      <c r="E16" s="145"/>
       <c r="F16" s="15" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="143"/>
+      <c r="H16" s="134"/>
     </row>
     <row r="17" spans="2:12" ht="15.75" customHeight="1">
       <c r="B17" s="13" t="s">
@@ -4366,14 +4346,14 @@
       <c r="D17" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="134"/>
+      <c r="E17" s="145"/>
       <c r="F17" s="15" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H17" s="143"/>
+      <c r="H17" s="134"/>
       <c r="I17" s="29"/>
       <c r="J17" s="29"/>
       <c r="K17" s="29"/>
@@ -4381,7 +4361,7 @@
     </row>
     <row r="18" spans="2:12" ht="15.75" customHeight="1">
       <c r="B18" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C18" s="14">
         <v>50</v>
@@ -4389,14 +4369,14 @@
       <c r="D18" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="134"/>
+      <c r="E18" s="145"/>
       <c r="F18" s="15" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="143"/>
+      <c r="H18" s="134"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
       <c r="K18" s="29"/>
@@ -4404,7 +4384,7 @@
     </row>
     <row r="19" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B19" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C19" s="17">
         <v>0</v>
@@ -4412,14 +4392,14 @@
       <c r="D19" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="135"/>
+      <c r="E19" s="148"/>
       <c r="F19" s="19" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="144"/>
+      <c r="H19" s="136"/>
       <c r="I19" s="29"/>
       <c r="J19" s="29"/>
       <c r="K19" s="29"/>
@@ -4435,22 +4415,22 @@
       <c r="D20" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="133">
+      <c r="E20" s="144">
         <v>100</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G20" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="H20" s="142" t="s">
-        <v>405</v>
+      <c r="H20" s="133" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="15.75" customHeight="1">
       <c r="B21" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C21" s="14">
         <v>30</v>
@@ -4458,18 +4438,18 @@
       <c r="D21" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="134"/>
+      <c r="E21" s="145"/>
       <c r="F21" s="15" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H21" s="143"/>
+      <c r="H21" s="134"/>
     </row>
     <row r="22" spans="2:12" ht="15.75" customHeight="1">
       <c r="B22" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C22" s="14">
         <v>50</v>
@@ -4477,14 +4457,14 @@
       <c r="D22" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="134"/>
+      <c r="E22" s="145"/>
       <c r="F22" s="15" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H22" s="143"/>
+      <c r="H22" s="134"/>
     </row>
     <row r="23" spans="2:12" ht="15.75" customHeight="1">
       <c r="B23" s="13" t="s">
@@ -4496,18 +4476,18 @@
       <c r="D23" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="134"/>
+      <c r="E23" s="145"/>
       <c r="F23" s="15" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H23" s="143"/>
+      <c r="H23" s="134"/>
     </row>
     <row r="24" spans="2:12" ht="15.75" customHeight="1">
       <c r="B24" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C24" s="14">
         <v>50</v>
@@ -4515,18 +4495,18 @@
       <c r="D24" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="134"/>
+      <c r="E24" s="145"/>
       <c r="F24" s="15" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H24" s="143"/>
+      <c r="H24" s="134"/>
     </row>
     <row r="25" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B25" s="107" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C25" s="17">
         <v>0</v>
@@ -4534,14 +4514,14 @@
       <c r="D25" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="135"/>
+      <c r="E25" s="148"/>
       <c r="F25" s="19" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H25" s="144"/>
+      <c r="H25" s="136"/>
     </row>
     <row r="26" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B26" s="21" t="s">
@@ -4553,22 +4533,22 @@
       <c r="D26" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="133">
+      <c r="E26" s="144">
         <v>100</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G26" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H26" s="142" t="s">
-        <v>404</v>
+      <c r="H26" s="133" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="27" spans="2:12" ht="15.75" customHeight="1">
       <c r="B27" s="13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C27" s="14">
         <v>30</v>
@@ -4576,18 +4556,18 @@
       <c r="D27" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="134"/>
+      <c r="E27" s="145"/>
       <c r="F27" s="15" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G27" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H27" s="143"/>
+      <c r="H27" s="134"/>
     </row>
     <row r="28" spans="2:12" ht="15.75" customHeight="1">
       <c r="B28" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C28" s="14">
         <v>50</v>
@@ -4595,18 +4575,18 @@
       <c r="D28" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="134"/>
+      <c r="E28" s="145"/>
       <c r="F28" s="15" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H28" s="143"/>
+      <c r="H28" s="134"/>
     </row>
     <row r="29" spans="2:12" ht="15.75" customHeight="1">
       <c r="B29" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C29" s="14">
         <v>20</v>
@@ -4614,18 +4594,18 @@
       <c r="D29" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="134"/>
+      <c r="E29" s="145"/>
       <c r="F29" s="15" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G29" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H29" s="143"/>
+      <c r="H29" s="134"/>
     </row>
     <row r="30" spans="2:12" ht="15.75" customHeight="1">
       <c r="B30" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C30" s="14">
         <v>50</v>
@@ -4633,18 +4613,18 @@
       <c r="D30" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="134"/>
+      <c r="E30" s="145"/>
       <c r="F30" s="15" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H30" s="143"/>
+      <c r="H30" s="134"/>
     </row>
     <row r="31" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B31" s="32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C31" s="33">
         <v>0</v>
@@ -4652,14 +4632,14 @@
       <c r="D31" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="136"/>
+      <c r="E31" s="146"/>
       <c r="F31" s="34" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H31" s="144"/>
+      <c r="H31" s="136"/>
     </row>
     <row r="32" spans="2:12" ht="25.9" thickTop="1">
       <c r="B32" s="36" t="s">
@@ -4671,17 +4651,17 @@
       <c r="D32" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="133">
+      <c r="E32" s="144">
         <v>112</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G32" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="H32" s="142" t="s">
-        <v>404</v>
+      <c r="H32" s="133" t="s">
+        <v>403</v>
       </c>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -4690,7 +4670,7 @@
     </row>
     <row r="33" spans="2:12" ht="15.75" customHeight="1">
       <c r="B33" s="87" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C33" s="14">
         <v>40</v>
@@ -4698,14 +4678,14 @@
       <c r="D33" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="134"/>
+      <c r="E33" s="145"/>
       <c r="F33" s="15" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H33" s="143"/>
+      <c r="H33" s="134"/>
       <c r="I33" s="29"/>
       <c r="J33" s="29"/>
       <c r="K33" s="29"/>
@@ -4721,14 +4701,14 @@
       <c r="D34" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="134"/>
+      <c r="E34" s="145"/>
       <c r="F34" s="15" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="143"/>
+      <c r="H34" s="134"/>
       <c r="I34" s="29"/>
       <c r="J34" s="29"/>
       <c r="K34" s="29"/>
@@ -4736,7 +4716,7 @@
     </row>
     <row r="35" spans="2:12" ht="15.75" customHeight="1">
       <c r="B35" s="38" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C35" s="14">
         <v>30</v>
@@ -4744,14 +4724,14 @@
       <c r="D35" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="134"/>
+      <c r="E35" s="145"/>
       <c r="F35" s="15" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H35" s="143"/>
+      <c r="H35" s="134"/>
       <c r="I35" s="29"/>
       <c r="J35" s="29"/>
       <c r="K35" s="29"/>
@@ -4759,7 +4739,7 @@
     </row>
     <row r="36" spans="2:12" ht="15.75" customHeight="1">
       <c r="B36" s="87" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C36" s="14">
         <v>60</v>
@@ -4767,14 +4747,14 @@
       <c r="D36" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="134"/>
+      <c r="E36" s="145"/>
       <c r="F36" s="15" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H36" s="143"/>
+      <c r="H36" s="134"/>
       <c r="I36" s="29"/>
       <c r="J36" s="29"/>
       <c r="K36" s="29"/>
@@ -4782,7 +4762,7 @@
     </row>
     <row r="37" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B37" s="108" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C37" s="24">
         <v>10</v>
@@ -4790,14 +4770,14 @@
       <c r="D37" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E37" s="136"/>
+      <c r="E37" s="146"/>
       <c r="F37" s="26" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G37" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="H37" s="144"/>
+      <c r="H37" s="136"/>
       <c r="I37" s="29"/>
       <c r="J37" s="29"/>
       <c r="K37" s="29"/>
@@ -4813,17 +4793,17 @@
       <c r="D38" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="133">
+      <c r="E38" s="144">
         <v>100</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G38" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="H38" s="142" t="s">
-        <v>404</v>
+      <c r="H38" s="133" t="s">
+        <v>403</v>
       </c>
       <c r="I38" s="29"/>
       <c r="J38" s="29"/>
@@ -4840,14 +4820,14 @@
       <c r="D39" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E39" s="134"/>
+      <c r="E39" s="145"/>
       <c r="F39" s="15" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H39" s="143"/>
+      <c r="H39" s="134"/>
       <c r="I39" s="29"/>
       <c r="J39" s="29"/>
       <c r="K39" s="29"/>
@@ -4863,14 +4843,14 @@
       <c r="D40" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E40" s="134"/>
+      <c r="E40" s="145"/>
       <c r="F40" s="15" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G40" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H40" s="143"/>
+      <c r="H40" s="134"/>
       <c r="I40" s="29"/>
       <c r="J40" s="29"/>
       <c r="K40" s="29"/>
@@ -4886,14 +4866,14 @@
       <c r="D41" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E41" s="134"/>
+      <c r="E41" s="145"/>
       <c r="F41" s="15" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G41" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H41" s="143"/>
+      <c r="H41" s="134"/>
       <c r="I41" s="29"/>
       <c r="J41" s="29"/>
       <c r="K41" s="29"/>
@@ -4901,7 +4881,7 @@
     </row>
     <row r="42" spans="2:12" ht="15.75" customHeight="1">
       <c r="B42" s="44" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C42" s="14">
         <v>50</v>
@@ -4909,14 +4889,14 @@
       <c r="D42" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E42" s="134"/>
+      <c r="E42" s="145"/>
       <c r="F42" s="15" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G42" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="143"/>
+      <c r="H42" s="134"/>
       <c r="I42" s="29"/>
       <c r="J42" s="29"/>
       <c r="K42" s="29"/>
@@ -4924,7 +4904,7 @@
     </row>
     <row r="43" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B43" s="45" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C43" s="24">
         <v>0</v>
@@ -4932,14 +4912,14 @@
       <c r="D43" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E43" s="136"/>
+      <c r="E43" s="146"/>
       <c r="F43" s="26" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G43" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="H43" s="144"/>
+      <c r="H43" s="136"/>
       <c r="I43" s="29"/>
       <c r="J43" s="29"/>
       <c r="K43" s="29"/>
@@ -4955,17 +4935,17 @@
       <c r="D44" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E44" s="137">
+      <c r="E44" s="149">
         <v>112</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G44" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H44" s="142" t="s">
-        <v>403</v>
+      <c r="H44" s="133" t="s">
+        <v>402</v>
       </c>
       <c r="I44" s="29"/>
       <c r="J44" s="29"/>
@@ -4974,7 +4954,7 @@
     </row>
     <row r="45" spans="2:12" ht="15.75" customHeight="1">
       <c r="B45" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C45" s="14">
         <v>50</v>
@@ -4982,14 +4962,14 @@
       <c r="D45" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E45" s="134"/>
+      <c r="E45" s="145"/>
       <c r="F45" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G45" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H45" s="143"/>
+      <c r="H45" s="134"/>
       <c r="I45" s="29"/>
       <c r="J45" s="29"/>
       <c r="K45" s="29"/>
@@ -4997,7 +4977,7 @@
     </row>
     <row r="46" spans="2:12" ht="15.75" customHeight="1">
       <c r="B46" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C46" s="14">
         <v>90</v>
@@ -5005,14 +4985,14 @@
       <c r="D46" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E46" s="134"/>
+      <c r="E46" s="145"/>
       <c r="F46" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G46" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H46" s="143"/>
+      <c r="H46" s="134"/>
       <c r="I46" s="29"/>
       <c r="J46" s="29"/>
       <c r="K46" s="29"/>
@@ -5020,7 +5000,7 @@
     </row>
     <row r="47" spans="2:12" ht="15.75" customHeight="1">
       <c r="B47" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C47" s="14">
         <v>30</v>
@@ -5028,14 +5008,14 @@
       <c r="D47" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E47" s="134"/>
+      <c r="E47" s="145"/>
       <c r="F47" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G47" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H47" s="143"/>
+      <c r="H47" s="134"/>
       <c r="I47" s="29"/>
       <c r="J47" s="29"/>
       <c r="K47" s="29"/>
@@ -5043,7 +5023,7 @@
     </row>
     <row r="48" spans="2:12" ht="15.75" customHeight="1">
       <c r="B48" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C48" s="14">
         <v>80</v>
@@ -5051,14 +5031,14 @@
       <c r="D48" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E48" s="134"/>
+      <c r="E48" s="145"/>
       <c r="F48" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G48" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H48" s="143"/>
+      <c r="H48" s="134"/>
       <c r="I48" s="29"/>
       <c r="J48" s="29"/>
       <c r="K48" s="29"/>
@@ -5066,7 +5046,7 @@
     </row>
     <row r="49" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B49" s="16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C49" s="17">
         <v>10</v>
@@ -5074,14 +5054,14 @@
       <c r="D49" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E49" s="135"/>
+      <c r="E49" s="148"/>
       <c r="F49" s="19" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G49" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H49" s="144"/>
+      <c r="H49" s="136"/>
       <c r="I49" s="29"/>
       <c r="J49" s="29"/>
       <c r="K49" s="29"/>
@@ -5097,17 +5077,17 @@
       <c r="D50" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E50" s="133">
+      <c r="E50" s="144">
         <v>112</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G50" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H50" s="142" t="s">
-        <v>406</v>
+      <c r="H50" s="133" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="51" spans="2:12" ht="15.75" customHeight="1">
@@ -5120,18 +5100,18 @@
       <c r="D51" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E51" s="134"/>
+      <c r="E51" s="145"/>
       <c r="F51" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G51" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H51" s="143"/>
+      <c r="H51" s="134"/>
     </row>
     <row r="52" spans="2:12" ht="15.75" customHeight="1">
       <c r="B52" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C52" s="14">
         <v>90</v>
@@ -5139,18 +5119,18 @@
       <c r="D52" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E52" s="134"/>
+      <c r="E52" s="145"/>
       <c r="F52" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G52" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H52" s="143"/>
+      <c r="H52" s="134"/>
     </row>
     <row r="53" spans="2:12" ht="15.75" customHeight="1">
       <c r="B53" s="13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C53" s="14">
         <v>30</v>
@@ -5158,18 +5138,18 @@
       <c r="D53" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E53" s="134"/>
+      <c r="E53" s="145"/>
       <c r="F53" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G53" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H53" s="143"/>
+      <c r="H53" s="134"/>
     </row>
     <row r="54" spans="2:12" ht="15.75" customHeight="1">
       <c r="B54" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C54" s="14">
         <v>80</v>
@@ -5177,18 +5157,18 @@
       <c r="D54" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E54" s="134"/>
+      <c r="E54" s="145"/>
       <c r="F54" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H54" s="143"/>
+      <c r="H54" s="134"/>
     </row>
     <row r="55" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B55" s="16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C55" s="17">
         <v>10</v>
@@ -5196,14 +5176,14 @@
       <c r="D55" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E55" s="135"/>
+      <c r="E55" s="148"/>
       <c r="F55" s="19" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G55" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H55" s="144"/>
+      <c r="H55" s="136"/>
     </row>
     <row r="56" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B56" s="36" t="s">
@@ -5213,9 +5193,9 @@
         <v>260</v>
       </c>
       <c r="D56" s="63" t="s">
-        <v>181</v>
-      </c>
-      <c r="E56" s="133">
+        <v>180</v>
+      </c>
+      <c r="E56" s="144">
         <v>112</v>
       </c>
       <c r="F56" s="47" t="s">
@@ -5224,104 +5204,104 @@
       <c r="G56" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="H56" s="142" t="s">
-        <v>407</v>
+      <c r="H56" s="133" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="57" spans="2:12" ht="15.75" customHeight="1">
       <c r="B57" s="38" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C57" s="49">
         <v>50</v>
       </c>
       <c r="D57" s="63" t="s">
-        <v>179</v>
-      </c>
-      <c r="E57" s="134"/>
+        <v>178</v>
+      </c>
+      <c r="E57" s="145"/>
       <c r="F57" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G57" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H57" s="143"/>
+      <c r="H57" s="134"/>
     </row>
     <row r="58" spans="2:12" ht="15.75" customHeight="1">
       <c r="B58" s="38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C58" s="49">
         <v>90</v>
       </c>
       <c r="D58" s="63" t="s">
-        <v>180</v>
-      </c>
-      <c r="E58" s="134"/>
+        <v>179</v>
+      </c>
+      <c r="E58" s="145"/>
       <c r="F58" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G58" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H58" s="143"/>
+      <c r="H58" s="134"/>
     </row>
     <row r="59" spans="2:12" ht="15.75" customHeight="1">
       <c r="B59" s="38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C59" s="49">
         <v>30</v>
       </c>
       <c r="D59" s="63" t="s">
-        <v>179</v>
-      </c>
-      <c r="E59" s="134"/>
+        <v>178</v>
+      </c>
+      <c r="E59" s="145"/>
       <c r="F59" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G59" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H59" s="143"/>
+      <c r="H59" s="134"/>
     </row>
     <row r="60" spans="2:12" ht="15.75" customHeight="1">
       <c r="B60" s="38" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C60" s="49">
         <v>80</v>
       </c>
       <c r="D60" s="63" t="s">
-        <v>180</v>
-      </c>
-      <c r="E60" s="134"/>
+        <v>179</v>
+      </c>
+      <c r="E60" s="145"/>
       <c r="F60" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G60" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H60" s="143"/>
+      <c r="H60" s="134"/>
     </row>
     <row r="61" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B61" s="51" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C61" s="52">
         <v>10</v>
       </c>
       <c r="D61" s="63" t="s">
-        <v>179</v>
-      </c>
-      <c r="E61" s="135"/>
+        <v>178</v>
+      </c>
+      <c r="E61" s="148"/>
       <c r="F61" s="53" t="s">
         <v>7</v>
       </c>
       <c r="G61" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H61" s="144"/>
+      <c r="H61" s="136"/>
     </row>
     <row r="62" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B62" s="36" t="s">
@@ -5333,17 +5313,17 @@
       <c r="D62" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E62" s="133">
+      <c r="E62" s="144">
         <v>143</v>
       </c>
       <c r="F62" s="31" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G62" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="H62" s="142" t="s">
-        <v>404</v>
+      <c r="H62" s="133" t="s">
+        <v>403</v>
       </c>
       <c r="I62" s="29"/>
       <c r="J62" s="29"/>
@@ -5352,7 +5332,7 @@
     </row>
     <row r="63" spans="2:12" ht="15.75" customHeight="1">
       <c r="B63" s="38" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C63" s="14">
         <v>60</v>
@@ -5360,14 +5340,14 @@
       <c r="D63" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E63" s="134"/>
+      <c r="E63" s="145"/>
       <c r="F63" s="15" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G63" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H63" s="143"/>
+      <c r="H63" s="134"/>
       <c r="I63" s="29"/>
       <c r="J63" s="29"/>
       <c r="K63" s="29"/>
@@ -5375,7 +5355,7 @@
     </row>
     <row r="64" spans="2:12" ht="15.75" customHeight="1">
       <c r="B64" s="38" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C64" s="14">
         <v>110</v>
@@ -5383,14 +5363,14 @@
       <c r="D64" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E64" s="134"/>
+      <c r="E64" s="145"/>
       <c r="F64" s="15" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G64" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H64" s="143"/>
+      <c r="H64" s="134"/>
       <c r="I64" s="29"/>
       <c r="J64" s="29"/>
       <c r="K64" s="29"/>
@@ -5398,7 +5378,7 @@
     </row>
     <row r="65" spans="2:12" ht="15.75" customHeight="1">
       <c r="B65" s="38" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C65" s="14">
         <v>35</v>
@@ -5406,14 +5386,14 @@
       <c r="D65" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E65" s="134"/>
+      <c r="E65" s="145"/>
       <c r="F65" s="15" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G65" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H65" s="143"/>
+      <c r="H65" s="134"/>
       <c r="I65" s="29"/>
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
@@ -5421,7 +5401,7 @@
     </row>
     <row r="66" spans="2:12" ht="15.75" customHeight="1">
       <c r="B66" s="38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C66" s="14">
         <v>95</v>
@@ -5429,14 +5409,14 @@
       <c r="D66" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E66" s="134"/>
+      <c r="E66" s="145"/>
       <c r="F66" s="15" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G66" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H66" s="143"/>
+      <c r="H66" s="134"/>
       <c r="I66" s="29"/>
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
@@ -5444,20 +5424,20 @@
     </row>
     <row r="67" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B67" s="51" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C67" s="17">
         <v>12</v>
       </c>
       <c r="D67" s="18"/>
-      <c r="E67" s="135"/>
+      <c r="E67" s="148"/>
       <c r="F67" s="19" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G67" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H67" s="144"/>
+      <c r="H67" s="136"/>
       <c r="I67" s="29"/>
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
@@ -5473,17 +5453,17 @@
       <c r="D68" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E68" s="133">
+      <c r="E68" s="144">
         <v>143</v>
       </c>
       <c r="F68" s="31" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G68" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="H68" s="142" t="s">
-        <v>404</v>
+      <c r="H68" s="133" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="69" spans="2:12" ht="15.75" customHeight="1">
@@ -5496,18 +5476,18 @@
       <c r="D69" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E69" s="134"/>
+      <c r="E69" s="145"/>
       <c r="F69" s="56" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G69" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="H69" s="143"/>
+      <c r="H69" s="134"/>
     </row>
     <row r="70" spans="2:12" ht="15.75" customHeight="1">
       <c r="B70" s="38" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C70" s="14">
         <v>110</v>
@@ -5515,18 +5495,18 @@
       <c r="D70" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E70" s="134"/>
+      <c r="E70" s="145"/>
       <c r="F70" s="15" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G70" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H70" s="143"/>
+      <c r="H70" s="134"/>
     </row>
     <row r="71" spans="2:12" ht="15.75" customHeight="1">
       <c r="B71" s="38" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C71" s="14">
         <v>35</v>
@@ -5534,18 +5514,18 @@
       <c r="D71" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E71" s="134"/>
+      <c r="E71" s="145"/>
       <c r="F71" s="56" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G71" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H71" s="143"/>
+      <c r="H71" s="134"/>
     </row>
     <row r="72" spans="2:12" ht="15.75" customHeight="1">
       <c r="B72" s="38" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C72" s="14">
         <v>95</v>
@@ -5553,18 +5533,18 @@
       <c r="D72" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E72" s="134"/>
+      <c r="E72" s="145"/>
       <c r="F72" s="15" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G72" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H72" s="143"/>
+      <c r="H72" s="134"/>
     </row>
     <row r="73" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B73" s="51" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C73" s="17">
         <v>12</v>
@@ -5572,14 +5552,14 @@
       <c r="D73" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E73" s="135"/>
+      <c r="E73" s="148"/>
       <c r="F73" s="57" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G73" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H73" s="144"/>
+      <c r="H73" s="136"/>
     </row>
     <row r="74" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B74" s="36" t="s">
@@ -5591,22 +5571,22 @@
       <c r="D74" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E74" s="133">
+      <c r="E74" s="144">
         <v>143</v>
       </c>
       <c r="F74" s="58" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G74" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="H74" s="142" t="s">
-        <v>404</v>
+      <c r="H74" s="133" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="75" spans="2:12" ht="15.75" customHeight="1">
       <c r="B75" s="38" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C75" s="49">
         <v>70</v>
@@ -5614,18 +5594,18 @@
       <c r="D75" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E75" s="134"/>
+      <c r="E75" s="145"/>
       <c r="F75" s="56" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G75" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="H75" s="143"/>
+      <c r="H75" s="134"/>
     </row>
     <row r="76" spans="2:12" ht="15.75" customHeight="1">
       <c r="B76" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C76" s="49">
         <v>110</v>
@@ -5633,18 +5613,18 @@
       <c r="D76" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E76" s="134"/>
+      <c r="E76" s="145"/>
       <c r="F76" s="56" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G76" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H76" s="143"/>
+      <c r="H76" s="134"/>
     </row>
     <row r="77" spans="2:12" ht="15.75" customHeight="1">
       <c r="B77" s="38" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C77" s="49">
         <v>35</v>
@@ -5652,18 +5632,18 @@
       <c r="D77" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E77" s="134"/>
+      <c r="E77" s="145"/>
       <c r="F77" s="56" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G77" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H77" s="143"/>
+      <c r="H77" s="134"/>
     </row>
     <row r="78" spans="2:12" ht="15.75" customHeight="1">
       <c r="B78" s="38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C78" s="49">
         <v>95</v>
@@ -5671,18 +5651,18 @@
       <c r="D78" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E78" s="134"/>
+      <c r="E78" s="145"/>
       <c r="F78" s="56" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G78" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H78" s="143"/>
+      <c r="H78" s="134"/>
     </row>
     <row r="79" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B79" s="51" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C79" s="52">
         <v>12</v>
@@ -5690,14 +5670,14 @@
       <c r="D79" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E79" s="135"/>
+      <c r="E79" s="148"/>
       <c r="F79" s="57" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G79" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H79" s="144"/>
+      <c r="H79" s="136"/>
     </row>
     <row r="80" spans="2:12" ht="38.65" thickTop="1">
       <c r="B80" s="40" t="s">
@@ -5709,17 +5689,17 @@
       <c r="D80" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E80" s="133">
+      <c r="E80" s="144">
         <v>112</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G80" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="H80" s="142" t="s">
-        <v>404</v>
+      <c r="H80" s="133" t="s">
+        <v>403</v>
       </c>
       <c r="I80" s="29"/>
       <c r="J80" s="29"/>
@@ -5728,7 +5708,7 @@
     </row>
     <row r="81" spans="2:12" ht="15.75" customHeight="1">
       <c r="B81" s="44" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C81" s="14">
         <v>60</v>
@@ -5736,14 +5716,14 @@
       <c r="D81" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E81" s="134"/>
+      <c r="E81" s="145"/>
       <c r="F81" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G81" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H81" s="143"/>
+      <c r="H81" s="134"/>
       <c r="I81" s="29"/>
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
@@ -5751,7 +5731,7 @@
     </row>
     <row r="82" spans="2:12" ht="15.75" customHeight="1">
       <c r="B82" s="44" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C82" s="14">
         <v>100</v>
@@ -5759,14 +5739,14 @@
       <c r="D82" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E82" s="134"/>
+      <c r="E82" s="145"/>
       <c r="F82" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G82" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H82" s="143"/>
+      <c r="H82" s="134"/>
       <c r="I82" s="29"/>
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
@@ -5782,14 +5762,14 @@
       <c r="D83" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E83" s="134"/>
+      <c r="E83" s="145"/>
       <c r="F83" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G83" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H83" s="143"/>
+      <c r="H83" s="134"/>
       <c r="I83" s="29"/>
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
@@ -5797,7 +5777,7 @@
     </row>
     <row r="84" spans="2:12" ht="15.75" customHeight="1">
       <c r="B84" s="44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C84" s="14">
         <v>90</v>
@@ -5805,14 +5785,14 @@
       <c r="D84" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E84" s="134"/>
+      <c r="E84" s="145"/>
       <c r="F84" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G84" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H84" s="143"/>
+      <c r="H84" s="134"/>
       <c r="I84" s="29"/>
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
@@ -5820,7 +5800,7 @@
     </row>
     <row r="85" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B85" s="60" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C85" s="24">
         <v>20</v>
@@ -5828,14 +5808,14 @@
       <c r="D85" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E85" s="136"/>
+      <c r="E85" s="146"/>
       <c r="F85" s="26" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G85" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H85" s="144"/>
+      <c r="H85" s="136"/>
       <c r="I85" s="29"/>
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
@@ -5851,7 +5831,7 @@
       <c r="D86" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E86" s="137">
+      <c r="E86" s="149">
         <v>125</v>
       </c>
       <c r="F86" s="11" t="s">
@@ -5860,8 +5840,8 @@
       <c r="G86" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H86" s="142" t="s">
-        <v>403</v>
+      <c r="H86" s="133" t="s">
+        <v>402</v>
       </c>
       <c r="I86" s="29"/>
       <c r="J86" s="29"/>
@@ -5878,14 +5858,14 @@
       <c r="D87" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E87" s="134"/>
+      <c r="E87" s="145"/>
       <c r="F87" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G87" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H87" s="143"/>
+      <c r="H87" s="134"/>
       <c r="I87" s="29"/>
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
@@ -5901,14 +5881,14 @@
       <c r="D88" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E88" s="134"/>
+      <c r="E88" s="145"/>
       <c r="F88" s="15" t="s">
         <v>62</v>
       </c>
       <c r="G88" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H88" s="143"/>
+      <c r="H88" s="134"/>
       <c r="I88" s="29"/>
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
@@ -5916,7 +5896,7 @@
     </row>
     <row r="89" spans="2:12" ht="15.75" customHeight="1">
       <c r="B89" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C89" s="14">
         <v>50</v>
@@ -5924,14 +5904,14 @@
       <c r="D89" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E89" s="134"/>
+      <c r="E89" s="145"/>
       <c r="F89" s="15" t="s">
         <v>63</v>
       </c>
       <c r="G89" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H89" s="143"/>
+      <c r="H89" s="134"/>
       <c r="I89" s="29"/>
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
@@ -5939,7 +5919,7 @@
     </row>
     <row r="90" spans="2:12" ht="15.75" customHeight="1">
       <c r="B90" s="13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C90" s="14">
         <v>120</v>
@@ -5947,14 +5927,14 @@
       <c r="D90" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E90" s="134"/>
+      <c r="E90" s="145"/>
       <c r="F90" s="15" t="s">
         <v>64</v>
       </c>
       <c r="G90" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H90" s="143"/>
+      <c r="H90" s="134"/>
       <c r="I90" s="29"/>
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
@@ -5962,7 +5942,7 @@
     </row>
     <row r="91" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B91" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C91" s="17">
         <v>30</v>
@@ -5970,14 +5950,14 @@
       <c r="D91" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E91" s="135"/>
+      <c r="E91" s="148"/>
       <c r="F91" s="19" t="s">
         <v>65</v>
       </c>
       <c r="G91" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H91" s="144"/>
+      <c r="H91" s="136"/>
       <c r="I91" s="29"/>
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
@@ -5985,30 +5965,30 @@
     </row>
     <row r="92" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B92" s="61" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C92" s="22">
         <v>440</v>
       </c>
       <c r="D92" s="62" t="s">
-        <v>320</v>
-      </c>
-      <c r="E92" s="133">
+        <v>319</v>
+      </c>
+      <c r="E92" s="144">
         <v>125</v>
       </c>
       <c r="F92" s="47" t="s">
         <v>66</v>
       </c>
       <c r="G92" s="48" t="s">
-        <v>323</v>
-      </c>
-      <c r="H92" s="145" t="s">
-        <v>408</v>
+        <v>322</v>
+      </c>
+      <c r="H92" s="140" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="93" spans="2:12" ht="15.75" customHeight="1">
       <c r="B93" s="44" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C93" s="14">
         <v>80</v>
@@ -6016,18 +5996,18 @@
       <c r="D93" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="E93" s="134"/>
+      <c r="E93" s="145"/>
       <c r="F93" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H93" s="146"/>
+      <c r="H93" s="138"/>
     </row>
     <row r="94" spans="2:12" ht="15.75" customHeight="1">
       <c r="B94" s="44" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C94" s="14">
         <v>140</v>
@@ -6035,18 +6015,18 @@
       <c r="D94" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="E94" s="134"/>
+      <c r="E94" s="145"/>
       <c r="F94" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G94" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H94" s="146"/>
+      <c r="H94" s="138"/>
     </row>
     <row r="95" spans="2:12" ht="15.75" customHeight="1">
       <c r="B95" s="44" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C95" s="14">
         <v>55</v>
@@ -6054,18 +6034,18 @@
       <c r="D95" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="E95" s="134"/>
+      <c r="E95" s="145"/>
       <c r="F95" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G95" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H95" s="146"/>
+      <c r="H95" s="138"/>
     </row>
     <row r="96" spans="2:12" ht="15.75" customHeight="1">
       <c r="B96" s="44" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C96" s="14">
         <v>130</v>
@@ -6073,18 +6053,18 @@
       <c r="D96" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="E96" s="134"/>
+      <c r="E96" s="145"/>
       <c r="F96" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G96" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H96" s="146"/>
+      <c r="H96" s="138"/>
     </row>
     <row r="97" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B97" s="64" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C97" s="17">
         <v>35</v>
@@ -6092,14 +6072,14 @@
       <c r="D97" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="E97" s="135"/>
+      <c r="E97" s="148"/>
       <c r="F97" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G97" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H97" s="147"/>
+      <c r="H97" s="139"/>
     </row>
     <row r="98" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B98" s="36" t="s">
@@ -6111,17 +6091,17 @@
       <c r="D98" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E98" s="133">
+      <c r="E98" s="144">
         <v>125</v>
       </c>
       <c r="F98" s="58" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G98" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="H98" s="142" t="s">
-        <v>404</v>
+      <c r="H98" s="133" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="99" spans="2:8" ht="15.75" customHeight="1">
@@ -6134,18 +6114,18 @@
       <c r="D99" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E99" s="134"/>
+      <c r="E99" s="145"/>
       <c r="F99" s="56" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G99" s="54" t="s">
-        <v>233</v>
-      </c>
-      <c r="H99" s="143"/>
+        <v>232</v>
+      </c>
+      <c r="H99" s="134"/>
     </row>
     <row r="100" spans="2:8" ht="15.75" customHeight="1">
       <c r="B100" s="38" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C100" s="14">
         <v>140</v>
@@ -6153,18 +6133,18 @@
       <c r="D100" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E100" s="134"/>
+      <c r="E100" s="145"/>
       <c r="F100" s="56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G100" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H100" s="143"/>
+      <c r="H100" s="134"/>
     </row>
     <row r="101" spans="2:8" ht="15.75" customHeight="1">
       <c r="B101" s="38" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C101" s="14">
         <v>55</v>
@@ -6172,18 +6152,18 @@
       <c r="D101" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E101" s="134"/>
+      <c r="E101" s="145"/>
       <c r="F101" s="56" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G101" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H101" s="143"/>
+      <c r="H101" s="134"/>
     </row>
     <row r="102" spans="2:8" ht="15.75" customHeight="1">
       <c r="B102" s="38" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C102" s="14">
         <v>130</v>
@@ -6191,18 +6171,18 @@
       <c r="D102" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E102" s="134"/>
+      <c r="E102" s="145"/>
       <c r="F102" s="56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G102" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H102" s="143"/>
+      <c r="H102" s="134"/>
     </row>
     <row r="103" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B103" s="51" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C103" s="17">
         <v>40</v>
@@ -6210,18 +6190,18 @@
       <c r="D103" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E103" s="135"/>
+      <c r="E103" s="148"/>
       <c r="F103" s="57" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G103" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="H103" s="144"/>
+      <c r="H103" s="136"/>
     </row>
     <row r="104" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B104" s="61" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C104" s="22">
         <v>450</v>
@@ -6229,7 +6209,7 @@
       <c r="D104" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E104" s="133">
+      <c r="E104" s="144">
         <v>125</v>
       </c>
       <c r="F104" s="31" t="s">
@@ -6238,8 +6218,8 @@
       <c r="G104" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="H104" s="142" t="s">
-        <v>404</v>
+      <c r="H104" s="133" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="105" spans="2:8" ht="15.75" customHeight="1">
@@ -6252,18 +6232,18 @@
       <c r="D105" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E105" s="134"/>
+      <c r="E105" s="145"/>
       <c r="F105" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G105" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H105" s="143"/>
+      <c r="H105" s="134"/>
     </row>
     <row r="106" spans="2:8" ht="15.75" customHeight="1">
       <c r="B106" s="44" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C106" s="14">
         <v>140</v>
@@ -6271,14 +6251,14 @@
       <c r="D106" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E106" s="134"/>
+      <c r="E106" s="145"/>
       <c r="F106" s="15" t="s">
         <v>62</v>
       </c>
       <c r="G106" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H106" s="143"/>
+      <c r="H106" s="134"/>
     </row>
     <row r="107" spans="2:8" ht="15.75" customHeight="1">
       <c r="B107" s="44" t="s">
@@ -6290,18 +6270,18 @@
       <c r="D107" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E107" s="134"/>
+      <c r="E107" s="145"/>
       <c r="F107" s="15" t="s">
         <v>75</v>
       </c>
       <c r="G107" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H107" s="143"/>
+      <c r="H107" s="134"/>
     </row>
     <row r="108" spans="2:8" ht="15.75" customHeight="1">
       <c r="B108" s="44" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C108" s="14">
         <v>130</v>
@@ -6309,18 +6289,18 @@
       <c r="D108" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E108" s="134"/>
+      <c r="E108" s="145"/>
       <c r="F108" s="15" t="s">
         <v>64</v>
       </c>
       <c r="G108" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H108" s="143"/>
+      <c r="H108" s="134"/>
     </row>
     <row r="109" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B109" s="66" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C109" s="33">
         <v>40</v>
@@ -6328,18 +6308,18 @@
       <c r="D109" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E109" s="136"/>
+      <c r="E109" s="146"/>
       <c r="F109" s="34" t="s">
         <v>65</v>
       </c>
       <c r="G109" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="H109" s="144"/>
+      <c r="H109" s="136"/>
     </row>
     <row r="110" spans="2:8" ht="25.5" customHeight="1" thickTop="1">
       <c r="B110" s="36" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C110" s="22">
         <v>450</v>
@@ -6347,22 +6327,22 @@
       <c r="D110" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E110" s="133">
+      <c r="E110" s="144">
         <v>125</v>
       </c>
       <c r="F110" s="72" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G110" s="37" t="s">
-        <v>358</v>
-      </c>
-      <c r="H110" s="142" t="s">
-        <v>404</v>
+        <v>357</v>
+      </c>
+      <c r="H110" s="133" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="111" spans="2:8" ht="15.75" customHeight="1">
       <c r="B111" s="38" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C111" s="14">
         <v>80</v>
@@ -6370,18 +6350,18 @@
       <c r="D111" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E111" s="134"/>
+      <c r="E111" s="145"/>
       <c r="F111" s="56" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G111" s="54" t="s">
-        <v>357</v>
-      </c>
-      <c r="H111" s="143"/>
+        <v>356</v>
+      </c>
+      <c r="H111" s="134"/>
     </row>
     <row r="112" spans="2:8" ht="15.75" customHeight="1">
       <c r="B112" s="38" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C112" s="14">
         <v>140</v>
@@ -6389,18 +6369,18 @@
       <c r="D112" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E112" s="134"/>
+      <c r="E112" s="145"/>
       <c r="F112" s="56" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G112" s="54" t="s">
-        <v>361</v>
-      </c>
-      <c r="H112" s="143"/>
+        <v>360</v>
+      </c>
+      <c r="H112" s="134"/>
     </row>
     <row r="113" spans="2:12" ht="15.75" customHeight="1">
       <c r="B113" s="38" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C113" s="14">
         <v>60</v>
@@ -6408,18 +6388,18 @@
       <c r="D113" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E113" s="134"/>
+      <c r="E113" s="145"/>
       <c r="F113" s="56" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G113" s="54" t="s">
-        <v>357</v>
-      </c>
-      <c r="H113" s="143"/>
+        <v>356</v>
+      </c>
+      <c r="H113" s="134"/>
     </row>
     <row r="114" spans="2:12" ht="15.75" customHeight="1">
       <c r="B114" s="38" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C114" s="14">
         <v>130</v>
@@ -6427,18 +6407,18 @@
       <c r="D114" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E114" s="134"/>
+      <c r="E114" s="145"/>
       <c r="F114" s="56" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G114" s="54" t="s">
-        <v>357</v>
-      </c>
-      <c r="H114" s="143"/>
+        <v>356</v>
+      </c>
+      <c r="H114" s="134"/>
     </row>
     <row r="115" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B115" s="51" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C115" s="17">
         <v>40</v>
@@ -6446,18 +6426,18 @@
       <c r="D115" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E115" s="135"/>
+      <c r="E115" s="148"/>
       <c r="F115" s="57" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G115" s="54" t="s">
-        <v>366</v>
-      </c>
-      <c r="H115" s="144"/>
+        <v>365</v>
+      </c>
+      <c r="H115" s="136"/>
     </row>
     <row r="116" spans="2:12" ht="25.9" thickTop="1">
       <c r="B116" s="68" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C116" s="22">
         <v>630</v>
@@ -6465,17 +6445,17 @@
       <c r="D116" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E116" s="133">
+      <c r="E116" s="144">
         <v>143</v>
       </c>
       <c r="F116" s="31" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G116" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="H116" s="142" t="s">
-        <v>415</v>
+      <c r="H116" s="133" t="s">
+        <v>414</v>
       </c>
       <c r="I116" s="29"/>
       <c r="J116" s="29"/>
@@ -6484,7 +6464,7 @@
     </row>
     <row r="117" spans="2:12" ht="15.75" customHeight="1">
       <c r="B117" s="70" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C117" s="14">
         <v>110</v>
@@ -6492,14 +6472,14 @@
       <c r="D117" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E117" s="134"/>
+      <c r="E117" s="145"/>
       <c r="F117" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G117" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H117" s="143"/>
+      <c r="H117" s="134"/>
       <c r="I117" s="29"/>
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
@@ -6507,7 +6487,7 @@
     </row>
     <row r="118" spans="2:12" ht="15.75" customHeight="1">
       <c r="B118" s="70" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C118" s="14">
         <v>190</v>
@@ -6515,14 +6495,14 @@
       <c r="D118" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E118" s="134"/>
+      <c r="E118" s="145"/>
       <c r="F118" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G118" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H118" s="143"/>
+      <c r="H118" s="134"/>
       <c r="I118" s="29"/>
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
@@ -6530,7 +6510,7 @@
     </row>
     <row r="119" spans="2:12" ht="15.75" customHeight="1">
       <c r="B119" s="70" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C119" s="14">
         <v>90</v>
@@ -6538,14 +6518,14 @@
       <c r="D119" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E119" s="134"/>
+      <c r="E119" s="145"/>
       <c r="F119" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G119" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H119" s="143"/>
+      <c r="H119" s="134"/>
       <c r="I119" s="29"/>
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
@@ -6553,7 +6533,7 @@
     </row>
     <row r="120" spans="2:12" ht="15.75" customHeight="1">
       <c r="B120" s="70" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C120" s="14">
         <v>180</v>
@@ -6561,14 +6541,14 @@
       <c r="D120" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E120" s="134"/>
+      <c r="E120" s="145"/>
       <c r="F120" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G120" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H120" s="143"/>
+      <c r="H120" s="134"/>
       <c r="I120" s="29"/>
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
@@ -6576,7 +6556,7 @@
     </row>
     <row r="121" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B121" s="71" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C121" s="24">
         <v>60</v>
@@ -6584,14 +6564,14 @@
       <c r="D121" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E121" s="136"/>
+      <c r="E121" s="146"/>
       <c r="F121" s="26" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G121" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="H121" s="144"/>
+      <c r="H121" s="136"/>
       <c r="I121" s="29"/>
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
@@ -6607,17 +6587,17 @@
       <c r="D122" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E122" s="133">
+      <c r="E122" s="144">
         <v>125</v>
       </c>
       <c r="F122" s="72" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G122" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="H122" s="142" t="s">
-        <v>404</v>
+      <c r="H122" s="133" t="s">
+        <v>403</v>
       </c>
       <c r="I122" s="29"/>
       <c r="J122" s="29"/>
@@ -6634,14 +6614,14 @@
       <c r="D123" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E123" s="134"/>
+      <c r="E123" s="145"/>
       <c r="F123" s="56" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G123" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H123" s="143"/>
+      <c r="H123" s="134"/>
       <c r="I123" s="29"/>
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
@@ -6657,14 +6637,14 @@
       <c r="D124" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E124" s="134"/>
+      <c r="E124" s="145"/>
       <c r="F124" s="56" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G124" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H124" s="143"/>
+      <c r="H124" s="134"/>
       <c r="I124" s="29"/>
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
@@ -6680,14 +6660,14 @@
       <c r="D125" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E125" s="134"/>
+      <c r="E125" s="145"/>
       <c r="F125" s="56" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G125" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H125" s="143"/>
+      <c r="H125" s="134"/>
       <c r="I125" s="29"/>
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
@@ -6695,7 +6675,7 @@
     </row>
     <row r="126" spans="2:12" ht="15.75" customHeight="1">
       <c r="B126" s="38" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C126" s="14">
         <v>190</v>
@@ -6703,14 +6683,14 @@
       <c r="D126" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E126" s="134"/>
+      <c r="E126" s="145"/>
       <c r="F126" s="56" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G126" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H126" s="143"/>
+      <c r="H126" s="134"/>
       <c r="I126" s="29"/>
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
@@ -6718,7 +6698,7 @@
     </row>
     <row r="127" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B127" s="39" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C127" s="24">
         <v>60</v>
@@ -6726,14 +6706,14 @@
       <c r="D127" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E127" s="136"/>
+      <c r="E127" s="146"/>
       <c r="F127" s="73" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G127" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="H127" s="144"/>
+      <c r="H127" s="136"/>
       <c r="I127" s="29"/>
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
@@ -6749,17 +6729,17 @@
       <c r="D128" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E128" s="133">
+      <c r="E128" s="144">
         <v>143</v>
       </c>
       <c r="F128" s="72" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G128" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="H128" s="142" t="s">
-        <v>404</v>
+      <c r="H128" s="133" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="129" spans="2:12" ht="15.75" customHeight="1">
@@ -6772,18 +6752,18 @@
       <c r="D129" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E129" s="134"/>
+      <c r="E129" s="145"/>
       <c r="F129" s="56" t="s">
-        <v>266</v>
-      </c>
-      <c r="G129" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="H129" s="143"/>
+        <v>265</v>
+      </c>
+      <c r="G129" s="77" t="s">
+        <v>118</v>
+      </c>
+      <c r="H129" s="134"/>
     </row>
     <row r="130" spans="2:12" ht="15.75" customHeight="1">
       <c r="B130" s="70" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C130" s="14">
         <v>190</v>
@@ -6791,18 +6771,18 @@
       <c r="D130" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E130" s="134"/>
+      <c r="E130" s="145"/>
       <c r="F130" s="56" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G130" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H130" s="143"/>
+      <c r="H130" s="134"/>
     </row>
     <row r="131" spans="2:12" ht="15.75" customHeight="1">
       <c r="B131" s="74" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C131" s="14">
         <v>90</v>
@@ -6810,18 +6790,18 @@
       <c r="D131" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E131" s="134"/>
+      <c r="E131" s="145"/>
       <c r="F131" s="56" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G131" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H131" s="143"/>
+      <c r="H131" s="134"/>
     </row>
     <row r="132" spans="2:12" ht="15.75" customHeight="1">
       <c r="B132" s="74" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C132" s="14">
         <v>180</v>
@@ -6829,18 +6809,18 @@
       <c r="D132" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E132" s="134"/>
+      <c r="E132" s="145"/>
       <c r="F132" s="56" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G132" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H132" s="143"/>
+      <c r="H132" s="134"/>
     </row>
     <row r="133" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B133" s="71" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C133" s="24">
         <v>60</v>
@@ -6848,18 +6828,18 @@
       <c r="D133" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E133" s="136"/>
+      <c r="E133" s="146"/>
       <c r="F133" s="73" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G133" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="H133" s="144"/>
+        <v>85</v>
+      </c>
+      <c r="H133" s="136"/>
     </row>
     <row r="134" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B134" s="75" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C134" s="76">
         <v>580</v>
@@ -6867,17 +6847,17 @@
       <c r="D134" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E134" s="138">
+      <c r="E134" s="147">
         <v>143</v>
       </c>
       <c r="F134" s="28" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G134" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H134" s="142" t="s">
-        <v>403</v>
+      <c r="H134" s="133" t="s">
+        <v>402</v>
       </c>
       <c r="I134" s="29"/>
       <c r="J134" s="29"/>
@@ -6886,7 +6866,7 @@
     </row>
     <row r="135" spans="2:12" ht="15.75" customHeight="1">
       <c r="B135" s="44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C135" s="14">
         <v>100</v>
@@ -6894,14 +6874,14 @@
       <c r="D135" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E135" s="134"/>
+      <c r="E135" s="145"/>
       <c r="F135" s="15" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G135" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H135" s="143"/>
+      <c r="H135" s="134"/>
       <c r="I135" s="29"/>
       <c r="J135" s="29"/>
       <c r="K135" s="29"/>
@@ -6909,7 +6889,7 @@
     </row>
     <row r="136" spans="2:12" ht="15.75" customHeight="1">
       <c r="B136" s="44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C136" s="14">
         <v>180</v>
@@ -6917,14 +6897,14 @@
       <c r="D136" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E136" s="134"/>
+      <c r="E136" s="145"/>
       <c r="F136" s="15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G136" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H136" s="143"/>
+      <c r="H136" s="134"/>
       <c r="I136" s="29"/>
       <c r="J136" s="29"/>
       <c r="K136" s="29"/>
@@ -6932,7 +6912,7 @@
     </row>
     <row r="137" spans="2:12" ht="15.75" customHeight="1">
       <c r="B137" s="44" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C137" s="14">
         <v>80</v>
@@ -6940,14 +6920,14 @@
       <c r="D137" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E137" s="134"/>
+      <c r="E137" s="145"/>
       <c r="F137" s="15" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G137" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H137" s="143"/>
+      <c r="H137" s="134"/>
       <c r="I137" s="29"/>
       <c r="J137" s="29"/>
       <c r="K137" s="29"/>
@@ -6955,7 +6935,7 @@
     </row>
     <row r="138" spans="2:12" ht="15.75" customHeight="1">
       <c r="B138" s="44" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C138" s="14">
         <v>170</v>
@@ -6963,14 +6943,14 @@
       <c r="D138" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E138" s="134"/>
+      <c r="E138" s="145"/>
       <c r="F138" s="15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G138" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H138" s="143"/>
+      <c r="H138" s="134"/>
       <c r="I138" s="29"/>
       <c r="J138" s="29"/>
       <c r="K138" s="29"/>
@@ -6978,7 +6958,7 @@
     </row>
     <row r="139" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B139" s="64" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C139" s="17">
         <v>50</v>
@@ -6986,14 +6966,14 @@
       <c r="D139" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E139" s="135"/>
+      <c r="E139" s="148"/>
       <c r="F139" s="19" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G139" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H139" s="144"/>
+      <c r="H139" s="136"/>
       <c r="I139" s="29"/>
       <c r="J139" s="29"/>
       <c r="K139" s="29"/>
@@ -7001,7 +6981,7 @@
     </row>
     <row r="140" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B140" s="61" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C140" s="22">
         <v>580</v>
@@ -7009,22 +6989,22 @@
       <c r="D140" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E140" s="133">
+      <c r="E140" s="144">
         <v>143</v>
       </c>
       <c r="F140" s="31" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G140" s="77" t="s">
-        <v>92</v>
-      </c>
-      <c r="H140" s="142" t="s">
-        <v>404</v>
+        <v>91</v>
+      </c>
+      <c r="H140" s="133" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="2:12" ht="15.75" customHeight="1">
       <c r="B141" s="44" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C141" s="14">
         <v>100</v>
@@ -7032,18 +7012,18 @@
       <c r="D141" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E141" s="134"/>
+      <c r="E141" s="145"/>
       <c r="F141" s="15" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G141" s="77" t="s">
-        <v>94</v>
-      </c>
-      <c r="H141" s="143"/>
+        <v>93</v>
+      </c>
+      <c r="H141" s="134"/>
     </row>
     <row r="142" spans="2:12" ht="15.75" customHeight="1">
       <c r="B142" s="44" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C142" s="14">
         <v>180</v>
@@ -7051,18 +7031,18 @@
       <c r="D142" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E142" s="134"/>
+      <c r="E142" s="145"/>
       <c r="F142" s="15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G142" s="78" t="s">
-        <v>95</v>
-      </c>
-      <c r="H142" s="143"/>
+        <v>94</v>
+      </c>
+      <c r="H142" s="134"/>
     </row>
     <row r="143" spans="2:12" ht="15.75" customHeight="1">
       <c r="B143" s="44" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C143" s="14">
         <v>80</v>
@@ -7070,18 +7050,18 @@
       <c r="D143" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E143" s="134"/>
+      <c r="E143" s="145"/>
       <c r="F143" s="15" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G143" s="77" t="s">
-        <v>94</v>
-      </c>
-      <c r="H143" s="143"/>
+        <v>93</v>
+      </c>
+      <c r="H143" s="134"/>
     </row>
     <row r="144" spans="2:12" ht="15.75" customHeight="1">
       <c r="B144" s="44" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C144" s="14">
         <v>170</v>
@@ -7089,18 +7069,18 @@
       <c r="D144" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E144" s="134"/>
+      <c r="E144" s="145"/>
       <c r="F144" s="15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G144" s="77" t="s">
-        <v>94</v>
-      </c>
-      <c r="H144" s="143"/>
+        <v>93</v>
+      </c>
+      <c r="H144" s="134"/>
     </row>
     <row r="145" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B145" s="64" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C145" s="17">
         <v>50</v>
@@ -7108,249 +7088,249 @@
       <c r="D145" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E145" s="135"/>
+      <c r="E145" s="148"/>
       <c r="F145" s="19" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G145" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="H145" s="144"/>
+        <v>96</v>
+      </c>
+      <c r="H145" s="136"/>
     </row>
     <row r="146" spans="1:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B146" s="112" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C146" s="22">
         <v>615</v>
       </c>
       <c r="D146" s="79" t="s">
-        <v>321</v>
-      </c>
-      <c r="E146" s="133">
+        <v>320</v>
+      </c>
+      <c r="E146" s="144">
         <v>143</v>
       </c>
       <c r="F146" s="47" t="s">
         <v>66</v>
       </c>
       <c r="G146" s="48" t="s">
-        <v>322</v>
-      </c>
-      <c r="H146" s="145" t="s">
-        <v>408</v>
+        <v>321</v>
+      </c>
+      <c r="H146" s="140" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="147" spans="1:12" ht="15.75" customHeight="1">
       <c r="B147" s="44" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C147" s="14">
         <v>105</v>
       </c>
       <c r="D147" s="80" t="s">
-        <v>98</v>
-      </c>
-      <c r="E147" s="134"/>
+        <v>97</v>
+      </c>
+      <c r="E147" s="145"/>
       <c r="F147" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G147" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H147" s="146"/>
+      <c r="H147" s="138"/>
     </row>
     <row r="148" spans="1:12" ht="15.75" customHeight="1">
       <c r="B148" s="44" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C148" s="14">
         <v>190</v>
       </c>
       <c r="D148" s="80" t="s">
-        <v>99</v>
-      </c>
-      <c r="E148" s="134"/>
+        <v>98</v>
+      </c>
+      <c r="E148" s="145"/>
       <c r="F148" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G148" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H148" s="146"/>
+      <c r="H148" s="138"/>
     </row>
     <row r="149" spans="1:12" ht="15.75" customHeight="1">
       <c r="B149" s="44" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C149" s="14">
         <v>85</v>
       </c>
       <c r="D149" s="80" t="s">
-        <v>98</v>
-      </c>
-      <c r="E149" s="134"/>
+        <v>97</v>
+      </c>
+      <c r="E149" s="145"/>
       <c r="F149" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G149" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H149" s="146"/>
+      <c r="H149" s="138"/>
     </row>
     <row r="150" spans="1:12" ht="15.75" customHeight="1">
       <c r="B150" s="44" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C150" s="14">
         <v>180</v>
       </c>
       <c r="D150" s="80" t="s">
-        <v>99</v>
-      </c>
-      <c r="E150" s="134"/>
+        <v>98</v>
+      </c>
+      <c r="E150" s="145"/>
       <c r="F150" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G150" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H150" s="146"/>
+      <c r="H150" s="138"/>
     </row>
     <row r="151" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B151" s="64" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C151" s="17">
         <v>55</v>
       </c>
       <c r="D151" s="81" t="s">
-        <v>98</v>
-      </c>
-      <c r="E151" s="135"/>
+        <v>97</v>
+      </c>
+      <c r="E151" s="148"/>
       <c r="F151" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G151" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H151" s="147"/>
+      <c r="H151" s="139"/>
     </row>
     <row r="152" spans="1:12" ht="13.5" thickTop="1">
       <c r="A152" s="111"/>
       <c r="B152" s="110" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C152" s="22">
         <v>615</v>
       </c>
       <c r="D152" s="109" t="s">
-        <v>379</v>
-      </c>
-      <c r="E152" s="133">
+        <v>378</v>
+      </c>
+      <c r="E152" s="144">
         <v>143</v>
       </c>
       <c r="F152" s="47" t="s">
         <v>66</v>
       </c>
       <c r="G152" s="114" t="s">
-        <v>375</v>
-      </c>
-      <c r="H152" s="145" t="s">
-        <v>408</v>
+        <v>374</v>
+      </c>
+      <c r="H152" s="140" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="153" spans="1:12" ht="15.75" customHeight="1">
       <c r="B153" s="113" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C153" s="14">
         <v>105</v>
       </c>
       <c r="D153" s="109" t="s">
-        <v>372</v>
-      </c>
-      <c r="E153" s="134"/>
+        <v>371</v>
+      </c>
+      <c r="E153" s="145"/>
       <c r="F153" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G153" s="12"/>
-      <c r="H153" s="146"/>
+      <c r="H153" s="138"/>
     </row>
     <row r="154" spans="1:12" ht="15.75" customHeight="1">
       <c r="B154" s="113" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C154" s="14">
         <v>190</v>
       </c>
       <c r="D154" s="109" t="s">
-        <v>374</v>
-      </c>
-      <c r="E154" s="134"/>
+        <v>373</v>
+      </c>
+      <c r="E154" s="145"/>
       <c r="F154" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G154" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H154" s="146"/>
+      <c r="H154" s="138"/>
     </row>
     <row r="155" spans="1:12" ht="15.75" customHeight="1">
       <c r="B155" s="113" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C155" s="14">
         <v>85</v>
       </c>
       <c r="D155" s="109" t="s">
-        <v>372</v>
-      </c>
-      <c r="E155" s="134"/>
+        <v>371</v>
+      </c>
+      <c r="E155" s="145"/>
       <c r="F155" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G155" s="12"/>
-      <c r="H155" s="146"/>
+      <c r="H155" s="138"/>
     </row>
     <row r="156" spans="1:12" ht="15.75" customHeight="1">
       <c r="B156" s="113" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C156" s="14">
         <v>180</v>
       </c>
       <c r="D156" s="109" t="s">
-        <v>374</v>
-      </c>
-      <c r="E156" s="134"/>
+        <v>373</v>
+      </c>
+      <c r="E156" s="145"/>
       <c r="F156" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G156" s="12"/>
-      <c r="H156" s="146"/>
+      <c r="H156" s="138"/>
     </row>
     <row r="157" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B157" s="116" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C157" s="17">
         <v>55</v>
       </c>
       <c r="D157" s="109" t="s">
-        <v>372</v>
-      </c>
-      <c r="E157" s="135"/>
+        <v>371</v>
+      </c>
+      <c r="E157" s="148"/>
       <c r="F157" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G157" s="115" t="s">
         <v>46</v>
       </c>
-      <c r="H157" s="147"/>
+      <c r="H157" s="139"/>
     </row>
     <row r="158" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B158" s="82" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C158" s="22">
         <v>580</v>
@@ -7358,17 +7338,17 @@
       <c r="D158" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E158" s="133">
+      <c r="E158" s="144">
         <v>167</v>
       </c>
       <c r="F158" s="31" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G158" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H158" s="142" t="s">
-        <v>404</v>
+      <c r="H158" s="133" t="s">
+        <v>403</v>
       </c>
       <c r="I158" s="29"/>
       <c r="J158" s="29"/>
@@ -7377,7 +7357,7 @@
     </row>
     <row r="159" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B159" s="84" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C159" s="14">
         <v>100</v>
@@ -7385,14 +7365,14 @@
       <c r="D159" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E159" s="134"/>
+      <c r="E159" s="145"/>
       <c r="F159" s="15" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G159" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H159" s="143"/>
+      <c r="H159" s="134"/>
       <c r="I159" s="29"/>
       <c r="J159" s="29"/>
       <c r="K159" s="29"/>
@@ -7400,7 +7380,7 @@
     </row>
     <row r="160" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B160" s="84" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C160" s="14">
         <v>180</v>
@@ -7408,14 +7388,14 @@
       <c r="D160" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E160" s="134"/>
+      <c r="E160" s="145"/>
       <c r="F160" s="15" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G160" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H160" s="143"/>
+      <c r="H160" s="134"/>
       <c r="I160" s="29"/>
       <c r="J160" s="29"/>
       <c r="K160" s="29"/>
@@ -7423,7 +7403,7 @@
     </row>
     <row r="161" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B161" s="84" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C161" s="14">
         <v>80</v>
@@ -7431,14 +7411,14 @@
       <c r="D161" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E161" s="134"/>
+      <c r="E161" s="145"/>
       <c r="F161" s="15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G161" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H161" s="143"/>
+      <c r="H161" s="134"/>
       <c r="I161" s="29"/>
       <c r="J161" s="29"/>
       <c r="K161" s="29"/>
@@ -7446,7 +7426,7 @@
     </row>
     <row r="162" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B162" s="84" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C162" s="14">
         <v>170</v>
@@ -7454,14 +7434,14 @@
       <c r="D162" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E162" s="134"/>
+      <c r="E162" s="145"/>
       <c r="F162" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G162" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H162" s="143"/>
+      <c r="H162" s="134"/>
       <c r="I162" s="29"/>
       <c r="J162" s="29"/>
       <c r="K162" s="29"/>
@@ -7469,7 +7449,7 @@
     </row>
     <row r="163" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B163" s="85" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C163" s="17">
         <v>50</v>
@@ -7477,14 +7457,14 @@
       <c r="D163" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E163" s="135"/>
+      <c r="E163" s="148"/>
       <c r="F163" s="19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G163" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="H163" s="144"/>
+      <c r="H163" s="136"/>
       <c r="I163" s="29"/>
       <c r="J163" s="29"/>
       <c r="K163" s="29"/>
@@ -7492,7 +7472,7 @@
     </row>
     <row r="164" spans="2:12" ht="26.25" thickTop="1" thickBot="1">
       <c r="B164" s="36" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C164" s="22">
         <v>580</v>
@@ -7500,22 +7480,22 @@
       <c r="D164" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E164" s="133">
+      <c r="E164" s="144">
         <v>125</v>
       </c>
       <c r="F164" s="58" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G164" s="37" t="s">
-        <v>101</v>
-      </c>
-      <c r="H164" s="142" t="s">
-        <v>404</v>
+        <v>100</v>
+      </c>
+      <c r="H164" s="133" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="165" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B165" s="38" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C165" s="14">
         <v>100</v>
@@ -7523,18 +7503,18 @@
       <c r="D165" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E165" s="134"/>
+      <c r="E165" s="145"/>
       <c r="F165" s="56" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G165" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H165" s="143"/>
+      <c r="H165" s="134"/>
     </row>
     <row r="166" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B166" s="38" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C166" s="14">
         <v>180</v>
@@ -7542,18 +7522,18 @@
       <c r="D166" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E166" s="134"/>
+      <c r="E166" s="145"/>
       <c r="F166" s="56" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G166" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H166" s="143"/>
+      <c r="H166" s="134"/>
     </row>
     <row r="167" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B167" s="38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C167" s="14">
         <v>80</v>
@@ -7561,18 +7541,18 @@
       <c r="D167" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E167" s="134"/>
+      <c r="E167" s="145"/>
       <c r="F167" s="56" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G167" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H167" s="143"/>
+      <c r="H167" s="134"/>
     </row>
     <row r="168" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B168" s="87" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C168" s="14">
         <v>170</v>
@@ -7580,18 +7560,18 @@
       <c r="D168" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E168" s="134"/>
+      <c r="E168" s="145"/>
       <c r="F168" s="56" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G168" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H168" s="143"/>
+      <c r="H168" s="134"/>
     </row>
     <row r="169" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B169" s="51" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C169" s="17">
         <v>50</v>
@@ -7599,18 +7579,18 @@
       <c r="D169" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E169" s="135"/>
+      <c r="E169" s="148"/>
       <c r="F169" s="57" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G169" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H169" s="144"/>
+      <c r="H169" s="136"/>
     </row>
     <row r="170" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B170" s="40" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C170" s="9">
         <v>580</v>
@@ -7618,7 +7598,7 @@
       <c r="D170" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E170" s="137">
+      <c r="E170" s="149">
         <v>200</v>
       </c>
       <c r="F170" s="50" t="s">
@@ -7627,8 +7607,8 @@
       <c r="G170" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H170" s="142" t="s">
-        <v>409</v>
+      <c r="H170" s="133" t="s">
+        <v>408</v>
       </c>
       <c r="I170" s="29"/>
       <c r="J170" s="29"/>
@@ -7637,7 +7617,7 @@
     </row>
     <row r="171" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B171" s="44" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C171" s="14">
         <v>100</v>
@@ -7645,14 +7625,14 @@
       <c r="D171" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E171" s="134"/>
+      <c r="E171" s="145"/>
       <c r="F171" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G171" s="55" t="s">
-        <v>104</v>
-      </c>
-      <c r="H171" s="143"/>
+        <v>103</v>
+      </c>
+      <c r="H171" s="134"/>
       <c r="I171" s="29"/>
       <c r="J171" s="29"/>
       <c r="K171" s="29"/>
@@ -7660,7 +7640,7 @@
     </row>
     <row r="172" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B172" s="44" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C172" s="14">
         <v>180</v>
@@ -7668,14 +7648,14 @@
       <c r="D172" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E172" s="134"/>
+      <c r="E172" s="145"/>
       <c r="F172" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G172" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="H172" s="143"/>
+        <v>104</v>
+      </c>
+      <c r="H172" s="134"/>
       <c r="I172" s="29"/>
       <c r="J172" s="29"/>
       <c r="K172" s="29"/>
@@ -7683,7 +7663,7 @@
     </row>
     <row r="173" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B173" s="44" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C173" s="14">
         <v>80</v>
@@ -7691,14 +7671,14 @@
       <c r="D173" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E173" s="134"/>
+      <c r="E173" s="145"/>
       <c r="F173" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G173" s="55" t="s">
-        <v>104</v>
-      </c>
-      <c r="H173" s="143"/>
+        <v>103</v>
+      </c>
+      <c r="H173" s="134"/>
       <c r="I173" s="29"/>
       <c r="J173" s="29"/>
       <c r="K173" s="29"/>
@@ -7706,7 +7686,7 @@
     </row>
     <row r="174" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B174" s="44" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C174" s="14">
         <v>170</v>
@@ -7714,14 +7694,14 @@
       <c r="D174" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E174" s="134"/>
+      <c r="E174" s="145"/>
       <c r="F174" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G174" s="55" t="s">
-        <v>104</v>
-      </c>
-      <c r="H174" s="143"/>
+        <v>103</v>
+      </c>
+      <c r="H174" s="134"/>
       <c r="I174" s="29"/>
       <c r="J174" s="29"/>
       <c r="K174" s="29"/>
@@ -7729,7 +7709,7 @@
     </row>
     <row r="175" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B175" s="60" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C175" s="24">
         <v>50</v>
@@ -7737,14 +7717,14 @@
       <c r="D175" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E175" s="136"/>
+      <c r="E175" s="146"/>
       <c r="F175" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G175" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="H175" s="144"/>
+        <v>105</v>
+      </c>
+      <c r="H175" s="136"/>
       <c r="I175" s="29"/>
       <c r="J175" s="29"/>
       <c r="K175" s="29"/>
@@ -7752,7 +7732,7 @@
     </row>
     <row r="176" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B176" s="36" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C176" s="22">
         <v>580</v>
@@ -7760,17 +7740,17 @@
       <c r="D176" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E176" s="133">
+      <c r="E176" s="144">
         <v>125</v>
       </c>
       <c r="F176" s="58" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G176" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="H176" s="142" t="s">
-        <v>404</v>
+        <v>107</v>
+      </c>
+      <c r="H176" s="133" t="s">
+        <v>403</v>
       </c>
       <c r="I176" s="29"/>
       <c r="J176" s="29"/>
@@ -7779,7 +7759,7 @@
     </row>
     <row r="177" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B177" s="38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C177" s="14">
         <v>100</v>
@@ -7787,14 +7767,14 @@
       <c r="D177" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E177" s="134"/>
+      <c r="E177" s="145"/>
       <c r="F177" s="56" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G177" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="H177" s="143"/>
+        <v>109</v>
+      </c>
+      <c r="H177" s="134"/>
       <c r="I177" s="29"/>
       <c r="J177" s="29"/>
       <c r="K177" s="29"/>
@@ -7802,7 +7782,7 @@
     </row>
     <row r="178" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B178" s="87" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C178" s="14">
         <v>180</v>
@@ -7810,14 +7790,14 @@
       <c r="D178" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E178" s="134"/>
+      <c r="E178" s="145"/>
       <c r="F178" s="56" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G178" s="78" t="s">
-        <v>112</v>
-      </c>
-      <c r="H178" s="143"/>
+        <v>111</v>
+      </c>
+      <c r="H178" s="134"/>
       <c r="I178" s="29"/>
       <c r="J178" s="29"/>
       <c r="K178" s="29"/>
@@ -7825,7 +7805,7 @@
     </row>
     <row r="179" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B179" s="38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C179" s="14">
         <v>80</v>
@@ -7833,14 +7813,14 @@
       <c r="D179" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E179" s="134"/>
+      <c r="E179" s="145"/>
       <c r="F179" s="56" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G179" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="H179" s="143"/>
+        <v>109</v>
+      </c>
+      <c r="H179" s="134"/>
       <c r="I179" s="29"/>
       <c r="J179" s="29"/>
       <c r="K179" s="29"/>
@@ -7848,7 +7828,7 @@
     </row>
     <row r="180" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B180" s="38" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C180" s="14">
         <v>170</v>
@@ -7856,14 +7836,14 @@
       <c r="D180" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E180" s="134"/>
+      <c r="E180" s="145"/>
       <c r="F180" s="56" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G180" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="H180" s="143"/>
+        <v>109</v>
+      </c>
+      <c r="H180" s="134"/>
       <c r="I180" s="29"/>
       <c r="J180" s="29"/>
       <c r="K180" s="29"/>
@@ -7871,7 +7851,7 @@
     </row>
     <row r="181" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B181" s="51" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C181" s="17">
         <v>50</v>
@@ -7879,14 +7859,14 @@
       <c r="D181" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E181" s="135"/>
+      <c r="E181" s="148"/>
       <c r="F181" s="88" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G181" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="H181" s="144"/>
+        <v>113</v>
+      </c>
+      <c r="H181" s="136"/>
       <c r="I181" s="29"/>
       <c r="J181" s="29"/>
       <c r="K181" s="29"/>
@@ -7894,7 +7874,7 @@
     </row>
     <row r="182" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B182" s="75" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C182" s="76">
         <v>1010</v>
@@ -7902,17 +7882,17 @@
       <c r="D182" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E182" s="138">
+      <c r="E182" s="147">
         <v>167</v>
       </c>
       <c r="F182" s="28" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G182" s="54" t="s">
-        <v>324</v>
-      </c>
-      <c r="H182" s="142" t="s">
-        <v>403</v>
+        <v>323</v>
+      </c>
+      <c r="H182" s="133" t="s">
+        <v>402</v>
       </c>
       <c r="I182" s="29"/>
       <c r="J182" s="29"/>
@@ -7921,7 +7901,7 @@
     </row>
     <row r="183" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B183" s="44" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C183" s="14">
         <v>140</v>
@@ -7929,14 +7909,14 @@
       <c r="D183" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E183" s="134"/>
+      <c r="E183" s="145"/>
       <c r="F183" s="15" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G183" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H183" s="143"/>
+      <c r="H183" s="134"/>
       <c r="I183" s="29"/>
       <c r="J183" s="29"/>
       <c r="K183" s="29"/>
@@ -7944,7 +7924,7 @@
     </row>
     <row r="184" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B184" s="42" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C184" s="14">
         <v>240</v>
@@ -7952,18 +7932,18 @@
       <c r="D184" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E184" s="134"/>
+      <c r="E184" s="145"/>
       <c r="F184" s="15" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G184" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H184" s="143"/>
+      <c r="H184" s="134"/>
     </row>
     <row r="185" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B185" s="42" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C185" s="14">
         <v>120</v>
@@ -7971,18 +7951,18 @@
       <c r="D185" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E185" s="134"/>
+      <c r="E185" s="145"/>
       <c r="F185" s="15" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G185" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H185" s="143"/>
+      <c r="H185" s="134"/>
     </row>
     <row r="186" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B186" s="44" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C186" s="14">
         <v>230</v>
@@ -7990,14 +7970,14 @@
       <c r="D186" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E186" s="134"/>
+      <c r="E186" s="145"/>
       <c r="F186" s="15" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G186" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H186" s="143"/>
+      <c r="H186" s="134"/>
       <c r="I186" s="29"/>
       <c r="J186" s="29"/>
       <c r="K186" s="29"/>
@@ -8005,7 +7985,7 @@
     </row>
     <row r="187" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B187" s="64" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C187" s="17">
         <v>80</v>
@@ -8013,14 +7993,14 @@
       <c r="D187" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E187" s="135"/>
+      <c r="E187" s="148"/>
       <c r="F187" s="19" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G187" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="H187" s="148"/>
+        <v>118</v>
+      </c>
+      <c r="H187" s="135"/>
       <c r="I187" s="29"/>
       <c r="J187" s="29"/>
       <c r="K187" s="29"/>
@@ -8028,7 +8008,7 @@
     </row>
     <row r="188" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B188" s="61" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C188" s="22">
         <v>1325</v>
@@ -8036,17 +8016,17 @@
       <c r="D188" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E188" s="133">
+      <c r="E188" s="144">
         <v>167</v>
       </c>
       <c r="F188" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G188" s="54" t="s">
-        <v>319</v>
-      </c>
-      <c r="H188" s="142" t="s">
-        <v>416</v>
+        <v>318</v>
+      </c>
+      <c r="H188" s="133" t="s">
+        <v>415</v>
       </c>
       <c r="I188" s="29"/>
       <c r="J188" s="29"/>
@@ -8055,7 +8035,7 @@
     </row>
     <row r="189" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B189" s="44" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C189" s="14">
         <v>160</v>
@@ -8063,14 +8043,14 @@
       <c r="D189" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E189" s="134"/>
+      <c r="E189" s="145"/>
       <c r="F189" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G189" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H189" s="143"/>
+      <c r="H189" s="134"/>
       <c r="I189" s="29"/>
       <c r="J189" s="29"/>
       <c r="K189" s="29"/>
@@ -8078,7 +8058,7 @@
     </row>
     <row r="190" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B190" s="44" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C190" s="14">
         <v>270</v>
@@ -8086,14 +8066,14 @@
       <c r="D190" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E190" s="134"/>
+      <c r="E190" s="145"/>
       <c r="F190" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G190" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H190" s="143"/>
+      <c r="H190" s="134"/>
       <c r="I190" s="29"/>
       <c r="J190" s="29"/>
       <c r="K190" s="29"/>
@@ -8101,7 +8081,7 @@
     </row>
     <row r="191" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B191" s="44" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C191" s="14">
         <v>140</v>
@@ -8109,14 +8089,14 @@
       <c r="D191" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E191" s="134"/>
+      <c r="E191" s="145"/>
       <c r="F191" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G191" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H191" s="143"/>
+      <c r="H191" s="134"/>
       <c r="I191" s="29"/>
       <c r="J191" s="29"/>
       <c r="K191" s="29"/>
@@ -8124,7 +8104,7 @@
     </row>
     <row r="192" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B192" s="44" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C192" s="14">
         <v>260</v>
@@ -8132,14 +8112,14 @@
       <c r="D192" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E192" s="134"/>
+      <c r="E192" s="145"/>
       <c r="F192" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G192" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H192" s="143"/>
+      <c r="H192" s="134"/>
       <c r="I192" s="29"/>
       <c r="J192" s="29"/>
       <c r="K192" s="29"/>
@@ -8147,7 +8127,7 @@
     </row>
     <row r="193" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B193" s="60" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C193" s="24">
         <v>95</v>
@@ -8155,14 +8135,14 @@
       <c r="D193" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E193" s="136"/>
+      <c r="E193" s="146"/>
       <c r="F193" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G193" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="H193" s="148"/>
+        <v>118</v>
+      </c>
+      <c r="H193" s="135"/>
       <c r="I193" s="29"/>
       <c r="J193" s="29"/>
       <c r="K193" s="29"/>
@@ -8170,7 +8150,7 @@
     </row>
     <row r="194" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B194" s="36" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C194" s="22">
         <v>810</v>
@@ -8178,22 +8158,22 @@
       <c r="D194" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E194" s="133">
+      <c r="E194" s="144">
         <v>143</v>
       </c>
       <c r="F194" s="72" t="s">
         <v>7</v>
       </c>
       <c r="G194" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="H194" s="142" t="s">
-        <v>404</v>
+        <v>122</v>
+      </c>
+      <c r="H194" s="133" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="195" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B195" s="38" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C195" s="14">
         <v>140</v>
@@ -8201,18 +8181,18 @@
       <c r="D195" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E195" s="134"/>
+      <c r="E195" s="145"/>
       <c r="F195" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G195" s="54" t="s">
-        <v>124</v>
-      </c>
-      <c r="H195" s="143"/>
+        <v>123</v>
+      </c>
+      <c r="H195" s="134"/>
     </row>
     <row r="196" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B196" s="38" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C196" s="14">
         <v>240</v>
@@ -8220,18 +8200,18 @@
       <c r="D196" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E196" s="134"/>
+      <c r="E196" s="145"/>
       <c r="F196" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G196" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H196" s="143"/>
+      <c r="H196" s="134"/>
     </row>
     <row r="197" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B197" s="38" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C197" s="14">
         <v>120</v>
@@ -8239,18 +8219,18 @@
       <c r="D197" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E197" s="134"/>
+      <c r="E197" s="145"/>
       <c r="F197" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G197" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H197" s="143"/>
+      <c r="H197" s="134"/>
     </row>
     <row r="198" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B198" s="38" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C198" s="14">
         <v>230</v>
@@ -8258,18 +8238,18 @@
       <c r="D198" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E198" s="134"/>
+      <c r="E198" s="145"/>
       <c r="F198" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G198" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H198" s="143"/>
+      <c r="H198" s="134"/>
     </row>
     <row r="199" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B199" s="39" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C199" s="24">
         <v>80</v>
@@ -8277,18 +8257,18 @@
       <c r="D199" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E199" s="136"/>
+      <c r="E199" s="146"/>
       <c r="F199" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G199" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="H199" s="144"/>
+        <v>118</v>
+      </c>
+      <c r="H199" s="136"/>
     </row>
     <row r="200" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B200" s="68" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C200" s="22">
         <v>1525</v>
@@ -8296,20 +8276,20 @@
       <c r="D200" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E200" s="133">
+      <c r="E200" s="144">
         <v>233</v>
       </c>
       <c r="F200" s="72"/>
       <c r="G200" s="48" t="s">
-        <v>332</v>
-      </c>
-      <c r="H200" s="149" t="s">
-        <v>406</v>
+        <v>331</v>
+      </c>
+      <c r="H200" s="137" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="201" spans="2:12" ht="15.75" customHeight="1">
       <c r="B201" s="74" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C201" s="14">
         <v>160</v>
@@ -8317,14 +8297,14 @@
       <c r="D201" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E201" s="134"/>
+      <c r="E201" s="145"/>
       <c r="F201" s="50"/>
       <c r="G201" s="12"/>
-      <c r="H201" s="146"/>
+      <c r="H201" s="138"/>
     </row>
     <row r="202" spans="2:12" ht="15.75" customHeight="1">
       <c r="B202" s="70" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C202" s="14">
         <v>270</v>
@@ -8332,16 +8312,16 @@
       <c r="D202" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E202" s="134"/>
+      <c r="E202" s="145"/>
       <c r="F202" s="50"/>
       <c r="G202" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H202" s="146"/>
+      <c r="H202" s="138"/>
     </row>
     <row r="203" spans="2:12" ht="15.75" customHeight="1">
       <c r="B203" s="70" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C203" s="14">
         <v>140</v>
@@ -8349,16 +8329,16 @@
       <c r="D203" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E203" s="134"/>
+      <c r="E203" s="145"/>
       <c r="F203" s="50"/>
       <c r="G203" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H203" s="146"/>
+      <c r="H203" s="138"/>
     </row>
     <row r="204" spans="2:12" ht="15.75" customHeight="1">
       <c r="B204" s="70" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C204" s="14">
         <v>260</v>
@@ -8366,16 +8346,16 @@
       <c r="D204" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E204" s="134"/>
+      <c r="E204" s="145"/>
       <c r="F204" s="50"/>
       <c r="G204" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H204" s="146"/>
+      <c r="H204" s="138"/>
     </row>
     <row r="205" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B205" s="71" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C205" s="24">
         <v>95</v>
@@ -8383,16 +8363,16 @@
       <c r="D205" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E205" s="136"/>
+      <c r="E205" s="146"/>
       <c r="F205" s="89"/>
       <c r="G205" s="90" t="s">
-        <v>119</v>
-      </c>
-      <c r="H205" s="147"/>
+        <v>118</v>
+      </c>
+      <c r="H205" s="139"/>
     </row>
     <row r="206" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B206" s="117" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C206" s="22">
         <v>1110</v>
@@ -8400,22 +8380,22 @@
       <c r="D206" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E206" s="133">
+      <c r="E206" s="144">
         <v>167</v>
       </c>
       <c r="F206" s="127" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G206" s="114" t="s">
-        <v>382</v>
-      </c>
-      <c r="H206" s="142" t="s">
-        <v>404</v>
+        <v>381</v>
+      </c>
+      <c r="H206" s="133" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="207" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B207" s="74" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C207" s="14">
         <v>200</v>
@@ -8423,18 +8403,18 @@
       <c r="D207" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E207" s="134"/>
+      <c r="E207" s="145"/>
       <c r="F207" s="127" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G207" s="119" t="s">
-        <v>384</v>
-      </c>
-      <c r="H207" s="143"/>
+        <v>383</v>
+      </c>
+      <c r="H207" s="134"/>
     </row>
     <row r="208" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B208" s="125" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C208" s="14">
         <v>300</v>
@@ -8442,18 +8422,18 @@
       <c r="D208" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E208" s="134"/>
+      <c r="E208" s="145"/>
       <c r="F208" s="127" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G208" s="120" t="s">
-        <v>383</v>
-      </c>
-      <c r="H208" s="143"/>
+        <v>382</v>
+      </c>
+      <c r="H208" s="134"/>
     </row>
     <row r="209" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B209" s="125" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C209" s="14">
         <v>180</v>
@@ -8461,18 +8441,18 @@
       <c r="D209" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E209" s="134"/>
+      <c r="E209" s="145"/>
       <c r="F209" s="127" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G209" s="119" t="s">
-        <v>384</v>
-      </c>
-      <c r="H209" s="143"/>
+        <v>383</v>
+      </c>
+      <c r="H209" s="134"/>
     </row>
     <row r="210" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B210" s="125" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C210" s="14">
         <v>290</v>
@@ -8480,18 +8460,18 @@
       <c r="D210" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E210" s="134"/>
+      <c r="E210" s="145"/>
       <c r="F210" s="127" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G210" s="122" t="s">
-        <v>384</v>
-      </c>
-      <c r="H210" s="143"/>
+        <v>383</v>
+      </c>
+      <c r="H210" s="134"/>
     </row>
     <row r="211" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B211" s="126" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C211" s="24">
         <v>140</v>
@@ -8499,18 +8479,18 @@
       <c r="D211" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E211" s="136"/>
+      <c r="E211" s="146"/>
       <c r="F211" s="127" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G211" s="121" t="s">
-        <v>384</v>
-      </c>
-      <c r="H211" s="144"/>
+        <v>383</v>
+      </c>
+      <c r="H211" s="136"/>
     </row>
     <row r="212" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B212" s="117" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C212" s="22">
         <v>1110</v>
@@ -8518,22 +8498,22 @@
       <c r="D212" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E212" s="139">
+      <c r="E212" s="141">
         <v>167</v>
       </c>
       <c r="F212" s="127" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G212" s="114" t="s">
-        <v>391</v>
-      </c>
-      <c r="H212" s="142" t="s">
-        <v>404</v>
+        <v>390</v>
+      </c>
+      <c r="H212" s="133" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="213" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B213" s="74" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C213" s="14">
         <v>200</v>
@@ -8541,18 +8521,18 @@
       <c r="D213" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E213" s="140"/>
+      <c r="E213" s="142"/>
       <c r="F213" s="127" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G213" s="118" t="s">
-        <v>393</v>
-      </c>
-      <c r="H213" s="143"/>
+        <v>392</v>
+      </c>
+      <c r="H213" s="134"/>
     </row>
     <row r="214" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B214" s="125" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C214" s="14">
         <v>300</v>
@@ -8560,18 +8540,18 @@
       <c r="D214" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E214" s="140"/>
+      <c r="E214" s="142"/>
       <c r="F214" s="127" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G214" s="118" t="s">
-        <v>395</v>
-      </c>
-      <c r="H214" s="143"/>
+        <v>394</v>
+      </c>
+      <c r="H214" s="134"/>
     </row>
     <row r="215" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B215" s="125" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C215" s="14">
         <v>180</v>
@@ -8579,18 +8559,18 @@
       <c r="D215" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E215" s="140"/>
+      <c r="E215" s="142"/>
       <c r="F215" s="127" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G215" s="118" t="s">
-        <v>393</v>
-      </c>
-      <c r="H215" s="143"/>
+        <v>392</v>
+      </c>
+      <c r="H215" s="134"/>
     </row>
     <row r="216" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B216" s="125" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C216" s="14">
         <v>290</v>
@@ -8598,18 +8578,18 @@
       <c r="D216" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E216" s="140"/>
+      <c r="E216" s="142"/>
       <c r="F216" s="127" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G216" s="118" t="s">
-        <v>393</v>
-      </c>
-      <c r="H216" s="143"/>
+        <v>392</v>
+      </c>
+      <c r="H216" s="134"/>
     </row>
     <row r="217" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B217" s="126" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C217" s="123">
         <v>140</v>
@@ -8617,18 +8597,18 @@
       <c r="D217" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="E217" s="141"/>
+      <c r="E217" s="143"/>
       <c r="F217" s="127" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G217" s="119" t="s">
-        <v>396</v>
-      </c>
-      <c r="H217" s="144"/>
+        <v>395</v>
+      </c>
+      <c r="H217" s="136"/>
     </row>
     <row r="218" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B218" s="91" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C218" s="92">
         <v>5</v>
@@ -8640,18 +8620,18 @@
         <v>100</v>
       </c>
       <c r="F218" s="94" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G218" s="59" t="s">
         <v>17</v>
       </c>
       <c r="H218" s="128" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="219" spans="2:8" ht="15.75" customHeight="1">
       <c r="B219" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C219" s="14">
         <v>12</v>
@@ -8669,12 +8649,12 @@
         <v>7</v>
       </c>
       <c r="H219" s="128" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="220" spans="2:8" ht="15.75" customHeight="1">
       <c r="B220" s="44" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C220" s="14">
         <v>30</v>
@@ -8692,12 +8672,12 @@
         <v>7</v>
       </c>
       <c r="H220" s="129" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="221" spans="2:8" ht="15.75" customHeight="1">
       <c r="B221" s="44" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C221" s="14">
         <v>35</v>
@@ -8709,18 +8689,18 @@
         <v>100</v>
       </c>
       <c r="F221" s="15" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G221" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H221" s="128" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="222" spans="2:8" ht="15.75" customHeight="1">
       <c r="B222" s="13" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C222" s="14">
         <v>58</v>
@@ -8732,18 +8712,18 @@
         <v>100</v>
       </c>
       <c r="F222" s="96" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G222" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H222" s="128" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="223" spans="2:8" ht="15.75" customHeight="1">
       <c r="B223" s="38" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C223" s="14">
         <v>60</v>
@@ -8758,15 +8738,15 @@
         <v>7</v>
       </c>
       <c r="G223" s="54" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H223" s="130" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="224" spans="2:8" ht="15.75" customHeight="1">
       <c r="B224" s="44" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C224" s="14">
         <v>70</v>
@@ -8784,12 +8764,12 @@
         <v>7</v>
       </c>
       <c r="H224" s="128" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="225" spans="2:8" ht="15.75" customHeight="1">
       <c r="B225" s="44" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C225" s="14">
         <v>70</v>
@@ -8807,12 +8787,12 @@
         <v>7</v>
       </c>
       <c r="H225" s="128" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="226" spans="2:8" ht="15.75" customHeight="1">
       <c r="B226" s="97" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C226" s="14">
         <v>100</v>
@@ -8830,12 +8810,12 @@
         <v>7</v>
       </c>
       <c r="H226" s="128" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="227" spans="2:8" ht="15.75" customHeight="1">
       <c r="B227" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C227" s="14">
         <v>115</v>
@@ -8847,18 +8827,18 @@
         <v>143</v>
       </c>
       <c r="F227" s="15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G227" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H227" s="128" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="228" spans="2:8" ht="15.75" customHeight="1">
       <c r="B228" s="87" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C228" s="14">
         <v>150</v>
@@ -8870,18 +8850,18 @@
         <v>125</v>
       </c>
       <c r="F228" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G228" s="54" t="s">
         <v>45</v>
       </c>
       <c r="H228" s="128" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="229" spans="2:8" ht="15.75" customHeight="1">
       <c r="B229" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C229" s="14">
         <v>160</v>
@@ -8893,18 +8873,18 @@
         <v>167</v>
       </c>
       <c r="F229" s="56" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G229" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H229" s="129" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="230" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B230" s="131" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C230" s="24">
         <v>200</v>
@@ -8919,10 +8899,10 @@
         <v>7</v>
       </c>
       <c r="G230" s="27" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H230" s="132" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="231" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
@@ -13789,30 +13769,38 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="72">
-    <mergeCell ref="H188:H193"/>
-    <mergeCell ref="H194:H199"/>
-    <mergeCell ref="H200:H205"/>
-    <mergeCell ref="H206:H211"/>
-    <mergeCell ref="H92:H97"/>
-    <mergeCell ref="H98:H103"/>
-    <mergeCell ref="H104:H109"/>
-    <mergeCell ref="H110:H115"/>
-    <mergeCell ref="H116:H121"/>
-    <mergeCell ref="H62:H67"/>
-    <mergeCell ref="H68:H73"/>
-    <mergeCell ref="H74:H79"/>
-    <mergeCell ref="H80:H85"/>
-    <mergeCell ref="H86:H91"/>
-    <mergeCell ref="H32:H37"/>
-    <mergeCell ref="H38:H43"/>
-    <mergeCell ref="H44:H49"/>
-    <mergeCell ref="H50:H55"/>
-    <mergeCell ref="H56:H61"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="H8:H13"/>
-    <mergeCell ref="H14:H19"/>
-    <mergeCell ref="H20:H25"/>
-    <mergeCell ref="H26:H31"/>
+    <mergeCell ref="E140:E145"/>
+    <mergeCell ref="E146:E151"/>
+    <mergeCell ref="E158:E163"/>
+    <mergeCell ref="E194:E199"/>
+    <mergeCell ref="E200:E205"/>
+    <mergeCell ref="E164:E169"/>
+    <mergeCell ref="E170:E175"/>
+    <mergeCell ref="E176:E181"/>
+    <mergeCell ref="E182:E187"/>
+    <mergeCell ref="E188:E193"/>
+    <mergeCell ref="E152:E157"/>
+    <mergeCell ref="E92:E97"/>
+    <mergeCell ref="E98:E103"/>
+    <mergeCell ref="E104:E109"/>
+    <mergeCell ref="E116:E121"/>
+    <mergeCell ref="E122:E127"/>
+    <mergeCell ref="E110:E115"/>
+    <mergeCell ref="E62:E67"/>
+    <mergeCell ref="E68:E73"/>
+    <mergeCell ref="E74:E79"/>
+    <mergeCell ref="E80:E85"/>
+    <mergeCell ref="E86:E91"/>
+    <mergeCell ref="E32:E37"/>
+    <mergeCell ref="E38:E43"/>
+    <mergeCell ref="E44:E49"/>
+    <mergeCell ref="E50:E55"/>
+    <mergeCell ref="E56:E61"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="E8:E13"/>
+    <mergeCell ref="E14:E19"/>
+    <mergeCell ref="E20:E25"/>
+    <mergeCell ref="E26:E31"/>
     <mergeCell ref="E212:E217"/>
     <mergeCell ref="E206:E211"/>
     <mergeCell ref="H122:H127"/>
@@ -13829,38 +13817,30 @@
     <mergeCell ref="E134:E139"/>
     <mergeCell ref="H212:H217"/>
     <mergeCell ref="H182:H187"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="E8:E13"/>
-    <mergeCell ref="E14:E19"/>
-    <mergeCell ref="E20:E25"/>
-    <mergeCell ref="E26:E31"/>
-    <mergeCell ref="E32:E37"/>
-    <mergeCell ref="E38:E43"/>
-    <mergeCell ref="E44:E49"/>
-    <mergeCell ref="E50:E55"/>
-    <mergeCell ref="E56:E61"/>
-    <mergeCell ref="E62:E67"/>
-    <mergeCell ref="E68:E73"/>
-    <mergeCell ref="E74:E79"/>
-    <mergeCell ref="E80:E85"/>
-    <mergeCell ref="E86:E91"/>
-    <mergeCell ref="E92:E97"/>
-    <mergeCell ref="E98:E103"/>
-    <mergeCell ref="E104:E109"/>
-    <mergeCell ref="E116:E121"/>
-    <mergeCell ref="E122:E127"/>
-    <mergeCell ref="E110:E115"/>
-    <mergeCell ref="E140:E145"/>
-    <mergeCell ref="E146:E151"/>
-    <mergeCell ref="E158:E163"/>
-    <mergeCell ref="E194:E199"/>
-    <mergeCell ref="E200:E205"/>
-    <mergeCell ref="E164:E169"/>
-    <mergeCell ref="E170:E175"/>
-    <mergeCell ref="E176:E181"/>
-    <mergeCell ref="E182:E187"/>
-    <mergeCell ref="E188:E193"/>
-    <mergeCell ref="E152:E157"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="H8:H13"/>
+    <mergeCell ref="H14:H19"/>
+    <mergeCell ref="H20:H25"/>
+    <mergeCell ref="H26:H31"/>
+    <mergeCell ref="H32:H37"/>
+    <mergeCell ref="H38:H43"/>
+    <mergeCell ref="H44:H49"/>
+    <mergeCell ref="H50:H55"/>
+    <mergeCell ref="H56:H61"/>
+    <mergeCell ref="H62:H67"/>
+    <mergeCell ref="H68:H73"/>
+    <mergeCell ref="H74:H79"/>
+    <mergeCell ref="H80:H85"/>
+    <mergeCell ref="H86:H91"/>
+    <mergeCell ref="H188:H193"/>
+    <mergeCell ref="H194:H199"/>
+    <mergeCell ref="H200:H205"/>
+    <mergeCell ref="H206:H211"/>
+    <mergeCell ref="H92:H97"/>
+    <mergeCell ref="H98:H103"/>
+    <mergeCell ref="H104:H109"/>
+    <mergeCell ref="H110:H115"/>
+    <mergeCell ref="H116:H121"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-source/护甲数据.xlsx
+++ b/data-source/护甲数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7473F8-0B25-4F76-900F-BC8450170062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2363F3-6393-4D77-A5FF-8A1EF0F4A2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2336,7 +2336,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2481,8 +2481,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2555,6 +2561,12 @@
         <bgColor rgb="FFEFEFEF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A86E8"/>
+        <bgColor rgb="FFFBBC04"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="55">
     <border>
@@ -3288,7 +3300,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3682,45 +3694,48 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3729,6 +3744,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF4A86E8"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -4049,7 +4069,7 @@
       <c r="D2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="149">
+      <c r="E2" s="137">
         <v>91</v>
       </c>
       <c r="F2" s="11" t="s">
@@ -4058,7 +4078,7 @@
       <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="133" t="s">
+      <c r="H2" s="142" t="s">
         <v>402</v>
       </c>
     </row>
@@ -4072,14 +4092,14 @@
       <c r="D3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="145"/>
+      <c r="E3" s="134"/>
       <c r="F3" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="134"/>
+      <c r="H3" s="143"/>
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1">
       <c r="B4" s="13" t="s">
@@ -4091,14 +4111,14 @@
       <c r="D4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="145"/>
+      <c r="E4" s="134"/>
       <c r="F4" s="15" t="s">
         <v>333</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="134"/>
+      <c r="H4" s="143"/>
     </row>
     <row r="5" spans="2:8" ht="15.75" customHeight="1">
       <c r="B5" s="13" t="s">
@@ -4110,14 +4130,14 @@
       <c r="D5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="145"/>
+      <c r="E5" s="134"/>
       <c r="F5" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="134"/>
+      <c r="H5" s="143"/>
     </row>
     <row r="6" spans="2:8" ht="15.75" customHeight="1">
       <c r="B6" s="13" t="s">
@@ -4129,14 +4149,14 @@
       <c r="D6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="145"/>
+      <c r="E6" s="134"/>
       <c r="F6" s="15" t="s">
         <v>333</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="134"/>
+      <c r="H6" s="143"/>
     </row>
     <row r="7" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B7" s="16" t="s">
@@ -4148,14 +4168,14 @@
       <c r="D7" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="148"/>
+      <c r="E7" s="135"/>
       <c r="F7" s="19" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="136"/>
+      <c r="H7" s="144"/>
     </row>
     <row r="8" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B8" s="21" t="s">
@@ -4167,7 +4187,7 @@
       <c r="D8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="144">
+      <c r="E8" s="133">
         <v>91</v>
       </c>
       <c r="F8" s="11" t="s">
@@ -4176,7 +4196,7 @@
       <c r="G8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="133" t="s">
+      <c r="H8" s="142" t="s">
         <v>403</v>
       </c>
     </row>
@@ -4190,14 +4210,14 @@
       <c r="D9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="145"/>
+      <c r="E9" s="134"/>
       <c r="F9" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="134"/>
+      <c r="H9" s="143"/>
     </row>
     <row r="10" spans="2:8" ht="15.75" customHeight="1">
       <c r="B10" s="13" t="s">
@@ -4209,14 +4229,14 @@
       <c r="D10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="145"/>
+      <c r="E10" s="134"/>
       <c r="F10" s="15" t="s">
         <v>333</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="134"/>
+      <c r="H10" s="143"/>
     </row>
     <row r="11" spans="2:8" ht="15.75" customHeight="1">
       <c r="B11" s="13" t="s">
@@ -4228,14 +4248,14 @@
       <c r="D11" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="145"/>
+      <c r="E11" s="134"/>
       <c r="F11" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="134"/>
+      <c r="H11" s="143"/>
     </row>
     <row r="12" spans="2:8" ht="15.75" customHeight="1">
       <c r="B12" s="13" t="s">
@@ -4247,14 +4267,14 @@
       <c r="D12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="145"/>
+      <c r="E12" s="134"/>
       <c r="F12" s="15" t="s">
         <v>333</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="134"/>
+      <c r="H12" s="143"/>
     </row>
     <row r="13" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B13" s="23" t="s">
@@ -4266,14 +4286,14 @@
       <c r="D13" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="146"/>
+      <c r="E13" s="136"/>
       <c r="F13" s="26" t="s">
         <v>9</v>
       </c>
       <c r="G13" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="136"/>
+      <c r="H13" s="144"/>
     </row>
     <row r="14" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B14" s="8" t="s">
@@ -4285,7 +4305,7 @@
       <c r="D14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="147">
+      <c r="E14" s="138">
         <v>100</v>
       </c>
       <c r="F14" s="28" t="s">
@@ -4294,7 +4314,7 @@
       <c r="G14" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="133" t="s">
+      <c r="H14" s="142" t="s">
         <v>402</v>
       </c>
     </row>
@@ -4308,14 +4328,14 @@
       <c r="D15" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="145"/>
+      <c r="E15" s="134"/>
       <c r="F15" s="15" t="s">
         <v>335</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H15" s="134"/>
+      <c r="H15" s="143"/>
     </row>
     <row r="16" spans="2:8" ht="15.75" customHeight="1">
       <c r="B16" s="13" t="s">
@@ -4327,14 +4347,14 @@
       <c r="D16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="145"/>
+      <c r="E16" s="134"/>
       <c r="F16" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="134"/>
+      <c r="H16" s="143"/>
     </row>
     <row r="17" spans="2:12" ht="15.75" customHeight="1">
       <c r="B17" s="13" t="s">
@@ -4346,14 +4366,14 @@
       <c r="D17" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="145"/>
+      <c r="E17" s="134"/>
       <c r="F17" s="15" t="s">
         <v>337</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H17" s="134"/>
+      <c r="H17" s="143"/>
       <c r="I17" s="29"/>
       <c r="J17" s="29"/>
       <c r="K17" s="29"/>
@@ -4369,14 +4389,14 @@
       <c r="D18" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="145"/>
+      <c r="E18" s="134"/>
       <c r="F18" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="134"/>
+      <c r="H18" s="143"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
       <c r="K18" s="29"/>
@@ -4392,14 +4412,14 @@
       <c r="D19" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="148"/>
+      <c r="E19" s="135"/>
       <c r="F19" s="19" t="s">
         <v>338</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="136"/>
+      <c r="H19" s="144"/>
       <c r="I19" s="29"/>
       <c r="J19" s="29"/>
       <c r="K19" s="29"/>
@@ -4415,7 +4435,7 @@
       <c r="D20" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="144">
+      <c r="E20" s="133">
         <v>100</v>
       </c>
       <c r="F20" s="11" t="s">
@@ -4424,7 +4444,7 @@
       <c r="G20" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="H20" s="133" t="s">
+      <c r="H20" s="142" t="s">
         <v>404</v>
       </c>
     </row>
@@ -4438,14 +4458,14 @@
       <c r="D21" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="145"/>
+      <c r="E21" s="134"/>
       <c r="F21" s="15" t="s">
         <v>335</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H21" s="134"/>
+      <c r="H21" s="143"/>
     </row>
     <row r="22" spans="2:12" ht="15.75" customHeight="1">
       <c r="B22" s="13" t="s">
@@ -4457,14 +4477,14 @@
       <c r="D22" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="145"/>
+      <c r="E22" s="134"/>
       <c r="F22" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H22" s="134"/>
+      <c r="H22" s="143"/>
     </row>
     <row r="23" spans="2:12" ht="15.75" customHeight="1">
       <c r="B23" s="13" t="s">
@@ -4476,14 +4496,14 @@
       <c r="D23" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="145"/>
+      <c r="E23" s="134"/>
       <c r="F23" s="15" t="s">
         <v>337</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H23" s="134"/>
+      <c r="H23" s="143"/>
     </row>
     <row r="24" spans="2:12" ht="15.75" customHeight="1">
       <c r="B24" s="13" t="s">
@@ -4495,14 +4515,14 @@
       <c r="D24" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="145"/>
+      <c r="E24" s="134"/>
       <c r="F24" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H24" s="134"/>
+      <c r="H24" s="143"/>
     </row>
     <row r="25" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B25" s="107" t="s">
@@ -4514,14 +4534,14 @@
       <c r="D25" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="148"/>
+      <c r="E25" s="135"/>
       <c r="F25" s="19" t="s">
         <v>338</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H25" s="136"/>
+      <c r="H25" s="144"/>
     </row>
     <row r="26" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B26" s="21" t="s">
@@ -4533,7 +4553,7 @@
       <c r="D26" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="144">
+      <c r="E26" s="133">
         <v>100</v>
       </c>
       <c r="F26" s="31" t="s">
@@ -4542,7 +4562,7 @@
       <c r="G26" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H26" s="133" t="s">
+      <c r="H26" s="142" t="s">
         <v>403</v>
       </c>
     </row>
@@ -4556,14 +4576,14 @@
       <c r="D27" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="145"/>
+      <c r="E27" s="134"/>
       <c r="F27" s="15" t="s">
         <v>335</v>
       </c>
       <c r="G27" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H27" s="134"/>
+      <c r="H27" s="143"/>
     </row>
     <row r="28" spans="2:12" ht="15.75" customHeight="1">
       <c r="B28" s="13" t="s">
@@ -4575,14 +4595,14 @@
       <c r="D28" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="145"/>
+      <c r="E28" s="134"/>
       <c r="F28" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H28" s="134"/>
+      <c r="H28" s="143"/>
     </row>
     <row r="29" spans="2:12" ht="15.75" customHeight="1">
       <c r="B29" s="13" t="s">
@@ -4594,14 +4614,14 @@
       <c r="D29" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="145"/>
+      <c r="E29" s="134"/>
       <c r="F29" s="15" t="s">
         <v>337</v>
       </c>
       <c r="G29" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H29" s="134"/>
+      <c r="H29" s="143"/>
     </row>
     <row r="30" spans="2:12" ht="15.75" customHeight="1">
       <c r="B30" s="13" t="s">
@@ -4613,14 +4633,14 @@
       <c r="D30" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="145"/>
+      <c r="E30" s="134"/>
       <c r="F30" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H30" s="134"/>
+      <c r="H30" s="143"/>
     </row>
     <row r="31" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B31" s="32" t="s">
@@ -4632,14 +4652,14 @@
       <c r="D31" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="146"/>
+      <c r="E31" s="136"/>
       <c r="F31" s="34" t="s">
         <v>338</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H31" s="136"/>
+      <c r="H31" s="144"/>
     </row>
     <row r="32" spans="2:12" ht="25.9" thickTop="1">
       <c r="B32" s="36" t="s">
@@ -4651,7 +4671,7 @@
       <c r="D32" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="144">
+      <c r="E32" s="133">
         <v>112</v>
       </c>
       <c r="F32" s="31" t="s">
@@ -4660,7 +4680,7 @@
       <c r="G32" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="H32" s="133" t="s">
+      <c r="H32" s="142" t="s">
         <v>403</v>
       </c>
       <c r="I32" s="29"/>
@@ -4678,14 +4698,14 @@
       <c r="D33" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="145"/>
+      <c r="E33" s="134"/>
       <c r="F33" s="15" t="s">
         <v>340</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H33" s="134"/>
+      <c r="H33" s="143"/>
       <c r="I33" s="29"/>
       <c r="J33" s="29"/>
       <c r="K33" s="29"/>
@@ -4701,14 +4721,14 @@
       <c r="D34" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="145"/>
+      <c r="E34" s="134"/>
       <c r="F34" s="15" t="s">
         <v>341</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="134"/>
+      <c r="H34" s="143"/>
       <c r="I34" s="29"/>
       <c r="J34" s="29"/>
       <c r="K34" s="29"/>
@@ -4724,14 +4744,14 @@
       <c r="D35" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="145"/>
+      <c r="E35" s="134"/>
       <c r="F35" s="15" t="s">
         <v>342</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H35" s="134"/>
+      <c r="H35" s="143"/>
       <c r="I35" s="29"/>
       <c r="J35" s="29"/>
       <c r="K35" s="29"/>
@@ -4747,14 +4767,14 @@
       <c r="D36" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="145"/>
+      <c r="E36" s="134"/>
       <c r="F36" s="15" t="s">
         <v>343</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H36" s="134"/>
+      <c r="H36" s="143"/>
       <c r="I36" s="29"/>
       <c r="J36" s="29"/>
       <c r="K36" s="29"/>
@@ -4770,14 +4790,14 @@
       <c r="D37" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E37" s="146"/>
+      <c r="E37" s="136"/>
       <c r="F37" s="26" t="s">
         <v>344</v>
       </c>
       <c r="G37" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="H37" s="136"/>
+      <c r="H37" s="144"/>
       <c r="I37" s="29"/>
       <c r="J37" s="29"/>
       <c r="K37" s="29"/>
@@ -4793,7 +4813,7 @@
       <c r="D38" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="144">
+      <c r="E38" s="133">
         <v>100</v>
       </c>
       <c r="F38" s="11" t="s">
@@ -4802,7 +4822,7 @@
       <c r="G38" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="H38" s="133" t="s">
+      <c r="H38" s="142" t="s">
         <v>403</v>
       </c>
       <c r="I38" s="29"/>
@@ -4820,14 +4840,14 @@
       <c r="D39" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E39" s="145"/>
+      <c r="E39" s="134"/>
       <c r="F39" s="15" t="s">
         <v>335</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H39" s="134"/>
+      <c r="H39" s="143"/>
       <c r="I39" s="29"/>
       <c r="J39" s="29"/>
       <c r="K39" s="29"/>
@@ -4843,14 +4863,14 @@
       <c r="D40" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E40" s="145"/>
+      <c r="E40" s="134"/>
       <c r="F40" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G40" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H40" s="134"/>
+      <c r="H40" s="143"/>
       <c r="I40" s="29"/>
       <c r="J40" s="29"/>
       <c r="K40" s="29"/>
@@ -4866,14 +4886,14 @@
       <c r="D41" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E41" s="145"/>
+      <c r="E41" s="134"/>
       <c r="F41" s="15" t="s">
         <v>337</v>
       </c>
       <c r="G41" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H41" s="134"/>
+      <c r="H41" s="143"/>
       <c r="I41" s="29"/>
       <c r="J41" s="29"/>
       <c r="K41" s="29"/>
@@ -4889,14 +4909,14 @@
       <c r="D42" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E42" s="145"/>
+      <c r="E42" s="134"/>
       <c r="F42" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G42" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="134"/>
+      <c r="H42" s="143"/>
       <c r="I42" s="29"/>
       <c r="J42" s="29"/>
       <c r="K42" s="29"/>
@@ -4912,14 +4932,14 @@
       <c r="D43" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E43" s="146"/>
+      <c r="E43" s="136"/>
       <c r="F43" s="26" t="s">
         <v>338</v>
       </c>
       <c r="G43" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="H43" s="136"/>
+      <c r="H43" s="144"/>
       <c r="I43" s="29"/>
       <c r="J43" s="29"/>
       <c r="K43" s="29"/>
@@ -4935,7 +4955,7 @@
       <c r="D44" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E44" s="149">
+      <c r="E44" s="137">
         <v>112</v>
       </c>
       <c r="F44" s="11" t="s">
@@ -4944,7 +4964,7 @@
       <c r="G44" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H44" s="133" t="s">
+      <c r="H44" s="142" t="s">
         <v>402</v>
       </c>
       <c r="I44" s="29"/>
@@ -4962,14 +4982,14 @@
       <c r="D45" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E45" s="145"/>
+      <c r="E45" s="134"/>
       <c r="F45" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G45" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H45" s="134"/>
+      <c r="H45" s="143"/>
       <c r="I45" s="29"/>
       <c r="J45" s="29"/>
       <c r="K45" s="29"/>
@@ -4985,14 +5005,14 @@
       <c r="D46" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E46" s="145"/>
+      <c r="E46" s="134"/>
       <c r="F46" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G46" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H46" s="134"/>
+      <c r="H46" s="143"/>
       <c r="I46" s="29"/>
       <c r="J46" s="29"/>
       <c r="K46" s="29"/>
@@ -5008,14 +5028,14 @@
       <c r="D47" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E47" s="145"/>
+      <c r="E47" s="134"/>
       <c r="F47" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G47" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H47" s="134"/>
+      <c r="H47" s="143"/>
       <c r="I47" s="29"/>
       <c r="J47" s="29"/>
       <c r="K47" s="29"/>
@@ -5031,14 +5051,14 @@
       <c r="D48" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E48" s="145"/>
+      <c r="E48" s="134"/>
       <c r="F48" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G48" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H48" s="134"/>
+      <c r="H48" s="143"/>
       <c r="I48" s="29"/>
       <c r="J48" s="29"/>
       <c r="K48" s="29"/>
@@ -5054,14 +5074,14 @@
       <c r="D49" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E49" s="148"/>
+      <c r="E49" s="135"/>
       <c r="F49" s="19" t="s">
         <v>346</v>
       </c>
       <c r="G49" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H49" s="136"/>
+      <c r="H49" s="144"/>
       <c r="I49" s="29"/>
       <c r="J49" s="29"/>
       <c r="K49" s="29"/>
@@ -5077,7 +5097,7 @@
       <c r="D50" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E50" s="144">
+      <c r="E50" s="133">
         <v>112</v>
       </c>
       <c r="F50" s="15" t="s">
@@ -5086,7 +5106,7 @@
       <c r="G50" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H50" s="133" t="s">
+      <c r="H50" s="142" t="s">
         <v>405</v>
       </c>
     </row>
@@ -5100,14 +5120,14 @@
       <c r="D51" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E51" s="145"/>
+      <c r="E51" s="134"/>
       <c r="F51" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G51" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H51" s="134"/>
+      <c r="H51" s="143"/>
     </row>
     <row r="52" spans="2:12" ht="15.75" customHeight="1">
       <c r="B52" s="13" t="s">
@@ -5119,14 +5139,14 @@
       <c r="D52" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E52" s="145"/>
+      <c r="E52" s="134"/>
       <c r="F52" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G52" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H52" s="134"/>
+      <c r="H52" s="143"/>
     </row>
     <row r="53" spans="2:12" ht="15.75" customHeight="1">
       <c r="B53" s="13" t="s">
@@ -5138,14 +5158,14 @@
       <c r="D53" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E53" s="145"/>
+      <c r="E53" s="134"/>
       <c r="F53" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G53" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H53" s="134"/>
+      <c r="H53" s="143"/>
     </row>
     <row r="54" spans="2:12" ht="15.75" customHeight="1">
       <c r="B54" s="13" t="s">
@@ -5157,14 +5177,14 @@
       <c r="D54" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E54" s="145"/>
+      <c r="E54" s="134"/>
       <c r="F54" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H54" s="134"/>
+      <c r="H54" s="143"/>
     </row>
     <row r="55" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B55" s="16" t="s">
@@ -5176,14 +5196,14 @@
       <c r="D55" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E55" s="148"/>
+      <c r="E55" s="135"/>
       <c r="F55" s="19" t="s">
         <v>346</v>
       </c>
       <c r="G55" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H55" s="136"/>
+      <c r="H55" s="144"/>
     </row>
     <row r="56" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B56" s="36" t="s">
@@ -5195,7 +5215,7 @@
       <c r="D56" s="63" t="s">
         <v>180</v>
       </c>
-      <c r="E56" s="144">
+      <c r="E56" s="133">
         <v>112</v>
       </c>
       <c r="F56" s="47" t="s">
@@ -5204,7 +5224,7 @@
       <c r="G56" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="H56" s="133" t="s">
+      <c r="H56" s="142" t="s">
         <v>406</v>
       </c>
     </row>
@@ -5218,14 +5238,14 @@
       <c r="D57" s="63" t="s">
         <v>178</v>
       </c>
-      <c r="E57" s="145"/>
+      <c r="E57" s="134"/>
       <c r="F57" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G57" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H57" s="134"/>
+      <c r="H57" s="143"/>
     </row>
     <row r="58" spans="2:12" ht="15.75" customHeight="1">
       <c r="B58" s="38" t="s">
@@ -5237,14 +5257,14 @@
       <c r="D58" s="63" t="s">
         <v>179</v>
       </c>
-      <c r="E58" s="145"/>
+      <c r="E58" s="134"/>
       <c r="F58" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G58" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H58" s="134"/>
+      <c r="H58" s="143"/>
     </row>
     <row r="59" spans="2:12" ht="15.75" customHeight="1">
       <c r="B59" s="38" t="s">
@@ -5256,14 +5276,14 @@
       <c r="D59" s="63" t="s">
         <v>178</v>
       </c>
-      <c r="E59" s="145"/>
+      <c r="E59" s="134"/>
       <c r="F59" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G59" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H59" s="134"/>
+      <c r="H59" s="143"/>
     </row>
     <row r="60" spans="2:12" ht="15.75" customHeight="1">
       <c r="B60" s="38" t="s">
@@ -5275,14 +5295,14 @@
       <c r="D60" s="63" t="s">
         <v>179</v>
       </c>
-      <c r="E60" s="145"/>
+      <c r="E60" s="134"/>
       <c r="F60" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G60" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H60" s="134"/>
+      <c r="H60" s="143"/>
     </row>
     <row r="61" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B61" s="51" t="s">
@@ -5294,14 +5314,14 @@
       <c r="D61" s="63" t="s">
         <v>178</v>
       </c>
-      <c r="E61" s="148"/>
+      <c r="E61" s="135"/>
       <c r="F61" s="53" t="s">
         <v>7</v>
       </c>
       <c r="G61" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H61" s="136"/>
+      <c r="H61" s="144"/>
     </row>
     <row r="62" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B62" s="36" t="s">
@@ -5313,7 +5333,7 @@
       <c r="D62" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E62" s="144">
+      <c r="E62" s="133">
         <v>143</v>
       </c>
       <c r="F62" s="31" t="s">
@@ -5322,7 +5342,7 @@
       <c r="G62" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="H62" s="133" t="s">
+      <c r="H62" s="142" t="s">
         <v>403</v>
       </c>
       <c r="I62" s="29"/>
@@ -5340,14 +5360,14 @@
       <c r="D63" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E63" s="145"/>
+      <c r="E63" s="134"/>
       <c r="F63" s="15" t="s">
         <v>419</v>
       </c>
       <c r="G63" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H63" s="134"/>
+      <c r="H63" s="143"/>
       <c r="I63" s="29"/>
       <c r="J63" s="29"/>
       <c r="K63" s="29"/>
@@ -5363,14 +5383,14 @@
       <c r="D64" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E64" s="145"/>
+      <c r="E64" s="134"/>
       <c r="F64" s="15" t="s">
         <v>420</v>
       </c>
       <c r="G64" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H64" s="134"/>
+      <c r="H64" s="143"/>
       <c r="I64" s="29"/>
       <c r="J64" s="29"/>
       <c r="K64" s="29"/>
@@ -5386,14 +5406,14 @@
       <c r="D65" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E65" s="145"/>
+      <c r="E65" s="134"/>
       <c r="F65" s="15" t="s">
         <v>421</v>
       </c>
       <c r="G65" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H65" s="134"/>
+      <c r="H65" s="143"/>
       <c r="I65" s="29"/>
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
@@ -5409,14 +5429,14 @@
       <c r="D66" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E66" s="145"/>
+      <c r="E66" s="134"/>
       <c r="F66" s="15" t="s">
         <v>422</v>
       </c>
       <c r="G66" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H66" s="134"/>
+      <c r="H66" s="143"/>
       <c r="I66" s="29"/>
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
@@ -5430,14 +5450,14 @@
         <v>12</v>
       </c>
       <c r="D67" s="18"/>
-      <c r="E67" s="148"/>
+      <c r="E67" s="135"/>
       <c r="F67" s="19" t="s">
         <v>423</v>
       </c>
       <c r="G67" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H67" s="136"/>
+      <c r="H67" s="144"/>
       <c r="I67" s="29"/>
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
@@ -5453,7 +5473,7 @@
       <c r="D68" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E68" s="144">
+      <c r="E68" s="133">
         <v>143</v>
       </c>
       <c r="F68" s="31" t="s">
@@ -5462,7 +5482,7 @@
       <c r="G68" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="H68" s="133" t="s">
+      <c r="H68" s="142" t="s">
         <v>403</v>
       </c>
     </row>
@@ -5476,14 +5496,14 @@
       <c r="D69" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E69" s="145"/>
+      <c r="E69" s="134"/>
       <c r="F69" s="56" t="s">
         <v>199</v>
       </c>
       <c r="G69" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="H69" s="134"/>
+      <c r="H69" s="143"/>
     </row>
     <row r="70" spans="2:12" ht="15.75" customHeight="1">
       <c r="B70" s="38" t="s">
@@ -5495,14 +5515,14 @@
       <c r="D70" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E70" s="145"/>
+      <c r="E70" s="134"/>
       <c r="F70" s="15" t="s">
         <v>200</v>
       </c>
       <c r="G70" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H70" s="134"/>
+      <c r="H70" s="143"/>
     </row>
     <row r="71" spans="2:12" ht="15.75" customHeight="1">
       <c r="B71" s="38" t="s">
@@ -5514,14 +5534,14 @@
       <c r="D71" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E71" s="145"/>
+      <c r="E71" s="134"/>
       <c r="F71" s="56" t="s">
         <v>425</v>
       </c>
       <c r="G71" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H71" s="134"/>
+      <c r="H71" s="143"/>
     </row>
     <row r="72" spans="2:12" ht="15.75" customHeight="1">
       <c r="B72" s="38" t="s">
@@ -5533,14 +5553,14 @@
       <c r="D72" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E72" s="145"/>
+      <c r="E72" s="134"/>
       <c r="F72" s="15" t="s">
         <v>201</v>
       </c>
       <c r="G72" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H72" s="134"/>
+      <c r="H72" s="143"/>
     </row>
     <row r="73" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B73" s="51" t="s">
@@ -5552,14 +5572,14 @@
       <c r="D73" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E73" s="148"/>
+      <c r="E73" s="135"/>
       <c r="F73" s="57" t="s">
         <v>202</v>
       </c>
       <c r="G73" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H73" s="136"/>
+      <c r="H73" s="144"/>
     </row>
     <row r="74" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B74" s="36" t="s">
@@ -5571,7 +5591,7 @@
       <c r="D74" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E74" s="144">
+      <c r="E74" s="133">
         <v>143</v>
       </c>
       <c r="F74" s="58" t="s">
@@ -5580,7 +5600,7 @@
       <c r="G74" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="H74" s="133" t="s">
+      <c r="H74" s="142" t="s">
         <v>403</v>
       </c>
     </row>
@@ -5594,14 +5614,14 @@
       <c r="D75" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E75" s="145"/>
+      <c r="E75" s="134"/>
       <c r="F75" s="56" t="s">
         <v>190</v>
       </c>
       <c r="G75" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="H75" s="134"/>
+      <c r="H75" s="143"/>
     </row>
     <row r="76" spans="2:12" ht="15.75" customHeight="1">
       <c r="B76" s="38" t="s">
@@ -5613,14 +5633,14 @@
       <c r="D76" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E76" s="145"/>
+      <c r="E76" s="134"/>
       <c r="F76" s="56" t="s">
         <v>191</v>
       </c>
       <c r="G76" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H76" s="134"/>
+      <c r="H76" s="143"/>
     </row>
     <row r="77" spans="2:12" ht="15.75" customHeight="1">
       <c r="B77" s="38" t="s">
@@ -5632,14 +5652,14 @@
       <c r="D77" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E77" s="145"/>
+      <c r="E77" s="134"/>
       <c r="F77" s="56" t="s">
         <v>427</v>
       </c>
       <c r="G77" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H77" s="134"/>
+      <c r="H77" s="143"/>
     </row>
     <row r="78" spans="2:12" ht="15.75" customHeight="1">
       <c r="B78" s="38" t="s">
@@ -5651,14 +5671,14 @@
       <c r="D78" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E78" s="145"/>
+      <c r="E78" s="134"/>
       <c r="F78" s="56" t="s">
         <v>192</v>
       </c>
       <c r="G78" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H78" s="134"/>
+      <c r="H78" s="143"/>
     </row>
     <row r="79" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B79" s="51" t="s">
@@ -5670,14 +5690,14 @@
       <c r="D79" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E79" s="148"/>
+      <c r="E79" s="135"/>
       <c r="F79" s="57" t="s">
         <v>190</v>
       </c>
       <c r="G79" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H79" s="136"/>
+      <c r="H79" s="144"/>
     </row>
     <row r="80" spans="2:12" ht="38.65" thickTop="1">
       <c r="B80" s="40" t="s">
@@ -5689,7 +5709,7 @@
       <c r="D80" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E80" s="144">
+      <c r="E80" s="133">
         <v>112</v>
       </c>
       <c r="F80" s="11" t="s">
@@ -5698,7 +5718,7 @@
       <c r="G80" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="H80" s="133" t="s">
+      <c r="H80" s="142" t="s">
         <v>403</v>
       </c>
       <c r="I80" s="29"/>
@@ -5716,14 +5736,14 @@
       <c r="D81" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E81" s="145"/>
+      <c r="E81" s="134"/>
       <c r="F81" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G81" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H81" s="134"/>
+      <c r="H81" s="143"/>
       <c r="I81" s="29"/>
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
@@ -5739,14 +5759,14 @@
       <c r="D82" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E82" s="145"/>
+      <c r="E82" s="134"/>
       <c r="F82" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G82" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H82" s="134"/>
+      <c r="H82" s="143"/>
       <c r="I82" s="29"/>
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
@@ -5762,14 +5782,14 @@
       <c r="D83" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E83" s="145"/>
+      <c r="E83" s="134"/>
       <c r="F83" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G83" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H83" s="134"/>
+      <c r="H83" s="143"/>
       <c r="I83" s="29"/>
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
@@ -5785,14 +5805,14 @@
       <c r="D84" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E84" s="145"/>
+      <c r="E84" s="134"/>
       <c r="F84" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G84" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H84" s="134"/>
+      <c r="H84" s="143"/>
       <c r="I84" s="29"/>
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
@@ -5808,14 +5828,14 @@
       <c r="D85" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E85" s="146"/>
+      <c r="E85" s="136"/>
       <c r="F85" s="26" t="s">
         <v>347</v>
       </c>
       <c r="G85" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H85" s="136"/>
+      <c r="H85" s="144"/>
       <c r="I85" s="29"/>
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
@@ -5831,7 +5851,7 @@
       <c r="D86" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E86" s="149">
+      <c r="E86" s="137">
         <v>125</v>
       </c>
       <c r="F86" s="11" t="s">
@@ -5840,7 +5860,7 @@
       <c r="G86" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H86" s="133" t="s">
+      <c r="H86" s="142" t="s">
         <v>402</v>
       </c>
       <c r="I86" s="29"/>
@@ -5858,14 +5878,14 @@
       <c r="D87" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E87" s="145"/>
+      <c r="E87" s="134"/>
       <c r="F87" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G87" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H87" s="134"/>
+      <c r="H87" s="143"/>
       <c r="I87" s="29"/>
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
@@ -5881,14 +5901,14 @@
       <c r="D88" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E88" s="145"/>
+      <c r="E88" s="134"/>
       <c r="F88" s="15" t="s">
         <v>62</v>
       </c>
       <c r="G88" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H88" s="134"/>
+      <c r="H88" s="143"/>
       <c r="I88" s="29"/>
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
@@ -5904,14 +5924,14 @@
       <c r="D89" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E89" s="145"/>
+      <c r="E89" s="134"/>
       <c r="F89" s="15" t="s">
         <v>63</v>
       </c>
       <c r="G89" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H89" s="134"/>
+      <c r="H89" s="143"/>
       <c r="I89" s="29"/>
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
@@ -5927,14 +5947,14 @@
       <c r="D90" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E90" s="145"/>
+      <c r="E90" s="134"/>
       <c r="F90" s="15" t="s">
         <v>64</v>
       </c>
       <c r="G90" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H90" s="134"/>
+      <c r="H90" s="143"/>
       <c r="I90" s="29"/>
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
@@ -5950,14 +5970,14 @@
       <c r="D91" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E91" s="148"/>
+      <c r="E91" s="135"/>
       <c r="F91" s="19" t="s">
         <v>65</v>
       </c>
       <c r="G91" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H91" s="136"/>
+      <c r="H91" s="144"/>
       <c r="I91" s="29"/>
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
@@ -5973,7 +5993,7 @@
       <c r="D92" s="62" t="s">
         <v>319</v>
       </c>
-      <c r="E92" s="144">
+      <c r="E92" s="133">
         <v>125</v>
       </c>
       <c r="F92" s="47" t="s">
@@ -5982,7 +6002,7 @@
       <c r="G92" s="48" t="s">
         <v>322</v>
       </c>
-      <c r="H92" s="140" t="s">
+      <c r="H92" s="145" t="s">
         <v>407</v>
       </c>
     </row>
@@ -5996,14 +6016,14 @@
       <c r="D93" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="E93" s="145"/>
+      <c r="E93" s="134"/>
       <c r="F93" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H93" s="138"/>
+      <c r="H93" s="146"/>
     </row>
     <row r="94" spans="2:12" ht="15.75" customHeight="1">
       <c r="B94" s="44" t="s">
@@ -6015,14 +6035,14 @@
       <c r="D94" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="E94" s="145"/>
+      <c r="E94" s="134"/>
       <c r="F94" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G94" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H94" s="138"/>
+      <c r="H94" s="146"/>
     </row>
     <row r="95" spans="2:12" ht="15.75" customHeight="1">
       <c r="B95" s="44" t="s">
@@ -6034,14 +6054,14 @@
       <c r="D95" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="E95" s="145"/>
+      <c r="E95" s="134"/>
       <c r="F95" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G95" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H95" s="138"/>
+      <c r="H95" s="146"/>
     </row>
     <row r="96" spans="2:12" ht="15.75" customHeight="1">
       <c r="B96" s="44" t="s">
@@ -6053,14 +6073,14 @@
       <c r="D96" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="E96" s="145"/>
+      <c r="E96" s="134"/>
       <c r="F96" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G96" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H96" s="138"/>
+      <c r="H96" s="146"/>
     </row>
     <row r="97" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B97" s="64" t="s">
@@ -6072,14 +6092,14 @@
       <c r="D97" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="E97" s="148"/>
+      <c r="E97" s="135"/>
       <c r="F97" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G97" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H97" s="139"/>
+      <c r="H97" s="147"/>
     </row>
     <row r="98" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B98" s="36" t="s">
@@ -6091,7 +6111,7 @@
       <c r="D98" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E98" s="144">
+      <c r="E98" s="133">
         <v>125</v>
       </c>
       <c r="F98" s="58" t="s">
@@ -6100,7 +6120,7 @@
       <c r="G98" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="H98" s="133" t="s">
+      <c r="H98" s="142" t="s">
         <v>403</v>
       </c>
     </row>
@@ -6114,14 +6134,14 @@
       <c r="D99" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E99" s="145"/>
+      <c r="E99" s="134"/>
       <c r="F99" s="56" t="s">
         <v>238</v>
       </c>
       <c r="G99" s="54" t="s">
         <v>232</v>
       </c>
-      <c r="H99" s="134"/>
+      <c r="H99" s="143"/>
     </row>
     <row r="100" spans="2:8" ht="15.75" customHeight="1">
       <c r="B100" s="38" t="s">
@@ -6133,14 +6153,14 @@
       <c r="D100" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E100" s="145"/>
+      <c r="E100" s="134"/>
       <c r="F100" s="56" t="s">
         <v>239</v>
       </c>
       <c r="G100" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H100" s="134"/>
+      <c r="H100" s="143"/>
     </row>
     <row r="101" spans="2:8" ht="15.75" customHeight="1">
       <c r="B101" s="38" t="s">
@@ -6152,14 +6172,14 @@
       <c r="D101" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E101" s="145"/>
+      <c r="E101" s="134"/>
       <c r="F101" s="56" t="s">
         <v>240</v>
       </c>
       <c r="G101" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H101" s="134"/>
+      <c r="H101" s="143"/>
     </row>
     <row r="102" spans="2:8" ht="15.75" customHeight="1">
       <c r="B102" s="38" t="s">
@@ -6171,14 +6191,14 @@
       <c r="D102" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E102" s="145"/>
+      <c r="E102" s="134"/>
       <c r="F102" s="56" t="s">
         <v>241</v>
       </c>
       <c r="G102" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H102" s="134"/>
+      <c r="H102" s="143"/>
     </row>
     <row r="103" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B103" s="51" t="s">
@@ -6190,14 +6210,14 @@
       <c r="D103" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E103" s="148"/>
+      <c r="E103" s="135"/>
       <c r="F103" s="57" t="s">
         <v>242</v>
       </c>
       <c r="G103" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="H103" s="136"/>
+      <c r="H103" s="144"/>
     </row>
     <row r="104" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B104" s="61" t="s">
@@ -6209,7 +6229,7 @@
       <c r="D104" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E104" s="144">
+      <c r="E104" s="133">
         <v>125</v>
       </c>
       <c r="F104" s="31" t="s">
@@ -6218,7 +6238,7 @@
       <c r="G104" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="H104" s="133" t="s">
+      <c r="H104" s="142" t="s">
         <v>403</v>
       </c>
     </row>
@@ -6232,14 +6252,14 @@
       <c r="D105" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E105" s="145"/>
+      <c r="E105" s="134"/>
       <c r="F105" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G105" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H105" s="134"/>
+      <c r="H105" s="143"/>
     </row>
     <row r="106" spans="2:8" ht="15.75" customHeight="1">
       <c r="B106" s="44" t="s">
@@ -6251,14 +6271,14 @@
       <c r="D106" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E106" s="145"/>
+      <c r="E106" s="134"/>
       <c r="F106" s="15" t="s">
         <v>62</v>
       </c>
       <c r="G106" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H106" s="134"/>
+      <c r="H106" s="143"/>
     </row>
     <row r="107" spans="2:8" ht="15.75" customHeight="1">
       <c r="B107" s="44" t="s">
@@ -6270,14 +6290,14 @@
       <c r="D107" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E107" s="145"/>
+      <c r="E107" s="134"/>
       <c r="F107" s="15" t="s">
         <v>75</v>
       </c>
       <c r="G107" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H107" s="134"/>
+      <c r="H107" s="143"/>
     </row>
     <row r="108" spans="2:8" ht="15.75" customHeight="1">
       <c r="B108" s="44" t="s">
@@ -6289,14 +6309,14 @@
       <c r="D108" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E108" s="145"/>
+      <c r="E108" s="134"/>
       <c r="F108" s="15" t="s">
         <v>64</v>
       </c>
       <c r="G108" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H108" s="134"/>
+      <c r="H108" s="143"/>
     </row>
     <row r="109" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B109" s="66" t="s">
@@ -6308,14 +6328,14 @@
       <c r="D109" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E109" s="146"/>
+      <c r="E109" s="136"/>
       <c r="F109" s="34" t="s">
         <v>65</v>
       </c>
       <c r="G109" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="H109" s="136"/>
+      <c r="H109" s="144"/>
     </row>
     <row r="110" spans="2:8" ht="25.5" customHeight="1" thickTop="1">
       <c r="B110" s="36" t="s">
@@ -6327,7 +6347,7 @@
       <c r="D110" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E110" s="144">
+      <c r="E110" s="133">
         <v>125</v>
       </c>
       <c r="F110" s="72" t="s">
@@ -6336,7 +6356,7 @@
       <c r="G110" s="37" t="s">
         <v>357</v>
       </c>
-      <c r="H110" s="133" t="s">
+      <c r="H110" s="142" t="s">
         <v>403</v>
       </c>
     </row>
@@ -6350,14 +6370,14 @@
       <c r="D111" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E111" s="145"/>
+      <c r="E111" s="134"/>
       <c r="F111" s="56" t="s">
         <v>359</v>
       </c>
       <c r="G111" s="54" t="s">
         <v>356</v>
       </c>
-      <c r="H111" s="134"/>
+      <c r="H111" s="143"/>
     </row>
     <row r="112" spans="2:8" ht="15.75" customHeight="1">
       <c r="B112" s="38" t="s">
@@ -6369,14 +6389,14 @@
       <c r="D112" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E112" s="145"/>
+      <c r="E112" s="134"/>
       <c r="F112" s="56" t="s">
         <v>355</v>
       </c>
       <c r="G112" s="54" t="s">
         <v>360</v>
       </c>
-      <c r="H112" s="134"/>
+      <c r="H112" s="143"/>
     </row>
     <row r="113" spans="2:12" ht="15.75" customHeight="1">
       <c r="B113" s="38" t="s">
@@ -6388,14 +6408,14 @@
       <c r="D113" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E113" s="145"/>
+      <c r="E113" s="134"/>
       <c r="F113" s="56" t="s">
         <v>362</v>
       </c>
       <c r="G113" s="54" t="s">
         <v>356</v>
       </c>
-      <c r="H113" s="134"/>
+      <c r="H113" s="143"/>
     </row>
     <row r="114" spans="2:12" ht="15.75" customHeight="1">
       <c r="B114" s="38" t="s">
@@ -6407,14 +6427,14 @@
       <c r="D114" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E114" s="145"/>
+      <c r="E114" s="134"/>
       <c r="F114" s="56" t="s">
         <v>428</v>
       </c>
       <c r="G114" s="54" t="s">
         <v>356</v>
       </c>
-      <c r="H114" s="134"/>
+      <c r="H114" s="143"/>
     </row>
     <row r="115" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B115" s="51" t="s">
@@ -6426,14 +6446,14 @@
       <c r="D115" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E115" s="148"/>
+      <c r="E115" s="135"/>
       <c r="F115" s="57" t="s">
         <v>366</v>
       </c>
       <c r="G115" s="54" t="s">
         <v>365</v>
       </c>
-      <c r="H115" s="136"/>
+      <c r="H115" s="144"/>
     </row>
     <row r="116" spans="2:12" ht="25.9" thickTop="1">
       <c r="B116" s="68" t="s">
@@ -6445,7 +6465,7 @@
       <c r="D116" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E116" s="144">
+      <c r="E116" s="133">
         <v>143</v>
       </c>
       <c r="F116" s="31" t="s">
@@ -6454,7 +6474,7 @@
       <c r="G116" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="H116" s="133" t="s">
+      <c r="H116" s="142" t="s">
         <v>414</v>
       </c>
       <c r="I116" s="29"/>
@@ -6472,14 +6492,14 @@
       <c r="D117" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E117" s="145"/>
+      <c r="E117" s="134"/>
       <c r="F117" s="15" t="s">
         <v>250</v>
       </c>
       <c r="G117" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H117" s="134"/>
+      <c r="H117" s="143"/>
       <c r="I117" s="29"/>
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
@@ -6495,14 +6515,14 @@
       <c r="D118" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E118" s="145"/>
+      <c r="E118" s="134"/>
       <c r="F118" s="15" t="s">
         <v>251</v>
       </c>
       <c r="G118" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H118" s="134"/>
+      <c r="H118" s="143"/>
       <c r="I118" s="29"/>
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
@@ -6518,14 +6538,14 @@
       <c r="D119" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E119" s="145"/>
+      <c r="E119" s="134"/>
       <c r="F119" s="15" t="s">
         <v>252</v>
       </c>
       <c r="G119" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H119" s="134"/>
+      <c r="H119" s="143"/>
       <c r="I119" s="29"/>
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
@@ -6541,14 +6561,14 @@
       <c r="D120" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E120" s="145"/>
+      <c r="E120" s="134"/>
       <c r="F120" s="15" t="s">
         <v>253</v>
       </c>
       <c r="G120" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H120" s="134"/>
+      <c r="H120" s="143"/>
       <c r="I120" s="29"/>
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
@@ -6564,14 +6584,14 @@
       <c r="D121" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E121" s="146"/>
+      <c r="E121" s="136"/>
       <c r="F121" s="26" t="s">
         <v>254</v>
       </c>
       <c r="G121" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="H121" s="136"/>
+      <c r="H121" s="144"/>
       <c r="I121" s="29"/>
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
@@ -6587,7 +6607,7 @@
       <c r="D122" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E122" s="144">
+      <c r="E122" s="133">
         <v>125</v>
       </c>
       <c r="F122" s="72" t="s">
@@ -6596,7 +6616,7 @@
       <c r="G122" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="H122" s="133" t="s">
+      <c r="H122" s="142" t="s">
         <v>403</v>
       </c>
       <c r="I122" s="29"/>
@@ -6614,14 +6634,14 @@
       <c r="D123" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E123" s="145"/>
+      <c r="E123" s="134"/>
       <c r="F123" s="56" t="s">
         <v>256</v>
       </c>
       <c r="G123" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H123" s="134"/>
+      <c r="H123" s="143"/>
       <c r="I123" s="29"/>
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
@@ -6637,14 +6657,14 @@
       <c r="D124" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E124" s="145"/>
+      <c r="E124" s="134"/>
       <c r="F124" s="56" t="s">
         <v>257</v>
       </c>
       <c r="G124" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H124" s="134"/>
+      <c r="H124" s="143"/>
       <c r="I124" s="29"/>
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
@@ -6660,14 +6680,14 @@
       <c r="D125" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E125" s="145"/>
+      <c r="E125" s="134"/>
       <c r="F125" s="56" t="s">
         <v>258</v>
       </c>
       <c r="G125" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H125" s="134"/>
+      <c r="H125" s="143"/>
       <c r="I125" s="29"/>
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
@@ -6683,14 +6703,14 @@
       <c r="D126" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E126" s="145"/>
+      <c r="E126" s="134"/>
       <c r="F126" s="56" t="s">
         <v>259</v>
       </c>
       <c r="G126" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H126" s="134"/>
+      <c r="H126" s="143"/>
       <c r="I126" s="29"/>
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
@@ -6706,14 +6726,14 @@
       <c r="D127" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E127" s="146"/>
+      <c r="E127" s="136"/>
       <c r="F127" s="73" t="s">
         <v>260</v>
       </c>
       <c r="G127" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="H127" s="136"/>
+      <c r="H127" s="144"/>
       <c r="I127" s="29"/>
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
@@ -6729,7 +6749,7 @@
       <c r="D128" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E128" s="144">
+      <c r="E128" s="133">
         <v>143</v>
       </c>
       <c r="F128" s="72" t="s">
@@ -6738,7 +6758,7 @@
       <c r="G128" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="H128" s="133" t="s">
+      <c r="H128" s="142" t="s">
         <v>403</v>
       </c>
     </row>
@@ -6752,14 +6772,14 @@
       <c r="D129" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E129" s="145"/>
+      <c r="E129" s="134"/>
       <c r="F129" s="56" t="s">
         <v>265</v>
       </c>
       <c r="G129" s="77" t="s">
         <v>118</v>
       </c>
-      <c r="H129" s="134"/>
+      <c r="H129" s="143"/>
     </row>
     <row r="130" spans="2:12" ht="15.75" customHeight="1">
       <c r="B130" s="70" t="s">
@@ -6771,14 +6791,14 @@
       <c r="D130" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E130" s="145"/>
+      <c r="E130" s="134"/>
       <c r="F130" s="56" t="s">
         <v>266</v>
       </c>
       <c r="G130" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H130" s="134"/>
+      <c r="H130" s="143"/>
     </row>
     <row r="131" spans="2:12" ht="15.75" customHeight="1">
       <c r="B131" s="74" t="s">
@@ -6790,14 +6810,14 @@
       <c r="D131" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E131" s="145"/>
+      <c r="E131" s="134"/>
       <c r="F131" s="56" t="s">
         <v>267</v>
       </c>
       <c r="G131" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H131" s="134"/>
+      <c r="H131" s="143"/>
     </row>
     <row r="132" spans="2:12" ht="15.75" customHeight="1">
       <c r="B132" s="74" t="s">
@@ -6809,14 +6829,14 @@
       <c r="D132" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E132" s="145"/>
+      <c r="E132" s="134"/>
       <c r="F132" s="56" t="s">
         <v>268</v>
       </c>
       <c r="G132" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H132" s="134"/>
+      <c r="H132" s="143"/>
     </row>
     <row r="133" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B133" s="71" t="s">
@@ -6828,14 +6848,14 @@
       <c r="D133" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E133" s="146"/>
+      <c r="E133" s="136"/>
       <c r="F133" s="73" t="s">
         <v>269</v>
       </c>
       <c r="G133" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="H133" s="136"/>
+      <c r="H133" s="144"/>
     </row>
     <row r="134" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B134" s="75" t="s">
@@ -6847,7 +6867,7 @@
       <c r="D134" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E134" s="147">
+      <c r="E134" s="138">
         <v>143</v>
       </c>
       <c r="F134" s="28" t="s">
@@ -6856,7 +6876,7 @@
       <c r="G134" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H134" s="133" t="s">
+      <c r="H134" s="142" t="s">
         <v>402</v>
       </c>
       <c r="I134" s="29"/>
@@ -6874,14 +6894,14 @@
       <c r="D135" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E135" s="145"/>
+      <c r="E135" s="134"/>
       <c r="F135" s="15" t="s">
         <v>271</v>
       </c>
       <c r="G135" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H135" s="134"/>
+      <c r="H135" s="143"/>
       <c r="I135" s="29"/>
       <c r="J135" s="29"/>
       <c r="K135" s="29"/>
@@ -6897,14 +6917,14 @@
       <c r="D136" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E136" s="145"/>
+      <c r="E136" s="134"/>
       <c r="F136" s="15" t="s">
         <v>272</v>
       </c>
       <c r="G136" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H136" s="134"/>
+      <c r="H136" s="143"/>
       <c r="I136" s="29"/>
       <c r="J136" s="29"/>
       <c r="K136" s="29"/>
@@ -6920,14 +6940,14 @@
       <c r="D137" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E137" s="145"/>
+      <c r="E137" s="134"/>
       <c r="F137" s="15" t="s">
         <v>273</v>
       </c>
       <c r="G137" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H137" s="134"/>
+      <c r="H137" s="143"/>
       <c r="I137" s="29"/>
       <c r="J137" s="29"/>
       <c r="K137" s="29"/>
@@ -6943,14 +6963,14 @@
       <c r="D138" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E138" s="145"/>
+      <c r="E138" s="134"/>
       <c r="F138" s="15" t="s">
         <v>274</v>
       </c>
       <c r="G138" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H138" s="134"/>
+      <c r="H138" s="143"/>
       <c r="I138" s="29"/>
       <c r="J138" s="29"/>
       <c r="K138" s="29"/>
@@ -6966,14 +6986,14 @@
       <c r="D139" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E139" s="148"/>
+      <c r="E139" s="135"/>
       <c r="F139" s="19" t="s">
         <v>275</v>
       </c>
       <c r="G139" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H139" s="136"/>
+      <c r="H139" s="144"/>
       <c r="I139" s="29"/>
       <c r="J139" s="29"/>
       <c r="K139" s="29"/>
@@ -6989,7 +7009,7 @@
       <c r="D140" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E140" s="144">
+      <c r="E140" s="133">
         <v>143</v>
       </c>
       <c r="F140" s="31" t="s">
@@ -6998,7 +7018,7 @@
       <c r="G140" s="77" t="s">
         <v>91</v>
       </c>
-      <c r="H140" s="133" t="s">
+      <c r="H140" s="142" t="s">
         <v>403</v>
       </c>
     </row>
@@ -7012,14 +7032,14 @@
       <c r="D141" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E141" s="145"/>
+      <c r="E141" s="134"/>
       <c r="F141" s="15" t="s">
         <v>271</v>
       </c>
       <c r="G141" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="H141" s="134"/>
+      <c r="H141" s="143"/>
     </row>
     <row r="142" spans="2:12" ht="15.75" customHeight="1">
       <c r="B142" s="44" t="s">
@@ -7031,14 +7051,14 @@
       <c r="D142" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E142" s="145"/>
+      <c r="E142" s="134"/>
       <c r="F142" s="15" t="s">
         <v>272</v>
       </c>
       <c r="G142" s="78" t="s">
         <v>94</v>
       </c>
-      <c r="H142" s="134"/>
+      <c r="H142" s="143"/>
     </row>
     <row r="143" spans="2:12" ht="15.75" customHeight="1">
       <c r="B143" s="44" t="s">
@@ -7050,14 +7070,14 @@
       <c r="D143" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E143" s="145"/>
+      <c r="E143" s="134"/>
       <c r="F143" s="15" t="s">
         <v>273</v>
       </c>
       <c r="G143" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="H143" s="134"/>
+      <c r="H143" s="143"/>
     </row>
     <row r="144" spans="2:12" ht="15.75" customHeight="1">
       <c r="B144" s="44" t="s">
@@ -7069,14 +7089,14 @@
       <c r="D144" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E144" s="145"/>
+      <c r="E144" s="134"/>
       <c r="F144" s="15" t="s">
         <v>274</v>
       </c>
       <c r="G144" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="H144" s="134"/>
+      <c r="H144" s="143"/>
     </row>
     <row r="145" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B145" s="64" t="s">
@@ -7088,14 +7108,14 @@
       <c r="D145" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E145" s="148"/>
+      <c r="E145" s="135"/>
       <c r="F145" s="19" t="s">
         <v>275</v>
       </c>
       <c r="G145" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="H145" s="136"/>
+      <c r="H145" s="144"/>
     </row>
     <row r="146" spans="1:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B146" s="112" t="s">
@@ -7107,7 +7127,7 @@
       <c r="D146" s="79" t="s">
         <v>320</v>
       </c>
-      <c r="E146" s="144">
+      <c r="E146" s="133">
         <v>143</v>
       </c>
       <c r="F146" s="47" t="s">
@@ -7116,7 +7136,7 @@
       <c r="G146" s="48" t="s">
         <v>321</v>
       </c>
-      <c r="H146" s="140" t="s">
+      <c r="H146" s="145" t="s">
         <v>407</v>
       </c>
     </row>
@@ -7130,14 +7150,14 @@
       <c r="D147" s="80" t="s">
         <v>97</v>
       </c>
-      <c r="E147" s="145"/>
+      <c r="E147" s="134"/>
       <c r="F147" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G147" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H147" s="138"/>
+      <c r="H147" s="146"/>
     </row>
     <row r="148" spans="1:12" ht="15.75" customHeight="1">
       <c r="B148" s="44" t="s">
@@ -7149,14 +7169,14 @@
       <c r="D148" s="80" t="s">
         <v>98</v>
       </c>
-      <c r="E148" s="145"/>
+      <c r="E148" s="134"/>
       <c r="F148" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G148" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H148" s="138"/>
+      <c r="H148" s="146"/>
     </row>
     <row r="149" spans="1:12" ht="15.75" customHeight="1">
       <c r="B149" s="44" t="s">
@@ -7168,14 +7188,14 @@
       <c r="D149" s="80" t="s">
         <v>97</v>
       </c>
-      <c r="E149" s="145"/>
+      <c r="E149" s="134"/>
       <c r="F149" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G149" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H149" s="138"/>
+      <c r="H149" s="146"/>
     </row>
     <row r="150" spans="1:12" ht="15.75" customHeight="1">
       <c r="B150" s="44" t="s">
@@ -7187,14 +7207,14 @@
       <c r="D150" s="80" t="s">
         <v>98</v>
       </c>
-      <c r="E150" s="145"/>
+      <c r="E150" s="134"/>
       <c r="F150" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G150" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H150" s="138"/>
+      <c r="H150" s="146"/>
     </row>
     <row r="151" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B151" s="64" t="s">
@@ -7206,14 +7226,14 @@
       <c r="D151" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="E151" s="148"/>
+      <c r="E151" s="135"/>
       <c r="F151" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G151" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H151" s="139"/>
+      <c r="H151" s="147"/>
     </row>
     <row r="152" spans="1:12" ht="13.5" thickTop="1">
       <c r="A152" s="111"/>
@@ -7226,7 +7246,7 @@
       <c r="D152" s="109" t="s">
         <v>378</v>
       </c>
-      <c r="E152" s="144">
+      <c r="E152" s="133">
         <v>143</v>
       </c>
       <c r="F152" s="47" t="s">
@@ -7235,7 +7255,7 @@
       <c r="G152" s="114" t="s">
         <v>374</v>
       </c>
-      <c r="H152" s="140" t="s">
+      <c r="H152" s="145" t="s">
         <v>407</v>
       </c>
     </row>
@@ -7249,12 +7269,12 @@
       <c r="D153" s="109" t="s">
         <v>371</v>
       </c>
-      <c r="E153" s="145"/>
+      <c r="E153" s="134"/>
       <c r="F153" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G153" s="12"/>
-      <c r="H153" s="138"/>
+      <c r="H153" s="146"/>
     </row>
     <row r="154" spans="1:12" ht="15.75" customHeight="1">
       <c r="B154" s="113" t="s">
@@ -7266,14 +7286,14 @@
       <c r="D154" s="109" t="s">
         <v>373</v>
       </c>
-      <c r="E154" s="145"/>
+      <c r="E154" s="134"/>
       <c r="F154" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G154" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H154" s="138"/>
+      <c r="H154" s="146"/>
     </row>
     <row r="155" spans="1:12" ht="15.75" customHeight="1">
       <c r="B155" s="113" t="s">
@@ -7285,12 +7305,12 @@
       <c r="D155" s="109" t="s">
         <v>371</v>
       </c>
-      <c r="E155" s="145"/>
+      <c r="E155" s="134"/>
       <c r="F155" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G155" s="12"/>
-      <c r="H155" s="138"/>
+      <c r="H155" s="146"/>
     </row>
     <row r="156" spans="1:12" ht="15.75" customHeight="1">
       <c r="B156" s="113" t="s">
@@ -7302,12 +7322,12 @@
       <c r="D156" s="109" t="s">
         <v>373</v>
       </c>
-      <c r="E156" s="145"/>
+      <c r="E156" s="134"/>
       <c r="F156" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G156" s="12"/>
-      <c r="H156" s="138"/>
+      <c r="H156" s="146"/>
     </row>
     <row r="157" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B157" s="116" t="s">
@@ -7319,14 +7339,14 @@
       <c r="D157" s="109" t="s">
         <v>371</v>
       </c>
-      <c r="E157" s="148"/>
+      <c r="E157" s="135"/>
       <c r="F157" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G157" s="115" t="s">
         <v>46</v>
       </c>
-      <c r="H157" s="139"/>
+      <c r="H157" s="147"/>
     </row>
     <row r="158" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B158" s="82" t="s">
@@ -7338,7 +7358,7 @@
       <c r="D158" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E158" s="144">
+      <c r="E158" s="133">
         <v>167</v>
       </c>
       <c r="F158" s="31" t="s">
@@ -7347,7 +7367,7 @@
       <c r="G158" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H158" s="133" t="s">
+      <c r="H158" s="142" t="s">
         <v>403</v>
       </c>
       <c r="I158" s="29"/>
@@ -7365,14 +7385,14 @@
       <c r="D159" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E159" s="145"/>
+      <c r="E159" s="134"/>
       <c r="F159" s="15" t="s">
         <v>271</v>
       </c>
       <c r="G159" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H159" s="134"/>
+      <c r="H159" s="143"/>
       <c r="I159" s="29"/>
       <c r="J159" s="29"/>
       <c r="K159" s="29"/>
@@ -7388,14 +7408,14 @@
       <c r="D160" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E160" s="145"/>
+      <c r="E160" s="134"/>
       <c r="F160" s="15" t="s">
         <v>276</v>
       </c>
       <c r="G160" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H160" s="134"/>
+      <c r="H160" s="143"/>
       <c r="I160" s="29"/>
       <c r="J160" s="29"/>
       <c r="K160" s="29"/>
@@ -7411,14 +7431,14 @@
       <c r="D161" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E161" s="145"/>
+      <c r="E161" s="134"/>
       <c r="F161" s="15" t="s">
         <v>277</v>
       </c>
       <c r="G161" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H161" s="134"/>
+      <c r="H161" s="143"/>
       <c r="I161" s="29"/>
       <c r="J161" s="29"/>
       <c r="K161" s="29"/>
@@ -7434,14 +7454,14 @@
       <c r="D162" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E162" s="145"/>
+      <c r="E162" s="134"/>
       <c r="F162" s="15" t="s">
         <v>278</v>
       </c>
       <c r="G162" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H162" s="134"/>
+      <c r="H162" s="143"/>
       <c r="I162" s="29"/>
       <c r="J162" s="29"/>
       <c r="K162" s="29"/>
@@ -7457,14 +7477,14 @@
       <c r="D163" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E163" s="148"/>
+      <c r="E163" s="135"/>
       <c r="F163" s="19" t="s">
         <v>279</v>
       </c>
       <c r="G163" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="H163" s="136"/>
+      <c r="H163" s="144"/>
       <c r="I163" s="29"/>
       <c r="J163" s="29"/>
       <c r="K163" s="29"/>
@@ -7480,7 +7500,7 @@
       <c r="D164" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E164" s="144">
+      <c r="E164" s="133">
         <v>125</v>
       </c>
       <c r="F164" s="58" t="s">
@@ -7489,7 +7509,7 @@
       <c r="G164" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="H164" s="133" t="s">
+      <c r="H164" s="142" t="s">
         <v>403</v>
       </c>
     </row>
@@ -7503,14 +7523,14 @@
       <c r="D165" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E165" s="145"/>
+      <c r="E165" s="134"/>
       <c r="F165" s="56" t="s">
         <v>194</v>
       </c>
       <c r="G165" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H165" s="134"/>
+      <c r="H165" s="143"/>
     </row>
     <row r="166" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B166" s="38" t="s">
@@ -7522,14 +7542,14 @@
       <c r="D166" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E166" s="145"/>
+      <c r="E166" s="134"/>
       <c r="F166" s="56" t="s">
         <v>195</v>
       </c>
       <c r="G166" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H166" s="134"/>
+      <c r="H166" s="143"/>
     </row>
     <row r="167" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B167" s="38" t="s">
@@ -7541,14 +7561,14 @@
       <c r="D167" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E167" s="145"/>
+      <c r="E167" s="134"/>
       <c r="F167" s="56" t="s">
         <v>196</v>
       </c>
       <c r="G167" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H167" s="134"/>
+      <c r="H167" s="143"/>
     </row>
     <row r="168" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B168" s="87" t="s">
@@ -7560,14 +7580,14 @@
       <c r="D168" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E168" s="145"/>
+      <c r="E168" s="134"/>
       <c r="F168" s="56" t="s">
         <v>197</v>
       </c>
       <c r="G168" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H168" s="134"/>
+      <c r="H168" s="143"/>
     </row>
     <row r="169" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B169" s="51" t="s">
@@ -7579,14 +7599,14 @@
       <c r="D169" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E169" s="148"/>
+      <c r="E169" s="135"/>
       <c r="F169" s="57" t="s">
         <v>198</v>
       </c>
       <c r="G169" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H169" s="136"/>
+      <c r="H169" s="144"/>
     </row>
     <row r="170" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B170" s="40" t="s">
@@ -7598,7 +7618,7 @@
       <c r="D170" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E170" s="149">
+      <c r="E170" s="137">
         <v>200</v>
       </c>
       <c r="F170" s="50" t="s">
@@ -7607,7 +7627,7 @@
       <c r="G170" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H170" s="133" t="s">
+      <c r="H170" s="142" t="s">
         <v>408</v>
       </c>
       <c r="I170" s="29"/>
@@ -7625,14 +7645,14 @@
       <c r="D171" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E171" s="145"/>
+      <c r="E171" s="134"/>
       <c r="F171" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G171" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="H171" s="134"/>
+      <c r="H171" s="143"/>
       <c r="I171" s="29"/>
       <c r="J171" s="29"/>
       <c r="K171" s="29"/>
@@ -7648,14 +7668,14 @@
       <c r="D172" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E172" s="145"/>
+      <c r="E172" s="134"/>
       <c r="F172" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G172" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="H172" s="134"/>
+      <c r="H172" s="143"/>
       <c r="I172" s="29"/>
       <c r="J172" s="29"/>
       <c r="K172" s="29"/>
@@ -7671,14 +7691,14 @@
       <c r="D173" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E173" s="145"/>
+      <c r="E173" s="134"/>
       <c r="F173" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G173" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="H173" s="134"/>
+      <c r="H173" s="143"/>
       <c r="I173" s="29"/>
       <c r="J173" s="29"/>
       <c r="K173" s="29"/>
@@ -7694,14 +7714,14 @@
       <c r="D174" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E174" s="145"/>
+      <c r="E174" s="134"/>
       <c r="F174" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G174" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="H174" s="134"/>
+      <c r="H174" s="143"/>
       <c r="I174" s="29"/>
       <c r="J174" s="29"/>
       <c r="K174" s="29"/>
@@ -7717,14 +7737,14 @@
       <c r="D175" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E175" s="146"/>
+      <c r="E175" s="136"/>
       <c r="F175" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G175" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="H175" s="136"/>
+      <c r="H175" s="144"/>
       <c r="I175" s="29"/>
       <c r="J175" s="29"/>
       <c r="K175" s="29"/>
@@ -7740,7 +7760,7 @@
       <c r="D176" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E176" s="144">
+      <c r="E176" s="133">
         <v>125</v>
       </c>
       <c r="F176" s="58" t="s">
@@ -7749,7 +7769,7 @@
       <c r="G176" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="H176" s="133" t="s">
+      <c r="H176" s="142" t="s">
         <v>403</v>
       </c>
       <c r="I176" s="29"/>
@@ -7767,14 +7787,14 @@
       <c r="D177" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E177" s="145"/>
+      <c r="E177" s="134"/>
       <c r="F177" s="56" t="s">
         <v>281</v>
       </c>
       <c r="G177" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="H177" s="134"/>
+      <c r="H177" s="143"/>
       <c r="I177" s="29"/>
       <c r="J177" s="29"/>
       <c r="K177" s="29"/>
@@ -7790,14 +7810,14 @@
       <c r="D178" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E178" s="145"/>
+      <c r="E178" s="134"/>
       <c r="F178" s="56" t="s">
         <v>282</v>
       </c>
       <c r="G178" s="78" t="s">
         <v>111</v>
       </c>
-      <c r="H178" s="134"/>
+      <c r="H178" s="143"/>
       <c r="I178" s="29"/>
       <c r="J178" s="29"/>
       <c r="K178" s="29"/>
@@ -7813,14 +7833,14 @@
       <c r="D179" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E179" s="145"/>
+      <c r="E179" s="134"/>
       <c r="F179" s="56" t="s">
         <v>283</v>
       </c>
       <c r="G179" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="H179" s="134"/>
+      <c r="H179" s="143"/>
       <c r="I179" s="29"/>
       <c r="J179" s="29"/>
       <c r="K179" s="29"/>
@@ -7836,14 +7856,14 @@
       <c r="D180" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E180" s="145"/>
+      <c r="E180" s="134"/>
       <c r="F180" s="56" t="s">
         <v>284</v>
       </c>
       <c r="G180" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="H180" s="134"/>
+      <c r="H180" s="143"/>
       <c r="I180" s="29"/>
       <c r="J180" s="29"/>
       <c r="K180" s="29"/>
@@ -7859,14 +7879,14 @@
       <c r="D181" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E181" s="148"/>
+      <c r="E181" s="135"/>
       <c r="F181" s="88" t="s">
         <v>285</v>
       </c>
       <c r="G181" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H181" s="136"/>
+      <c r="H181" s="144"/>
       <c r="I181" s="29"/>
       <c r="J181" s="29"/>
       <c r="K181" s="29"/>
@@ -7882,7 +7902,7 @@
       <c r="D182" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E182" s="147">
+      <c r="E182" s="138">
         <v>167</v>
       </c>
       <c r="F182" s="28" t="s">
@@ -7891,7 +7911,7 @@
       <c r="G182" s="54" t="s">
         <v>323</v>
       </c>
-      <c r="H182" s="133" t="s">
+      <c r="H182" s="142" t="s">
         <v>402</v>
       </c>
       <c r="I182" s="29"/>
@@ -7909,14 +7929,14 @@
       <c r="D183" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E183" s="145"/>
+      <c r="E183" s="134"/>
       <c r="F183" s="15" t="s">
         <v>309</v>
       </c>
       <c r="G183" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H183" s="134"/>
+      <c r="H183" s="143"/>
       <c r="I183" s="29"/>
       <c r="J183" s="29"/>
       <c r="K183" s="29"/>
@@ -7932,14 +7952,14 @@
       <c r="D184" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E184" s="145"/>
+      <c r="E184" s="134"/>
       <c r="F184" s="15" t="s">
         <v>310</v>
       </c>
       <c r="G184" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H184" s="134"/>
+      <c r="H184" s="143"/>
     </row>
     <row r="185" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B185" s="42" t="s">
@@ -7951,14 +7971,14 @@
       <c r="D185" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E185" s="145"/>
+      <c r="E185" s="134"/>
       <c r="F185" s="15" t="s">
         <v>311</v>
       </c>
       <c r="G185" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H185" s="134"/>
+      <c r="H185" s="143"/>
     </row>
     <row r="186" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B186" s="44" t="s">
@@ -7970,14 +7990,14 @@
       <c r="D186" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E186" s="145"/>
+      <c r="E186" s="134"/>
       <c r="F186" s="15" t="s">
         <v>310</v>
       </c>
       <c r="G186" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H186" s="134"/>
+      <c r="H186" s="143"/>
       <c r="I186" s="29"/>
       <c r="J186" s="29"/>
       <c r="K186" s="29"/>
@@ -7993,14 +8013,14 @@
       <c r="D187" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E187" s="148"/>
+      <c r="E187" s="135"/>
       <c r="F187" s="19" t="s">
         <v>312</v>
       </c>
       <c r="G187" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="H187" s="135"/>
+      <c r="H187" s="148"/>
       <c r="I187" s="29"/>
       <c r="J187" s="29"/>
       <c r="K187" s="29"/>
@@ -8016,7 +8036,7 @@
       <c r="D188" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E188" s="144">
+      <c r="E188" s="133">
         <v>167</v>
       </c>
       <c r="F188" s="50" t="s">
@@ -8025,7 +8045,7 @@
       <c r="G188" s="54" t="s">
         <v>318</v>
       </c>
-      <c r="H188" s="133" t="s">
+      <c r="H188" s="142" t="s">
         <v>415</v>
       </c>
       <c r="I188" s="29"/>
@@ -8043,14 +8063,14 @@
       <c r="D189" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E189" s="145"/>
+      <c r="E189" s="134"/>
       <c r="F189" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G189" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H189" s="134"/>
+      <c r="H189" s="143"/>
       <c r="I189" s="29"/>
       <c r="J189" s="29"/>
       <c r="K189" s="29"/>
@@ -8066,14 +8086,14 @@
       <c r="D190" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E190" s="145"/>
+      <c r="E190" s="134"/>
       <c r="F190" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G190" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H190" s="134"/>
+      <c r="H190" s="143"/>
       <c r="I190" s="29"/>
       <c r="J190" s="29"/>
       <c r="K190" s="29"/>
@@ -8089,14 +8109,14 @@
       <c r="D191" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E191" s="145"/>
+      <c r="E191" s="134"/>
       <c r="F191" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G191" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H191" s="134"/>
+      <c r="H191" s="143"/>
       <c r="I191" s="29"/>
       <c r="J191" s="29"/>
       <c r="K191" s="29"/>
@@ -8112,14 +8132,14 @@
       <c r="D192" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E192" s="145"/>
+      <c r="E192" s="134"/>
       <c r="F192" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G192" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H192" s="134"/>
+      <c r="H192" s="143"/>
       <c r="I192" s="29"/>
       <c r="J192" s="29"/>
       <c r="K192" s="29"/>
@@ -8135,14 +8155,14 @@
       <c r="D193" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E193" s="146"/>
+      <c r="E193" s="136"/>
       <c r="F193" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G193" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="H193" s="135"/>
+      <c r="H193" s="148"/>
       <c r="I193" s="29"/>
       <c r="J193" s="29"/>
       <c r="K193" s="29"/>
@@ -8158,7 +8178,7 @@
       <c r="D194" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E194" s="144">
+      <c r="E194" s="133">
         <v>143</v>
       </c>
       <c r="F194" s="72" t="s">
@@ -8167,7 +8187,7 @@
       <c r="G194" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="H194" s="133" t="s">
+      <c r="H194" s="142" t="s">
         <v>403</v>
       </c>
     </row>
@@ -8181,14 +8201,14 @@
       <c r="D195" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E195" s="145"/>
+      <c r="E195" s="134"/>
       <c r="F195" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G195" s="54" t="s">
         <v>123</v>
       </c>
-      <c r="H195" s="134"/>
+      <c r="H195" s="143"/>
     </row>
     <row r="196" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B196" s="38" t="s">
@@ -8200,14 +8220,14 @@
       <c r="D196" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E196" s="145"/>
+      <c r="E196" s="134"/>
       <c r="F196" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G196" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H196" s="134"/>
+      <c r="H196" s="143"/>
     </row>
     <row r="197" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B197" s="38" t="s">
@@ -8219,14 +8239,14 @@
       <c r="D197" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E197" s="145"/>
+      <c r="E197" s="134"/>
       <c r="F197" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G197" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H197" s="134"/>
+      <c r="H197" s="143"/>
     </row>
     <row r="198" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B198" s="38" t="s">
@@ -8238,14 +8258,14 @@
       <c r="D198" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E198" s="145"/>
+      <c r="E198" s="134"/>
       <c r="F198" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G198" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H198" s="134"/>
+      <c r="H198" s="143"/>
     </row>
     <row r="199" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B199" s="39" t="s">
@@ -8257,14 +8277,14 @@
       <c r="D199" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E199" s="146"/>
+      <c r="E199" s="136"/>
       <c r="F199" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G199" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="H199" s="136"/>
+      <c r="H199" s="144"/>
     </row>
     <row r="200" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B200" s="68" t="s">
@@ -8276,14 +8296,14 @@
       <c r="D200" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E200" s="144">
+      <c r="E200" s="133">
         <v>233</v>
       </c>
       <c r="F200" s="72"/>
       <c r="G200" s="48" t="s">
         <v>331</v>
       </c>
-      <c r="H200" s="137" t="s">
+      <c r="H200" s="149" t="s">
         <v>405</v>
       </c>
     </row>
@@ -8297,10 +8317,10 @@
       <c r="D201" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E201" s="145"/>
+      <c r="E201" s="134"/>
       <c r="F201" s="50"/>
       <c r="G201" s="12"/>
-      <c r="H201" s="138"/>
+      <c r="H201" s="146"/>
     </row>
     <row r="202" spans="2:12" ht="15.75" customHeight="1">
       <c r="B202" s="70" t="s">
@@ -8312,12 +8332,12 @@
       <c r="D202" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E202" s="145"/>
+      <c r="E202" s="134"/>
       <c r="F202" s="50"/>
       <c r="G202" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H202" s="138"/>
+      <c r="H202" s="146"/>
     </row>
     <row r="203" spans="2:12" ht="15.75" customHeight="1">
       <c r="B203" s="70" t="s">
@@ -8329,12 +8349,12 @@
       <c r="D203" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E203" s="145"/>
+      <c r="E203" s="134"/>
       <c r="F203" s="50"/>
       <c r="G203" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H203" s="138"/>
+      <c r="H203" s="146"/>
     </row>
     <row r="204" spans="2:12" ht="15.75" customHeight="1">
       <c r="B204" s="70" t="s">
@@ -8346,12 +8366,12 @@
       <c r="D204" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E204" s="145"/>
+      <c r="E204" s="134"/>
       <c r="F204" s="50"/>
       <c r="G204" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H204" s="138"/>
+      <c r="H204" s="146"/>
     </row>
     <row r="205" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B205" s="71" t="s">
@@ -8363,12 +8383,12 @@
       <c r="D205" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E205" s="146"/>
+      <c r="E205" s="136"/>
       <c r="F205" s="89"/>
       <c r="G205" s="90" t="s">
         <v>118</v>
       </c>
-      <c r="H205" s="139"/>
+      <c r="H205" s="147"/>
     </row>
     <row r="206" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B206" s="117" t="s">
@@ -8380,7 +8400,7 @@
       <c r="D206" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E206" s="144">
+      <c r="E206" s="133">
         <v>167</v>
       </c>
       <c r="F206" s="127" t="s">
@@ -8389,7 +8409,7 @@
       <c r="G206" s="114" t="s">
         <v>381</v>
       </c>
-      <c r="H206" s="133" t="s">
+      <c r="H206" s="142" t="s">
         <v>403</v>
       </c>
     </row>
@@ -8403,14 +8423,14 @@
       <c r="D207" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E207" s="145"/>
+      <c r="E207" s="134"/>
       <c r="F207" s="127" t="s">
         <v>309</v>
       </c>
       <c r="G207" s="119" t="s">
         <v>383</v>
       </c>
-      <c r="H207" s="134"/>
+      <c r="H207" s="143"/>
     </row>
     <row r="208" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B208" s="125" t="s">
@@ -8422,14 +8442,14 @@
       <c r="D208" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E208" s="145"/>
+      <c r="E208" s="134"/>
       <c r="F208" s="127" t="s">
         <v>310</v>
       </c>
       <c r="G208" s="120" t="s">
         <v>382</v>
       </c>
-      <c r="H208" s="134"/>
+      <c r="H208" s="143"/>
     </row>
     <row r="209" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B209" s="125" t="s">
@@ -8441,14 +8461,14 @@
       <c r="D209" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E209" s="145"/>
+      <c r="E209" s="134"/>
       <c r="F209" s="127" t="s">
         <v>311</v>
       </c>
       <c r="G209" s="119" t="s">
         <v>383</v>
       </c>
-      <c r="H209" s="134"/>
+      <c r="H209" s="143"/>
     </row>
     <row r="210" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B210" s="125" t="s">
@@ -8460,14 +8480,14 @@
       <c r="D210" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E210" s="145"/>
+      <c r="E210" s="134"/>
       <c r="F210" s="127" t="s">
         <v>310</v>
       </c>
       <c r="G210" s="122" t="s">
         <v>383</v>
       </c>
-      <c r="H210" s="134"/>
+      <c r="H210" s="143"/>
     </row>
     <row r="211" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B211" s="126" t="s">
@@ -8479,14 +8499,14 @@
       <c r="D211" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E211" s="146"/>
+      <c r="E211" s="136"/>
       <c r="F211" s="127" t="s">
         <v>312</v>
       </c>
       <c r="G211" s="121" t="s">
         <v>383</v>
       </c>
-      <c r="H211" s="136"/>
+      <c r="H211" s="144"/>
     </row>
     <row r="212" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B212" s="117" t="s">
@@ -8498,7 +8518,7 @@
       <c r="D212" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E212" s="141">
+      <c r="E212" s="139">
         <v>167</v>
       </c>
       <c r="F212" s="127" t="s">
@@ -8507,7 +8527,7 @@
       <c r="G212" s="114" t="s">
         <v>390</v>
       </c>
-      <c r="H212" s="133" t="s">
+      <c r="H212" s="142" t="s">
         <v>403</v>
       </c>
     </row>
@@ -8521,14 +8541,14 @@
       <c r="D213" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E213" s="142"/>
+      <c r="E213" s="140"/>
       <c r="F213" s="127" t="s">
         <v>399</v>
       </c>
       <c r="G213" s="118" t="s">
         <v>392</v>
       </c>
-      <c r="H213" s="134"/>
+      <c r="H213" s="143"/>
     </row>
     <row r="214" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B214" s="125" t="s">
@@ -8540,14 +8560,14 @@
       <c r="D214" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E214" s="142"/>
+      <c r="E214" s="140"/>
       <c r="F214" s="127" t="s">
         <v>310</v>
       </c>
       <c r="G214" s="118" t="s">
         <v>394</v>
       </c>
-      <c r="H214" s="134"/>
+      <c r="H214" s="143"/>
     </row>
     <row r="215" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B215" s="125" t="s">
@@ -8559,14 +8579,14 @@
       <c r="D215" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E215" s="142"/>
+      <c r="E215" s="140"/>
       <c r="F215" s="127" t="s">
         <v>311</v>
       </c>
       <c r="G215" s="118" t="s">
         <v>392</v>
       </c>
-      <c r="H215" s="134"/>
+      <c r="H215" s="143"/>
     </row>
     <row r="216" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B216" s="125" t="s">
@@ -8578,14 +8598,14 @@
       <c r="D216" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E216" s="142"/>
+      <c r="E216" s="140"/>
       <c r="F216" s="127" t="s">
         <v>310</v>
       </c>
       <c r="G216" s="118" t="s">
         <v>392</v>
       </c>
-      <c r="H216" s="134"/>
+      <c r="H216" s="143"/>
     </row>
     <row r="217" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B217" s="126" t="s">
@@ -8597,14 +8617,14 @@
       <c r="D217" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="E217" s="143"/>
+      <c r="E217" s="141"/>
       <c r="F217" s="127" t="s">
         <v>312</v>
       </c>
       <c r="G217" s="119" t="s">
         <v>395</v>
       </c>
-      <c r="H217" s="136"/>
+      <c r="H217" s="144"/>
     </row>
     <row r="218" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B218" s="91" t="s">
@@ -8837,7 +8857,7 @@
       </c>
     </row>
     <row r="228" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B228" s="87" t="s">
+      <c r="B228" s="150" t="s">
         <v>134</v>
       </c>
       <c r="C228" s="14">
@@ -13769,38 +13789,30 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="72">
-    <mergeCell ref="E140:E145"/>
-    <mergeCell ref="E146:E151"/>
-    <mergeCell ref="E158:E163"/>
-    <mergeCell ref="E194:E199"/>
-    <mergeCell ref="E200:E205"/>
-    <mergeCell ref="E164:E169"/>
-    <mergeCell ref="E170:E175"/>
-    <mergeCell ref="E176:E181"/>
-    <mergeCell ref="E182:E187"/>
-    <mergeCell ref="E188:E193"/>
-    <mergeCell ref="E152:E157"/>
-    <mergeCell ref="E92:E97"/>
-    <mergeCell ref="E98:E103"/>
-    <mergeCell ref="E104:E109"/>
-    <mergeCell ref="E116:E121"/>
-    <mergeCell ref="E122:E127"/>
-    <mergeCell ref="E110:E115"/>
-    <mergeCell ref="E62:E67"/>
-    <mergeCell ref="E68:E73"/>
-    <mergeCell ref="E74:E79"/>
-    <mergeCell ref="E80:E85"/>
-    <mergeCell ref="E86:E91"/>
-    <mergeCell ref="E32:E37"/>
-    <mergeCell ref="E38:E43"/>
-    <mergeCell ref="E44:E49"/>
-    <mergeCell ref="E50:E55"/>
-    <mergeCell ref="E56:E61"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="E8:E13"/>
-    <mergeCell ref="E14:E19"/>
-    <mergeCell ref="E20:E25"/>
-    <mergeCell ref="E26:E31"/>
+    <mergeCell ref="H188:H193"/>
+    <mergeCell ref="H194:H199"/>
+    <mergeCell ref="H200:H205"/>
+    <mergeCell ref="H206:H211"/>
+    <mergeCell ref="H92:H97"/>
+    <mergeCell ref="H98:H103"/>
+    <mergeCell ref="H104:H109"/>
+    <mergeCell ref="H110:H115"/>
+    <mergeCell ref="H116:H121"/>
+    <mergeCell ref="H62:H67"/>
+    <mergeCell ref="H68:H73"/>
+    <mergeCell ref="H74:H79"/>
+    <mergeCell ref="H80:H85"/>
+    <mergeCell ref="H86:H91"/>
+    <mergeCell ref="H32:H37"/>
+    <mergeCell ref="H38:H43"/>
+    <mergeCell ref="H44:H49"/>
+    <mergeCell ref="H50:H55"/>
+    <mergeCell ref="H56:H61"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="H8:H13"/>
+    <mergeCell ref="H14:H19"/>
+    <mergeCell ref="H20:H25"/>
+    <mergeCell ref="H26:H31"/>
     <mergeCell ref="E212:E217"/>
     <mergeCell ref="E206:E211"/>
     <mergeCell ref="H122:H127"/>
@@ -13817,30 +13829,38 @@
     <mergeCell ref="E134:E139"/>
     <mergeCell ref="H212:H217"/>
     <mergeCell ref="H182:H187"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="H8:H13"/>
-    <mergeCell ref="H14:H19"/>
-    <mergeCell ref="H20:H25"/>
-    <mergeCell ref="H26:H31"/>
-    <mergeCell ref="H32:H37"/>
-    <mergeCell ref="H38:H43"/>
-    <mergeCell ref="H44:H49"/>
-    <mergeCell ref="H50:H55"/>
-    <mergeCell ref="H56:H61"/>
-    <mergeCell ref="H62:H67"/>
-    <mergeCell ref="H68:H73"/>
-    <mergeCell ref="H74:H79"/>
-    <mergeCell ref="H80:H85"/>
-    <mergeCell ref="H86:H91"/>
-    <mergeCell ref="H188:H193"/>
-    <mergeCell ref="H194:H199"/>
-    <mergeCell ref="H200:H205"/>
-    <mergeCell ref="H206:H211"/>
-    <mergeCell ref="H92:H97"/>
-    <mergeCell ref="H98:H103"/>
-    <mergeCell ref="H104:H109"/>
-    <mergeCell ref="H110:H115"/>
-    <mergeCell ref="H116:H121"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="E8:E13"/>
+    <mergeCell ref="E14:E19"/>
+    <mergeCell ref="E20:E25"/>
+    <mergeCell ref="E26:E31"/>
+    <mergeCell ref="E32:E37"/>
+    <mergeCell ref="E38:E43"/>
+    <mergeCell ref="E44:E49"/>
+    <mergeCell ref="E50:E55"/>
+    <mergeCell ref="E56:E61"/>
+    <mergeCell ref="E62:E67"/>
+    <mergeCell ref="E68:E73"/>
+    <mergeCell ref="E74:E79"/>
+    <mergeCell ref="E80:E85"/>
+    <mergeCell ref="E86:E91"/>
+    <mergeCell ref="E92:E97"/>
+    <mergeCell ref="E98:E103"/>
+    <mergeCell ref="E104:E109"/>
+    <mergeCell ref="E116:E121"/>
+    <mergeCell ref="E122:E127"/>
+    <mergeCell ref="E110:E115"/>
+    <mergeCell ref="E140:E145"/>
+    <mergeCell ref="E146:E151"/>
+    <mergeCell ref="E158:E163"/>
+    <mergeCell ref="E194:E199"/>
+    <mergeCell ref="E200:E205"/>
+    <mergeCell ref="E164:E169"/>
+    <mergeCell ref="E170:E175"/>
+    <mergeCell ref="E176:E181"/>
+    <mergeCell ref="E182:E187"/>
+    <mergeCell ref="E188:E193"/>
+    <mergeCell ref="E152:E157"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-source/护甲数据.xlsx
+++ b/data-source/护甲数据.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2363F3-6393-4D77-A5FF-8A1EF0F4A2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{264F6624-5171-44FE-B7EE-F09F199F009C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3694,48 +3694,48 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4069,7 +4069,7 @@
       <c r="D2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="137">
+      <c r="E2" s="150">
         <v>91</v>
       </c>
       <c r="F2" s="11" t="s">
@@ -4078,7 +4078,7 @@
       <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="142" t="s">
+      <c r="H2" s="134" t="s">
         <v>402</v>
       </c>
     </row>
@@ -4092,14 +4092,14 @@
       <c r="D3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="134"/>
+      <c r="E3" s="146"/>
       <c r="F3" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="143"/>
+      <c r="H3" s="135"/>
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1">
       <c r="B4" s="13" t="s">
@@ -4111,14 +4111,14 @@
       <c r="D4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="134"/>
+      <c r="E4" s="146"/>
       <c r="F4" s="15" t="s">
         <v>333</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="143"/>
+      <c r="H4" s="135"/>
     </row>
     <row r="5" spans="2:8" ht="15.75" customHeight="1">
       <c r="B5" s="13" t="s">
@@ -4130,14 +4130,14 @@
       <c r="D5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="134"/>
+      <c r="E5" s="146"/>
       <c r="F5" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="143"/>
+      <c r="H5" s="135"/>
     </row>
     <row r="6" spans="2:8" ht="15.75" customHeight="1">
       <c r="B6" s="13" t="s">
@@ -4149,14 +4149,14 @@
       <c r="D6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="134"/>
+      <c r="E6" s="146"/>
       <c r="F6" s="15" t="s">
         <v>333</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="143"/>
+      <c r="H6" s="135"/>
     </row>
     <row r="7" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B7" s="16" t="s">
@@ -4168,14 +4168,14 @@
       <c r="D7" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="135"/>
+      <c r="E7" s="149"/>
       <c r="F7" s="19" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="144"/>
+      <c r="H7" s="137"/>
     </row>
     <row r="8" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B8" s="21" t="s">
@@ -4187,7 +4187,7 @@
       <c r="D8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="133">
+      <c r="E8" s="145">
         <v>91</v>
       </c>
       <c r="F8" s="11" t="s">
@@ -4196,7 +4196,7 @@
       <c r="G8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="142" t="s">
+      <c r="H8" s="134" t="s">
         <v>403</v>
       </c>
     </row>
@@ -4210,14 +4210,14 @@
       <c r="D9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="134"/>
+      <c r="E9" s="146"/>
       <c r="F9" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="143"/>
+      <c r="H9" s="135"/>
     </row>
     <row r="10" spans="2:8" ht="15.75" customHeight="1">
       <c r="B10" s="13" t="s">
@@ -4229,14 +4229,14 @@
       <c r="D10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="134"/>
+      <c r="E10" s="146"/>
       <c r="F10" s="15" t="s">
         <v>333</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="143"/>
+      <c r="H10" s="135"/>
     </row>
     <row r="11" spans="2:8" ht="15.75" customHeight="1">
       <c r="B11" s="13" t="s">
@@ -4248,14 +4248,14 @@
       <c r="D11" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="134"/>
+      <c r="E11" s="146"/>
       <c r="F11" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="143"/>
+      <c r="H11" s="135"/>
     </row>
     <row r="12" spans="2:8" ht="15.75" customHeight="1">
       <c r="B12" s="13" t="s">
@@ -4267,14 +4267,14 @@
       <c r="D12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="134"/>
+      <c r="E12" s="146"/>
       <c r="F12" s="15" t="s">
         <v>333</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="143"/>
+      <c r="H12" s="135"/>
     </row>
     <row r="13" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B13" s="23" t="s">
@@ -4286,14 +4286,14 @@
       <c r="D13" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="136"/>
+      <c r="E13" s="147"/>
       <c r="F13" s="26" t="s">
         <v>9</v>
       </c>
       <c r="G13" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="144"/>
+      <c r="H13" s="137"/>
     </row>
     <row r="14" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B14" s="8" t="s">
@@ -4305,7 +4305,7 @@
       <c r="D14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="138">
+      <c r="E14" s="148">
         <v>100</v>
       </c>
       <c r="F14" s="28" t="s">
@@ -4314,7 +4314,7 @@
       <c r="G14" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="142" t="s">
+      <c r="H14" s="134" t="s">
         <v>402</v>
       </c>
     </row>
@@ -4328,14 +4328,14 @@
       <c r="D15" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="134"/>
+      <c r="E15" s="146"/>
       <c r="F15" s="15" t="s">
         <v>335</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H15" s="143"/>
+      <c r="H15" s="135"/>
     </row>
     <row r="16" spans="2:8" ht="15.75" customHeight="1">
       <c r="B16" s="13" t="s">
@@ -4347,14 +4347,14 @@
       <c r="D16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="134"/>
+      <c r="E16" s="146"/>
       <c r="F16" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="143"/>
+      <c r="H16" s="135"/>
     </row>
     <row r="17" spans="2:12" ht="15.75" customHeight="1">
       <c r="B17" s="13" t="s">
@@ -4366,14 +4366,14 @@
       <c r="D17" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="134"/>
+      <c r="E17" s="146"/>
       <c r="F17" s="15" t="s">
         <v>337</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H17" s="143"/>
+      <c r="H17" s="135"/>
       <c r="I17" s="29"/>
       <c r="J17" s="29"/>
       <c r="K17" s="29"/>
@@ -4389,14 +4389,14 @@
       <c r="D18" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="134"/>
+      <c r="E18" s="146"/>
       <c r="F18" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="143"/>
+      <c r="H18" s="135"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
       <c r="K18" s="29"/>
@@ -4412,14 +4412,14 @@
       <c r="D19" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="135"/>
+      <c r="E19" s="149"/>
       <c r="F19" s="19" t="s">
         <v>338</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="144"/>
+      <c r="H19" s="137"/>
       <c r="I19" s="29"/>
       <c r="J19" s="29"/>
       <c r="K19" s="29"/>
@@ -4435,7 +4435,7 @@
       <c r="D20" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="133">
+      <c r="E20" s="145">
         <v>100</v>
       </c>
       <c r="F20" s="11" t="s">
@@ -4444,7 +4444,7 @@
       <c r="G20" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="H20" s="142" t="s">
+      <c r="H20" s="134" t="s">
         <v>404</v>
       </c>
     </row>
@@ -4458,14 +4458,14 @@
       <c r="D21" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="134"/>
+      <c r="E21" s="146"/>
       <c r="F21" s="15" t="s">
         <v>335</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H21" s="143"/>
+      <c r="H21" s="135"/>
     </row>
     <row r="22" spans="2:12" ht="15.75" customHeight="1">
       <c r="B22" s="13" t="s">
@@ -4477,14 +4477,14 @@
       <c r="D22" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="134"/>
+      <c r="E22" s="146"/>
       <c r="F22" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H22" s="143"/>
+      <c r="H22" s="135"/>
     </row>
     <row r="23" spans="2:12" ht="15.75" customHeight="1">
       <c r="B23" s="13" t="s">
@@ -4496,14 +4496,14 @@
       <c r="D23" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="134"/>
+      <c r="E23" s="146"/>
       <c r="F23" s="15" t="s">
         <v>337</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H23" s="143"/>
+      <c r="H23" s="135"/>
     </row>
     <row r="24" spans="2:12" ht="15.75" customHeight="1">
       <c r="B24" s="13" t="s">
@@ -4515,14 +4515,14 @@
       <c r="D24" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="134"/>
+      <c r="E24" s="146"/>
       <c r="F24" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H24" s="143"/>
+      <c r="H24" s="135"/>
     </row>
     <row r="25" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B25" s="107" t="s">
@@ -4534,14 +4534,14 @@
       <c r="D25" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="135"/>
+      <c r="E25" s="149"/>
       <c r="F25" s="19" t="s">
         <v>338</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H25" s="144"/>
+      <c r="H25" s="137"/>
     </row>
     <row r="26" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B26" s="21" t="s">
@@ -4553,7 +4553,7 @@
       <c r="D26" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="133">
+      <c r="E26" s="145">
         <v>100</v>
       </c>
       <c r="F26" s="31" t="s">
@@ -4562,7 +4562,7 @@
       <c r="G26" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H26" s="142" t="s">
+      <c r="H26" s="134" t="s">
         <v>403</v>
       </c>
     </row>
@@ -4576,14 +4576,14 @@
       <c r="D27" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="134"/>
+      <c r="E27" s="146"/>
       <c r="F27" s="15" t="s">
         <v>335</v>
       </c>
       <c r="G27" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H27" s="143"/>
+      <c r="H27" s="135"/>
     </row>
     <row r="28" spans="2:12" ht="15.75" customHeight="1">
       <c r="B28" s="13" t="s">
@@ -4595,14 +4595,14 @@
       <c r="D28" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="134"/>
+      <c r="E28" s="146"/>
       <c r="F28" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H28" s="143"/>
+      <c r="H28" s="135"/>
     </row>
     <row r="29" spans="2:12" ht="15.75" customHeight="1">
       <c r="B29" s="13" t="s">
@@ -4614,14 +4614,14 @@
       <c r="D29" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="134"/>
+      <c r="E29" s="146"/>
       <c r="F29" s="15" t="s">
         <v>337</v>
       </c>
       <c r="G29" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H29" s="143"/>
+      <c r="H29" s="135"/>
     </row>
     <row r="30" spans="2:12" ht="15.75" customHeight="1">
       <c r="B30" s="13" t="s">
@@ -4633,14 +4633,14 @@
       <c r="D30" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="134"/>
+      <c r="E30" s="146"/>
       <c r="F30" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H30" s="143"/>
+      <c r="H30" s="135"/>
     </row>
     <row r="31" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B31" s="32" t="s">
@@ -4652,14 +4652,14 @@
       <c r="D31" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="136"/>
+      <c r="E31" s="147"/>
       <c r="F31" s="34" t="s">
         <v>338</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H31" s="144"/>
+      <c r="H31" s="137"/>
     </row>
     <row r="32" spans="2:12" ht="25.9" thickTop="1">
       <c r="B32" s="36" t="s">
@@ -4671,7 +4671,7 @@
       <c r="D32" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="133">
+      <c r="E32" s="145">
         <v>112</v>
       </c>
       <c r="F32" s="31" t="s">
@@ -4680,7 +4680,7 @@
       <c r="G32" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="H32" s="142" t="s">
+      <c r="H32" s="134" t="s">
         <v>403</v>
       </c>
       <c r="I32" s="29"/>
@@ -4698,14 +4698,14 @@
       <c r="D33" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="134"/>
+      <c r="E33" s="146"/>
       <c r="F33" s="15" t="s">
         <v>340</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H33" s="143"/>
+      <c r="H33" s="135"/>
       <c r="I33" s="29"/>
       <c r="J33" s="29"/>
       <c r="K33" s="29"/>
@@ -4721,14 +4721,14 @@
       <c r="D34" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="134"/>
+      <c r="E34" s="146"/>
       <c r="F34" s="15" t="s">
         <v>341</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="143"/>
+      <c r="H34" s="135"/>
       <c r="I34" s="29"/>
       <c r="J34" s="29"/>
       <c r="K34" s="29"/>
@@ -4744,14 +4744,14 @@
       <c r="D35" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="134"/>
+      <c r="E35" s="146"/>
       <c r="F35" s="15" t="s">
         <v>342</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H35" s="143"/>
+      <c r="H35" s="135"/>
       <c r="I35" s="29"/>
       <c r="J35" s="29"/>
       <c r="K35" s="29"/>
@@ -4767,14 +4767,14 @@
       <c r="D36" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="134"/>
+      <c r="E36" s="146"/>
       <c r="F36" s="15" t="s">
         <v>343</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H36" s="143"/>
+      <c r="H36" s="135"/>
       <c r="I36" s="29"/>
       <c r="J36" s="29"/>
       <c r="K36" s="29"/>
@@ -4790,14 +4790,14 @@
       <c r="D37" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E37" s="136"/>
+      <c r="E37" s="147"/>
       <c r="F37" s="26" t="s">
         <v>344</v>
       </c>
       <c r="G37" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="H37" s="144"/>
+      <c r="H37" s="137"/>
       <c r="I37" s="29"/>
       <c r="J37" s="29"/>
       <c r="K37" s="29"/>
@@ -4813,7 +4813,7 @@
       <c r="D38" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="133">
+      <c r="E38" s="145">
         <v>100</v>
       </c>
       <c r="F38" s="11" t="s">
@@ -4822,7 +4822,7 @@
       <c r="G38" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="H38" s="142" t="s">
+      <c r="H38" s="134" t="s">
         <v>403</v>
       </c>
       <c r="I38" s="29"/>
@@ -4840,14 +4840,14 @@
       <c r="D39" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E39" s="134"/>
+      <c r="E39" s="146"/>
       <c r="F39" s="15" t="s">
         <v>335</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H39" s="143"/>
+      <c r="H39" s="135"/>
       <c r="I39" s="29"/>
       <c r="J39" s="29"/>
       <c r="K39" s="29"/>
@@ -4863,14 +4863,14 @@
       <c r="D40" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E40" s="134"/>
+      <c r="E40" s="146"/>
       <c r="F40" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G40" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H40" s="143"/>
+      <c r="H40" s="135"/>
       <c r="I40" s="29"/>
       <c r="J40" s="29"/>
       <c r="K40" s="29"/>
@@ -4886,14 +4886,14 @@
       <c r="D41" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E41" s="134"/>
+      <c r="E41" s="146"/>
       <c r="F41" s="15" t="s">
         <v>337</v>
       </c>
       <c r="G41" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H41" s="143"/>
+      <c r="H41" s="135"/>
       <c r="I41" s="29"/>
       <c r="J41" s="29"/>
       <c r="K41" s="29"/>
@@ -4909,14 +4909,14 @@
       <c r="D42" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E42" s="134"/>
+      <c r="E42" s="146"/>
       <c r="F42" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G42" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H42" s="143"/>
+      <c r="H42" s="135"/>
       <c r="I42" s="29"/>
       <c r="J42" s="29"/>
       <c r="K42" s="29"/>
@@ -4932,14 +4932,14 @@
       <c r="D43" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E43" s="136"/>
+      <c r="E43" s="147"/>
       <c r="F43" s="26" t="s">
         <v>338</v>
       </c>
       <c r="G43" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="H43" s="144"/>
+      <c r="H43" s="137"/>
       <c r="I43" s="29"/>
       <c r="J43" s="29"/>
       <c r="K43" s="29"/>
@@ -4955,7 +4955,7 @@
       <c r="D44" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E44" s="137">
+      <c r="E44" s="150">
         <v>112</v>
       </c>
       <c r="F44" s="11" t="s">
@@ -4964,7 +4964,7 @@
       <c r="G44" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H44" s="142" t="s">
+      <c r="H44" s="134" t="s">
         <v>402</v>
       </c>
       <c r="I44" s="29"/>
@@ -4982,14 +4982,14 @@
       <c r="D45" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E45" s="134"/>
+      <c r="E45" s="146"/>
       <c r="F45" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G45" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H45" s="143"/>
+      <c r="H45" s="135"/>
       <c r="I45" s="29"/>
       <c r="J45" s="29"/>
       <c r="K45" s="29"/>
@@ -5005,14 +5005,14 @@
       <c r="D46" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E46" s="134"/>
+      <c r="E46" s="146"/>
       <c r="F46" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G46" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H46" s="143"/>
+      <c r="H46" s="135"/>
       <c r="I46" s="29"/>
       <c r="J46" s="29"/>
       <c r="K46" s="29"/>
@@ -5028,14 +5028,14 @@
       <c r="D47" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E47" s="134"/>
+      <c r="E47" s="146"/>
       <c r="F47" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G47" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H47" s="143"/>
+      <c r="H47" s="135"/>
       <c r="I47" s="29"/>
       <c r="J47" s="29"/>
       <c r="K47" s="29"/>
@@ -5051,14 +5051,14 @@
       <c r="D48" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E48" s="134"/>
+      <c r="E48" s="146"/>
       <c r="F48" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G48" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H48" s="143"/>
+      <c r="H48" s="135"/>
       <c r="I48" s="29"/>
       <c r="J48" s="29"/>
       <c r="K48" s="29"/>
@@ -5074,14 +5074,14 @@
       <c r="D49" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E49" s="135"/>
+      <c r="E49" s="149"/>
       <c r="F49" s="19" t="s">
         <v>346</v>
       </c>
       <c r="G49" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H49" s="144"/>
+      <c r="H49" s="137"/>
       <c r="I49" s="29"/>
       <c r="J49" s="29"/>
       <c r="K49" s="29"/>
@@ -5097,7 +5097,7 @@
       <c r="D50" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E50" s="133">
+      <c r="E50" s="145">
         <v>112</v>
       </c>
       <c r="F50" s="15" t="s">
@@ -5106,7 +5106,7 @@
       <c r="G50" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H50" s="142" t="s">
+      <c r="H50" s="134" t="s">
         <v>405</v>
       </c>
     </row>
@@ -5120,14 +5120,14 @@
       <c r="D51" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E51" s="134"/>
+      <c r="E51" s="146"/>
       <c r="F51" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G51" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H51" s="143"/>
+      <c r="H51" s="135"/>
     </row>
     <row r="52" spans="2:12" ht="15.75" customHeight="1">
       <c r="B52" s="13" t="s">
@@ -5139,14 +5139,14 @@
       <c r="D52" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E52" s="134"/>
+      <c r="E52" s="146"/>
       <c r="F52" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G52" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H52" s="143"/>
+      <c r="H52" s="135"/>
     </row>
     <row r="53" spans="2:12" ht="15.75" customHeight="1">
       <c r="B53" s="13" t="s">
@@ -5158,14 +5158,14 @@
       <c r="D53" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E53" s="134"/>
+      <c r="E53" s="146"/>
       <c r="F53" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G53" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H53" s="143"/>
+      <c r="H53" s="135"/>
     </row>
     <row r="54" spans="2:12" ht="15.75" customHeight="1">
       <c r="B54" s="13" t="s">
@@ -5177,14 +5177,14 @@
       <c r="D54" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E54" s="134"/>
+      <c r="E54" s="146"/>
       <c r="F54" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H54" s="143"/>
+      <c r="H54" s="135"/>
     </row>
     <row r="55" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B55" s="16" t="s">
@@ -5196,14 +5196,14 @@
       <c r="D55" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E55" s="135"/>
+      <c r="E55" s="149"/>
       <c r="F55" s="19" t="s">
         <v>346</v>
       </c>
       <c r="G55" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H55" s="144"/>
+      <c r="H55" s="137"/>
     </row>
     <row r="56" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B56" s="36" t="s">
@@ -5215,7 +5215,7 @@
       <c r="D56" s="63" t="s">
         <v>180</v>
       </c>
-      <c r="E56" s="133">
+      <c r="E56" s="145">
         <v>112</v>
       </c>
       <c r="F56" s="47" t="s">
@@ -5224,7 +5224,7 @@
       <c r="G56" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="H56" s="142" t="s">
+      <c r="H56" s="134" t="s">
         <v>406</v>
       </c>
     </row>
@@ -5238,14 +5238,14 @@
       <c r="D57" s="63" t="s">
         <v>178</v>
       </c>
-      <c r="E57" s="134"/>
+      <c r="E57" s="146"/>
       <c r="F57" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G57" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H57" s="143"/>
+      <c r="H57" s="135"/>
     </row>
     <row r="58" spans="2:12" ht="15.75" customHeight="1">
       <c r="B58" s="38" t="s">
@@ -5257,14 +5257,14 @@
       <c r="D58" s="63" t="s">
         <v>179</v>
       </c>
-      <c r="E58" s="134"/>
+      <c r="E58" s="146"/>
       <c r="F58" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G58" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H58" s="143"/>
+      <c r="H58" s="135"/>
     </row>
     <row r="59" spans="2:12" ht="15.75" customHeight="1">
       <c r="B59" s="38" t="s">
@@ -5276,14 +5276,14 @@
       <c r="D59" s="63" t="s">
         <v>178</v>
       </c>
-      <c r="E59" s="134"/>
+      <c r="E59" s="146"/>
       <c r="F59" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G59" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H59" s="143"/>
+      <c r="H59" s="135"/>
     </row>
     <row r="60" spans="2:12" ht="15.75" customHeight="1">
       <c r="B60" s="38" t="s">
@@ -5295,14 +5295,14 @@
       <c r="D60" s="63" t="s">
         <v>179</v>
       </c>
-      <c r="E60" s="134"/>
+      <c r="E60" s="146"/>
       <c r="F60" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G60" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H60" s="143"/>
+      <c r="H60" s="135"/>
     </row>
     <row r="61" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B61" s="51" t="s">
@@ -5314,14 +5314,14 @@
       <c r="D61" s="63" t="s">
         <v>178</v>
       </c>
-      <c r="E61" s="135"/>
+      <c r="E61" s="149"/>
       <c r="F61" s="53" t="s">
         <v>7</v>
       </c>
       <c r="G61" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H61" s="144"/>
+      <c r="H61" s="137"/>
     </row>
     <row r="62" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B62" s="36" t="s">
@@ -5333,7 +5333,7 @@
       <c r="D62" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E62" s="133">
+      <c r="E62" s="145">
         <v>143</v>
       </c>
       <c r="F62" s="31" t="s">
@@ -5342,7 +5342,7 @@
       <c r="G62" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="H62" s="142" t="s">
+      <c r="H62" s="134" t="s">
         <v>403</v>
       </c>
       <c r="I62" s="29"/>
@@ -5360,14 +5360,14 @@
       <c r="D63" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E63" s="134"/>
+      <c r="E63" s="146"/>
       <c r="F63" s="15" t="s">
         <v>419</v>
       </c>
       <c r="G63" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H63" s="143"/>
+      <c r="H63" s="135"/>
       <c r="I63" s="29"/>
       <c r="J63" s="29"/>
       <c r="K63" s="29"/>
@@ -5383,14 +5383,14 @@
       <c r="D64" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E64" s="134"/>
+      <c r="E64" s="146"/>
       <c r="F64" s="15" t="s">
         <v>420</v>
       </c>
       <c r="G64" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H64" s="143"/>
+      <c r="H64" s="135"/>
       <c r="I64" s="29"/>
       <c r="J64" s="29"/>
       <c r="K64" s="29"/>
@@ -5406,14 +5406,14 @@
       <c r="D65" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E65" s="134"/>
+      <c r="E65" s="146"/>
       <c r="F65" s="15" t="s">
         <v>421</v>
       </c>
       <c r="G65" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H65" s="143"/>
+      <c r="H65" s="135"/>
       <c r="I65" s="29"/>
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
@@ -5429,14 +5429,14 @@
       <c r="D66" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E66" s="134"/>
+      <c r="E66" s="146"/>
       <c r="F66" s="15" t="s">
         <v>422</v>
       </c>
       <c r="G66" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H66" s="143"/>
+      <c r="H66" s="135"/>
       <c r="I66" s="29"/>
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
@@ -5450,14 +5450,14 @@
         <v>12</v>
       </c>
       <c r="D67" s="18"/>
-      <c r="E67" s="135"/>
+      <c r="E67" s="149"/>
       <c r="F67" s="19" t="s">
         <v>423</v>
       </c>
       <c r="G67" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H67" s="144"/>
+      <c r="H67" s="137"/>
       <c r="I67" s="29"/>
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
@@ -5473,7 +5473,7 @@
       <c r="D68" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E68" s="133">
+      <c r="E68" s="145">
         <v>143</v>
       </c>
       <c r="F68" s="31" t="s">
@@ -5482,7 +5482,7 @@
       <c r="G68" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="H68" s="142" t="s">
+      <c r="H68" s="134" t="s">
         <v>403</v>
       </c>
     </row>
@@ -5496,14 +5496,14 @@
       <c r="D69" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E69" s="134"/>
+      <c r="E69" s="146"/>
       <c r="F69" s="56" t="s">
         <v>199</v>
       </c>
       <c r="G69" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="H69" s="143"/>
+      <c r="H69" s="135"/>
     </row>
     <row r="70" spans="2:12" ht="15.75" customHeight="1">
       <c r="B70" s="38" t="s">
@@ -5515,14 +5515,14 @@
       <c r="D70" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E70" s="134"/>
+      <c r="E70" s="146"/>
       <c r="F70" s="15" t="s">
         <v>200</v>
       </c>
       <c r="G70" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H70" s="143"/>
+      <c r="H70" s="135"/>
     </row>
     <row r="71" spans="2:12" ht="15.75" customHeight="1">
       <c r="B71" s="38" t="s">
@@ -5534,14 +5534,14 @@
       <c r="D71" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E71" s="134"/>
+      <c r="E71" s="146"/>
       <c r="F71" s="56" t="s">
         <v>425</v>
       </c>
       <c r="G71" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H71" s="143"/>
+      <c r="H71" s="135"/>
     </row>
     <row r="72" spans="2:12" ht="15.75" customHeight="1">
       <c r="B72" s="38" t="s">
@@ -5553,14 +5553,14 @@
       <c r="D72" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E72" s="134"/>
+      <c r="E72" s="146"/>
       <c r="F72" s="15" t="s">
         <v>201</v>
       </c>
       <c r="G72" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H72" s="143"/>
+      <c r="H72" s="135"/>
     </row>
     <row r="73" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B73" s="51" t="s">
@@ -5572,14 +5572,14 @@
       <c r="D73" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E73" s="135"/>
+      <c r="E73" s="149"/>
       <c r="F73" s="57" t="s">
         <v>202</v>
       </c>
       <c r="G73" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H73" s="144"/>
+      <c r="H73" s="137"/>
     </row>
     <row r="74" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B74" s="36" t="s">
@@ -5591,7 +5591,7 @@
       <c r="D74" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E74" s="133">
+      <c r="E74" s="145">
         <v>143</v>
       </c>
       <c r="F74" s="58" t="s">
@@ -5600,7 +5600,7 @@
       <c r="G74" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="H74" s="142" t="s">
+      <c r="H74" s="134" t="s">
         <v>403</v>
       </c>
     </row>
@@ -5614,14 +5614,14 @@
       <c r="D75" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E75" s="134"/>
+      <c r="E75" s="146"/>
       <c r="F75" s="56" t="s">
         <v>190</v>
       </c>
       <c r="G75" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="H75" s="143"/>
+      <c r="H75" s="135"/>
     </row>
     <row r="76" spans="2:12" ht="15.75" customHeight="1">
       <c r="B76" s="38" t="s">
@@ -5633,14 +5633,14 @@
       <c r="D76" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E76" s="134"/>
+      <c r="E76" s="146"/>
       <c r="F76" s="56" t="s">
         <v>191</v>
       </c>
       <c r="G76" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H76" s="143"/>
+      <c r="H76" s="135"/>
     </row>
     <row r="77" spans="2:12" ht="15.75" customHeight="1">
       <c r="B77" s="38" t="s">
@@ -5652,14 +5652,14 @@
       <c r="D77" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E77" s="134"/>
+      <c r="E77" s="146"/>
       <c r="F77" s="56" t="s">
         <v>427</v>
       </c>
       <c r="G77" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H77" s="143"/>
+      <c r="H77" s="135"/>
     </row>
     <row r="78" spans="2:12" ht="15.75" customHeight="1">
       <c r="B78" s="38" t="s">
@@ -5671,14 +5671,14 @@
       <c r="D78" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E78" s="134"/>
+      <c r="E78" s="146"/>
       <c r="F78" s="56" t="s">
         <v>192</v>
       </c>
       <c r="G78" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H78" s="143"/>
+      <c r="H78" s="135"/>
     </row>
     <row r="79" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B79" s="51" t="s">
@@ -5690,14 +5690,14 @@
       <c r="D79" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E79" s="135"/>
+      <c r="E79" s="149"/>
       <c r="F79" s="57" t="s">
         <v>190</v>
       </c>
       <c r="G79" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H79" s="144"/>
+      <c r="H79" s="137"/>
     </row>
     <row r="80" spans="2:12" ht="38.65" thickTop="1">
       <c r="B80" s="40" t="s">
@@ -5709,7 +5709,7 @@
       <c r="D80" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E80" s="133">
+      <c r="E80" s="145">
         <v>112</v>
       </c>
       <c r="F80" s="11" t="s">
@@ -5718,7 +5718,7 @@
       <c r="G80" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="H80" s="142" t="s">
+      <c r="H80" s="134" t="s">
         <v>403</v>
       </c>
       <c r="I80" s="29"/>
@@ -5736,14 +5736,14 @@
       <c r="D81" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E81" s="134"/>
+      <c r="E81" s="146"/>
       <c r="F81" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G81" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H81" s="143"/>
+      <c r="H81" s="135"/>
       <c r="I81" s="29"/>
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
@@ -5759,14 +5759,14 @@
       <c r="D82" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E82" s="134"/>
+      <c r="E82" s="146"/>
       <c r="F82" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G82" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H82" s="143"/>
+      <c r="H82" s="135"/>
       <c r="I82" s="29"/>
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
@@ -5782,14 +5782,14 @@
       <c r="D83" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E83" s="134"/>
+      <c r="E83" s="146"/>
       <c r="F83" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G83" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H83" s="143"/>
+      <c r="H83" s="135"/>
       <c r="I83" s="29"/>
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
@@ -5805,14 +5805,14 @@
       <c r="D84" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E84" s="134"/>
+      <c r="E84" s="146"/>
       <c r="F84" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G84" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H84" s="143"/>
+      <c r="H84" s="135"/>
       <c r="I84" s="29"/>
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
@@ -5828,14 +5828,14 @@
       <c r="D85" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E85" s="136"/>
+      <c r="E85" s="147"/>
       <c r="F85" s="26" t="s">
         <v>347</v>
       </c>
       <c r="G85" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H85" s="144"/>
+      <c r="H85" s="137"/>
       <c r="I85" s="29"/>
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
@@ -5851,7 +5851,7 @@
       <c r="D86" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E86" s="137">
+      <c r="E86" s="150">
         <v>125</v>
       </c>
       <c r="F86" s="11" t="s">
@@ -5860,7 +5860,7 @@
       <c r="G86" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H86" s="142" t="s">
+      <c r="H86" s="134" t="s">
         <v>402</v>
       </c>
       <c r="I86" s="29"/>
@@ -5878,14 +5878,14 @@
       <c r="D87" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E87" s="134"/>
+      <c r="E87" s="146"/>
       <c r="F87" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G87" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H87" s="143"/>
+      <c r="H87" s="135"/>
       <c r="I87" s="29"/>
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
@@ -5901,14 +5901,14 @@
       <c r="D88" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E88" s="134"/>
+      <c r="E88" s="146"/>
       <c r="F88" s="15" t="s">
         <v>62</v>
       </c>
       <c r="G88" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H88" s="143"/>
+      <c r="H88" s="135"/>
       <c r="I88" s="29"/>
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
@@ -5924,14 +5924,14 @@
       <c r="D89" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E89" s="134"/>
+      <c r="E89" s="146"/>
       <c r="F89" s="15" t="s">
         <v>63</v>
       </c>
       <c r="G89" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H89" s="143"/>
+      <c r="H89" s="135"/>
       <c r="I89" s="29"/>
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
@@ -5947,14 +5947,14 @@
       <c r="D90" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E90" s="134"/>
+      <c r="E90" s="146"/>
       <c r="F90" s="15" t="s">
         <v>64</v>
       </c>
       <c r="G90" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H90" s="143"/>
+      <c r="H90" s="135"/>
       <c r="I90" s="29"/>
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
@@ -5970,14 +5970,14 @@
       <c r="D91" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E91" s="135"/>
+      <c r="E91" s="149"/>
       <c r="F91" s="19" t="s">
         <v>65</v>
       </c>
       <c r="G91" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H91" s="144"/>
+      <c r="H91" s="137"/>
       <c r="I91" s="29"/>
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
@@ -5993,7 +5993,7 @@
       <c r="D92" s="62" t="s">
         <v>319</v>
       </c>
-      <c r="E92" s="133">
+      <c r="E92" s="145">
         <v>125</v>
       </c>
       <c r="F92" s="47" t="s">
@@ -6002,7 +6002,7 @@
       <c r="G92" s="48" t="s">
         <v>322</v>
       </c>
-      <c r="H92" s="145" t="s">
+      <c r="H92" s="141" t="s">
         <v>407</v>
       </c>
     </row>
@@ -6016,14 +6016,14 @@
       <c r="D93" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="E93" s="134"/>
+      <c r="E93" s="146"/>
       <c r="F93" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G93" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H93" s="146"/>
+      <c r="H93" s="139"/>
     </row>
     <row r="94" spans="2:12" ht="15.75" customHeight="1">
       <c r="B94" s="44" t="s">
@@ -6035,14 +6035,14 @@
       <c r="D94" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="E94" s="134"/>
+      <c r="E94" s="146"/>
       <c r="F94" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G94" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H94" s="146"/>
+      <c r="H94" s="139"/>
     </row>
     <row r="95" spans="2:12" ht="15.75" customHeight="1">
       <c r="B95" s="44" t="s">
@@ -6054,14 +6054,14 @@
       <c r="D95" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="E95" s="134"/>
+      <c r="E95" s="146"/>
       <c r="F95" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G95" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H95" s="146"/>
+      <c r="H95" s="139"/>
     </row>
     <row r="96" spans="2:12" ht="15.75" customHeight="1">
       <c r="B96" s="44" t="s">
@@ -6073,14 +6073,14 @@
       <c r="D96" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="E96" s="134"/>
+      <c r="E96" s="146"/>
       <c r="F96" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G96" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H96" s="146"/>
+      <c r="H96" s="139"/>
     </row>
     <row r="97" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B97" s="64" t="s">
@@ -6092,14 +6092,14 @@
       <c r="D97" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="E97" s="135"/>
+      <c r="E97" s="149"/>
       <c r="F97" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G97" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H97" s="147"/>
+      <c r="H97" s="140"/>
     </row>
     <row r="98" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B98" s="36" t="s">
@@ -6111,7 +6111,7 @@
       <c r="D98" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E98" s="133">
+      <c r="E98" s="145">
         <v>125</v>
       </c>
       <c r="F98" s="58" t="s">
@@ -6120,7 +6120,7 @@
       <c r="G98" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="H98" s="142" t="s">
+      <c r="H98" s="134" t="s">
         <v>403</v>
       </c>
     </row>
@@ -6134,14 +6134,14 @@
       <c r="D99" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E99" s="134"/>
+      <c r="E99" s="146"/>
       <c r="F99" s="56" t="s">
         <v>238</v>
       </c>
       <c r="G99" s="54" t="s">
         <v>232</v>
       </c>
-      <c r="H99" s="143"/>
+      <c r="H99" s="135"/>
     </row>
     <row r="100" spans="2:8" ht="15.75" customHeight="1">
       <c r="B100" s="38" t="s">
@@ -6153,14 +6153,14 @@
       <c r="D100" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E100" s="134"/>
+      <c r="E100" s="146"/>
       <c r="F100" s="56" t="s">
         <v>239</v>
       </c>
       <c r="G100" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H100" s="143"/>
+      <c r="H100" s="135"/>
     </row>
     <row r="101" spans="2:8" ht="15.75" customHeight="1">
       <c r="B101" s="38" t="s">
@@ -6172,14 +6172,14 @@
       <c r="D101" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E101" s="134"/>
+      <c r="E101" s="146"/>
       <c r="F101" s="56" t="s">
         <v>240</v>
       </c>
       <c r="G101" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H101" s="143"/>
+      <c r="H101" s="135"/>
     </row>
     <row r="102" spans="2:8" ht="15.75" customHeight="1">
       <c r="B102" s="38" t="s">
@@ -6191,14 +6191,14 @@
       <c r="D102" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E102" s="134"/>
+      <c r="E102" s="146"/>
       <c r="F102" s="56" t="s">
         <v>241</v>
       </c>
       <c r="G102" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H102" s="143"/>
+      <c r="H102" s="135"/>
     </row>
     <row r="103" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B103" s="51" t="s">
@@ -6210,14 +6210,14 @@
       <c r="D103" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E103" s="135"/>
+      <c r="E103" s="149"/>
       <c r="F103" s="57" t="s">
         <v>242</v>
       </c>
       <c r="G103" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="H103" s="144"/>
+      <c r="H103" s="137"/>
     </row>
     <row r="104" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B104" s="61" t="s">
@@ -6229,7 +6229,7 @@
       <c r="D104" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E104" s="133">
+      <c r="E104" s="145">
         <v>125</v>
       </c>
       <c r="F104" s="31" t="s">
@@ -6238,7 +6238,7 @@
       <c r="G104" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="H104" s="142" t="s">
+      <c r="H104" s="134" t="s">
         <v>403</v>
       </c>
     </row>
@@ -6252,14 +6252,14 @@
       <c r="D105" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E105" s="134"/>
+      <c r="E105" s="146"/>
       <c r="F105" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G105" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H105" s="143"/>
+      <c r="H105" s="135"/>
     </row>
     <row r="106" spans="2:8" ht="15.75" customHeight="1">
       <c r="B106" s="44" t="s">
@@ -6271,14 +6271,14 @@
       <c r="D106" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E106" s="134"/>
+      <c r="E106" s="146"/>
       <c r="F106" s="15" t="s">
         <v>62</v>
       </c>
       <c r="G106" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H106" s="143"/>
+      <c r="H106" s="135"/>
     </row>
     <row r="107" spans="2:8" ht="15.75" customHeight="1">
       <c r="B107" s="44" t="s">
@@ -6290,14 +6290,14 @@
       <c r="D107" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E107" s="134"/>
+      <c r="E107" s="146"/>
       <c r="F107" s="15" t="s">
         <v>75</v>
       </c>
       <c r="G107" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H107" s="143"/>
+      <c r="H107" s="135"/>
     </row>
     <row r="108" spans="2:8" ht="15.75" customHeight="1">
       <c r="B108" s="44" t="s">
@@ -6309,14 +6309,14 @@
       <c r="D108" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E108" s="134"/>
+      <c r="E108" s="146"/>
       <c r="F108" s="15" t="s">
         <v>64</v>
       </c>
       <c r="G108" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H108" s="143"/>
+      <c r="H108" s="135"/>
     </row>
     <row r="109" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B109" s="66" t="s">
@@ -6328,14 +6328,14 @@
       <c r="D109" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E109" s="136"/>
+      <c r="E109" s="147"/>
       <c r="F109" s="34" t="s">
         <v>65</v>
       </c>
       <c r="G109" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="H109" s="144"/>
+      <c r="H109" s="137"/>
     </row>
     <row r="110" spans="2:8" ht="25.5" customHeight="1" thickTop="1">
       <c r="B110" s="36" t="s">
@@ -6347,7 +6347,7 @@
       <c r="D110" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E110" s="133">
+      <c r="E110" s="145">
         <v>125</v>
       </c>
       <c r="F110" s="72" t="s">
@@ -6356,7 +6356,7 @@
       <c r="G110" s="37" t="s">
         <v>357</v>
       </c>
-      <c r="H110" s="142" t="s">
+      <c r="H110" s="134" t="s">
         <v>403</v>
       </c>
     </row>
@@ -6370,14 +6370,14 @@
       <c r="D111" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E111" s="134"/>
+      <c r="E111" s="146"/>
       <c r="F111" s="56" t="s">
         <v>359</v>
       </c>
       <c r="G111" s="54" t="s">
         <v>356</v>
       </c>
-      <c r="H111" s="143"/>
+      <c r="H111" s="135"/>
     </row>
     <row r="112" spans="2:8" ht="15.75" customHeight="1">
       <c r="B112" s="38" t="s">
@@ -6389,14 +6389,14 @@
       <c r="D112" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E112" s="134"/>
+      <c r="E112" s="146"/>
       <c r="F112" s="56" t="s">
         <v>355</v>
       </c>
       <c r="G112" s="54" t="s">
         <v>360</v>
       </c>
-      <c r="H112" s="143"/>
+      <c r="H112" s="135"/>
     </row>
     <row r="113" spans="2:12" ht="15.75" customHeight="1">
       <c r="B113" s="38" t="s">
@@ -6408,14 +6408,14 @@
       <c r="D113" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E113" s="134"/>
+      <c r="E113" s="146"/>
       <c r="F113" s="56" t="s">
         <v>362</v>
       </c>
       <c r="G113" s="54" t="s">
         <v>356</v>
       </c>
-      <c r="H113" s="143"/>
+      <c r="H113" s="135"/>
     </row>
     <row r="114" spans="2:12" ht="15.75" customHeight="1">
       <c r="B114" s="38" t="s">
@@ -6427,14 +6427,14 @@
       <c r="D114" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E114" s="134"/>
+      <c r="E114" s="146"/>
       <c r="F114" s="56" t="s">
         <v>428</v>
       </c>
       <c r="G114" s="54" t="s">
         <v>356</v>
       </c>
-      <c r="H114" s="143"/>
+      <c r="H114" s="135"/>
     </row>
     <row r="115" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B115" s="51" t="s">
@@ -6446,14 +6446,14 @@
       <c r="D115" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E115" s="135"/>
+      <c r="E115" s="149"/>
       <c r="F115" s="57" t="s">
         <v>366</v>
       </c>
       <c r="G115" s="54" t="s">
         <v>365</v>
       </c>
-      <c r="H115" s="144"/>
+      <c r="H115" s="137"/>
     </row>
     <row r="116" spans="2:12" ht="25.9" thickTop="1">
       <c r="B116" s="68" t="s">
@@ -6465,7 +6465,7 @@
       <c r="D116" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E116" s="133">
+      <c r="E116" s="145">
         <v>143</v>
       </c>
       <c r="F116" s="31" t="s">
@@ -6474,7 +6474,7 @@
       <c r="G116" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="H116" s="142" t="s">
+      <c r="H116" s="134" t="s">
         <v>414</v>
       </c>
       <c r="I116" s="29"/>
@@ -6492,14 +6492,14 @@
       <c r="D117" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E117" s="134"/>
+      <c r="E117" s="146"/>
       <c r="F117" s="15" t="s">
         <v>250</v>
       </c>
       <c r="G117" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H117" s="143"/>
+      <c r="H117" s="135"/>
       <c r="I117" s="29"/>
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
@@ -6515,14 +6515,14 @@
       <c r="D118" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E118" s="134"/>
+      <c r="E118" s="146"/>
       <c r="F118" s="15" t="s">
         <v>251</v>
       </c>
       <c r="G118" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H118" s="143"/>
+      <c r="H118" s="135"/>
       <c r="I118" s="29"/>
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
@@ -6538,14 +6538,14 @@
       <c r="D119" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E119" s="134"/>
+      <c r="E119" s="146"/>
       <c r="F119" s="15" t="s">
         <v>252</v>
       </c>
       <c r="G119" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H119" s="143"/>
+      <c r="H119" s="135"/>
       <c r="I119" s="29"/>
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
@@ -6561,14 +6561,14 @@
       <c r="D120" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E120" s="134"/>
+      <c r="E120" s="146"/>
       <c r="F120" s="15" t="s">
         <v>253</v>
       </c>
       <c r="G120" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H120" s="143"/>
+      <c r="H120" s="135"/>
       <c r="I120" s="29"/>
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
@@ -6584,14 +6584,14 @@
       <c r="D121" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E121" s="136"/>
+      <c r="E121" s="147"/>
       <c r="F121" s="26" t="s">
         <v>254</v>
       </c>
       <c r="G121" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="H121" s="144"/>
+      <c r="H121" s="137"/>
       <c r="I121" s="29"/>
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
@@ -6607,7 +6607,7 @@
       <c r="D122" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E122" s="133">
+      <c r="E122" s="145">
         <v>125</v>
       </c>
       <c r="F122" s="72" t="s">
@@ -6616,7 +6616,7 @@
       <c r="G122" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="H122" s="142" t="s">
+      <c r="H122" s="134" t="s">
         <v>403</v>
       </c>
       <c r="I122" s="29"/>
@@ -6634,14 +6634,14 @@
       <c r="D123" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E123" s="134"/>
+      <c r="E123" s="146"/>
       <c r="F123" s="56" t="s">
         <v>256</v>
       </c>
       <c r="G123" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H123" s="143"/>
+      <c r="H123" s="135"/>
       <c r="I123" s="29"/>
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
@@ -6657,14 +6657,14 @@
       <c r="D124" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E124" s="134"/>
+      <c r="E124" s="146"/>
       <c r="F124" s="56" t="s">
         <v>257</v>
       </c>
       <c r="G124" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H124" s="143"/>
+      <c r="H124" s="135"/>
       <c r="I124" s="29"/>
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
@@ -6680,14 +6680,14 @@
       <c r="D125" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E125" s="134"/>
+      <c r="E125" s="146"/>
       <c r="F125" s="56" t="s">
         <v>258</v>
       </c>
       <c r="G125" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H125" s="143"/>
+      <c r="H125" s="135"/>
       <c r="I125" s="29"/>
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
@@ -6703,14 +6703,14 @@
       <c r="D126" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E126" s="134"/>
+      <c r="E126" s="146"/>
       <c r="F126" s="56" t="s">
         <v>259</v>
       </c>
       <c r="G126" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H126" s="143"/>
+      <c r="H126" s="135"/>
       <c r="I126" s="29"/>
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
@@ -6726,14 +6726,14 @@
       <c r="D127" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E127" s="136"/>
+      <c r="E127" s="147"/>
       <c r="F127" s="73" t="s">
         <v>260</v>
       </c>
       <c r="G127" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="H127" s="144"/>
+      <c r="H127" s="137"/>
       <c r="I127" s="29"/>
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
@@ -6749,7 +6749,7 @@
       <c r="D128" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E128" s="133">
+      <c r="E128" s="145">
         <v>143</v>
       </c>
       <c r="F128" s="72" t="s">
@@ -6758,7 +6758,7 @@
       <c r="G128" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="H128" s="142" t="s">
+      <c r="H128" s="134" t="s">
         <v>403</v>
       </c>
     </row>
@@ -6772,14 +6772,14 @@
       <c r="D129" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E129" s="134"/>
+      <c r="E129" s="146"/>
       <c r="F129" s="56" t="s">
         <v>265</v>
       </c>
       <c r="G129" s="77" t="s">
         <v>118</v>
       </c>
-      <c r="H129" s="143"/>
+      <c r="H129" s="135"/>
     </row>
     <row r="130" spans="2:12" ht="15.75" customHeight="1">
       <c r="B130" s="70" t="s">
@@ -6791,14 +6791,14 @@
       <c r="D130" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E130" s="134"/>
+      <c r="E130" s="146"/>
       <c r="F130" s="56" t="s">
         <v>266</v>
       </c>
       <c r="G130" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H130" s="143"/>
+      <c r="H130" s="135"/>
     </row>
     <row r="131" spans="2:12" ht="15.75" customHeight="1">
       <c r="B131" s="74" t="s">
@@ -6810,14 +6810,14 @@
       <c r="D131" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E131" s="134"/>
+      <c r="E131" s="146"/>
       <c r="F131" s="56" t="s">
         <v>267</v>
       </c>
       <c r="G131" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H131" s="143"/>
+      <c r="H131" s="135"/>
     </row>
     <row r="132" spans="2:12" ht="15.75" customHeight="1">
       <c r="B132" s="74" t="s">
@@ -6829,14 +6829,14 @@
       <c r="D132" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E132" s="134"/>
+      <c r="E132" s="146"/>
       <c r="F132" s="56" t="s">
         <v>268</v>
       </c>
       <c r="G132" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H132" s="143"/>
+      <c r="H132" s="135"/>
     </row>
     <row r="133" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B133" s="71" t="s">
@@ -6848,14 +6848,14 @@
       <c r="D133" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E133" s="136"/>
+      <c r="E133" s="147"/>
       <c r="F133" s="73" t="s">
         <v>269</v>
       </c>
       <c r="G133" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="H133" s="144"/>
+      <c r="H133" s="137"/>
     </row>
     <row r="134" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B134" s="75" t="s">
@@ -6867,7 +6867,7 @@
       <c r="D134" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E134" s="138">
+      <c r="E134" s="148">
         <v>143</v>
       </c>
       <c r="F134" s="28" t="s">
@@ -6876,7 +6876,7 @@
       <c r="G134" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H134" s="142" t="s">
+      <c r="H134" s="134" t="s">
         <v>402</v>
       </c>
       <c r="I134" s="29"/>
@@ -6894,14 +6894,14 @@
       <c r="D135" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E135" s="134"/>
+      <c r="E135" s="146"/>
       <c r="F135" s="15" t="s">
         <v>271</v>
       </c>
       <c r="G135" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H135" s="143"/>
+      <c r="H135" s="135"/>
       <c r="I135" s="29"/>
       <c r="J135" s="29"/>
       <c r="K135" s="29"/>
@@ -6917,14 +6917,14 @@
       <c r="D136" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E136" s="134"/>
+      <c r="E136" s="146"/>
       <c r="F136" s="15" t="s">
         <v>272</v>
       </c>
       <c r="G136" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H136" s="143"/>
+      <c r="H136" s="135"/>
       <c r="I136" s="29"/>
       <c r="J136" s="29"/>
       <c r="K136" s="29"/>
@@ -6940,14 +6940,14 @@
       <c r="D137" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E137" s="134"/>
+      <c r="E137" s="146"/>
       <c r="F137" s="15" t="s">
         <v>273</v>
       </c>
       <c r="G137" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H137" s="143"/>
+      <c r="H137" s="135"/>
       <c r="I137" s="29"/>
       <c r="J137" s="29"/>
       <c r="K137" s="29"/>
@@ -6963,14 +6963,14 @@
       <c r="D138" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E138" s="134"/>
+      <c r="E138" s="146"/>
       <c r="F138" s="15" t="s">
         <v>274</v>
       </c>
       <c r="G138" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H138" s="143"/>
+      <c r="H138" s="135"/>
       <c r="I138" s="29"/>
       <c r="J138" s="29"/>
       <c r="K138" s="29"/>
@@ -6986,14 +6986,14 @@
       <c r="D139" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E139" s="135"/>
+      <c r="E139" s="149"/>
       <c r="F139" s="19" t="s">
         <v>275</v>
       </c>
       <c r="G139" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H139" s="144"/>
+      <c r="H139" s="137"/>
       <c r="I139" s="29"/>
       <c r="J139" s="29"/>
       <c r="K139" s="29"/>
@@ -7009,7 +7009,7 @@
       <c r="D140" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E140" s="133">
+      <c r="E140" s="145">
         <v>143</v>
       </c>
       <c r="F140" s="31" t="s">
@@ -7018,7 +7018,7 @@
       <c r="G140" s="77" t="s">
         <v>91</v>
       </c>
-      <c r="H140" s="142" t="s">
+      <c r="H140" s="134" t="s">
         <v>403</v>
       </c>
     </row>
@@ -7032,14 +7032,14 @@
       <c r="D141" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E141" s="134"/>
+      <c r="E141" s="146"/>
       <c r="F141" s="15" t="s">
         <v>271</v>
       </c>
       <c r="G141" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="H141" s="143"/>
+      <c r="H141" s="135"/>
     </row>
     <row r="142" spans="2:12" ht="15.75" customHeight="1">
       <c r="B142" s="44" t="s">
@@ -7051,14 +7051,14 @@
       <c r="D142" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E142" s="134"/>
+      <c r="E142" s="146"/>
       <c r="F142" s="15" t="s">
         <v>272</v>
       </c>
       <c r="G142" s="78" t="s">
         <v>94</v>
       </c>
-      <c r="H142" s="143"/>
+      <c r="H142" s="135"/>
     </row>
     <row r="143" spans="2:12" ht="15.75" customHeight="1">
       <c r="B143" s="44" t="s">
@@ -7070,14 +7070,14 @@
       <c r="D143" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E143" s="134"/>
+      <c r="E143" s="146"/>
       <c r="F143" s="15" t="s">
         <v>273</v>
       </c>
       <c r="G143" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="H143" s="143"/>
+      <c r="H143" s="135"/>
     </row>
     <row r="144" spans="2:12" ht="15.75" customHeight="1">
       <c r="B144" s="44" t="s">
@@ -7089,14 +7089,14 @@
       <c r="D144" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E144" s="134"/>
+      <c r="E144" s="146"/>
       <c r="F144" s="15" t="s">
         <v>274</v>
       </c>
       <c r="G144" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="H144" s="143"/>
+      <c r="H144" s="135"/>
     </row>
     <row r="145" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B145" s="64" t="s">
@@ -7108,14 +7108,14 @@
       <c r="D145" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E145" s="135"/>
+      <c r="E145" s="149"/>
       <c r="F145" s="19" t="s">
         <v>275</v>
       </c>
       <c r="G145" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="H145" s="144"/>
+      <c r="H145" s="137"/>
     </row>
     <row r="146" spans="1:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B146" s="112" t="s">
@@ -7127,7 +7127,7 @@
       <c r="D146" s="79" t="s">
         <v>320</v>
       </c>
-      <c r="E146" s="133">
+      <c r="E146" s="145">
         <v>143</v>
       </c>
       <c r="F146" s="47" t="s">
@@ -7136,7 +7136,7 @@
       <c r="G146" s="48" t="s">
         <v>321</v>
       </c>
-      <c r="H146" s="145" t="s">
+      <c r="H146" s="141" t="s">
         <v>407</v>
       </c>
     </row>
@@ -7150,14 +7150,14 @@
       <c r="D147" s="80" t="s">
         <v>97</v>
       </c>
-      <c r="E147" s="134"/>
+      <c r="E147" s="146"/>
       <c r="F147" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G147" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H147" s="146"/>
+      <c r="H147" s="139"/>
     </row>
     <row r="148" spans="1:12" ht="15.75" customHeight="1">
       <c r="B148" s="44" t="s">
@@ -7169,14 +7169,14 @@
       <c r="D148" s="80" t="s">
         <v>98</v>
       </c>
-      <c r="E148" s="134"/>
+      <c r="E148" s="146"/>
       <c r="F148" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G148" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H148" s="146"/>
+      <c r="H148" s="139"/>
     </row>
     <row r="149" spans="1:12" ht="15.75" customHeight="1">
       <c r="B149" s="44" t="s">
@@ -7188,14 +7188,14 @@
       <c r="D149" s="80" t="s">
         <v>97</v>
       </c>
-      <c r="E149" s="134"/>
+      <c r="E149" s="146"/>
       <c r="F149" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G149" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H149" s="146"/>
+      <c r="H149" s="139"/>
     </row>
     <row r="150" spans="1:12" ht="15.75" customHeight="1">
       <c r="B150" s="44" t="s">
@@ -7207,14 +7207,14 @@
       <c r="D150" s="80" t="s">
         <v>98</v>
       </c>
-      <c r="E150" s="134"/>
+      <c r="E150" s="146"/>
       <c r="F150" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G150" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H150" s="146"/>
+      <c r="H150" s="139"/>
     </row>
     <row r="151" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B151" s="64" t="s">
@@ -7226,14 +7226,14 @@
       <c r="D151" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="E151" s="135"/>
+      <c r="E151" s="149"/>
       <c r="F151" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G151" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H151" s="147"/>
+      <c r="H151" s="140"/>
     </row>
     <row r="152" spans="1:12" ht="13.5" thickTop="1">
       <c r="A152" s="111"/>
@@ -7246,7 +7246,7 @@
       <c r="D152" s="109" t="s">
         <v>378</v>
       </c>
-      <c r="E152" s="133">
+      <c r="E152" s="145">
         <v>143</v>
       </c>
       <c r="F152" s="47" t="s">
@@ -7255,7 +7255,7 @@
       <c r="G152" s="114" t="s">
         <v>374</v>
       </c>
-      <c r="H152" s="145" t="s">
+      <c r="H152" s="141" t="s">
         <v>407</v>
       </c>
     </row>
@@ -7269,12 +7269,12 @@
       <c r="D153" s="109" t="s">
         <v>371</v>
       </c>
-      <c r="E153" s="134"/>
+      <c r="E153" s="146"/>
       <c r="F153" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G153" s="12"/>
-      <c r="H153" s="146"/>
+      <c r="H153" s="139"/>
     </row>
     <row r="154" spans="1:12" ht="15.75" customHeight="1">
       <c r="B154" s="113" t="s">
@@ -7286,14 +7286,14 @@
       <c r="D154" s="109" t="s">
         <v>373</v>
       </c>
-      <c r="E154" s="134"/>
+      <c r="E154" s="146"/>
       <c r="F154" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G154" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H154" s="146"/>
+      <c r="H154" s="139"/>
     </row>
     <row r="155" spans="1:12" ht="15.75" customHeight="1">
       <c r="B155" s="113" t="s">
@@ -7305,12 +7305,12 @@
       <c r="D155" s="109" t="s">
         <v>371</v>
       </c>
-      <c r="E155" s="134"/>
+      <c r="E155" s="146"/>
       <c r="F155" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G155" s="12"/>
-      <c r="H155" s="146"/>
+      <c r="H155" s="139"/>
     </row>
     <row r="156" spans="1:12" ht="15.75" customHeight="1">
       <c r="B156" s="113" t="s">
@@ -7322,12 +7322,12 @@
       <c r="D156" s="109" t="s">
         <v>373</v>
       </c>
-      <c r="E156" s="134"/>
+      <c r="E156" s="146"/>
       <c r="F156" s="50" t="s">
         <v>66</v>
       </c>
       <c r="G156" s="12"/>
-      <c r="H156" s="146"/>
+      <c r="H156" s="139"/>
     </row>
     <row r="157" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B157" s="116" t="s">
@@ -7339,14 +7339,14 @@
       <c r="D157" s="109" t="s">
         <v>371</v>
       </c>
-      <c r="E157" s="135"/>
+      <c r="E157" s="149"/>
       <c r="F157" s="53" t="s">
         <v>66</v>
       </c>
       <c r="G157" s="115" t="s">
         <v>46</v>
       </c>
-      <c r="H157" s="147"/>
+      <c r="H157" s="140"/>
     </row>
     <row r="158" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B158" s="82" t="s">
@@ -7358,7 +7358,7 @@
       <c r="D158" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E158" s="133">
+      <c r="E158" s="145">
         <v>167</v>
       </c>
       <c r="F158" s="31" t="s">
@@ -7367,7 +7367,7 @@
       <c r="G158" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H158" s="142" t="s">
+      <c r="H158" s="134" t="s">
         <v>403</v>
       </c>
       <c r="I158" s="29"/>
@@ -7385,14 +7385,14 @@
       <c r="D159" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E159" s="134"/>
+      <c r="E159" s="146"/>
       <c r="F159" s="15" t="s">
         <v>271</v>
       </c>
       <c r="G159" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H159" s="143"/>
+      <c r="H159" s="135"/>
       <c r="I159" s="29"/>
       <c r="J159" s="29"/>
       <c r="K159" s="29"/>
@@ -7408,14 +7408,14 @@
       <c r="D160" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E160" s="134"/>
+      <c r="E160" s="146"/>
       <c r="F160" s="15" t="s">
         <v>276</v>
       </c>
       <c r="G160" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H160" s="143"/>
+      <c r="H160" s="135"/>
       <c r="I160" s="29"/>
       <c r="J160" s="29"/>
       <c r="K160" s="29"/>
@@ -7431,14 +7431,14 @@
       <c r="D161" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E161" s="134"/>
+      <c r="E161" s="146"/>
       <c r="F161" s="15" t="s">
         <v>277</v>
       </c>
       <c r="G161" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H161" s="143"/>
+      <c r="H161" s="135"/>
       <c r="I161" s="29"/>
       <c r="J161" s="29"/>
       <c r="K161" s="29"/>
@@ -7454,14 +7454,14 @@
       <c r="D162" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E162" s="134"/>
+      <c r="E162" s="146"/>
       <c r="F162" s="15" t="s">
         <v>278</v>
       </c>
       <c r="G162" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H162" s="143"/>
+      <c r="H162" s="135"/>
       <c r="I162" s="29"/>
       <c r="J162" s="29"/>
       <c r="K162" s="29"/>
@@ -7477,14 +7477,14 @@
       <c r="D163" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E163" s="135"/>
+      <c r="E163" s="149"/>
       <c r="F163" s="19" t="s">
         <v>279</v>
       </c>
       <c r="G163" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="H163" s="144"/>
+      <c r="H163" s="137"/>
       <c r="I163" s="29"/>
       <c r="J163" s="29"/>
       <c r="K163" s="29"/>
@@ -7500,7 +7500,7 @@
       <c r="D164" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E164" s="133">
+      <c r="E164" s="145">
         <v>125</v>
       </c>
       <c r="F164" s="58" t="s">
@@ -7509,7 +7509,7 @@
       <c r="G164" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="H164" s="142" t="s">
+      <c r="H164" s="134" t="s">
         <v>403</v>
       </c>
     </row>
@@ -7523,14 +7523,14 @@
       <c r="D165" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E165" s="134"/>
+      <c r="E165" s="146"/>
       <c r="F165" s="56" t="s">
         <v>194</v>
       </c>
       <c r="G165" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H165" s="143"/>
+      <c r="H165" s="135"/>
     </row>
     <row r="166" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B166" s="38" t="s">
@@ -7542,14 +7542,14 @@
       <c r="D166" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E166" s="134"/>
+      <c r="E166" s="146"/>
       <c r="F166" s="56" t="s">
         <v>195</v>
       </c>
       <c r="G166" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H166" s="143"/>
+      <c r="H166" s="135"/>
     </row>
     <row r="167" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B167" s="38" t="s">
@@ -7561,14 +7561,14 @@
       <c r="D167" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E167" s="134"/>
+      <c r="E167" s="146"/>
       <c r="F167" s="56" t="s">
         <v>196</v>
       </c>
       <c r="G167" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H167" s="143"/>
+      <c r="H167" s="135"/>
     </row>
     <row r="168" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B168" s="87" t="s">
@@ -7580,14 +7580,14 @@
       <c r="D168" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E168" s="134"/>
+      <c r="E168" s="146"/>
       <c r="F168" s="56" t="s">
         <v>197</v>
       </c>
       <c r="G168" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H168" s="143"/>
+      <c r="H168" s="135"/>
     </row>
     <row r="169" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B169" s="51" t="s">
@@ -7599,14 +7599,14 @@
       <c r="D169" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E169" s="135"/>
+      <c r="E169" s="149"/>
       <c r="F169" s="57" t="s">
         <v>198</v>
       </c>
       <c r="G169" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H169" s="144"/>
+      <c r="H169" s="137"/>
     </row>
     <row r="170" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B170" s="40" t="s">
@@ -7618,7 +7618,7 @@
       <c r="D170" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E170" s="137">
+      <c r="E170" s="150">
         <v>200</v>
       </c>
       <c r="F170" s="50" t="s">
@@ -7627,7 +7627,7 @@
       <c r="G170" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H170" s="142" t="s">
+      <c r="H170" s="134" t="s">
         <v>408</v>
       </c>
       <c r="I170" s="29"/>
@@ -7645,14 +7645,14 @@
       <c r="D171" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E171" s="134"/>
+      <c r="E171" s="146"/>
       <c r="F171" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G171" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="H171" s="143"/>
+      <c r="H171" s="135"/>
       <c r="I171" s="29"/>
       <c r="J171" s="29"/>
       <c r="K171" s="29"/>
@@ -7668,14 +7668,14 @@
       <c r="D172" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E172" s="134"/>
+      <c r="E172" s="146"/>
       <c r="F172" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G172" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="H172" s="143"/>
+      <c r="H172" s="135"/>
       <c r="I172" s="29"/>
       <c r="J172" s="29"/>
       <c r="K172" s="29"/>
@@ -7691,14 +7691,14 @@
       <c r="D173" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E173" s="134"/>
+      <c r="E173" s="146"/>
       <c r="F173" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G173" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="H173" s="143"/>
+      <c r="H173" s="135"/>
       <c r="I173" s="29"/>
       <c r="J173" s="29"/>
       <c r="K173" s="29"/>
@@ -7714,14 +7714,14 @@
       <c r="D174" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E174" s="134"/>
+      <c r="E174" s="146"/>
       <c r="F174" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G174" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="H174" s="143"/>
+      <c r="H174" s="135"/>
       <c r="I174" s="29"/>
       <c r="J174" s="29"/>
       <c r="K174" s="29"/>
@@ -7737,14 +7737,14 @@
       <c r="D175" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E175" s="136"/>
+      <c r="E175" s="147"/>
       <c r="F175" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G175" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="H175" s="144"/>
+      <c r="H175" s="137"/>
       <c r="I175" s="29"/>
       <c r="J175" s="29"/>
       <c r="K175" s="29"/>
@@ -7760,7 +7760,7 @@
       <c r="D176" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E176" s="133">
+      <c r="E176" s="145">
         <v>125</v>
       </c>
       <c r="F176" s="58" t="s">
@@ -7769,7 +7769,7 @@
       <c r="G176" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="H176" s="142" t="s">
+      <c r="H176" s="134" t="s">
         <v>403</v>
       </c>
       <c r="I176" s="29"/>
@@ -7787,14 +7787,14 @@
       <c r="D177" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E177" s="134"/>
+      <c r="E177" s="146"/>
       <c r="F177" s="56" t="s">
         <v>281</v>
       </c>
       <c r="G177" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="H177" s="143"/>
+      <c r="H177" s="135"/>
       <c r="I177" s="29"/>
       <c r="J177" s="29"/>
       <c r="K177" s="29"/>
@@ -7810,14 +7810,14 @@
       <c r="D178" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E178" s="134"/>
+      <c r="E178" s="146"/>
       <c r="F178" s="56" t="s">
         <v>282</v>
       </c>
       <c r="G178" s="78" t="s">
         <v>111</v>
       </c>
-      <c r="H178" s="143"/>
+      <c r="H178" s="135"/>
       <c r="I178" s="29"/>
       <c r="J178" s="29"/>
       <c r="K178" s="29"/>
@@ -7833,14 +7833,14 @@
       <c r="D179" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E179" s="134"/>
+      <c r="E179" s="146"/>
       <c r="F179" s="56" t="s">
         <v>283</v>
       </c>
       <c r="G179" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="H179" s="143"/>
+      <c r="H179" s="135"/>
       <c r="I179" s="29"/>
       <c r="J179" s="29"/>
       <c r="K179" s="29"/>
@@ -7856,14 +7856,14 @@
       <c r="D180" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E180" s="134"/>
+      <c r="E180" s="146"/>
       <c r="F180" s="56" t="s">
         <v>284</v>
       </c>
       <c r="G180" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="H180" s="143"/>
+      <c r="H180" s="135"/>
       <c r="I180" s="29"/>
       <c r="J180" s="29"/>
       <c r="K180" s="29"/>
@@ -7879,14 +7879,14 @@
       <c r="D181" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E181" s="135"/>
+      <c r="E181" s="149"/>
       <c r="F181" s="88" t="s">
         <v>285</v>
       </c>
       <c r="G181" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="H181" s="144"/>
+      <c r="H181" s="137"/>
       <c r="I181" s="29"/>
       <c r="J181" s="29"/>
       <c r="K181" s="29"/>
@@ -7902,7 +7902,7 @@
       <c r="D182" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E182" s="138">
+      <c r="E182" s="148">
         <v>167</v>
       </c>
       <c r="F182" s="28" t="s">
@@ -7911,7 +7911,7 @@
       <c r="G182" s="54" t="s">
         <v>323</v>
       </c>
-      <c r="H182" s="142" t="s">
+      <c r="H182" s="134" t="s">
         <v>402</v>
       </c>
       <c r="I182" s="29"/>
@@ -7929,14 +7929,14 @@
       <c r="D183" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E183" s="134"/>
+      <c r="E183" s="146"/>
       <c r="F183" s="15" t="s">
         <v>309</v>
       </c>
       <c r="G183" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H183" s="143"/>
+      <c r="H183" s="135"/>
       <c r="I183" s="29"/>
       <c r="J183" s="29"/>
       <c r="K183" s="29"/>
@@ -7952,14 +7952,14 @@
       <c r="D184" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E184" s="134"/>
+      <c r="E184" s="146"/>
       <c r="F184" s="15" t="s">
         <v>310</v>
       </c>
       <c r="G184" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H184" s="143"/>
+      <c r="H184" s="135"/>
     </row>
     <row r="185" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B185" s="42" t="s">
@@ -7971,14 +7971,14 @@
       <c r="D185" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E185" s="134"/>
+      <c r="E185" s="146"/>
       <c r="F185" s="15" t="s">
         <v>311</v>
       </c>
       <c r="G185" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H185" s="143"/>
+      <c r="H185" s="135"/>
     </row>
     <row r="186" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B186" s="44" t="s">
@@ -7990,14 +7990,14 @@
       <c r="D186" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E186" s="134"/>
+      <c r="E186" s="146"/>
       <c r="F186" s="15" t="s">
         <v>310</v>
       </c>
       <c r="G186" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H186" s="143"/>
+      <c r="H186" s="135"/>
       <c r="I186" s="29"/>
       <c r="J186" s="29"/>
       <c r="K186" s="29"/>
@@ -8013,14 +8013,14 @@
       <c r="D187" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E187" s="135"/>
+      <c r="E187" s="149"/>
       <c r="F187" s="19" t="s">
         <v>312</v>
       </c>
       <c r="G187" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="H187" s="148"/>
+      <c r="H187" s="136"/>
       <c r="I187" s="29"/>
       <c r="J187" s="29"/>
       <c r="K187" s="29"/>
@@ -8036,7 +8036,7 @@
       <c r="D188" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E188" s="133">
+      <c r="E188" s="145">
         <v>167</v>
       </c>
       <c r="F188" s="50" t="s">
@@ -8045,7 +8045,7 @@
       <c r="G188" s="54" t="s">
         <v>318</v>
       </c>
-      <c r="H188" s="142" t="s">
+      <c r="H188" s="134" t="s">
         <v>415</v>
       </c>
       <c r="I188" s="29"/>
@@ -8063,14 +8063,14 @@
       <c r="D189" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E189" s="134"/>
+      <c r="E189" s="146"/>
       <c r="F189" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G189" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H189" s="143"/>
+      <c r="H189" s="135"/>
       <c r="I189" s="29"/>
       <c r="J189" s="29"/>
       <c r="K189" s="29"/>
@@ -8086,14 +8086,14 @@
       <c r="D190" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E190" s="134"/>
+      <c r="E190" s="146"/>
       <c r="F190" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G190" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H190" s="143"/>
+      <c r="H190" s="135"/>
       <c r="I190" s="29"/>
       <c r="J190" s="29"/>
       <c r="K190" s="29"/>
@@ -8109,14 +8109,14 @@
       <c r="D191" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E191" s="134"/>
+      <c r="E191" s="146"/>
       <c r="F191" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G191" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H191" s="143"/>
+      <c r="H191" s="135"/>
       <c r="I191" s="29"/>
       <c r="J191" s="29"/>
       <c r="K191" s="29"/>
@@ -8132,14 +8132,14 @@
       <c r="D192" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E192" s="134"/>
+      <c r="E192" s="146"/>
       <c r="F192" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G192" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H192" s="143"/>
+      <c r="H192" s="135"/>
       <c r="I192" s="29"/>
       <c r="J192" s="29"/>
       <c r="K192" s="29"/>
@@ -8155,14 +8155,14 @@
       <c r="D193" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E193" s="136"/>
+      <c r="E193" s="147"/>
       <c r="F193" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G193" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="H193" s="148"/>
+      <c r="H193" s="136"/>
       <c r="I193" s="29"/>
       <c r="J193" s="29"/>
       <c r="K193" s="29"/>
@@ -8178,7 +8178,7 @@
       <c r="D194" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E194" s="133">
+      <c r="E194" s="145">
         <v>143</v>
       </c>
       <c r="F194" s="72" t="s">
@@ -8187,7 +8187,7 @@
       <c r="G194" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="H194" s="142" t="s">
+      <c r="H194" s="134" t="s">
         <v>403</v>
       </c>
     </row>
@@ -8201,14 +8201,14 @@
       <c r="D195" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E195" s="134"/>
+      <c r="E195" s="146"/>
       <c r="F195" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G195" s="54" t="s">
         <v>123</v>
       </c>
-      <c r="H195" s="143"/>
+      <c r="H195" s="135"/>
     </row>
     <row r="196" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B196" s="38" t="s">
@@ -8220,14 +8220,14 @@
       <c r="D196" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E196" s="134"/>
+      <c r="E196" s="146"/>
       <c r="F196" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G196" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="H196" s="143"/>
+      <c r="H196" s="135"/>
     </row>
     <row r="197" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B197" s="38" t="s">
@@ -8239,14 +8239,14 @@
       <c r="D197" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E197" s="134"/>
+      <c r="E197" s="146"/>
       <c r="F197" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G197" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H197" s="143"/>
+      <c r="H197" s="135"/>
     </row>
     <row r="198" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B198" s="38" t="s">
@@ -8258,14 +8258,14 @@
       <c r="D198" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E198" s="134"/>
+      <c r="E198" s="146"/>
       <c r="F198" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G198" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H198" s="143"/>
+      <c r="H198" s="135"/>
     </row>
     <row r="199" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B199" s="39" t="s">
@@ -8277,14 +8277,14 @@
       <c r="D199" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E199" s="136"/>
+      <c r="E199" s="147"/>
       <c r="F199" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G199" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="H199" s="144"/>
+      <c r="H199" s="137"/>
     </row>
     <row r="200" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B200" s="68" t="s">
@@ -8296,14 +8296,14 @@
       <c r="D200" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E200" s="133">
+      <c r="E200" s="145">
         <v>233</v>
       </c>
       <c r="F200" s="72"/>
       <c r="G200" s="48" t="s">
         <v>331</v>
       </c>
-      <c r="H200" s="149" t="s">
+      <c r="H200" s="138" t="s">
         <v>405</v>
       </c>
     </row>
@@ -8317,10 +8317,10 @@
       <c r="D201" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E201" s="134"/>
+      <c r="E201" s="146"/>
       <c r="F201" s="50"/>
       <c r="G201" s="12"/>
-      <c r="H201" s="146"/>
+      <c r="H201" s="139"/>
     </row>
     <row r="202" spans="2:12" ht="15.75" customHeight="1">
       <c r="B202" s="70" t="s">
@@ -8332,12 +8332,12 @@
       <c r="D202" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E202" s="134"/>
+      <c r="E202" s="146"/>
       <c r="F202" s="50"/>
       <c r="G202" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H202" s="146"/>
+      <c r="H202" s="139"/>
     </row>
     <row r="203" spans="2:12" ht="15.75" customHeight="1">
       <c r="B203" s="70" t="s">
@@ -8349,12 +8349,12 @@
       <c r="D203" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E203" s="134"/>
+      <c r="E203" s="146"/>
       <c r="F203" s="50"/>
       <c r="G203" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H203" s="146"/>
+      <c r="H203" s="139"/>
     </row>
     <row r="204" spans="2:12" ht="15.75" customHeight="1">
       <c r="B204" s="70" t="s">
@@ -8366,12 +8366,12 @@
       <c r="D204" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E204" s="134"/>
+      <c r="E204" s="146"/>
       <c r="F204" s="50"/>
       <c r="G204" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H204" s="146"/>
+      <c r="H204" s="139"/>
     </row>
     <row r="205" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B205" s="71" t="s">
@@ -8383,12 +8383,12 @@
       <c r="D205" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E205" s="136"/>
+      <c r="E205" s="147"/>
       <c r="F205" s="89"/>
       <c r="G205" s="90" t="s">
         <v>118</v>
       </c>
-      <c r="H205" s="147"/>
+      <c r="H205" s="140"/>
     </row>
     <row r="206" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B206" s="117" t="s">
@@ -8400,7 +8400,7 @@
       <c r="D206" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E206" s="133">
+      <c r="E206" s="145">
         <v>167</v>
       </c>
       <c r="F206" s="127" t="s">
@@ -8409,7 +8409,7 @@
       <c r="G206" s="114" t="s">
         <v>381</v>
       </c>
-      <c r="H206" s="142" t="s">
+      <c r="H206" s="134" t="s">
         <v>403</v>
       </c>
     </row>
@@ -8423,14 +8423,14 @@
       <c r="D207" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E207" s="134"/>
+      <c r="E207" s="146"/>
       <c r="F207" s="127" t="s">
         <v>309</v>
       </c>
       <c r="G207" s="119" t="s">
         <v>383</v>
       </c>
-      <c r="H207" s="143"/>
+      <c r="H207" s="135"/>
     </row>
     <row r="208" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B208" s="125" t="s">
@@ -8442,14 +8442,14 @@
       <c r="D208" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E208" s="134"/>
+      <c r="E208" s="146"/>
       <c r="F208" s="127" t="s">
         <v>310</v>
       </c>
       <c r="G208" s="120" t="s">
         <v>382</v>
       </c>
-      <c r="H208" s="143"/>
+      <c r="H208" s="135"/>
     </row>
     <row r="209" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B209" s="125" t="s">
@@ -8461,14 +8461,14 @@
       <c r="D209" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E209" s="134"/>
+      <c r="E209" s="146"/>
       <c r="F209" s="127" t="s">
         <v>311</v>
       </c>
       <c r="G209" s="119" t="s">
         <v>383</v>
       </c>
-      <c r="H209" s="143"/>
+      <c r="H209" s="135"/>
     </row>
     <row r="210" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B210" s="125" t="s">
@@ -8480,14 +8480,14 @@
       <c r="D210" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E210" s="134"/>
+      <c r="E210" s="146"/>
       <c r="F210" s="127" t="s">
         <v>310</v>
       </c>
       <c r="G210" s="122" t="s">
         <v>383</v>
       </c>
-      <c r="H210" s="143"/>
+      <c r="H210" s="135"/>
     </row>
     <row r="211" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B211" s="126" t="s">
@@ -8499,14 +8499,14 @@
       <c r="D211" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E211" s="136"/>
+      <c r="E211" s="147"/>
       <c r="F211" s="127" t="s">
         <v>312</v>
       </c>
       <c r="G211" s="121" t="s">
         <v>383</v>
       </c>
-      <c r="H211" s="144"/>
+      <c r="H211" s="137"/>
     </row>
     <row r="212" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B212" s="117" t="s">
@@ -8518,7 +8518,7 @@
       <c r="D212" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E212" s="139">
+      <c r="E212" s="142">
         <v>167</v>
       </c>
       <c r="F212" s="127" t="s">
@@ -8527,7 +8527,7 @@
       <c r="G212" s="114" t="s">
         <v>390</v>
       </c>
-      <c r="H212" s="142" t="s">
+      <c r="H212" s="134" t="s">
         <v>403</v>
       </c>
     </row>
@@ -8541,14 +8541,14 @@
       <c r="D213" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E213" s="140"/>
+      <c r="E213" s="143"/>
       <c r="F213" s="127" t="s">
         <v>399</v>
       </c>
       <c r="G213" s="118" t="s">
         <v>392</v>
       </c>
-      <c r="H213" s="143"/>
+      <c r="H213" s="135"/>
     </row>
     <row r="214" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B214" s="125" t="s">
@@ -8560,14 +8560,14 @@
       <c r="D214" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E214" s="140"/>
+      <c r="E214" s="143"/>
       <c r="F214" s="127" t="s">
         <v>310</v>
       </c>
       <c r="G214" s="118" t="s">
         <v>394</v>
       </c>
-      <c r="H214" s="143"/>
+      <c r="H214" s="135"/>
     </row>
     <row r="215" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B215" s="125" t="s">
@@ -8579,14 +8579,14 @@
       <c r="D215" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E215" s="140"/>
+      <c r="E215" s="143"/>
       <c r="F215" s="127" t="s">
         <v>311</v>
       </c>
       <c r="G215" s="118" t="s">
         <v>392</v>
       </c>
-      <c r="H215" s="143"/>
+      <c r="H215" s="135"/>
     </row>
     <row r="216" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B216" s="125" t="s">
@@ -8598,14 +8598,14 @@
       <c r="D216" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E216" s="140"/>
+      <c r="E216" s="143"/>
       <c r="F216" s="127" t="s">
         <v>310</v>
       </c>
       <c r="G216" s="118" t="s">
         <v>392</v>
       </c>
-      <c r="H216" s="143"/>
+      <c r="H216" s="135"/>
     </row>
     <row r="217" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B217" s="126" t="s">
@@ -8617,14 +8617,14 @@
       <c r="D217" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="E217" s="141"/>
+      <c r="E217" s="144"/>
       <c r="F217" s="127" t="s">
         <v>312</v>
       </c>
       <c r="G217" s="119" t="s">
         <v>395</v>
       </c>
-      <c r="H217" s="144"/>
+      <c r="H217" s="137"/>
     </row>
     <row r="218" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B218" s="91" t="s">
@@ -8815,7 +8815,7 @@
         <v>351</v>
       </c>
       <c r="C226" s="14">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="D226" s="10" t="s">
         <v>7</v>
@@ -8857,7 +8857,7 @@
       </c>
     </row>
     <row r="228" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B228" s="150" t="s">
+      <c r="B228" s="133" t="s">
         <v>134</v>
       </c>
       <c r="C228" s="14">
@@ -13789,30 +13789,38 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="72">
-    <mergeCell ref="H188:H193"/>
-    <mergeCell ref="H194:H199"/>
-    <mergeCell ref="H200:H205"/>
-    <mergeCell ref="H206:H211"/>
-    <mergeCell ref="H92:H97"/>
-    <mergeCell ref="H98:H103"/>
-    <mergeCell ref="H104:H109"/>
-    <mergeCell ref="H110:H115"/>
-    <mergeCell ref="H116:H121"/>
-    <mergeCell ref="H62:H67"/>
-    <mergeCell ref="H68:H73"/>
-    <mergeCell ref="H74:H79"/>
-    <mergeCell ref="H80:H85"/>
-    <mergeCell ref="H86:H91"/>
-    <mergeCell ref="H32:H37"/>
-    <mergeCell ref="H38:H43"/>
-    <mergeCell ref="H44:H49"/>
-    <mergeCell ref="H50:H55"/>
-    <mergeCell ref="H56:H61"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="H8:H13"/>
-    <mergeCell ref="H14:H19"/>
-    <mergeCell ref="H20:H25"/>
-    <mergeCell ref="H26:H31"/>
+    <mergeCell ref="E140:E145"/>
+    <mergeCell ref="E146:E151"/>
+    <mergeCell ref="E158:E163"/>
+    <mergeCell ref="E194:E199"/>
+    <mergeCell ref="E200:E205"/>
+    <mergeCell ref="E164:E169"/>
+    <mergeCell ref="E170:E175"/>
+    <mergeCell ref="E176:E181"/>
+    <mergeCell ref="E182:E187"/>
+    <mergeCell ref="E188:E193"/>
+    <mergeCell ref="E152:E157"/>
+    <mergeCell ref="E92:E97"/>
+    <mergeCell ref="E98:E103"/>
+    <mergeCell ref="E104:E109"/>
+    <mergeCell ref="E116:E121"/>
+    <mergeCell ref="E122:E127"/>
+    <mergeCell ref="E110:E115"/>
+    <mergeCell ref="E62:E67"/>
+    <mergeCell ref="E68:E73"/>
+    <mergeCell ref="E74:E79"/>
+    <mergeCell ref="E80:E85"/>
+    <mergeCell ref="E86:E91"/>
+    <mergeCell ref="E32:E37"/>
+    <mergeCell ref="E38:E43"/>
+    <mergeCell ref="E44:E49"/>
+    <mergeCell ref="E50:E55"/>
+    <mergeCell ref="E56:E61"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="E8:E13"/>
+    <mergeCell ref="E14:E19"/>
+    <mergeCell ref="E20:E25"/>
+    <mergeCell ref="E26:E31"/>
     <mergeCell ref="E212:E217"/>
     <mergeCell ref="E206:E211"/>
     <mergeCell ref="H122:H127"/>
@@ -13829,38 +13837,30 @@
     <mergeCell ref="E134:E139"/>
     <mergeCell ref="H212:H217"/>
     <mergeCell ref="H182:H187"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="E8:E13"/>
-    <mergeCell ref="E14:E19"/>
-    <mergeCell ref="E20:E25"/>
-    <mergeCell ref="E26:E31"/>
-    <mergeCell ref="E32:E37"/>
-    <mergeCell ref="E38:E43"/>
-    <mergeCell ref="E44:E49"/>
-    <mergeCell ref="E50:E55"/>
-    <mergeCell ref="E56:E61"/>
-    <mergeCell ref="E62:E67"/>
-    <mergeCell ref="E68:E73"/>
-    <mergeCell ref="E74:E79"/>
-    <mergeCell ref="E80:E85"/>
-    <mergeCell ref="E86:E91"/>
-    <mergeCell ref="E92:E97"/>
-    <mergeCell ref="E98:E103"/>
-    <mergeCell ref="E104:E109"/>
-    <mergeCell ref="E116:E121"/>
-    <mergeCell ref="E122:E127"/>
-    <mergeCell ref="E110:E115"/>
-    <mergeCell ref="E140:E145"/>
-    <mergeCell ref="E146:E151"/>
-    <mergeCell ref="E158:E163"/>
-    <mergeCell ref="E194:E199"/>
-    <mergeCell ref="E200:E205"/>
-    <mergeCell ref="E164:E169"/>
-    <mergeCell ref="E170:E175"/>
-    <mergeCell ref="E176:E181"/>
-    <mergeCell ref="E182:E187"/>
-    <mergeCell ref="E188:E193"/>
-    <mergeCell ref="E152:E157"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="H8:H13"/>
+    <mergeCell ref="H14:H19"/>
+    <mergeCell ref="H20:H25"/>
+    <mergeCell ref="H26:H31"/>
+    <mergeCell ref="H32:H37"/>
+    <mergeCell ref="H38:H43"/>
+    <mergeCell ref="H44:H49"/>
+    <mergeCell ref="H50:H55"/>
+    <mergeCell ref="H56:H61"/>
+    <mergeCell ref="H62:H67"/>
+    <mergeCell ref="H68:H73"/>
+    <mergeCell ref="H74:H79"/>
+    <mergeCell ref="H80:H85"/>
+    <mergeCell ref="H86:H91"/>
+    <mergeCell ref="H188:H193"/>
+    <mergeCell ref="H194:H199"/>
+    <mergeCell ref="H200:H205"/>
+    <mergeCell ref="H206:H211"/>
+    <mergeCell ref="H92:H97"/>
+    <mergeCell ref="H98:H103"/>
+    <mergeCell ref="H104:H109"/>
+    <mergeCell ref="H110:H115"/>
+    <mergeCell ref="H116:H121"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-source/护甲数据.xlsx
+++ b/data-source/护甲数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{264F6624-5171-44FE-B7EE-F09F199F009C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE96422-52E5-4319-9F56-98474E2DB986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="434">
   <si>
     <t>护甲</t>
   </si>
@@ -207,9 +207,6 @@
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
-  </si>
-  <si>
-    <t>增加潜行时的移动速度；10%的几率躲避敌人的攻击</t>
   </si>
   <si>
     <t>夜猎者兜帽</t>
@@ -363,12 +360,6 @@
   </si>
   <si>
     <t xml:space="preserve">狂战士套装（T3+级）  </t>
-  </si>
-  <si>
-    <t>~9.4%概率免疫眩晕</t>
-  </si>
-  <si>
-    <t>减少投掷武器与吹箭伤害（0.85倍）</t>
   </si>
   <si>
     <t xml:space="preserve">法尔维斯套装（T3+级）  </t>
@@ -2330,6 +2321,24 @@
   </si>
   <si>
     <t>哀悼收割者靴子</t>
+  </si>
+  <si>
+    <t>减少投掷武器与吹箭伤害（0.85倍）；如果附近有多个敌人，护甲增加30</t>
+  </si>
+  <si>
+    <t>额外快捷栏；如果附近有多个敌人，护甲增加30</t>
+  </si>
+  <si>
+    <t>如果附近有多个敌人，护甲增加30</t>
+  </si>
+  <si>
+    <t>移动速度：12；如果附近有多个敌人，护甲增加30</t>
+  </si>
+  <si>
+    <t>~9.4%概率免疫眩晕；全套一共在附近有多个敌人时，护甲增加150</t>
+  </si>
+  <si>
+    <t>增加潜行时的移动速度；全套一共10%的几率躲避敌人的攻击</t>
   </si>
 </sst>
 </file>
@@ -3300,7 +3309,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3697,46 +3706,49 @@
     <xf numFmtId="0" fontId="22" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4056,7 +4068,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
@@ -4069,22 +4081,22 @@
       <c r="D2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="150">
+      <c r="E2" s="138">
         <v>91</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="134" t="s">
-        <v>402</v>
+      <c r="H2" s="143" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="15.75" customHeight="1">
       <c r="B3" s="13" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C3" s="14">
         <v>10</v>
@@ -4092,18 +4104,18 @@
       <c r="D3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="146"/>
+      <c r="E3" s="135"/>
       <c r="F3" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="135"/>
+      <c r="H3" s="144"/>
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1">
       <c r="B4" s="13" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C4" s="14">
         <v>25</v>
@@ -4111,18 +4123,18 @@
       <c r="D4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="146"/>
+      <c r="E4" s="135"/>
       <c r="F4" s="15" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="135"/>
+      <c r="H4" s="144"/>
     </row>
     <row r="5" spans="2:8" ht="15.75" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C5" s="14">
         <v>10</v>
@@ -4130,18 +4142,18 @@
       <c r="D5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="146"/>
+      <c r="E5" s="135"/>
       <c r="F5" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="135"/>
+      <c r="H5" s="144"/>
     </row>
     <row r="6" spans="2:8" ht="15.75" customHeight="1">
       <c r="B6" s="13" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C6" s="14">
         <v>25</v>
@@ -4149,18 +4161,18 @@
       <c r="D6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="146"/>
+      <c r="E6" s="135"/>
       <c r="F6" s="15" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="135"/>
+      <c r="H6" s="144"/>
     </row>
     <row r="7" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B7" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C7" s="17">
         <v>0</v>
@@ -4168,14 +4180,14 @@
       <c r="D7" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="149"/>
+      <c r="E7" s="136"/>
       <c r="F7" s="19" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="137"/>
+      <c r="H7" s="145"/>
     </row>
     <row r="8" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B8" s="21" t="s">
@@ -4187,17 +4199,17 @@
       <c r="D8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="145">
+      <c r="E8" s="134">
         <v>91</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="134" t="s">
-        <v>403</v>
+      <c r="H8" s="143" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15.75" customHeight="1">
@@ -4210,14 +4222,14 @@
       <c r="D9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="146"/>
+      <c r="E9" s="135"/>
       <c r="F9" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="135"/>
+      <c r="H9" s="144"/>
     </row>
     <row r="10" spans="2:8" ht="15.75" customHeight="1">
       <c r="B10" s="13" t="s">
@@ -4229,14 +4241,14 @@
       <c r="D10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="146"/>
+      <c r="E10" s="135"/>
       <c r="F10" s="15" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="135"/>
+      <c r="H10" s="144"/>
     </row>
     <row r="11" spans="2:8" ht="15.75" customHeight="1">
       <c r="B11" s="13" t="s">
@@ -4248,18 +4260,18 @@
       <c r="D11" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="146"/>
+      <c r="E11" s="135"/>
       <c r="F11" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="135"/>
+      <c r="H11" s="144"/>
     </row>
     <row r="12" spans="2:8" ht="15.75" customHeight="1">
       <c r="B12" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C12" s="14">
         <v>25</v>
@@ -4267,18 +4279,18 @@
       <c r="D12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="146"/>
+      <c r="E12" s="135"/>
       <c r="F12" s="15" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="135"/>
+      <c r="H12" s="144"/>
     </row>
     <row r="13" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B13" s="23" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C13" s="24">
         <v>0</v>
@@ -4286,14 +4298,14 @@
       <c r="D13" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="147"/>
+      <c r="E13" s="137"/>
       <c r="F13" s="26" t="s">
         <v>9</v>
       </c>
       <c r="G13" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="137"/>
+      <c r="H13" s="145"/>
     </row>
     <row r="14" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B14" s="8" t="s">
@@ -4305,22 +4317,22 @@
       <c r="D14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="148">
+      <c r="E14" s="139">
         <v>100</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="134" t="s">
-        <v>402</v>
+      <c r="H14" s="143" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15.75" customHeight="1">
       <c r="B15" s="13" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C15" s="14">
         <v>30</v>
@@ -4328,18 +4340,18 @@
       <c r="D15" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="146"/>
+      <c r="E15" s="135"/>
       <c r="F15" s="15" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H15" s="135"/>
+      <c r="H15" s="144"/>
     </row>
     <row r="16" spans="2:8" ht="15.75" customHeight="1">
       <c r="B16" s="13" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C16" s="14">
         <v>50</v>
@@ -4347,14 +4359,14 @@
       <c r="D16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="146"/>
+      <c r="E16" s="135"/>
       <c r="F16" s="15" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="135"/>
+      <c r="H16" s="144"/>
     </row>
     <row r="17" spans="2:12" ht="15.75" customHeight="1">
       <c r="B17" s="13" t="s">
@@ -4366,14 +4378,14 @@
       <c r="D17" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="146"/>
+      <c r="E17" s="135"/>
       <c r="F17" s="15" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H17" s="135"/>
+      <c r="H17" s="144"/>
       <c r="I17" s="29"/>
       <c r="J17" s="29"/>
       <c r="K17" s="29"/>
@@ -4381,7 +4393,7 @@
     </row>
     <row r="18" spans="2:12" ht="15.75" customHeight="1">
       <c r="B18" s="13" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C18" s="14">
         <v>50</v>
@@ -4389,14 +4401,14 @@
       <c r="D18" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="146"/>
+      <c r="E18" s="135"/>
       <c r="F18" s="15" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="135"/>
+      <c r="H18" s="144"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
       <c r="K18" s="29"/>
@@ -4404,7 +4416,7 @@
     </row>
     <row r="19" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B19" s="16" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C19" s="17">
         <v>0</v>
@@ -4412,14 +4424,14 @@
       <c r="D19" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="149"/>
+      <c r="E19" s="136"/>
       <c r="F19" s="19" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="137"/>
+      <c r="H19" s="145"/>
       <c r="I19" s="29"/>
       <c r="J19" s="29"/>
       <c r="K19" s="29"/>
@@ -4435,22 +4447,22 @@
       <c r="D20" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="145">
+      <c r="E20" s="134">
         <v>100</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="G20" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="H20" s="134" t="s">
-        <v>404</v>
+      <c r="H20" s="143" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="15.75" customHeight="1">
       <c r="B21" s="13" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C21" s="14">
         <v>30</v>
@@ -4458,18 +4470,18 @@
       <c r="D21" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="146"/>
+      <c r="E21" s="135"/>
       <c r="F21" s="15" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H21" s="135"/>
+      <c r="H21" s="144"/>
     </row>
     <row r="22" spans="2:12" ht="15.75" customHeight="1">
       <c r="B22" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C22" s="14">
         <v>50</v>
@@ -4477,14 +4489,14 @@
       <c r="D22" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="146"/>
+      <c r="E22" s="135"/>
       <c r="F22" s="15" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H22" s="135"/>
+      <c r="H22" s="144"/>
     </row>
     <row r="23" spans="2:12" ht="15.75" customHeight="1">
       <c r="B23" s="13" t="s">
@@ -4496,18 +4508,18 @@
       <c r="D23" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="146"/>
+      <c r="E23" s="135"/>
       <c r="F23" s="15" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H23" s="135"/>
+      <c r="H23" s="144"/>
     </row>
     <row r="24" spans="2:12" ht="15.75" customHeight="1">
       <c r="B24" s="13" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C24" s="14">
         <v>50</v>
@@ -4515,18 +4527,18 @@
       <c r="D24" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="146"/>
+      <c r="E24" s="135"/>
       <c r="F24" s="15" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H24" s="135"/>
+      <c r="H24" s="144"/>
     </row>
     <row r="25" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B25" s="107" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C25" s="17">
         <v>0</v>
@@ -4534,14 +4546,14 @@
       <c r="D25" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="149"/>
+      <c r="E25" s="136"/>
       <c r="F25" s="19" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H25" s="137"/>
+      <c r="H25" s="145"/>
     </row>
     <row r="26" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B26" s="21" t="s">
@@ -4553,22 +4565,22 @@
       <c r="D26" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="145">
+      <c r="E26" s="134">
         <v>100</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="G26" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H26" s="134" t="s">
-        <v>403</v>
+      <c r="H26" s="143" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="27" spans="2:12" ht="15.75" customHeight="1">
       <c r="B27" s="13" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C27" s="14">
         <v>30</v>
@@ -4576,18 +4588,18 @@
       <c r="D27" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="146"/>
+      <c r="E27" s="135"/>
       <c r="F27" s="15" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="G27" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H27" s="135"/>
+      <c r="H27" s="144"/>
     </row>
     <row r="28" spans="2:12" ht="15.75" customHeight="1">
       <c r="B28" s="13" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C28" s="14">
         <v>50</v>
@@ -4595,18 +4607,18 @@
       <c r="D28" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="146"/>
+      <c r="E28" s="135"/>
       <c r="F28" s="15" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H28" s="135"/>
+      <c r="H28" s="144"/>
     </row>
     <row r="29" spans="2:12" ht="15.75" customHeight="1">
       <c r="B29" s="13" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C29" s="14">
         <v>20</v>
@@ -4614,18 +4626,18 @@
       <c r="D29" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="146"/>
+      <c r="E29" s="135"/>
       <c r="F29" s="15" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G29" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H29" s="135"/>
+      <c r="H29" s="144"/>
     </row>
     <row r="30" spans="2:12" ht="15.75" customHeight="1">
       <c r="B30" s="13" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C30" s="14">
         <v>50</v>
@@ -4633,18 +4645,18 @@
       <c r="D30" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="146"/>
+      <c r="E30" s="135"/>
       <c r="F30" s="15" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H30" s="135"/>
+      <c r="H30" s="144"/>
     </row>
     <row r="31" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B31" s="32" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C31" s="33">
         <v>0</v>
@@ -4652,14 +4664,14 @@
       <c r="D31" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="147"/>
+      <c r="E31" s="137"/>
       <c r="F31" s="34" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H31" s="137"/>
+      <c r="H31" s="145"/>
     </row>
     <row r="32" spans="2:12" ht="25.9" thickTop="1">
       <c r="B32" s="36" t="s">
@@ -4671,17 +4683,17 @@
       <c r="D32" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="145">
+      <c r="E32" s="134">
         <v>112</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G32" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="H32" s="134" t="s">
-        <v>403</v>
+      <c r="H32" s="143" t="s">
+        <v>400</v>
       </c>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -4690,7 +4702,7 @@
     </row>
     <row r="33" spans="2:12" ht="15.75" customHeight="1">
       <c r="B33" s="87" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C33" s="14">
         <v>40</v>
@@ -4698,14 +4710,14 @@
       <c r="D33" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="146"/>
+      <c r="E33" s="135"/>
       <c r="F33" s="15" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H33" s="135"/>
+      <c r="H33" s="144"/>
       <c r="I33" s="29"/>
       <c r="J33" s="29"/>
       <c r="K33" s="29"/>
@@ -4721,14 +4733,14 @@
       <c r="D34" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="146"/>
+      <c r="E34" s="135"/>
       <c r="F34" s="15" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="135"/>
+      <c r="H34" s="144"/>
       <c r="I34" s="29"/>
       <c r="J34" s="29"/>
       <c r="K34" s="29"/>
@@ -4736,7 +4748,7 @@
     </row>
     <row r="35" spans="2:12" ht="15.75" customHeight="1">
       <c r="B35" s="38" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C35" s="14">
         <v>30</v>
@@ -4744,14 +4756,14 @@
       <c r="D35" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="146"/>
+      <c r="E35" s="135"/>
       <c r="F35" s="15" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H35" s="135"/>
+      <c r="H35" s="144"/>
       <c r="I35" s="29"/>
       <c r="J35" s="29"/>
       <c r="K35" s="29"/>
@@ -4759,7 +4771,7 @@
     </row>
     <row r="36" spans="2:12" ht="15.75" customHeight="1">
       <c r="B36" s="87" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C36" s="14">
         <v>60</v>
@@ -4767,14 +4779,14 @@
       <c r="D36" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="146"/>
+      <c r="E36" s="135"/>
       <c r="F36" s="15" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H36" s="135"/>
+      <c r="H36" s="144"/>
       <c r="I36" s="29"/>
       <c r="J36" s="29"/>
       <c r="K36" s="29"/>
@@ -4782,7 +4794,7 @@
     </row>
     <row r="37" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B37" s="108" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C37" s="24">
         <v>10</v>
@@ -4790,14 +4802,14 @@
       <c r="D37" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E37" s="147"/>
+      <c r="E37" s="137"/>
       <c r="F37" s="26" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G37" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="H37" s="137"/>
+      <c r="H37" s="145"/>
       <c r="I37" s="29"/>
       <c r="J37" s="29"/>
       <c r="K37" s="29"/>
@@ -4813,17 +4825,17 @@
       <c r="D38" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="145">
+      <c r="E38" s="134">
         <v>100</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="G38" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="H38" s="134" t="s">
-        <v>403</v>
+        <v>433</v>
+      </c>
+      <c r="H38" s="143" t="s">
+        <v>400</v>
       </c>
       <c r="I38" s="29"/>
       <c r="J38" s="29"/>
@@ -4832,7 +4844,7 @@
     </row>
     <row r="39" spans="2:12" ht="15.75" customHeight="1">
       <c r="B39" s="42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C39" s="14">
         <v>30</v>
@@ -4840,14 +4852,14 @@
       <c r="D39" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E39" s="146"/>
+      <c r="E39" s="135"/>
       <c r="F39" s="15" t="s">
-        <v>335</v>
-      </c>
-      <c r="G39" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H39" s="135"/>
+        <v>332</v>
+      </c>
+      <c r="G39" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="H39" s="144"/>
       <c r="I39" s="29"/>
       <c r="J39" s="29"/>
       <c r="K39" s="29"/>
@@ -4855,7 +4867,7 @@
     </row>
     <row r="40" spans="2:12" ht="15.75" customHeight="1">
       <c r="B40" s="42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C40" s="14">
         <v>50</v>
@@ -4863,14 +4875,14 @@
       <c r="D40" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E40" s="146"/>
+      <c r="E40" s="135"/>
       <c r="F40" s="15" t="s">
-        <v>336</v>
-      </c>
-      <c r="G40" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H40" s="135"/>
+        <v>333</v>
+      </c>
+      <c r="G40" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="H40" s="144"/>
       <c r="I40" s="29"/>
       <c r="J40" s="29"/>
       <c r="K40" s="29"/>
@@ -4878,7 +4890,7 @@
     </row>
     <row r="41" spans="2:12" ht="15.75" customHeight="1">
       <c r="B41" s="44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C41" s="14">
         <v>20</v>
@@ -4886,14 +4898,14 @@
       <c r="D41" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E41" s="146"/>
+      <c r="E41" s="135"/>
       <c r="F41" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="G41" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H41" s="135"/>
+        <v>334</v>
+      </c>
+      <c r="G41" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="H41" s="144"/>
       <c r="I41" s="29"/>
       <c r="J41" s="29"/>
       <c r="K41" s="29"/>
@@ -4901,7 +4913,7 @@
     </row>
     <row r="42" spans="2:12" ht="15.75" customHeight="1">
       <c r="B42" s="44" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C42" s="14">
         <v>50</v>
@@ -4909,14 +4921,14 @@
       <c r="D42" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E42" s="146"/>
+      <c r="E42" s="135"/>
       <c r="F42" s="15" t="s">
-        <v>336</v>
-      </c>
-      <c r="G42" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H42" s="135"/>
+        <v>333</v>
+      </c>
+      <c r="G42" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="H42" s="144"/>
       <c r="I42" s="29"/>
       <c r="J42" s="29"/>
       <c r="K42" s="29"/>
@@ -4924,7 +4936,7 @@
     </row>
     <row r="43" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B43" s="45" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C43" s="24">
         <v>0</v>
@@ -4932,14 +4944,14 @@
       <c r="D43" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E43" s="147"/>
+      <c r="E43" s="137"/>
       <c r="F43" s="26" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="G43" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="H43" s="137"/>
+        <v>30</v>
+      </c>
+      <c r="H43" s="145"/>
       <c r="I43" s="29"/>
       <c r="J43" s="29"/>
       <c r="K43" s="29"/>
@@ -4947,7 +4959,7 @@
     </row>
     <row r="44" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B44" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C44" s="9">
         <v>260</v>
@@ -4955,17 +4967,17 @@
       <c r="D44" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E44" s="150">
+      <c r="E44" s="138">
         <v>112</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G44" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H44" s="134" t="s">
-        <v>402</v>
+      <c r="H44" s="143" t="s">
+        <v>399</v>
       </c>
       <c r="I44" s="29"/>
       <c r="J44" s="29"/>
@@ -4974,7 +4986,7 @@
     </row>
     <row r="45" spans="2:12" ht="15.75" customHeight="1">
       <c r="B45" s="13" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C45" s="14">
         <v>50</v>
@@ -4982,14 +4994,14 @@
       <c r="D45" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E45" s="146"/>
+      <c r="E45" s="135"/>
       <c r="F45" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G45" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H45" s="135"/>
+      <c r="H45" s="144"/>
       <c r="I45" s="29"/>
       <c r="J45" s="29"/>
       <c r="K45" s="29"/>
@@ -4997,7 +5009,7 @@
     </row>
     <row r="46" spans="2:12" ht="15.75" customHeight="1">
       <c r="B46" s="13" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C46" s="14">
         <v>90</v>
@@ -5005,14 +5017,14 @@
       <c r="D46" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E46" s="146"/>
+      <c r="E46" s="135"/>
       <c r="F46" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G46" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H46" s="135"/>
+      <c r="H46" s="144"/>
       <c r="I46" s="29"/>
       <c r="J46" s="29"/>
       <c r="K46" s="29"/>
@@ -5020,7 +5032,7 @@
     </row>
     <row r="47" spans="2:12" ht="15.75" customHeight="1">
       <c r="B47" s="13" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C47" s="14">
         <v>30</v>
@@ -5028,14 +5040,14 @@
       <c r="D47" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E47" s="146"/>
+      <c r="E47" s="135"/>
       <c r="F47" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G47" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H47" s="135"/>
+      <c r="H47" s="144"/>
       <c r="I47" s="29"/>
       <c r="J47" s="29"/>
       <c r="K47" s="29"/>
@@ -5043,7 +5055,7 @@
     </row>
     <row r="48" spans="2:12" ht="15.75" customHeight="1">
       <c r="B48" s="13" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C48" s="14">
         <v>80</v>
@@ -5051,14 +5063,14 @@
       <c r="D48" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E48" s="146"/>
+      <c r="E48" s="135"/>
       <c r="F48" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G48" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H48" s="135"/>
+      <c r="H48" s="144"/>
       <c r="I48" s="29"/>
       <c r="J48" s="29"/>
       <c r="K48" s="29"/>
@@ -5066,7 +5078,7 @@
     </row>
     <row r="49" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B49" s="16" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C49" s="17">
         <v>10</v>
@@ -5074,14 +5086,14 @@
       <c r="D49" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E49" s="149"/>
+      <c r="E49" s="136"/>
       <c r="F49" s="19" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G49" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="H49" s="137"/>
+        <v>36</v>
+      </c>
+      <c r="H49" s="145"/>
       <c r="I49" s="29"/>
       <c r="J49" s="29"/>
       <c r="K49" s="29"/>
@@ -5089,7 +5101,7 @@
     </row>
     <row r="50" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B50" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C50" s="9">
         <v>260</v>
@@ -5097,22 +5109,22 @@
       <c r="D50" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E50" s="145">
+      <c r="E50" s="134">
         <v>112</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G50" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H50" s="134" t="s">
-        <v>405</v>
+      <c r="H50" s="143" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="51" spans="2:12" ht="15.75" customHeight="1">
       <c r="B51" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C51" s="14">
         <v>50</v>
@@ -5120,18 +5132,18 @@
       <c r="D51" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E51" s="146"/>
+      <c r="E51" s="135"/>
       <c r="F51" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G51" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H51" s="135"/>
+      <c r="H51" s="144"/>
     </row>
     <row r="52" spans="2:12" ht="15.75" customHeight="1">
       <c r="B52" s="13" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C52" s="14">
         <v>90</v>
@@ -5139,18 +5151,18 @@
       <c r="D52" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E52" s="146"/>
+      <c r="E52" s="135"/>
       <c r="F52" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G52" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H52" s="135"/>
+      <c r="H52" s="144"/>
     </row>
     <row r="53" spans="2:12" ht="15.75" customHeight="1">
       <c r="B53" s="13" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C53" s="14">
         <v>30</v>
@@ -5158,18 +5170,18 @@
       <c r="D53" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E53" s="146"/>
+      <c r="E53" s="135"/>
       <c r="F53" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G53" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H53" s="135"/>
+      <c r="H53" s="144"/>
     </row>
     <row r="54" spans="2:12" ht="15.75" customHeight="1">
       <c r="B54" s="13" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C54" s="14">
         <v>80</v>
@@ -5177,18 +5189,18 @@
       <c r="D54" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E54" s="146"/>
+      <c r="E54" s="135"/>
       <c r="F54" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H54" s="135"/>
+      <c r="H54" s="144"/>
     </row>
     <row r="55" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B55" s="16" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C55" s="17">
         <v>10</v>
@@ -5196,136 +5208,136 @@
       <c r="D55" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E55" s="149"/>
+      <c r="E55" s="136"/>
       <c r="F55" s="19" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G55" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="H55" s="137"/>
+        <v>36</v>
+      </c>
+      <c r="H55" s="145"/>
     </row>
     <row r="56" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B56" s="36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C56" s="46">
         <v>260</v>
       </c>
       <c r="D56" s="63" t="s">
-        <v>180</v>
-      </c>
-      <c r="E56" s="145">
+        <v>177</v>
+      </c>
+      <c r="E56" s="134">
         <v>112</v>
       </c>
       <c r="F56" s="47" t="s">
         <v>7</v>
       </c>
       <c r="G56" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="H56" s="134" t="s">
-        <v>406</v>
+        <v>40</v>
+      </c>
+      <c r="H56" s="143" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="57" spans="2:12" ht="15.75" customHeight="1">
       <c r="B57" s="38" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C57" s="49">
         <v>50</v>
       </c>
       <c r="D57" s="63" t="s">
-        <v>178</v>
-      </c>
-      <c r="E57" s="146"/>
+        <v>175</v>
+      </c>
+      <c r="E57" s="135"/>
       <c r="F57" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G57" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H57" s="135"/>
+      <c r="H57" s="144"/>
     </row>
     <row r="58" spans="2:12" ht="15.75" customHeight="1">
       <c r="B58" s="38" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C58" s="49">
         <v>90</v>
       </c>
       <c r="D58" s="63" t="s">
-        <v>179</v>
-      </c>
-      <c r="E58" s="146"/>
+        <v>176</v>
+      </c>
+      <c r="E58" s="135"/>
       <c r="F58" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G58" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H58" s="135"/>
+      <c r="H58" s="144"/>
     </row>
     <row r="59" spans="2:12" ht="15.75" customHeight="1">
       <c r="B59" s="38" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C59" s="49">
         <v>30</v>
       </c>
       <c r="D59" s="63" t="s">
-        <v>178</v>
-      </c>
-      <c r="E59" s="146"/>
+        <v>175</v>
+      </c>
+      <c r="E59" s="135"/>
       <c r="F59" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G59" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H59" s="135"/>
+      <c r="H59" s="144"/>
     </row>
     <row r="60" spans="2:12" ht="15.75" customHeight="1">
       <c r="B60" s="38" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C60" s="49">
         <v>80</v>
       </c>
       <c r="D60" s="63" t="s">
-        <v>179</v>
-      </c>
-      <c r="E60" s="146"/>
+        <v>176</v>
+      </c>
+      <c r="E60" s="135"/>
       <c r="F60" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G60" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H60" s="135"/>
+      <c r="H60" s="144"/>
     </row>
     <row r="61" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B61" s="51" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C61" s="52">
         <v>10</v>
       </c>
       <c r="D61" s="63" t="s">
-        <v>178</v>
-      </c>
-      <c r="E61" s="149"/>
+        <v>175</v>
+      </c>
+      <c r="E61" s="136"/>
       <c r="F61" s="53" t="s">
         <v>7</v>
       </c>
       <c r="G61" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="H61" s="137"/>
+        <v>36</v>
+      </c>
+      <c r="H61" s="145"/>
     </row>
     <row r="62" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B62" s="36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C62" s="22">
         <v>312</v>
@@ -5333,17 +5345,17 @@
       <c r="D62" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E62" s="145">
+      <c r="E62" s="134">
         <v>143</v>
       </c>
       <c r="F62" s="31" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="G62" s="48" t="s">
-        <v>43</v>
-      </c>
-      <c r="H62" s="134" t="s">
-        <v>403</v>
+        <v>42</v>
+      </c>
+      <c r="H62" s="143" t="s">
+        <v>400</v>
       </c>
       <c r="I62" s="29"/>
       <c r="J62" s="29"/>
@@ -5352,7 +5364,7 @@
     </row>
     <row r="63" spans="2:12" ht="15.75" customHeight="1">
       <c r="B63" s="38" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C63" s="14">
         <v>60</v>
@@ -5360,14 +5372,14 @@
       <c r="D63" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E63" s="146"/>
+      <c r="E63" s="135"/>
       <c r="F63" s="15" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="G63" s="54" t="s">
-        <v>44</v>
-      </c>
-      <c r="H63" s="135"/>
+        <v>43</v>
+      </c>
+      <c r="H63" s="144"/>
       <c r="I63" s="29"/>
       <c r="J63" s="29"/>
       <c r="K63" s="29"/>
@@ -5375,7 +5387,7 @@
     </row>
     <row r="64" spans="2:12" ht="15.75" customHeight="1">
       <c r="B64" s="38" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C64" s="14">
         <v>110</v>
@@ -5383,14 +5395,14 @@
       <c r="D64" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E64" s="146"/>
+      <c r="E64" s="135"/>
       <c r="F64" s="15" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="G64" s="55" t="s">
-        <v>45</v>
-      </c>
-      <c r="H64" s="135"/>
+        <v>44</v>
+      </c>
+      <c r="H64" s="144"/>
       <c r="I64" s="29"/>
       <c r="J64" s="29"/>
       <c r="K64" s="29"/>
@@ -5398,7 +5410,7 @@
     </row>
     <row r="65" spans="2:12" ht="15.75" customHeight="1">
       <c r="B65" s="38" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C65" s="14">
         <v>35</v>
@@ -5406,14 +5418,14 @@
       <c r="D65" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E65" s="146"/>
+      <c r="E65" s="135"/>
       <c r="F65" s="15" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="G65" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H65" s="135"/>
+      <c r="H65" s="144"/>
       <c r="I65" s="29"/>
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
@@ -5421,7 +5433,7 @@
     </row>
     <row r="66" spans="2:12" ht="15.75" customHeight="1">
       <c r="B66" s="38" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C66" s="14">
         <v>95</v>
@@ -5429,14 +5441,14 @@
       <c r="D66" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E66" s="146"/>
+      <c r="E66" s="135"/>
       <c r="F66" s="15" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="G66" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H66" s="135"/>
+      <c r="H66" s="144"/>
       <c r="I66" s="29"/>
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
@@ -5444,20 +5456,20 @@
     </row>
     <row r="67" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B67" s="51" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C67" s="17">
         <v>12</v>
       </c>
       <c r="D67" s="18"/>
-      <c r="E67" s="149"/>
+      <c r="E67" s="136"/>
       <c r="F67" s="19" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="G67" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="H67" s="137"/>
+        <v>45</v>
+      </c>
+      <c r="H67" s="145"/>
       <c r="I67" s="29"/>
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
@@ -5465,7 +5477,7 @@
     </row>
     <row r="68" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B68" s="36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C68" s="22">
         <v>322</v>
@@ -5473,22 +5485,22 @@
       <c r="D68" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E68" s="145">
+      <c r="E68" s="134">
         <v>143</v>
       </c>
       <c r="F68" s="31" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="G68" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="H68" s="134" t="s">
-        <v>403</v>
+        <v>47</v>
+      </c>
+      <c r="H68" s="143" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="69" spans="2:12" ht="15.75" customHeight="1">
       <c r="B69" s="38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C69" s="14">
         <v>70</v>
@@ -5496,18 +5508,18 @@
       <c r="D69" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E69" s="146"/>
+      <c r="E69" s="135"/>
       <c r="F69" s="56" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G69" s="55" t="s">
-        <v>50</v>
-      </c>
-      <c r="H69" s="135"/>
+        <v>49</v>
+      </c>
+      <c r="H69" s="144"/>
     </row>
     <row r="70" spans="2:12" ht="15.75" customHeight="1">
       <c r="B70" s="38" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C70" s="14">
         <v>110</v>
@@ -5515,18 +5527,18 @@
       <c r="D70" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E70" s="146"/>
+      <c r="E70" s="135"/>
       <c r="F70" s="15" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G70" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="H70" s="135"/>
+        <v>44</v>
+      </c>
+      <c r="H70" s="144"/>
     </row>
     <row r="71" spans="2:12" ht="15.75" customHeight="1">
       <c r="B71" s="38" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C71" s="14">
         <v>35</v>
@@ -5534,18 +5546,18 @@
       <c r="D71" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E71" s="146"/>
+      <c r="E71" s="135"/>
       <c r="F71" s="56" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="G71" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H71" s="135"/>
+      <c r="H71" s="144"/>
     </row>
     <row r="72" spans="2:12" ht="15.75" customHeight="1">
       <c r="B72" s="38" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C72" s="14">
         <v>95</v>
@@ -5553,18 +5565,18 @@
       <c r="D72" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E72" s="146"/>
+      <c r="E72" s="135"/>
       <c r="F72" s="15" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G72" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H72" s="135"/>
+      <c r="H72" s="144"/>
     </row>
     <row r="73" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B73" s="51" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C73" s="17">
         <v>12</v>
@@ -5572,18 +5584,18 @@
       <c r="D73" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E73" s="149"/>
+      <c r="E73" s="136"/>
       <c r="F73" s="57" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="G73" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="H73" s="137"/>
-    </row>
-    <row r="74" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
+        <v>45</v>
+      </c>
+      <c r="H73" s="145"/>
+    </row>
+    <row r="74" spans="2:12" ht="31.5" customHeight="1" thickTop="1">
       <c r="B74" s="36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C74" s="46">
         <v>322</v>
@@ -5591,22 +5603,22 @@
       <c r="D74" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E74" s="145">
+      <c r="E74" s="134">
         <v>143</v>
       </c>
       <c r="F74" s="58" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="G74" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="H74" s="134" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="75" spans="2:12" ht="15.75" customHeight="1">
+        <v>432</v>
+      </c>
+      <c r="H74" s="143" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" ht="26.65" customHeight="1">
       <c r="B75" s="38" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C75" s="49">
         <v>70</v>
@@ -5614,18 +5626,18 @@
       <c r="D75" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E75" s="146"/>
+      <c r="E75" s="135"/>
       <c r="F75" s="56" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G75" s="54" t="s">
-        <v>53</v>
-      </c>
-      <c r="H75" s="135"/>
+        <v>428</v>
+      </c>
+      <c r="H75" s="144"/>
     </row>
     <row r="76" spans="2:12" ht="15.75" customHeight="1">
       <c r="B76" s="38" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C76" s="49">
         <v>110</v>
@@ -5633,18 +5645,18 @@
       <c r="D76" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E76" s="146"/>
+      <c r="E76" s="135"/>
       <c r="F76" s="56" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G76" s="55" t="s">
-        <v>45</v>
-      </c>
-      <c r="H76" s="135"/>
+        <v>429</v>
+      </c>
+      <c r="H76" s="144"/>
     </row>
     <row r="77" spans="2:12" ht="15.75" customHeight="1">
       <c r="B77" s="38" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C77" s="49">
         <v>35</v>
@@ -5652,18 +5664,18 @@
       <c r="D77" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E77" s="146"/>
+      <c r="E77" s="135"/>
       <c r="F77" s="56" t="s">
-        <v>427</v>
-      </c>
-      <c r="G77" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="H77" s="135"/>
+        <v>424</v>
+      </c>
+      <c r="G77" s="151" t="s">
+        <v>430</v>
+      </c>
+      <c r="H77" s="144"/>
     </row>
     <row r="78" spans="2:12" ht="15.75" customHeight="1">
       <c r="B78" s="38" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C78" s="49">
         <v>95</v>
@@ -5671,18 +5683,18 @@
       <c r="D78" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E78" s="146"/>
+      <c r="E78" s="135"/>
       <c r="F78" s="56" t="s">
-        <v>192</v>
-      </c>
-      <c r="G78" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="H78" s="135"/>
+        <v>189</v>
+      </c>
+      <c r="G78" s="151" t="s">
+        <v>430</v>
+      </c>
+      <c r="H78" s="144"/>
     </row>
     <row r="79" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B79" s="51" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C79" s="52">
         <v>12</v>
@@ -5690,18 +5702,18 @@
       <c r="D79" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E79" s="149"/>
+      <c r="E79" s="136"/>
       <c r="F79" s="57" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G79" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="H79" s="137"/>
+        <v>431</v>
+      </c>
+      <c r="H79" s="145"/>
     </row>
     <row r="80" spans="2:12" ht="38.65" thickTop="1">
       <c r="B80" s="40" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C80" s="9">
         <v>310</v>
@@ -5709,17 +5721,17 @@
       <c r="D80" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E80" s="145">
+      <c r="E80" s="134">
         <v>112</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G80" s="59" t="s">
-        <v>55</v>
-      </c>
-      <c r="H80" s="134" t="s">
-        <v>403</v>
+        <v>52</v>
+      </c>
+      <c r="H80" s="143" t="s">
+        <v>400</v>
       </c>
       <c r="I80" s="29"/>
       <c r="J80" s="29"/>
@@ -5728,7 +5740,7 @@
     </row>
     <row r="81" spans="2:12" ht="15.75" customHeight="1">
       <c r="B81" s="44" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C81" s="14">
         <v>60</v>
@@ -5736,14 +5748,14 @@
       <c r="D81" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E81" s="146"/>
+      <c r="E81" s="135"/>
       <c r="F81" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G81" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H81" s="135"/>
+      <c r="H81" s="144"/>
       <c r="I81" s="29"/>
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
@@ -5751,7 +5763,7 @@
     </row>
     <row r="82" spans="2:12" ht="15.75" customHeight="1">
       <c r="B82" s="44" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C82" s="14">
         <v>100</v>
@@ -5759,14 +5771,14 @@
       <c r="D82" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E82" s="146"/>
+      <c r="E82" s="135"/>
       <c r="F82" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G82" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H82" s="135"/>
+      <c r="H82" s="144"/>
       <c r="I82" s="29"/>
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
@@ -5774,7 +5786,7 @@
     </row>
     <row r="83" spans="2:12" ht="15.75" customHeight="1">
       <c r="B83" s="44" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C83" s="14">
         <v>40</v>
@@ -5782,14 +5794,14 @@
       <c r="D83" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E83" s="146"/>
+      <c r="E83" s="135"/>
       <c r="F83" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G83" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H83" s="135"/>
+      <c r="H83" s="144"/>
       <c r="I83" s="29"/>
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
@@ -5797,7 +5809,7 @@
     </row>
     <row r="84" spans="2:12" ht="15.75" customHeight="1">
       <c r="B84" s="44" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C84" s="14">
         <v>90</v>
@@ -5805,14 +5817,14 @@
       <c r="D84" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E84" s="146"/>
+      <c r="E84" s="135"/>
       <c r="F84" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G84" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H84" s="135"/>
+      <c r="H84" s="144"/>
       <c r="I84" s="29"/>
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
@@ -5820,7 +5832,7 @@
     </row>
     <row r="85" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B85" s="60" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C85" s="24">
         <v>20</v>
@@ -5828,14 +5840,14 @@
       <c r="D85" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E85" s="147"/>
+      <c r="E85" s="137"/>
       <c r="F85" s="26" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G85" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="H85" s="137"/>
+        <v>36</v>
+      </c>
+      <c r="H85" s="145"/>
       <c r="I85" s="29"/>
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
@@ -5843,7 +5855,7 @@
     </row>
     <row r="86" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B86" s="8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C86" s="9">
         <v>400</v>
@@ -5851,17 +5863,17 @@
       <c r="D86" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E86" s="150">
+      <c r="E86" s="138">
         <v>125</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G86" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H86" s="134" t="s">
-        <v>402</v>
+      <c r="H86" s="143" t="s">
+        <v>399</v>
       </c>
       <c r="I86" s="29"/>
       <c r="J86" s="29"/>
@@ -5870,7 +5882,7 @@
     </row>
     <row r="87" spans="2:12" ht="15.75" customHeight="1">
       <c r="B87" s="13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C87" s="14">
         <v>70</v>
@@ -5878,14 +5890,14 @@
       <c r="D87" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E87" s="146"/>
+      <c r="E87" s="135"/>
       <c r="F87" s="15" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G87" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H87" s="135"/>
+      <c r="H87" s="144"/>
       <c r="I87" s="29"/>
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
@@ -5893,7 +5905,7 @@
     </row>
     <row r="88" spans="2:12" ht="15.75" customHeight="1">
       <c r="B88" s="13" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C88" s="14">
         <v>130</v>
@@ -5901,14 +5913,14 @@
       <c r="D88" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E88" s="146"/>
+      <c r="E88" s="135"/>
       <c r="F88" s="15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G88" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="H88" s="135"/>
+        <v>44</v>
+      </c>
+      <c r="H88" s="144"/>
       <c r="I88" s="29"/>
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
@@ -5916,7 +5928,7 @@
     </row>
     <row r="89" spans="2:12" ht="15.75" customHeight="1">
       <c r="B89" s="13" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C89" s="14">
         <v>50</v>
@@ -5924,14 +5936,14 @@
       <c r="D89" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E89" s="146"/>
+      <c r="E89" s="135"/>
       <c r="F89" s="15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G89" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H89" s="135"/>
+      <c r="H89" s="144"/>
       <c r="I89" s="29"/>
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
@@ -5939,7 +5951,7 @@
     </row>
     <row r="90" spans="2:12" ht="15.75" customHeight="1">
       <c r="B90" s="13" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C90" s="14">
         <v>120</v>
@@ -5947,14 +5959,14 @@
       <c r="D90" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E90" s="146"/>
+      <c r="E90" s="135"/>
       <c r="F90" s="15" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G90" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H90" s="135"/>
+      <c r="H90" s="144"/>
       <c r="I90" s="29"/>
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
@@ -5962,7 +5974,7 @@
     </row>
     <row r="91" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B91" s="16" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C91" s="17">
         <v>30</v>
@@ -5970,14 +5982,14 @@
       <c r="D91" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E91" s="149"/>
+      <c r="E91" s="136"/>
       <c r="F91" s="19" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G91" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H91" s="137"/>
+      <c r="H91" s="145"/>
       <c r="I91" s="29"/>
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
@@ -5985,125 +5997,125 @@
     </row>
     <row r="92" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B92" s="61" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C92" s="22">
         <v>440</v>
       </c>
       <c r="D92" s="62" t="s">
+        <v>316</v>
+      </c>
+      <c r="E92" s="134">
+        <v>125</v>
+      </c>
+      <c r="F92" s="47" t="s">
+        <v>63</v>
+      </c>
+      <c r="G92" s="48" t="s">
         <v>319</v>
       </c>
-      <c r="E92" s="145">
-        <v>125</v>
-      </c>
-      <c r="F92" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="G92" s="48" t="s">
-        <v>322</v>
-      </c>
-      <c r="H92" s="141" t="s">
-        <v>407</v>
+      <c r="H92" s="146" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="93" spans="2:12" ht="15.75" customHeight="1">
       <c r="B93" s="44" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C93" s="14">
         <v>80</v>
       </c>
       <c r="D93" s="63" t="s">
-        <v>67</v>
-      </c>
-      <c r="E93" s="146"/>
+        <v>64</v>
+      </c>
+      <c r="E93" s="135"/>
       <c r="F93" s="50" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G93" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H93" s="139"/>
+      <c r="H93" s="147"/>
     </row>
     <row r="94" spans="2:12" ht="15.75" customHeight="1">
       <c r="B94" s="44" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C94" s="14">
         <v>140</v>
       </c>
       <c r="D94" s="63" t="s">
-        <v>68</v>
-      </c>
-      <c r="E94" s="146"/>
+        <v>65</v>
+      </c>
+      <c r="E94" s="135"/>
       <c r="F94" s="50" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G94" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="H94" s="139"/>
+        <v>44</v>
+      </c>
+      <c r="H94" s="147"/>
     </row>
     <row r="95" spans="2:12" ht="15.75" customHeight="1">
       <c r="B95" s="44" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C95" s="14">
         <v>55</v>
       </c>
       <c r="D95" s="63" t="s">
-        <v>67</v>
-      </c>
-      <c r="E95" s="146"/>
+        <v>64</v>
+      </c>
+      <c r="E95" s="135"/>
       <c r="F95" s="50" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G95" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H95" s="139"/>
+      <c r="H95" s="147"/>
     </row>
     <row r="96" spans="2:12" ht="15.75" customHeight="1">
       <c r="B96" s="44" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C96" s="14">
         <v>130</v>
       </c>
       <c r="D96" s="63" t="s">
-        <v>68</v>
-      </c>
-      <c r="E96" s="146"/>
+        <v>65</v>
+      </c>
+      <c r="E96" s="135"/>
       <c r="F96" s="50" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G96" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H96" s="139"/>
+      <c r="H96" s="147"/>
     </row>
     <row r="97" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B97" s="64" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C97" s="17">
         <v>35</v>
       </c>
       <c r="D97" s="65" t="s">
-        <v>67</v>
-      </c>
-      <c r="E97" s="149"/>
+        <v>64</v>
+      </c>
+      <c r="E97" s="136"/>
       <c r="F97" s="53" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G97" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="H97" s="140"/>
+        <v>45</v>
+      </c>
+      <c r="H97" s="148"/>
     </row>
     <row r="98" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B98" s="36" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C98" s="22">
         <v>440</v>
@@ -6111,22 +6123,22 @@
       <c r="D98" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E98" s="145">
+      <c r="E98" s="134">
         <v>125</v>
       </c>
       <c r="F98" s="58" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="G98" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="H98" s="134" t="s">
-        <v>403</v>
+        <v>67</v>
+      </c>
+      <c r="H98" s="143" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="99" spans="2:8" ht="15.75" customHeight="1">
       <c r="B99" s="38" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C99" s="14">
         <v>75</v>
@@ -6134,18 +6146,18 @@
       <c r="D99" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E99" s="146"/>
+      <c r="E99" s="135"/>
       <c r="F99" s="56" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G99" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="H99" s="135"/>
+        <v>229</v>
+      </c>
+      <c r="H99" s="144"/>
     </row>
     <row r="100" spans="2:8" ht="15.75" customHeight="1">
       <c r="B100" s="38" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C100" s="14">
         <v>140</v>
@@ -6153,18 +6165,18 @@
       <c r="D100" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E100" s="146"/>
+      <c r="E100" s="135"/>
       <c r="F100" s="56" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G100" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="H100" s="135"/>
+        <v>44</v>
+      </c>
+      <c r="H100" s="144"/>
     </row>
     <row r="101" spans="2:8" ht="15.75" customHeight="1">
       <c r="B101" s="38" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C101" s="14">
         <v>55</v>
@@ -6172,18 +6184,18 @@
       <c r="D101" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E101" s="146"/>
+      <c r="E101" s="135"/>
       <c r="F101" s="56" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G101" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H101" s="135"/>
+      <c r="H101" s="144"/>
     </row>
     <row r="102" spans="2:8" ht="15.75" customHeight="1">
       <c r="B102" s="38" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C102" s="14">
         <v>130</v>
@@ -6191,18 +6203,18 @@
       <c r="D102" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E102" s="146"/>
+      <c r="E102" s="135"/>
       <c r="F102" s="56" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G102" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H102" s="135"/>
+      <c r="H102" s="144"/>
     </row>
     <row r="103" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B103" s="51" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C103" s="17">
         <v>40</v>
@@ -6210,18 +6222,18 @@
       <c r="D103" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E103" s="149"/>
+      <c r="E103" s="136"/>
       <c r="F103" s="57" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="G103" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="H103" s="137"/>
+        <v>69</v>
+      </c>
+      <c r="H103" s="145"/>
     </row>
     <row r="104" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B104" s="61" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C104" s="22">
         <v>450</v>
@@ -6229,22 +6241,22 @@
       <c r="D104" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E104" s="145">
+      <c r="E104" s="134">
         <v>125</v>
       </c>
       <c r="F104" s="31" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G104" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="H104" s="134" t="s">
-        <v>403</v>
+      <c r="H104" s="143" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="105" spans="2:8" ht="15.75" customHeight="1">
       <c r="B105" s="44" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C105" s="14">
         <v>80</v>
@@ -6252,18 +6264,18 @@
       <c r="D105" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E105" s="146"/>
+      <c r="E105" s="135"/>
       <c r="F105" s="15" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G105" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H105" s="135"/>
+      <c r="H105" s="144"/>
     </row>
     <row r="106" spans="2:8" ht="15.75" customHeight="1">
       <c r="B106" s="44" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C106" s="14">
         <v>140</v>
@@ -6271,18 +6283,18 @@
       <c r="D106" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E106" s="146"/>
+      <c r="E106" s="135"/>
       <c r="F106" s="15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G106" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="H106" s="135"/>
+        <v>44</v>
+      </c>
+      <c r="H106" s="144"/>
     </row>
     <row r="107" spans="2:8" ht="15.75" customHeight="1">
       <c r="B107" s="44" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C107" s="14">
         <v>60</v>
@@ -6290,18 +6302,18 @@
       <c r="D107" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E107" s="146"/>
+      <c r="E107" s="135"/>
       <c r="F107" s="15" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G107" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H107" s="135"/>
+      <c r="H107" s="144"/>
     </row>
     <row r="108" spans="2:8" ht="15.75" customHeight="1">
       <c r="B108" s="44" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C108" s="14">
         <v>130</v>
@@ -6309,18 +6321,18 @@
       <c r="D108" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E108" s="146"/>
+      <c r="E108" s="135"/>
       <c r="F108" s="15" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G108" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H108" s="135"/>
+      <c r="H108" s="144"/>
     </row>
     <row r="109" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B109" s="66" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C109" s="33">
         <v>40</v>
@@ -6328,18 +6340,18 @@
       <c r="D109" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E109" s="147"/>
+      <c r="E109" s="137"/>
       <c r="F109" s="34" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G109" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="H109" s="137"/>
+      <c r="H109" s="145"/>
     </row>
     <row r="110" spans="2:8" ht="25.5" customHeight="1" thickTop="1">
       <c r="B110" s="36" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C110" s="22">
         <v>450</v>
@@ -6347,22 +6359,22 @@
       <c r="D110" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E110" s="145">
+      <c r="E110" s="134">
         <v>125</v>
       </c>
       <c r="F110" s="72" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G110" s="37" t="s">
-        <v>357</v>
-      </c>
-      <c r="H110" s="134" t="s">
-        <v>403</v>
+        <v>354</v>
+      </c>
+      <c r="H110" s="143" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="111" spans="2:8" ht="15.75" customHeight="1">
       <c r="B111" s="38" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C111" s="14">
         <v>80</v>
@@ -6370,18 +6382,18 @@
       <c r="D111" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E111" s="146"/>
+      <c r="E111" s="135"/>
       <c r="F111" s="56" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="G111" s="54" t="s">
-        <v>356</v>
-      </c>
-      <c r="H111" s="135"/>
+        <v>353</v>
+      </c>
+      <c r="H111" s="144"/>
     </row>
     <row r="112" spans="2:8" ht="15.75" customHeight="1">
       <c r="B112" s="38" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C112" s="14">
         <v>140</v>
@@ -6389,18 +6401,18 @@
       <c r="D112" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E112" s="146"/>
+      <c r="E112" s="135"/>
       <c r="F112" s="56" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G112" s="54" t="s">
-        <v>360</v>
-      </c>
-      <c r="H112" s="135"/>
+        <v>357</v>
+      </c>
+      <c r="H112" s="144"/>
     </row>
     <row r="113" spans="2:12" ht="15.75" customHeight="1">
       <c r="B113" s="38" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C113" s="14">
         <v>60</v>
@@ -6408,18 +6420,18 @@
       <c r="D113" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E113" s="146"/>
+      <c r="E113" s="135"/>
       <c r="F113" s="56" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="G113" s="54" t="s">
-        <v>356</v>
-      </c>
-      <c r="H113" s="135"/>
+        <v>353</v>
+      </c>
+      <c r="H113" s="144"/>
     </row>
     <row r="114" spans="2:12" ht="15.75" customHeight="1">
       <c r="B114" s="38" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C114" s="14">
         <v>130</v>
@@ -6427,18 +6439,18 @@
       <c r="D114" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E114" s="146"/>
+      <c r="E114" s="135"/>
       <c r="F114" s="56" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="G114" s="54" t="s">
-        <v>356</v>
-      </c>
-      <c r="H114" s="135"/>
+        <v>353</v>
+      </c>
+      <c r="H114" s="144"/>
     </row>
     <row r="115" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B115" s="51" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C115" s="17">
         <v>40</v>
@@ -6446,18 +6458,18 @@
       <c r="D115" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E115" s="149"/>
+      <c r="E115" s="136"/>
       <c r="F115" s="57" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="G115" s="54" t="s">
-        <v>365</v>
-      </c>
-      <c r="H115" s="137"/>
+        <v>362</v>
+      </c>
+      <c r="H115" s="145"/>
     </row>
     <row r="116" spans="2:12" ht="25.9" thickTop="1">
       <c r="B116" s="68" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C116" s="22">
         <v>630</v>
@@ -6465,17 +6477,17 @@
       <c r="D116" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E116" s="145">
+      <c r="E116" s="134">
         <v>143</v>
       </c>
       <c r="F116" s="31" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G116" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="H116" s="134" t="s">
-        <v>414</v>
+        <v>73</v>
+      </c>
+      <c r="H116" s="143" t="s">
+        <v>411</v>
       </c>
       <c r="I116" s="29"/>
       <c r="J116" s="29"/>
@@ -6484,7 +6496,7 @@
     </row>
     <row r="117" spans="2:12" ht="15.75" customHeight="1">
       <c r="B117" s="70" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C117" s="14">
         <v>110</v>
@@ -6492,14 +6504,14 @@
       <c r="D117" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E117" s="146"/>
+      <c r="E117" s="135"/>
       <c r="F117" s="15" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G117" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H117" s="135"/>
+      <c r="H117" s="144"/>
       <c r="I117" s="29"/>
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
@@ -6507,7 +6519,7 @@
     </row>
     <row r="118" spans="2:12" ht="15.75" customHeight="1">
       <c r="B118" s="70" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C118" s="14">
         <v>190</v>
@@ -6515,14 +6527,14 @@
       <c r="D118" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E118" s="146"/>
+      <c r="E118" s="135"/>
       <c r="F118" s="15" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G118" s="55" t="s">
-        <v>45</v>
-      </c>
-      <c r="H118" s="135"/>
+        <v>44</v>
+      </c>
+      <c r="H118" s="144"/>
       <c r="I118" s="29"/>
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
@@ -6530,7 +6542,7 @@
     </row>
     <row r="119" spans="2:12" ht="15.75" customHeight="1">
       <c r="B119" s="70" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C119" s="14">
         <v>90</v>
@@ -6538,14 +6550,14 @@
       <c r="D119" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E119" s="146"/>
+      <c r="E119" s="135"/>
       <c r="F119" s="15" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G119" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H119" s="135"/>
+      <c r="H119" s="144"/>
       <c r="I119" s="29"/>
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
@@ -6553,7 +6565,7 @@
     </row>
     <row r="120" spans="2:12" ht="15.75" customHeight="1">
       <c r="B120" s="70" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C120" s="14">
         <v>180</v>
@@ -6561,14 +6573,14 @@
       <c r="D120" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E120" s="146"/>
+      <c r="E120" s="135"/>
       <c r="F120" s="15" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G120" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H120" s="135"/>
+      <c r="H120" s="144"/>
       <c r="I120" s="29"/>
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
@@ -6576,7 +6588,7 @@
     </row>
     <row r="121" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B121" s="71" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C121" s="24">
         <v>60</v>
@@ -6584,14 +6596,14 @@
       <c r="D121" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E121" s="147"/>
+      <c r="E121" s="137"/>
       <c r="F121" s="26" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G121" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="H121" s="137"/>
+        <v>45</v>
+      </c>
+      <c r="H121" s="145"/>
       <c r="I121" s="29"/>
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
@@ -6599,7 +6611,7 @@
     </row>
     <row r="122" spans="2:12" ht="25.9" thickTop="1">
       <c r="B122" s="36" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C122" s="22">
         <v>650</v>
@@ -6607,17 +6619,17 @@
       <c r="D122" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E122" s="145">
+      <c r="E122" s="134">
         <v>125</v>
       </c>
       <c r="F122" s="72" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G122" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="H122" s="134" t="s">
-        <v>403</v>
+        <v>75</v>
+      </c>
+      <c r="H122" s="143" t="s">
+        <v>400</v>
       </c>
       <c r="I122" s="29"/>
       <c r="J122" s="29"/>
@@ -6626,7 +6638,7 @@
     </row>
     <row r="123" spans="2:12" ht="15.75" customHeight="1">
       <c r="B123" s="38" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C123" s="14">
         <v>110</v>
@@ -6634,14 +6646,14 @@
       <c r="D123" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E123" s="146"/>
+      <c r="E123" s="135"/>
       <c r="F123" s="56" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G123" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H123" s="135"/>
+      <c r="H123" s="144"/>
       <c r="I123" s="29"/>
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
@@ -6649,7 +6661,7 @@
     </row>
     <row r="124" spans="2:12" ht="15.75" customHeight="1">
       <c r="B124" s="38" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C124" s="14">
         <v>200</v>
@@ -6657,14 +6669,14 @@
       <c r="D124" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E124" s="146"/>
+      <c r="E124" s="135"/>
       <c r="F124" s="56" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G124" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="H124" s="135"/>
+        <v>44</v>
+      </c>
+      <c r="H124" s="144"/>
       <c r="I124" s="29"/>
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
@@ -6672,7 +6684,7 @@
     </row>
     <row r="125" spans="2:12" ht="15.75" customHeight="1">
       <c r="B125" s="38" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C125" s="14">
         <v>90</v>
@@ -6680,14 +6692,14 @@
       <c r="D125" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E125" s="146"/>
+      <c r="E125" s="135"/>
       <c r="F125" s="56" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="G125" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H125" s="135"/>
+      <c r="H125" s="144"/>
       <c r="I125" s="29"/>
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
@@ -6695,7 +6707,7 @@
     </row>
     <row r="126" spans="2:12" ht="15.75" customHeight="1">
       <c r="B126" s="38" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C126" s="14">
         <v>190</v>
@@ -6703,14 +6715,14 @@
       <c r="D126" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E126" s="146"/>
+      <c r="E126" s="135"/>
       <c r="F126" s="56" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G126" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H126" s="135"/>
+      <c r="H126" s="144"/>
       <c r="I126" s="29"/>
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
@@ -6718,7 +6730,7 @@
     </row>
     <row r="127" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B127" s="39" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C127" s="24">
         <v>60</v>
@@ -6726,14 +6738,14 @@
       <c r="D127" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E127" s="147"/>
+      <c r="E127" s="137"/>
       <c r="F127" s="73" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G127" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="H127" s="137"/>
+        <v>45</v>
+      </c>
+      <c r="H127" s="145"/>
       <c r="I127" s="29"/>
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
@@ -6741,7 +6753,7 @@
     </row>
     <row r="128" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B128" s="68" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C128" s="22">
         <v>630</v>
@@ -6749,22 +6761,22 @@
       <c r="D128" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E128" s="145">
+      <c r="E128" s="134">
         <v>143</v>
       </c>
       <c r="F128" s="72" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="G128" s="48" t="s">
-        <v>83</v>
-      </c>
-      <c r="H128" s="134" t="s">
-        <v>403</v>
+        <v>80</v>
+      </c>
+      <c r="H128" s="143" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="129" spans="2:12" ht="15.75" customHeight="1">
       <c r="B129" s="74" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C129" s="14">
         <v>110</v>
@@ -6772,18 +6784,18 @@
       <c r="D129" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E129" s="146"/>
+      <c r="E129" s="135"/>
       <c r="F129" s="56" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="G129" s="77" t="s">
-        <v>118</v>
-      </c>
-      <c r="H129" s="135"/>
+        <v>115</v>
+      </c>
+      <c r="H129" s="144"/>
     </row>
     <row r="130" spans="2:12" ht="15.75" customHeight="1">
       <c r="B130" s="70" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C130" s="14">
         <v>190</v>
@@ -6791,18 +6803,18 @@
       <c r="D130" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E130" s="146"/>
+      <c r="E130" s="135"/>
       <c r="F130" s="56" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="G130" s="55" t="s">
-        <v>45</v>
-      </c>
-      <c r="H130" s="135"/>
+        <v>44</v>
+      </c>
+      <c r="H130" s="144"/>
     </row>
     <row r="131" spans="2:12" ht="15.75" customHeight="1">
       <c r="B131" s="74" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C131" s="14">
         <v>90</v>
@@ -6810,18 +6822,18 @@
       <c r="D131" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E131" s="146"/>
+      <c r="E131" s="135"/>
       <c r="F131" s="56" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="G131" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H131" s="135"/>
+      <c r="H131" s="144"/>
     </row>
     <row r="132" spans="2:12" ht="15.75" customHeight="1">
       <c r="B132" s="74" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C132" s="14">
         <v>180</v>
@@ -6829,18 +6841,18 @@
       <c r="D132" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E132" s="146"/>
+      <c r="E132" s="135"/>
       <c r="F132" s="56" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G132" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H132" s="135"/>
+      <c r="H132" s="144"/>
     </row>
     <row r="133" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B133" s="71" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C133" s="24">
         <v>60</v>
@@ -6848,18 +6860,18 @@
       <c r="D133" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E133" s="147"/>
+      <c r="E133" s="137"/>
       <c r="F133" s="73" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G133" s="27" t="s">
-        <v>85</v>
-      </c>
-      <c r="H133" s="137"/>
+        <v>82</v>
+      </c>
+      <c r="H133" s="145"/>
     </row>
     <row r="134" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B134" s="75" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C134" s="76">
         <v>580</v>
@@ -6867,17 +6879,17 @@
       <c r="D134" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E134" s="148">
+      <c r="E134" s="139">
         <v>143</v>
       </c>
       <c r="F134" s="28" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G134" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H134" s="134" t="s">
-        <v>402</v>
+      <c r="H134" s="143" t="s">
+        <v>399</v>
       </c>
       <c r="I134" s="29"/>
       <c r="J134" s="29"/>
@@ -6886,7 +6898,7 @@
     </row>
     <row r="135" spans="2:12" ht="15.75" customHeight="1">
       <c r="B135" s="44" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C135" s="14">
         <v>100</v>
@@ -6894,14 +6906,14 @@
       <c r="D135" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E135" s="146"/>
+      <c r="E135" s="135"/>
       <c r="F135" s="15" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G135" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H135" s="135"/>
+      <c r="H135" s="144"/>
       <c r="I135" s="29"/>
       <c r="J135" s="29"/>
       <c r="K135" s="29"/>
@@ -6909,7 +6921,7 @@
     </row>
     <row r="136" spans="2:12" ht="15.75" customHeight="1">
       <c r="B136" s="44" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C136" s="14">
         <v>180</v>
@@ -6917,14 +6929,14 @@
       <c r="D136" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E136" s="146"/>
+      <c r="E136" s="135"/>
       <c r="F136" s="15" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G136" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="H136" s="135"/>
+        <v>44</v>
+      </c>
+      <c r="H136" s="144"/>
       <c r="I136" s="29"/>
       <c r="J136" s="29"/>
       <c r="K136" s="29"/>
@@ -6932,7 +6944,7 @@
     </row>
     <row r="137" spans="2:12" ht="15.75" customHeight="1">
       <c r="B137" s="44" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C137" s="14">
         <v>80</v>
@@ -6940,14 +6952,14 @@
       <c r="D137" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E137" s="146"/>
+      <c r="E137" s="135"/>
       <c r="F137" s="15" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G137" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H137" s="135"/>
+      <c r="H137" s="144"/>
       <c r="I137" s="29"/>
       <c r="J137" s="29"/>
       <c r="K137" s="29"/>
@@ -6955,7 +6967,7 @@
     </row>
     <row r="138" spans="2:12" ht="15.75" customHeight="1">
       <c r="B138" s="44" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C138" s="14">
         <v>170</v>
@@ -6963,14 +6975,14 @@
       <c r="D138" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E138" s="146"/>
+      <c r="E138" s="135"/>
       <c r="F138" s="15" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G138" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H138" s="135"/>
+      <c r="H138" s="144"/>
       <c r="I138" s="29"/>
       <c r="J138" s="29"/>
       <c r="K138" s="29"/>
@@ -6978,7 +6990,7 @@
     </row>
     <row r="139" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B139" s="64" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C139" s="17">
         <v>50</v>
@@ -6986,14 +6998,14 @@
       <c r="D139" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E139" s="149"/>
+      <c r="E139" s="136"/>
       <c r="F139" s="19" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G139" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="H139" s="137"/>
+        <v>45</v>
+      </c>
+      <c r="H139" s="145"/>
       <c r="I139" s="29"/>
       <c r="J139" s="29"/>
       <c r="K139" s="29"/>
@@ -7001,7 +7013,7 @@
     </row>
     <row r="140" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B140" s="61" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C140" s="22">
         <v>580</v>
@@ -7009,22 +7021,22 @@
       <c r="D140" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E140" s="145">
+      <c r="E140" s="134">
         <v>143</v>
       </c>
       <c r="F140" s="31" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G140" s="77" t="s">
-        <v>91</v>
-      </c>
-      <c r="H140" s="134" t="s">
-        <v>403</v>
+        <v>88</v>
+      </c>
+      <c r="H140" s="143" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="141" spans="2:12" ht="15.75" customHeight="1">
       <c r="B141" s="44" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C141" s="14">
         <v>100</v>
@@ -7032,18 +7044,18 @@
       <c r="D141" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E141" s="146"/>
+      <c r="E141" s="135"/>
       <c r="F141" s="15" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G141" s="77" t="s">
-        <v>93</v>
-      </c>
-      <c r="H141" s="135"/>
+        <v>90</v>
+      </c>
+      <c r="H141" s="144"/>
     </row>
     <row r="142" spans="2:12" ht="15.75" customHeight="1">
       <c r="B142" s="44" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C142" s="14">
         <v>180</v>
@@ -7051,18 +7063,18 @@
       <c r="D142" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E142" s="146"/>
+      <c r="E142" s="135"/>
       <c r="F142" s="15" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G142" s="78" t="s">
-        <v>94</v>
-      </c>
-      <c r="H142" s="135"/>
+        <v>91</v>
+      </c>
+      <c r="H142" s="144"/>
     </row>
     <row r="143" spans="2:12" ht="15.75" customHeight="1">
       <c r="B143" s="44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C143" s="14">
         <v>80</v>
@@ -7070,18 +7082,18 @@
       <c r="D143" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E143" s="146"/>
+      <c r="E143" s="135"/>
       <c r="F143" s="15" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G143" s="77" t="s">
-        <v>93</v>
-      </c>
-      <c r="H143" s="135"/>
+        <v>90</v>
+      </c>
+      <c r="H143" s="144"/>
     </row>
     <row r="144" spans="2:12" ht="15.75" customHeight="1">
       <c r="B144" s="44" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C144" s="14">
         <v>170</v>
@@ -7089,18 +7101,18 @@
       <c r="D144" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E144" s="146"/>
+      <c r="E144" s="135"/>
       <c r="F144" s="15" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G144" s="77" t="s">
-        <v>93</v>
-      </c>
-      <c r="H144" s="135"/>
+        <v>90</v>
+      </c>
+      <c r="H144" s="144"/>
     </row>
     <row r="145" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B145" s="64" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C145" s="17">
         <v>50</v>
@@ -7108,249 +7120,249 @@
       <c r="D145" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E145" s="149"/>
+      <c r="E145" s="136"/>
       <c r="F145" s="19" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G145" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="H145" s="137"/>
+        <v>93</v>
+      </c>
+      <c r="H145" s="145"/>
     </row>
     <row r="146" spans="1:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B146" s="112" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C146" s="22">
         <v>615</v>
       </c>
       <c r="D146" s="79" t="s">
-        <v>320</v>
-      </c>
-      <c r="E146" s="145">
+        <v>317</v>
+      </c>
+      <c r="E146" s="134">
         <v>143</v>
       </c>
       <c r="F146" s="47" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G146" s="48" t="s">
-        <v>321</v>
-      </c>
-      <c r="H146" s="141" t="s">
-        <v>407</v>
+        <v>318</v>
+      </c>
+      <c r="H146" s="146" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="147" spans="1:12" ht="15.75" customHeight="1">
       <c r="B147" s="44" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C147" s="14">
         <v>105</v>
       </c>
       <c r="D147" s="80" t="s">
-        <v>97</v>
-      </c>
-      <c r="E147" s="146"/>
+        <v>94</v>
+      </c>
+      <c r="E147" s="135"/>
       <c r="F147" s="50" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G147" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H147" s="139"/>
+      <c r="H147" s="147"/>
     </row>
     <row r="148" spans="1:12" ht="15.75" customHeight="1">
       <c r="B148" s="44" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C148" s="14">
         <v>190</v>
       </c>
       <c r="D148" s="80" t="s">
-        <v>98</v>
-      </c>
-      <c r="E148" s="146"/>
+        <v>95</v>
+      </c>
+      <c r="E148" s="135"/>
       <c r="F148" s="50" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G148" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="H148" s="139"/>
+        <v>44</v>
+      </c>
+      <c r="H148" s="147"/>
     </row>
     <row r="149" spans="1:12" ht="15.75" customHeight="1">
       <c r="B149" s="44" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C149" s="14">
         <v>85</v>
       </c>
       <c r="D149" s="80" t="s">
-        <v>97</v>
-      </c>
-      <c r="E149" s="146"/>
+        <v>94</v>
+      </c>
+      <c r="E149" s="135"/>
       <c r="F149" s="50" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G149" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H149" s="139"/>
+      <c r="H149" s="147"/>
     </row>
     <row r="150" spans="1:12" ht="15.75" customHeight="1">
       <c r="B150" s="44" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C150" s="14">
         <v>180</v>
       </c>
       <c r="D150" s="80" t="s">
-        <v>98</v>
-      </c>
-      <c r="E150" s="146"/>
+        <v>95</v>
+      </c>
+      <c r="E150" s="135"/>
       <c r="F150" s="50" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G150" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H150" s="139"/>
+      <c r="H150" s="147"/>
     </row>
     <row r="151" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B151" s="64" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C151" s="17">
         <v>55</v>
       </c>
       <c r="D151" s="81" t="s">
-        <v>97</v>
-      </c>
-      <c r="E151" s="149"/>
+        <v>94</v>
+      </c>
+      <c r="E151" s="136"/>
       <c r="F151" s="53" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G151" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="H151" s="140"/>
+        <v>45</v>
+      </c>
+      <c r="H151" s="148"/>
     </row>
     <row r="152" spans="1:12" ht="13.5" thickTop="1">
       <c r="A152" s="111"/>
       <c r="B152" s="110" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C152" s="22">
         <v>615</v>
       </c>
       <c r="D152" s="109" t="s">
-        <v>378</v>
-      </c>
-      <c r="E152" s="145">
+        <v>375</v>
+      </c>
+      <c r="E152" s="134">
         <v>143</v>
       </c>
       <c r="F152" s="47" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G152" s="114" t="s">
-        <v>374</v>
-      </c>
-      <c r="H152" s="141" t="s">
-        <v>407</v>
+        <v>371</v>
+      </c>
+      <c r="H152" s="146" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="153" spans="1:12" ht="15.75" customHeight="1">
       <c r="B153" s="113" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C153" s="14">
         <v>105</v>
       </c>
       <c r="D153" s="109" t="s">
-        <v>371</v>
-      </c>
-      <c r="E153" s="146"/>
+        <v>368</v>
+      </c>
+      <c r="E153" s="135"/>
       <c r="F153" s="50" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G153" s="12"/>
-      <c r="H153" s="139"/>
+      <c r="H153" s="147"/>
     </row>
     <row r="154" spans="1:12" ht="15.75" customHeight="1">
       <c r="B154" s="113" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C154" s="14">
         <v>190</v>
       </c>
       <c r="D154" s="109" t="s">
-        <v>373</v>
-      </c>
-      <c r="E154" s="146"/>
+        <v>370</v>
+      </c>
+      <c r="E154" s="135"/>
       <c r="F154" s="50" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G154" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="H154" s="139"/>
+        <v>44</v>
+      </c>
+      <c r="H154" s="147"/>
     </row>
     <row r="155" spans="1:12" ht="15.75" customHeight="1">
       <c r="B155" s="113" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C155" s="14">
         <v>85</v>
       </c>
       <c r="D155" s="109" t="s">
-        <v>371</v>
-      </c>
-      <c r="E155" s="146"/>
+        <v>368</v>
+      </c>
+      <c r="E155" s="135"/>
       <c r="F155" s="50" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G155" s="12"/>
-      <c r="H155" s="139"/>
+      <c r="H155" s="147"/>
     </row>
     <row r="156" spans="1:12" ht="15.75" customHeight="1">
       <c r="B156" s="113" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C156" s="14">
         <v>180</v>
       </c>
       <c r="D156" s="109" t="s">
-        <v>373</v>
-      </c>
-      <c r="E156" s="146"/>
+        <v>370</v>
+      </c>
+      <c r="E156" s="135"/>
       <c r="F156" s="50" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G156" s="12"/>
-      <c r="H156" s="139"/>
+      <c r="H156" s="147"/>
     </row>
     <row r="157" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B157" s="116" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C157" s="17">
         <v>55</v>
       </c>
       <c r="D157" s="109" t="s">
-        <v>371</v>
-      </c>
-      <c r="E157" s="149"/>
+        <v>368</v>
+      </c>
+      <c r="E157" s="136"/>
       <c r="F157" s="53" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G157" s="115" t="s">
-        <v>46</v>
-      </c>
-      <c r="H157" s="140"/>
+        <v>45</v>
+      </c>
+      <c r="H157" s="148"/>
     </row>
     <row r="158" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B158" s="82" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C158" s="22">
         <v>580</v>
@@ -7358,17 +7370,17 @@
       <c r="D158" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E158" s="145">
+      <c r="E158" s="134">
         <v>167</v>
       </c>
       <c r="F158" s="31" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G158" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H158" s="134" t="s">
-        <v>403</v>
+      <c r="H158" s="143" t="s">
+        <v>400</v>
       </c>
       <c r="I158" s="29"/>
       <c r="J158" s="29"/>
@@ -7377,7 +7389,7 @@
     </row>
     <row r="159" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B159" s="84" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C159" s="14">
         <v>100</v>
@@ -7385,14 +7397,14 @@
       <c r="D159" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E159" s="146"/>
+      <c r="E159" s="135"/>
       <c r="F159" s="15" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G159" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H159" s="135"/>
+      <c r="H159" s="144"/>
       <c r="I159" s="29"/>
       <c r="J159" s="29"/>
       <c r="K159" s="29"/>
@@ -7400,7 +7412,7 @@
     </row>
     <row r="160" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B160" s="84" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C160" s="14">
         <v>180</v>
@@ -7408,14 +7420,14 @@
       <c r="D160" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E160" s="146"/>
+      <c r="E160" s="135"/>
       <c r="F160" s="15" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G160" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="H160" s="135"/>
+        <v>44</v>
+      </c>
+      <c r="H160" s="144"/>
       <c r="I160" s="29"/>
       <c r="J160" s="29"/>
       <c r="K160" s="29"/>
@@ -7423,7 +7435,7 @@
     </row>
     <row r="161" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B161" s="84" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C161" s="14">
         <v>80</v>
@@ -7431,14 +7443,14 @@
       <c r="D161" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E161" s="146"/>
+      <c r="E161" s="135"/>
       <c r="F161" s="15" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G161" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H161" s="135"/>
+      <c r="H161" s="144"/>
       <c r="I161" s="29"/>
       <c r="J161" s="29"/>
       <c r="K161" s="29"/>
@@ -7446,7 +7458,7 @@
     </row>
     <row r="162" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B162" s="84" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C162" s="14">
         <v>170</v>
@@ -7454,14 +7466,14 @@
       <c r="D162" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E162" s="146"/>
+      <c r="E162" s="135"/>
       <c r="F162" s="15" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G162" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H162" s="135"/>
+      <c r="H162" s="144"/>
       <c r="I162" s="29"/>
       <c r="J162" s="29"/>
       <c r="K162" s="29"/>
@@ -7469,7 +7481,7 @@
     </row>
     <row r="163" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B163" s="85" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C163" s="17">
         <v>50</v>
@@ -7477,14 +7489,14 @@
       <c r="D163" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E163" s="149"/>
+      <c r="E163" s="136"/>
       <c r="F163" s="19" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G163" s="86" t="s">
-        <v>46</v>
-      </c>
-      <c r="H163" s="137"/>
+        <v>45</v>
+      </c>
+      <c r="H163" s="145"/>
       <c r="I163" s="29"/>
       <c r="J163" s="29"/>
       <c r="K163" s="29"/>
@@ -7492,7 +7504,7 @@
     </row>
     <row r="164" spans="2:12" ht="26.25" thickTop="1" thickBot="1">
       <c r="B164" s="36" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C164" s="22">
         <v>580</v>
@@ -7500,22 +7512,22 @@
       <c r="D164" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E164" s="145">
+      <c r="E164" s="134">
         <v>125</v>
       </c>
       <c r="F164" s="58" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G164" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="H164" s="134" t="s">
-        <v>403</v>
+        <v>97</v>
+      </c>
+      <c r="H164" s="143" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="165" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B165" s="38" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C165" s="14">
         <v>100</v>
@@ -7523,18 +7535,18 @@
       <c r="D165" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E165" s="146"/>
+      <c r="E165" s="135"/>
       <c r="F165" s="56" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G165" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H165" s="135"/>
+      <c r="H165" s="144"/>
     </row>
     <row r="166" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B166" s="38" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C166" s="14">
         <v>180</v>
@@ -7542,18 +7554,18 @@
       <c r="D166" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E166" s="146"/>
+      <c r="E166" s="135"/>
       <c r="F166" s="56" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G166" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="H166" s="135"/>
+        <v>44</v>
+      </c>
+      <c r="H166" s="144"/>
     </row>
     <row r="167" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B167" s="38" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C167" s="14">
         <v>80</v>
@@ -7561,18 +7573,18 @@
       <c r="D167" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E167" s="146"/>
+      <c r="E167" s="135"/>
       <c r="F167" s="56" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G167" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H167" s="135"/>
+      <c r="H167" s="144"/>
     </row>
     <row r="168" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B168" s="87" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C168" s="14">
         <v>170</v>
@@ -7580,18 +7592,18 @@
       <c r="D168" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E168" s="146"/>
+      <c r="E168" s="135"/>
       <c r="F168" s="56" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G168" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H168" s="135"/>
+      <c r="H168" s="144"/>
     </row>
     <row r="169" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B169" s="51" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C169" s="17">
         <v>50</v>
@@ -7599,18 +7611,18 @@
       <c r="D169" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E169" s="149"/>
+      <c r="E169" s="136"/>
       <c r="F169" s="57" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G169" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="H169" s="137"/>
+        <v>45</v>
+      </c>
+      <c r="H169" s="145"/>
     </row>
     <row r="170" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B170" s="40" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C170" s="9">
         <v>580</v>
@@ -7618,7 +7630,7 @@
       <c r="D170" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E170" s="150">
+      <c r="E170" s="138">
         <v>200</v>
       </c>
       <c r="F170" s="50" t="s">
@@ -7627,8 +7639,8 @@
       <c r="G170" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H170" s="134" t="s">
-        <v>408</v>
+      <c r="H170" s="143" t="s">
+        <v>405</v>
       </c>
       <c r="I170" s="29"/>
       <c r="J170" s="29"/>
@@ -7637,7 +7649,7 @@
     </row>
     <row r="171" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B171" s="44" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C171" s="14">
         <v>100</v>
@@ -7645,14 +7657,14 @@
       <c r="D171" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E171" s="146"/>
+      <c r="E171" s="135"/>
       <c r="F171" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G171" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="H171" s="135"/>
+        <v>100</v>
+      </c>
+      <c r="H171" s="144"/>
       <c r="I171" s="29"/>
       <c r="J171" s="29"/>
       <c r="K171" s="29"/>
@@ -7660,7 +7672,7 @@
     </row>
     <row r="172" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B172" s="44" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C172" s="14">
         <v>180</v>
@@ -7668,14 +7680,14 @@
       <c r="D172" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E172" s="146"/>
+      <c r="E172" s="135"/>
       <c r="F172" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G172" s="55" t="s">
-        <v>104</v>
-      </c>
-      <c r="H172" s="135"/>
+        <v>101</v>
+      </c>
+      <c r="H172" s="144"/>
       <c r="I172" s="29"/>
       <c r="J172" s="29"/>
       <c r="K172" s="29"/>
@@ -7683,7 +7695,7 @@
     </row>
     <row r="173" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B173" s="44" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C173" s="14">
         <v>80</v>
@@ -7691,14 +7703,14 @@
       <c r="D173" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E173" s="146"/>
+      <c r="E173" s="135"/>
       <c r="F173" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G173" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="H173" s="135"/>
+        <v>100</v>
+      </c>
+      <c r="H173" s="144"/>
       <c r="I173" s="29"/>
       <c r="J173" s="29"/>
       <c r="K173" s="29"/>
@@ -7706,7 +7718,7 @@
     </row>
     <row r="174" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B174" s="44" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C174" s="14">
         <v>170</v>
@@ -7714,14 +7726,14 @@
       <c r="D174" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E174" s="146"/>
+      <c r="E174" s="135"/>
       <c r="F174" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G174" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="H174" s="135"/>
+        <v>100</v>
+      </c>
+      <c r="H174" s="144"/>
       <c r="I174" s="29"/>
       <c r="J174" s="29"/>
       <c r="K174" s="29"/>
@@ -7729,7 +7741,7 @@
     </row>
     <row r="175" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B175" s="60" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C175" s="24">
         <v>50</v>
@@ -7737,14 +7749,14 @@
       <c r="D175" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E175" s="147"/>
+      <c r="E175" s="137"/>
       <c r="F175" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G175" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="H175" s="137"/>
+        <v>102</v>
+      </c>
+      <c r="H175" s="145"/>
       <c r="I175" s="29"/>
       <c r="J175" s="29"/>
       <c r="K175" s="29"/>
@@ -7752,7 +7764,7 @@
     </row>
     <row r="176" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B176" s="36" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C176" s="22">
         <v>580</v>
@@ -7760,17 +7772,17 @@
       <c r="D176" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E176" s="145">
+      <c r="E176" s="134">
         <v>125</v>
       </c>
       <c r="F176" s="58" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="G176" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="H176" s="134" t="s">
-        <v>403</v>
+        <v>104</v>
+      </c>
+      <c r="H176" s="143" t="s">
+        <v>400</v>
       </c>
       <c r="I176" s="29"/>
       <c r="J176" s="29"/>
@@ -7779,7 +7791,7 @@
     </row>
     <row r="177" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B177" s="38" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C177" s="14">
         <v>100</v>
@@ -7787,14 +7799,14 @@
       <c r="D177" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E177" s="146"/>
+      <c r="E177" s="135"/>
       <c r="F177" s="56" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G177" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="H177" s="135"/>
+        <v>106</v>
+      </c>
+      <c r="H177" s="144"/>
       <c r="I177" s="29"/>
       <c r="J177" s="29"/>
       <c r="K177" s="29"/>
@@ -7802,7 +7814,7 @@
     </row>
     <row r="178" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B178" s="87" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C178" s="14">
         <v>180</v>
@@ -7810,14 +7822,14 @@
       <c r="D178" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E178" s="146"/>
+      <c r="E178" s="135"/>
       <c r="F178" s="56" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G178" s="78" t="s">
-        <v>111</v>
-      </c>
-      <c r="H178" s="135"/>
+        <v>108</v>
+      </c>
+      <c r="H178" s="144"/>
       <c r="I178" s="29"/>
       <c r="J178" s="29"/>
       <c r="K178" s="29"/>
@@ -7825,7 +7837,7 @@
     </row>
     <row r="179" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B179" s="38" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C179" s="14">
         <v>80</v>
@@ -7833,14 +7845,14 @@
       <c r="D179" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E179" s="146"/>
+      <c r="E179" s="135"/>
       <c r="F179" s="56" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G179" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="H179" s="135"/>
+        <v>106</v>
+      </c>
+      <c r="H179" s="144"/>
       <c r="I179" s="29"/>
       <c r="J179" s="29"/>
       <c r="K179" s="29"/>
@@ -7848,7 +7860,7 @@
     </row>
     <row r="180" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B180" s="38" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C180" s="14">
         <v>170</v>
@@ -7856,14 +7868,14 @@
       <c r="D180" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E180" s="146"/>
+      <c r="E180" s="135"/>
       <c r="F180" s="56" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G180" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="H180" s="135"/>
+        <v>106</v>
+      </c>
+      <c r="H180" s="144"/>
       <c r="I180" s="29"/>
       <c r="J180" s="29"/>
       <c r="K180" s="29"/>
@@ -7871,7 +7883,7 @@
     </row>
     <row r="181" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B181" s="51" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C181" s="17">
         <v>50</v>
@@ -7879,14 +7891,14 @@
       <c r="D181" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E181" s="149"/>
+      <c r="E181" s="136"/>
       <c r="F181" s="88" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G181" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="H181" s="137"/>
+        <v>110</v>
+      </c>
+      <c r="H181" s="145"/>
       <c r="I181" s="29"/>
       <c r="J181" s="29"/>
       <c r="K181" s="29"/>
@@ -7894,7 +7906,7 @@
     </row>
     <row r="182" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B182" s="75" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C182" s="76">
         <v>1010</v>
@@ -7902,17 +7914,17 @@
       <c r="D182" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E182" s="148">
+      <c r="E182" s="139">
         <v>167</v>
       </c>
       <c r="F182" s="28" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G182" s="54" t="s">
-        <v>323</v>
-      </c>
-      <c r="H182" s="134" t="s">
-        <v>402</v>
+        <v>320</v>
+      </c>
+      <c r="H182" s="143" t="s">
+        <v>399</v>
       </c>
       <c r="I182" s="29"/>
       <c r="J182" s="29"/>
@@ -7921,7 +7933,7 @@
     </row>
     <row r="183" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B183" s="44" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C183" s="14">
         <v>140</v>
@@ -7929,14 +7941,14 @@
       <c r="D183" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E183" s="146"/>
+      <c r="E183" s="135"/>
       <c r="F183" s="15" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G183" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H183" s="135"/>
+      <c r="H183" s="144"/>
       <c r="I183" s="29"/>
       <c r="J183" s="29"/>
       <c r="K183" s="29"/>
@@ -7944,7 +7956,7 @@
     </row>
     <row r="184" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B184" s="42" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C184" s="14">
         <v>240</v>
@@ -7952,18 +7964,18 @@
       <c r="D184" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E184" s="146"/>
+      <c r="E184" s="135"/>
       <c r="F184" s="15" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G184" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="H184" s="135"/>
+        <v>44</v>
+      </c>
+      <c r="H184" s="144"/>
     </row>
     <row r="185" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B185" s="42" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C185" s="14">
         <v>120</v>
@@ -7971,18 +7983,18 @@
       <c r="D185" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E185" s="146"/>
+      <c r="E185" s="135"/>
       <c r="F185" s="15" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G185" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H185" s="135"/>
+      <c r="H185" s="144"/>
     </row>
     <row r="186" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B186" s="44" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C186" s="14">
         <v>230</v>
@@ -7990,14 +8002,14 @@
       <c r="D186" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E186" s="146"/>
+      <c r="E186" s="135"/>
       <c r="F186" s="15" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G186" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H186" s="135"/>
+      <c r="H186" s="144"/>
       <c r="I186" s="29"/>
       <c r="J186" s="29"/>
       <c r="K186" s="29"/>
@@ -8005,7 +8017,7 @@
     </row>
     <row r="187" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B187" s="64" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C187" s="17">
         <v>80</v>
@@ -8013,14 +8025,14 @@
       <c r="D187" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E187" s="149"/>
+      <c r="E187" s="136"/>
       <c r="F187" s="19" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G187" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="H187" s="136"/>
+        <v>115</v>
+      </c>
+      <c r="H187" s="149"/>
       <c r="I187" s="29"/>
       <c r="J187" s="29"/>
       <c r="K187" s="29"/>
@@ -8028,7 +8040,7 @@
     </row>
     <row r="188" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B188" s="61" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C188" s="22">
         <v>1325</v>
@@ -8036,17 +8048,17 @@
       <c r="D188" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E188" s="145">
+      <c r="E188" s="134">
         <v>167</v>
       </c>
       <c r="F188" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G188" s="54" t="s">
-        <v>318</v>
-      </c>
-      <c r="H188" s="134" t="s">
-        <v>415</v>
+        <v>315</v>
+      </c>
+      <c r="H188" s="143" t="s">
+        <v>412</v>
       </c>
       <c r="I188" s="29"/>
       <c r="J188" s="29"/>
@@ -8055,7 +8067,7 @@
     </row>
     <row r="189" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B189" s="44" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C189" s="14">
         <v>160</v>
@@ -8063,14 +8075,14 @@
       <c r="D189" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E189" s="146"/>
+      <c r="E189" s="135"/>
       <c r="F189" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G189" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H189" s="135"/>
+      <c r="H189" s="144"/>
       <c r="I189" s="29"/>
       <c r="J189" s="29"/>
       <c r="K189" s="29"/>
@@ -8078,7 +8090,7 @@
     </row>
     <row r="190" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B190" s="44" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C190" s="14">
         <v>270</v>
@@ -8086,14 +8098,14 @@
       <c r="D190" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E190" s="146"/>
+      <c r="E190" s="135"/>
       <c r="F190" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G190" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="H190" s="135"/>
+        <v>44</v>
+      </c>
+      <c r="H190" s="144"/>
       <c r="I190" s="29"/>
       <c r="J190" s="29"/>
       <c r="K190" s="29"/>
@@ -8101,7 +8113,7 @@
     </row>
     <row r="191" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B191" s="44" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C191" s="14">
         <v>140</v>
@@ -8109,14 +8121,14 @@
       <c r="D191" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E191" s="146"/>
+      <c r="E191" s="135"/>
       <c r="F191" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G191" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H191" s="135"/>
+      <c r="H191" s="144"/>
       <c r="I191" s="29"/>
       <c r="J191" s="29"/>
       <c r="K191" s="29"/>
@@ -8124,7 +8136,7 @@
     </row>
     <row r="192" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B192" s="44" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C192" s="14">
         <v>260</v>
@@ -8132,14 +8144,14 @@
       <c r="D192" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E192" s="146"/>
+      <c r="E192" s="135"/>
       <c r="F192" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G192" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H192" s="135"/>
+      <c r="H192" s="144"/>
       <c r="I192" s="29"/>
       <c r="J192" s="29"/>
       <c r="K192" s="29"/>
@@ -8147,7 +8159,7 @@
     </row>
     <row r="193" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B193" s="60" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C193" s="24">
         <v>95</v>
@@ -8155,14 +8167,14 @@
       <c r="D193" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E193" s="147"/>
+      <c r="E193" s="137"/>
       <c r="F193" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G193" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="H193" s="136"/>
+        <v>115</v>
+      </c>
+      <c r="H193" s="149"/>
       <c r="I193" s="29"/>
       <c r="J193" s="29"/>
       <c r="K193" s="29"/>
@@ -8170,7 +8182,7 @@
     </row>
     <row r="194" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B194" s="36" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C194" s="22">
         <v>810</v>
@@ -8178,22 +8190,22 @@
       <c r="D194" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E194" s="145">
+      <c r="E194" s="134">
         <v>143</v>
       </c>
       <c r="F194" s="72" t="s">
         <v>7</v>
       </c>
       <c r="G194" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="H194" s="134" t="s">
-        <v>403</v>
+        <v>119</v>
+      </c>
+      <c r="H194" s="143" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="195" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B195" s="38" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C195" s="14">
         <v>140</v>
@@ -8201,18 +8213,18 @@
       <c r="D195" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E195" s="146"/>
+      <c r="E195" s="135"/>
       <c r="F195" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G195" s="54" t="s">
-        <v>123</v>
-      </c>
-      <c r="H195" s="135"/>
+        <v>120</v>
+      </c>
+      <c r="H195" s="144"/>
     </row>
     <row r="196" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B196" s="38" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C196" s="14">
         <v>240</v>
@@ -8220,18 +8232,18 @@
       <c r="D196" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E196" s="146"/>
+      <c r="E196" s="135"/>
       <c r="F196" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G196" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="H196" s="135"/>
+        <v>44</v>
+      </c>
+      <c r="H196" s="144"/>
     </row>
     <row r="197" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B197" s="38" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C197" s="14">
         <v>120</v>
@@ -8239,18 +8251,18 @@
       <c r="D197" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E197" s="146"/>
+      <c r="E197" s="135"/>
       <c r="F197" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G197" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H197" s="135"/>
+      <c r="H197" s="144"/>
     </row>
     <row r="198" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B198" s="38" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C198" s="14">
         <v>230</v>
@@ -8258,18 +8270,18 @@
       <c r="D198" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E198" s="146"/>
+      <c r="E198" s="135"/>
       <c r="F198" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G198" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H198" s="135"/>
+      <c r="H198" s="144"/>
     </row>
     <row r="199" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B199" s="39" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C199" s="24">
         <v>80</v>
@@ -8277,18 +8289,18 @@
       <c r="D199" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E199" s="147"/>
+      <c r="E199" s="137"/>
       <c r="F199" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G199" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="H199" s="137"/>
+        <v>115</v>
+      </c>
+      <c r="H199" s="145"/>
     </row>
     <row r="200" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B200" s="68" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C200" s="22">
         <v>1525</v>
@@ -8296,20 +8308,20 @@
       <c r="D200" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E200" s="145">
+      <c r="E200" s="134">
         <v>233</v>
       </c>
       <c r="F200" s="72"/>
       <c r="G200" s="48" t="s">
-        <v>331</v>
-      </c>
-      <c r="H200" s="138" t="s">
-        <v>405</v>
+        <v>328</v>
+      </c>
+      <c r="H200" s="150" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="201" spans="2:12" ht="15.75" customHeight="1">
       <c r="B201" s="74" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C201" s="14">
         <v>160</v>
@@ -8317,14 +8329,14 @@
       <c r="D201" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E201" s="146"/>
+      <c r="E201" s="135"/>
       <c r="F201" s="50"/>
       <c r="G201" s="12"/>
-      <c r="H201" s="139"/>
+      <c r="H201" s="147"/>
     </row>
     <row r="202" spans="2:12" ht="15.75" customHeight="1">
       <c r="B202" s="70" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C202" s="14">
         <v>270</v>
@@ -8332,16 +8344,16 @@
       <c r="D202" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E202" s="146"/>
+      <c r="E202" s="135"/>
       <c r="F202" s="50"/>
       <c r="G202" s="55" t="s">
-        <v>45</v>
-      </c>
-      <c r="H202" s="139"/>
+        <v>44</v>
+      </c>
+      <c r="H202" s="147"/>
     </row>
     <row r="203" spans="2:12" ht="15.75" customHeight="1">
       <c r="B203" s="70" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C203" s="14">
         <v>140</v>
@@ -8349,16 +8361,16 @@
       <c r="D203" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E203" s="146"/>
+      <c r="E203" s="135"/>
       <c r="F203" s="50"/>
       <c r="G203" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H203" s="139"/>
+      <c r="H203" s="147"/>
     </row>
     <row r="204" spans="2:12" ht="15.75" customHeight="1">
       <c r="B204" s="70" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C204" s="14">
         <v>260</v>
@@ -8366,16 +8378,16 @@
       <c r="D204" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E204" s="146"/>
+      <c r="E204" s="135"/>
       <c r="F204" s="50"/>
       <c r="G204" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H204" s="139"/>
+      <c r="H204" s="147"/>
     </row>
     <row r="205" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B205" s="71" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C205" s="24">
         <v>95</v>
@@ -8383,16 +8395,16 @@
       <c r="D205" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E205" s="147"/>
+      <c r="E205" s="137"/>
       <c r="F205" s="89"/>
       <c r="G205" s="90" t="s">
-        <v>118</v>
-      </c>
-      <c r="H205" s="140"/>
+        <v>115</v>
+      </c>
+      <c r="H205" s="148"/>
     </row>
     <row r="206" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B206" s="117" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C206" s="22">
         <v>1110</v>
@@ -8400,22 +8412,22 @@
       <c r="D206" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E206" s="145">
+      <c r="E206" s="134">
         <v>167</v>
       </c>
       <c r="F206" s="127" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="G206" s="114" t="s">
-        <v>381</v>
-      </c>
-      <c r="H206" s="134" t="s">
-        <v>403</v>
+        <v>378</v>
+      </c>
+      <c r="H206" s="143" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="207" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B207" s="74" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C207" s="14">
         <v>200</v>
@@ -8423,18 +8435,18 @@
       <c r="D207" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E207" s="146"/>
+      <c r="E207" s="135"/>
       <c r="F207" s="127" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G207" s="119" t="s">
-        <v>383</v>
-      </c>
-      <c r="H207" s="135"/>
+        <v>380</v>
+      </c>
+      <c r="H207" s="144"/>
     </row>
     <row r="208" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B208" s="125" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C208" s="14">
         <v>300</v>
@@ -8442,18 +8454,18 @@
       <c r="D208" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E208" s="146"/>
+      <c r="E208" s="135"/>
       <c r="F208" s="127" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G208" s="120" t="s">
-        <v>382</v>
-      </c>
-      <c r="H208" s="135"/>
+        <v>379</v>
+      </c>
+      <c r="H208" s="144"/>
     </row>
     <row r="209" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B209" s="125" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C209" s="14">
         <v>180</v>
@@ -8461,18 +8473,18 @@
       <c r="D209" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E209" s="146"/>
+      <c r="E209" s="135"/>
       <c r="F209" s="127" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G209" s="119" t="s">
-        <v>383</v>
-      </c>
-      <c r="H209" s="135"/>
+        <v>380</v>
+      </c>
+      <c r="H209" s="144"/>
     </row>
     <row r="210" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B210" s="125" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C210" s="14">
         <v>290</v>
@@ -8480,18 +8492,18 @@
       <c r="D210" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E210" s="146"/>
+      <c r="E210" s="135"/>
       <c r="F210" s="127" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G210" s="122" t="s">
-        <v>383</v>
-      </c>
-      <c r="H210" s="135"/>
+        <v>380</v>
+      </c>
+      <c r="H210" s="144"/>
     </row>
     <row r="211" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B211" s="126" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C211" s="24">
         <v>140</v>
@@ -8499,18 +8511,18 @@
       <c r="D211" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E211" s="147"/>
+      <c r="E211" s="137"/>
       <c r="F211" s="127" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G211" s="121" t="s">
-        <v>383</v>
-      </c>
-      <c r="H211" s="137"/>
+        <v>380</v>
+      </c>
+      <c r="H211" s="145"/>
     </row>
     <row r="212" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B212" s="117" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C212" s="22">
         <v>1110</v>
@@ -8518,22 +8530,22 @@
       <c r="D212" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E212" s="142">
+      <c r="E212" s="140">
         <v>167</v>
       </c>
       <c r="F212" s="127" t="s">
+        <v>397</v>
+      </c>
+      <c r="G212" s="114" t="s">
+        <v>387</v>
+      </c>
+      <c r="H212" s="143" t="s">
         <v>400</v>
-      </c>
-      <c r="G212" s="114" t="s">
-        <v>390</v>
-      </c>
-      <c r="H212" s="134" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="213" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B213" s="74" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C213" s="14">
         <v>200</v>
@@ -8541,18 +8553,18 @@
       <c r="D213" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E213" s="143"/>
+      <c r="E213" s="141"/>
       <c r="F213" s="127" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="G213" s="118" t="s">
-        <v>392</v>
-      </c>
-      <c r="H213" s="135"/>
+        <v>389</v>
+      </c>
+      <c r="H213" s="144"/>
     </row>
     <row r="214" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B214" s="125" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C214" s="14">
         <v>300</v>
@@ -8560,18 +8572,18 @@
       <c r="D214" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E214" s="143"/>
+      <c r="E214" s="141"/>
       <c r="F214" s="127" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G214" s="118" t="s">
-        <v>394</v>
-      </c>
-      <c r="H214" s="135"/>
+        <v>391</v>
+      </c>
+      <c r="H214" s="144"/>
     </row>
     <row r="215" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B215" s="125" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C215" s="14">
         <v>180</v>
@@ -8579,18 +8591,18 @@
       <c r="D215" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E215" s="143"/>
+      <c r="E215" s="141"/>
       <c r="F215" s="127" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G215" s="118" t="s">
-        <v>392</v>
-      </c>
-      <c r="H215" s="135"/>
+        <v>389</v>
+      </c>
+      <c r="H215" s="144"/>
     </row>
     <row r="216" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B216" s="125" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C216" s="14">
         <v>290</v>
@@ -8598,18 +8610,18 @@
       <c r="D216" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E216" s="143"/>
+      <c r="E216" s="141"/>
       <c r="F216" s="127" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G216" s="118" t="s">
-        <v>392</v>
-      </c>
-      <c r="H216" s="135"/>
+        <v>389</v>
+      </c>
+      <c r="H216" s="144"/>
     </row>
     <row r="217" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B217" s="126" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C217" s="123">
         <v>140</v>
@@ -8617,18 +8629,18 @@
       <c r="D217" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="E217" s="144"/>
+      <c r="E217" s="142"/>
       <c r="F217" s="127" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G217" s="119" t="s">
-        <v>395</v>
-      </c>
-      <c r="H217" s="137"/>
+        <v>392</v>
+      </c>
+      <c r="H217" s="145"/>
     </row>
     <row r="218" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B218" s="91" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C218" s="92">
         <v>5</v>
@@ -8640,18 +8652,18 @@
         <v>100</v>
       </c>
       <c r="F218" s="94" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="G218" s="59" t="s">
         <v>17</v>
       </c>
       <c r="H218" s="128" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="219" spans="2:8" ht="15.75" customHeight="1">
       <c r="B219" s="13" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C219" s="14">
         <v>12</v>
@@ -8669,12 +8681,12 @@
         <v>7</v>
       </c>
       <c r="H219" s="128" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="220" spans="2:8" ht="15.75" customHeight="1">
       <c r="B220" s="44" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C220" s="14">
         <v>30</v>
@@ -8692,12 +8704,12 @@
         <v>7</v>
       </c>
       <c r="H220" s="129" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="221" spans="2:8" ht="15.75" customHeight="1">
       <c r="B221" s="44" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C221" s="14">
         <v>35</v>
@@ -8709,18 +8721,18 @@
         <v>100</v>
       </c>
       <c r="F221" s="15" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="G221" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H221" s="128" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="222" spans="2:8" ht="15.75" customHeight="1">
       <c r="B222" s="13" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C222" s="14">
         <v>58</v>
@@ -8732,18 +8744,18 @@
         <v>100</v>
       </c>
       <c r="F222" s="96" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G222" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H222" s="128" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="223" spans="2:8" ht="15.75" customHeight="1">
       <c r="B223" s="38" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C223" s="14">
         <v>60</v>
@@ -8758,15 +8770,15 @@
         <v>7</v>
       </c>
       <c r="G223" s="54" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H223" s="130" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="224" spans="2:8" ht="15.75" customHeight="1">
       <c r="B224" s="44" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C224" s="14">
         <v>70</v>
@@ -8784,12 +8796,12 @@
         <v>7</v>
       </c>
       <c r="H224" s="128" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="225" spans="2:8" ht="15.75" customHeight="1">
       <c r="B225" s="44" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C225" s="14">
         <v>70</v>
@@ -8807,12 +8819,12 @@
         <v>7</v>
       </c>
       <c r="H225" s="128" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="226" spans="2:8" ht="15.75" customHeight="1">
       <c r="B226" s="97" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C226" s="14">
         <v>110</v>
@@ -8824,18 +8836,18 @@
         <v>112</v>
       </c>
       <c r="F226" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G226" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H226" s="128" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="227" spans="2:8" ht="15.75" customHeight="1">
       <c r="B227" s="44" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C227" s="14">
         <v>115</v>
@@ -8847,18 +8859,18 @@
         <v>143</v>
       </c>
       <c r="F227" s="15" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="G227" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H227" s="128" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="228" spans="2:8" ht="15.75" customHeight="1">
       <c r="B228" s="133" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C228" s="14">
         <v>150</v>
@@ -8870,18 +8882,18 @@
         <v>125</v>
       </c>
       <c r="F228" s="15" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G228" s="54" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H228" s="128" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="229" spans="2:8" ht="15.75" customHeight="1">
       <c r="B229" s="44" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C229" s="14">
         <v>160</v>
@@ -8893,18 +8905,18 @@
         <v>167</v>
       </c>
       <c r="F229" s="56" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G229" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H229" s="129" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="230" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B230" s="131" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C230" s="24">
         <v>200</v>
@@ -8919,10 +8931,10 @@
         <v>7</v>
       </c>
       <c r="G230" s="27" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H230" s="132" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="231" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
@@ -13789,38 +13801,30 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="72">
-    <mergeCell ref="E140:E145"/>
-    <mergeCell ref="E146:E151"/>
-    <mergeCell ref="E158:E163"/>
-    <mergeCell ref="E194:E199"/>
-    <mergeCell ref="E200:E205"/>
-    <mergeCell ref="E164:E169"/>
-    <mergeCell ref="E170:E175"/>
-    <mergeCell ref="E176:E181"/>
-    <mergeCell ref="E182:E187"/>
-    <mergeCell ref="E188:E193"/>
-    <mergeCell ref="E152:E157"/>
-    <mergeCell ref="E92:E97"/>
-    <mergeCell ref="E98:E103"/>
-    <mergeCell ref="E104:E109"/>
-    <mergeCell ref="E116:E121"/>
-    <mergeCell ref="E122:E127"/>
-    <mergeCell ref="E110:E115"/>
-    <mergeCell ref="E62:E67"/>
-    <mergeCell ref="E68:E73"/>
-    <mergeCell ref="E74:E79"/>
-    <mergeCell ref="E80:E85"/>
-    <mergeCell ref="E86:E91"/>
-    <mergeCell ref="E32:E37"/>
-    <mergeCell ref="E38:E43"/>
-    <mergeCell ref="E44:E49"/>
-    <mergeCell ref="E50:E55"/>
-    <mergeCell ref="E56:E61"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="E8:E13"/>
-    <mergeCell ref="E14:E19"/>
-    <mergeCell ref="E20:E25"/>
-    <mergeCell ref="E26:E31"/>
+    <mergeCell ref="H188:H193"/>
+    <mergeCell ref="H194:H199"/>
+    <mergeCell ref="H200:H205"/>
+    <mergeCell ref="H206:H211"/>
+    <mergeCell ref="H92:H97"/>
+    <mergeCell ref="H98:H103"/>
+    <mergeCell ref="H104:H109"/>
+    <mergeCell ref="H110:H115"/>
+    <mergeCell ref="H116:H121"/>
+    <mergeCell ref="H62:H67"/>
+    <mergeCell ref="H68:H73"/>
+    <mergeCell ref="H74:H79"/>
+    <mergeCell ref="H80:H85"/>
+    <mergeCell ref="H86:H91"/>
+    <mergeCell ref="H32:H37"/>
+    <mergeCell ref="H38:H43"/>
+    <mergeCell ref="H44:H49"/>
+    <mergeCell ref="H50:H55"/>
+    <mergeCell ref="H56:H61"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="H8:H13"/>
+    <mergeCell ref="H14:H19"/>
+    <mergeCell ref="H20:H25"/>
+    <mergeCell ref="H26:H31"/>
     <mergeCell ref="E212:E217"/>
     <mergeCell ref="E206:E211"/>
     <mergeCell ref="H122:H127"/>
@@ -13837,30 +13841,38 @@
     <mergeCell ref="E134:E139"/>
     <mergeCell ref="H212:H217"/>
     <mergeCell ref="H182:H187"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="H8:H13"/>
-    <mergeCell ref="H14:H19"/>
-    <mergeCell ref="H20:H25"/>
-    <mergeCell ref="H26:H31"/>
-    <mergeCell ref="H32:H37"/>
-    <mergeCell ref="H38:H43"/>
-    <mergeCell ref="H44:H49"/>
-    <mergeCell ref="H50:H55"/>
-    <mergeCell ref="H56:H61"/>
-    <mergeCell ref="H62:H67"/>
-    <mergeCell ref="H68:H73"/>
-    <mergeCell ref="H74:H79"/>
-    <mergeCell ref="H80:H85"/>
-    <mergeCell ref="H86:H91"/>
-    <mergeCell ref="H188:H193"/>
-    <mergeCell ref="H194:H199"/>
-    <mergeCell ref="H200:H205"/>
-    <mergeCell ref="H206:H211"/>
-    <mergeCell ref="H92:H97"/>
-    <mergeCell ref="H98:H103"/>
-    <mergeCell ref="H104:H109"/>
-    <mergeCell ref="H110:H115"/>
-    <mergeCell ref="H116:H121"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="E8:E13"/>
+    <mergeCell ref="E14:E19"/>
+    <mergeCell ref="E20:E25"/>
+    <mergeCell ref="E26:E31"/>
+    <mergeCell ref="E32:E37"/>
+    <mergeCell ref="E38:E43"/>
+    <mergeCell ref="E44:E49"/>
+    <mergeCell ref="E50:E55"/>
+    <mergeCell ref="E56:E61"/>
+    <mergeCell ref="E62:E67"/>
+    <mergeCell ref="E68:E73"/>
+    <mergeCell ref="E74:E79"/>
+    <mergeCell ref="E80:E85"/>
+    <mergeCell ref="E86:E91"/>
+    <mergeCell ref="E92:E97"/>
+    <mergeCell ref="E98:E103"/>
+    <mergeCell ref="E104:E109"/>
+    <mergeCell ref="E116:E121"/>
+    <mergeCell ref="E122:E127"/>
+    <mergeCell ref="E110:E115"/>
+    <mergeCell ref="E140:E145"/>
+    <mergeCell ref="E146:E151"/>
+    <mergeCell ref="E158:E163"/>
+    <mergeCell ref="E194:E199"/>
+    <mergeCell ref="E200:E205"/>
+    <mergeCell ref="E164:E169"/>
+    <mergeCell ref="E170:E175"/>
+    <mergeCell ref="E176:E181"/>
+    <mergeCell ref="E182:E187"/>
+    <mergeCell ref="E188:E193"/>
+    <mergeCell ref="E152:E157"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-source/护甲数据.xlsx
+++ b/data-source/护甲数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE96422-52E5-4319-9F56-98474E2DB986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1B7A21-A3A0-4DDE-98AF-A918DA809780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1101,9 +1101,6 @@
     <t xml:space="preserve">圣殿骑士手套  </t>
   </si>
   <si>
-    <t xml:space="preserve">角斗士套装（T6+级）  </t>
-  </si>
-  <si>
     <t>~25.2%概率使攻击者流血（10点流血伤害×5次）</t>
   </si>
   <si>
@@ -2339,6 +2336,9 @@
   </si>
   <si>
     <t>增加潜行时的移动速度；全套一共10%的几率躲避敌人的攻击</t>
+  </si>
+  <si>
+    <t xml:space="preserve">角斗士套装（T6级）  </t>
   </si>
 </sst>
 </file>
@@ -3309,7 +3309,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3746,9 +3746,6 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4068,7 +4065,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
@@ -4085,18 +4082,18 @@
         <v>91</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="143" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="15.75" customHeight="1">
       <c r="B3" s="13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C3" s="14">
         <v>10</v>
@@ -4115,7 +4112,7 @@
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1">
       <c r="B4" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C4" s="14">
         <v>25</v>
@@ -4125,7 +4122,7 @@
       </c>
       <c r="E4" s="135"/>
       <c r="F4" s="15" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>7</v>
@@ -4134,7 +4131,7 @@
     </row>
     <row r="5" spans="2:8" ht="15.75" customHeight="1">
       <c r="B5" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C5" s="14">
         <v>10</v>
@@ -4153,7 +4150,7 @@
     </row>
     <row r="6" spans="2:8" ht="15.75" customHeight="1">
       <c r="B6" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C6" s="14">
         <v>25</v>
@@ -4163,7 +4160,7 @@
       </c>
       <c r="E6" s="135"/>
       <c r="F6" s="15" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>7</v>
@@ -4172,7 +4169,7 @@
     </row>
     <row r="7" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B7" s="16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C7" s="17">
         <v>0</v>
@@ -4203,13 +4200,13 @@
         <v>91</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H8" s="143" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15.75" customHeight="1">
@@ -4243,7 +4240,7 @@
       </c>
       <c r="E10" s="135"/>
       <c r="F10" s="15" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>7</v>
@@ -4271,7 +4268,7 @@
     </row>
     <row r="12" spans="2:8" ht="15.75" customHeight="1">
       <c r="B12" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C12" s="14">
         <v>25</v>
@@ -4281,7 +4278,7 @@
       </c>
       <c r="E12" s="135"/>
       <c r="F12" s="15" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>7</v>
@@ -4290,7 +4287,7 @@
     </row>
     <row r="13" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B13" s="23" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C13" s="24">
         <v>0</v>
@@ -4321,18 +4318,18 @@
         <v>100</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H14" s="143" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15.75" customHeight="1">
       <c r="B15" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C15" s="14">
         <v>30</v>
@@ -4342,7 +4339,7 @@
       </c>
       <c r="E15" s="135"/>
       <c r="F15" s="15" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>7</v>
@@ -4351,7 +4348,7 @@
     </row>
     <row r="16" spans="2:8" ht="15.75" customHeight="1">
       <c r="B16" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C16" s="14">
         <v>50</v>
@@ -4361,7 +4358,7 @@
       </c>
       <c r="E16" s="135"/>
       <c r="F16" s="15" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>7</v>
@@ -4380,7 +4377,7 @@
       </c>
       <c r="E17" s="135"/>
       <c r="F17" s="15" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>7</v>
@@ -4393,7 +4390,7 @@
     </row>
     <row r="18" spans="2:12" ht="15.75" customHeight="1">
       <c r="B18" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="14">
         <v>50</v>
@@ -4403,7 +4400,7 @@
       </c>
       <c r="E18" s="135"/>
       <c r="F18" s="15" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>7</v>
@@ -4416,7 +4413,7 @@
     </row>
     <row r="19" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B19" s="16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C19" s="17">
         <v>0</v>
@@ -4426,7 +4423,7 @@
       </c>
       <c r="E19" s="136"/>
       <c r="F19" s="19" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>17</v>
@@ -4451,18 +4448,18 @@
         <v>100</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G20" s="30" t="s">
         <v>7</v>
       </c>
       <c r="H20" s="143" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="15.75" customHeight="1">
       <c r="B21" s="13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C21" s="14">
         <v>30</v>
@@ -4472,7 +4469,7 @@
       </c>
       <c r="E21" s="135"/>
       <c r="F21" s="15" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>7</v>
@@ -4481,7 +4478,7 @@
     </row>
     <row r="22" spans="2:12" ht="15.75" customHeight="1">
       <c r="B22" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C22" s="14">
         <v>50</v>
@@ -4491,7 +4488,7 @@
       </c>
       <c r="E22" s="135"/>
       <c r="F22" s="15" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>7</v>
@@ -4510,7 +4507,7 @@
       </c>
       <c r="E23" s="135"/>
       <c r="F23" s="15" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>7</v>
@@ -4519,7 +4516,7 @@
     </row>
     <row r="24" spans="2:12" ht="15.75" customHeight="1">
       <c r="B24" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C24" s="14">
         <v>50</v>
@@ -4529,7 +4526,7 @@
       </c>
       <c r="E24" s="135"/>
       <c r="F24" s="15" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>7</v>
@@ -4538,7 +4535,7 @@
     </row>
     <row r="25" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B25" s="107" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C25" s="17">
         <v>0</v>
@@ -4548,7 +4545,7 @@
       </c>
       <c r="E25" s="136"/>
       <c r="F25" s="19" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>17</v>
@@ -4569,18 +4566,18 @@
         <v>100</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G26" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H26" s="143" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="27" spans="2:12" ht="15.75" customHeight="1">
       <c r="B27" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C27" s="14">
         <v>30</v>
@@ -4590,7 +4587,7 @@
       </c>
       <c r="E27" s="135"/>
       <c r="F27" s="15" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G27" s="12" t="s">
         <v>7</v>
@@ -4599,7 +4596,7 @@
     </row>
     <row r="28" spans="2:12" ht="15.75" customHeight="1">
       <c r="B28" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C28" s="14">
         <v>50</v>
@@ -4609,7 +4606,7 @@
       </c>
       <c r="E28" s="135"/>
       <c r="F28" s="15" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>7</v>
@@ -4618,7 +4615,7 @@
     </row>
     <row r="29" spans="2:12" ht="15.75" customHeight="1">
       <c r="B29" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C29" s="14">
         <v>20</v>
@@ -4628,7 +4625,7 @@
       </c>
       <c r="E29" s="135"/>
       <c r="F29" s="15" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G29" s="12" t="s">
         <v>7</v>
@@ -4637,7 +4634,7 @@
     </row>
     <row r="30" spans="2:12" ht="15.75" customHeight="1">
       <c r="B30" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C30" s="14">
         <v>50</v>
@@ -4647,7 +4644,7 @@
       </c>
       <c r="E30" s="135"/>
       <c r="F30" s="15" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>7</v>
@@ -4656,7 +4653,7 @@
     </row>
     <row r="31" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B31" s="32" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C31" s="33">
         <v>0</v>
@@ -4666,7 +4663,7 @@
       </c>
       <c r="E31" s="137"/>
       <c r="F31" s="34" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>17</v>
@@ -4687,13 +4684,13 @@
         <v>112</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G32" s="37" t="s">
         <v>22</v>
       </c>
       <c r="H32" s="143" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -4702,7 +4699,7 @@
     </row>
     <row r="33" spans="2:12" ht="15.75" customHeight="1">
       <c r="B33" s="87" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C33" s="14">
         <v>40</v>
@@ -4712,7 +4709,7 @@
       </c>
       <c r="E33" s="135"/>
       <c r="F33" s="15" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>7</v>
@@ -4735,7 +4732,7 @@
       </c>
       <c r="E34" s="135"/>
       <c r="F34" s="15" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>7</v>
@@ -4748,7 +4745,7 @@
     </row>
     <row r="35" spans="2:12" ht="15.75" customHeight="1">
       <c r="B35" s="38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C35" s="14">
         <v>30</v>
@@ -4758,7 +4755,7 @@
       </c>
       <c r="E35" s="135"/>
       <c r="F35" s="15" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>7</v>
@@ -4771,7 +4768,7 @@
     </row>
     <row r="36" spans="2:12" ht="15.75" customHeight="1">
       <c r="B36" s="87" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C36" s="14">
         <v>60</v>
@@ -4781,7 +4778,7 @@
       </c>
       <c r="E36" s="135"/>
       <c r="F36" s="15" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>7</v>
@@ -4794,7 +4791,7 @@
     </row>
     <row r="37" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B37" s="108" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C37" s="24">
         <v>10</v>
@@ -4804,7 +4801,7 @@
       </c>
       <c r="E37" s="137"/>
       <c r="F37" s="26" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G37" s="27" t="s">
         <v>24</v>
@@ -4829,13 +4826,13 @@
         <v>100</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G38" s="41" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H38" s="143" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I38" s="29"/>
       <c r="J38" s="29"/>
@@ -4854,9 +4851,9 @@
       </c>
       <c r="E39" s="135"/>
       <c r="F39" s="15" t="s">
-        <v>332</v>
-      </c>
-      <c r="G39" s="151" t="s">
+        <v>331</v>
+      </c>
+      <c r="G39" s="54" t="s">
         <v>27</v>
       </c>
       <c r="H39" s="144"/>
@@ -4877,9 +4874,9 @@
       </c>
       <c r="E40" s="135"/>
       <c r="F40" s="15" t="s">
-        <v>333</v>
-      </c>
-      <c r="G40" s="151" t="s">
+        <v>332</v>
+      </c>
+      <c r="G40" s="54" t="s">
         <v>27</v>
       </c>
       <c r="H40" s="144"/>
@@ -4900,9 +4897,9 @@
       </c>
       <c r="E41" s="135"/>
       <c r="F41" s="15" t="s">
-        <v>334</v>
-      </c>
-      <c r="G41" s="151" t="s">
+        <v>333</v>
+      </c>
+      <c r="G41" s="54" t="s">
         <v>27</v>
       </c>
       <c r="H41" s="144"/>
@@ -4913,7 +4910,7 @@
     </row>
     <row r="42" spans="2:12" ht="15.75" customHeight="1">
       <c r="B42" s="44" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C42" s="14">
         <v>50</v>
@@ -4923,9 +4920,9 @@
       </c>
       <c r="E42" s="135"/>
       <c r="F42" s="15" t="s">
-        <v>333</v>
-      </c>
-      <c r="G42" s="151" t="s">
+        <v>332</v>
+      </c>
+      <c r="G42" s="54" t="s">
         <v>27</v>
       </c>
       <c r="H42" s="144"/>
@@ -4936,7 +4933,7 @@
     </row>
     <row r="43" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B43" s="45" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C43" s="24">
         <v>0</v>
@@ -4946,7 +4943,7 @@
       </c>
       <c r="E43" s="137"/>
       <c r="F43" s="26" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G43" s="27" t="s">
         <v>30</v>
@@ -4971,13 +4968,13 @@
         <v>112</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G44" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H44" s="143" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I44" s="29"/>
       <c r="J44" s="29"/>
@@ -4986,7 +4983,7 @@
     </row>
     <row r="45" spans="2:12" ht="15.75" customHeight="1">
       <c r="B45" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C45" s="14">
         <v>50</v>
@@ -5009,7 +5006,7 @@
     </row>
     <row r="46" spans="2:12" ht="15.75" customHeight="1">
       <c r="B46" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C46" s="14">
         <v>90</v>
@@ -5032,7 +5029,7 @@
     </row>
     <row r="47" spans="2:12" ht="15.75" customHeight="1">
       <c r="B47" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C47" s="14">
         <v>30</v>
@@ -5055,7 +5052,7 @@
     </row>
     <row r="48" spans="2:12" ht="15.75" customHeight="1">
       <c r="B48" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C48" s="14">
         <v>80</v>
@@ -5078,7 +5075,7 @@
     </row>
     <row r="49" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B49" s="16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C49" s="17">
         <v>10</v>
@@ -5088,7 +5085,7 @@
       </c>
       <c r="E49" s="136"/>
       <c r="F49" s="19" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G49" s="20" t="s">
         <v>36</v>
@@ -5113,13 +5110,13 @@
         <v>112</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G50" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H50" s="143" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="51" spans="2:12" ht="15.75" customHeight="1">
@@ -5143,7 +5140,7 @@
     </row>
     <row r="52" spans="2:12" ht="15.75" customHeight="1">
       <c r="B52" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C52" s="14">
         <v>90</v>
@@ -5162,7 +5159,7 @@
     </row>
     <row r="53" spans="2:12" ht="15.75" customHeight="1">
       <c r="B53" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C53" s="14">
         <v>30</v>
@@ -5181,7 +5178,7 @@
     </row>
     <row r="54" spans="2:12" ht="15.75" customHeight="1">
       <c r="B54" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C54" s="14">
         <v>80</v>
@@ -5200,7 +5197,7 @@
     </row>
     <row r="55" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B55" s="16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C55" s="17">
         <v>10</v>
@@ -5210,7 +5207,7 @@
       </c>
       <c r="E55" s="136"/>
       <c r="F55" s="19" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G55" s="20" t="s">
         <v>36</v>
@@ -5225,7 +5222,7 @@
         <v>260</v>
       </c>
       <c r="D56" s="63" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E56" s="134">
         <v>112</v>
@@ -5237,18 +5234,18 @@
         <v>40</v>
       </c>
       <c r="H56" s="143" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="57" spans="2:12" ht="15.75" customHeight="1">
       <c r="B57" s="38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C57" s="49">
         <v>50</v>
       </c>
       <c r="D57" s="63" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E57" s="135"/>
       <c r="F57" s="50" t="s">
@@ -5261,13 +5258,13 @@
     </row>
     <row r="58" spans="2:12" ht="15.75" customHeight="1">
       <c r="B58" s="38" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C58" s="49">
         <v>90</v>
       </c>
       <c r="D58" s="63" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E58" s="135"/>
       <c r="F58" s="50" t="s">
@@ -5280,13 +5277,13 @@
     </row>
     <row r="59" spans="2:12" ht="15.75" customHeight="1">
       <c r="B59" s="38" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C59" s="49">
         <v>30</v>
       </c>
       <c r="D59" s="63" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E59" s="135"/>
       <c r="F59" s="50" t="s">
@@ -5299,13 +5296,13 @@
     </row>
     <row r="60" spans="2:12" ht="15.75" customHeight="1">
       <c r="B60" s="38" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C60" s="49">
         <v>80</v>
       </c>
       <c r="D60" s="63" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E60" s="135"/>
       <c r="F60" s="50" t="s">
@@ -5318,13 +5315,13 @@
     </row>
     <row r="61" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B61" s="51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C61" s="52">
         <v>10</v>
       </c>
       <c r="D61" s="63" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E61" s="136"/>
       <c r="F61" s="53" t="s">
@@ -5349,13 +5346,13 @@
         <v>143</v>
       </c>
       <c r="F62" s="31" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G62" s="48" t="s">
         <v>42</v>
       </c>
       <c r="H62" s="143" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I62" s="29"/>
       <c r="J62" s="29"/>
@@ -5364,7 +5361,7 @@
     </row>
     <row r="63" spans="2:12" ht="15.75" customHeight="1">
       <c r="B63" s="38" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C63" s="14">
         <v>60</v>
@@ -5374,7 +5371,7 @@
       </c>
       <c r="E63" s="135"/>
       <c r="F63" s="15" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G63" s="54" t="s">
         <v>43</v>
@@ -5387,7 +5384,7 @@
     </row>
     <row r="64" spans="2:12" ht="15.75" customHeight="1">
       <c r="B64" s="38" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C64" s="14">
         <v>110</v>
@@ -5397,7 +5394,7 @@
       </c>
       <c r="E64" s="135"/>
       <c r="F64" s="15" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G64" s="55" t="s">
         <v>44</v>
@@ -5410,7 +5407,7 @@
     </row>
     <row r="65" spans="2:12" ht="15.75" customHeight="1">
       <c r="B65" s="38" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C65" s="14">
         <v>35</v>
@@ -5420,7 +5417,7 @@
       </c>
       <c r="E65" s="135"/>
       <c r="F65" s="15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G65" s="12" t="s">
         <v>7</v>
@@ -5433,7 +5430,7 @@
     </row>
     <row r="66" spans="2:12" ht="15.75" customHeight="1">
       <c r="B66" s="38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C66" s="14">
         <v>95</v>
@@ -5443,7 +5440,7 @@
       </c>
       <c r="E66" s="135"/>
       <c r="F66" s="15" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G66" s="12" t="s">
         <v>7</v>
@@ -5456,7 +5453,7 @@
     </row>
     <row r="67" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B67" s="51" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C67" s="17">
         <v>12</v>
@@ -5464,7 +5461,7 @@
       <c r="D67" s="18"/>
       <c r="E67" s="136"/>
       <c r="F67" s="19" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G67" s="20" t="s">
         <v>45</v>
@@ -5489,13 +5486,13 @@
         <v>143</v>
       </c>
       <c r="F68" s="31" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G68" s="37" t="s">
         <v>47</v>
       </c>
       <c r="H68" s="143" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="69" spans="2:12" ht="15.75" customHeight="1">
@@ -5510,7 +5507,7 @@
       </c>
       <c r="E69" s="135"/>
       <c r="F69" s="56" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G69" s="55" t="s">
         <v>49</v>
@@ -5519,7 +5516,7 @@
     </row>
     <row r="70" spans="2:12" ht="15.75" customHeight="1">
       <c r="B70" s="38" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C70" s="14">
         <v>110</v>
@@ -5529,7 +5526,7 @@
       </c>
       <c r="E70" s="135"/>
       <c r="F70" s="15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G70" s="54" t="s">
         <v>44</v>
@@ -5538,7 +5535,7 @@
     </row>
     <row r="71" spans="2:12" ht="15.75" customHeight="1">
       <c r="B71" s="38" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C71" s="14">
         <v>35</v>
@@ -5548,7 +5545,7 @@
       </c>
       <c r="E71" s="135"/>
       <c r="F71" s="56" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G71" s="12" t="s">
         <v>7</v>
@@ -5557,7 +5554,7 @@
     </row>
     <row r="72" spans="2:12" ht="15.75" customHeight="1">
       <c r="B72" s="38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C72" s="14">
         <v>95</v>
@@ -5567,7 +5564,7 @@
       </c>
       <c r="E72" s="135"/>
       <c r="F72" s="15" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G72" s="12" t="s">
         <v>7</v>
@@ -5576,7 +5573,7 @@
     </row>
     <row r="73" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B73" s="51" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C73" s="17">
         <v>12</v>
@@ -5586,7 +5583,7 @@
       </c>
       <c r="E73" s="136"/>
       <c r="F73" s="57" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G73" s="20" t="s">
         <v>45</v>
@@ -5607,18 +5604,18 @@
         <v>143</v>
       </c>
       <c r="F74" s="58" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G74" s="37" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H74" s="143" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="75" spans="2:12" ht="26.65" customHeight="1">
       <c r="B75" s="38" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C75" s="49">
         <v>70</v>
@@ -5628,16 +5625,16 @@
       </c>
       <c r="E75" s="135"/>
       <c r="F75" s="56" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G75" s="54" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H75" s="144"/>
     </row>
     <row r="76" spans="2:12" ht="15.75" customHeight="1">
       <c r="B76" s="38" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C76" s="49">
         <v>110</v>
@@ -5647,16 +5644,16 @@
       </c>
       <c r="E76" s="135"/>
       <c r="F76" s="56" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G76" s="55" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H76" s="144"/>
     </row>
     <row r="77" spans="2:12" ht="15.75" customHeight="1">
       <c r="B77" s="38" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C77" s="49">
         <v>35</v>
@@ -5666,16 +5663,16 @@
       </c>
       <c r="E77" s="135"/>
       <c r="F77" s="56" t="s">
-        <v>424</v>
-      </c>
-      <c r="G77" s="151" t="s">
-        <v>430</v>
+        <v>423</v>
+      </c>
+      <c r="G77" s="54" t="s">
+        <v>429</v>
       </c>
       <c r="H77" s="144"/>
     </row>
     <row r="78" spans="2:12" ht="15.75" customHeight="1">
       <c r="B78" s="38" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C78" s="49">
         <v>95</v>
@@ -5685,16 +5682,16 @@
       </c>
       <c r="E78" s="135"/>
       <c r="F78" s="56" t="s">
-        <v>189</v>
-      </c>
-      <c r="G78" s="151" t="s">
-        <v>430</v>
+        <v>188</v>
+      </c>
+      <c r="G78" s="54" t="s">
+        <v>429</v>
       </c>
       <c r="H78" s="144"/>
     </row>
     <row r="79" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B79" s="51" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C79" s="52">
         <v>12</v>
@@ -5704,10 +5701,10 @@
       </c>
       <c r="E79" s="136"/>
       <c r="F79" s="57" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G79" s="20" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H79" s="145"/>
     </row>
@@ -5725,13 +5722,13 @@
         <v>112</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G80" s="59" t="s">
         <v>52</v>
       </c>
       <c r="H80" s="143" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I80" s="29"/>
       <c r="J80" s="29"/>
@@ -5740,7 +5737,7 @@
     </row>
     <row r="81" spans="2:12" ht="15.75" customHeight="1">
       <c r="B81" s="44" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C81" s="14">
         <v>60</v>
@@ -5763,7 +5760,7 @@
     </row>
     <row r="82" spans="2:12" ht="15.75" customHeight="1">
       <c r="B82" s="44" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C82" s="14">
         <v>100</v>
@@ -5809,7 +5806,7 @@
     </row>
     <row r="84" spans="2:12" ht="15.75" customHeight="1">
       <c r="B84" s="44" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C84" s="14">
         <v>90</v>
@@ -5832,7 +5829,7 @@
     </row>
     <row r="85" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B85" s="60" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C85" s="24">
         <v>20</v>
@@ -5842,7 +5839,7 @@
       </c>
       <c r="E85" s="137"/>
       <c r="F85" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G85" s="27" t="s">
         <v>36</v>
@@ -5873,7 +5870,7 @@
         <v>7</v>
       </c>
       <c r="H86" s="143" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I86" s="29"/>
       <c r="J86" s="29"/>
@@ -5928,7 +5925,7 @@
     </row>
     <row r="89" spans="2:12" ht="15.75" customHeight="1">
       <c r="B89" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C89" s="14">
         <v>50</v>
@@ -5951,7 +5948,7 @@
     </row>
     <row r="90" spans="2:12" ht="15.75" customHeight="1">
       <c r="B90" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C90" s="14">
         <v>120</v>
@@ -5974,7 +5971,7 @@
     </row>
     <row r="91" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B91" s="16" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C91" s="17">
         <v>30</v>
@@ -5997,13 +5994,13 @@
     </row>
     <row r="92" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B92" s="61" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C92" s="22">
         <v>440</v>
       </c>
       <c r="D92" s="62" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E92" s="134">
         <v>125</v>
@@ -6012,15 +6009,15 @@
         <v>63</v>
       </c>
       <c r="G92" s="48" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H92" s="146" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="93" spans="2:12" ht="15.75" customHeight="1">
       <c r="B93" s="44" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C93" s="14">
         <v>80</v>
@@ -6039,7 +6036,7 @@
     </row>
     <row r="94" spans="2:12" ht="15.75" customHeight="1">
       <c r="B94" s="44" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C94" s="14">
         <v>140</v>
@@ -6058,7 +6055,7 @@
     </row>
     <row r="95" spans="2:12" ht="15.75" customHeight="1">
       <c r="B95" s="44" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C95" s="14">
         <v>55</v>
@@ -6077,7 +6074,7 @@
     </row>
     <row r="96" spans="2:12" ht="15.75" customHeight="1">
       <c r="B96" s="44" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C96" s="14">
         <v>130</v>
@@ -6096,7 +6093,7 @@
     </row>
     <row r="97" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B97" s="64" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C97" s="17">
         <v>35</v>
@@ -6127,13 +6124,13 @@
         <v>125</v>
       </c>
       <c r="F98" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G98" s="37" t="s">
         <v>67</v>
       </c>
       <c r="H98" s="143" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="99" spans="2:8" ht="15.75" customHeight="1">
@@ -6148,16 +6145,16 @@
       </c>
       <c r="E99" s="135"/>
       <c r="F99" s="56" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G99" s="54" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H99" s="144"/>
     </row>
     <row r="100" spans="2:8" ht="15.75" customHeight="1">
       <c r="B100" s="38" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C100" s="14">
         <v>140</v>
@@ -6167,7 +6164,7 @@
       </c>
       <c r="E100" s="135"/>
       <c r="F100" s="56" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G100" s="54" t="s">
         <v>44</v>
@@ -6176,7 +6173,7 @@
     </row>
     <row r="101" spans="2:8" ht="15.75" customHeight="1">
       <c r="B101" s="38" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C101" s="14">
         <v>55</v>
@@ -6186,7 +6183,7 @@
       </c>
       <c r="E101" s="135"/>
       <c r="F101" s="56" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G101" s="12" t="s">
         <v>7</v>
@@ -6195,7 +6192,7 @@
     </row>
     <row r="102" spans="2:8" ht="15.75" customHeight="1">
       <c r="B102" s="38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C102" s="14">
         <v>130</v>
@@ -6205,7 +6202,7 @@
       </c>
       <c r="E102" s="135"/>
       <c r="F102" s="56" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G102" s="12" t="s">
         <v>7</v>
@@ -6214,7 +6211,7 @@
     </row>
     <row r="103" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B103" s="51" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C103" s="17">
         <v>40</v>
@@ -6224,7 +6221,7 @@
       </c>
       <c r="E103" s="136"/>
       <c r="F103" s="57" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G103" s="20" t="s">
         <v>69</v>
@@ -6233,7 +6230,7 @@
     </row>
     <row r="104" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B104" s="61" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C104" s="22">
         <v>450</v>
@@ -6251,7 +6248,7 @@
         <v>17</v>
       </c>
       <c r="H104" s="143" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="105" spans="2:8" ht="15.75" customHeight="1">
@@ -6275,7 +6272,7 @@
     </row>
     <row r="106" spans="2:8" ht="15.75" customHeight="1">
       <c r="B106" s="44" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C106" s="14">
         <v>140</v>
@@ -6313,7 +6310,7 @@
     </row>
     <row r="108" spans="2:8" ht="15.75" customHeight="1">
       <c r="B108" s="44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C108" s="14">
         <v>130</v>
@@ -6332,7 +6329,7 @@
     </row>
     <row r="109" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B109" s="66" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C109" s="33">
         <v>40</v>
@@ -6351,7 +6348,7 @@
     </row>
     <row r="110" spans="2:8" ht="25.5" customHeight="1" thickTop="1">
       <c r="B110" s="36" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C110" s="22">
         <v>450</v>
@@ -6363,18 +6360,18 @@
         <v>125</v>
       </c>
       <c r="F110" s="72" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G110" s="37" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H110" s="143" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="111" spans="2:8" ht="15.75" customHeight="1">
       <c r="B111" s="38" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C111" s="14">
         <v>80</v>
@@ -6384,16 +6381,16 @@
       </c>
       <c r="E111" s="135"/>
       <c r="F111" s="56" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G111" s="54" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H111" s="144"/>
     </row>
     <row r="112" spans="2:8" ht="15.75" customHeight="1">
       <c r="B112" s="38" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C112" s="14">
         <v>140</v>
@@ -6403,16 +6400,16 @@
       </c>
       <c r="E112" s="135"/>
       <c r="F112" s="56" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G112" s="54" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H112" s="144"/>
     </row>
     <row r="113" spans="2:12" ht="15.75" customHeight="1">
       <c r="B113" s="38" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C113" s="14">
         <v>60</v>
@@ -6422,16 +6419,16 @@
       </c>
       <c r="E113" s="135"/>
       <c r="F113" s="56" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G113" s="54" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H113" s="144"/>
     </row>
     <row r="114" spans="2:12" ht="15.75" customHeight="1">
       <c r="B114" s="38" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C114" s="14">
         <v>130</v>
@@ -6441,16 +6438,16 @@
       </c>
       <c r="E114" s="135"/>
       <c r="F114" s="56" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G114" s="54" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H114" s="144"/>
     </row>
     <row r="115" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B115" s="51" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C115" s="17">
         <v>40</v>
@@ -6460,16 +6457,16 @@
       </c>
       <c r="E115" s="136"/>
       <c r="F115" s="57" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G115" s="54" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H115" s="145"/>
     </row>
     <row r="116" spans="2:12" ht="25.9" thickTop="1">
       <c r="B116" s="68" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C116" s="22">
         <v>630</v>
@@ -6481,13 +6478,13 @@
         <v>143</v>
       </c>
       <c r="F116" s="31" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G116" s="48" t="s">
         <v>73</v>
       </c>
       <c r="H116" s="143" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I116" s="29"/>
       <c r="J116" s="29"/>
@@ -6496,7 +6493,7 @@
     </row>
     <row r="117" spans="2:12" ht="15.75" customHeight="1">
       <c r="B117" s="70" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C117" s="14">
         <v>110</v>
@@ -6506,7 +6503,7 @@
       </c>
       <c r="E117" s="135"/>
       <c r="F117" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G117" s="12" t="s">
         <v>7</v>
@@ -6519,7 +6516,7 @@
     </row>
     <row r="118" spans="2:12" ht="15.75" customHeight="1">
       <c r="B118" s="70" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C118" s="14">
         <v>190</v>
@@ -6529,7 +6526,7 @@
       </c>
       <c r="E118" s="135"/>
       <c r="F118" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G118" s="55" t="s">
         <v>44</v>
@@ -6542,7 +6539,7 @@
     </row>
     <row r="119" spans="2:12" ht="15.75" customHeight="1">
       <c r="B119" s="70" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C119" s="14">
         <v>90</v>
@@ -6552,7 +6549,7 @@
       </c>
       <c r="E119" s="135"/>
       <c r="F119" s="15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G119" s="12" t="s">
         <v>7</v>
@@ -6565,7 +6562,7 @@
     </row>
     <row r="120" spans="2:12" ht="15.75" customHeight="1">
       <c r="B120" s="70" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C120" s="14">
         <v>180</v>
@@ -6575,7 +6572,7 @@
       </c>
       <c r="E120" s="135"/>
       <c r="F120" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G120" s="12" t="s">
         <v>7</v>
@@ -6588,7 +6585,7 @@
     </row>
     <row r="121" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B121" s="71" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C121" s="24">
         <v>60</v>
@@ -6598,7 +6595,7 @@
       </c>
       <c r="E121" s="137"/>
       <c r="F121" s="26" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G121" s="27" t="s">
         <v>45</v>
@@ -6623,13 +6620,13 @@
         <v>125</v>
       </c>
       <c r="F122" s="72" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G122" s="37" t="s">
         <v>75</v>
       </c>
       <c r="H122" s="143" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I122" s="29"/>
       <c r="J122" s="29"/>
@@ -6648,7 +6645,7 @@
       </c>
       <c r="E123" s="135"/>
       <c r="F123" s="56" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G123" s="12" t="s">
         <v>7</v>
@@ -6671,7 +6668,7 @@
       </c>
       <c r="E124" s="135"/>
       <c r="F124" s="56" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G124" s="54" t="s">
         <v>44</v>
@@ -6694,7 +6691,7 @@
       </c>
       <c r="E125" s="135"/>
       <c r="F125" s="56" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G125" s="12" t="s">
         <v>7</v>
@@ -6707,7 +6704,7 @@
     </row>
     <row r="126" spans="2:12" ht="15.75" customHeight="1">
       <c r="B126" s="38" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C126" s="14">
         <v>190</v>
@@ -6717,7 +6714,7 @@
       </c>
       <c r="E126" s="135"/>
       <c r="F126" s="56" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G126" s="12" t="s">
         <v>7</v>
@@ -6730,7 +6727,7 @@
     </row>
     <row r="127" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B127" s="39" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C127" s="24">
         <v>60</v>
@@ -6740,7 +6737,7 @@
       </c>
       <c r="E127" s="137"/>
       <c r="F127" s="73" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G127" s="27" t="s">
         <v>45</v>
@@ -6765,13 +6762,13 @@
         <v>143</v>
       </c>
       <c r="F128" s="72" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G128" s="48" t="s">
         <v>80</v>
       </c>
       <c r="H128" s="143" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="129" spans="2:12" ht="15.75" customHeight="1">
@@ -6786,7 +6783,7 @@
       </c>
       <c r="E129" s="135"/>
       <c r="F129" s="56" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G129" s="77" t="s">
         <v>115</v>
@@ -6795,7 +6792,7 @@
     </row>
     <row r="130" spans="2:12" ht="15.75" customHeight="1">
       <c r="B130" s="70" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C130" s="14">
         <v>190</v>
@@ -6805,7 +6802,7 @@
       </c>
       <c r="E130" s="135"/>
       <c r="F130" s="56" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G130" s="55" t="s">
         <v>44</v>
@@ -6814,7 +6811,7 @@
     </row>
     <row r="131" spans="2:12" ht="15.75" customHeight="1">
       <c r="B131" s="74" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C131" s="14">
         <v>90</v>
@@ -6824,7 +6821,7 @@
       </c>
       <c r="E131" s="135"/>
       <c r="F131" s="56" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G131" s="12" t="s">
         <v>7</v>
@@ -6833,7 +6830,7 @@
     </row>
     <row r="132" spans="2:12" ht="15.75" customHeight="1">
       <c r="B132" s="74" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C132" s="14">
         <v>180</v>
@@ -6843,7 +6840,7 @@
       </c>
       <c r="E132" s="135"/>
       <c r="F132" s="56" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G132" s="12" t="s">
         <v>7</v>
@@ -6852,7 +6849,7 @@
     </row>
     <row r="133" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B133" s="71" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C133" s="24">
         <v>60</v>
@@ -6862,7 +6859,7 @@
       </c>
       <c r="E133" s="137"/>
       <c r="F133" s="73" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G133" s="27" t="s">
         <v>82</v>
@@ -6883,13 +6880,13 @@
         <v>143</v>
       </c>
       <c r="F134" s="28" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G134" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H134" s="143" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I134" s="29"/>
       <c r="J134" s="29"/>
@@ -6908,7 +6905,7 @@
       </c>
       <c r="E135" s="135"/>
       <c r="F135" s="15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G135" s="12" t="s">
         <v>7</v>
@@ -6931,7 +6928,7 @@
       </c>
       <c r="E136" s="135"/>
       <c r="F136" s="15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G136" s="54" t="s">
         <v>44</v>
@@ -6944,7 +6941,7 @@
     </row>
     <row r="137" spans="2:12" ht="15.75" customHeight="1">
       <c r="B137" s="44" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C137" s="14">
         <v>80</v>
@@ -6954,7 +6951,7 @@
       </c>
       <c r="E137" s="135"/>
       <c r="F137" s="15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G137" s="12" t="s">
         <v>7</v>
@@ -6967,7 +6964,7 @@
     </row>
     <row r="138" spans="2:12" ht="15.75" customHeight="1">
       <c r="B138" s="44" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C138" s="14">
         <v>170</v>
@@ -6977,7 +6974,7 @@
       </c>
       <c r="E138" s="135"/>
       <c r="F138" s="15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G138" s="12" t="s">
         <v>7</v>
@@ -7000,7 +6997,7 @@
       </c>
       <c r="E139" s="136"/>
       <c r="F139" s="19" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G139" s="20" t="s">
         <v>45</v>
@@ -7025,13 +7022,13 @@
         <v>143</v>
       </c>
       <c r="F140" s="31" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G140" s="77" t="s">
         <v>88</v>
       </c>
       <c r="H140" s="143" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="141" spans="2:12" ht="15.75" customHeight="1">
@@ -7046,7 +7043,7 @@
       </c>
       <c r="E141" s="135"/>
       <c r="F141" s="15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G141" s="77" t="s">
         <v>90</v>
@@ -7055,7 +7052,7 @@
     </row>
     <row r="142" spans="2:12" ht="15.75" customHeight="1">
       <c r="B142" s="44" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C142" s="14">
         <v>180</v>
@@ -7065,7 +7062,7 @@
       </c>
       <c r="E142" s="135"/>
       <c r="F142" s="15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G142" s="78" t="s">
         <v>91</v>
@@ -7084,7 +7081,7 @@
       </c>
       <c r="E143" s="135"/>
       <c r="F143" s="15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G143" s="77" t="s">
         <v>90</v>
@@ -7093,7 +7090,7 @@
     </row>
     <row r="144" spans="2:12" ht="15.75" customHeight="1">
       <c r="B144" s="44" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C144" s="14">
         <v>170</v>
@@ -7103,7 +7100,7 @@
       </c>
       <c r="E144" s="135"/>
       <c r="F144" s="15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G144" s="77" t="s">
         <v>90</v>
@@ -7112,7 +7109,7 @@
     </row>
     <row r="145" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B145" s="64" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C145" s="17">
         <v>50</v>
@@ -7122,7 +7119,7 @@
       </c>
       <c r="E145" s="136"/>
       <c r="F145" s="19" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G145" s="20" t="s">
         <v>93</v>
@@ -7131,13 +7128,13 @@
     </row>
     <row r="146" spans="1:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B146" s="112" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C146" s="22">
         <v>615</v>
       </c>
       <c r="D146" s="79" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E146" s="134">
         <v>143</v>
@@ -7146,15 +7143,15 @@
         <v>63</v>
       </c>
       <c r="G146" s="48" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H146" s="146" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="147" spans="1:12" ht="15.75" customHeight="1">
       <c r="B147" s="44" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C147" s="14">
         <v>105</v>
@@ -7173,7 +7170,7 @@
     </row>
     <row r="148" spans="1:12" ht="15.75" customHeight="1">
       <c r="B148" s="44" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C148" s="14">
         <v>190</v>
@@ -7192,7 +7189,7 @@
     </row>
     <row r="149" spans="1:12" ht="15.75" customHeight="1">
       <c r="B149" s="44" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C149" s="14">
         <v>85</v>
@@ -7211,7 +7208,7 @@
     </row>
     <row r="150" spans="1:12" ht="15.75" customHeight="1">
       <c r="B150" s="44" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C150" s="14">
         <v>180</v>
@@ -7230,7 +7227,7 @@
     </row>
     <row r="151" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B151" s="64" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C151" s="17">
         <v>55</v>
@@ -7250,13 +7247,13 @@
     <row r="152" spans="1:12" ht="13.5" thickTop="1">
       <c r="A152" s="111"/>
       <c r="B152" s="110" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C152" s="22">
         <v>615</v>
       </c>
       <c r="D152" s="109" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E152" s="134">
         <v>143</v>
@@ -7265,21 +7262,21 @@
         <v>63</v>
       </c>
       <c r="G152" s="114" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H152" s="146" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="153" spans="1:12" ht="15.75" customHeight="1">
       <c r="B153" s="113" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C153" s="14">
         <v>105</v>
       </c>
       <c r="D153" s="109" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E153" s="135"/>
       <c r="F153" s="50" t="s">
@@ -7290,13 +7287,13 @@
     </row>
     <row r="154" spans="1:12" ht="15.75" customHeight="1">
       <c r="B154" s="113" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C154" s="14">
         <v>190</v>
       </c>
       <c r="D154" s="109" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E154" s="135"/>
       <c r="F154" s="50" t="s">
@@ -7309,13 +7306,13 @@
     </row>
     <row r="155" spans="1:12" ht="15.75" customHeight="1">
       <c r="B155" s="113" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C155" s="14">
         <v>85</v>
       </c>
       <c r="D155" s="109" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E155" s="135"/>
       <c r="F155" s="50" t="s">
@@ -7326,13 +7323,13 @@
     </row>
     <row r="156" spans="1:12" ht="15.75" customHeight="1">
       <c r="B156" s="113" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C156" s="14">
         <v>180</v>
       </c>
       <c r="D156" s="109" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E156" s="135"/>
       <c r="F156" s="50" t="s">
@@ -7343,13 +7340,13 @@
     </row>
     <row r="157" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B157" s="116" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C157" s="17">
         <v>55</v>
       </c>
       <c r="D157" s="109" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E157" s="136"/>
       <c r="F157" s="53" t="s">
@@ -7362,7 +7359,7 @@
     </row>
     <row r="158" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B158" s="82" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C158" s="22">
         <v>580</v>
@@ -7374,13 +7371,13 @@
         <v>167</v>
       </c>
       <c r="F158" s="31" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G158" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H158" s="143" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I158" s="29"/>
       <c r="J158" s="29"/>
@@ -7389,7 +7386,7 @@
     </row>
     <row r="159" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B159" s="84" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C159" s="14">
         <v>100</v>
@@ -7399,7 +7396,7 @@
       </c>
       <c r="E159" s="135"/>
       <c r="F159" s="15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G159" s="12" t="s">
         <v>7</v>
@@ -7412,7 +7409,7 @@
     </row>
     <row r="160" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B160" s="84" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C160" s="14">
         <v>180</v>
@@ -7422,7 +7419,7 @@
       </c>
       <c r="E160" s="135"/>
       <c r="F160" s="15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G160" s="54" t="s">
         <v>44</v>
@@ -7435,7 +7432,7 @@
     </row>
     <row r="161" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B161" s="84" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C161" s="14">
         <v>80</v>
@@ -7445,7 +7442,7 @@
       </c>
       <c r="E161" s="135"/>
       <c r="F161" s="15" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G161" s="12" t="s">
         <v>7</v>
@@ -7458,7 +7455,7 @@
     </row>
     <row r="162" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B162" s="84" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C162" s="14">
         <v>170</v>
@@ -7468,7 +7465,7 @@
       </c>
       <c r="E162" s="135"/>
       <c r="F162" s="15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G162" s="12" t="s">
         <v>7</v>
@@ -7481,7 +7478,7 @@
     </row>
     <row r="163" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B163" s="85" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C163" s="17">
         <v>50</v>
@@ -7491,7 +7488,7 @@
       </c>
       <c r="E163" s="136"/>
       <c r="F163" s="19" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G163" s="86" t="s">
         <v>45</v>
@@ -7516,13 +7513,13 @@
         <v>125</v>
       </c>
       <c r="F164" s="58" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G164" s="37" t="s">
         <v>97</v>
       </c>
       <c r="H164" s="143" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="165" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
@@ -7537,7 +7534,7 @@
       </c>
       <c r="E165" s="135"/>
       <c r="F165" s="56" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G165" s="12" t="s">
         <v>7</v>
@@ -7546,7 +7543,7 @@
     </row>
     <row r="166" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B166" s="38" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C166" s="14">
         <v>180</v>
@@ -7556,7 +7553,7 @@
       </c>
       <c r="E166" s="135"/>
       <c r="F166" s="56" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G166" s="54" t="s">
         <v>44</v>
@@ -7575,7 +7572,7 @@
       </c>
       <c r="E167" s="135"/>
       <c r="F167" s="56" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G167" s="12" t="s">
         <v>7</v>
@@ -7584,7 +7581,7 @@
     </row>
     <row r="168" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B168" s="87" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C168" s="14">
         <v>170</v>
@@ -7594,7 +7591,7 @@
       </c>
       <c r="E168" s="135"/>
       <c r="F168" s="56" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G168" s="12" t="s">
         <v>7</v>
@@ -7603,7 +7600,7 @@
     </row>
     <row r="169" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B169" s="51" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C169" s="17">
         <v>50</v>
@@ -7613,7 +7610,7 @@
       </c>
       <c r="E169" s="136"/>
       <c r="F169" s="57" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G169" s="20" t="s">
         <v>45</v>
@@ -7622,7 +7619,7 @@
     </row>
     <row r="170" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B170" s="40" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C170" s="9">
         <v>580</v>
@@ -7640,7 +7637,7 @@
         <v>7</v>
       </c>
       <c r="H170" s="143" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="I170" s="29"/>
       <c r="J170" s="29"/>
@@ -7649,7 +7646,7 @@
     </row>
     <row r="171" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B171" s="44" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C171" s="14">
         <v>100</v>
@@ -7672,7 +7669,7 @@
     </row>
     <row r="172" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B172" s="44" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C172" s="14">
         <v>180</v>
@@ -7695,7 +7692,7 @@
     </row>
     <row r="173" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B173" s="44" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C173" s="14">
         <v>80</v>
@@ -7718,7 +7715,7 @@
     </row>
     <row r="174" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B174" s="44" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C174" s="14">
         <v>170</v>
@@ -7741,7 +7738,7 @@
     </row>
     <row r="175" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B175" s="60" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C175" s="24">
         <v>50</v>
@@ -7776,13 +7773,13 @@
         <v>125</v>
       </c>
       <c r="F176" s="58" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G176" s="37" t="s">
         <v>104</v>
       </c>
       <c r="H176" s="143" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I176" s="29"/>
       <c r="J176" s="29"/>
@@ -7801,7 +7798,7 @@
       </c>
       <c r="E177" s="135"/>
       <c r="F177" s="56" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G177" s="12" t="s">
         <v>106</v>
@@ -7824,7 +7821,7 @@
       </c>
       <c r="E178" s="135"/>
       <c r="F178" s="56" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G178" s="78" t="s">
         <v>108</v>
@@ -7847,7 +7844,7 @@
       </c>
       <c r="E179" s="135"/>
       <c r="F179" s="56" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G179" s="12" t="s">
         <v>106</v>
@@ -7860,7 +7857,7 @@
     </row>
     <row r="180" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B180" s="38" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C180" s="14">
         <v>170</v>
@@ -7870,7 +7867,7 @@
       </c>
       <c r="E180" s="135"/>
       <c r="F180" s="56" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G180" s="12" t="s">
         <v>106</v>
@@ -7883,7 +7880,7 @@
     </row>
     <row r="181" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B181" s="51" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C181" s="17">
         <v>50</v>
@@ -7893,7 +7890,7 @@
       </c>
       <c r="E181" s="136"/>
       <c r="F181" s="88" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G181" s="20" t="s">
         <v>110</v>
@@ -7918,13 +7915,13 @@
         <v>167</v>
       </c>
       <c r="F182" s="28" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G182" s="54" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H182" s="143" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I182" s="29"/>
       <c r="J182" s="29"/>
@@ -7943,7 +7940,7 @@
       </c>
       <c r="E183" s="135"/>
       <c r="F183" s="15" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G183" s="12" t="s">
         <v>7</v>
@@ -7966,7 +7963,7 @@
       </c>
       <c r="E184" s="135"/>
       <c r="F184" s="15" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G184" s="54" t="s">
         <v>44</v>
@@ -7975,7 +7972,7 @@
     </row>
     <row r="185" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B185" s="42" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C185" s="14">
         <v>120</v>
@@ -7985,7 +7982,7 @@
       </c>
       <c r="E185" s="135"/>
       <c r="F185" s="15" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G185" s="12" t="s">
         <v>7</v>
@@ -8004,7 +8001,7 @@
       </c>
       <c r="E186" s="135"/>
       <c r="F186" s="15" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G186" s="12" t="s">
         <v>7</v>
@@ -8017,7 +8014,7 @@
     </row>
     <row r="187" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B187" s="64" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C187" s="17">
         <v>80</v>
@@ -8027,7 +8024,7 @@
       </c>
       <c r="E187" s="136"/>
       <c r="F187" s="19" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G187" s="20" t="s">
         <v>115</v>
@@ -8055,10 +8052,10 @@
         <v>7</v>
       </c>
       <c r="G188" s="54" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H188" s="143" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I188" s="29"/>
       <c r="J188" s="29"/>
@@ -8067,7 +8064,7 @@
     </row>
     <row r="189" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B189" s="44" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C189" s="14">
         <v>160</v>
@@ -8090,7 +8087,7 @@
     </row>
     <row r="190" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B190" s="44" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C190" s="14">
         <v>270</v>
@@ -8136,7 +8133,7 @@
     </row>
     <row r="192" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B192" s="44" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C192" s="14">
         <v>260</v>
@@ -8159,7 +8156,7 @@
     </row>
     <row r="193" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B193" s="60" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C193" s="24">
         <v>95</v>
@@ -8182,7 +8179,7 @@
     </row>
     <row r="194" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B194" s="36" t="s">
-        <v>118</v>
+        <v>433</v>
       </c>
       <c r="C194" s="22">
         <v>810</v>
@@ -8197,15 +8194,15 @@
         <v>7</v>
       </c>
       <c r="G194" s="37" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H194" s="143" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="195" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B195" s="38" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C195" s="14">
         <v>140</v>
@@ -8218,13 +8215,13 @@
         <v>7</v>
       </c>
       <c r="G195" s="54" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H195" s="144"/>
     </row>
     <row r="196" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B196" s="38" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C196" s="14">
         <v>240</v>
@@ -8243,7 +8240,7 @@
     </row>
     <row r="197" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B197" s="38" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C197" s="14">
         <v>120</v>
@@ -8262,7 +8259,7 @@
     </row>
     <row r="198" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B198" s="38" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C198" s="14">
         <v>230</v>
@@ -8281,7 +8278,7 @@
     </row>
     <row r="199" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B199" s="39" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C199" s="24">
         <v>80</v>
@@ -8300,7 +8297,7 @@
     </row>
     <row r="200" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B200" s="68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C200" s="22">
         <v>1525</v>
@@ -8313,15 +8310,15 @@
       </c>
       <c r="F200" s="72"/>
       <c r="G200" s="48" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H200" s="150" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="201" spans="2:12" ht="15.75" customHeight="1">
       <c r="B201" s="74" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C201" s="14">
         <v>160</v>
@@ -8336,7 +8333,7 @@
     </row>
     <row r="202" spans="2:12" ht="15.75" customHeight="1">
       <c r="B202" s="70" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C202" s="14">
         <v>270</v>
@@ -8353,7 +8350,7 @@
     </row>
     <row r="203" spans="2:12" ht="15.75" customHeight="1">
       <c r="B203" s="70" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C203" s="14">
         <v>140</v>
@@ -8370,7 +8367,7 @@
     </row>
     <row r="204" spans="2:12" ht="15.75" customHeight="1">
       <c r="B204" s="70" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C204" s="14">
         <v>260</v>
@@ -8387,7 +8384,7 @@
     </row>
     <row r="205" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B205" s="71" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C205" s="24">
         <v>95</v>
@@ -8404,7 +8401,7 @@
     </row>
     <row r="206" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B206" s="117" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C206" s="22">
         <v>1110</v>
@@ -8416,18 +8413,18 @@
         <v>167</v>
       </c>
       <c r="F206" s="127" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G206" s="114" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H206" s="143" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="207" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B207" s="74" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C207" s="14">
         <v>200</v>
@@ -8437,16 +8434,16 @@
       </c>
       <c r="E207" s="135"/>
       <c r="F207" s="127" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G207" s="119" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H207" s="144"/>
     </row>
     <row r="208" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B208" s="125" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C208" s="14">
         <v>300</v>
@@ -8456,16 +8453,16 @@
       </c>
       <c r="E208" s="135"/>
       <c r="F208" s="127" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G208" s="120" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H208" s="144"/>
     </row>
     <row r="209" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B209" s="125" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C209" s="14">
         <v>180</v>
@@ -8475,16 +8472,16 @@
       </c>
       <c r="E209" s="135"/>
       <c r="F209" s="127" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G209" s="119" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H209" s="144"/>
     </row>
     <row r="210" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B210" s="125" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C210" s="14">
         <v>290</v>
@@ -8494,16 +8491,16 @@
       </c>
       <c r="E210" s="135"/>
       <c r="F210" s="127" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G210" s="122" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H210" s="144"/>
     </row>
     <row r="211" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B211" s="126" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C211" s="24">
         <v>140</v>
@@ -8513,16 +8510,16 @@
       </c>
       <c r="E211" s="137"/>
       <c r="F211" s="127" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G211" s="121" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H211" s="145"/>
     </row>
     <row r="212" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B212" s="117" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C212" s="22">
         <v>1110</v>
@@ -8534,18 +8531,18 @@
         <v>167</v>
       </c>
       <c r="F212" s="127" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G212" s="114" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H212" s="143" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="213" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B213" s="74" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C213" s="14">
         <v>200</v>
@@ -8555,16 +8552,16 @@
       </c>
       <c r="E213" s="141"/>
       <c r="F213" s="127" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G213" s="118" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H213" s="144"/>
     </row>
     <row r="214" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B214" s="125" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C214" s="14">
         <v>300</v>
@@ -8574,16 +8571,16 @@
       </c>
       <c r="E214" s="141"/>
       <c r="F214" s="127" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G214" s="118" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H214" s="144"/>
     </row>
     <row r="215" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B215" s="125" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C215" s="14">
         <v>180</v>
@@ -8593,16 +8590,16 @@
       </c>
       <c r="E215" s="141"/>
       <c r="F215" s="127" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G215" s="118" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H215" s="144"/>
     </row>
     <row r="216" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B216" s="125" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C216" s="14">
         <v>290</v>
@@ -8612,16 +8609,16 @@
       </c>
       <c r="E216" s="141"/>
       <c r="F216" s="127" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G216" s="118" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H216" s="144"/>
     </row>
     <row r="217" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B217" s="126" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C217" s="123">
         <v>140</v>
@@ -8631,16 +8628,16 @@
       </c>
       <c r="E217" s="142"/>
       <c r="F217" s="127" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G217" s="119" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H217" s="145"/>
     </row>
     <row r="218" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B218" s="91" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C218" s="92">
         <v>5</v>
@@ -8652,18 +8649,18 @@
         <v>100</v>
       </c>
       <c r="F218" s="94" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G218" s="59" t="s">
         <v>17</v>
       </c>
       <c r="H218" s="128" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="219" spans="2:8" ht="15.75" customHeight="1">
       <c r="B219" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C219" s="14">
         <v>12</v>
@@ -8681,12 +8678,12 @@
         <v>7</v>
       </c>
       <c r="H219" s="128" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="220" spans="2:8" ht="15.75" customHeight="1">
       <c r="B220" s="44" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C220" s="14">
         <v>30</v>
@@ -8704,12 +8701,12 @@
         <v>7</v>
       </c>
       <c r="H220" s="129" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="221" spans="2:8" ht="15.75" customHeight="1">
       <c r="B221" s="44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C221" s="14">
         <v>35</v>
@@ -8721,18 +8718,18 @@
         <v>100</v>
       </c>
       <c r="F221" s="15" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G221" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H221" s="128" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="222" spans="2:8" ht="15.75" customHeight="1">
       <c r="B222" s="13" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C222" s="14">
         <v>58</v>
@@ -8744,18 +8741,18 @@
         <v>100</v>
       </c>
       <c r="F222" s="96" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G222" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H222" s="128" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="223" spans="2:8" ht="15.75" customHeight="1">
       <c r="B223" s="38" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C223" s="14">
         <v>60</v>
@@ -8770,15 +8767,15 @@
         <v>7</v>
       </c>
       <c r="G223" s="54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H223" s="130" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="224" spans="2:8" ht="15.75" customHeight="1">
       <c r="B224" s="44" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C224" s="14">
         <v>70</v>
@@ -8796,12 +8793,12 @@
         <v>7</v>
       </c>
       <c r="H224" s="128" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="225" spans="2:8" ht="15.75" customHeight="1">
       <c r="B225" s="44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C225" s="14">
         <v>70</v>
@@ -8819,12 +8816,12 @@
         <v>7</v>
       </c>
       <c r="H225" s="128" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="226" spans="2:8" ht="15.75" customHeight="1">
       <c r="B226" s="97" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C226" s="14">
         <v>110</v>
@@ -8842,12 +8839,12 @@
         <v>7</v>
       </c>
       <c r="H226" s="128" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="227" spans="2:8" ht="15.75" customHeight="1">
       <c r="B227" s="44" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C227" s="14">
         <v>115</v>
@@ -8859,18 +8856,18 @@
         <v>143</v>
       </c>
       <c r="F227" s="15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G227" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H227" s="128" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="228" spans="2:8" ht="15.75" customHeight="1">
       <c r="B228" s="133" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C228" s="14">
         <v>150</v>
@@ -8882,18 +8879,18 @@
         <v>125</v>
       </c>
       <c r="F228" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G228" s="54" t="s">
         <v>44</v>
       </c>
       <c r="H228" s="128" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="229" spans="2:8" ht="15.75" customHeight="1">
       <c r="B229" s="44" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C229" s="14">
         <v>160</v>
@@ -8905,18 +8902,18 @@
         <v>167</v>
       </c>
       <c r="F229" s="56" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G229" s="12" t="s">
         <v>7</v>
       </c>
       <c r="H229" s="129" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="230" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B230" s="131" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C230" s="24">
         <v>200</v>
@@ -8931,10 +8928,10 @@
         <v>7</v>
       </c>
       <c r="G230" s="27" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H230" s="132" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="231" spans="2:8" ht="15.75" customHeight="1" thickTop="1">

--- a/data-source/护甲数据.xlsx
+++ b/data-source/护甲数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1B7A21-A3A0-4DDE-98AF-A918DA809780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C50D7EE-0525-43AA-8E03-6C568D1FF4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="435">
   <si>
     <t>护甲</t>
   </si>
@@ -2339,6 +2339,9 @@
   </si>
   <si>
     <t xml:space="preserve">角斗士套装（T6级）  </t>
+  </si>
+  <si>
+    <t>酷吏二层，叛徒地下墓穴</t>
   </si>
 </sst>
 </file>
@@ -3309,7 +3312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3706,45 +3709,48 @@
     <xf numFmtId="0" fontId="22" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4078,7 +4084,7 @@
       <c r="D2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="138">
+      <c r="E2" s="150">
         <v>91</v>
       </c>
       <c r="F2" s="11" t="s">
@@ -4087,7 +4093,7 @@
       <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="143" t="s">
+      <c r="H2" s="134" t="s">
         <v>398</v>
       </c>
     </row>
@@ -4101,14 +4107,14 @@
       <c r="D3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="135"/>
+      <c r="E3" s="146"/>
       <c r="F3" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="144"/>
+      <c r="H3" s="135"/>
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1">
       <c r="B4" s="13" t="s">
@@ -4120,14 +4126,14 @@
       <c r="D4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="135"/>
+      <c r="E4" s="146"/>
       <c r="F4" s="15" t="s">
         <v>329</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="144"/>
+      <c r="H4" s="135"/>
     </row>
     <row r="5" spans="2:8" ht="15.75" customHeight="1">
       <c r="B5" s="13" t="s">
@@ -4139,14 +4145,14 @@
       <c r="D5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="135"/>
+      <c r="E5" s="146"/>
       <c r="F5" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="144"/>
+      <c r="H5" s="135"/>
     </row>
     <row r="6" spans="2:8" ht="15.75" customHeight="1">
       <c r="B6" s="13" t="s">
@@ -4158,14 +4164,14 @@
       <c r="D6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="135"/>
+      <c r="E6" s="146"/>
       <c r="F6" s="15" t="s">
         <v>329</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="144"/>
+      <c r="H6" s="135"/>
     </row>
     <row r="7" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B7" s="16" t="s">
@@ -4177,14 +4183,14 @@
       <c r="D7" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="136"/>
+      <c r="E7" s="149"/>
       <c r="F7" s="19" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="145"/>
+      <c r="H7" s="137"/>
     </row>
     <row r="8" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B8" s="21" t="s">
@@ -4196,7 +4202,7 @@
       <c r="D8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="134">
+      <c r="E8" s="145">
         <v>91</v>
       </c>
       <c r="F8" s="11" t="s">
@@ -4205,7 +4211,7 @@
       <c r="G8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="143" t="s">
+      <c r="H8" s="134" t="s">
         <v>399</v>
       </c>
     </row>
@@ -4219,14 +4225,14 @@
       <c r="D9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="135"/>
+      <c r="E9" s="146"/>
       <c r="F9" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="144"/>
+      <c r="H9" s="135"/>
     </row>
     <row r="10" spans="2:8" ht="15.75" customHeight="1">
       <c r="B10" s="13" t="s">
@@ -4238,14 +4244,14 @@
       <c r="D10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="135"/>
+      <c r="E10" s="146"/>
       <c r="F10" s="15" t="s">
         <v>329</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="144"/>
+      <c r="H10" s="135"/>
     </row>
     <row r="11" spans="2:8" ht="15.75" customHeight="1">
       <c r="B11" s="13" t="s">
@@ -4257,14 +4263,14 @@
       <c r="D11" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="135"/>
+      <c r="E11" s="146"/>
       <c r="F11" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="144"/>
+      <c r="H11" s="135"/>
     </row>
     <row r="12" spans="2:8" ht="15.75" customHeight="1">
       <c r="B12" s="13" t="s">
@@ -4276,14 +4282,14 @@
       <c r="D12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="135"/>
+      <c r="E12" s="146"/>
       <c r="F12" s="15" t="s">
         <v>329</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="144"/>
+      <c r="H12" s="135"/>
     </row>
     <row r="13" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B13" s="23" t="s">
@@ -4295,14 +4301,14 @@
       <c r="D13" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="137"/>
+      <c r="E13" s="147"/>
       <c r="F13" s="26" t="s">
         <v>9</v>
       </c>
       <c r="G13" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="145"/>
+      <c r="H13" s="137"/>
     </row>
     <row r="14" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B14" s="8" t="s">
@@ -4314,7 +4320,7 @@
       <c r="D14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="139">
+      <c r="E14" s="148">
         <v>100</v>
       </c>
       <c r="F14" s="28" t="s">
@@ -4323,7 +4329,7 @@
       <c r="G14" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="143" t="s">
+      <c r="H14" s="134" t="s">
         <v>398</v>
       </c>
     </row>
@@ -4337,14 +4343,14 @@
       <c r="D15" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="135"/>
+      <c r="E15" s="146"/>
       <c r="F15" s="15" t="s">
         <v>331</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H15" s="144"/>
+      <c r="H15" s="135"/>
     </row>
     <row r="16" spans="2:8" ht="15.75" customHeight="1">
       <c r="B16" s="13" t="s">
@@ -4356,14 +4362,14 @@
       <c r="D16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="135"/>
+      <c r="E16" s="146"/>
       <c r="F16" s="15" t="s">
         <v>332</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="144"/>
+      <c r="H16" s="135"/>
     </row>
     <row r="17" spans="2:12" ht="15.75" customHeight="1">
       <c r="B17" s="13" t="s">
@@ -4375,14 +4381,14 @@
       <c r="D17" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="135"/>
+      <c r="E17" s="146"/>
       <c r="F17" s="15" t="s">
         <v>333</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H17" s="144"/>
+      <c r="H17" s="135"/>
       <c r="I17" s="29"/>
       <c r="J17" s="29"/>
       <c r="K17" s="29"/>
@@ -4398,14 +4404,14 @@
       <c r="D18" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="135"/>
+      <c r="E18" s="146"/>
       <c r="F18" s="15" t="s">
         <v>332</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="144"/>
+      <c r="H18" s="135"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
       <c r="K18" s="29"/>
@@ -4421,14 +4427,14 @@
       <c r="D19" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="136"/>
+      <c r="E19" s="149"/>
       <c r="F19" s="19" t="s">
         <v>334</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="145"/>
+      <c r="H19" s="137"/>
       <c r="I19" s="29"/>
       <c r="J19" s="29"/>
       <c r="K19" s="29"/>
@@ -4444,7 +4450,7 @@
       <c r="D20" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="134">
+      <c r="E20" s="145">
         <v>100</v>
       </c>
       <c r="F20" s="11" t="s">
@@ -4453,7 +4459,7 @@
       <c r="G20" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="H20" s="143" t="s">
+      <c r="H20" s="134" t="s">
         <v>400</v>
       </c>
     </row>
@@ -4467,14 +4473,14 @@
       <c r="D21" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="135"/>
+      <c r="E21" s="146"/>
       <c r="F21" s="15" t="s">
         <v>331</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H21" s="144"/>
+      <c r="H21" s="135"/>
     </row>
     <row r="22" spans="2:12" ht="15.75" customHeight="1">
       <c r="B22" s="13" t="s">
@@ -4486,14 +4492,14 @@
       <c r="D22" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="135"/>
+      <c r="E22" s="146"/>
       <c r="F22" s="15" t="s">
         <v>332</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H22" s="144"/>
+      <c r="H22" s="135"/>
     </row>
     <row r="23" spans="2:12" ht="15.75" customHeight="1">
       <c r="B23" s="13" t="s">
@@ -4505,14 +4511,14 @@
       <c r="D23" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="135"/>
+      <c r="E23" s="146"/>
       <c r="F23" s="15" t="s">
         <v>333</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H23" s="144"/>
+      <c r="H23" s="135"/>
     </row>
     <row r="24" spans="2:12" ht="15.75" customHeight="1">
       <c r="B24" s="13" t="s">
@@ -4524,14 +4530,14 @@
       <c r="D24" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="135"/>
+      <c r="E24" s="146"/>
       <c r="F24" s="15" t="s">
         <v>332</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H24" s="144"/>
+      <c r="H24" s="135"/>
     </row>
     <row r="25" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B25" s="107" t="s">
@@ -4543,14 +4549,14 @@
       <c r="D25" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="136"/>
+      <c r="E25" s="149"/>
       <c r="F25" s="19" t="s">
         <v>334</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H25" s="145"/>
+      <c r="H25" s="137"/>
     </row>
     <row r="26" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B26" s="21" t="s">
@@ -4562,7 +4568,7 @@
       <c r="D26" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="134">
+      <c r="E26" s="145">
         <v>100</v>
       </c>
       <c r="F26" s="31" t="s">
@@ -4571,7 +4577,7 @@
       <c r="G26" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H26" s="143" t="s">
+      <c r="H26" s="134" t="s">
         <v>399</v>
       </c>
     </row>
@@ -4585,14 +4591,14 @@
       <c r="D27" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="135"/>
+      <c r="E27" s="146"/>
       <c r="F27" s="15" t="s">
         <v>331</v>
       </c>
       <c r="G27" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H27" s="144"/>
+      <c r="H27" s="135"/>
     </row>
     <row r="28" spans="2:12" ht="15.75" customHeight="1">
       <c r="B28" s="13" t="s">
@@ -4604,14 +4610,14 @@
       <c r="D28" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="135"/>
+      <c r="E28" s="146"/>
       <c r="F28" s="15" t="s">
         <v>332</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H28" s="144"/>
+      <c r="H28" s="135"/>
     </row>
     <row r="29" spans="2:12" ht="15.75" customHeight="1">
       <c r="B29" s="13" t="s">
@@ -4623,14 +4629,14 @@
       <c r="D29" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="135"/>
+      <c r="E29" s="146"/>
       <c r="F29" s="15" t="s">
         <v>333</v>
       </c>
       <c r="G29" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H29" s="144"/>
+      <c r="H29" s="135"/>
     </row>
     <row r="30" spans="2:12" ht="15.75" customHeight="1">
       <c r="B30" s="13" t="s">
@@ -4642,14 +4648,14 @@
       <c r="D30" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="135"/>
+      <c r="E30" s="146"/>
       <c r="F30" s="15" t="s">
         <v>332</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H30" s="144"/>
+      <c r="H30" s="135"/>
     </row>
     <row r="31" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B31" s="32" t="s">
@@ -4661,14 +4667,14 @@
       <c r="D31" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="137"/>
+      <c r="E31" s="147"/>
       <c r="F31" s="34" t="s">
         <v>334</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H31" s="145"/>
+      <c r="H31" s="137"/>
     </row>
     <row r="32" spans="2:12" ht="25.9" thickTop="1">
       <c r="B32" s="36" t="s">
@@ -4680,7 +4686,7 @@
       <c r="D32" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="134">
+      <c r="E32" s="145">
         <v>112</v>
       </c>
       <c r="F32" s="31" t="s">
@@ -4689,7 +4695,7 @@
       <c r="G32" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="H32" s="143" t="s">
+      <c r="H32" s="134" t="s">
         <v>399</v>
       </c>
       <c r="I32" s="29"/>
@@ -4707,14 +4713,14 @@
       <c r="D33" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="135"/>
+      <c r="E33" s="146"/>
       <c r="F33" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H33" s="144"/>
+      <c r="H33" s="135"/>
       <c r="I33" s="29"/>
       <c r="J33" s="29"/>
       <c r="K33" s="29"/>
@@ -4730,14 +4736,14 @@
       <c r="D34" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="135"/>
+      <c r="E34" s="146"/>
       <c r="F34" s="15" t="s">
         <v>337</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="144"/>
+      <c r="H34" s="135"/>
       <c r="I34" s="29"/>
       <c r="J34" s="29"/>
       <c r="K34" s="29"/>
@@ -4753,14 +4759,14 @@
       <c r="D35" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="135"/>
+      <c r="E35" s="146"/>
       <c r="F35" s="15" t="s">
         <v>338</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H35" s="144"/>
+      <c r="H35" s="135"/>
       <c r="I35" s="29"/>
       <c r="J35" s="29"/>
       <c r="K35" s="29"/>
@@ -4776,14 +4782,14 @@
       <c r="D36" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="135"/>
+      <c r="E36" s="146"/>
       <c r="F36" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H36" s="144"/>
+      <c r="H36" s="135"/>
       <c r="I36" s="29"/>
       <c r="J36" s="29"/>
       <c r="K36" s="29"/>
@@ -4799,14 +4805,14 @@
       <c r="D37" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E37" s="137"/>
+      <c r="E37" s="147"/>
       <c r="F37" s="26" t="s">
         <v>340</v>
       </c>
       <c r="G37" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="H37" s="145"/>
+      <c r="H37" s="137"/>
       <c r="I37" s="29"/>
       <c r="J37" s="29"/>
       <c r="K37" s="29"/>
@@ -4822,7 +4828,7 @@
       <c r="D38" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="134">
+      <c r="E38" s="145">
         <v>100</v>
       </c>
       <c r="F38" s="11" t="s">
@@ -4831,7 +4837,7 @@
       <c r="G38" s="41" t="s">
         <v>432</v>
       </c>
-      <c r="H38" s="143" t="s">
+      <c r="H38" s="134" t="s">
         <v>399</v>
       </c>
       <c r="I38" s="29"/>
@@ -4849,14 +4855,14 @@
       <c r="D39" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E39" s="135"/>
+      <c r="E39" s="146"/>
       <c r="F39" s="15" t="s">
         <v>331</v>
       </c>
       <c r="G39" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="H39" s="144"/>
+      <c r="H39" s="135"/>
       <c r="I39" s="29"/>
       <c r="J39" s="29"/>
       <c r="K39" s="29"/>
@@ -4872,14 +4878,14 @@
       <c r="D40" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E40" s="135"/>
+      <c r="E40" s="146"/>
       <c r="F40" s="15" t="s">
         <v>332</v>
       </c>
       <c r="G40" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="H40" s="144"/>
+      <c r="H40" s="135"/>
       <c r="I40" s="29"/>
       <c r="J40" s="29"/>
       <c r="K40" s="29"/>
@@ -4895,14 +4901,14 @@
       <c r="D41" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E41" s="135"/>
+      <c r="E41" s="146"/>
       <c r="F41" s="15" t="s">
         <v>333</v>
       </c>
       <c r="G41" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="H41" s="144"/>
+      <c r="H41" s="135"/>
       <c r="I41" s="29"/>
       <c r="J41" s="29"/>
       <c r="K41" s="29"/>
@@ -4918,14 +4924,14 @@
       <c r="D42" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E42" s="135"/>
+      <c r="E42" s="146"/>
       <c r="F42" s="15" t="s">
         <v>332</v>
       </c>
       <c r="G42" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="H42" s="144"/>
+      <c r="H42" s="135"/>
       <c r="I42" s="29"/>
       <c r="J42" s="29"/>
       <c r="K42" s="29"/>
@@ -4941,14 +4947,14 @@
       <c r="D43" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E43" s="137"/>
+      <c r="E43" s="147"/>
       <c r="F43" s="26" t="s">
         <v>334</v>
       </c>
       <c r="G43" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="H43" s="145"/>
+      <c r="H43" s="137"/>
       <c r="I43" s="29"/>
       <c r="J43" s="29"/>
       <c r="K43" s="29"/>
@@ -4964,7 +4970,7 @@
       <c r="D44" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E44" s="138">
+      <c r="E44" s="150">
         <v>112</v>
       </c>
       <c r="F44" s="11" t="s">
@@ -4973,7 +4979,7 @@
       <c r="G44" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H44" s="143" t="s">
+      <c r="H44" s="134" t="s">
         <v>398</v>
       </c>
       <c r="I44" s="29"/>
@@ -4991,14 +4997,14 @@
       <c r="D45" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E45" s="135"/>
+      <c r="E45" s="146"/>
       <c r="F45" s="15" t="s">
         <v>32</v>
       </c>
       <c r="G45" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H45" s="144"/>
+      <c r="H45" s="135"/>
       <c r="I45" s="29"/>
       <c r="J45" s="29"/>
       <c r="K45" s="29"/>
@@ -5014,14 +5020,14 @@
       <c r="D46" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E46" s="135"/>
+      <c r="E46" s="146"/>
       <c r="F46" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G46" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H46" s="144"/>
+      <c r="H46" s="135"/>
       <c r="I46" s="29"/>
       <c r="J46" s="29"/>
       <c r="K46" s="29"/>
@@ -5037,14 +5043,14 @@
       <c r="D47" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E47" s="135"/>
+      <c r="E47" s="146"/>
       <c r="F47" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G47" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H47" s="144"/>
+      <c r="H47" s="135"/>
       <c r="I47" s="29"/>
       <c r="J47" s="29"/>
       <c r="K47" s="29"/>
@@ -5060,14 +5066,14 @@
       <c r="D48" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E48" s="135"/>
+      <c r="E48" s="146"/>
       <c r="F48" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G48" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H48" s="144"/>
+      <c r="H48" s="135"/>
       <c r="I48" s="29"/>
       <c r="J48" s="29"/>
       <c r="K48" s="29"/>
@@ -5083,14 +5089,14 @@
       <c r="D49" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E49" s="136"/>
+      <c r="E49" s="149"/>
       <c r="F49" s="19" t="s">
         <v>342</v>
       </c>
       <c r="G49" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="H49" s="145"/>
+      <c r="H49" s="137"/>
       <c r="I49" s="29"/>
       <c r="J49" s="29"/>
       <c r="K49" s="29"/>
@@ -5106,7 +5112,7 @@
       <c r="D50" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E50" s="134">
+      <c r="E50" s="145">
         <v>112</v>
       </c>
       <c r="F50" s="15" t="s">
@@ -5115,7 +5121,7 @@
       <c r="G50" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H50" s="143" t="s">
+      <c r="H50" s="134" t="s">
         <v>401</v>
       </c>
     </row>
@@ -5129,14 +5135,14 @@
       <c r="D51" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E51" s="135"/>
+      <c r="E51" s="146"/>
       <c r="F51" s="15" t="s">
         <v>32</v>
       </c>
       <c r="G51" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H51" s="144"/>
+      <c r="H51" s="135"/>
     </row>
     <row r="52" spans="2:12" ht="15.75" customHeight="1">
       <c r="B52" s="13" t="s">
@@ -5148,14 +5154,14 @@
       <c r="D52" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E52" s="135"/>
+      <c r="E52" s="146"/>
       <c r="F52" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G52" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H52" s="144"/>
+      <c r="H52" s="135"/>
     </row>
     <row r="53" spans="2:12" ht="15.75" customHeight="1">
       <c r="B53" s="13" t="s">
@@ -5167,14 +5173,14 @@
       <c r="D53" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E53" s="135"/>
+      <c r="E53" s="146"/>
       <c r="F53" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G53" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H53" s="144"/>
+      <c r="H53" s="135"/>
     </row>
     <row r="54" spans="2:12" ht="15.75" customHeight="1">
       <c r="B54" s="13" t="s">
@@ -5186,14 +5192,14 @@
       <c r="D54" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E54" s="135"/>
+      <c r="E54" s="146"/>
       <c r="F54" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H54" s="144"/>
+      <c r="H54" s="135"/>
     </row>
     <row r="55" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B55" s="16" t="s">
@@ -5205,14 +5211,14 @@
       <c r="D55" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E55" s="136"/>
+      <c r="E55" s="149"/>
       <c r="F55" s="19" t="s">
         <v>342</v>
       </c>
       <c r="G55" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="H55" s="145"/>
+      <c r="H55" s="137"/>
     </row>
     <row r="56" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B56" s="36" t="s">
@@ -5224,7 +5230,7 @@
       <c r="D56" s="63" t="s">
         <v>176</v>
       </c>
-      <c r="E56" s="134">
+      <c r="E56" s="145">
         <v>112</v>
       </c>
       <c r="F56" s="47" t="s">
@@ -5233,7 +5239,7 @@
       <c r="G56" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="H56" s="143" t="s">
+      <c r="H56" s="134" t="s">
         <v>402</v>
       </c>
     </row>
@@ -5247,14 +5253,14 @@
       <c r="D57" s="63" t="s">
         <v>174</v>
       </c>
-      <c r="E57" s="135"/>
+      <c r="E57" s="146"/>
       <c r="F57" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G57" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H57" s="144"/>
+      <c r="H57" s="135"/>
     </row>
     <row r="58" spans="2:12" ht="15.75" customHeight="1">
       <c r="B58" s="38" t="s">
@@ -5266,14 +5272,14 @@
       <c r="D58" s="63" t="s">
         <v>175</v>
       </c>
-      <c r="E58" s="135"/>
+      <c r="E58" s="146"/>
       <c r="F58" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G58" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H58" s="144"/>
+      <c r="H58" s="135"/>
     </row>
     <row r="59" spans="2:12" ht="15.75" customHeight="1">
       <c r="B59" s="38" t="s">
@@ -5285,14 +5291,14 @@
       <c r="D59" s="63" t="s">
         <v>174</v>
       </c>
-      <c r="E59" s="135"/>
+      <c r="E59" s="146"/>
       <c r="F59" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G59" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H59" s="144"/>
+      <c r="H59" s="135"/>
     </row>
     <row r="60" spans="2:12" ht="15.75" customHeight="1">
       <c r="B60" s="38" t="s">
@@ -5304,14 +5310,14 @@
       <c r="D60" s="63" t="s">
         <v>175</v>
       </c>
-      <c r="E60" s="135"/>
+      <c r="E60" s="146"/>
       <c r="F60" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G60" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H60" s="144"/>
+      <c r="H60" s="135"/>
     </row>
     <row r="61" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B61" s="51" t="s">
@@ -5323,14 +5329,14 @@
       <c r="D61" s="63" t="s">
         <v>174</v>
       </c>
-      <c r="E61" s="136"/>
+      <c r="E61" s="149"/>
       <c r="F61" s="53" t="s">
         <v>7</v>
       </c>
       <c r="G61" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="H61" s="145"/>
+      <c r="H61" s="137"/>
     </row>
     <row r="62" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B62" s="36" t="s">
@@ -5342,7 +5348,7 @@
       <c r="D62" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E62" s="134">
+      <c r="E62" s="145">
         <v>143</v>
       </c>
       <c r="F62" s="31" t="s">
@@ -5351,7 +5357,7 @@
       <c r="G62" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="H62" s="143" t="s">
+      <c r="H62" s="134" t="s">
         <v>399</v>
       </c>
       <c r="I62" s="29"/>
@@ -5369,14 +5375,14 @@
       <c r="D63" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E63" s="135"/>
+      <c r="E63" s="146"/>
       <c r="F63" s="15" t="s">
         <v>415</v>
       </c>
       <c r="G63" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="H63" s="144"/>
+      <c r="H63" s="135"/>
       <c r="I63" s="29"/>
       <c r="J63" s="29"/>
       <c r="K63" s="29"/>
@@ -5392,14 +5398,14 @@
       <c r="D64" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E64" s="135"/>
+      <c r="E64" s="146"/>
       <c r="F64" s="15" t="s">
         <v>416</v>
       </c>
       <c r="G64" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="H64" s="144"/>
+      <c r="H64" s="135"/>
       <c r="I64" s="29"/>
       <c r="J64" s="29"/>
       <c r="K64" s="29"/>
@@ -5415,14 +5421,14 @@
       <c r="D65" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E65" s="135"/>
+      <c r="E65" s="146"/>
       <c r="F65" s="15" t="s">
         <v>417</v>
       </c>
       <c r="G65" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H65" s="144"/>
+      <c r="H65" s="135"/>
       <c r="I65" s="29"/>
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
@@ -5438,14 +5444,14 @@
       <c r="D66" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E66" s="135"/>
+      <c r="E66" s="146"/>
       <c r="F66" s="15" t="s">
         <v>418</v>
       </c>
       <c r="G66" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H66" s="144"/>
+      <c r="H66" s="135"/>
       <c r="I66" s="29"/>
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
@@ -5459,14 +5465,14 @@
         <v>12</v>
       </c>
       <c r="D67" s="18"/>
-      <c r="E67" s="136"/>
+      <c r="E67" s="149"/>
       <c r="F67" s="19" t="s">
         <v>419</v>
       </c>
       <c r="G67" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="H67" s="145"/>
+      <c r="H67" s="137"/>
       <c r="I67" s="29"/>
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
@@ -5482,7 +5488,7 @@
       <c r="D68" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E68" s="134">
+      <c r="E68" s="145">
         <v>143</v>
       </c>
       <c r="F68" s="31" t="s">
@@ -5491,7 +5497,7 @@
       <c r="G68" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="H68" s="143" t="s">
+      <c r="H68" s="134" t="s">
         <v>399</v>
       </c>
     </row>
@@ -5505,14 +5511,14 @@
       <c r="D69" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E69" s="135"/>
+      <c r="E69" s="146"/>
       <c r="F69" s="56" t="s">
         <v>195</v>
       </c>
       <c r="G69" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="H69" s="144"/>
+      <c r="H69" s="135"/>
     </row>
     <row r="70" spans="2:12" ht="15.75" customHeight="1">
       <c r="B70" s="38" t="s">
@@ -5524,14 +5530,14 @@
       <c r="D70" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E70" s="135"/>
+      <c r="E70" s="146"/>
       <c r="F70" s="15" t="s">
         <v>196</v>
       </c>
       <c r="G70" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H70" s="144"/>
+      <c r="H70" s="135"/>
     </row>
     <row r="71" spans="2:12" ht="15.75" customHeight="1">
       <c r="B71" s="38" t="s">
@@ -5543,14 +5549,14 @@
       <c r="D71" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E71" s="135"/>
+      <c r="E71" s="146"/>
       <c r="F71" s="56" t="s">
         <v>421</v>
       </c>
       <c r="G71" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H71" s="144"/>
+      <c r="H71" s="135"/>
     </row>
     <row r="72" spans="2:12" ht="15.75" customHeight="1">
       <c r="B72" s="38" t="s">
@@ -5562,14 +5568,14 @@
       <c r="D72" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E72" s="135"/>
+      <c r="E72" s="146"/>
       <c r="F72" s="15" t="s">
         <v>197</v>
       </c>
       <c r="G72" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H72" s="144"/>
+      <c r="H72" s="135"/>
     </row>
     <row r="73" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B73" s="51" t="s">
@@ -5581,14 +5587,14 @@
       <c r="D73" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E73" s="136"/>
+      <c r="E73" s="149"/>
       <c r="F73" s="57" t="s">
         <v>198</v>
       </c>
       <c r="G73" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="H73" s="145"/>
+      <c r="H73" s="137"/>
     </row>
     <row r="74" spans="2:12" ht="31.5" customHeight="1" thickTop="1">
       <c r="B74" s="36" t="s">
@@ -5600,7 +5606,7 @@
       <c r="D74" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E74" s="134">
+      <c r="E74" s="145">
         <v>143</v>
       </c>
       <c r="F74" s="58" t="s">
@@ -5609,7 +5615,7 @@
       <c r="G74" s="37" t="s">
         <v>431</v>
       </c>
-      <c r="H74" s="143" t="s">
+      <c r="H74" s="134" t="s">
         <v>399</v>
       </c>
     </row>
@@ -5623,14 +5629,14 @@
       <c r="D75" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E75" s="135"/>
+      <c r="E75" s="146"/>
       <c r="F75" s="56" t="s">
         <v>186</v>
       </c>
       <c r="G75" s="54" t="s">
         <v>427</v>
       </c>
-      <c r="H75" s="144"/>
+      <c r="H75" s="135"/>
     </row>
     <row r="76" spans="2:12" ht="15.75" customHeight="1">
       <c r="B76" s="38" t="s">
@@ -5642,14 +5648,14 @@
       <c r="D76" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E76" s="135"/>
+      <c r="E76" s="146"/>
       <c r="F76" s="56" t="s">
         <v>187</v>
       </c>
       <c r="G76" s="55" t="s">
         <v>428</v>
       </c>
-      <c r="H76" s="144"/>
+      <c r="H76" s="135"/>
     </row>
     <row r="77" spans="2:12" ht="15.75" customHeight="1">
       <c r="B77" s="38" t="s">
@@ -5661,14 +5667,14 @@
       <c r="D77" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E77" s="135"/>
+      <c r="E77" s="146"/>
       <c r="F77" s="56" t="s">
         <v>423</v>
       </c>
       <c r="G77" s="54" t="s">
         <v>429</v>
       </c>
-      <c r="H77" s="144"/>
+      <c r="H77" s="135"/>
     </row>
     <row r="78" spans="2:12" ht="15.75" customHeight="1">
       <c r="B78" s="38" t="s">
@@ -5680,14 +5686,14 @@
       <c r="D78" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E78" s="135"/>
+      <c r="E78" s="146"/>
       <c r="F78" s="56" t="s">
         <v>188</v>
       </c>
       <c r="G78" s="54" t="s">
         <v>429</v>
       </c>
-      <c r="H78" s="144"/>
+      <c r="H78" s="135"/>
     </row>
     <row r="79" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B79" s="51" t="s">
@@ -5699,14 +5705,14 @@
       <c r="D79" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E79" s="136"/>
+      <c r="E79" s="149"/>
       <c r="F79" s="57" t="s">
         <v>186</v>
       </c>
       <c r="G79" s="20" t="s">
         <v>430</v>
       </c>
-      <c r="H79" s="145"/>
+      <c r="H79" s="137"/>
     </row>
     <row r="80" spans="2:12" ht="38.65" thickTop="1">
       <c r="B80" s="40" t="s">
@@ -5718,7 +5724,7 @@
       <c r="D80" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E80" s="134">
+      <c r="E80" s="145">
         <v>112</v>
       </c>
       <c r="F80" s="11" t="s">
@@ -5727,7 +5733,7 @@
       <c r="G80" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="H80" s="143" t="s">
+      <c r="H80" s="134" t="s">
         <v>399</v>
       </c>
       <c r="I80" s="29"/>
@@ -5745,14 +5751,14 @@
       <c r="D81" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E81" s="135"/>
+      <c r="E81" s="146"/>
       <c r="F81" s="15" t="s">
         <v>32</v>
       </c>
       <c r="G81" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H81" s="144"/>
+      <c r="H81" s="135"/>
       <c r="I81" s="29"/>
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
@@ -5768,14 +5774,14 @@
       <c r="D82" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E82" s="135"/>
+      <c r="E82" s="146"/>
       <c r="F82" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G82" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H82" s="144"/>
+      <c r="H82" s="135"/>
       <c r="I82" s="29"/>
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
@@ -5791,14 +5797,14 @@
       <c r="D83" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E83" s="135"/>
+      <c r="E83" s="146"/>
       <c r="F83" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G83" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H83" s="144"/>
+      <c r="H83" s="135"/>
       <c r="I83" s="29"/>
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
@@ -5814,14 +5820,14 @@
       <c r="D84" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E84" s="135"/>
+      <c r="E84" s="146"/>
       <c r="F84" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G84" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H84" s="144"/>
+      <c r="H84" s="135"/>
       <c r="I84" s="29"/>
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
@@ -5837,14 +5843,14 @@
       <c r="D85" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E85" s="137"/>
+      <c r="E85" s="147"/>
       <c r="F85" s="26" t="s">
         <v>343</v>
       </c>
       <c r="G85" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="H85" s="145"/>
+      <c r="H85" s="137"/>
       <c r="I85" s="29"/>
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
@@ -5860,7 +5866,7 @@
       <c r="D86" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E86" s="138">
+      <c r="E86" s="150">
         <v>125</v>
       </c>
       <c r="F86" s="11" t="s">
@@ -5869,7 +5875,7 @@
       <c r="G86" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H86" s="143" t="s">
+      <c r="H86" s="134" t="s">
         <v>398</v>
       </c>
       <c r="I86" s="29"/>
@@ -5887,14 +5893,14 @@
       <c r="D87" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E87" s="135"/>
+      <c r="E87" s="146"/>
       <c r="F87" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G87" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H87" s="144"/>
+      <c r="H87" s="135"/>
       <c r="I87" s="29"/>
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
@@ -5910,14 +5916,14 @@
       <c r="D88" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E88" s="135"/>
+      <c r="E88" s="146"/>
       <c r="F88" s="15" t="s">
         <v>59</v>
       </c>
       <c r="G88" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H88" s="144"/>
+      <c r="H88" s="135"/>
       <c r="I88" s="29"/>
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
@@ -5933,14 +5939,14 @@
       <c r="D89" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E89" s="135"/>
+      <c r="E89" s="146"/>
       <c r="F89" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G89" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H89" s="144"/>
+      <c r="H89" s="135"/>
       <c r="I89" s="29"/>
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
@@ -5956,14 +5962,14 @@
       <c r="D90" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E90" s="135"/>
+      <c r="E90" s="146"/>
       <c r="F90" s="15" t="s">
         <v>61</v>
       </c>
       <c r="G90" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H90" s="144"/>
+      <c r="H90" s="135"/>
       <c r="I90" s="29"/>
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
@@ -5979,14 +5985,14 @@
       <c r="D91" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E91" s="136"/>
+      <c r="E91" s="149"/>
       <c r="F91" s="19" t="s">
         <v>62</v>
       </c>
       <c r="G91" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H91" s="145"/>
+      <c r="H91" s="137"/>
       <c r="I91" s="29"/>
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
@@ -6002,7 +6008,7 @@
       <c r="D92" s="62" t="s">
         <v>315</v>
       </c>
-      <c r="E92" s="134">
+      <c r="E92" s="145">
         <v>125</v>
       </c>
       <c r="F92" s="47" t="s">
@@ -6011,7 +6017,7 @@
       <c r="G92" s="48" t="s">
         <v>318</v>
       </c>
-      <c r="H92" s="146" t="s">
+      <c r="H92" s="141" t="s">
         <v>403</v>
       </c>
     </row>
@@ -6025,14 +6031,14 @@
       <c r="D93" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="E93" s="135"/>
+      <c r="E93" s="146"/>
       <c r="F93" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G93" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H93" s="147"/>
+      <c r="H93" s="139"/>
     </row>
     <row r="94" spans="2:12" ht="15.75" customHeight="1">
       <c r="B94" s="44" t="s">
@@ -6044,14 +6050,14 @@
       <c r="D94" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="E94" s="135"/>
+      <c r="E94" s="146"/>
       <c r="F94" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G94" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H94" s="147"/>
+      <c r="H94" s="139"/>
     </row>
     <row r="95" spans="2:12" ht="15.75" customHeight="1">
       <c r="B95" s="44" t="s">
@@ -6063,14 +6069,14 @@
       <c r="D95" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="E95" s="135"/>
+      <c r="E95" s="146"/>
       <c r="F95" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G95" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H95" s="147"/>
+      <c r="H95" s="139"/>
     </row>
     <row r="96" spans="2:12" ht="15.75" customHeight="1">
       <c r="B96" s="44" t="s">
@@ -6082,14 +6088,14 @@
       <c r="D96" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="E96" s="135"/>
+      <c r="E96" s="146"/>
       <c r="F96" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G96" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H96" s="147"/>
+      <c r="H96" s="139"/>
     </row>
     <row r="97" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B97" s="64" t="s">
@@ -6101,14 +6107,14 @@
       <c r="D97" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="E97" s="136"/>
+      <c r="E97" s="149"/>
       <c r="F97" s="53" t="s">
         <v>63</v>
       </c>
       <c r="G97" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="H97" s="148"/>
+      <c r="H97" s="140"/>
     </row>
     <row r="98" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B98" s="36" t="s">
@@ -6120,7 +6126,7 @@
       <c r="D98" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E98" s="134">
+      <c r="E98" s="145">
         <v>125</v>
       </c>
       <c r="F98" s="58" t="s">
@@ -6129,7 +6135,7 @@
       <c r="G98" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="H98" s="143" t="s">
+      <c r="H98" s="134" t="s">
         <v>399</v>
       </c>
     </row>
@@ -6143,14 +6149,14 @@
       <c r="D99" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E99" s="135"/>
+      <c r="E99" s="146"/>
       <c r="F99" s="56" t="s">
         <v>234</v>
       </c>
       <c r="G99" s="54" t="s">
         <v>228</v>
       </c>
-      <c r="H99" s="144"/>
+      <c r="H99" s="135"/>
     </row>
     <row r="100" spans="2:8" ht="15.75" customHeight="1">
       <c r="B100" s="38" t="s">
@@ -6162,14 +6168,14 @@
       <c r="D100" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E100" s="135"/>
+      <c r="E100" s="146"/>
       <c r="F100" s="56" t="s">
         <v>235</v>
       </c>
       <c r="G100" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H100" s="144"/>
+      <c r="H100" s="135"/>
     </row>
     <row r="101" spans="2:8" ht="15.75" customHeight="1">
       <c r="B101" s="38" t="s">
@@ -6181,14 +6187,14 @@
       <c r="D101" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E101" s="135"/>
+      <c r="E101" s="146"/>
       <c r="F101" s="56" t="s">
         <v>236</v>
       </c>
       <c r="G101" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H101" s="144"/>
+      <c r="H101" s="135"/>
     </row>
     <row r="102" spans="2:8" ht="15.75" customHeight="1">
       <c r="B102" s="38" t="s">
@@ -6200,14 +6206,14 @@
       <c r="D102" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E102" s="135"/>
+      <c r="E102" s="146"/>
       <c r="F102" s="56" t="s">
         <v>237</v>
       </c>
       <c r="G102" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H102" s="144"/>
+      <c r="H102" s="135"/>
     </row>
     <row r="103" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B103" s="51" t="s">
@@ -6219,14 +6225,14 @@
       <c r="D103" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E103" s="136"/>
+      <c r="E103" s="149"/>
       <c r="F103" s="57" t="s">
         <v>238</v>
       </c>
       <c r="G103" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="H103" s="145"/>
+      <c r="H103" s="137"/>
     </row>
     <row r="104" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B104" s="61" t="s">
@@ -6238,7 +6244,7 @@
       <c r="D104" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E104" s="134">
+      <c r="E104" s="145">
         <v>125</v>
       </c>
       <c r="F104" s="31" t="s">
@@ -6247,7 +6253,7 @@
       <c r="G104" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="H104" s="143" t="s">
+      <c r="H104" s="134" t="s">
         <v>399</v>
       </c>
     </row>
@@ -6261,14 +6267,14 @@
       <c r="D105" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E105" s="135"/>
+      <c r="E105" s="146"/>
       <c r="F105" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G105" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H105" s="144"/>
+      <c r="H105" s="135"/>
     </row>
     <row r="106" spans="2:8" ht="15.75" customHeight="1">
       <c r="B106" s="44" t="s">
@@ -6280,14 +6286,14 @@
       <c r="D106" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E106" s="135"/>
+      <c r="E106" s="146"/>
       <c r="F106" s="15" t="s">
         <v>59</v>
       </c>
       <c r="G106" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H106" s="144"/>
+      <c r="H106" s="135"/>
     </row>
     <row r="107" spans="2:8" ht="15.75" customHeight="1">
       <c r="B107" s="44" t="s">
@@ -6299,14 +6305,14 @@
       <c r="D107" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E107" s="135"/>
+      <c r="E107" s="146"/>
       <c r="F107" s="15" t="s">
         <v>72</v>
       </c>
       <c r="G107" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H107" s="144"/>
+      <c r="H107" s="135"/>
     </row>
     <row r="108" spans="2:8" ht="15.75" customHeight="1">
       <c r="B108" s="44" t="s">
@@ -6318,14 +6324,14 @@
       <c r="D108" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E108" s="135"/>
+      <c r="E108" s="146"/>
       <c r="F108" s="15" t="s">
         <v>61</v>
       </c>
       <c r="G108" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H108" s="144"/>
+      <c r="H108" s="135"/>
     </row>
     <row r="109" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B109" s="66" t="s">
@@ -6337,14 +6343,14 @@
       <c r="D109" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E109" s="137"/>
+      <c r="E109" s="147"/>
       <c r="F109" s="34" t="s">
         <v>62</v>
       </c>
       <c r="G109" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="H109" s="145"/>
+      <c r="H109" s="137"/>
     </row>
     <row r="110" spans="2:8" ht="25.5" customHeight="1" thickTop="1">
       <c r="B110" s="36" t="s">
@@ -6356,7 +6362,7 @@
       <c r="D110" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E110" s="134">
+      <c r="E110" s="145">
         <v>125</v>
       </c>
       <c r="F110" s="72" t="s">
@@ -6365,7 +6371,7 @@
       <c r="G110" s="37" t="s">
         <v>353</v>
       </c>
-      <c r="H110" s="143" t="s">
+      <c r="H110" s="134" t="s">
         <v>399</v>
       </c>
     </row>
@@ -6379,14 +6385,14 @@
       <c r="D111" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E111" s="135"/>
+      <c r="E111" s="146"/>
       <c r="F111" s="56" t="s">
         <v>355</v>
       </c>
       <c r="G111" s="54" t="s">
         <v>352</v>
       </c>
-      <c r="H111" s="144"/>
+      <c r="H111" s="135"/>
     </row>
     <row r="112" spans="2:8" ht="15.75" customHeight="1">
       <c r="B112" s="38" t="s">
@@ -6398,14 +6404,14 @@
       <c r="D112" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E112" s="135"/>
+      <c r="E112" s="146"/>
       <c r="F112" s="56" t="s">
         <v>351</v>
       </c>
       <c r="G112" s="54" t="s">
         <v>356</v>
       </c>
-      <c r="H112" s="144"/>
+      <c r="H112" s="135"/>
     </row>
     <row r="113" spans="2:12" ht="15.75" customHeight="1">
       <c r="B113" s="38" t="s">
@@ -6417,14 +6423,14 @@
       <c r="D113" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E113" s="135"/>
+      <c r="E113" s="146"/>
       <c r="F113" s="56" t="s">
         <v>358</v>
       </c>
       <c r="G113" s="54" t="s">
         <v>352</v>
       </c>
-      <c r="H113" s="144"/>
+      <c r="H113" s="135"/>
     </row>
     <row r="114" spans="2:12" ht="15.75" customHeight="1">
       <c r="B114" s="38" t="s">
@@ -6436,14 +6442,14 @@
       <c r="D114" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E114" s="135"/>
+      <c r="E114" s="146"/>
       <c r="F114" s="56" t="s">
         <v>424</v>
       </c>
       <c r="G114" s="54" t="s">
         <v>352</v>
       </c>
-      <c r="H114" s="144"/>
+      <c r="H114" s="135"/>
     </row>
     <row r="115" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B115" s="51" t="s">
@@ -6455,14 +6461,14 @@
       <c r="D115" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E115" s="136"/>
+      <c r="E115" s="149"/>
       <c r="F115" s="57" t="s">
         <v>362</v>
       </c>
       <c r="G115" s="54" t="s">
         <v>361</v>
       </c>
-      <c r="H115" s="145"/>
+      <c r="H115" s="137"/>
     </row>
     <row r="116" spans="2:12" ht="25.9" thickTop="1">
       <c r="B116" s="68" t="s">
@@ -6474,7 +6480,7 @@
       <c r="D116" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E116" s="134">
+      <c r="E116" s="145">
         <v>143</v>
       </c>
       <c r="F116" s="31" t="s">
@@ -6483,7 +6489,7 @@
       <c r="G116" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="H116" s="143" t="s">
+      <c r="H116" s="134" t="s">
         <v>410</v>
       </c>
       <c r="I116" s="29"/>
@@ -6501,14 +6507,14 @@
       <c r="D117" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E117" s="135"/>
+      <c r="E117" s="146"/>
       <c r="F117" s="15" t="s">
         <v>246</v>
       </c>
       <c r="G117" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H117" s="144"/>
+      <c r="H117" s="135"/>
       <c r="I117" s="29"/>
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
@@ -6524,14 +6530,14 @@
       <c r="D118" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E118" s="135"/>
+      <c r="E118" s="146"/>
       <c r="F118" s="15" t="s">
         <v>247</v>
       </c>
       <c r="G118" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="H118" s="144"/>
+      <c r="H118" s="135"/>
       <c r="I118" s="29"/>
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
@@ -6547,14 +6553,14 @@
       <c r="D119" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E119" s="135"/>
+      <c r="E119" s="146"/>
       <c r="F119" s="15" t="s">
         <v>248</v>
       </c>
       <c r="G119" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H119" s="144"/>
+      <c r="H119" s="135"/>
       <c r="I119" s="29"/>
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
@@ -6570,14 +6576,14 @@
       <c r="D120" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E120" s="135"/>
+      <c r="E120" s="146"/>
       <c r="F120" s="15" t="s">
         <v>249</v>
       </c>
       <c r="G120" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H120" s="144"/>
+      <c r="H120" s="135"/>
       <c r="I120" s="29"/>
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
@@ -6593,14 +6599,14 @@
       <c r="D121" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E121" s="137"/>
+      <c r="E121" s="147"/>
       <c r="F121" s="26" t="s">
         <v>250</v>
       </c>
       <c r="G121" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="H121" s="145"/>
+      <c r="H121" s="137"/>
       <c r="I121" s="29"/>
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
@@ -6616,7 +6622,7 @@
       <c r="D122" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E122" s="134">
+      <c r="E122" s="145">
         <v>125</v>
       </c>
       <c r="F122" s="72" t="s">
@@ -6625,7 +6631,7 @@
       <c r="G122" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="H122" s="143" t="s">
+      <c r="H122" s="134" t="s">
         <v>399</v>
       </c>
       <c r="I122" s="29"/>
@@ -6643,14 +6649,14 @@
       <c r="D123" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E123" s="135"/>
+      <c r="E123" s="146"/>
       <c r="F123" s="56" t="s">
         <v>252</v>
       </c>
       <c r="G123" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H123" s="144"/>
+      <c r="H123" s="135"/>
       <c r="I123" s="29"/>
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
@@ -6666,14 +6672,14 @@
       <c r="D124" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E124" s="135"/>
+      <c r="E124" s="146"/>
       <c r="F124" s="56" t="s">
         <v>253</v>
       </c>
       <c r="G124" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H124" s="144"/>
+      <c r="H124" s="135"/>
       <c r="I124" s="29"/>
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
@@ -6689,14 +6695,14 @@
       <c r="D125" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E125" s="135"/>
+      <c r="E125" s="146"/>
       <c r="F125" s="56" t="s">
         <v>254</v>
       </c>
       <c r="G125" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H125" s="144"/>
+      <c r="H125" s="135"/>
       <c r="I125" s="29"/>
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
@@ -6712,14 +6718,14 @@
       <c r="D126" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E126" s="135"/>
+      <c r="E126" s="146"/>
       <c r="F126" s="56" t="s">
         <v>255</v>
       </c>
       <c r="G126" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H126" s="144"/>
+      <c r="H126" s="135"/>
       <c r="I126" s="29"/>
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
@@ -6735,14 +6741,14 @@
       <c r="D127" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E127" s="137"/>
+      <c r="E127" s="147"/>
       <c r="F127" s="73" t="s">
         <v>256</v>
       </c>
       <c r="G127" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="H127" s="145"/>
+      <c r="H127" s="137"/>
       <c r="I127" s="29"/>
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
@@ -6758,7 +6764,7 @@
       <c r="D128" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E128" s="134">
+      <c r="E128" s="145">
         <v>143</v>
       </c>
       <c r="F128" s="72" t="s">
@@ -6767,7 +6773,7 @@
       <c r="G128" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="H128" s="143" t="s">
+      <c r="H128" s="134" t="s">
         <v>399</v>
       </c>
     </row>
@@ -6781,14 +6787,14 @@
       <c r="D129" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E129" s="135"/>
+      <c r="E129" s="146"/>
       <c r="F129" s="56" t="s">
         <v>261</v>
       </c>
       <c r="G129" s="77" t="s">
         <v>115</v>
       </c>
-      <c r="H129" s="144"/>
+      <c r="H129" s="135"/>
     </row>
     <row r="130" spans="2:12" ht="15.75" customHeight="1">
       <c r="B130" s="70" t="s">
@@ -6800,14 +6806,14 @@
       <c r="D130" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E130" s="135"/>
+      <c r="E130" s="146"/>
       <c r="F130" s="56" t="s">
         <v>262</v>
       </c>
       <c r="G130" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="H130" s="144"/>
+      <c r="H130" s="135"/>
     </row>
     <row r="131" spans="2:12" ht="15.75" customHeight="1">
       <c r="B131" s="74" t="s">
@@ -6819,14 +6825,14 @@
       <c r="D131" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E131" s="135"/>
+      <c r="E131" s="146"/>
       <c r="F131" s="56" t="s">
         <v>263</v>
       </c>
       <c r="G131" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H131" s="144"/>
+      <c r="H131" s="135"/>
     </row>
     <row r="132" spans="2:12" ht="15.75" customHeight="1">
       <c r="B132" s="74" t="s">
@@ -6838,14 +6844,14 @@
       <c r="D132" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E132" s="135"/>
+      <c r="E132" s="146"/>
       <c r="F132" s="56" t="s">
         <v>264</v>
       </c>
       <c r="G132" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H132" s="144"/>
+      <c r="H132" s="135"/>
     </row>
     <row r="133" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B133" s="71" t="s">
@@ -6857,14 +6863,14 @@
       <c r="D133" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E133" s="137"/>
+      <c r="E133" s="147"/>
       <c r="F133" s="73" t="s">
         <v>265</v>
       </c>
       <c r="G133" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="H133" s="145"/>
+      <c r="H133" s="137"/>
     </row>
     <row r="134" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B134" s="75" t="s">
@@ -6876,7 +6882,7 @@
       <c r="D134" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E134" s="139">
+      <c r="E134" s="148">
         <v>143</v>
       </c>
       <c r="F134" s="28" t="s">
@@ -6885,7 +6891,7 @@
       <c r="G134" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H134" s="143" t="s">
+      <c r="H134" s="134" t="s">
         <v>398</v>
       </c>
       <c r="I134" s="29"/>
@@ -6903,14 +6909,14 @@
       <c r="D135" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E135" s="135"/>
+      <c r="E135" s="146"/>
       <c r="F135" s="15" t="s">
         <v>267</v>
       </c>
       <c r="G135" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H135" s="144"/>
+      <c r="H135" s="135"/>
       <c r="I135" s="29"/>
       <c r="J135" s="29"/>
       <c r="K135" s="29"/>
@@ -6926,14 +6932,14 @@
       <c r="D136" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E136" s="135"/>
+      <c r="E136" s="146"/>
       <c r="F136" s="15" t="s">
         <v>268</v>
       </c>
       <c r="G136" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H136" s="144"/>
+      <c r="H136" s="135"/>
       <c r="I136" s="29"/>
       <c r="J136" s="29"/>
       <c r="K136" s="29"/>
@@ -6949,14 +6955,14 @@
       <c r="D137" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E137" s="135"/>
+      <c r="E137" s="146"/>
       <c r="F137" s="15" t="s">
         <v>269</v>
       </c>
       <c r="G137" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H137" s="144"/>
+      <c r="H137" s="135"/>
       <c r="I137" s="29"/>
       <c r="J137" s="29"/>
       <c r="K137" s="29"/>
@@ -6972,14 +6978,14 @@
       <c r="D138" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E138" s="135"/>
+      <c r="E138" s="146"/>
       <c r="F138" s="15" t="s">
         <v>270</v>
       </c>
       <c r="G138" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H138" s="144"/>
+      <c r="H138" s="135"/>
       <c r="I138" s="29"/>
       <c r="J138" s="29"/>
       <c r="K138" s="29"/>
@@ -6995,14 +7001,14 @@
       <c r="D139" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E139" s="136"/>
+      <c r="E139" s="149"/>
       <c r="F139" s="19" t="s">
         <v>271</v>
       </c>
       <c r="G139" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="H139" s="145"/>
+      <c r="H139" s="137"/>
       <c r="I139" s="29"/>
       <c r="J139" s="29"/>
       <c r="K139" s="29"/>
@@ -7018,7 +7024,7 @@
       <c r="D140" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E140" s="134">
+      <c r="E140" s="145">
         <v>143</v>
       </c>
       <c r="F140" s="31" t="s">
@@ -7027,7 +7033,7 @@
       <c r="G140" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="H140" s="143" t="s">
+      <c r="H140" s="134" t="s">
         <v>399</v>
       </c>
     </row>
@@ -7041,14 +7047,14 @@
       <c r="D141" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E141" s="135"/>
+      <c r="E141" s="146"/>
       <c r="F141" s="15" t="s">
         <v>267</v>
       </c>
       <c r="G141" s="77" t="s">
         <v>90</v>
       </c>
-      <c r="H141" s="144"/>
+      <c r="H141" s="135"/>
     </row>
     <row r="142" spans="2:12" ht="15.75" customHeight="1">
       <c r="B142" s="44" t="s">
@@ -7060,14 +7066,14 @@
       <c r="D142" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E142" s="135"/>
+      <c r="E142" s="146"/>
       <c r="F142" s="15" t="s">
         <v>268</v>
       </c>
       <c r="G142" s="78" t="s">
         <v>91</v>
       </c>
-      <c r="H142" s="144"/>
+      <c r="H142" s="135"/>
     </row>
     <row r="143" spans="2:12" ht="15.75" customHeight="1">
       <c r="B143" s="44" t="s">
@@ -7079,14 +7085,14 @@
       <c r="D143" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E143" s="135"/>
+      <c r="E143" s="146"/>
       <c r="F143" s="15" t="s">
         <v>269</v>
       </c>
       <c r="G143" s="77" t="s">
         <v>90</v>
       </c>
-      <c r="H143" s="144"/>
+      <c r="H143" s="135"/>
     </row>
     <row r="144" spans="2:12" ht="15.75" customHeight="1">
       <c r="B144" s="44" t="s">
@@ -7098,14 +7104,14 @@
       <c r="D144" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E144" s="135"/>
+      <c r="E144" s="146"/>
       <c r="F144" s="15" t="s">
         <v>270</v>
       </c>
       <c r="G144" s="77" t="s">
         <v>90</v>
       </c>
-      <c r="H144" s="144"/>
+      <c r="H144" s="135"/>
     </row>
     <row r="145" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B145" s="64" t="s">
@@ -7117,14 +7123,14 @@
       <c r="D145" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E145" s="136"/>
+      <c r="E145" s="149"/>
       <c r="F145" s="19" t="s">
         <v>271</v>
       </c>
       <c r="G145" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="H145" s="145"/>
+      <c r="H145" s="137"/>
     </row>
     <row r="146" spans="1:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B146" s="112" t="s">
@@ -7136,7 +7142,7 @@
       <c r="D146" s="79" t="s">
         <v>316</v>
       </c>
-      <c r="E146" s="134">
+      <c r="E146" s="145">
         <v>143</v>
       </c>
       <c r="F146" s="47" t="s">
@@ -7145,7 +7151,7 @@
       <c r="G146" s="48" t="s">
         <v>317</v>
       </c>
-      <c r="H146" s="146" t="s">
+      <c r="H146" s="141" t="s">
         <v>403</v>
       </c>
     </row>
@@ -7159,14 +7165,14 @@
       <c r="D147" s="80" t="s">
         <v>94</v>
       </c>
-      <c r="E147" s="135"/>
+      <c r="E147" s="146"/>
       <c r="F147" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G147" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H147" s="147"/>
+      <c r="H147" s="139"/>
     </row>
     <row r="148" spans="1:12" ht="15.75" customHeight="1">
       <c r="B148" s="44" t="s">
@@ -7178,14 +7184,14 @@
       <c r="D148" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="E148" s="135"/>
+      <c r="E148" s="146"/>
       <c r="F148" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G148" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H148" s="147"/>
+      <c r="H148" s="139"/>
     </row>
     <row r="149" spans="1:12" ht="15.75" customHeight="1">
       <c r="B149" s="44" t="s">
@@ -7197,14 +7203,14 @@
       <c r="D149" s="80" t="s">
         <v>94</v>
       </c>
-      <c r="E149" s="135"/>
+      <c r="E149" s="146"/>
       <c r="F149" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G149" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H149" s="147"/>
+      <c r="H149" s="139"/>
     </row>
     <row r="150" spans="1:12" ht="15.75" customHeight="1">
       <c r="B150" s="44" t="s">
@@ -7216,14 +7222,14 @@
       <c r="D150" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="E150" s="135"/>
+      <c r="E150" s="146"/>
       <c r="F150" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G150" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H150" s="147"/>
+      <c r="H150" s="139"/>
     </row>
     <row r="151" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B151" s="64" t="s">
@@ -7235,14 +7241,14 @@
       <c r="D151" s="81" t="s">
         <v>94</v>
       </c>
-      <c r="E151" s="136"/>
+      <c r="E151" s="149"/>
       <c r="F151" s="53" t="s">
         <v>63</v>
       </c>
       <c r="G151" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="H151" s="148"/>
+      <c r="H151" s="140"/>
     </row>
     <row r="152" spans="1:12" ht="13.5" thickTop="1">
       <c r="A152" s="111"/>
@@ -7255,7 +7261,7 @@
       <c r="D152" s="109" t="s">
         <v>374</v>
       </c>
-      <c r="E152" s="134">
+      <c r="E152" s="145">
         <v>143</v>
       </c>
       <c r="F152" s="47" t="s">
@@ -7264,7 +7270,7 @@
       <c r="G152" s="114" t="s">
         <v>370</v>
       </c>
-      <c r="H152" s="146" t="s">
+      <c r="H152" s="141" t="s">
         <v>403</v>
       </c>
     </row>
@@ -7278,12 +7284,12 @@
       <c r="D153" s="109" t="s">
         <v>367</v>
       </c>
-      <c r="E153" s="135"/>
+      <c r="E153" s="146"/>
       <c r="F153" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G153" s="12"/>
-      <c r="H153" s="147"/>
+      <c r="H153" s="139"/>
     </row>
     <row r="154" spans="1:12" ht="15.75" customHeight="1">
       <c r="B154" s="113" t="s">
@@ -7295,14 +7301,14 @@
       <c r="D154" s="109" t="s">
         <v>369</v>
       </c>
-      <c r="E154" s="135"/>
+      <c r="E154" s="146"/>
       <c r="F154" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G154" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H154" s="147"/>
+      <c r="H154" s="139"/>
     </row>
     <row r="155" spans="1:12" ht="15.75" customHeight="1">
       <c r="B155" s="113" t="s">
@@ -7314,12 +7320,12 @@
       <c r="D155" s="109" t="s">
         <v>367</v>
       </c>
-      <c r="E155" s="135"/>
+      <c r="E155" s="146"/>
       <c r="F155" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G155" s="12"/>
-      <c r="H155" s="147"/>
+      <c r="H155" s="139"/>
     </row>
     <row r="156" spans="1:12" ht="15.75" customHeight="1">
       <c r="B156" s="113" t="s">
@@ -7331,12 +7337,12 @@
       <c r="D156" s="109" t="s">
         <v>369</v>
       </c>
-      <c r="E156" s="135"/>
+      <c r="E156" s="146"/>
       <c r="F156" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G156" s="12"/>
-      <c r="H156" s="147"/>
+      <c r="H156" s="139"/>
     </row>
     <row r="157" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B157" s="116" t="s">
@@ -7348,14 +7354,14 @@
       <c r="D157" s="109" t="s">
         <v>367</v>
       </c>
-      <c r="E157" s="136"/>
+      <c r="E157" s="149"/>
       <c r="F157" s="53" t="s">
         <v>63</v>
       </c>
       <c r="G157" s="115" t="s">
         <v>45</v>
       </c>
-      <c r="H157" s="148"/>
+      <c r="H157" s="140"/>
     </row>
     <row r="158" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B158" s="82" t="s">
@@ -7367,7 +7373,7 @@
       <c r="D158" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E158" s="134">
+      <c r="E158" s="145">
         <v>167</v>
       </c>
       <c r="F158" s="31" t="s">
@@ -7376,7 +7382,7 @@
       <c r="G158" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H158" s="143" t="s">
+      <c r="H158" s="134" t="s">
         <v>399</v>
       </c>
       <c r="I158" s="29"/>
@@ -7394,14 +7400,14 @@
       <c r="D159" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E159" s="135"/>
+      <c r="E159" s="146"/>
       <c r="F159" s="15" t="s">
         <v>267</v>
       </c>
       <c r="G159" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H159" s="144"/>
+      <c r="H159" s="135"/>
       <c r="I159" s="29"/>
       <c r="J159" s="29"/>
       <c r="K159" s="29"/>
@@ -7417,14 +7423,14 @@
       <c r="D160" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E160" s="135"/>
+      <c r="E160" s="146"/>
       <c r="F160" s="15" t="s">
         <v>272</v>
       </c>
       <c r="G160" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H160" s="144"/>
+      <c r="H160" s="135"/>
       <c r="I160" s="29"/>
       <c r="J160" s="29"/>
       <c r="K160" s="29"/>
@@ -7440,14 +7446,14 @@
       <c r="D161" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E161" s="135"/>
+      <c r="E161" s="146"/>
       <c r="F161" s="15" t="s">
         <v>273</v>
       </c>
       <c r="G161" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H161" s="144"/>
+      <c r="H161" s="135"/>
       <c r="I161" s="29"/>
       <c r="J161" s="29"/>
       <c r="K161" s="29"/>
@@ -7463,14 +7469,14 @@
       <c r="D162" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E162" s="135"/>
+      <c r="E162" s="146"/>
       <c r="F162" s="15" t="s">
         <v>274</v>
       </c>
       <c r="G162" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H162" s="144"/>
+      <c r="H162" s="135"/>
       <c r="I162" s="29"/>
       <c r="J162" s="29"/>
       <c r="K162" s="29"/>
@@ -7486,14 +7492,14 @@
       <c r="D163" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E163" s="136"/>
+      <c r="E163" s="149"/>
       <c r="F163" s="19" t="s">
         <v>275</v>
       </c>
       <c r="G163" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="H163" s="145"/>
+      <c r="H163" s="137"/>
       <c r="I163" s="29"/>
       <c r="J163" s="29"/>
       <c r="K163" s="29"/>
@@ -7509,7 +7515,7 @@
       <c r="D164" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E164" s="134">
+      <c r="E164" s="145">
         <v>125</v>
       </c>
       <c r="F164" s="58" t="s">
@@ -7518,7 +7524,7 @@
       <c r="G164" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="H164" s="143" t="s">
+      <c r="H164" s="134" t="s">
         <v>399</v>
       </c>
     </row>
@@ -7532,14 +7538,14 @@
       <c r="D165" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E165" s="135"/>
+      <c r="E165" s="146"/>
       <c r="F165" s="56" t="s">
         <v>190</v>
       </c>
       <c r="G165" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H165" s="144"/>
+      <c r="H165" s="135"/>
     </row>
     <row r="166" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B166" s="38" t="s">
@@ -7551,14 +7557,14 @@
       <c r="D166" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E166" s="135"/>
+      <c r="E166" s="146"/>
       <c r="F166" s="56" t="s">
         <v>191</v>
       </c>
       <c r="G166" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H166" s="144"/>
+      <c r="H166" s="135"/>
     </row>
     <row r="167" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B167" s="38" t="s">
@@ -7570,14 +7576,14 @@
       <c r="D167" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E167" s="135"/>
+      <c r="E167" s="146"/>
       <c r="F167" s="56" t="s">
         <v>192</v>
       </c>
       <c r="G167" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H167" s="144"/>
+      <c r="H167" s="135"/>
     </row>
     <row r="168" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B168" s="87" t="s">
@@ -7589,14 +7595,14 @@
       <c r="D168" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E168" s="135"/>
+      <c r="E168" s="146"/>
       <c r="F168" s="56" t="s">
         <v>193</v>
       </c>
       <c r="G168" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H168" s="144"/>
+      <c r="H168" s="135"/>
     </row>
     <row r="169" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B169" s="51" t="s">
@@ -7608,14 +7614,14 @@
       <c r="D169" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E169" s="136"/>
+      <c r="E169" s="149"/>
       <c r="F169" s="57" t="s">
         <v>194</v>
       </c>
       <c r="G169" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="H169" s="145"/>
+      <c r="H169" s="137"/>
     </row>
     <row r="170" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B170" s="40" t="s">
@@ -7627,7 +7633,7 @@
       <c r="D170" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E170" s="138">
+      <c r="E170" s="150">
         <v>200</v>
       </c>
       <c r="F170" s="50" t="s">
@@ -7636,7 +7642,7 @@
       <c r="G170" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H170" s="143" t="s">
+      <c r="H170" s="134" t="s">
         <v>404</v>
       </c>
       <c r="I170" s="29"/>
@@ -7654,14 +7660,14 @@
       <c r="D171" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E171" s="135"/>
+      <c r="E171" s="146"/>
       <c r="F171" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G171" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="H171" s="144"/>
+      <c r="H171" s="135"/>
       <c r="I171" s="29"/>
       <c r="J171" s="29"/>
       <c r="K171" s="29"/>
@@ -7677,14 +7683,14 @@
       <c r="D172" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E172" s="135"/>
+      <c r="E172" s="146"/>
       <c r="F172" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G172" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="H172" s="144"/>
+      <c r="H172" s="135"/>
       <c r="I172" s="29"/>
       <c r="J172" s="29"/>
       <c r="K172" s="29"/>
@@ -7700,14 +7706,14 @@
       <c r="D173" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E173" s="135"/>
+      <c r="E173" s="146"/>
       <c r="F173" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G173" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="H173" s="144"/>
+      <c r="H173" s="135"/>
       <c r="I173" s="29"/>
       <c r="J173" s="29"/>
       <c r="K173" s="29"/>
@@ -7723,14 +7729,14 @@
       <c r="D174" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E174" s="135"/>
+      <c r="E174" s="146"/>
       <c r="F174" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G174" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="H174" s="144"/>
+      <c r="H174" s="135"/>
       <c r="I174" s="29"/>
       <c r="J174" s="29"/>
       <c r="K174" s="29"/>
@@ -7746,14 +7752,14 @@
       <c r="D175" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E175" s="137"/>
+      <c r="E175" s="147"/>
       <c r="F175" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G175" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="H175" s="145"/>
+      <c r="H175" s="137"/>
       <c r="I175" s="29"/>
       <c r="J175" s="29"/>
       <c r="K175" s="29"/>
@@ -7769,7 +7775,7 @@
       <c r="D176" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E176" s="134">
+      <c r="E176" s="145">
         <v>125</v>
       </c>
       <c r="F176" s="58" t="s">
@@ -7778,7 +7784,7 @@
       <c r="G176" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="H176" s="143" t="s">
+      <c r="H176" s="134" t="s">
         <v>399</v>
       </c>
       <c r="I176" s="29"/>
@@ -7796,14 +7802,14 @@
       <c r="D177" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E177" s="135"/>
+      <c r="E177" s="146"/>
       <c r="F177" s="56" t="s">
         <v>277</v>
       </c>
       <c r="G177" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="H177" s="144"/>
+      <c r="H177" s="135"/>
       <c r="I177" s="29"/>
       <c r="J177" s="29"/>
       <c r="K177" s="29"/>
@@ -7819,14 +7825,14 @@
       <c r="D178" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E178" s="135"/>
+      <c r="E178" s="146"/>
       <c r="F178" s="56" t="s">
         <v>278</v>
       </c>
       <c r="G178" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="H178" s="144"/>
+      <c r="H178" s="135"/>
       <c r="I178" s="29"/>
       <c r="J178" s="29"/>
       <c r="K178" s="29"/>
@@ -7842,14 +7848,14 @@
       <c r="D179" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E179" s="135"/>
+      <c r="E179" s="146"/>
       <c r="F179" s="56" t="s">
         <v>279</v>
       </c>
       <c r="G179" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="H179" s="144"/>
+      <c r="H179" s="135"/>
       <c r="I179" s="29"/>
       <c r="J179" s="29"/>
       <c r="K179" s="29"/>
@@ -7865,14 +7871,14 @@
       <c r="D180" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E180" s="135"/>
+      <c r="E180" s="146"/>
       <c r="F180" s="56" t="s">
         <v>280</v>
       </c>
       <c r="G180" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="H180" s="144"/>
+      <c r="H180" s="135"/>
       <c r="I180" s="29"/>
       <c r="J180" s="29"/>
       <c r="K180" s="29"/>
@@ -7888,14 +7894,14 @@
       <c r="D181" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E181" s="136"/>
+      <c r="E181" s="149"/>
       <c r="F181" s="88" t="s">
         <v>281</v>
       </c>
       <c r="G181" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="H181" s="145"/>
+      <c r="H181" s="137"/>
       <c r="I181" s="29"/>
       <c r="J181" s="29"/>
       <c r="K181" s="29"/>
@@ -7911,7 +7917,7 @@
       <c r="D182" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E182" s="139">
+      <c r="E182" s="148">
         <v>167</v>
       </c>
       <c r="F182" s="28" t="s">
@@ -7920,7 +7926,7 @@
       <c r="G182" s="54" t="s">
         <v>319</v>
       </c>
-      <c r="H182" s="143" t="s">
+      <c r="H182" s="134" t="s">
         <v>398</v>
       </c>
       <c r="I182" s="29"/>
@@ -7938,14 +7944,14 @@
       <c r="D183" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E183" s="135"/>
+      <c r="E183" s="146"/>
       <c r="F183" s="15" t="s">
         <v>305</v>
       </c>
       <c r="G183" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H183" s="144"/>
+      <c r="H183" s="135"/>
       <c r="I183" s="29"/>
       <c r="J183" s="29"/>
       <c r="K183" s="29"/>
@@ -7961,14 +7967,14 @@
       <c r="D184" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E184" s="135"/>
+      <c r="E184" s="146"/>
       <c r="F184" s="15" t="s">
         <v>306</v>
       </c>
       <c r="G184" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H184" s="144"/>
+      <c r="H184" s="135"/>
     </row>
     <row r="185" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B185" s="42" t="s">
@@ -7980,14 +7986,14 @@
       <c r="D185" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E185" s="135"/>
+      <c r="E185" s="146"/>
       <c r="F185" s="15" t="s">
         <v>307</v>
       </c>
       <c r="G185" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H185" s="144"/>
+      <c r="H185" s="135"/>
     </row>
     <row r="186" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B186" s="44" t="s">
@@ -7999,14 +8005,14 @@
       <c r="D186" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E186" s="135"/>
+      <c r="E186" s="146"/>
       <c r="F186" s="15" t="s">
         <v>306</v>
       </c>
       <c r="G186" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H186" s="144"/>
+      <c r="H186" s="135"/>
       <c r="I186" s="29"/>
       <c r="J186" s="29"/>
       <c r="K186" s="29"/>
@@ -8022,14 +8028,14 @@
       <c r="D187" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E187" s="136"/>
+      <c r="E187" s="149"/>
       <c r="F187" s="19" t="s">
         <v>308</v>
       </c>
       <c r="G187" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="H187" s="149"/>
+      <c r="H187" s="136"/>
       <c r="I187" s="29"/>
       <c r="J187" s="29"/>
       <c r="K187" s="29"/>
@@ -8045,7 +8051,7 @@
       <c r="D188" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E188" s="134">
+      <c r="E188" s="145">
         <v>167</v>
       </c>
       <c r="F188" s="50" t="s">
@@ -8054,7 +8060,7 @@
       <c r="G188" s="54" t="s">
         <v>314</v>
       </c>
-      <c r="H188" s="143" t="s">
+      <c r="H188" s="134" t="s">
         <v>411</v>
       </c>
       <c r="I188" s="29"/>
@@ -8072,14 +8078,14 @@
       <c r="D189" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E189" s="135"/>
+      <c r="E189" s="146"/>
       <c r="F189" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G189" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H189" s="144"/>
+      <c r="H189" s="135"/>
       <c r="I189" s="29"/>
       <c r="J189" s="29"/>
       <c r="K189" s="29"/>
@@ -8095,14 +8101,14 @@
       <c r="D190" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E190" s="135"/>
+      <c r="E190" s="146"/>
       <c r="F190" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G190" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H190" s="144"/>
+      <c r="H190" s="135"/>
       <c r="I190" s="29"/>
       <c r="J190" s="29"/>
       <c r="K190" s="29"/>
@@ -8118,14 +8124,14 @@
       <c r="D191" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E191" s="135"/>
+      <c r="E191" s="146"/>
       <c r="F191" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G191" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H191" s="144"/>
+      <c r="H191" s="135"/>
       <c r="I191" s="29"/>
       <c r="J191" s="29"/>
       <c r="K191" s="29"/>
@@ -8141,14 +8147,14 @@
       <c r="D192" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E192" s="135"/>
+      <c r="E192" s="146"/>
       <c r="F192" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G192" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H192" s="144"/>
+      <c r="H192" s="135"/>
       <c r="I192" s="29"/>
       <c r="J192" s="29"/>
       <c r="K192" s="29"/>
@@ -8164,14 +8170,14 @@
       <c r="D193" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E193" s="137"/>
+      <c r="E193" s="147"/>
       <c r="F193" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G193" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="H193" s="149"/>
+      <c r="H193" s="136"/>
       <c r="I193" s="29"/>
       <c r="J193" s="29"/>
       <c r="K193" s="29"/>
@@ -8187,7 +8193,7 @@
       <c r="D194" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E194" s="134">
+      <c r="E194" s="145">
         <v>143</v>
       </c>
       <c r="F194" s="72" t="s">
@@ -8196,8 +8202,8 @@
       <c r="G194" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="H194" s="143" t="s">
-        <v>399</v>
+      <c r="H194" s="151" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="195" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
@@ -8210,14 +8216,14 @@
       <c r="D195" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E195" s="135"/>
+      <c r="E195" s="146"/>
       <c r="F195" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G195" s="54" t="s">
         <v>119</v>
       </c>
-      <c r="H195" s="144"/>
+      <c r="H195" s="135"/>
     </row>
     <row r="196" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B196" s="38" t="s">
@@ -8229,14 +8235,14 @@
       <c r="D196" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E196" s="135"/>
+      <c r="E196" s="146"/>
       <c r="F196" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G196" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H196" s="144"/>
+      <c r="H196" s="135"/>
     </row>
     <row r="197" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B197" s="38" t="s">
@@ -8248,14 +8254,14 @@
       <c r="D197" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E197" s="135"/>
+      <c r="E197" s="146"/>
       <c r="F197" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G197" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H197" s="144"/>
+      <c r="H197" s="135"/>
     </row>
     <row r="198" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B198" s="38" t="s">
@@ -8267,14 +8273,14 @@
       <c r="D198" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E198" s="135"/>
+      <c r="E198" s="146"/>
       <c r="F198" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G198" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H198" s="144"/>
+      <c r="H198" s="135"/>
     </row>
     <row r="199" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B199" s="39" t="s">
@@ -8286,14 +8292,14 @@
       <c r="D199" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E199" s="137"/>
+      <c r="E199" s="147"/>
       <c r="F199" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G199" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="H199" s="145"/>
+      <c r="H199" s="137"/>
     </row>
     <row r="200" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B200" s="68" t="s">
@@ -8305,14 +8311,14 @@
       <c r="D200" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E200" s="134">
+      <c r="E200" s="145">
         <v>233</v>
       </c>
       <c r="F200" s="72"/>
       <c r="G200" s="48" t="s">
         <v>327</v>
       </c>
-      <c r="H200" s="150" t="s">
+      <c r="H200" s="138" t="s">
         <v>401</v>
       </c>
     </row>
@@ -8326,10 +8332,10 @@
       <c r="D201" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E201" s="135"/>
+      <c r="E201" s="146"/>
       <c r="F201" s="50"/>
       <c r="G201" s="12"/>
-      <c r="H201" s="147"/>
+      <c r="H201" s="139"/>
     </row>
     <row r="202" spans="2:12" ht="15.75" customHeight="1">
       <c r="B202" s="70" t="s">
@@ -8341,12 +8347,12 @@
       <c r="D202" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E202" s="135"/>
+      <c r="E202" s="146"/>
       <c r="F202" s="50"/>
       <c r="G202" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="H202" s="147"/>
+      <c r="H202" s="139"/>
     </row>
     <row r="203" spans="2:12" ht="15.75" customHeight="1">
       <c r="B203" s="70" t="s">
@@ -8358,12 +8364,12 @@
       <c r="D203" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E203" s="135"/>
+      <c r="E203" s="146"/>
       <c r="F203" s="50"/>
       <c r="G203" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H203" s="147"/>
+      <c r="H203" s="139"/>
     </row>
     <row r="204" spans="2:12" ht="15.75" customHeight="1">
       <c r="B204" s="70" t="s">
@@ -8375,12 +8381,12 @@
       <c r="D204" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E204" s="135"/>
+      <c r="E204" s="146"/>
       <c r="F204" s="50"/>
       <c r="G204" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H204" s="147"/>
+      <c r="H204" s="139"/>
     </row>
     <row r="205" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B205" s="71" t="s">
@@ -8392,12 +8398,12 @@
       <c r="D205" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E205" s="137"/>
+      <c r="E205" s="147"/>
       <c r="F205" s="89"/>
       <c r="G205" s="90" t="s">
         <v>115</v>
       </c>
-      <c r="H205" s="148"/>
+      <c r="H205" s="140"/>
     </row>
     <row r="206" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B206" s="117" t="s">
@@ -8409,7 +8415,7 @@
       <c r="D206" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E206" s="134">
+      <c r="E206" s="145">
         <v>167</v>
       </c>
       <c r="F206" s="127" t="s">
@@ -8418,7 +8424,7 @@
       <c r="G206" s="114" t="s">
         <v>377</v>
       </c>
-      <c r="H206" s="143" t="s">
+      <c r="H206" s="134" t="s">
         <v>399</v>
       </c>
     </row>
@@ -8432,14 +8438,14 @@
       <c r="D207" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E207" s="135"/>
+      <c r="E207" s="146"/>
       <c r="F207" s="127" t="s">
         <v>305</v>
       </c>
       <c r="G207" s="119" t="s">
         <v>379</v>
       </c>
-      <c r="H207" s="144"/>
+      <c r="H207" s="135"/>
     </row>
     <row r="208" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B208" s="125" t="s">
@@ -8451,14 +8457,14 @@
       <c r="D208" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E208" s="135"/>
+      <c r="E208" s="146"/>
       <c r="F208" s="127" t="s">
         <v>306</v>
       </c>
       <c r="G208" s="120" t="s">
         <v>378</v>
       </c>
-      <c r="H208" s="144"/>
+      <c r="H208" s="135"/>
     </row>
     <row r="209" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B209" s="125" t="s">
@@ -8470,14 +8476,14 @@
       <c r="D209" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E209" s="135"/>
+      <c r="E209" s="146"/>
       <c r="F209" s="127" t="s">
         <v>307</v>
       </c>
       <c r="G209" s="119" t="s">
         <v>379</v>
       </c>
-      <c r="H209" s="144"/>
+      <c r="H209" s="135"/>
     </row>
     <row r="210" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B210" s="125" t="s">
@@ -8489,14 +8495,14 @@
       <c r="D210" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E210" s="135"/>
+      <c r="E210" s="146"/>
       <c r="F210" s="127" t="s">
         <v>306</v>
       </c>
       <c r="G210" s="122" t="s">
         <v>379</v>
       </c>
-      <c r="H210" s="144"/>
+      <c r="H210" s="135"/>
     </row>
     <row r="211" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B211" s="126" t="s">
@@ -8508,14 +8514,14 @@
       <c r="D211" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E211" s="137"/>
+      <c r="E211" s="147"/>
       <c r="F211" s="127" t="s">
         <v>308</v>
       </c>
       <c r="G211" s="121" t="s">
         <v>379</v>
       </c>
-      <c r="H211" s="145"/>
+      <c r="H211" s="137"/>
     </row>
     <row r="212" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B212" s="117" t="s">
@@ -8527,7 +8533,7 @@
       <c r="D212" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E212" s="140">
+      <c r="E212" s="142">
         <v>167</v>
       </c>
       <c r="F212" s="127" t="s">
@@ -8536,7 +8542,7 @@
       <c r="G212" s="114" t="s">
         <v>386</v>
       </c>
-      <c r="H212" s="143" t="s">
+      <c r="H212" s="134" t="s">
         <v>399</v>
       </c>
     </row>
@@ -8550,14 +8556,14 @@
       <c r="D213" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E213" s="141"/>
+      <c r="E213" s="143"/>
       <c r="F213" s="127" t="s">
         <v>395</v>
       </c>
       <c r="G213" s="118" t="s">
         <v>388</v>
       </c>
-      <c r="H213" s="144"/>
+      <c r="H213" s="135"/>
     </row>
     <row r="214" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B214" s="125" t="s">
@@ -8569,14 +8575,14 @@
       <c r="D214" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E214" s="141"/>
+      <c r="E214" s="143"/>
       <c r="F214" s="127" t="s">
         <v>306</v>
       </c>
       <c r="G214" s="118" t="s">
         <v>390</v>
       </c>
-      <c r="H214" s="144"/>
+      <c r="H214" s="135"/>
     </row>
     <row r="215" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B215" s="125" t="s">
@@ -8588,14 +8594,14 @@
       <c r="D215" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E215" s="141"/>
+      <c r="E215" s="143"/>
       <c r="F215" s="127" t="s">
         <v>307</v>
       </c>
       <c r="G215" s="118" t="s">
         <v>388</v>
       </c>
-      <c r="H215" s="144"/>
+      <c r="H215" s="135"/>
     </row>
     <row r="216" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B216" s="125" t="s">
@@ -8607,14 +8613,14 @@
       <c r="D216" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E216" s="141"/>
+      <c r="E216" s="143"/>
       <c r="F216" s="127" t="s">
         <v>306</v>
       </c>
       <c r="G216" s="118" t="s">
         <v>388</v>
       </c>
-      <c r="H216" s="144"/>
+      <c r="H216" s="135"/>
     </row>
     <row r="217" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B217" s="126" t="s">
@@ -8626,14 +8632,14 @@
       <c r="D217" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="E217" s="142"/>
+      <c r="E217" s="144"/>
       <c r="F217" s="127" t="s">
         <v>308</v>
       </c>
       <c r="G217" s="119" t="s">
         <v>391</v>
       </c>
-      <c r="H217" s="145"/>
+      <c r="H217" s="137"/>
     </row>
     <row r="218" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B218" s="91" t="s">
@@ -13798,30 +13804,38 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="72">
-    <mergeCell ref="H188:H193"/>
-    <mergeCell ref="H194:H199"/>
-    <mergeCell ref="H200:H205"/>
-    <mergeCell ref="H206:H211"/>
-    <mergeCell ref="H92:H97"/>
-    <mergeCell ref="H98:H103"/>
-    <mergeCell ref="H104:H109"/>
-    <mergeCell ref="H110:H115"/>
-    <mergeCell ref="H116:H121"/>
-    <mergeCell ref="H62:H67"/>
-    <mergeCell ref="H68:H73"/>
-    <mergeCell ref="H74:H79"/>
-    <mergeCell ref="H80:H85"/>
-    <mergeCell ref="H86:H91"/>
-    <mergeCell ref="H32:H37"/>
-    <mergeCell ref="H38:H43"/>
-    <mergeCell ref="H44:H49"/>
-    <mergeCell ref="H50:H55"/>
-    <mergeCell ref="H56:H61"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="H8:H13"/>
-    <mergeCell ref="H14:H19"/>
-    <mergeCell ref="H20:H25"/>
-    <mergeCell ref="H26:H31"/>
+    <mergeCell ref="E140:E145"/>
+    <mergeCell ref="E146:E151"/>
+    <mergeCell ref="E158:E163"/>
+    <mergeCell ref="E194:E199"/>
+    <mergeCell ref="E200:E205"/>
+    <mergeCell ref="E164:E169"/>
+    <mergeCell ref="E170:E175"/>
+    <mergeCell ref="E176:E181"/>
+    <mergeCell ref="E182:E187"/>
+    <mergeCell ref="E188:E193"/>
+    <mergeCell ref="E152:E157"/>
+    <mergeCell ref="E92:E97"/>
+    <mergeCell ref="E98:E103"/>
+    <mergeCell ref="E104:E109"/>
+    <mergeCell ref="E116:E121"/>
+    <mergeCell ref="E122:E127"/>
+    <mergeCell ref="E110:E115"/>
+    <mergeCell ref="E62:E67"/>
+    <mergeCell ref="E68:E73"/>
+    <mergeCell ref="E74:E79"/>
+    <mergeCell ref="E80:E85"/>
+    <mergeCell ref="E86:E91"/>
+    <mergeCell ref="E32:E37"/>
+    <mergeCell ref="E38:E43"/>
+    <mergeCell ref="E44:E49"/>
+    <mergeCell ref="E50:E55"/>
+    <mergeCell ref="E56:E61"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="E8:E13"/>
+    <mergeCell ref="E14:E19"/>
+    <mergeCell ref="E20:E25"/>
+    <mergeCell ref="E26:E31"/>
     <mergeCell ref="E212:E217"/>
     <mergeCell ref="E206:E211"/>
     <mergeCell ref="H122:H127"/>
@@ -13838,38 +13852,30 @@
     <mergeCell ref="E134:E139"/>
     <mergeCell ref="H212:H217"/>
     <mergeCell ref="H182:H187"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="E8:E13"/>
-    <mergeCell ref="E14:E19"/>
-    <mergeCell ref="E20:E25"/>
-    <mergeCell ref="E26:E31"/>
-    <mergeCell ref="E32:E37"/>
-    <mergeCell ref="E38:E43"/>
-    <mergeCell ref="E44:E49"/>
-    <mergeCell ref="E50:E55"/>
-    <mergeCell ref="E56:E61"/>
-    <mergeCell ref="E62:E67"/>
-    <mergeCell ref="E68:E73"/>
-    <mergeCell ref="E74:E79"/>
-    <mergeCell ref="E80:E85"/>
-    <mergeCell ref="E86:E91"/>
-    <mergeCell ref="E92:E97"/>
-    <mergeCell ref="E98:E103"/>
-    <mergeCell ref="E104:E109"/>
-    <mergeCell ref="E116:E121"/>
-    <mergeCell ref="E122:E127"/>
-    <mergeCell ref="E110:E115"/>
-    <mergeCell ref="E140:E145"/>
-    <mergeCell ref="E146:E151"/>
-    <mergeCell ref="E158:E163"/>
-    <mergeCell ref="E194:E199"/>
-    <mergeCell ref="E200:E205"/>
-    <mergeCell ref="E164:E169"/>
-    <mergeCell ref="E170:E175"/>
-    <mergeCell ref="E176:E181"/>
-    <mergeCell ref="E182:E187"/>
-    <mergeCell ref="E188:E193"/>
-    <mergeCell ref="E152:E157"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="H8:H13"/>
+    <mergeCell ref="H14:H19"/>
+    <mergeCell ref="H20:H25"/>
+    <mergeCell ref="H26:H31"/>
+    <mergeCell ref="H32:H37"/>
+    <mergeCell ref="H38:H43"/>
+    <mergeCell ref="H44:H49"/>
+    <mergeCell ref="H50:H55"/>
+    <mergeCell ref="H56:H61"/>
+    <mergeCell ref="H62:H67"/>
+    <mergeCell ref="H68:H73"/>
+    <mergeCell ref="H74:H79"/>
+    <mergeCell ref="H80:H85"/>
+    <mergeCell ref="H86:H91"/>
+    <mergeCell ref="H188:H193"/>
+    <mergeCell ref="H194:H199"/>
+    <mergeCell ref="H200:H205"/>
+    <mergeCell ref="H206:H211"/>
+    <mergeCell ref="H92:H97"/>
+    <mergeCell ref="H98:H103"/>
+    <mergeCell ref="H104:H109"/>
+    <mergeCell ref="H110:H115"/>
+    <mergeCell ref="H116:H121"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-source/护甲数据.xlsx
+++ b/data-source/护甲数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C50D7EE-0525-43AA-8E03-6C568D1FF4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2505E5B-E92D-448C-AD10-6F2486B8B5AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2170,9 +2170,6 @@
     <t>尖刺头盔</t>
   </si>
   <si>
-    <t>全套装备：减少出些造成的伤害30%</t>
-  </si>
-  <si>
     <t>额外快捷栏；在近战中对攻击者造成5伤害</t>
   </si>
   <si>
@@ -2342,6 +2339,9 @@
   </si>
   <si>
     <t>酷吏二层，叛徒地下墓穴</t>
+  </si>
+  <si>
+    <t>全套装备：减少出血造成的伤害30%</t>
   </si>
 </sst>
 </file>
@@ -3709,48 +3709,48 @@
     <xf numFmtId="0" fontId="22" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4071,7 +4071,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
@@ -4084,7 +4084,7 @@
       <c r="D2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="150">
+      <c r="E2" s="138">
         <v>91</v>
       </c>
       <c r="F2" s="11" t="s">
@@ -4093,8 +4093,8 @@
       <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="134" t="s">
-        <v>398</v>
+      <c r="H2" s="143" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="15.75" customHeight="1">
@@ -4107,14 +4107,14 @@
       <c r="D3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="146"/>
+      <c r="E3" s="135"/>
       <c r="F3" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="135"/>
+      <c r="H3" s="144"/>
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1">
       <c r="B4" s="13" t="s">
@@ -4126,14 +4126,14 @@
       <c r="D4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="146"/>
+      <c r="E4" s="135"/>
       <c r="F4" s="15" t="s">
         <v>329</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="135"/>
+      <c r="H4" s="144"/>
     </row>
     <row r="5" spans="2:8" ht="15.75" customHeight="1">
       <c r="B5" s="13" t="s">
@@ -4145,14 +4145,14 @@
       <c r="D5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="146"/>
+      <c r="E5" s="135"/>
       <c r="F5" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="135"/>
+      <c r="H5" s="144"/>
     </row>
     <row r="6" spans="2:8" ht="15.75" customHeight="1">
       <c r="B6" s="13" t="s">
@@ -4164,14 +4164,14 @@
       <c r="D6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="146"/>
+      <c r="E6" s="135"/>
       <c r="F6" s="15" t="s">
         <v>329</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="135"/>
+      <c r="H6" s="144"/>
     </row>
     <row r="7" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B7" s="16" t="s">
@@ -4183,14 +4183,14 @@
       <c r="D7" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="149"/>
+      <c r="E7" s="136"/>
       <c r="F7" s="19" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="137"/>
+      <c r="H7" s="145"/>
     </row>
     <row r="8" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B8" s="21" t="s">
@@ -4202,7 +4202,7 @@
       <c r="D8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="145">
+      <c r="E8" s="134">
         <v>91</v>
       </c>
       <c r="F8" s="11" t="s">
@@ -4211,8 +4211,8 @@
       <c r="G8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="134" t="s">
-        <v>399</v>
+      <c r="H8" s="143" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15.75" customHeight="1">
@@ -4225,14 +4225,14 @@
       <c r="D9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="146"/>
+      <c r="E9" s="135"/>
       <c r="F9" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="135"/>
+      <c r="H9" s="144"/>
     </row>
     <row r="10" spans="2:8" ht="15.75" customHeight="1">
       <c r="B10" s="13" t="s">
@@ -4244,14 +4244,14 @@
       <c r="D10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="146"/>
+      <c r="E10" s="135"/>
       <c r="F10" s="15" t="s">
         <v>329</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="135"/>
+      <c r="H10" s="144"/>
     </row>
     <row r="11" spans="2:8" ht="15.75" customHeight="1">
       <c r="B11" s="13" t="s">
@@ -4263,14 +4263,14 @@
       <c r="D11" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="146"/>
+      <c r="E11" s="135"/>
       <c r="F11" s="15" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="135"/>
+      <c r="H11" s="144"/>
     </row>
     <row r="12" spans="2:8" ht="15.75" customHeight="1">
       <c r="B12" s="13" t="s">
@@ -4282,14 +4282,14 @@
       <c r="D12" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="146"/>
+      <c r="E12" s="135"/>
       <c r="F12" s="15" t="s">
         <v>329</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="135"/>
+      <c r="H12" s="144"/>
     </row>
     <row r="13" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B13" s="23" t="s">
@@ -4301,14 +4301,14 @@
       <c r="D13" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="147"/>
+      <c r="E13" s="137"/>
       <c r="F13" s="26" t="s">
         <v>9</v>
       </c>
       <c r="G13" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="137"/>
+      <c r="H13" s="145"/>
     </row>
     <row r="14" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B14" s="8" t="s">
@@ -4320,7 +4320,7 @@
       <c r="D14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="148">
+      <c r="E14" s="139">
         <v>100</v>
       </c>
       <c r="F14" s="28" t="s">
@@ -4329,8 +4329,8 @@
       <c r="G14" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="134" t="s">
-        <v>398</v>
+      <c r="H14" s="143" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15.75" customHeight="1">
@@ -4343,14 +4343,14 @@
       <c r="D15" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="146"/>
+      <c r="E15" s="135"/>
       <c r="F15" s="15" t="s">
         <v>331</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H15" s="135"/>
+      <c r="H15" s="144"/>
     </row>
     <row r="16" spans="2:8" ht="15.75" customHeight="1">
       <c r="B16" s="13" t="s">
@@ -4362,14 +4362,14 @@
       <c r="D16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="146"/>
+      <c r="E16" s="135"/>
       <c r="F16" s="15" t="s">
         <v>332</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="135"/>
+      <c r="H16" s="144"/>
     </row>
     <row r="17" spans="2:12" ht="15.75" customHeight="1">
       <c r="B17" s="13" t="s">
@@ -4381,14 +4381,14 @@
       <c r="D17" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="146"/>
+      <c r="E17" s="135"/>
       <c r="F17" s="15" t="s">
         <v>333</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H17" s="135"/>
+      <c r="H17" s="144"/>
       <c r="I17" s="29"/>
       <c r="J17" s="29"/>
       <c r="K17" s="29"/>
@@ -4404,14 +4404,14 @@
       <c r="D18" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="146"/>
+      <c r="E18" s="135"/>
       <c r="F18" s="15" t="s">
         <v>332</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="135"/>
+      <c r="H18" s="144"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
       <c r="K18" s="29"/>
@@ -4427,14 +4427,14 @@
       <c r="D19" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="149"/>
+      <c r="E19" s="136"/>
       <c r="F19" s="19" t="s">
         <v>334</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="137"/>
+      <c r="H19" s="145"/>
       <c r="I19" s="29"/>
       <c r="J19" s="29"/>
       <c r="K19" s="29"/>
@@ -4450,7 +4450,7 @@
       <c r="D20" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="145">
+      <c r="E20" s="134">
         <v>100</v>
       </c>
       <c r="F20" s="11" t="s">
@@ -4459,8 +4459,8 @@
       <c r="G20" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="H20" s="134" t="s">
-        <v>400</v>
+      <c r="H20" s="143" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="15.75" customHeight="1">
@@ -4473,14 +4473,14 @@
       <c r="D21" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="146"/>
+      <c r="E21" s="135"/>
       <c r="F21" s="15" t="s">
         <v>331</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H21" s="135"/>
+      <c r="H21" s="144"/>
     </row>
     <row r="22" spans="2:12" ht="15.75" customHeight="1">
       <c r="B22" s="13" t="s">
@@ -4492,14 +4492,14 @@
       <c r="D22" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="146"/>
+      <c r="E22" s="135"/>
       <c r="F22" s="15" t="s">
         <v>332</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H22" s="135"/>
+      <c r="H22" s="144"/>
     </row>
     <row r="23" spans="2:12" ht="15.75" customHeight="1">
       <c r="B23" s="13" t="s">
@@ -4511,14 +4511,14 @@
       <c r="D23" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="146"/>
+      <c r="E23" s="135"/>
       <c r="F23" s="15" t="s">
         <v>333</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H23" s="135"/>
+      <c r="H23" s="144"/>
     </row>
     <row r="24" spans="2:12" ht="15.75" customHeight="1">
       <c r="B24" s="13" t="s">
@@ -4530,14 +4530,14 @@
       <c r="D24" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="146"/>
+      <c r="E24" s="135"/>
       <c r="F24" s="15" t="s">
         <v>332</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H24" s="135"/>
+      <c r="H24" s="144"/>
     </row>
     <row r="25" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B25" s="107" t="s">
@@ -4549,14 +4549,14 @@
       <c r="D25" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="149"/>
+      <c r="E25" s="136"/>
       <c r="F25" s="19" t="s">
         <v>334</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H25" s="137"/>
+      <c r="H25" s="145"/>
     </row>
     <row r="26" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B26" s="21" t="s">
@@ -4568,7 +4568,7 @@
       <c r="D26" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="145">
+      <c r="E26" s="134">
         <v>100</v>
       </c>
       <c r="F26" s="31" t="s">
@@ -4577,8 +4577,8 @@
       <c r="G26" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H26" s="134" t="s">
-        <v>399</v>
+      <c r="H26" s="143" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="27" spans="2:12" ht="15.75" customHeight="1">
@@ -4591,14 +4591,14 @@
       <c r="D27" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="146"/>
+      <c r="E27" s="135"/>
       <c r="F27" s="15" t="s">
         <v>331</v>
       </c>
       <c r="G27" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H27" s="135"/>
+      <c r="H27" s="144"/>
     </row>
     <row r="28" spans="2:12" ht="15.75" customHeight="1">
       <c r="B28" s="13" t="s">
@@ -4610,14 +4610,14 @@
       <c r="D28" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="146"/>
+      <c r="E28" s="135"/>
       <c r="F28" s="15" t="s">
         <v>332</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H28" s="135"/>
+      <c r="H28" s="144"/>
     </row>
     <row r="29" spans="2:12" ht="15.75" customHeight="1">
       <c r="B29" s="13" t="s">
@@ -4629,14 +4629,14 @@
       <c r="D29" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="146"/>
+      <c r="E29" s="135"/>
       <c r="F29" s="15" t="s">
         <v>333</v>
       </c>
       <c r="G29" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H29" s="135"/>
+      <c r="H29" s="144"/>
     </row>
     <row r="30" spans="2:12" ht="15.75" customHeight="1">
       <c r="B30" s="13" t="s">
@@ -4648,14 +4648,14 @@
       <c r="D30" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="146"/>
+      <c r="E30" s="135"/>
       <c r="F30" s="15" t="s">
         <v>332</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H30" s="135"/>
+      <c r="H30" s="144"/>
     </row>
     <row r="31" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B31" s="32" t="s">
@@ -4667,14 +4667,14 @@
       <c r="D31" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="147"/>
+      <c r="E31" s="137"/>
       <c r="F31" s="34" t="s">
         <v>334</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="H31" s="137"/>
+      <c r="H31" s="145"/>
     </row>
     <row r="32" spans="2:12" ht="25.9" thickTop="1">
       <c r="B32" s="36" t="s">
@@ -4686,7 +4686,7 @@
       <c r="D32" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="145">
+      <c r="E32" s="134">
         <v>112</v>
       </c>
       <c r="F32" s="31" t="s">
@@ -4695,8 +4695,8 @@
       <c r="G32" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="H32" s="134" t="s">
-        <v>399</v>
+      <c r="H32" s="143" t="s">
+        <v>398</v>
       </c>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -4713,14 +4713,14 @@
       <c r="D33" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="146"/>
+      <c r="E33" s="135"/>
       <c r="F33" s="15" t="s">
         <v>336</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H33" s="135"/>
+      <c r="H33" s="144"/>
       <c r="I33" s="29"/>
       <c r="J33" s="29"/>
       <c r="K33" s="29"/>
@@ -4736,14 +4736,14 @@
       <c r="D34" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="146"/>
+      <c r="E34" s="135"/>
       <c r="F34" s="15" t="s">
         <v>337</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="135"/>
+      <c r="H34" s="144"/>
       <c r="I34" s="29"/>
       <c r="J34" s="29"/>
       <c r="K34" s="29"/>
@@ -4759,14 +4759,14 @@
       <c r="D35" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="146"/>
+      <c r="E35" s="135"/>
       <c r="F35" s="15" t="s">
         <v>338</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H35" s="135"/>
+      <c r="H35" s="144"/>
       <c r="I35" s="29"/>
       <c r="J35" s="29"/>
       <c r="K35" s="29"/>
@@ -4782,14 +4782,14 @@
       <c r="D36" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="146"/>
+      <c r="E36" s="135"/>
       <c r="F36" s="15" t="s">
         <v>339</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H36" s="135"/>
+      <c r="H36" s="144"/>
       <c r="I36" s="29"/>
       <c r="J36" s="29"/>
       <c r="K36" s="29"/>
@@ -4805,14 +4805,14 @@
       <c r="D37" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E37" s="147"/>
+      <c r="E37" s="137"/>
       <c r="F37" s="26" t="s">
         <v>340</v>
       </c>
       <c r="G37" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="H37" s="137"/>
+      <c r="H37" s="145"/>
       <c r="I37" s="29"/>
       <c r="J37" s="29"/>
       <c r="K37" s="29"/>
@@ -4828,17 +4828,17 @@
       <c r="D38" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="145">
+      <c r="E38" s="134">
         <v>100</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>330</v>
       </c>
       <c r="G38" s="41" t="s">
-        <v>432</v>
-      </c>
-      <c r="H38" s="134" t="s">
-        <v>399</v>
+        <v>431</v>
+      </c>
+      <c r="H38" s="143" t="s">
+        <v>398</v>
       </c>
       <c r="I38" s="29"/>
       <c r="J38" s="29"/>
@@ -4855,14 +4855,14 @@
       <c r="D39" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E39" s="146"/>
+      <c r="E39" s="135"/>
       <c r="F39" s="15" t="s">
         <v>331</v>
       </c>
       <c r="G39" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="H39" s="135"/>
+      <c r="H39" s="144"/>
       <c r="I39" s="29"/>
       <c r="J39" s="29"/>
       <c r="K39" s="29"/>
@@ -4878,14 +4878,14 @@
       <c r="D40" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E40" s="146"/>
+      <c r="E40" s="135"/>
       <c r="F40" s="15" t="s">
         <v>332</v>
       </c>
       <c r="G40" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="H40" s="135"/>
+      <c r="H40" s="144"/>
       <c r="I40" s="29"/>
       <c r="J40" s="29"/>
       <c r="K40" s="29"/>
@@ -4901,14 +4901,14 @@
       <c r="D41" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E41" s="146"/>
+      <c r="E41" s="135"/>
       <c r="F41" s="15" t="s">
         <v>333</v>
       </c>
       <c r="G41" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="H41" s="135"/>
+      <c r="H41" s="144"/>
       <c r="I41" s="29"/>
       <c r="J41" s="29"/>
       <c r="K41" s="29"/>
@@ -4924,14 +4924,14 @@
       <c r="D42" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E42" s="146"/>
+      <c r="E42" s="135"/>
       <c r="F42" s="15" t="s">
         <v>332</v>
       </c>
       <c r="G42" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="H42" s="135"/>
+      <c r="H42" s="144"/>
       <c r="I42" s="29"/>
       <c r="J42" s="29"/>
       <c r="K42" s="29"/>
@@ -4947,14 +4947,14 @@
       <c r="D43" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E43" s="147"/>
+      <c r="E43" s="137"/>
       <c r="F43" s="26" t="s">
         <v>334</v>
       </c>
       <c r="G43" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="H43" s="137"/>
+      <c r="H43" s="145"/>
       <c r="I43" s="29"/>
       <c r="J43" s="29"/>
       <c r="K43" s="29"/>
@@ -4970,7 +4970,7 @@
       <c r="D44" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E44" s="150">
+      <c r="E44" s="138">
         <v>112</v>
       </c>
       <c r="F44" s="11" t="s">
@@ -4979,8 +4979,8 @@
       <c r="G44" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H44" s="134" t="s">
-        <v>398</v>
+      <c r="H44" s="143" t="s">
+        <v>397</v>
       </c>
       <c r="I44" s="29"/>
       <c r="J44" s="29"/>
@@ -4997,14 +4997,14 @@
       <c r="D45" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E45" s="146"/>
+      <c r="E45" s="135"/>
       <c r="F45" s="15" t="s">
         <v>32</v>
       </c>
       <c r="G45" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H45" s="135"/>
+      <c r="H45" s="144"/>
       <c r="I45" s="29"/>
       <c r="J45" s="29"/>
       <c r="K45" s="29"/>
@@ -5020,14 +5020,14 @@
       <c r="D46" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E46" s="146"/>
+      <c r="E46" s="135"/>
       <c r="F46" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G46" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H46" s="135"/>
+      <c r="H46" s="144"/>
       <c r="I46" s="29"/>
       <c r="J46" s="29"/>
       <c r="K46" s="29"/>
@@ -5043,14 +5043,14 @@
       <c r="D47" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E47" s="146"/>
+      <c r="E47" s="135"/>
       <c r="F47" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G47" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H47" s="135"/>
+      <c r="H47" s="144"/>
       <c r="I47" s="29"/>
       <c r="J47" s="29"/>
       <c r="K47" s="29"/>
@@ -5066,14 +5066,14 @@
       <c r="D48" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E48" s="146"/>
+      <c r="E48" s="135"/>
       <c r="F48" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G48" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H48" s="135"/>
+      <c r="H48" s="144"/>
       <c r="I48" s="29"/>
       <c r="J48" s="29"/>
       <c r="K48" s="29"/>
@@ -5089,14 +5089,14 @@
       <c r="D49" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E49" s="149"/>
+      <c r="E49" s="136"/>
       <c r="F49" s="19" t="s">
         <v>342</v>
       </c>
       <c r="G49" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="H49" s="137"/>
+      <c r="H49" s="145"/>
       <c r="I49" s="29"/>
       <c r="J49" s="29"/>
       <c r="K49" s="29"/>
@@ -5112,7 +5112,7 @@
       <c r="D50" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E50" s="145">
+      <c r="E50" s="134">
         <v>112</v>
       </c>
       <c r="F50" s="15" t="s">
@@ -5121,8 +5121,8 @@
       <c r="G50" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H50" s="134" t="s">
-        <v>401</v>
+      <c r="H50" s="143" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="51" spans="2:12" ht="15.75" customHeight="1">
@@ -5135,14 +5135,14 @@
       <c r="D51" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E51" s="146"/>
+      <c r="E51" s="135"/>
       <c r="F51" s="15" t="s">
         <v>32</v>
       </c>
       <c r="G51" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H51" s="135"/>
+      <c r="H51" s="144"/>
     </row>
     <row r="52" spans="2:12" ht="15.75" customHeight="1">
       <c r="B52" s="13" t="s">
@@ -5154,14 +5154,14 @@
       <c r="D52" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E52" s="146"/>
+      <c r="E52" s="135"/>
       <c r="F52" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G52" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H52" s="135"/>
+      <c r="H52" s="144"/>
     </row>
     <row r="53" spans="2:12" ht="15.75" customHeight="1">
       <c r="B53" s="13" t="s">
@@ -5173,14 +5173,14 @@
       <c r="D53" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E53" s="146"/>
+      <c r="E53" s="135"/>
       <c r="F53" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G53" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H53" s="135"/>
+      <c r="H53" s="144"/>
     </row>
     <row r="54" spans="2:12" ht="15.75" customHeight="1">
       <c r="B54" s="13" t="s">
@@ -5192,14 +5192,14 @@
       <c r="D54" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E54" s="146"/>
+      <c r="E54" s="135"/>
       <c r="F54" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H54" s="135"/>
+      <c r="H54" s="144"/>
     </row>
     <row r="55" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B55" s="16" t="s">
@@ -5211,14 +5211,14 @@
       <c r="D55" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E55" s="149"/>
+      <c r="E55" s="136"/>
       <c r="F55" s="19" t="s">
         <v>342</v>
       </c>
       <c r="G55" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="H55" s="137"/>
+      <c r="H55" s="145"/>
     </row>
     <row r="56" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B56" s="36" t="s">
@@ -5230,7 +5230,7 @@
       <c r="D56" s="63" t="s">
         <v>176</v>
       </c>
-      <c r="E56" s="145">
+      <c r="E56" s="134">
         <v>112</v>
       </c>
       <c r="F56" s="47" t="s">
@@ -5239,8 +5239,8 @@
       <c r="G56" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="H56" s="134" t="s">
-        <v>402</v>
+      <c r="H56" s="143" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="57" spans="2:12" ht="15.75" customHeight="1">
@@ -5253,14 +5253,14 @@
       <c r="D57" s="63" t="s">
         <v>174</v>
       </c>
-      <c r="E57" s="146"/>
+      <c r="E57" s="135"/>
       <c r="F57" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G57" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H57" s="135"/>
+      <c r="H57" s="144"/>
     </row>
     <row r="58" spans="2:12" ht="15.75" customHeight="1">
       <c r="B58" s="38" t="s">
@@ -5272,14 +5272,14 @@
       <c r="D58" s="63" t="s">
         <v>175</v>
       </c>
-      <c r="E58" s="146"/>
+      <c r="E58" s="135"/>
       <c r="F58" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G58" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H58" s="135"/>
+      <c r="H58" s="144"/>
     </row>
     <row r="59" spans="2:12" ht="15.75" customHeight="1">
       <c r="B59" s="38" t="s">
@@ -5291,14 +5291,14 @@
       <c r="D59" s="63" t="s">
         <v>174</v>
       </c>
-      <c r="E59" s="146"/>
+      <c r="E59" s="135"/>
       <c r="F59" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G59" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H59" s="135"/>
+      <c r="H59" s="144"/>
     </row>
     <row r="60" spans="2:12" ht="15.75" customHeight="1">
       <c r="B60" s="38" t="s">
@@ -5310,14 +5310,14 @@
       <c r="D60" s="63" t="s">
         <v>175</v>
       </c>
-      <c r="E60" s="146"/>
+      <c r="E60" s="135"/>
       <c r="F60" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G60" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H60" s="135"/>
+      <c r="H60" s="144"/>
     </row>
     <row r="61" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B61" s="51" t="s">
@@ -5329,14 +5329,14 @@
       <c r="D61" s="63" t="s">
         <v>174</v>
       </c>
-      <c r="E61" s="149"/>
+      <c r="E61" s="136"/>
       <c r="F61" s="53" t="s">
         <v>7</v>
       </c>
       <c r="G61" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="H61" s="137"/>
+      <c r="H61" s="145"/>
     </row>
     <row r="62" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B62" s="36" t="s">
@@ -5348,17 +5348,17 @@
       <c r="D62" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E62" s="145">
+      <c r="E62" s="134">
         <v>143</v>
       </c>
       <c r="F62" s="31" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G62" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="H62" s="134" t="s">
-        <v>399</v>
+      <c r="H62" s="143" t="s">
+        <v>398</v>
       </c>
       <c r="I62" s="29"/>
       <c r="J62" s="29"/>
@@ -5375,14 +5375,14 @@
       <c r="D63" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E63" s="146"/>
+      <c r="E63" s="135"/>
       <c r="F63" s="15" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G63" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="H63" s="135"/>
+      <c r="H63" s="144"/>
       <c r="I63" s="29"/>
       <c r="J63" s="29"/>
       <c r="K63" s="29"/>
@@ -5398,14 +5398,14 @@
       <c r="D64" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E64" s="146"/>
+      <c r="E64" s="135"/>
       <c r="F64" s="15" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G64" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="H64" s="135"/>
+      <c r="H64" s="144"/>
       <c r="I64" s="29"/>
       <c r="J64" s="29"/>
       <c r="K64" s="29"/>
@@ -5421,14 +5421,14 @@
       <c r="D65" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E65" s="146"/>
+      <c r="E65" s="135"/>
       <c r="F65" s="15" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G65" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H65" s="135"/>
+      <c r="H65" s="144"/>
       <c r="I65" s="29"/>
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
@@ -5444,14 +5444,14 @@
       <c r="D66" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E66" s="146"/>
+      <c r="E66" s="135"/>
       <c r="F66" s="15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G66" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H66" s="135"/>
+      <c r="H66" s="144"/>
       <c r="I66" s="29"/>
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
@@ -5465,14 +5465,14 @@
         <v>12</v>
       </c>
       <c r="D67" s="18"/>
-      <c r="E67" s="149"/>
+      <c r="E67" s="136"/>
       <c r="F67" s="19" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G67" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="H67" s="137"/>
+      <c r="H67" s="145"/>
       <c r="I67" s="29"/>
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
@@ -5488,17 +5488,17 @@
       <c r="D68" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E68" s="145">
+      <c r="E68" s="134">
         <v>143</v>
       </c>
       <c r="F68" s="31" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G68" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="H68" s="134" t="s">
-        <v>399</v>
+      <c r="H68" s="143" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="69" spans="2:12" ht="15.75" customHeight="1">
@@ -5511,14 +5511,14 @@
       <c r="D69" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E69" s="146"/>
+      <c r="E69" s="135"/>
       <c r="F69" s="56" t="s">
         <v>195</v>
       </c>
       <c r="G69" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="H69" s="135"/>
+      <c r="H69" s="144"/>
     </row>
     <row r="70" spans="2:12" ht="15.75" customHeight="1">
       <c r="B70" s="38" t="s">
@@ -5530,14 +5530,14 @@
       <c r="D70" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E70" s="146"/>
+      <c r="E70" s="135"/>
       <c r="F70" s="15" t="s">
         <v>196</v>
       </c>
       <c r="G70" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H70" s="135"/>
+      <c r="H70" s="144"/>
     </row>
     <row r="71" spans="2:12" ht="15.75" customHeight="1">
       <c r="B71" s="38" t="s">
@@ -5549,14 +5549,14 @@
       <c r="D71" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E71" s="146"/>
+      <c r="E71" s="135"/>
       <c r="F71" s="56" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G71" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H71" s="135"/>
+      <c r="H71" s="144"/>
     </row>
     <row r="72" spans="2:12" ht="15.75" customHeight="1">
       <c r="B72" s="38" t="s">
@@ -5568,14 +5568,14 @@
       <c r="D72" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E72" s="146"/>
+      <c r="E72" s="135"/>
       <c r="F72" s="15" t="s">
         <v>197</v>
       </c>
       <c r="G72" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H72" s="135"/>
+      <c r="H72" s="144"/>
     </row>
     <row r="73" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B73" s="51" t="s">
@@ -5587,14 +5587,14 @@
       <c r="D73" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E73" s="149"/>
+      <c r="E73" s="136"/>
       <c r="F73" s="57" t="s">
         <v>198</v>
       </c>
       <c r="G73" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="H73" s="137"/>
+      <c r="H73" s="145"/>
     </row>
     <row r="74" spans="2:12" ht="31.5" customHeight="1" thickTop="1">
       <c r="B74" s="36" t="s">
@@ -5606,17 +5606,17 @@
       <c r="D74" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E74" s="145">
+      <c r="E74" s="134">
         <v>143</v>
       </c>
       <c r="F74" s="58" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G74" s="37" t="s">
-        <v>431</v>
-      </c>
-      <c r="H74" s="134" t="s">
-        <v>399</v>
+        <v>430</v>
+      </c>
+      <c r="H74" s="143" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="75" spans="2:12" ht="26.65" customHeight="1">
@@ -5629,14 +5629,14 @@
       <c r="D75" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E75" s="146"/>
+      <c r="E75" s="135"/>
       <c r="F75" s="56" t="s">
         <v>186</v>
       </c>
       <c r="G75" s="54" t="s">
-        <v>427</v>
-      </c>
-      <c r="H75" s="135"/>
+        <v>426</v>
+      </c>
+      <c r="H75" s="144"/>
     </row>
     <row r="76" spans="2:12" ht="15.75" customHeight="1">
       <c r="B76" s="38" t="s">
@@ -5648,14 +5648,14 @@
       <c r="D76" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E76" s="146"/>
+      <c r="E76" s="135"/>
       <c r="F76" s="56" t="s">
         <v>187</v>
       </c>
       <c r="G76" s="55" t="s">
-        <v>428</v>
-      </c>
-      <c r="H76" s="135"/>
+        <v>427</v>
+      </c>
+      <c r="H76" s="144"/>
     </row>
     <row r="77" spans="2:12" ht="15.75" customHeight="1">
       <c r="B77" s="38" t="s">
@@ -5667,14 +5667,14 @@
       <c r="D77" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E77" s="146"/>
+      <c r="E77" s="135"/>
       <c r="F77" s="56" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G77" s="54" t="s">
-        <v>429</v>
-      </c>
-      <c r="H77" s="135"/>
+        <v>428</v>
+      </c>
+      <c r="H77" s="144"/>
     </row>
     <row r="78" spans="2:12" ht="15.75" customHeight="1">
       <c r="B78" s="38" t="s">
@@ -5686,14 +5686,14 @@
       <c r="D78" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E78" s="146"/>
+      <c r="E78" s="135"/>
       <c r="F78" s="56" t="s">
         <v>188</v>
       </c>
       <c r="G78" s="54" t="s">
-        <v>429</v>
-      </c>
-      <c r="H78" s="135"/>
+        <v>428</v>
+      </c>
+      <c r="H78" s="144"/>
     </row>
     <row r="79" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B79" s="51" t="s">
@@ -5705,14 +5705,14 @@
       <c r="D79" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E79" s="149"/>
+      <c r="E79" s="136"/>
       <c r="F79" s="57" t="s">
         <v>186</v>
       </c>
       <c r="G79" s="20" t="s">
-        <v>430</v>
-      </c>
-      <c r="H79" s="137"/>
+        <v>429</v>
+      </c>
+      <c r="H79" s="145"/>
     </row>
     <row r="80" spans="2:12" ht="38.65" thickTop="1">
       <c r="B80" s="40" t="s">
@@ -5724,7 +5724,7 @@
       <c r="D80" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E80" s="145">
+      <c r="E80" s="134">
         <v>112</v>
       </c>
       <c r="F80" s="11" t="s">
@@ -5733,8 +5733,8 @@
       <c r="G80" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="H80" s="134" t="s">
-        <v>399</v>
+      <c r="H80" s="143" t="s">
+        <v>398</v>
       </c>
       <c r="I80" s="29"/>
       <c r="J80" s="29"/>
@@ -5751,14 +5751,14 @@
       <c r="D81" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E81" s="146"/>
+      <c r="E81" s="135"/>
       <c r="F81" s="15" t="s">
         <v>32</v>
       </c>
       <c r="G81" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H81" s="135"/>
+      <c r="H81" s="144"/>
       <c r="I81" s="29"/>
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
@@ -5774,14 +5774,14 @@
       <c r="D82" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E82" s="146"/>
+      <c r="E82" s="135"/>
       <c r="F82" s="15" t="s">
         <v>33</v>
       </c>
       <c r="G82" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H82" s="135"/>
+      <c r="H82" s="144"/>
       <c r="I82" s="29"/>
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
@@ -5797,14 +5797,14 @@
       <c r="D83" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E83" s="146"/>
+      <c r="E83" s="135"/>
       <c r="F83" s="15" t="s">
         <v>34</v>
       </c>
       <c r="G83" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H83" s="135"/>
+      <c r="H83" s="144"/>
       <c r="I83" s="29"/>
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
@@ -5820,14 +5820,14 @@
       <c r="D84" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E84" s="146"/>
+      <c r="E84" s="135"/>
       <c r="F84" s="15" t="s">
         <v>35</v>
       </c>
       <c r="G84" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H84" s="135"/>
+      <c r="H84" s="144"/>
       <c r="I84" s="29"/>
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
@@ -5843,14 +5843,14 @@
       <c r="D85" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E85" s="147"/>
+      <c r="E85" s="137"/>
       <c r="F85" s="26" t="s">
         <v>343</v>
       </c>
       <c r="G85" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="H85" s="137"/>
+      <c r="H85" s="145"/>
       <c r="I85" s="29"/>
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
@@ -5866,7 +5866,7 @@
       <c r="D86" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E86" s="150">
+      <c r="E86" s="138">
         <v>125</v>
       </c>
       <c r="F86" s="11" t="s">
@@ -5875,8 +5875,8 @@
       <c r="G86" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H86" s="134" t="s">
-        <v>398</v>
+      <c r="H86" s="143" t="s">
+        <v>397</v>
       </c>
       <c r="I86" s="29"/>
       <c r="J86" s="29"/>
@@ -5893,14 +5893,14 @@
       <c r="D87" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E87" s="146"/>
+      <c r="E87" s="135"/>
       <c r="F87" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G87" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H87" s="135"/>
+      <c r="H87" s="144"/>
       <c r="I87" s="29"/>
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
@@ -5916,14 +5916,14 @@
       <c r="D88" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E88" s="146"/>
+      <c r="E88" s="135"/>
       <c r="F88" s="15" t="s">
         <v>59</v>
       </c>
       <c r="G88" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H88" s="135"/>
+      <c r="H88" s="144"/>
       <c r="I88" s="29"/>
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
@@ -5939,14 +5939,14 @@
       <c r="D89" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E89" s="146"/>
+      <c r="E89" s="135"/>
       <c r="F89" s="15" t="s">
         <v>60</v>
       </c>
       <c r="G89" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H89" s="135"/>
+      <c r="H89" s="144"/>
       <c r="I89" s="29"/>
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
@@ -5962,14 +5962,14 @@
       <c r="D90" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E90" s="146"/>
+      <c r="E90" s="135"/>
       <c r="F90" s="15" t="s">
         <v>61</v>
       </c>
       <c r="G90" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H90" s="135"/>
+      <c r="H90" s="144"/>
       <c r="I90" s="29"/>
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
@@ -5985,14 +5985,14 @@
       <c r="D91" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E91" s="149"/>
+      <c r="E91" s="136"/>
       <c r="F91" s="19" t="s">
         <v>62</v>
       </c>
       <c r="G91" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H91" s="137"/>
+      <c r="H91" s="145"/>
       <c r="I91" s="29"/>
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
@@ -6008,7 +6008,7 @@
       <c r="D92" s="62" t="s">
         <v>315</v>
       </c>
-      <c r="E92" s="145">
+      <c r="E92" s="134">
         <v>125</v>
       </c>
       <c r="F92" s="47" t="s">
@@ -6017,8 +6017,8 @@
       <c r="G92" s="48" t="s">
         <v>318</v>
       </c>
-      <c r="H92" s="141" t="s">
-        <v>403</v>
+      <c r="H92" s="146" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="93" spans="2:12" ht="15.75" customHeight="1">
@@ -6031,14 +6031,14 @@
       <c r="D93" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="E93" s="146"/>
+      <c r="E93" s="135"/>
       <c r="F93" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G93" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H93" s="139"/>
+      <c r="H93" s="147"/>
     </row>
     <row r="94" spans="2:12" ht="15.75" customHeight="1">
       <c r="B94" s="44" t="s">
@@ -6050,14 +6050,14 @@
       <c r="D94" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="E94" s="146"/>
+      <c r="E94" s="135"/>
       <c r="F94" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G94" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H94" s="139"/>
+      <c r="H94" s="147"/>
     </row>
     <row r="95" spans="2:12" ht="15.75" customHeight="1">
       <c r="B95" s="44" t="s">
@@ -6069,14 +6069,14 @@
       <c r="D95" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="E95" s="146"/>
+      <c r="E95" s="135"/>
       <c r="F95" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G95" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H95" s="139"/>
+      <c r="H95" s="147"/>
     </row>
     <row r="96" spans="2:12" ht="15.75" customHeight="1">
       <c r="B96" s="44" t="s">
@@ -6088,14 +6088,14 @@
       <c r="D96" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="E96" s="146"/>
+      <c r="E96" s="135"/>
       <c r="F96" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G96" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H96" s="139"/>
+      <c r="H96" s="147"/>
     </row>
     <row r="97" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B97" s="64" t="s">
@@ -6107,14 +6107,14 @@
       <c r="D97" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="E97" s="149"/>
+      <c r="E97" s="136"/>
       <c r="F97" s="53" t="s">
         <v>63</v>
       </c>
       <c r="G97" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="H97" s="140"/>
+      <c r="H97" s="148"/>
     </row>
     <row r="98" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B98" s="36" t="s">
@@ -6126,7 +6126,7 @@
       <c r="D98" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E98" s="145">
+      <c r="E98" s="134">
         <v>125</v>
       </c>
       <c r="F98" s="58" t="s">
@@ -6135,8 +6135,8 @@
       <c r="G98" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="H98" s="134" t="s">
-        <v>399</v>
+      <c r="H98" s="143" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="99" spans="2:8" ht="15.75" customHeight="1">
@@ -6149,14 +6149,14 @@
       <c r="D99" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E99" s="146"/>
+      <c r="E99" s="135"/>
       <c r="F99" s="56" t="s">
         <v>234</v>
       </c>
       <c r="G99" s="54" t="s">
         <v>228</v>
       </c>
-      <c r="H99" s="135"/>
+      <c r="H99" s="144"/>
     </row>
     <row r="100" spans="2:8" ht="15.75" customHeight="1">
       <c r="B100" s="38" t="s">
@@ -6168,14 +6168,14 @@
       <c r="D100" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E100" s="146"/>
+      <c r="E100" s="135"/>
       <c r="F100" s="56" t="s">
         <v>235</v>
       </c>
       <c r="G100" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H100" s="135"/>
+      <c r="H100" s="144"/>
     </row>
     <row r="101" spans="2:8" ht="15.75" customHeight="1">
       <c r="B101" s="38" t="s">
@@ -6187,14 +6187,14 @@
       <c r="D101" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E101" s="146"/>
+      <c r="E101" s="135"/>
       <c r="F101" s="56" t="s">
         <v>236</v>
       </c>
       <c r="G101" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H101" s="135"/>
+      <c r="H101" s="144"/>
     </row>
     <row r="102" spans="2:8" ht="15.75" customHeight="1">
       <c r="B102" s="38" t="s">
@@ -6206,14 +6206,14 @@
       <c r="D102" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E102" s="146"/>
+      <c r="E102" s="135"/>
       <c r="F102" s="56" t="s">
         <v>237</v>
       </c>
       <c r="G102" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H102" s="135"/>
+      <c r="H102" s="144"/>
     </row>
     <row r="103" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B103" s="51" t="s">
@@ -6225,14 +6225,14 @@
       <c r="D103" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E103" s="149"/>
+      <c r="E103" s="136"/>
       <c r="F103" s="57" t="s">
         <v>238</v>
       </c>
       <c r="G103" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="H103" s="137"/>
+      <c r="H103" s="145"/>
     </row>
     <row r="104" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B104" s="61" t="s">
@@ -6244,7 +6244,7 @@
       <c r="D104" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E104" s="145">
+      <c r="E104" s="134">
         <v>125</v>
       </c>
       <c r="F104" s="31" t="s">
@@ -6253,8 +6253,8 @@
       <c r="G104" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="H104" s="134" t="s">
-        <v>399</v>
+      <c r="H104" s="143" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="105" spans="2:8" ht="15.75" customHeight="1">
@@ -6267,14 +6267,14 @@
       <c r="D105" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E105" s="146"/>
+      <c r="E105" s="135"/>
       <c r="F105" s="15" t="s">
         <v>57</v>
       </c>
       <c r="G105" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H105" s="135"/>
+      <c r="H105" s="144"/>
     </row>
     <row r="106" spans="2:8" ht="15.75" customHeight="1">
       <c r="B106" s="44" t="s">
@@ -6286,14 +6286,14 @@
       <c r="D106" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E106" s="146"/>
+      <c r="E106" s="135"/>
       <c r="F106" s="15" t="s">
         <v>59</v>
       </c>
       <c r="G106" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H106" s="135"/>
+      <c r="H106" s="144"/>
     </row>
     <row r="107" spans="2:8" ht="15.75" customHeight="1">
       <c r="B107" s="44" t="s">
@@ -6305,14 +6305,14 @@
       <c r="D107" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E107" s="146"/>
+      <c r="E107" s="135"/>
       <c r="F107" s="15" t="s">
         <v>72</v>
       </c>
       <c r="G107" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H107" s="135"/>
+      <c r="H107" s="144"/>
     </row>
     <row r="108" spans="2:8" ht="15.75" customHeight="1">
       <c r="B108" s="44" t="s">
@@ -6324,14 +6324,14 @@
       <c r="D108" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E108" s="146"/>
+      <c r="E108" s="135"/>
       <c r="F108" s="15" t="s">
         <v>61</v>
       </c>
       <c r="G108" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H108" s="135"/>
+      <c r="H108" s="144"/>
     </row>
     <row r="109" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B109" s="66" t="s">
@@ -6343,14 +6343,14 @@
       <c r="D109" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E109" s="147"/>
+      <c r="E109" s="137"/>
       <c r="F109" s="34" t="s">
         <v>62</v>
       </c>
       <c r="G109" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="H109" s="137"/>
+      <c r="H109" s="145"/>
     </row>
     <row r="110" spans="2:8" ht="25.5" customHeight="1" thickTop="1">
       <c r="B110" s="36" t="s">
@@ -6362,7 +6362,7 @@
       <c r="D110" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E110" s="145">
+      <c r="E110" s="134">
         <v>125</v>
       </c>
       <c r="F110" s="72" t="s">
@@ -6371,8 +6371,8 @@
       <c r="G110" s="37" t="s">
         <v>353</v>
       </c>
-      <c r="H110" s="134" t="s">
-        <v>399</v>
+      <c r="H110" s="143" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="111" spans="2:8" ht="15.75" customHeight="1">
@@ -6385,14 +6385,14 @@
       <c r="D111" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E111" s="146"/>
+      <c r="E111" s="135"/>
       <c r="F111" s="56" t="s">
         <v>355</v>
       </c>
       <c r="G111" s="54" t="s">
         <v>352</v>
       </c>
-      <c r="H111" s="135"/>
+      <c r="H111" s="144"/>
     </row>
     <row r="112" spans="2:8" ht="15.75" customHeight="1">
       <c r="B112" s="38" t="s">
@@ -6404,14 +6404,14 @@
       <c r="D112" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E112" s="146"/>
+      <c r="E112" s="135"/>
       <c r="F112" s="56" t="s">
         <v>351</v>
       </c>
       <c r="G112" s="54" t="s">
         <v>356</v>
       </c>
-      <c r="H112" s="135"/>
+      <c r="H112" s="144"/>
     </row>
     <row r="113" spans="2:12" ht="15.75" customHeight="1">
       <c r="B113" s="38" t="s">
@@ -6423,14 +6423,14 @@
       <c r="D113" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E113" s="146"/>
+      <c r="E113" s="135"/>
       <c r="F113" s="56" t="s">
         <v>358</v>
       </c>
       <c r="G113" s="54" t="s">
         <v>352</v>
       </c>
-      <c r="H113" s="135"/>
+      <c r="H113" s="144"/>
     </row>
     <row r="114" spans="2:12" ht="15.75" customHeight="1">
       <c r="B114" s="38" t="s">
@@ -6442,14 +6442,14 @@
       <c r="D114" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E114" s="146"/>
+      <c r="E114" s="135"/>
       <c r="F114" s="56" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G114" s="54" t="s">
         <v>352</v>
       </c>
-      <c r="H114" s="135"/>
+      <c r="H114" s="144"/>
     </row>
     <row r="115" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B115" s="51" t="s">
@@ -6461,14 +6461,14 @@
       <c r="D115" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E115" s="149"/>
+      <c r="E115" s="136"/>
       <c r="F115" s="57" t="s">
         <v>362</v>
       </c>
       <c r="G115" s="54" t="s">
         <v>361</v>
       </c>
-      <c r="H115" s="137"/>
+      <c r="H115" s="145"/>
     </row>
     <row r="116" spans="2:12" ht="25.9" thickTop="1">
       <c r="B116" s="68" t="s">
@@ -6480,7 +6480,7 @@
       <c r="D116" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E116" s="145">
+      <c r="E116" s="134">
         <v>143</v>
       </c>
       <c r="F116" s="31" t="s">
@@ -6489,8 +6489,8 @@
       <c r="G116" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="H116" s="134" t="s">
-        <v>410</v>
+      <c r="H116" s="143" t="s">
+        <v>409</v>
       </c>
       <c r="I116" s="29"/>
       <c r="J116" s="29"/>
@@ -6507,14 +6507,14 @@
       <c r="D117" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E117" s="146"/>
+      <c r="E117" s="135"/>
       <c r="F117" s="15" t="s">
         <v>246</v>
       </c>
       <c r="G117" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H117" s="135"/>
+      <c r="H117" s="144"/>
       <c r="I117" s="29"/>
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
@@ -6530,14 +6530,14 @@
       <c r="D118" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E118" s="146"/>
+      <c r="E118" s="135"/>
       <c r="F118" s="15" t="s">
         <v>247</v>
       </c>
       <c r="G118" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="H118" s="135"/>
+      <c r="H118" s="144"/>
       <c r="I118" s="29"/>
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
@@ -6553,14 +6553,14 @@
       <c r="D119" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E119" s="146"/>
+      <c r="E119" s="135"/>
       <c r="F119" s="15" t="s">
         <v>248</v>
       </c>
       <c r="G119" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H119" s="135"/>
+      <c r="H119" s="144"/>
       <c r="I119" s="29"/>
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
@@ -6576,14 +6576,14 @@
       <c r="D120" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E120" s="146"/>
+      <c r="E120" s="135"/>
       <c r="F120" s="15" t="s">
         <v>249</v>
       </c>
       <c r="G120" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H120" s="135"/>
+      <c r="H120" s="144"/>
       <c r="I120" s="29"/>
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
@@ -6599,14 +6599,14 @@
       <c r="D121" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E121" s="147"/>
+      <c r="E121" s="137"/>
       <c r="F121" s="26" t="s">
         <v>250</v>
       </c>
       <c r="G121" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="H121" s="137"/>
+      <c r="H121" s="145"/>
       <c r="I121" s="29"/>
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
@@ -6622,7 +6622,7 @@
       <c r="D122" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E122" s="145">
+      <c r="E122" s="134">
         <v>125</v>
       </c>
       <c r="F122" s="72" t="s">
@@ -6631,8 +6631,8 @@
       <c r="G122" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="H122" s="134" t="s">
-        <v>399</v>
+      <c r="H122" s="143" t="s">
+        <v>398</v>
       </c>
       <c r="I122" s="29"/>
       <c r="J122" s="29"/>
@@ -6649,14 +6649,14 @@
       <c r="D123" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E123" s="146"/>
+      <c r="E123" s="135"/>
       <c r="F123" s="56" t="s">
         <v>252</v>
       </c>
       <c r="G123" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H123" s="135"/>
+      <c r="H123" s="144"/>
       <c r="I123" s="29"/>
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
@@ -6672,14 +6672,14 @@
       <c r="D124" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E124" s="146"/>
+      <c r="E124" s="135"/>
       <c r="F124" s="56" t="s">
         <v>253</v>
       </c>
       <c r="G124" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H124" s="135"/>
+      <c r="H124" s="144"/>
       <c r="I124" s="29"/>
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
@@ -6695,14 +6695,14 @@
       <c r="D125" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E125" s="146"/>
+      <c r="E125" s="135"/>
       <c r="F125" s="56" t="s">
         <v>254</v>
       </c>
       <c r="G125" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H125" s="135"/>
+      <c r="H125" s="144"/>
       <c r="I125" s="29"/>
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
@@ -6710,7 +6710,7 @@
     </row>
     <row r="126" spans="2:12" ht="15.75" customHeight="1">
       <c r="B126" s="38" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C126" s="14">
         <v>190</v>
@@ -6718,14 +6718,14 @@
       <c r="D126" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E126" s="146"/>
+      <c r="E126" s="135"/>
       <c r="F126" s="56" t="s">
         <v>255</v>
       </c>
       <c r="G126" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H126" s="135"/>
+      <c r="H126" s="144"/>
       <c r="I126" s="29"/>
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
@@ -6733,7 +6733,7 @@
     </row>
     <row r="127" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B127" s="39" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C127" s="24">
         <v>60</v>
@@ -6741,14 +6741,14 @@
       <c r="D127" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="E127" s="147"/>
+      <c r="E127" s="137"/>
       <c r="F127" s="73" t="s">
         <v>256</v>
       </c>
       <c r="G127" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="H127" s="137"/>
+      <c r="H127" s="145"/>
       <c r="I127" s="29"/>
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
@@ -6764,7 +6764,7 @@
       <c r="D128" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E128" s="145">
+      <c r="E128" s="134">
         <v>143</v>
       </c>
       <c r="F128" s="72" t="s">
@@ -6773,8 +6773,8 @@
       <c r="G128" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="H128" s="134" t="s">
-        <v>399</v>
+      <c r="H128" s="143" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="129" spans="2:12" ht="15.75" customHeight="1">
@@ -6787,14 +6787,14 @@
       <c r="D129" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E129" s="146"/>
+      <c r="E129" s="135"/>
       <c r="F129" s="56" t="s">
         <v>261</v>
       </c>
       <c r="G129" s="77" t="s">
         <v>115</v>
       </c>
-      <c r="H129" s="135"/>
+      <c r="H129" s="144"/>
     </row>
     <row r="130" spans="2:12" ht="15.75" customHeight="1">
       <c r="B130" s="70" t="s">
@@ -6806,14 +6806,14 @@
       <c r="D130" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E130" s="146"/>
+      <c r="E130" s="135"/>
       <c r="F130" s="56" t="s">
         <v>262</v>
       </c>
       <c r="G130" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="H130" s="135"/>
+      <c r="H130" s="144"/>
     </row>
     <row r="131" spans="2:12" ht="15.75" customHeight="1">
       <c r="B131" s="74" t="s">
@@ -6825,14 +6825,14 @@
       <c r="D131" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E131" s="146"/>
+      <c r="E131" s="135"/>
       <c r="F131" s="56" t="s">
         <v>263</v>
       </c>
       <c r="G131" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H131" s="135"/>
+      <c r="H131" s="144"/>
     </row>
     <row r="132" spans="2:12" ht="15.75" customHeight="1">
       <c r="B132" s="74" t="s">
@@ -6844,14 +6844,14 @@
       <c r="D132" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E132" s="146"/>
+      <c r="E132" s="135"/>
       <c r="F132" s="56" t="s">
         <v>264</v>
       </c>
       <c r="G132" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H132" s="135"/>
+      <c r="H132" s="144"/>
     </row>
     <row r="133" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B133" s="71" t="s">
@@ -6863,14 +6863,14 @@
       <c r="D133" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E133" s="147"/>
+      <c r="E133" s="137"/>
       <c r="F133" s="73" t="s">
         <v>265</v>
       </c>
       <c r="G133" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="H133" s="137"/>
+      <c r="H133" s="145"/>
     </row>
     <row r="134" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B134" s="75" t="s">
@@ -6882,7 +6882,7 @@
       <c r="D134" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E134" s="148">
+      <c r="E134" s="139">
         <v>143</v>
       </c>
       <c r="F134" s="28" t="s">
@@ -6891,8 +6891,8 @@
       <c r="G134" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H134" s="134" t="s">
-        <v>398</v>
+      <c r="H134" s="143" t="s">
+        <v>397</v>
       </c>
       <c r="I134" s="29"/>
       <c r="J134" s="29"/>
@@ -6909,14 +6909,14 @@
       <c r="D135" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E135" s="146"/>
+      <c r="E135" s="135"/>
       <c r="F135" s="15" t="s">
         <v>267</v>
       </c>
       <c r="G135" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H135" s="135"/>
+      <c r="H135" s="144"/>
       <c r="I135" s="29"/>
       <c r="J135" s="29"/>
       <c r="K135" s="29"/>
@@ -6932,14 +6932,14 @@
       <c r="D136" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E136" s="146"/>
+      <c r="E136" s="135"/>
       <c r="F136" s="15" t="s">
         <v>268</v>
       </c>
       <c r="G136" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H136" s="135"/>
+      <c r="H136" s="144"/>
       <c r="I136" s="29"/>
       <c r="J136" s="29"/>
       <c r="K136" s="29"/>
@@ -6955,14 +6955,14 @@
       <c r="D137" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E137" s="146"/>
+      <c r="E137" s="135"/>
       <c r="F137" s="15" t="s">
         <v>269</v>
       </c>
       <c r="G137" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H137" s="135"/>
+      <c r="H137" s="144"/>
       <c r="I137" s="29"/>
       <c r="J137" s="29"/>
       <c r="K137" s="29"/>
@@ -6978,14 +6978,14 @@
       <c r="D138" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E138" s="146"/>
+      <c r="E138" s="135"/>
       <c r="F138" s="15" t="s">
         <v>270</v>
       </c>
       <c r="G138" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H138" s="135"/>
+      <c r="H138" s="144"/>
       <c r="I138" s="29"/>
       <c r="J138" s="29"/>
       <c r="K138" s="29"/>
@@ -7001,14 +7001,14 @@
       <c r="D139" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E139" s="149"/>
+      <c r="E139" s="136"/>
       <c r="F139" s="19" t="s">
         <v>271</v>
       </c>
       <c r="G139" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="H139" s="137"/>
+      <c r="H139" s="145"/>
       <c r="I139" s="29"/>
       <c r="J139" s="29"/>
       <c r="K139" s="29"/>
@@ -7024,7 +7024,7 @@
       <c r="D140" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E140" s="145">
+      <c r="E140" s="134">
         <v>143</v>
       </c>
       <c r="F140" s="31" t="s">
@@ -7033,8 +7033,8 @@
       <c r="G140" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="H140" s="134" t="s">
-        <v>399</v>
+      <c r="H140" s="143" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="141" spans="2:12" ht="15.75" customHeight="1">
@@ -7047,14 +7047,14 @@
       <c r="D141" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E141" s="146"/>
+      <c r="E141" s="135"/>
       <c r="F141" s="15" t="s">
         <v>267</v>
       </c>
       <c r="G141" s="77" t="s">
         <v>90</v>
       </c>
-      <c r="H141" s="135"/>
+      <c r="H141" s="144"/>
     </row>
     <row r="142" spans="2:12" ht="15.75" customHeight="1">
       <c r="B142" s="44" t="s">
@@ -7066,14 +7066,14 @@
       <c r="D142" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E142" s="146"/>
+      <c r="E142" s="135"/>
       <c r="F142" s="15" t="s">
         <v>268</v>
       </c>
       <c r="G142" s="78" t="s">
         <v>91</v>
       </c>
-      <c r="H142" s="135"/>
+      <c r="H142" s="144"/>
     </row>
     <row r="143" spans="2:12" ht="15.75" customHeight="1">
       <c r="B143" s="44" t="s">
@@ -7085,14 +7085,14 @@
       <c r="D143" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E143" s="146"/>
+      <c r="E143" s="135"/>
       <c r="F143" s="15" t="s">
         <v>269</v>
       </c>
       <c r="G143" s="77" t="s">
         <v>90</v>
       </c>
-      <c r="H143" s="135"/>
+      <c r="H143" s="144"/>
     </row>
     <row r="144" spans="2:12" ht="15.75" customHeight="1">
       <c r="B144" s="44" t="s">
@@ -7104,14 +7104,14 @@
       <c r="D144" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E144" s="146"/>
+      <c r="E144" s="135"/>
       <c r="F144" s="15" t="s">
         <v>270</v>
       </c>
       <c r="G144" s="77" t="s">
         <v>90</v>
       </c>
-      <c r="H144" s="135"/>
+      <c r="H144" s="144"/>
     </row>
     <row r="145" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B145" s="64" t="s">
@@ -7123,14 +7123,14 @@
       <c r="D145" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E145" s="149"/>
+      <c r="E145" s="136"/>
       <c r="F145" s="19" t="s">
         <v>271</v>
       </c>
       <c r="G145" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="H145" s="137"/>
+      <c r="H145" s="145"/>
     </row>
     <row r="146" spans="1:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B146" s="112" t="s">
@@ -7142,7 +7142,7 @@
       <c r="D146" s="79" t="s">
         <v>316</v>
       </c>
-      <c r="E146" s="145">
+      <c r="E146" s="134">
         <v>143</v>
       </c>
       <c r="F146" s="47" t="s">
@@ -7151,8 +7151,8 @@
       <c r="G146" s="48" t="s">
         <v>317</v>
       </c>
-      <c r="H146" s="141" t="s">
-        <v>403</v>
+      <c r="H146" s="146" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="147" spans="1:12" ht="15.75" customHeight="1">
@@ -7165,14 +7165,14 @@
       <c r="D147" s="80" t="s">
         <v>94</v>
       </c>
-      <c r="E147" s="146"/>
+      <c r="E147" s="135"/>
       <c r="F147" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G147" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H147" s="139"/>
+      <c r="H147" s="147"/>
     </row>
     <row r="148" spans="1:12" ht="15.75" customHeight="1">
       <c r="B148" s="44" t="s">
@@ -7184,14 +7184,14 @@
       <c r="D148" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="E148" s="146"/>
+      <c r="E148" s="135"/>
       <c r="F148" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G148" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H148" s="139"/>
+      <c r="H148" s="147"/>
     </row>
     <row r="149" spans="1:12" ht="15.75" customHeight="1">
       <c r="B149" s="44" t="s">
@@ -7203,14 +7203,14 @@
       <c r="D149" s="80" t="s">
         <v>94</v>
       </c>
-      <c r="E149" s="146"/>
+      <c r="E149" s="135"/>
       <c r="F149" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G149" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H149" s="139"/>
+      <c r="H149" s="147"/>
     </row>
     <row r="150" spans="1:12" ht="15.75" customHeight="1">
       <c r="B150" s="44" t="s">
@@ -7222,14 +7222,14 @@
       <c r="D150" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="E150" s="146"/>
+      <c r="E150" s="135"/>
       <c r="F150" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G150" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H150" s="139"/>
+      <c r="H150" s="147"/>
     </row>
     <row r="151" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B151" s="64" t="s">
@@ -7241,14 +7241,14 @@
       <c r="D151" s="81" t="s">
         <v>94</v>
       </c>
-      <c r="E151" s="149"/>
+      <c r="E151" s="136"/>
       <c r="F151" s="53" t="s">
         <v>63</v>
       </c>
       <c r="G151" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="H151" s="140"/>
+      <c r="H151" s="148"/>
     </row>
     <row r="152" spans="1:12" ht="13.5" thickTop="1">
       <c r="A152" s="111"/>
@@ -7261,7 +7261,7 @@
       <c r="D152" s="109" t="s">
         <v>374</v>
       </c>
-      <c r="E152" s="145">
+      <c r="E152" s="134">
         <v>143</v>
       </c>
       <c r="F152" s="47" t="s">
@@ -7270,8 +7270,8 @@
       <c r="G152" s="114" t="s">
         <v>370</v>
       </c>
-      <c r="H152" s="141" t="s">
-        <v>403</v>
+      <c r="H152" s="146" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="153" spans="1:12" ht="15.75" customHeight="1">
@@ -7284,12 +7284,12 @@
       <c r="D153" s="109" t="s">
         <v>367</v>
       </c>
-      <c r="E153" s="146"/>
+      <c r="E153" s="135"/>
       <c r="F153" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G153" s="12"/>
-      <c r="H153" s="139"/>
+      <c r="H153" s="147"/>
     </row>
     <row r="154" spans="1:12" ht="15.75" customHeight="1">
       <c r="B154" s="113" t="s">
@@ -7301,14 +7301,14 @@
       <c r="D154" s="109" t="s">
         <v>369</v>
       </c>
-      <c r="E154" s="146"/>
+      <c r="E154" s="135"/>
       <c r="F154" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G154" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H154" s="139"/>
+      <c r="H154" s="147"/>
     </row>
     <row r="155" spans="1:12" ht="15.75" customHeight="1">
       <c r="B155" s="113" t="s">
@@ -7320,12 +7320,12 @@
       <c r="D155" s="109" t="s">
         <v>367</v>
       </c>
-      <c r="E155" s="146"/>
+      <c r="E155" s="135"/>
       <c r="F155" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G155" s="12"/>
-      <c r="H155" s="139"/>
+      <c r="H155" s="147"/>
     </row>
     <row r="156" spans="1:12" ht="15.75" customHeight="1">
       <c r="B156" s="113" t="s">
@@ -7337,12 +7337,12 @@
       <c r="D156" s="109" t="s">
         <v>369</v>
       </c>
-      <c r="E156" s="146"/>
+      <c r="E156" s="135"/>
       <c r="F156" s="50" t="s">
         <v>63</v>
       </c>
       <c r="G156" s="12"/>
-      <c r="H156" s="139"/>
+      <c r="H156" s="147"/>
     </row>
     <row r="157" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B157" s="116" t="s">
@@ -7354,18 +7354,18 @@
       <c r="D157" s="109" t="s">
         <v>367</v>
       </c>
-      <c r="E157" s="149"/>
+      <c r="E157" s="136"/>
       <c r="F157" s="53" t="s">
         <v>63</v>
       </c>
       <c r="G157" s="115" t="s">
         <v>45</v>
       </c>
-      <c r="H157" s="140"/>
+      <c r="H157" s="148"/>
     </row>
     <row r="158" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B158" s="82" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C158" s="22">
         <v>580</v>
@@ -7373,7 +7373,7 @@
       <c r="D158" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E158" s="145">
+      <c r="E158" s="134">
         <v>167</v>
       </c>
       <c r="F158" s="31" t="s">
@@ -7382,8 +7382,8 @@
       <c r="G158" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H158" s="134" t="s">
-        <v>399</v>
+      <c r="H158" s="143" t="s">
+        <v>398</v>
       </c>
       <c r="I158" s="29"/>
       <c r="J158" s="29"/>
@@ -7400,14 +7400,14 @@
       <c r="D159" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E159" s="146"/>
+      <c r="E159" s="135"/>
       <c r="F159" s="15" t="s">
         <v>267</v>
       </c>
       <c r="G159" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H159" s="135"/>
+      <c r="H159" s="144"/>
       <c r="I159" s="29"/>
       <c r="J159" s="29"/>
       <c r="K159" s="29"/>
@@ -7423,14 +7423,14 @@
       <c r="D160" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E160" s="146"/>
+      <c r="E160" s="135"/>
       <c r="F160" s="15" t="s">
         <v>272</v>
       </c>
       <c r="G160" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H160" s="135"/>
+      <c r="H160" s="144"/>
       <c r="I160" s="29"/>
       <c r="J160" s="29"/>
       <c r="K160" s="29"/>
@@ -7446,14 +7446,14 @@
       <c r="D161" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E161" s="146"/>
+      <c r="E161" s="135"/>
       <c r="F161" s="15" t="s">
         <v>273</v>
       </c>
       <c r="G161" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H161" s="135"/>
+      <c r="H161" s="144"/>
       <c r="I161" s="29"/>
       <c r="J161" s="29"/>
       <c r="K161" s="29"/>
@@ -7469,14 +7469,14 @@
       <c r="D162" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E162" s="146"/>
+      <c r="E162" s="135"/>
       <c r="F162" s="15" t="s">
         <v>274</v>
       </c>
       <c r="G162" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H162" s="135"/>
+      <c r="H162" s="144"/>
       <c r="I162" s="29"/>
       <c r="J162" s="29"/>
       <c r="K162" s="29"/>
@@ -7492,14 +7492,14 @@
       <c r="D163" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E163" s="149"/>
+      <c r="E163" s="136"/>
       <c r="F163" s="19" t="s">
         <v>275</v>
       </c>
       <c r="G163" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="H163" s="137"/>
+      <c r="H163" s="145"/>
       <c r="I163" s="29"/>
       <c r="J163" s="29"/>
       <c r="K163" s="29"/>
@@ -7515,7 +7515,7 @@
       <c r="D164" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E164" s="145">
+      <c r="E164" s="134">
         <v>125</v>
       </c>
       <c r="F164" s="58" t="s">
@@ -7524,8 +7524,8 @@
       <c r="G164" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="H164" s="134" t="s">
-        <v>399</v>
+      <c r="H164" s="143" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="165" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
@@ -7538,14 +7538,14 @@
       <c r="D165" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E165" s="146"/>
+      <c r="E165" s="135"/>
       <c r="F165" s="56" t="s">
         <v>190</v>
       </c>
       <c r="G165" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H165" s="135"/>
+      <c r="H165" s="144"/>
     </row>
     <row r="166" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B166" s="38" t="s">
@@ -7557,14 +7557,14 @@
       <c r="D166" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E166" s="146"/>
+      <c r="E166" s="135"/>
       <c r="F166" s="56" t="s">
         <v>191</v>
       </c>
       <c r="G166" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H166" s="135"/>
+      <c r="H166" s="144"/>
     </row>
     <row r="167" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B167" s="38" t="s">
@@ -7576,14 +7576,14 @@
       <c r="D167" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E167" s="146"/>
+      <c r="E167" s="135"/>
       <c r="F167" s="56" t="s">
         <v>192</v>
       </c>
       <c r="G167" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H167" s="135"/>
+      <c r="H167" s="144"/>
     </row>
     <row r="168" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B168" s="87" t="s">
@@ -7595,14 +7595,14 @@
       <c r="D168" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E168" s="146"/>
+      <c r="E168" s="135"/>
       <c r="F168" s="56" t="s">
         <v>193</v>
       </c>
       <c r="G168" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H168" s="135"/>
+      <c r="H168" s="144"/>
     </row>
     <row r="169" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B169" s="51" t="s">
@@ -7614,18 +7614,18 @@
       <c r="D169" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E169" s="149"/>
+      <c r="E169" s="136"/>
       <c r="F169" s="57" t="s">
         <v>194</v>
       </c>
       <c r="G169" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="H169" s="137"/>
+      <c r="H169" s="145"/>
     </row>
     <row r="170" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B170" s="40" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C170" s="9">
         <v>580</v>
@@ -7633,7 +7633,7 @@
       <c r="D170" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E170" s="150">
+      <c r="E170" s="138">
         <v>200</v>
       </c>
       <c r="F170" s="50" t="s">
@@ -7642,8 +7642,8 @@
       <c r="G170" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H170" s="134" t="s">
-        <v>404</v>
+      <c r="H170" s="143" t="s">
+        <v>403</v>
       </c>
       <c r="I170" s="29"/>
       <c r="J170" s="29"/>
@@ -7660,14 +7660,14 @@
       <c r="D171" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E171" s="146"/>
+      <c r="E171" s="135"/>
       <c r="F171" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G171" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="H171" s="135"/>
+      <c r="H171" s="144"/>
       <c r="I171" s="29"/>
       <c r="J171" s="29"/>
       <c r="K171" s="29"/>
@@ -7683,14 +7683,14 @@
       <c r="D172" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E172" s="146"/>
+      <c r="E172" s="135"/>
       <c r="F172" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G172" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="H172" s="135"/>
+      <c r="H172" s="144"/>
       <c r="I172" s="29"/>
       <c r="J172" s="29"/>
       <c r="K172" s="29"/>
@@ -7706,14 +7706,14 @@
       <c r="D173" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E173" s="146"/>
+      <c r="E173" s="135"/>
       <c r="F173" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G173" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="H173" s="135"/>
+      <c r="H173" s="144"/>
       <c r="I173" s="29"/>
       <c r="J173" s="29"/>
       <c r="K173" s="29"/>
@@ -7729,14 +7729,14 @@
       <c r="D174" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E174" s="146"/>
+      <c r="E174" s="135"/>
       <c r="F174" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G174" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="H174" s="135"/>
+      <c r="H174" s="144"/>
       <c r="I174" s="29"/>
       <c r="J174" s="29"/>
       <c r="K174" s="29"/>
@@ -7752,14 +7752,14 @@
       <c r="D175" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E175" s="147"/>
+      <c r="E175" s="137"/>
       <c r="F175" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G175" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="H175" s="137"/>
+      <c r="H175" s="145"/>
       <c r="I175" s="29"/>
       <c r="J175" s="29"/>
       <c r="K175" s="29"/>
@@ -7775,7 +7775,7 @@
       <c r="D176" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E176" s="145">
+      <c r="E176" s="134">
         <v>125</v>
       </c>
       <c r="F176" s="58" t="s">
@@ -7784,8 +7784,8 @@
       <c r="G176" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="H176" s="134" t="s">
-        <v>399</v>
+      <c r="H176" s="143" t="s">
+        <v>398</v>
       </c>
       <c r="I176" s="29"/>
       <c r="J176" s="29"/>
@@ -7802,14 +7802,14 @@
       <c r="D177" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E177" s="146"/>
+      <c r="E177" s="135"/>
       <c r="F177" s="56" t="s">
         <v>277</v>
       </c>
       <c r="G177" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="H177" s="135"/>
+      <c r="H177" s="144"/>
       <c r="I177" s="29"/>
       <c r="J177" s="29"/>
       <c r="K177" s="29"/>
@@ -7825,14 +7825,14 @@
       <c r="D178" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E178" s="146"/>
+      <c r="E178" s="135"/>
       <c r="F178" s="56" t="s">
         <v>278</v>
       </c>
       <c r="G178" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="H178" s="135"/>
+      <c r="H178" s="144"/>
       <c r="I178" s="29"/>
       <c r="J178" s="29"/>
       <c r="K178" s="29"/>
@@ -7848,14 +7848,14 @@
       <c r="D179" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E179" s="146"/>
+      <c r="E179" s="135"/>
       <c r="F179" s="56" t="s">
         <v>279</v>
       </c>
       <c r="G179" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="H179" s="135"/>
+      <c r="H179" s="144"/>
       <c r="I179" s="29"/>
       <c r="J179" s="29"/>
       <c r="K179" s="29"/>
@@ -7871,14 +7871,14 @@
       <c r="D180" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E180" s="146"/>
+      <c r="E180" s="135"/>
       <c r="F180" s="56" t="s">
         <v>280</v>
       </c>
       <c r="G180" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="H180" s="135"/>
+      <c r="H180" s="144"/>
       <c r="I180" s="29"/>
       <c r="J180" s="29"/>
       <c r="K180" s="29"/>
@@ -7894,14 +7894,14 @@
       <c r="D181" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E181" s="149"/>
+      <c r="E181" s="136"/>
       <c r="F181" s="88" t="s">
         <v>281</v>
       </c>
       <c r="G181" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="H181" s="137"/>
+      <c r="H181" s="145"/>
       <c r="I181" s="29"/>
       <c r="J181" s="29"/>
       <c r="K181" s="29"/>
@@ -7917,7 +7917,7 @@
       <c r="D182" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E182" s="148">
+      <c r="E182" s="139">
         <v>167</v>
       </c>
       <c r="F182" s="28" t="s">
@@ -7926,8 +7926,8 @@
       <c r="G182" s="54" t="s">
         <v>319</v>
       </c>
-      <c r="H182" s="134" t="s">
-        <v>398</v>
+      <c r="H182" s="143" t="s">
+        <v>397</v>
       </c>
       <c r="I182" s="29"/>
       <c r="J182" s="29"/>
@@ -7944,14 +7944,14 @@
       <c r="D183" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E183" s="146"/>
+      <c r="E183" s="135"/>
       <c r="F183" s="15" t="s">
         <v>305</v>
       </c>
       <c r="G183" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H183" s="135"/>
+      <c r="H183" s="144"/>
       <c r="I183" s="29"/>
       <c r="J183" s="29"/>
       <c r="K183" s="29"/>
@@ -7967,14 +7967,14 @@
       <c r="D184" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E184" s="146"/>
+      <c r="E184" s="135"/>
       <c r="F184" s="15" t="s">
         <v>306</v>
       </c>
       <c r="G184" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H184" s="135"/>
+      <c r="H184" s="144"/>
     </row>
     <row r="185" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B185" s="42" t="s">
@@ -7986,14 +7986,14 @@
       <c r="D185" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E185" s="146"/>
+      <c r="E185" s="135"/>
       <c r="F185" s="15" t="s">
         <v>307</v>
       </c>
       <c r="G185" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H185" s="135"/>
+      <c r="H185" s="144"/>
     </row>
     <row r="186" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B186" s="44" t="s">
@@ -8005,14 +8005,14 @@
       <c r="D186" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E186" s="146"/>
+      <c r="E186" s="135"/>
       <c r="F186" s="15" t="s">
         <v>306</v>
       </c>
       <c r="G186" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H186" s="135"/>
+      <c r="H186" s="144"/>
       <c r="I186" s="29"/>
       <c r="J186" s="29"/>
       <c r="K186" s="29"/>
@@ -8028,14 +8028,14 @@
       <c r="D187" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E187" s="149"/>
+      <c r="E187" s="136"/>
       <c r="F187" s="19" t="s">
         <v>308</v>
       </c>
       <c r="G187" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="H187" s="136"/>
+      <c r="H187" s="149"/>
       <c r="I187" s="29"/>
       <c r="J187" s="29"/>
       <c r="K187" s="29"/>
@@ -8051,7 +8051,7 @@
       <c r="D188" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E188" s="145">
+      <c r="E188" s="134">
         <v>167</v>
       </c>
       <c r="F188" s="50" t="s">
@@ -8060,8 +8060,8 @@
       <c r="G188" s="54" t="s">
         <v>314</v>
       </c>
-      <c r="H188" s="134" t="s">
-        <v>411</v>
+      <c r="H188" s="143" t="s">
+        <v>410</v>
       </c>
       <c r="I188" s="29"/>
       <c r="J188" s="29"/>
@@ -8078,14 +8078,14 @@
       <c r="D189" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E189" s="146"/>
+      <c r="E189" s="135"/>
       <c r="F189" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G189" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H189" s="135"/>
+      <c r="H189" s="144"/>
       <c r="I189" s="29"/>
       <c r="J189" s="29"/>
       <c r="K189" s="29"/>
@@ -8101,14 +8101,14 @@
       <c r="D190" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E190" s="146"/>
+      <c r="E190" s="135"/>
       <c r="F190" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G190" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H190" s="135"/>
+      <c r="H190" s="144"/>
       <c r="I190" s="29"/>
       <c r="J190" s="29"/>
       <c r="K190" s="29"/>
@@ -8124,14 +8124,14 @@
       <c r="D191" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E191" s="146"/>
+      <c r="E191" s="135"/>
       <c r="F191" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G191" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H191" s="135"/>
+      <c r="H191" s="144"/>
       <c r="I191" s="29"/>
       <c r="J191" s="29"/>
       <c r="K191" s="29"/>
@@ -8147,14 +8147,14 @@
       <c r="D192" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E192" s="146"/>
+      <c r="E192" s="135"/>
       <c r="F192" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G192" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H192" s="135"/>
+      <c r="H192" s="144"/>
       <c r="I192" s="29"/>
       <c r="J192" s="29"/>
       <c r="K192" s="29"/>
@@ -8170,14 +8170,14 @@
       <c r="D193" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E193" s="147"/>
+      <c r="E193" s="137"/>
       <c r="F193" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G193" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="H193" s="136"/>
+      <c r="H193" s="149"/>
       <c r="I193" s="29"/>
       <c r="J193" s="29"/>
       <c r="K193" s="29"/>
@@ -8185,7 +8185,7 @@
     </row>
     <row r="194" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B194" s="36" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C194" s="22">
         <v>810</v>
@@ -8193,7 +8193,7 @@
       <c r="D194" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E194" s="145">
+      <c r="E194" s="134">
         <v>143</v>
       </c>
       <c r="F194" s="72" t="s">
@@ -8202,8 +8202,8 @@
       <c r="G194" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="H194" s="151" t="s">
-        <v>434</v>
+      <c r="H194" s="150" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="195" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
@@ -8216,14 +8216,14 @@
       <c r="D195" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E195" s="146"/>
+      <c r="E195" s="135"/>
       <c r="F195" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G195" s="54" t="s">
         <v>119</v>
       </c>
-      <c r="H195" s="135"/>
+      <c r="H195" s="144"/>
     </row>
     <row r="196" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B196" s="38" t="s">
@@ -8235,14 +8235,14 @@
       <c r="D196" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E196" s="146"/>
+      <c r="E196" s="135"/>
       <c r="F196" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G196" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H196" s="135"/>
+      <c r="H196" s="144"/>
     </row>
     <row r="197" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B197" s="38" t="s">
@@ -8254,14 +8254,14 @@
       <c r="D197" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E197" s="146"/>
+      <c r="E197" s="135"/>
       <c r="F197" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G197" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H197" s="135"/>
+      <c r="H197" s="144"/>
     </row>
     <row r="198" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B198" s="38" t="s">
@@ -8273,14 +8273,14 @@
       <c r="D198" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="E198" s="146"/>
+      <c r="E198" s="135"/>
       <c r="F198" s="50" t="s">
         <v>7</v>
       </c>
       <c r="G198" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H198" s="135"/>
+      <c r="H198" s="144"/>
     </row>
     <row r="199" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B199" s="39" t="s">
@@ -8292,14 +8292,14 @@
       <c r="D199" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E199" s="147"/>
+      <c r="E199" s="137"/>
       <c r="F199" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G199" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="H199" s="137"/>
+      <c r="H199" s="145"/>
     </row>
     <row r="200" spans="2:12" ht="15.75" customHeight="1" thickTop="1">
       <c r="B200" s="68" t="s">
@@ -8311,15 +8311,15 @@
       <c r="D200" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E200" s="145">
+      <c r="E200" s="134">
         <v>233</v>
       </c>
       <c r="F200" s="72"/>
       <c r="G200" s="48" t="s">
         <v>327</v>
       </c>
-      <c r="H200" s="138" t="s">
-        <v>401</v>
+      <c r="H200" s="151" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="201" spans="2:12" ht="15.75" customHeight="1">
@@ -8332,10 +8332,10 @@
       <c r="D201" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E201" s="146"/>
+      <c r="E201" s="135"/>
       <c r="F201" s="50"/>
       <c r="G201" s="12"/>
-      <c r="H201" s="139"/>
+      <c r="H201" s="147"/>
     </row>
     <row r="202" spans="2:12" ht="15.75" customHeight="1">
       <c r="B202" s="70" t="s">
@@ -8347,12 +8347,12 @@
       <c r="D202" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E202" s="146"/>
+      <c r="E202" s="135"/>
       <c r="F202" s="50"/>
       <c r="G202" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="H202" s="139"/>
+      <c r="H202" s="147"/>
     </row>
     <row r="203" spans="2:12" ht="15.75" customHeight="1">
       <c r="B203" s="70" t="s">
@@ -8364,12 +8364,12 @@
       <c r="D203" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E203" s="146"/>
+      <c r="E203" s="135"/>
       <c r="F203" s="50"/>
       <c r="G203" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H203" s="139"/>
+      <c r="H203" s="147"/>
     </row>
     <row r="204" spans="2:12" ht="15.75" customHeight="1">
       <c r="B204" s="70" t="s">
@@ -8381,12 +8381,12 @@
       <c r="D204" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E204" s="146"/>
+      <c r="E204" s="135"/>
       <c r="F204" s="50"/>
       <c r="G204" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H204" s="139"/>
+      <c r="H204" s="147"/>
     </row>
     <row r="205" spans="2:12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B205" s="71" t="s">
@@ -8398,12 +8398,12 @@
       <c r="D205" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E205" s="147"/>
+      <c r="E205" s="137"/>
       <c r="F205" s="89"/>
       <c r="G205" s="90" t="s">
         <v>115</v>
       </c>
-      <c r="H205" s="140"/>
+      <c r="H205" s="148"/>
     </row>
     <row r="206" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B206" s="117" t="s">
@@ -8415,17 +8415,17 @@
       <c r="D206" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E206" s="145">
+      <c r="E206" s="134">
         <v>167</v>
       </c>
       <c r="F206" s="127" t="s">
-        <v>384</v>
-      </c>
-      <c r="G206" s="114" t="s">
-        <v>377</v>
-      </c>
-      <c r="H206" s="134" t="s">
-        <v>399</v>
+        <v>383</v>
+      </c>
+      <c r="G206" s="48" t="s">
+        <v>434</v>
+      </c>
+      <c r="H206" s="143" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="207" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
@@ -8438,18 +8438,18 @@
       <c r="D207" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E207" s="146"/>
+      <c r="E207" s="135"/>
       <c r="F207" s="127" t="s">
         <v>305</v>
       </c>
       <c r="G207" s="119" t="s">
-        <v>379</v>
-      </c>
-      <c r="H207" s="135"/>
+        <v>378</v>
+      </c>
+      <c r="H207" s="144"/>
     </row>
     <row r="208" spans="2:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B208" s="125" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C208" s="14">
         <v>300</v>
@@ -8457,18 +8457,18 @@
       <c r="D208" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E208" s="146"/>
+      <c r="E208" s="135"/>
       <c r="F208" s="127" t="s">
         <v>306</v>
       </c>
       <c r="G208" s="120" t="s">
-        <v>378</v>
-      </c>
-      <c r="H208" s="135"/>
+        <v>377</v>
+      </c>
+      <c r="H208" s="144"/>
     </row>
     <row r="209" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B209" s="125" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C209" s="14">
         <v>180</v>
@@ -8476,18 +8476,18 @@
       <c r="D209" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E209" s="146"/>
+      <c r="E209" s="135"/>
       <c r="F209" s="127" t="s">
         <v>307</v>
       </c>
       <c r="G209" s="119" t="s">
-        <v>379</v>
-      </c>
-      <c r="H209" s="135"/>
+        <v>378</v>
+      </c>
+      <c r="H209" s="144"/>
     </row>
     <row r="210" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B210" s="125" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C210" s="14">
         <v>290</v>
@@ -8495,18 +8495,18 @@
       <c r="D210" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E210" s="146"/>
+      <c r="E210" s="135"/>
       <c r="F210" s="127" t="s">
         <v>306</v>
       </c>
       <c r="G210" s="122" t="s">
-        <v>379</v>
-      </c>
-      <c r="H210" s="135"/>
+        <v>378</v>
+      </c>
+      <c r="H210" s="144"/>
     </row>
     <row r="211" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B211" s="126" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C211" s="24">
         <v>140</v>
@@ -8514,18 +8514,18 @@
       <c r="D211" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E211" s="147"/>
+      <c r="E211" s="137"/>
       <c r="F211" s="127" t="s">
         <v>308</v>
       </c>
       <c r="G211" s="121" t="s">
-        <v>379</v>
-      </c>
-      <c r="H211" s="137"/>
+        <v>378</v>
+      </c>
+      <c r="H211" s="145"/>
     </row>
     <row r="212" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B212" s="117" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C212" s="22">
         <v>1110</v>
@@ -8533,22 +8533,22 @@
       <c r="D212" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="E212" s="142">
+      <c r="E212" s="140">
         <v>167</v>
       </c>
       <c r="F212" s="127" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G212" s="114" t="s">
-        <v>386</v>
-      </c>
-      <c r="H212" s="134" t="s">
-        <v>399</v>
+        <v>385</v>
+      </c>
+      <c r="H212" s="143" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="213" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B213" s="74" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C213" s="14">
         <v>200</v>
@@ -8556,18 +8556,18 @@
       <c r="D213" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E213" s="143"/>
+      <c r="E213" s="141"/>
       <c r="F213" s="127" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G213" s="118" t="s">
-        <v>388</v>
-      </c>
-      <c r="H213" s="135"/>
+        <v>387</v>
+      </c>
+      <c r="H213" s="144"/>
     </row>
     <row r="214" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B214" s="125" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C214" s="14">
         <v>300</v>
@@ -8575,18 +8575,18 @@
       <c r="D214" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E214" s="143"/>
+      <c r="E214" s="141"/>
       <c r="F214" s="127" t="s">
         <v>306</v>
       </c>
       <c r="G214" s="118" t="s">
-        <v>390</v>
-      </c>
-      <c r="H214" s="135"/>
+        <v>389</v>
+      </c>
+      <c r="H214" s="144"/>
     </row>
     <row r="215" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B215" s="125" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C215" s="14">
         <v>180</v>
@@ -8594,18 +8594,18 @@
       <c r="D215" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E215" s="143"/>
+      <c r="E215" s="141"/>
       <c r="F215" s="127" t="s">
         <v>307</v>
       </c>
       <c r="G215" s="118" t="s">
-        <v>388</v>
-      </c>
-      <c r="H215" s="135"/>
+        <v>387</v>
+      </c>
+      <c r="H215" s="144"/>
     </row>
     <row r="216" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B216" s="125" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C216" s="14">
         <v>290</v>
@@ -8613,18 +8613,18 @@
       <c r="D216" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E216" s="143"/>
+      <c r="E216" s="141"/>
       <c r="F216" s="127" t="s">
         <v>306</v>
       </c>
       <c r="G216" s="118" t="s">
-        <v>388</v>
-      </c>
-      <c r="H216" s="135"/>
+        <v>387</v>
+      </c>
+      <c r="H216" s="144"/>
     </row>
     <row r="217" spans="2:8" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B217" s="126" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C217" s="123">
         <v>140</v>
@@ -8632,14 +8632,14 @@
       <c r="D217" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="E217" s="144"/>
+      <c r="E217" s="142"/>
       <c r="F217" s="127" t="s">
         <v>308</v>
       </c>
       <c r="G217" s="119" t="s">
-        <v>391</v>
-      </c>
-      <c r="H217" s="137"/>
+        <v>390</v>
+      </c>
+      <c r="H217" s="145"/>
     </row>
     <row r="218" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
       <c r="B218" s="91" t="s">
@@ -8661,7 +8661,7 @@
         <v>17</v>
       </c>
       <c r="H218" s="128" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="219" spans="2:8" ht="15.75" customHeight="1">
@@ -8684,7 +8684,7 @@
         <v>7</v>
       </c>
       <c r="H219" s="128" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="220" spans="2:8" ht="15.75" customHeight="1">
@@ -8707,7 +8707,7 @@
         <v>7</v>
       </c>
       <c r="H220" s="129" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="221" spans="2:8" ht="15.75" customHeight="1">
@@ -8730,7 +8730,7 @@
         <v>7</v>
       </c>
       <c r="H221" s="128" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="222" spans="2:8" ht="15.75" customHeight="1">
@@ -8753,7 +8753,7 @@
         <v>7</v>
       </c>
       <c r="H222" s="128" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="223" spans="2:8" ht="15.75" customHeight="1">
@@ -8776,7 +8776,7 @@
         <v>126</v>
       </c>
       <c r="H223" s="130" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="224" spans="2:8" ht="15.75" customHeight="1">
@@ -8799,7 +8799,7 @@
         <v>7</v>
       </c>
       <c r="H224" s="128" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="225" spans="2:8" ht="15.75" customHeight="1">
@@ -8822,7 +8822,7 @@
         <v>7</v>
       </c>
       <c r="H225" s="128" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="226" spans="2:8" ht="15.75" customHeight="1">
@@ -8845,7 +8845,7 @@
         <v>7</v>
       </c>
       <c r="H226" s="128" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="227" spans="2:8" ht="15.75" customHeight="1">
@@ -8868,7 +8868,7 @@
         <v>7</v>
       </c>
       <c r="H227" s="128" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="228" spans="2:8" ht="15.75" customHeight="1">
@@ -8891,7 +8891,7 @@
         <v>44</v>
       </c>
       <c r="H228" s="128" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="229" spans="2:8" ht="15.75" customHeight="1">
@@ -8914,12 +8914,12 @@
         <v>7</v>
       </c>
       <c r="H229" s="129" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="230" spans="2:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="B230" s="131" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C230" s="24">
         <v>200</v>
@@ -8937,7 +8937,7 @@
         <v>134</v>
       </c>
       <c r="H230" s="132" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="231" spans="2:8" ht="15.75" customHeight="1" thickTop="1">
@@ -13804,38 +13804,30 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="72">
-    <mergeCell ref="E140:E145"/>
-    <mergeCell ref="E146:E151"/>
-    <mergeCell ref="E158:E163"/>
-    <mergeCell ref="E194:E199"/>
-    <mergeCell ref="E200:E205"/>
-    <mergeCell ref="E164:E169"/>
-    <mergeCell ref="E170:E175"/>
-    <mergeCell ref="E176:E181"/>
-    <mergeCell ref="E182:E187"/>
-    <mergeCell ref="E188:E193"/>
-    <mergeCell ref="E152:E157"/>
-    <mergeCell ref="E92:E97"/>
-    <mergeCell ref="E98:E103"/>
-    <mergeCell ref="E104:E109"/>
-    <mergeCell ref="E116:E121"/>
-    <mergeCell ref="E122:E127"/>
-    <mergeCell ref="E110:E115"/>
-    <mergeCell ref="E62:E67"/>
-    <mergeCell ref="E68:E73"/>
-    <mergeCell ref="E74:E79"/>
-    <mergeCell ref="E80:E85"/>
-    <mergeCell ref="E86:E91"/>
-    <mergeCell ref="E32:E37"/>
-    <mergeCell ref="E38:E43"/>
-    <mergeCell ref="E44:E49"/>
-    <mergeCell ref="E50:E55"/>
-    <mergeCell ref="E56:E61"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="E8:E13"/>
-    <mergeCell ref="E14:E19"/>
-    <mergeCell ref="E20:E25"/>
-    <mergeCell ref="E26:E31"/>
+    <mergeCell ref="H188:H193"/>
+    <mergeCell ref="H194:H199"/>
+    <mergeCell ref="H200:H205"/>
+    <mergeCell ref="H206:H211"/>
+    <mergeCell ref="H92:H97"/>
+    <mergeCell ref="H98:H103"/>
+    <mergeCell ref="H104:H109"/>
+    <mergeCell ref="H110:H115"/>
+    <mergeCell ref="H116:H121"/>
+    <mergeCell ref="H62:H67"/>
+    <mergeCell ref="H68:H73"/>
+    <mergeCell ref="H74:H79"/>
+    <mergeCell ref="H80:H85"/>
+    <mergeCell ref="H86:H91"/>
+    <mergeCell ref="H32:H37"/>
+    <mergeCell ref="H38:H43"/>
+    <mergeCell ref="H44:H49"/>
+    <mergeCell ref="H50:H55"/>
+    <mergeCell ref="H56:H61"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="H8:H13"/>
+    <mergeCell ref="H14:H19"/>
+    <mergeCell ref="H20:H25"/>
+    <mergeCell ref="H26:H31"/>
     <mergeCell ref="E212:E217"/>
     <mergeCell ref="E206:E211"/>
     <mergeCell ref="H122:H127"/>
@@ -13852,30 +13844,38 @@
     <mergeCell ref="E134:E139"/>
     <mergeCell ref="H212:H217"/>
     <mergeCell ref="H182:H187"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="H8:H13"/>
-    <mergeCell ref="H14:H19"/>
-    <mergeCell ref="H20:H25"/>
-    <mergeCell ref="H26:H31"/>
-    <mergeCell ref="H32:H37"/>
-    <mergeCell ref="H38:H43"/>
-    <mergeCell ref="H44:H49"/>
-    <mergeCell ref="H50:H55"/>
-    <mergeCell ref="H56:H61"/>
-    <mergeCell ref="H62:H67"/>
-    <mergeCell ref="H68:H73"/>
-    <mergeCell ref="H74:H79"/>
-    <mergeCell ref="H80:H85"/>
-    <mergeCell ref="H86:H91"/>
-    <mergeCell ref="H188:H193"/>
-    <mergeCell ref="H194:H199"/>
-    <mergeCell ref="H200:H205"/>
-    <mergeCell ref="H206:H211"/>
-    <mergeCell ref="H92:H97"/>
-    <mergeCell ref="H98:H103"/>
-    <mergeCell ref="H104:H109"/>
-    <mergeCell ref="H110:H115"/>
-    <mergeCell ref="H116:H121"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="E8:E13"/>
+    <mergeCell ref="E14:E19"/>
+    <mergeCell ref="E20:E25"/>
+    <mergeCell ref="E26:E31"/>
+    <mergeCell ref="E32:E37"/>
+    <mergeCell ref="E38:E43"/>
+    <mergeCell ref="E44:E49"/>
+    <mergeCell ref="E50:E55"/>
+    <mergeCell ref="E56:E61"/>
+    <mergeCell ref="E62:E67"/>
+    <mergeCell ref="E68:E73"/>
+    <mergeCell ref="E74:E79"/>
+    <mergeCell ref="E80:E85"/>
+    <mergeCell ref="E86:E91"/>
+    <mergeCell ref="E92:E97"/>
+    <mergeCell ref="E98:E103"/>
+    <mergeCell ref="E104:E109"/>
+    <mergeCell ref="E116:E121"/>
+    <mergeCell ref="E122:E127"/>
+    <mergeCell ref="E110:E115"/>
+    <mergeCell ref="E140:E145"/>
+    <mergeCell ref="E146:E151"/>
+    <mergeCell ref="E158:E163"/>
+    <mergeCell ref="E194:E199"/>
+    <mergeCell ref="E200:E205"/>
+    <mergeCell ref="E164:E169"/>
+    <mergeCell ref="E170:E175"/>
+    <mergeCell ref="E176:E181"/>
+    <mergeCell ref="E182:E187"/>
+    <mergeCell ref="E188:E193"/>
+    <mergeCell ref="E152:E157"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
